--- a/ТКИ-341_Реверс_Инжиниринг.xlsx
+++ b/ТКИ-341_Реверс_Инжиниринг.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22527"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\flash_a\Documents\GIT\Reverse_Engineering\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C4EFF40-C37B-4BC1-B666-FAA6EE55066E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10500"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,12 +21,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="48">
   <si>
     <t>ВЕДОМОСТЬ ПОСЕЩАЕМОСТИ ЗАНЯТИЙ СТУДЕНТАМИ ГРУППЫ ТКИ "Компьютерная безопасность" ИТТСУ РУТ (МИИТ)</t>
   </si>
@@ -188,19 +189,30 @@
   <si>
     <t>bulaniisergey@mail.ru</t>
   </si>
+  <si>
+    <t>2п</t>
+  </si>
+  <si>
+    <t>1п</t>
+  </si>
+  <si>
+    <t>Энтропия</t>
+  </si>
+  <si>
+    <t>Задача</t>
+  </si>
+  <si>
+    <t>С, С++</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-* #\.##0.00_-;\-* #\.##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-* #\.##0.00\ &quot;₽&quot;_-;\-* #\.##0.00\ &quot;₽&quot;_-;_-* \-??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="180" formatCode="dd\.mm\.yyyy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="168" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -221,353 +233,16 @@
       <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -590,253 +265,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -857,74 +290,39 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Запятая" xfId="1" builtinId="3"/>
-    <cellStyle name="Денежный" xfId="2" builtinId="4"/>
-    <cellStyle name="Процент" xfId="3" builtinId="5"/>
-    <cellStyle name="Запятая [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Денежный [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Гиперссылка" xfId="6" builtinId="8"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="7" builtinId="9"/>
-    <cellStyle name="Примечание" xfId="8" builtinId="10"/>
-    <cellStyle name="Предупреждающий текст" xfId="9" builtinId="11"/>
-    <cellStyle name="Заголовок" xfId="10" builtinId="15"/>
-    <cellStyle name="Пояснительный текст" xfId="11" builtinId="53"/>
-    <cellStyle name="Заголовок 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Заголовок 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Заголовок 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Заголовок 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Ввод" xfId="16" builtinId="20"/>
-    <cellStyle name="Вывод" xfId="17" builtinId="21"/>
-    <cellStyle name="Вычисление" xfId="18" builtinId="22"/>
-    <cellStyle name="Проверить ячейку" xfId="19" builtinId="23"/>
-    <cellStyle name="Связанная ячейка" xfId="20" builtinId="24"/>
-    <cellStyle name="Итого" xfId="21" builtinId="25"/>
-    <cellStyle name="Хороший" xfId="22" builtinId="26"/>
-    <cellStyle name="Плохой" xfId="23" builtinId="27"/>
-    <cellStyle name="Нейтральный" xfId="24" builtinId="28"/>
-    <cellStyle name="Акцент1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% — Акцент1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% — Акцент1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% — Акцент1" xfId="28" builtinId="32"/>
-    <cellStyle name="Акцент2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% — Акцент2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% — Акцент2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% — Акцент2" xfId="32" builtinId="36"/>
-    <cellStyle name="Акцент3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% — Акцент3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% — Акцент3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% — Акцент3" xfId="36" builtinId="40"/>
-    <cellStyle name="Акцент4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% — Акцент4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% — Акцент4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% — Акцент4" xfId="40" builtinId="44"/>
-    <cellStyle name="Акцент5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% — Акцент5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% — Акцент5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% — Акцент5" xfId="44" builtinId="48"/>
-    <cellStyle name="Акцент6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% — Акцент6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% — Акцент6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% — Акцент6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1182,85 +580,91 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:AP37"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AQ37"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="37.3333333333333" customWidth="1"/>
-    <col min="3" max="3" width="9" style="8"/>
-    <col min="4" max="4" width="10.8888888888889"/>
+    <col min="2" max="2" width="37.28515625" customWidth="1"/>
+    <col min="3" max="4" width="9" style="8"/>
+    <col min="5" max="5" width="10.85546875"/>
+    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:42">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:43" ht="14.45" customHeight="1">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
-      <c r="AF1" s="1"/>
-      <c r="AG1" s="1"/>
-      <c r="AH1" s="1"/>
-      <c r="AI1" s="1"/>
-      <c r="AJ1" s="1"/>
-      <c r="AK1" s="1"/>
-      <c r="AL1" s="1"/>
-      <c r="AM1" s="1"/>
-      <c r="AN1" s="1"/>
-      <c r="AO1" s="1"/>
-      <c r="AP1" s="1"/>
-    </row>
-    <row r="2" ht="27.6" customHeight="1" spans="1:42">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="13"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="13"/>
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="13"/>
+      <c r="AE1" s="13"/>
+      <c r="AF1" s="13"/>
+      <c r="AG1" s="13"/>
+      <c r="AH1" s="13"/>
+      <c r="AI1" s="13"/>
+      <c r="AJ1" s="13"/>
+      <c r="AK1" s="13"/>
+      <c r="AL1" s="13"/>
+      <c r="AM1" s="13"/>
+      <c r="AN1" s="13"/>
+      <c r="AO1" s="13"/>
+      <c r="AP1" s="13"/>
+      <c r="AQ1" s="13"/>
+    </row>
+    <row r="2" spans="1:43" ht="27.6" customHeight="1">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="10" t="s">
+      <c r="B2" s="15"/>
+      <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="10">
         <v>46062</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="F2" s="10">
+        <v>46065</v>
+      </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
-      <c r="L2" s="3"/>
+      <c r="L2" s="2"/>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
@@ -1269,9 +673,13 @@
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
       <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
+      <c r="U2" s="3" t="s">
+        <v>45</v>
+      </c>
       <c r="V2" s="3"/>
-      <c r="W2" s="3"/>
+      <c r="W2" s="3" t="s">
+        <v>47</v>
+      </c>
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
@@ -1290,19 +698,20 @@
       <c r="AM2" s="3"/>
       <c r="AN2" s="3"/>
       <c r="AO2" s="3"/>
-      <c r="AP2" s="1" t="s">
+      <c r="AP2" s="3"/>
+      <c r="AQ2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="27.6" spans="1:42">
+    <row r="3" spans="1:43">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="2"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -1310,7 +719,7 @@
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
-      <c r="L3" s="3"/>
+      <c r="L3" s="2"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
@@ -1340,29 +749,32 @@
       <c r="AM3" s="3"/>
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
-      <c r="AP3" s="1"/>
-    </row>
-    <row r="4" spans="1:42">
+      <c r="AP3" s="3"/>
+      <c r="AQ3" s="1"/>
+    </row>
+    <row r="4" spans="1:43">
       <c r="A4" s="2">
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="9">
         <v>1</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
-      <c r="L4" s="3"/>
+      <c r="L4" s="2"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
@@ -1392,29 +804,32 @@
       <c r="AM4" s="3"/>
       <c r="AN4" s="3"/>
       <c r="AO4" s="3"/>
-      <c r="AP4" s="1"/>
-    </row>
-    <row r="5" spans="1:42">
+      <c r="AP4" s="3"/>
+      <c r="AQ4" s="1"/>
+    </row>
+    <row r="5" spans="1:43">
       <c r="A5" s="2">
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="9">
         <v>2</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
-      <c r="L5" s="3"/>
+      <c r="L5" s="2"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
@@ -1444,29 +859,32 @@
       <c r="AM5" s="3"/>
       <c r="AN5" s="3"/>
       <c r="AO5" s="3"/>
-      <c r="AP5" s="1"/>
-    </row>
-    <row r="6" spans="1:42">
+      <c r="AP5" s="3"/>
+      <c r="AQ5" s="1"/>
+    </row>
+    <row r="6" spans="1:43">
       <c r="A6" s="2">
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="9">
         <v>3</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
-      <c r="L6" s="3"/>
+      <c r="L6" s="2"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
@@ -1496,29 +914,32 @@
       <c r="AM6" s="3"/>
       <c r="AN6" s="3"/>
       <c r="AO6" s="3"/>
-      <c r="AP6" s="1"/>
-    </row>
-    <row r="7" spans="1:42">
+      <c r="AP6" s="3"/>
+      <c r="AQ6" s="1"/>
+    </row>
+    <row r="7" spans="1:43">
       <c r="A7" s="2">
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="9">
         <v>4</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
-      <c r="L7" s="3"/>
+      <c r="L7" s="2"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
@@ -1548,29 +969,32 @@
       <c r="AM7" s="3"/>
       <c r="AN7" s="3"/>
       <c r="AO7" s="3"/>
-      <c r="AP7" s="1"/>
-    </row>
-    <row r="8" ht="18" customHeight="1" spans="1:42">
+      <c r="AP7" s="3"/>
+      <c r="AQ7" s="1"/>
+    </row>
+    <row r="8" spans="1:43" ht="18" customHeight="1">
       <c r="A8" s="2">
         <v>5</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="9">
         <v>5</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
-      <c r="L8" s="3"/>
+      <c r="L8" s="2"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
@@ -1600,29 +1024,32 @@
       <c r="AM8" s="3"/>
       <c r="AN8" s="3"/>
       <c r="AO8" s="3"/>
-      <c r="AP8" s="1"/>
-    </row>
-    <row r="9" spans="1:42">
+      <c r="AP8" s="3"/>
+      <c r="AQ8" s="1"/>
+    </row>
+    <row r="9" spans="1:43">
       <c r="A9" s="2">
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="9">
         <v>6</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
-      <c r="L9" s="3"/>
+      <c r="L9" s="2"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
@@ -1652,29 +1079,32 @@
       <c r="AM9" s="3"/>
       <c r="AN9" s="3"/>
       <c r="AO9" s="3"/>
-      <c r="AP9" s="1"/>
-    </row>
-    <row r="10" spans="1:42">
+      <c r="AP9" s="3"/>
+      <c r="AQ9" s="1"/>
+    </row>
+    <row r="10" spans="1:43">
       <c r="A10" s="2">
         <v>7</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="10">
-        <v>7</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
+      <c r="C10" s="9">
+        <v>7</v>
+      </c>
+      <c r="D10" s="9"/>
+      <c r="E10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
-      <c r="L10" s="3"/>
+      <c r="L10" s="2"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
@@ -1704,185 +1134,197 @@
       <c r="AM10" s="3"/>
       <c r="AN10" s="3"/>
       <c r="AO10" s="3"/>
-      <c r="AP10" s="1"/>
-    </row>
-    <row r="11" customHeight="1" spans="1:42">
+      <c r="AP10" s="3"/>
+      <c r="AQ10" s="1"/>
+    </row>
+    <row r="11" spans="1:43" ht="14.45" customHeight="1">
       <c r="A11" s="2">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="9">
         <v>8</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="13"/>
-      <c r="S11" s="13"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
-      <c r="AA11" s="3"/>
-      <c r="AB11" s="3"/>
-      <c r="AC11" s="3"/>
-      <c r="AD11" s="3"/>
-      <c r="AE11" s="3"/>
-      <c r="AF11" s="3"/>
-      <c r="AG11" s="3"/>
-      <c r="AH11" s="3"/>
-      <c r="AI11" s="3"/>
-      <c r="AJ11" s="3"/>
-      <c r="AK11" s="3"/>
-      <c r="AL11" s="3"/>
-      <c r="AM11" s="3"/>
-      <c r="AN11" s="3"/>
-      <c r="AO11" s="3"/>
-      <c r="AP11" s="1"/>
-    </row>
-    <row r="12" spans="1:42">
+      <c r="D11" s="9"/>
+      <c r="E11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="12"/>
+      <c r="R11" s="12"/>
+      <c r="S11" s="12"/>
+      <c r="T11" s="12"/>
+      <c r="U11" s="16"/>
+      <c r="V11" s="16"/>
+      <c r="W11" s="16"/>
+      <c r="X11" s="16"/>
+      <c r="Y11" s="16"/>
+      <c r="Z11" s="16"/>
+      <c r="AA11" s="16"/>
+      <c r="AB11" s="16"/>
+      <c r="AC11" s="16"/>
+      <c r="AD11" s="16"/>
+      <c r="AE11" s="16"/>
+      <c r="AF11" s="16"/>
+      <c r="AG11" s="16"/>
+      <c r="AH11" s="16"/>
+      <c r="AI11" s="16"/>
+      <c r="AJ11" s="16"/>
+      <c r="AK11" s="16"/>
+      <c r="AL11" s="16"/>
+      <c r="AM11" s="16"/>
+      <c r="AN11" s="16"/>
+      <c r="AO11" s="16"/>
+      <c r="AP11" s="16"/>
+      <c r="AQ11" s="13"/>
+    </row>
+    <row r="12" spans="1:43">
       <c r="A12" s="2">
         <v>9</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="9">
         <v>9</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="13"/>
-      <c r="Q12" s="13"/>
-      <c r="R12" s="13"/>
-      <c r="S12" s="13"/>
-      <c r="T12" s="3"/>
-      <c r="U12" s="3"/>
-      <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
-      <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="3"/>
-      <c r="AA12" s="3"/>
-      <c r="AB12" s="3"/>
-      <c r="AC12" s="3"/>
-      <c r="AD12" s="3"/>
-      <c r="AE12" s="3"/>
-      <c r="AF12" s="3"/>
-      <c r="AG12" s="3"/>
-      <c r="AH12" s="3"/>
-      <c r="AI12" s="3"/>
-      <c r="AJ12" s="3"/>
-      <c r="AK12" s="3"/>
-      <c r="AL12" s="3"/>
-      <c r="AM12" s="3"/>
-      <c r="AN12" s="3"/>
-      <c r="AO12" s="3"/>
-      <c r="AP12" s="1"/>
-    </row>
-    <row r="13" spans="1:42">
+      <c r="D12" s="9"/>
+      <c r="E12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="12"/>
+      <c r="S12" s="12"/>
+      <c r="T12" s="12"/>
+      <c r="U12" s="16"/>
+      <c r="V12" s="16"/>
+      <c r="W12" s="16"/>
+      <c r="X12" s="16"/>
+      <c r="Y12" s="16"/>
+      <c r="Z12" s="16"/>
+      <c r="AA12" s="16"/>
+      <c r="AB12" s="16"/>
+      <c r="AC12" s="16"/>
+      <c r="AD12" s="16"/>
+      <c r="AE12" s="16"/>
+      <c r="AF12" s="16"/>
+      <c r="AG12" s="16"/>
+      <c r="AH12" s="16"/>
+      <c r="AI12" s="16"/>
+      <c r="AJ12" s="16"/>
+      <c r="AK12" s="16"/>
+      <c r="AL12" s="16"/>
+      <c r="AM12" s="16"/>
+      <c r="AN12" s="16"/>
+      <c r="AO12" s="16"/>
+      <c r="AP12" s="16"/>
+      <c r="AQ12" s="13"/>
+    </row>
+    <row r="13" spans="1:43">
       <c r="A13" s="2">
         <v>10</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="9">
         <v>10</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
-      <c r="P13" s="13"/>
-      <c r="Q13" s="13"/>
-      <c r="R13" s="13"/>
-      <c r="S13" s="13"/>
-      <c r="T13" s="3"/>
-      <c r="U13" s="3"/>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="3"/>
-      <c r="AA13" s="3"/>
-      <c r="AB13" s="3"/>
-      <c r="AC13" s="3"/>
-      <c r="AD13" s="3"/>
-      <c r="AE13" s="3"/>
-      <c r="AF13" s="3"/>
-      <c r="AG13" s="3"/>
-      <c r="AH13" s="3"/>
-      <c r="AI13" s="3"/>
-      <c r="AJ13" s="3"/>
-      <c r="AK13" s="3"/>
-      <c r="AL13" s="3"/>
-      <c r="AM13" s="3"/>
-      <c r="AN13" s="3"/>
-      <c r="AO13" s="3"/>
-      <c r="AP13" s="1"/>
-    </row>
-    <row r="14" spans="1:42">
+      <c r="D13" s="9"/>
+      <c r="E13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="12"/>
+      <c r="S13" s="12"/>
+      <c r="T13" s="12"/>
+      <c r="U13" s="16"/>
+      <c r="V13" s="16"/>
+      <c r="W13" s="16"/>
+      <c r="X13" s="16"/>
+      <c r="Y13" s="16"/>
+      <c r="Z13" s="16"/>
+      <c r="AA13" s="16"/>
+      <c r="AB13" s="16"/>
+      <c r="AC13" s="16"/>
+      <c r="AD13" s="16"/>
+      <c r="AE13" s="16"/>
+      <c r="AF13" s="16"/>
+      <c r="AG13" s="16"/>
+      <c r="AH13" s="16"/>
+      <c r="AI13" s="16"/>
+      <c r="AJ13" s="16"/>
+      <c r="AK13" s="16"/>
+      <c r="AL13" s="16"/>
+      <c r="AM13" s="16"/>
+      <c r="AN13" s="16"/>
+      <c r="AO13" s="16"/>
+      <c r="AP13" s="16"/>
+      <c r="AQ13" s="13"/>
+    </row>
+    <row r="14" spans="1:43">
       <c r="A14" s="2">
         <v>11</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="9">
         <v>11</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
-      <c r="L14" s="3"/>
+      <c r="L14" s="2"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
@@ -1912,29 +1354,32 @@
       <c r="AM14" s="3"/>
       <c r="AN14" s="3"/>
       <c r="AO14" s="3"/>
-      <c r="AP14" s="1"/>
-    </row>
-    <row r="15" spans="1:42">
+      <c r="AP14" s="3"/>
+      <c r="AQ14" s="1"/>
+    </row>
+    <row r="15" spans="1:43">
       <c r="A15" s="2">
         <v>12</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="9">
         <v>8</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
-      <c r="L15" s="3"/>
+      <c r="L15" s="2"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
@@ -1964,29 +1409,32 @@
       <c r="AM15" s="3"/>
       <c r="AN15" s="3"/>
       <c r="AO15" s="3"/>
-      <c r="AP15" s="1"/>
-    </row>
-    <row r="16" spans="1:42">
+      <c r="AP15" s="3"/>
+      <c r="AQ15" s="1"/>
+    </row>
+    <row r="16" spans="1:43">
       <c r="A16" s="2">
         <v>13</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="9">
         <v>12</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
-      <c r="L16" s="3"/>
+      <c r="L16" s="2"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
@@ -2016,29 +1464,32 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
-      <c r="AP16" s="1"/>
-    </row>
-    <row r="17" spans="1:42">
+      <c r="AP16" s="3"/>
+      <c r="AQ16" s="1"/>
+    </row>
+    <row r="17" spans="1:43">
       <c r="A17" s="2">
         <v>14</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="9">
         <v>13</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
-      <c r="L17" s="3"/>
+      <c r="L17" s="2"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
@@ -2068,29 +1519,32 @@
       <c r="AM17" s="3"/>
       <c r="AN17" s="3"/>
       <c r="AO17" s="3"/>
-      <c r="AP17" s="1"/>
-    </row>
-    <row r="18" spans="1:42">
+      <c r="AP17" s="3"/>
+      <c r="AQ17" s="1"/>
+    </row>
+    <row r="18" spans="1:43">
       <c r="A18" s="2">
         <v>15</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="9">
         <v>4</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
-      <c r="L18" s="3"/>
+      <c r="L18" s="2"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
@@ -2120,29 +1574,32 @@
       <c r="AM18" s="3"/>
       <c r="AN18" s="3"/>
       <c r="AO18" s="3"/>
-      <c r="AP18" s="1"/>
-    </row>
-    <row r="19" spans="1:42">
+      <c r="AP18" s="3"/>
+      <c r="AQ18" s="1"/>
+    </row>
+    <row r="19" spans="1:43">
       <c r="A19" s="2">
         <v>16</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="9">
         <v>6</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
-      <c r="L19" s="3"/>
+      <c r="L19" s="2"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
@@ -2172,29 +1629,32 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
-      <c r="AP19" s="1"/>
-    </row>
-    <row r="20" spans="1:42">
+      <c r="AP19" s="3"/>
+      <c r="AQ19" s="1"/>
+    </row>
+    <row r="20" spans="1:43">
       <c r="A20" s="2">
         <v>17</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="9">
         <v>16</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="9"/>
+      <c r="E20" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
+      <c r="F20" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
-      <c r="L20" s="3"/>
+      <c r="L20" s="2"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
@@ -2224,29 +1684,32 @@
       <c r="AM20" s="3"/>
       <c r="AN20" s="3"/>
       <c r="AO20" s="3"/>
-      <c r="AP20" s="1"/>
-    </row>
-    <row r="21" spans="1:42">
+      <c r="AP20" s="3"/>
+      <c r="AQ20" s="1"/>
+    </row>
+    <row r="21" spans="1:43">
       <c r="A21" s="2">
         <v>18</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="9">
         <v>5</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
-      <c r="L21" s="3"/>
+      <c r="L21" s="2"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
@@ -2276,29 +1739,32 @@
       <c r="AM21" s="3"/>
       <c r="AN21" s="3"/>
       <c r="AO21" s="3"/>
-      <c r="AP21" s="1"/>
-    </row>
-    <row r="22" spans="1:42">
+      <c r="AP21" s="3"/>
+      <c r="AQ21" s="1"/>
+    </row>
+    <row r="22" spans="1:43">
       <c r="A22" s="2">
         <v>19</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="9">
         <v>14</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="9"/>
+      <c r="E22" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
+      <c r="F22" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
-      <c r="L22" s="3"/>
+      <c r="L22" s="2"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
@@ -2328,29 +1794,32 @@
       <c r="AM22" s="3"/>
       <c r="AN22" s="3"/>
       <c r="AO22" s="3"/>
-      <c r="AP22" s="1"/>
-    </row>
-    <row r="23" spans="1:42">
+      <c r="AP22" s="3"/>
+      <c r="AQ22" s="1"/>
+    </row>
+    <row r="23" spans="1:43">
       <c r="A23" s="2">
         <v>20</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="9">
         <v>14</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
-      <c r="L23" s="3"/>
+      <c r="L23" s="2"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
@@ -2380,29 +1849,32 @@
       <c r="AM23" s="3"/>
       <c r="AN23" s="3"/>
       <c r="AO23" s="3"/>
-      <c r="AP23" s="1"/>
-    </row>
-    <row r="24" spans="1:42">
+      <c r="AP23" s="3"/>
+      <c r="AQ23" s="1"/>
+    </row>
+    <row r="24" spans="1:43">
       <c r="A24" s="2">
         <v>21</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="10">
+      <c r="C24" s="9">
         <v>15</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
-      <c r="L24" s="3"/>
+      <c r="L24" s="2"/>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
@@ -2432,29 +1904,32 @@
       <c r="AM24" s="3"/>
       <c r="AN24" s="3"/>
       <c r="AO24" s="3"/>
-      <c r="AP24" s="1"/>
-    </row>
-    <row r="25" spans="1:42">
+      <c r="AP24" s="3"/>
+      <c r="AQ24" s="1"/>
+    </row>
+    <row r="25" spans="1:43">
       <c r="A25" s="2">
         <v>22</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="10">
+      <c r="C25" s="9">
         <v>9</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
-      <c r="L25" s="3"/>
+      <c r="L25" s="2"/>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
@@ -2484,29 +1959,32 @@
       <c r="AM25" s="3"/>
       <c r="AN25" s="3"/>
       <c r="AO25" s="3"/>
-      <c r="AP25" s="1"/>
-    </row>
-    <row r="26" spans="1:42">
+      <c r="AP25" s="3"/>
+      <c r="AQ25" s="1"/>
+    </row>
+    <row r="26" spans="1:43">
       <c r="A26" s="2">
         <v>23</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="10">
+      <c r="C26" s="9">
         <v>16</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="9"/>
+      <c r="E26" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
+      <c r="F26" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
-      <c r="L26" s="3"/>
+      <c r="L26" s="2"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
@@ -2536,29 +2014,32 @@
       <c r="AM26" s="3"/>
       <c r="AN26" s="3"/>
       <c r="AO26" s="3"/>
-      <c r="AP26" s="1"/>
-    </row>
-    <row r="27" spans="1:42">
+      <c r="AP26" s="3"/>
+      <c r="AQ26" s="1"/>
+    </row>
+    <row r="27" spans="1:43">
       <c r="A27" s="2">
         <v>24</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="10">
+      <c r="C27" s="9">
         <v>2</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
-      <c r="L27" s="3"/>
+      <c r="L27" s="2"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
@@ -2588,29 +2069,32 @@
       <c r="AM27" s="3"/>
       <c r="AN27" s="3"/>
       <c r="AO27" s="3"/>
-      <c r="AP27" s="1"/>
-    </row>
-    <row r="28" spans="1:42">
+      <c r="AP27" s="3"/>
+      <c r="AQ27" s="1"/>
+    </row>
+    <row r="28" spans="1:43">
       <c r="A28" s="2">
         <v>25</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="10">
+      <c r="C28" s="9">
         <v>1</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
-      <c r="L28" s="3"/>
+      <c r="L28" s="2"/>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
@@ -2640,29 +2124,32 @@
       <c r="AM28" s="3"/>
       <c r="AN28" s="3"/>
       <c r="AO28" s="3"/>
-      <c r="AP28" s="1"/>
-    </row>
-    <row r="29" spans="1:42">
+      <c r="AP28" s="3"/>
+      <c r="AQ28" s="1"/>
+    </row>
+    <row r="29" spans="1:43">
       <c r="A29" s="2">
         <v>26</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C29" s="10">
+      <c r="C29" s="9">
         <v>13</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
-      <c r="L29" s="3"/>
+      <c r="L29" s="2"/>
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
@@ -2692,29 +2179,32 @@
       <c r="AM29" s="3"/>
       <c r="AN29" s="3"/>
       <c r="AO29" s="3"/>
-      <c r="AP29" s="1"/>
-    </row>
-    <row r="30" spans="1:42">
+      <c r="AP29" s="3"/>
+      <c r="AQ29" s="1"/>
+    </row>
+    <row r="30" spans="1:43">
       <c r="A30" s="2">
         <v>27</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="10">
+      <c r="C30" s="9">
         <v>12</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
-      <c r="L30" s="3"/>
+      <c r="L30" s="2"/>
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
@@ -2744,29 +2234,32 @@
       <c r="AM30" s="3"/>
       <c r="AN30" s="3"/>
       <c r="AO30" s="3"/>
-      <c r="AP30" s="1"/>
-    </row>
-    <row r="31" spans="1:42">
+      <c r="AP30" s="3"/>
+      <c r="AQ30" s="1"/>
+    </row>
+    <row r="31" spans="1:43">
       <c r="A31" s="2">
         <v>28</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="10">
+      <c r="C31" s="9">
         <v>3</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
-      <c r="L31" s="3"/>
+      <c r="L31" s="2"/>
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
@@ -2796,29 +2289,32 @@
       <c r="AM31" s="3"/>
       <c r="AN31" s="3"/>
       <c r="AO31" s="3"/>
-      <c r="AP31" s="1"/>
-    </row>
-    <row r="32" spans="1:42">
+      <c r="AP31" s="3"/>
+      <c r="AQ31" s="1"/>
+    </row>
+    <row r="32" spans="1:43">
       <c r="A32" s="2">
         <v>29</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="10">
+      <c r="C32" s="9">
         <v>15</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
-      <c r="L32" s="3"/>
+      <c r="L32" s="2"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
@@ -2848,29 +2344,32 @@
       <c r="AM32" s="3"/>
       <c r="AN32" s="3"/>
       <c r="AO32" s="3"/>
-      <c r="AP32" s="1"/>
-    </row>
-    <row r="33" spans="1:42">
+      <c r="AP32" s="3"/>
+      <c r="AQ32" s="1"/>
+    </row>
+    <row r="33" spans="1:43">
       <c r="A33" s="2">
         <v>30</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="10">
-        <v>7</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
+      <c r="C33" s="9">
+        <v>7</v>
+      </c>
+      <c r="D33" s="9"/>
+      <c r="E33" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
-      <c r="L33" s="3"/>
+      <c r="L33" s="2"/>
       <c r="M33" s="3"/>
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
@@ -2900,29 +2399,32 @@
       <c r="AM33" s="3"/>
       <c r="AN33" s="3"/>
       <c r="AO33" s="3"/>
-      <c r="AP33" s="1"/>
-    </row>
-    <row r="34" spans="1:42">
+      <c r="AP33" s="3"/>
+      <c r="AQ33" s="1"/>
+    </row>
+    <row r="34" spans="1:43">
       <c r="A34" s="2">
         <v>31</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="10">
+      <c r="C34" s="9">
         <v>10</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
-      <c r="L34" s="3"/>
+      <c r="L34" s="2"/>
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
@@ -2952,29 +2454,32 @@
       <c r="AM34" s="3"/>
       <c r="AN34" s="3"/>
       <c r="AO34" s="3"/>
-      <c r="AP34" s="1"/>
-    </row>
-    <row r="35" spans="1:42">
+      <c r="AP34" s="3"/>
+      <c r="AQ34" s="1"/>
+    </row>
+    <row r="35" spans="1:43">
       <c r="A35" s="2">
         <v>32</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="10">
+      <c r="C35" s="9">
         <v>11</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
-      <c r="L35" s="3"/>
+      <c r="L35" s="2"/>
       <c r="M35" s="3"/>
       <c r="N35" s="3"/>
       <c r="O35" s="3"/>
@@ -3004,11 +2509,12 @@
       <c r="AM35" s="3"/>
       <c r="AN35" s="3"/>
       <c r="AO35" s="3"/>
-      <c r="AP35" s="1"/>
-    </row>
-    <row r="36" spans="3:42">
-      <c r="C36" s="10"/>
-      <c r="D36" s="2"/>
+      <c r="AP35" s="3"/>
+      <c r="AQ35" s="1"/>
+    </row>
+    <row r="36" spans="1:43">
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
@@ -3016,7 +2522,7 @@
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
-      <c r="L36" s="3"/>
+      <c r="L36" s="2"/>
       <c r="M36" s="3"/>
       <c r="N36" s="3"/>
       <c r="O36" s="3"/>
@@ -3046,23 +2552,27 @@
       <c r="AM36" s="3"/>
       <c r="AN36" s="3"/>
       <c r="AO36" s="3"/>
-      <c r="AP36" s="1"/>
-    </row>
-    <row r="37" spans="1:42">
+      <c r="AP36" s="3"/>
+      <c r="AQ36" s="1"/>
+    </row>
+    <row r="37" spans="1:43">
       <c r="A37" t="s">
         <v>40</v>
       </c>
-      <c r="B37"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
-      <c r="L37" s="3"/>
+      <c r="L37" s="2"/>
       <c r="M37" s="3"/>
       <c r="N37" s="3"/>
       <c r="O37" s="3"/>
@@ -3092,13 +2602,22 @@
       <c r="AM37" s="3"/>
       <c r="AN37" s="3"/>
       <c r="AO37" s="3"/>
-      <c r="AP37" s="1"/>
+      <c r="AP37" s="3"/>
+      <c r="AQ37" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A1:AP1"/>
+    <mergeCell ref="AN11:AN13"/>
+    <mergeCell ref="AO11:AO13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AQ11:AQ13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
+    <mergeCell ref="A1:AQ1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="T11:T13"/>
     <mergeCell ref="U11:U13"/>
     <mergeCell ref="V11:V13"/>
     <mergeCell ref="W11:W13"/>
@@ -3113,77 +2632,67 @@
     <mergeCell ref="AF11:AF13"/>
     <mergeCell ref="AG11:AG13"/>
     <mergeCell ref="AH11:AH13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="AN11:AN13"/>
-    <mergeCell ref="AO11:AO13"/>
-    <mergeCell ref="AP11:AP13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AP37"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
-      <c r="AF1" s="1"/>
-      <c r="AG1" s="1"/>
-      <c r="AH1" s="1"/>
-      <c r="AI1" s="1"/>
-      <c r="AJ1" s="1"/>
-      <c r="AK1" s="1"/>
-      <c r="AL1" s="1"/>
-      <c r="AM1" s="1"/>
-      <c r="AN1" s="1"/>
-      <c r="AO1" s="1"/>
-      <c r="AP1" s="1"/>
-    </row>
-    <row r="2" ht="27.6" spans="1:42">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="13"/>
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="13"/>
+      <c r="AE1" s="13"/>
+      <c r="AF1" s="13"/>
+      <c r="AG1" s="13"/>
+      <c r="AH1" s="13"/>
+      <c r="AI1" s="13"/>
+      <c r="AJ1" s="13"/>
+      <c r="AK1" s="13"/>
+      <c r="AL1" s="13"/>
+      <c r="AM1" s="13"/>
+      <c r="AN1" s="13"/>
+      <c r="AO1" s="13"/>
+      <c r="AP1" s="13"/>
+    </row>
+    <row r="2" spans="1:42" ht="30">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="15"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -3227,7 +2736,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="27.6" spans="1:42">
+    <row r="3" spans="1:42" ht="45">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -3467,7 +2976,7 @@
       <c r="AO7" s="3"/>
       <c r="AP7" s="1"/>
     </row>
-    <row r="8" ht="55.2" spans="1:42">
+    <row r="8" spans="1:42" ht="60">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -3612,142 +3121,142 @@
       <c r="AP10" s="1"/>
     </row>
     <row r="11" spans="1:42">
-      <c r="A11" s="2">
+      <c r="A11" s="15">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
-      <c r="AA11" s="3"/>
-      <c r="AB11" s="3"/>
-      <c r="AC11" s="3"/>
-      <c r="AD11" s="3"/>
-      <c r="AE11" s="3"/>
-      <c r="AF11" s="3"/>
-      <c r="AG11" s="3"/>
-      <c r="AH11" s="3"/>
-      <c r="AI11" s="3"/>
-      <c r="AJ11" s="3"/>
-      <c r="AK11" s="3"/>
-      <c r="AL11" s="3"/>
-      <c r="AM11" s="3"/>
-      <c r="AN11" s="3"/>
-      <c r="AO11" s="3"/>
-      <c r="AP11" s="1"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="16"/>
+      <c r="R11" s="16"/>
+      <c r="S11" s="16"/>
+      <c r="T11" s="16"/>
+      <c r="U11" s="16"/>
+      <c r="V11" s="16"/>
+      <c r="W11" s="16"/>
+      <c r="X11" s="16"/>
+      <c r="Y11" s="16"/>
+      <c r="Z11" s="16"/>
+      <c r="AA11" s="16"/>
+      <c r="AB11" s="16"/>
+      <c r="AC11" s="16"/>
+      <c r="AD11" s="16"/>
+      <c r="AE11" s="16"/>
+      <c r="AF11" s="16"/>
+      <c r="AG11" s="16"/>
+      <c r="AH11" s="16"/>
+      <c r="AI11" s="16"/>
+      <c r="AJ11" s="16"/>
+      <c r="AK11" s="16"/>
+      <c r="AL11" s="16"/>
+      <c r="AM11" s="16"/>
+      <c r="AN11" s="16"/>
+      <c r="AO11" s="16"/>
+      <c r="AP11" s="13"/>
     </row>
     <row r="12" spans="1:42">
-      <c r="A12" s="2"/>
+      <c r="A12" s="15"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
-      <c r="U12" s="3"/>
-      <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
-      <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="3"/>
-      <c r="AA12" s="3"/>
-      <c r="AB12" s="3"/>
-      <c r="AC12" s="3"/>
-      <c r="AD12" s="3"/>
-      <c r="AE12" s="3"/>
-      <c r="AF12" s="3"/>
-      <c r="AG12" s="3"/>
-      <c r="AH12" s="3"/>
-      <c r="AI12" s="3"/>
-      <c r="AJ12" s="3"/>
-      <c r="AK12" s="3"/>
-      <c r="AL12" s="3"/>
-      <c r="AM12" s="3"/>
-      <c r="AN12" s="3"/>
-      <c r="AO12" s="3"/>
-      <c r="AP12" s="1"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="16"/>
+      <c r="T12" s="16"/>
+      <c r="U12" s="16"/>
+      <c r="V12" s="16"/>
+      <c r="W12" s="16"/>
+      <c r="X12" s="16"/>
+      <c r="Y12" s="16"/>
+      <c r="Z12" s="16"/>
+      <c r="AA12" s="16"/>
+      <c r="AB12" s="16"/>
+      <c r="AC12" s="16"/>
+      <c r="AD12" s="16"/>
+      <c r="AE12" s="16"/>
+      <c r="AF12" s="16"/>
+      <c r="AG12" s="16"/>
+      <c r="AH12" s="16"/>
+      <c r="AI12" s="16"/>
+      <c r="AJ12" s="16"/>
+      <c r="AK12" s="16"/>
+      <c r="AL12" s="16"/>
+      <c r="AM12" s="16"/>
+      <c r="AN12" s="16"/>
+      <c r="AO12" s="16"/>
+      <c r="AP12" s="13"/>
     </row>
     <row r="13" spans="1:42">
-      <c r="A13" s="2"/>
+      <c r="A13" s="15"/>
       <c r="B13" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
-      <c r="U13" s="3"/>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="3"/>
-      <c r="AA13" s="3"/>
-      <c r="AB13" s="3"/>
-      <c r="AC13" s="3"/>
-      <c r="AD13" s="3"/>
-      <c r="AE13" s="3"/>
-      <c r="AF13" s="3"/>
-      <c r="AG13" s="3"/>
-      <c r="AH13" s="3"/>
-      <c r="AI13" s="3"/>
-      <c r="AJ13" s="3"/>
-      <c r="AK13" s="3"/>
-      <c r="AL13" s="3"/>
-      <c r="AM13" s="3"/>
-      <c r="AN13" s="3"/>
-      <c r="AO13" s="3"/>
-      <c r="AP13" s="1"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="16"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="16"/>
+      <c r="R13" s="16"/>
+      <c r="S13" s="16"/>
+      <c r="T13" s="16"/>
+      <c r="U13" s="16"/>
+      <c r="V13" s="16"/>
+      <c r="W13" s="16"/>
+      <c r="X13" s="16"/>
+      <c r="Y13" s="16"/>
+      <c r="Z13" s="16"/>
+      <c r="AA13" s="16"/>
+      <c r="AB13" s="16"/>
+      <c r="AC13" s="16"/>
+      <c r="AD13" s="16"/>
+      <c r="AE13" s="16"/>
+      <c r="AF13" s="16"/>
+      <c r="AG13" s="16"/>
+      <c r="AH13" s="16"/>
+      <c r="AI13" s="16"/>
+      <c r="AJ13" s="16"/>
+      <c r="AK13" s="16"/>
+      <c r="AL13" s="16"/>
+      <c r="AM13" s="16"/>
+      <c r="AN13" s="16"/>
+      <c r="AO13" s="16"/>
+      <c r="AP13" s="13"/>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" s="2">
@@ -4903,6 +4412,33 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="AO11:AO13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
+    <mergeCell ref="AN11:AN13"/>
+    <mergeCell ref="AE11:AE13"/>
+    <mergeCell ref="AF11:AF13"/>
+    <mergeCell ref="AG11:AG13"/>
+    <mergeCell ref="AH11:AH13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="Z11:Z13"/>
+    <mergeCell ref="AA11:AA13"/>
+    <mergeCell ref="AB11:AB13"/>
+    <mergeCell ref="AC11:AC13"/>
+    <mergeCell ref="AD11:AD13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="V11:V13"/>
+    <mergeCell ref="W11:W13"/>
+    <mergeCell ref="X11:X13"/>
+    <mergeCell ref="Y11:Y13"/>
+    <mergeCell ref="P11:P13"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="T11:T13"/>
     <mergeCell ref="A1:AP1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A11:A13"/>
@@ -4919,35 +4455,7 @@
     <mergeCell ref="M11:M13"/>
     <mergeCell ref="N11:N13"/>
     <mergeCell ref="O11:O13"/>
-    <mergeCell ref="P11:P13"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="T11:T13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="V11:V13"/>
-    <mergeCell ref="W11:W13"/>
-    <mergeCell ref="X11:X13"/>
-    <mergeCell ref="Y11:Y13"/>
-    <mergeCell ref="Z11:Z13"/>
-    <mergeCell ref="AA11:AA13"/>
-    <mergeCell ref="AB11:AB13"/>
-    <mergeCell ref="AC11:AC13"/>
-    <mergeCell ref="AD11:AD13"/>
-    <mergeCell ref="AE11:AE13"/>
-    <mergeCell ref="AF11:AF13"/>
-    <mergeCell ref="AG11:AG13"/>
-    <mergeCell ref="AH11:AH13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="AN11:AN13"/>
-    <mergeCell ref="AO11:AO13"/>
-    <mergeCell ref="AP11:AP13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/ТКИ-341_Реверс_Инжиниринг.xlsx
+++ b/ТКИ-341_Реверс_Инжиниринг.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\flash_a\Documents\GIT\Reverse_Engineering\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\Reverse_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C4EFF40-C37B-4BC1-B666-FAA6EE55066E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E6E146F-C19B-4818-B5F9-EBE98908C860}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1290" yWindow="1170" windowWidth="23640" windowHeight="10035" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="48">
   <si>
     <t>ВЕДОМОСТЬ ПОСЕЩАЕМОСТИ ЗАНЯТИЙ СТУДЕНТАМИ ГРУППЫ ТКИ "Компьютерная безопасность" ИТТСУ РУТ (МИИТ)</t>
   </si>
@@ -210,7 +210,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="dd\.mm\.yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -269,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -292,12 +292,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -307,9 +313,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -592,61 +595,62 @@
     <col min="2" max="2" width="37.28515625" customWidth="1"/>
     <col min="3" max="4" width="9" style="8"/>
     <col min="5" max="5" width="10.85546875"/>
-    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="14.45" customHeight="1">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13"/>
-      <c r="Y1" s="13"/>
-      <c r="Z1" s="13"/>
-      <c r="AA1" s="13"/>
-      <c r="AB1" s="13"/>
-      <c r="AC1" s="13"/>
-      <c r="AD1" s="13"/>
-      <c r="AE1" s="13"/>
-      <c r="AF1" s="13"/>
-      <c r="AG1" s="13"/>
-      <c r="AH1" s="13"/>
-      <c r="AI1" s="13"/>
-      <c r="AJ1" s="13"/>
-      <c r="AK1" s="13"/>
-      <c r="AL1" s="13"/>
-      <c r="AM1" s="13"/>
-      <c r="AN1" s="13"/>
-      <c r="AO1" s="13"/>
-      <c r="AP1" s="13"/>
-      <c r="AQ1" s="13"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15"/>
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15"/>
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15"/>
+      <c r="AI1" s="15"/>
+      <c r="AJ1" s="15"/>
+      <c r="AK1" s="15"/>
+      <c r="AL1" s="15"/>
+      <c r="AM1" s="15"/>
+      <c r="AN1" s="15"/>
+      <c r="AO1" s="15"/>
+      <c r="AP1" s="15"/>
+      <c r="AQ1" s="15"/>
     </row>
     <row r="2" spans="1:43" ht="27.6" customHeight="1">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
+      <c r="B2" s="17"/>
       <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
@@ -659,7 +663,9 @@
       <c r="F2" s="10">
         <v>46065</v>
       </c>
-      <c r="G2" s="2"/>
+      <c r="G2" s="10">
+        <v>46072</v>
+      </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
@@ -769,7 +775,9 @@
       <c r="F4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="2"/>
+      <c r="G4" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
@@ -824,7 +832,9 @@
       <c r="F5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="2"/>
+      <c r="G5" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
@@ -879,7 +889,9 @@
       <c r="F6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="2"/>
+      <c r="G6" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
@@ -934,7 +946,9 @@
       <c r="F7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="2"/>
+      <c r="G7" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
@@ -989,7 +1003,9 @@
       <c r="F8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G8" s="2"/>
+      <c r="G8" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -1044,7 +1060,9 @@
       <c r="F9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="2"/>
+      <c r="G9" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -1099,7 +1117,9 @@
       <c r="F10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G10" s="2"/>
+      <c r="G10" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
@@ -1154,7 +1174,9 @@
       <c r="F11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="11"/>
+      <c r="G11" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
       <c r="J11" s="11"/>
@@ -1168,29 +1190,29 @@
       <c r="R11" s="12"/>
       <c r="S11" s="12"/>
       <c r="T11" s="12"/>
-      <c r="U11" s="16"/>
-      <c r="V11" s="16"/>
-      <c r="W11" s="16"/>
-      <c r="X11" s="16"/>
-      <c r="Y11" s="16"/>
-      <c r="Z11" s="16"/>
-      <c r="AA11" s="16"/>
-      <c r="AB11" s="16"/>
-      <c r="AC11" s="16"/>
-      <c r="AD11" s="16"/>
-      <c r="AE11" s="16"/>
-      <c r="AF11" s="16"/>
-      <c r="AG11" s="16"/>
-      <c r="AH11" s="16"/>
-      <c r="AI11" s="16"/>
-      <c r="AJ11" s="16"/>
-      <c r="AK11" s="16"/>
-      <c r="AL11" s="16"/>
-      <c r="AM11" s="16"/>
-      <c r="AN11" s="16"/>
-      <c r="AO11" s="16"/>
-      <c r="AP11" s="16"/>
-      <c r="AQ11" s="13"/>
+      <c r="U11" s="12"/>
+      <c r="V11" s="12"/>
+      <c r="W11" s="12"/>
+      <c r="X11" s="12"/>
+      <c r="Y11" s="12"/>
+      <c r="Z11" s="12"/>
+      <c r="AA11" s="14"/>
+      <c r="AB11" s="14"/>
+      <c r="AC11" s="14"/>
+      <c r="AD11" s="14"/>
+      <c r="AE11" s="14"/>
+      <c r="AF11" s="14"/>
+      <c r="AG11" s="14"/>
+      <c r="AH11" s="14"/>
+      <c r="AI11" s="14"/>
+      <c r="AJ11" s="14"/>
+      <c r="AK11" s="14"/>
+      <c r="AL11" s="14"/>
+      <c r="AM11" s="14"/>
+      <c r="AN11" s="14"/>
+      <c r="AO11" s="14"/>
+      <c r="AP11" s="14"/>
+      <c r="AQ11" s="15"/>
     </row>
     <row r="12" spans="1:43">
       <c r="A12" s="2">
@@ -1209,7 +1231,9 @@
       <c r="F12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="11"/>
+      <c r="G12" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
       <c r="J12" s="11"/>
@@ -1223,29 +1247,29 @@
       <c r="R12" s="12"/>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
-      <c r="U12" s="16"/>
-      <c r="V12" s="16"/>
-      <c r="W12" s="16"/>
-      <c r="X12" s="16"/>
-      <c r="Y12" s="16"/>
-      <c r="Z12" s="16"/>
-      <c r="AA12" s="16"/>
-      <c r="AB12" s="16"/>
-      <c r="AC12" s="16"/>
-      <c r="AD12" s="16"/>
-      <c r="AE12" s="16"/>
-      <c r="AF12" s="16"/>
-      <c r="AG12" s="16"/>
-      <c r="AH12" s="16"/>
-      <c r="AI12" s="16"/>
-      <c r="AJ12" s="16"/>
-      <c r="AK12" s="16"/>
-      <c r="AL12" s="16"/>
-      <c r="AM12" s="16"/>
-      <c r="AN12" s="16"/>
-      <c r="AO12" s="16"/>
-      <c r="AP12" s="16"/>
-      <c r="AQ12" s="13"/>
+      <c r="U12" s="12"/>
+      <c r="V12" s="12"/>
+      <c r="W12" s="12"/>
+      <c r="X12" s="12"/>
+      <c r="Y12" s="12"/>
+      <c r="Z12" s="12"/>
+      <c r="AA12" s="14"/>
+      <c r="AB12" s="14"/>
+      <c r="AC12" s="14"/>
+      <c r="AD12" s="14"/>
+      <c r="AE12" s="14"/>
+      <c r="AF12" s="14"/>
+      <c r="AG12" s="14"/>
+      <c r="AH12" s="14"/>
+      <c r="AI12" s="14"/>
+      <c r="AJ12" s="14"/>
+      <c r="AK12" s="14"/>
+      <c r="AL12" s="14"/>
+      <c r="AM12" s="14"/>
+      <c r="AN12" s="14"/>
+      <c r="AO12" s="14"/>
+      <c r="AP12" s="14"/>
+      <c r="AQ12" s="15"/>
     </row>
     <row r="13" spans="1:43">
       <c r="A13" s="2">
@@ -1264,7 +1288,9 @@
       <c r="F13" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="11"/>
+      <c r="G13" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
       <c r="J13" s="11"/>
@@ -1278,29 +1304,31 @@
       <c r="R13" s="12"/>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
-      <c r="U13" s="16"/>
-      <c r="V13" s="16"/>
-      <c r="W13" s="16"/>
-      <c r="X13" s="16"/>
-      <c r="Y13" s="16"/>
-      <c r="Z13" s="16"/>
-      <c r="AA13" s="16"/>
-      <c r="AB13" s="16"/>
-      <c r="AC13" s="16"/>
-      <c r="AD13" s="16"/>
-      <c r="AE13" s="16"/>
-      <c r="AF13" s="16"/>
-      <c r="AG13" s="16"/>
-      <c r="AH13" s="16"/>
-      <c r="AI13" s="16"/>
-      <c r="AJ13" s="16"/>
-      <c r="AK13" s="16"/>
-      <c r="AL13" s="16"/>
-      <c r="AM13" s="16"/>
-      <c r="AN13" s="16"/>
-      <c r="AO13" s="16"/>
-      <c r="AP13" s="16"/>
-      <c r="AQ13" s="13"/>
+      <c r="U13" s="10">
+        <v>46072</v>
+      </c>
+      <c r="V13" s="12"/>
+      <c r="W13" s="12"/>
+      <c r="X13" s="12"/>
+      <c r="Y13" s="12"/>
+      <c r="Z13" s="12"/>
+      <c r="AA13" s="14"/>
+      <c r="AB13" s="14"/>
+      <c r="AC13" s="14"/>
+      <c r="AD13" s="14"/>
+      <c r="AE13" s="14"/>
+      <c r="AF13" s="14"/>
+      <c r="AG13" s="14"/>
+      <c r="AH13" s="14"/>
+      <c r="AI13" s="14"/>
+      <c r="AJ13" s="14"/>
+      <c r="AK13" s="14"/>
+      <c r="AL13" s="14"/>
+      <c r="AM13" s="14"/>
+      <c r="AN13" s="14"/>
+      <c r="AO13" s="14"/>
+      <c r="AP13" s="14"/>
+      <c r="AQ13" s="15"/>
     </row>
     <row r="14" spans="1:43">
       <c r="A14" s="2">
@@ -1319,7 +1347,9 @@
       <c r="F14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G14" s="2"/>
+      <c r="G14" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
@@ -1374,7 +1404,9 @@
       <c r="F15" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G15" s="2"/>
+      <c r="G15" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
@@ -1429,7 +1461,9 @@
       <c r="F16" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G16" s="2"/>
+      <c r="G16" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -1484,7 +1518,9 @@
       <c r="F17" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G17" s="2"/>
+      <c r="G17" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -1539,7 +1575,9 @@
       <c r="F18" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G18" s="2"/>
+      <c r="G18" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -1594,7 +1632,9 @@
       <c r="F19" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G19" s="2"/>
+      <c r="G19" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -1649,7 +1689,9 @@
       <c r="F20" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G20" s="2"/>
+      <c r="G20" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
@@ -1704,7 +1746,9 @@
       <c r="F21" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G21" s="2"/>
+      <c r="G21" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
@@ -1759,7 +1803,9 @@
       <c r="F22" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G22" s="2"/>
+      <c r="G22" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
@@ -1773,7 +1819,9 @@
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
       <c r="T22" s="3"/>
-      <c r="U22" s="3"/>
+      <c r="U22" s="10">
+        <v>46072</v>
+      </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
@@ -1814,7 +1862,9 @@
       <c r="F23" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G23" s="2"/>
+      <c r="G23" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
@@ -1828,7 +1878,9 @@
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
-      <c r="U23" s="3"/>
+      <c r="U23" s="10">
+        <v>46072</v>
+      </c>
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
       <c r="X23" s="3"/>
@@ -1869,7 +1921,9 @@
       <c r="F24" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G24" s="2"/>
+      <c r="G24" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
@@ -1924,7 +1978,9 @@
       <c r="F25" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G25" s="2"/>
+      <c r="G25" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
@@ -1979,7 +2035,9 @@
       <c r="F26" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G26" s="2"/>
+      <c r="G26" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
@@ -2034,7 +2092,9 @@
       <c r="F27" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G27" s="2"/>
+      <c r="G27" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
@@ -2089,7 +2149,9 @@
       <c r="F28" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G28" s="2"/>
+      <c r="G28" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
@@ -2144,7 +2206,9 @@
       <c r="F29" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G29" s="2"/>
+      <c r="G29" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
@@ -2199,7 +2263,9 @@
       <c r="F30" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G30" s="2"/>
+      <c r="G30" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
@@ -2254,7 +2320,9 @@
       <c r="F31" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G31" s="2"/>
+      <c r="G31" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
@@ -2309,7 +2377,9 @@
       <c r="F32" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G32" s="2"/>
+      <c r="G32" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
@@ -2364,7 +2434,9 @@
       <c r="F33" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G33" s="2"/>
+      <c r="G33" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
@@ -2419,7 +2491,9 @@
       <c r="F34" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G34" s="2"/>
+      <c r="G34" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
@@ -2433,7 +2507,9 @@
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
-      <c r="U34" s="3"/>
+      <c r="U34" s="10">
+        <v>46072</v>
+      </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
@@ -2474,7 +2550,9 @@
       <c r="F35" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G35" s="2"/>
+      <c r="G35" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
@@ -2567,7 +2645,9 @@
       <c r="F37" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G37" s="2"/>
+      <c r="G37" s="13" t="s">
+        <v>43</v>
+      </c>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
@@ -2606,7 +2686,17 @@
       <c r="AQ37" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="19">
+    <mergeCell ref="A1:AQ1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="AA11:AA13"/>
+    <mergeCell ref="AB11:AB13"/>
+    <mergeCell ref="AC11:AC13"/>
+    <mergeCell ref="AD11:AD13"/>
+    <mergeCell ref="AE11:AE13"/>
+    <mergeCell ref="AF11:AF13"/>
+    <mergeCell ref="AG11:AG13"/>
+    <mergeCell ref="AH11:AH13"/>
     <mergeCell ref="AN11:AN13"/>
     <mergeCell ref="AO11:AO13"/>
     <mergeCell ref="AP11:AP13"/>
@@ -2616,22 +2706,6 @@
     <mergeCell ref="AK11:AK13"/>
     <mergeCell ref="AL11:AL13"/>
     <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="A1:AQ1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="V11:V13"/>
-    <mergeCell ref="W11:W13"/>
-    <mergeCell ref="X11:X13"/>
-    <mergeCell ref="Y11:Y13"/>
-    <mergeCell ref="Z11:Z13"/>
-    <mergeCell ref="AA11:AA13"/>
-    <mergeCell ref="AB11:AB13"/>
-    <mergeCell ref="AC11:AC13"/>
-    <mergeCell ref="AD11:AD13"/>
-    <mergeCell ref="AE11:AE13"/>
-    <mergeCell ref="AF11:AF13"/>
-    <mergeCell ref="AG11:AG13"/>
-    <mergeCell ref="AH11:AH13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2643,56 +2717,56 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13"/>
-      <c r="Y1" s="13"/>
-      <c r="Z1" s="13"/>
-      <c r="AA1" s="13"/>
-      <c r="AB1" s="13"/>
-      <c r="AC1" s="13"/>
-      <c r="AD1" s="13"/>
-      <c r="AE1" s="13"/>
-      <c r="AF1" s="13"/>
-      <c r="AG1" s="13"/>
-      <c r="AH1" s="13"/>
-      <c r="AI1" s="13"/>
-      <c r="AJ1" s="13"/>
-      <c r="AK1" s="13"/>
-      <c r="AL1" s="13"/>
-      <c r="AM1" s="13"/>
-      <c r="AN1" s="13"/>
-      <c r="AO1" s="13"/>
-      <c r="AP1" s="13"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15"/>
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15"/>
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15"/>
+      <c r="AI1" s="15"/>
+      <c r="AJ1" s="15"/>
+      <c r="AK1" s="15"/>
+      <c r="AL1" s="15"/>
+      <c r="AM1" s="15"/>
+      <c r="AN1" s="15"/>
+      <c r="AO1" s="15"/>
+      <c r="AP1" s="15"/>
     </row>
     <row r="2" spans="1:42" ht="30">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
+      <c r="B2" s="17"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -3121,142 +3195,142 @@
       <c r="AP10" s="1"/>
     </row>
     <row r="11" spans="1:42">
-      <c r="A11" s="15">
+      <c r="A11" s="17">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="16"/>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="16"/>
-      <c r="R11" s="16"/>
-      <c r="S11" s="16"/>
-      <c r="T11" s="16"/>
-      <c r="U11" s="16"/>
-      <c r="V11" s="16"/>
-      <c r="W11" s="16"/>
-      <c r="X11" s="16"/>
-      <c r="Y11" s="16"/>
-      <c r="Z11" s="16"/>
-      <c r="AA11" s="16"/>
-      <c r="AB11" s="16"/>
-      <c r="AC11" s="16"/>
-      <c r="AD11" s="16"/>
-      <c r="AE11" s="16"/>
-      <c r="AF11" s="16"/>
-      <c r="AG11" s="16"/>
-      <c r="AH11" s="16"/>
-      <c r="AI11" s="16"/>
-      <c r="AJ11" s="16"/>
-      <c r="AK11" s="16"/>
-      <c r="AL11" s="16"/>
-      <c r="AM11" s="16"/>
-      <c r="AN11" s="16"/>
-      <c r="AO11" s="16"/>
-      <c r="AP11" s="13"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="14"/>
+      <c r="P11" s="14"/>
+      <c r="Q11" s="14"/>
+      <c r="R11" s="14"/>
+      <c r="S11" s="14"/>
+      <c r="T11" s="14"/>
+      <c r="U11" s="14"/>
+      <c r="V11" s="14"/>
+      <c r="W11" s="14"/>
+      <c r="X11" s="14"/>
+      <c r="Y11" s="14"/>
+      <c r="Z11" s="14"/>
+      <c r="AA11" s="14"/>
+      <c r="AB11" s="14"/>
+      <c r="AC11" s="14"/>
+      <c r="AD11" s="14"/>
+      <c r="AE11" s="14"/>
+      <c r="AF11" s="14"/>
+      <c r="AG11" s="14"/>
+      <c r="AH11" s="14"/>
+      <c r="AI11" s="14"/>
+      <c r="AJ11" s="14"/>
+      <c r="AK11" s="14"/>
+      <c r="AL11" s="14"/>
+      <c r="AM11" s="14"/>
+      <c r="AN11" s="14"/>
+      <c r="AO11" s="14"/>
+      <c r="AP11" s="15"/>
     </row>
     <row r="12" spans="1:42">
-      <c r="A12" s="15"/>
+      <c r="A12" s="17"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="16"/>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="16"/>
-      <c r="R12" s="16"/>
-      <c r="S12" s="16"/>
-      <c r="T12" s="16"/>
-      <c r="U12" s="16"/>
-      <c r="V12" s="16"/>
-      <c r="W12" s="16"/>
-      <c r="X12" s="16"/>
-      <c r="Y12" s="16"/>
-      <c r="Z12" s="16"/>
-      <c r="AA12" s="16"/>
-      <c r="AB12" s="16"/>
-      <c r="AC12" s="16"/>
-      <c r="AD12" s="16"/>
-      <c r="AE12" s="16"/>
-      <c r="AF12" s="16"/>
-      <c r="AG12" s="16"/>
-      <c r="AH12" s="16"/>
-      <c r="AI12" s="16"/>
-      <c r="AJ12" s="16"/>
-      <c r="AK12" s="16"/>
-      <c r="AL12" s="16"/>
-      <c r="AM12" s="16"/>
-      <c r="AN12" s="16"/>
-      <c r="AO12" s="16"/>
-      <c r="AP12" s="13"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="14"/>
+      <c r="Q12" s="14"/>
+      <c r="R12" s="14"/>
+      <c r="S12" s="14"/>
+      <c r="T12" s="14"/>
+      <c r="U12" s="14"/>
+      <c r="V12" s="14"/>
+      <c r="W12" s="14"/>
+      <c r="X12" s="14"/>
+      <c r="Y12" s="14"/>
+      <c r="Z12" s="14"/>
+      <c r="AA12" s="14"/>
+      <c r="AB12" s="14"/>
+      <c r="AC12" s="14"/>
+      <c r="AD12" s="14"/>
+      <c r="AE12" s="14"/>
+      <c r="AF12" s="14"/>
+      <c r="AG12" s="14"/>
+      <c r="AH12" s="14"/>
+      <c r="AI12" s="14"/>
+      <c r="AJ12" s="14"/>
+      <c r="AK12" s="14"/>
+      <c r="AL12" s="14"/>
+      <c r="AM12" s="14"/>
+      <c r="AN12" s="14"/>
+      <c r="AO12" s="14"/>
+      <c r="AP12" s="15"/>
     </row>
     <row r="13" spans="1:42">
-      <c r="A13" s="15"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="16"/>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="16"/>
-      <c r="R13" s="16"/>
-      <c r="S13" s="16"/>
-      <c r="T13" s="16"/>
-      <c r="U13" s="16"/>
-      <c r="V13" s="16"/>
-      <c r="W13" s="16"/>
-      <c r="X13" s="16"/>
-      <c r="Y13" s="16"/>
-      <c r="Z13" s="16"/>
-      <c r="AA13" s="16"/>
-      <c r="AB13" s="16"/>
-      <c r="AC13" s="16"/>
-      <c r="AD13" s="16"/>
-      <c r="AE13" s="16"/>
-      <c r="AF13" s="16"/>
-      <c r="AG13" s="16"/>
-      <c r="AH13" s="16"/>
-      <c r="AI13" s="16"/>
-      <c r="AJ13" s="16"/>
-      <c r="AK13" s="16"/>
-      <c r="AL13" s="16"/>
-      <c r="AM13" s="16"/>
-      <c r="AN13" s="16"/>
-      <c r="AO13" s="16"/>
-      <c r="AP13" s="13"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="14"/>
+      <c r="Q13" s="14"/>
+      <c r="R13" s="14"/>
+      <c r="S13" s="14"/>
+      <c r="T13" s="14"/>
+      <c r="U13" s="14"/>
+      <c r="V13" s="14"/>
+      <c r="W13" s="14"/>
+      <c r="X13" s="14"/>
+      <c r="Y13" s="14"/>
+      <c r="Z13" s="14"/>
+      <c r="AA13" s="14"/>
+      <c r="AB13" s="14"/>
+      <c r="AC13" s="14"/>
+      <c r="AD13" s="14"/>
+      <c r="AE13" s="14"/>
+      <c r="AF13" s="14"/>
+      <c r="AG13" s="14"/>
+      <c r="AH13" s="14"/>
+      <c r="AI13" s="14"/>
+      <c r="AJ13" s="14"/>
+      <c r="AK13" s="14"/>
+      <c r="AL13" s="14"/>
+      <c r="AM13" s="14"/>
+      <c r="AN13" s="14"/>
+      <c r="AO13" s="14"/>
+      <c r="AP13" s="15"/>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" s="2">
@@ -4412,33 +4486,6 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="AO11:AO13"/>
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="AN11:AN13"/>
-    <mergeCell ref="AE11:AE13"/>
-    <mergeCell ref="AF11:AF13"/>
-    <mergeCell ref="AG11:AG13"/>
-    <mergeCell ref="AH11:AH13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="Z11:Z13"/>
-    <mergeCell ref="AA11:AA13"/>
-    <mergeCell ref="AB11:AB13"/>
-    <mergeCell ref="AC11:AC13"/>
-    <mergeCell ref="AD11:AD13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="V11:V13"/>
-    <mergeCell ref="W11:W13"/>
-    <mergeCell ref="X11:X13"/>
-    <mergeCell ref="Y11:Y13"/>
-    <mergeCell ref="P11:P13"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="T11:T13"/>
     <mergeCell ref="A1:AP1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A11:A13"/>
@@ -4455,6 +4502,33 @@
     <mergeCell ref="M11:M13"/>
     <mergeCell ref="N11:N13"/>
     <mergeCell ref="O11:O13"/>
+    <mergeCell ref="P11:P13"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="T11:T13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="V11:V13"/>
+    <mergeCell ref="W11:W13"/>
+    <mergeCell ref="X11:X13"/>
+    <mergeCell ref="Y11:Y13"/>
+    <mergeCell ref="Z11:Z13"/>
+    <mergeCell ref="AA11:AA13"/>
+    <mergeCell ref="AB11:AB13"/>
+    <mergeCell ref="AC11:AC13"/>
+    <mergeCell ref="AD11:AD13"/>
+    <mergeCell ref="AE11:AE13"/>
+    <mergeCell ref="AF11:AF13"/>
+    <mergeCell ref="AG11:AG13"/>
+    <mergeCell ref="AH11:AH13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="AO11:AO13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
+    <mergeCell ref="AN11:AN13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ТКИ-341_Реверс_Инжиниринг.xlsx
+++ b/ТКИ-341_Реверс_Инжиниринг.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\Reverse_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E6E146F-C19B-4818-B5F9-EBE98908C860}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31552B86-B003-4FFD-AE86-4113765861B6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1290" yWindow="1170" windowWidth="23640" windowHeight="10035" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="50">
   <si>
     <t>ВЕДОМОСТЬ ПОСЕЩАЕМОСТИ ЗАНЯТИЙ СТУДЕНТАМИ ГРУППЫ ТКИ "Компьютерная безопасность" ИТТСУ РУТ (МИИТ)</t>
   </si>
@@ -204,6 +204,12 @@
   <si>
     <t>С, С++</t>
   </si>
+  <si>
+    <t>сопротивление параллельного соединения</t>
+  </si>
+  <si>
+    <t>расстояние между двумя точками на плоскости</t>
+  </si>
 </sst>
 </file>
 
@@ -234,12 +240,18 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -269,7 +281,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -303,9 +315,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -314,6 +323,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -600,57 +616,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="14.45" customHeight="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15"/>
-      <c r="U1" s="15"/>
-      <c r="V1" s="15"/>
-      <c r="W1" s="15"/>
-      <c r="X1" s="15"/>
-      <c r="Y1" s="15"/>
-      <c r="Z1" s="15"/>
-      <c r="AA1" s="15"/>
-      <c r="AB1" s="15"/>
-      <c r="AC1" s="15"/>
-      <c r="AD1" s="15"/>
-      <c r="AE1" s="15"/>
-      <c r="AF1" s="15"/>
-      <c r="AG1" s="15"/>
-      <c r="AH1" s="15"/>
-      <c r="AI1" s="15"/>
-      <c r="AJ1" s="15"/>
-      <c r="AK1" s="15"/>
-      <c r="AL1" s="15"/>
-      <c r="AM1" s="15"/>
-      <c r="AN1" s="15"/>
-      <c r="AO1" s="15"/>
-      <c r="AP1" s="15"/>
-      <c r="AQ1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
+      <c r="Y1" s="14"/>
+      <c r="Z1" s="14"/>
+      <c r="AA1" s="14"/>
+      <c r="AB1" s="14"/>
+      <c r="AC1" s="14"/>
+      <c r="AD1" s="14"/>
+      <c r="AE1" s="14"/>
+      <c r="AF1" s="14"/>
+      <c r="AG1" s="14"/>
+      <c r="AH1" s="14"/>
+      <c r="AI1" s="14"/>
+      <c r="AJ1" s="14"/>
+      <c r="AK1" s="14"/>
+      <c r="AL1" s="14"/>
+      <c r="AM1" s="14"/>
+      <c r="AN1" s="14"/>
+      <c r="AO1" s="14"/>
+      <c r="AP1" s="14"/>
+      <c r="AQ1" s="14"/>
     </row>
     <row r="2" spans="1:43" ht="27.6" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17"/>
+      <c r="B2" s="16"/>
       <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1196,23 +1212,23 @@
       <c r="X11" s="12"/>
       <c r="Y11" s="12"/>
       <c r="Z11" s="12"/>
-      <c r="AA11" s="14"/>
-      <c r="AB11" s="14"/>
-      <c r="AC11" s="14"/>
-      <c r="AD11" s="14"/>
-      <c r="AE11" s="14"/>
-      <c r="AF11" s="14"/>
-      <c r="AG11" s="14"/>
-      <c r="AH11" s="14"/>
-      <c r="AI11" s="14"/>
-      <c r="AJ11" s="14"/>
-      <c r="AK11" s="14"/>
-      <c r="AL11" s="14"/>
-      <c r="AM11" s="14"/>
-      <c r="AN11" s="14"/>
-      <c r="AO11" s="14"/>
-      <c r="AP11" s="14"/>
-      <c r="AQ11" s="15"/>
+      <c r="AA11" s="17"/>
+      <c r="AB11" s="17"/>
+      <c r="AC11" s="17"/>
+      <c r="AD11" s="17"/>
+      <c r="AE11" s="17"/>
+      <c r="AF11" s="17"/>
+      <c r="AG11" s="17"/>
+      <c r="AH11" s="17"/>
+      <c r="AI11" s="17"/>
+      <c r="AJ11" s="17"/>
+      <c r="AK11" s="17"/>
+      <c r="AL11" s="17"/>
+      <c r="AM11" s="17"/>
+      <c r="AN11" s="17"/>
+      <c r="AO11" s="17"/>
+      <c r="AP11" s="17"/>
+      <c r="AQ11" s="14"/>
     </row>
     <row r="12" spans="1:43">
       <c r="A12" s="2">
@@ -1253,35 +1269,37 @@
       <c r="X12" s="12"/>
       <c r="Y12" s="12"/>
       <c r="Z12" s="12"/>
-      <c r="AA12" s="14"/>
-      <c r="AB12" s="14"/>
-      <c r="AC12" s="14"/>
-      <c r="AD12" s="14"/>
-      <c r="AE12" s="14"/>
-      <c r="AF12" s="14"/>
-      <c r="AG12" s="14"/>
-      <c r="AH12" s="14"/>
-      <c r="AI12" s="14"/>
-      <c r="AJ12" s="14"/>
-      <c r="AK12" s="14"/>
-      <c r="AL12" s="14"/>
-      <c r="AM12" s="14"/>
-      <c r="AN12" s="14"/>
-      <c r="AO12" s="14"/>
-      <c r="AP12" s="14"/>
-      <c r="AQ12" s="15"/>
+      <c r="AA12" s="17"/>
+      <c r="AB12" s="17"/>
+      <c r="AC12" s="17"/>
+      <c r="AD12" s="17"/>
+      <c r="AE12" s="17"/>
+      <c r="AF12" s="17"/>
+      <c r="AG12" s="17"/>
+      <c r="AH12" s="17"/>
+      <c r="AI12" s="17"/>
+      <c r="AJ12" s="17"/>
+      <c r="AK12" s="17"/>
+      <c r="AL12" s="17"/>
+      <c r="AM12" s="17"/>
+      <c r="AN12" s="17"/>
+      <c r="AO12" s="17"/>
+      <c r="AP12" s="17"/>
+      <c r="AQ12" s="14"/>
     </row>
     <row r="13" spans="1:43">
       <c r="A13" s="2">
         <v>10</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="19" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="9">
         <v>10</v>
       </c>
-      <c r="D13" s="9"/>
+      <c r="D13" s="9" t="s">
+        <v>49</v>
+      </c>
       <c r="E13" s="2" t="s">
         <v>7</v>
       </c>
@@ -1304,7 +1322,7 @@
       <c r="R13" s="12"/>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
-      <c r="U13" s="10">
+      <c r="U13" s="18">
         <v>46072</v>
       </c>
       <c r="V13" s="12"/>
@@ -1312,23 +1330,23 @@
       <c r="X13" s="12"/>
       <c r="Y13" s="12"/>
       <c r="Z13" s="12"/>
-      <c r="AA13" s="14"/>
-      <c r="AB13" s="14"/>
-      <c r="AC13" s="14"/>
-      <c r="AD13" s="14"/>
-      <c r="AE13" s="14"/>
-      <c r="AF13" s="14"/>
-      <c r="AG13" s="14"/>
-      <c r="AH13" s="14"/>
-      <c r="AI13" s="14"/>
-      <c r="AJ13" s="14"/>
-      <c r="AK13" s="14"/>
-      <c r="AL13" s="14"/>
-      <c r="AM13" s="14"/>
-      <c r="AN13" s="14"/>
-      <c r="AO13" s="14"/>
-      <c r="AP13" s="14"/>
-      <c r="AQ13" s="15"/>
+      <c r="AA13" s="17"/>
+      <c r="AB13" s="17"/>
+      <c r="AC13" s="17"/>
+      <c r="AD13" s="17"/>
+      <c r="AE13" s="17"/>
+      <c r="AF13" s="17"/>
+      <c r="AG13" s="17"/>
+      <c r="AH13" s="17"/>
+      <c r="AI13" s="17"/>
+      <c r="AJ13" s="17"/>
+      <c r="AK13" s="17"/>
+      <c r="AL13" s="17"/>
+      <c r="AM13" s="17"/>
+      <c r="AN13" s="17"/>
+      <c r="AO13" s="17"/>
+      <c r="AP13" s="17"/>
+      <c r="AQ13" s="14"/>
     </row>
     <row r="14" spans="1:43">
       <c r="A14" s="2">
@@ -1819,7 +1837,7 @@
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
       <c r="T22" s="3"/>
-      <c r="U22" s="10">
+      <c r="U22" s="18">
         <v>46072</v>
       </c>
       <c r="V22" s="3"/>
@@ -1849,13 +1867,15 @@
       <c r="A23" s="2">
         <v>20</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="19" t="s">
         <v>27</v>
       </c>
       <c r="C23" s="9">
         <v>14</v>
       </c>
-      <c r="D23" s="9"/>
+      <c r="D23" s="9" t="s">
+        <v>48</v>
+      </c>
       <c r="E23" s="2" t="s">
         <v>7</v>
       </c>
@@ -1878,7 +1898,7 @@
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
-      <c r="U23" s="10">
+      <c r="U23" s="18">
         <v>46072</v>
       </c>
       <c r="V23" s="3"/>
@@ -2507,7 +2527,7 @@
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
-      <c r="U34" s="10">
+      <c r="U34" s="18">
         <v>46072</v>
       </c>
       <c r="V34" s="3"/>
@@ -2687,6 +2707,9 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
     <mergeCell ref="A1:AQ1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="AA11:AA13"/>
@@ -2703,9 +2726,6 @@
     <mergeCell ref="AQ11:AQ13"/>
     <mergeCell ref="AI11:AI13"/>
     <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2717,56 +2737,56 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15"/>
-      <c r="U1" s="15"/>
-      <c r="V1" s="15"/>
-      <c r="W1" s="15"/>
-      <c r="X1" s="15"/>
-      <c r="Y1" s="15"/>
-      <c r="Z1" s="15"/>
-      <c r="AA1" s="15"/>
-      <c r="AB1" s="15"/>
-      <c r="AC1" s="15"/>
-      <c r="AD1" s="15"/>
-      <c r="AE1" s="15"/>
-      <c r="AF1" s="15"/>
-      <c r="AG1" s="15"/>
-      <c r="AH1" s="15"/>
-      <c r="AI1" s="15"/>
-      <c r="AJ1" s="15"/>
-      <c r="AK1" s="15"/>
-      <c r="AL1" s="15"/>
-      <c r="AM1" s="15"/>
-      <c r="AN1" s="15"/>
-      <c r="AO1" s="15"/>
-      <c r="AP1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
+      <c r="Y1" s="14"/>
+      <c r="Z1" s="14"/>
+      <c r="AA1" s="14"/>
+      <c r="AB1" s="14"/>
+      <c r="AC1" s="14"/>
+      <c r="AD1" s="14"/>
+      <c r="AE1" s="14"/>
+      <c r="AF1" s="14"/>
+      <c r="AG1" s="14"/>
+      <c r="AH1" s="14"/>
+      <c r="AI1" s="14"/>
+      <c r="AJ1" s="14"/>
+      <c r="AK1" s="14"/>
+      <c r="AL1" s="14"/>
+      <c r="AM1" s="14"/>
+      <c r="AN1" s="14"/>
+      <c r="AO1" s="14"/>
+      <c r="AP1" s="14"/>
     </row>
     <row r="2" spans="1:42" ht="30">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17"/>
+      <c r="B2" s="16"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -3195,142 +3215,142 @@
       <c r="AP10" s="1"/>
     </row>
     <row r="11" spans="1:42">
-      <c r="A11" s="17">
+      <c r="A11" s="16">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="14"/>
-      <c r="O11" s="14"/>
-      <c r="P11" s="14"/>
-      <c r="Q11" s="14"/>
-      <c r="R11" s="14"/>
-      <c r="S11" s="14"/>
-      <c r="T11" s="14"/>
-      <c r="U11" s="14"/>
-      <c r="V11" s="14"/>
-      <c r="W11" s="14"/>
-      <c r="X11" s="14"/>
-      <c r="Y11" s="14"/>
-      <c r="Z11" s="14"/>
-      <c r="AA11" s="14"/>
-      <c r="AB11" s="14"/>
-      <c r="AC11" s="14"/>
-      <c r="AD11" s="14"/>
-      <c r="AE11" s="14"/>
-      <c r="AF11" s="14"/>
-      <c r="AG11" s="14"/>
-      <c r="AH11" s="14"/>
-      <c r="AI11" s="14"/>
-      <c r="AJ11" s="14"/>
-      <c r="AK11" s="14"/>
-      <c r="AL11" s="14"/>
-      <c r="AM11" s="14"/>
-      <c r="AN11" s="14"/>
-      <c r="AO11" s="14"/>
-      <c r="AP11" s="15"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="17"/>
+      <c r="U11" s="17"/>
+      <c r="V11" s="17"/>
+      <c r="W11" s="17"/>
+      <c r="X11" s="17"/>
+      <c r="Y11" s="17"/>
+      <c r="Z11" s="17"/>
+      <c r="AA11" s="17"/>
+      <c r="AB11" s="17"/>
+      <c r="AC11" s="17"/>
+      <c r="AD11" s="17"/>
+      <c r="AE11" s="17"/>
+      <c r="AF11" s="17"/>
+      <c r="AG11" s="17"/>
+      <c r="AH11" s="17"/>
+      <c r="AI11" s="17"/>
+      <c r="AJ11" s="17"/>
+      <c r="AK11" s="17"/>
+      <c r="AL11" s="17"/>
+      <c r="AM11" s="17"/>
+      <c r="AN11" s="17"/>
+      <c r="AO11" s="17"/>
+      <c r="AP11" s="14"/>
     </row>
     <row r="12" spans="1:42">
-      <c r="A12" s="17"/>
+      <c r="A12" s="16"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="14"/>
-      <c r="Q12" s="14"/>
-      <c r="R12" s="14"/>
-      <c r="S12" s="14"/>
-      <c r="T12" s="14"/>
-      <c r="U12" s="14"/>
-      <c r="V12" s="14"/>
-      <c r="W12" s="14"/>
-      <c r="X12" s="14"/>
-      <c r="Y12" s="14"/>
-      <c r="Z12" s="14"/>
-      <c r="AA12" s="14"/>
-      <c r="AB12" s="14"/>
-      <c r="AC12" s="14"/>
-      <c r="AD12" s="14"/>
-      <c r="AE12" s="14"/>
-      <c r="AF12" s="14"/>
-      <c r="AG12" s="14"/>
-      <c r="AH12" s="14"/>
-      <c r="AI12" s="14"/>
-      <c r="AJ12" s="14"/>
-      <c r="AK12" s="14"/>
-      <c r="AL12" s="14"/>
-      <c r="AM12" s="14"/>
-      <c r="AN12" s="14"/>
-      <c r="AO12" s="14"/>
-      <c r="AP12" s="15"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="17"/>
+      <c r="S12" s="17"/>
+      <c r="T12" s="17"/>
+      <c r="U12" s="17"/>
+      <c r="V12" s="17"/>
+      <c r="W12" s="17"/>
+      <c r="X12" s="17"/>
+      <c r="Y12" s="17"/>
+      <c r="Z12" s="17"/>
+      <c r="AA12" s="17"/>
+      <c r="AB12" s="17"/>
+      <c r="AC12" s="17"/>
+      <c r="AD12" s="17"/>
+      <c r="AE12" s="17"/>
+      <c r="AF12" s="17"/>
+      <c r="AG12" s="17"/>
+      <c r="AH12" s="17"/>
+      <c r="AI12" s="17"/>
+      <c r="AJ12" s="17"/>
+      <c r="AK12" s="17"/>
+      <c r="AL12" s="17"/>
+      <c r="AM12" s="17"/>
+      <c r="AN12" s="17"/>
+      <c r="AO12" s="17"/>
+      <c r="AP12" s="14"/>
     </row>
     <row r="13" spans="1:42">
-      <c r="A13" s="17"/>
+      <c r="A13" s="16"/>
       <c r="B13" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="14"/>
-      <c r="P13" s="14"/>
-      <c r="Q13" s="14"/>
-      <c r="R13" s="14"/>
-      <c r="S13" s="14"/>
-      <c r="T13" s="14"/>
-      <c r="U13" s="14"/>
-      <c r="V13" s="14"/>
-      <c r="W13" s="14"/>
-      <c r="X13" s="14"/>
-      <c r="Y13" s="14"/>
-      <c r="Z13" s="14"/>
-      <c r="AA13" s="14"/>
-      <c r="AB13" s="14"/>
-      <c r="AC13" s="14"/>
-      <c r="AD13" s="14"/>
-      <c r="AE13" s="14"/>
-      <c r="AF13" s="14"/>
-      <c r="AG13" s="14"/>
-      <c r="AH13" s="14"/>
-      <c r="AI13" s="14"/>
-      <c r="AJ13" s="14"/>
-      <c r="AK13" s="14"/>
-      <c r="AL13" s="14"/>
-      <c r="AM13" s="14"/>
-      <c r="AN13" s="14"/>
-      <c r="AO13" s="14"/>
-      <c r="AP13" s="15"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="17"/>
+      <c r="S13" s="17"/>
+      <c r="T13" s="17"/>
+      <c r="U13" s="17"/>
+      <c r="V13" s="17"/>
+      <c r="W13" s="17"/>
+      <c r="X13" s="17"/>
+      <c r="Y13" s="17"/>
+      <c r="Z13" s="17"/>
+      <c r="AA13" s="17"/>
+      <c r="AB13" s="17"/>
+      <c r="AC13" s="17"/>
+      <c r="AD13" s="17"/>
+      <c r="AE13" s="17"/>
+      <c r="AF13" s="17"/>
+      <c r="AG13" s="17"/>
+      <c r="AH13" s="17"/>
+      <c r="AI13" s="17"/>
+      <c r="AJ13" s="17"/>
+      <c r="AK13" s="17"/>
+      <c r="AL13" s="17"/>
+      <c r="AM13" s="17"/>
+      <c r="AN13" s="17"/>
+      <c r="AO13" s="17"/>
+      <c r="AP13" s="14"/>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" s="2">
@@ -4486,6 +4506,33 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="AO11:AO13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
+    <mergeCell ref="AN11:AN13"/>
+    <mergeCell ref="AE11:AE13"/>
+    <mergeCell ref="AF11:AF13"/>
+    <mergeCell ref="AG11:AG13"/>
+    <mergeCell ref="AH11:AH13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="Z11:Z13"/>
+    <mergeCell ref="AA11:AA13"/>
+    <mergeCell ref="AB11:AB13"/>
+    <mergeCell ref="AC11:AC13"/>
+    <mergeCell ref="AD11:AD13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="V11:V13"/>
+    <mergeCell ref="W11:W13"/>
+    <mergeCell ref="X11:X13"/>
+    <mergeCell ref="Y11:Y13"/>
+    <mergeCell ref="P11:P13"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="T11:T13"/>
     <mergeCell ref="A1:AP1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A11:A13"/>
@@ -4502,33 +4549,6 @@
     <mergeCell ref="M11:M13"/>
     <mergeCell ref="N11:N13"/>
     <mergeCell ref="O11:O13"/>
-    <mergeCell ref="P11:P13"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="T11:T13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="V11:V13"/>
-    <mergeCell ref="W11:W13"/>
-    <mergeCell ref="X11:X13"/>
-    <mergeCell ref="Y11:Y13"/>
-    <mergeCell ref="Z11:Z13"/>
-    <mergeCell ref="AA11:AA13"/>
-    <mergeCell ref="AB11:AB13"/>
-    <mergeCell ref="AC11:AC13"/>
-    <mergeCell ref="AD11:AD13"/>
-    <mergeCell ref="AE11:AE13"/>
-    <mergeCell ref="AF11:AF13"/>
-    <mergeCell ref="AG11:AG13"/>
-    <mergeCell ref="AH11:AH13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="AO11:AO13"/>
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="AN11:AN13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ТКИ-341_Реверс_Инжиниринг.xlsx
+++ b/ТКИ-341_Реверс_Инжиниринг.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\Reverse_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31552B86-B003-4FFD-AE86-4113765861B6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9422486-19A0-44D9-A049-A8C94251E87D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="54">
   <si>
     <t>ВЕДОМОСТЬ ПОСЕЩАЕМОСТИ ЗАНЯТИЙ СТУДЕНТАМИ ГРУППЫ ТКИ "Компьютерная безопасность" ИТТСУ РУТ (МИИТ)</t>
   </si>
@@ -209,6 +209,18 @@
   </si>
   <si>
     <t>расстояние между двумя точками на плоскости</t>
+  </si>
+  <si>
+    <t>сортировка пузырьком</t>
+  </si>
+  <si>
+    <t>ввод массива и сумма элементов</t>
+  </si>
+  <si>
+    <t>ввод массива и сумма элементов, имеющих нечетные значения</t>
+  </si>
+  <si>
+    <t>расчет потенциальной энергии пружины</t>
   </si>
 </sst>
 </file>
@@ -314,6 +326,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -323,13 +342,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -616,57 +628,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="14.45" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="14"/>
-      <c r="U1" s="14"/>
-      <c r="V1" s="14"/>
-      <c r="W1" s="14"/>
-      <c r="X1" s="14"/>
-      <c r="Y1" s="14"/>
-      <c r="Z1" s="14"/>
-      <c r="AA1" s="14"/>
-      <c r="AB1" s="14"/>
-      <c r="AC1" s="14"/>
-      <c r="AD1" s="14"/>
-      <c r="AE1" s="14"/>
-      <c r="AF1" s="14"/>
-      <c r="AG1" s="14"/>
-      <c r="AH1" s="14"/>
-      <c r="AI1" s="14"/>
-      <c r="AJ1" s="14"/>
-      <c r="AK1" s="14"/>
-      <c r="AL1" s="14"/>
-      <c r="AM1" s="14"/>
-      <c r="AN1" s="14"/>
-      <c r="AO1" s="14"/>
-      <c r="AP1" s="14"/>
-      <c r="AQ1" s="14"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
+      <c r="S1" s="17"/>
+      <c r="T1" s="17"/>
+      <c r="U1" s="17"/>
+      <c r="V1" s="17"/>
+      <c r="W1" s="17"/>
+      <c r="X1" s="17"/>
+      <c r="Y1" s="17"/>
+      <c r="Z1" s="17"/>
+      <c r="AA1" s="17"/>
+      <c r="AB1" s="17"/>
+      <c r="AC1" s="17"/>
+      <c r="AD1" s="17"/>
+      <c r="AE1" s="17"/>
+      <c r="AF1" s="17"/>
+      <c r="AG1" s="17"/>
+      <c r="AH1" s="17"/>
+      <c r="AI1" s="17"/>
+      <c r="AJ1" s="17"/>
+      <c r="AK1" s="17"/>
+      <c r="AL1" s="17"/>
+      <c r="AM1" s="17"/>
+      <c r="AN1" s="17"/>
+      <c r="AO1" s="17"/>
+      <c r="AP1" s="17"/>
+      <c r="AQ1" s="17"/>
     </row>
     <row r="2" spans="1:43" ht="27.6" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="16"/>
+      <c r="B2" s="19"/>
       <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1126,7 +1138,9 @@
       <c r="C10" s="9">
         <v>7</v>
       </c>
-      <c r="D10" s="9"/>
+      <c r="D10" s="9" t="s">
+        <v>51</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>7</v>
       </c>
@@ -1212,35 +1226,37 @@
       <c r="X11" s="12"/>
       <c r="Y11" s="12"/>
       <c r="Z11" s="12"/>
-      <c r="AA11" s="17"/>
-      <c r="AB11" s="17"/>
-      <c r="AC11" s="17"/>
-      <c r="AD11" s="17"/>
-      <c r="AE11" s="17"/>
-      <c r="AF11" s="17"/>
-      <c r="AG11" s="17"/>
-      <c r="AH11" s="17"/>
-      <c r="AI11" s="17"/>
-      <c r="AJ11" s="17"/>
-      <c r="AK11" s="17"/>
-      <c r="AL11" s="17"/>
-      <c r="AM11" s="17"/>
-      <c r="AN11" s="17"/>
-      <c r="AO11" s="17"/>
-      <c r="AP11" s="17"/>
-      <c r="AQ11" s="14"/>
+      <c r="AA11" s="16"/>
+      <c r="AB11" s="16"/>
+      <c r="AC11" s="16"/>
+      <c r="AD11" s="16"/>
+      <c r="AE11" s="16"/>
+      <c r="AF11" s="16"/>
+      <c r="AG11" s="16"/>
+      <c r="AH11" s="16"/>
+      <c r="AI11" s="16"/>
+      <c r="AJ11" s="16"/>
+      <c r="AK11" s="16"/>
+      <c r="AL11" s="16"/>
+      <c r="AM11" s="16"/>
+      <c r="AN11" s="16"/>
+      <c r="AO11" s="16"/>
+      <c r="AP11" s="16"/>
+      <c r="AQ11" s="17"/>
     </row>
     <row r="12" spans="1:43">
       <c r="A12" s="2">
         <v>9</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="15" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="9">
         <v>9</v>
       </c>
-      <c r="D12" s="9"/>
+      <c r="D12" s="9" t="s">
+        <v>53</v>
+      </c>
       <c r="E12" s="2" t="s">
         <v>7</v>
       </c>
@@ -1263,35 +1279,37 @@
       <c r="R12" s="12"/>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
+      <c r="U12" s="14">
+        <v>46072</v>
+      </c>
       <c r="V12" s="12"/>
       <c r="W12" s="12"/>
       <c r="X12" s="12"/>
       <c r="Y12" s="12"/>
       <c r="Z12" s="12"/>
-      <c r="AA12" s="17"/>
-      <c r="AB12" s="17"/>
-      <c r="AC12" s="17"/>
-      <c r="AD12" s="17"/>
-      <c r="AE12" s="17"/>
-      <c r="AF12" s="17"/>
-      <c r="AG12" s="17"/>
-      <c r="AH12" s="17"/>
-      <c r="AI12" s="17"/>
-      <c r="AJ12" s="17"/>
-      <c r="AK12" s="17"/>
-      <c r="AL12" s="17"/>
-      <c r="AM12" s="17"/>
-      <c r="AN12" s="17"/>
-      <c r="AO12" s="17"/>
-      <c r="AP12" s="17"/>
-      <c r="AQ12" s="14"/>
+      <c r="AA12" s="16"/>
+      <c r="AB12" s="16"/>
+      <c r="AC12" s="16"/>
+      <c r="AD12" s="16"/>
+      <c r="AE12" s="16"/>
+      <c r="AF12" s="16"/>
+      <c r="AG12" s="16"/>
+      <c r="AH12" s="16"/>
+      <c r="AI12" s="16"/>
+      <c r="AJ12" s="16"/>
+      <c r="AK12" s="16"/>
+      <c r="AL12" s="16"/>
+      <c r="AM12" s="16"/>
+      <c r="AN12" s="16"/>
+      <c r="AO12" s="16"/>
+      <c r="AP12" s="16"/>
+      <c r="AQ12" s="17"/>
     </row>
     <row r="13" spans="1:43">
       <c r="A13" s="2">
         <v>10</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="15" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="9">
@@ -1322,7 +1340,7 @@
       <c r="R13" s="12"/>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
-      <c r="U13" s="18">
+      <c r="U13" s="14">
         <v>46072</v>
       </c>
       <c r="V13" s="12"/>
@@ -1330,23 +1348,23 @@
       <c r="X13" s="12"/>
       <c r="Y13" s="12"/>
       <c r="Z13" s="12"/>
-      <c r="AA13" s="17"/>
-      <c r="AB13" s="17"/>
-      <c r="AC13" s="17"/>
-      <c r="AD13" s="17"/>
-      <c r="AE13" s="17"/>
-      <c r="AF13" s="17"/>
-      <c r="AG13" s="17"/>
-      <c r="AH13" s="17"/>
-      <c r="AI13" s="17"/>
-      <c r="AJ13" s="17"/>
-      <c r="AK13" s="17"/>
-      <c r="AL13" s="17"/>
-      <c r="AM13" s="17"/>
-      <c r="AN13" s="17"/>
-      <c r="AO13" s="17"/>
-      <c r="AP13" s="17"/>
-      <c r="AQ13" s="14"/>
+      <c r="AA13" s="16"/>
+      <c r="AB13" s="16"/>
+      <c r="AC13" s="16"/>
+      <c r="AD13" s="16"/>
+      <c r="AE13" s="16"/>
+      <c r="AF13" s="16"/>
+      <c r="AG13" s="16"/>
+      <c r="AH13" s="16"/>
+      <c r="AI13" s="16"/>
+      <c r="AJ13" s="16"/>
+      <c r="AK13" s="16"/>
+      <c r="AL13" s="16"/>
+      <c r="AM13" s="16"/>
+      <c r="AN13" s="16"/>
+      <c r="AO13" s="16"/>
+      <c r="AP13" s="16"/>
+      <c r="AQ13" s="17"/>
     </row>
     <row r="14" spans="1:43">
       <c r="A14" s="2">
@@ -1495,7 +1513,9 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
+      <c r="U16" s="14">
+        <v>46072</v>
+      </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
@@ -1523,13 +1543,15 @@
       <c r="A17" s="2">
         <v>14</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="15" t="s">
         <v>20</v>
       </c>
       <c r="C17" s="9">
         <v>13</v>
       </c>
-      <c r="D17" s="9"/>
+      <c r="D17" s="9" t="s">
+        <v>52</v>
+      </c>
       <c r="E17" s="2" t="s">
         <v>7</v>
       </c>
@@ -1552,7 +1574,9 @@
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
       <c r="T17" s="3"/>
-      <c r="U17" s="3"/>
+      <c r="U17" s="14">
+        <v>46072</v>
+      </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
       <c r="X17" s="3"/>
@@ -1837,7 +1861,7 @@
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
       <c r="T22" s="3"/>
-      <c r="U22" s="18">
+      <c r="U22" s="14">
         <v>46072</v>
       </c>
       <c r="V22" s="3"/>
@@ -1867,7 +1891,7 @@
       <c r="A23" s="2">
         <v>20</v>
       </c>
-      <c r="B23" s="19" t="s">
+      <c r="B23" s="15" t="s">
         <v>27</v>
       </c>
       <c r="C23" s="9">
@@ -1898,7 +1922,7 @@
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
-      <c r="U23" s="18">
+      <c r="U23" s="14">
         <v>46072</v>
       </c>
       <c r="V23" s="3"/>
@@ -2014,7 +2038,9 @@
       <c r="R25" s="3"/>
       <c r="S25" s="3"/>
       <c r="T25" s="3"/>
-      <c r="U25" s="3"/>
+      <c r="U25" s="14">
+        <v>46072</v>
+      </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
@@ -2242,7 +2268,9 @@
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
-      <c r="U29" s="3"/>
+      <c r="U29" s="14">
+        <v>46072</v>
+      </c>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
@@ -2270,13 +2298,15 @@
       <c r="A30" s="2">
         <v>27</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="15" t="s">
         <v>34</v>
       </c>
       <c r="C30" s="9">
         <v>12</v>
       </c>
-      <c r="D30" s="9"/>
+      <c r="D30" s="9" t="s">
+        <v>50</v>
+      </c>
       <c r="E30" s="2" t="s">
         <v>7</v>
       </c>
@@ -2299,7 +2329,9 @@
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
-      <c r="U30" s="3"/>
+      <c r="U30" s="14">
+        <v>46072</v>
+      </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
@@ -2527,7 +2559,7 @@
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
-      <c r="U34" s="18">
+      <c r="U34" s="14">
         <v>46072</v>
       </c>
       <c r="V34" s="3"/>
@@ -2707,6 +2739,9 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="AQ11:AQ13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="AJ11:AJ13"/>
     <mergeCell ref="AK11:AK13"/>
     <mergeCell ref="AL11:AL13"/>
     <mergeCell ref="AM11:AM13"/>
@@ -2723,9 +2758,6 @@
     <mergeCell ref="AN11:AN13"/>
     <mergeCell ref="AO11:AO13"/>
     <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AQ11:AQ13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="AJ11:AJ13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2737,56 +2769,56 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="14"/>
-      <c r="U1" s="14"/>
-      <c r="V1" s="14"/>
-      <c r="W1" s="14"/>
-      <c r="X1" s="14"/>
-      <c r="Y1" s="14"/>
-      <c r="Z1" s="14"/>
-      <c r="AA1" s="14"/>
-      <c r="AB1" s="14"/>
-      <c r="AC1" s="14"/>
-      <c r="AD1" s="14"/>
-      <c r="AE1" s="14"/>
-      <c r="AF1" s="14"/>
-      <c r="AG1" s="14"/>
-      <c r="AH1" s="14"/>
-      <c r="AI1" s="14"/>
-      <c r="AJ1" s="14"/>
-      <c r="AK1" s="14"/>
-      <c r="AL1" s="14"/>
-      <c r="AM1" s="14"/>
-      <c r="AN1" s="14"/>
-      <c r="AO1" s="14"/>
-      <c r="AP1" s="14"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
+      <c r="S1" s="17"/>
+      <c r="T1" s="17"/>
+      <c r="U1" s="17"/>
+      <c r="V1" s="17"/>
+      <c r="W1" s="17"/>
+      <c r="X1" s="17"/>
+      <c r="Y1" s="17"/>
+      <c r="Z1" s="17"/>
+      <c r="AA1" s="17"/>
+      <c r="AB1" s="17"/>
+      <c r="AC1" s="17"/>
+      <c r="AD1" s="17"/>
+      <c r="AE1" s="17"/>
+      <c r="AF1" s="17"/>
+      <c r="AG1" s="17"/>
+      <c r="AH1" s="17"/>
+      <c r="AI1" s="17"/>
+      <c r="AJ1" s="17"/>
+      <c r="AK1" s="17"/>
+      <c r="AL1" s="17"/>
+      <c r="AM1" s="17"/>
+      <c r="AN1" s="17"/>
+      <c r="AO1" s="17"/>
+      <c r="AP1" s="17"/>
     </row>
     <row r="2" spans="1:42" ht="30">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="16"/>
+      <c r="B2" s="19"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -3215,142 +3247,142 @@
       <c r="AP10" s="1"/>
     </row>
     <row r="11" spans="1:42">
-      <c r="A11" s="16">
+      <c r="A11" s="19">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="17"/>
-      <c r="Q11" s="17"/>
-      <c r="R11" s="17"/>
-      <c r="S11" s="17"/>
-      <c r="T11" s="17"/>
-      <c r="U11" s="17"/>
-      <c r="V11" s="17"/>
-      <c r="W11" s="17"/>
-      <c r="X11" s="17"/>
-      <c r="Y11" s="17"/>
-      <c r="Z11" s="17"/>
-      <c r="AA11" s="17"/>
-      <c r="AB11" s="17"/>
-      <c r="AC11" s="17"/>
-      <c r="AD11" s="17"/>
-      <c r="AE11" s="17"/>
-      <c r="AF11" s="17"/>
-      <c r="AG11" s="17"/>
-      <c r="AH11" s="17"/>
-      <c r="AI11" s="17"/>
-      <c r="AJ11" s="17"/>
-      <c r="AK11" s="17"/>
-      <c r="AL11" s="17"/>
-      <c r="AM11" s="17"/>
-      <c r="AN11" s="17"/>
-      <c r="AO11" s="17"/>
-      <c r="AP11" s="14"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="16"/>
+      <c r="R11" s="16"/>
+      <c r="S11" s="16"/>
+      <c r="T11" s="16"/>
+      <c r="U11" s="16"/>
+      <c r="V11" s="16"/>
+      <c r="W11" s="16"/>
+      <c r="X11" s="16"/>
+      <c r="Y11" s="16"/>
+      <c r="Z11" s="16"/>
+      <c r="AA11" s="16"/>
+      <c r="AB11" s="16"/>
+      <c r="AC11" s="16"/>
+      <c r="AD11" s="16"/>
+      <c r="AE11" s="16"/>
+      <c r="AF11" s="16"/>
+      <c r="AG11" s="16"/>
+      <c r="AH11" s="16"/>
+      <c r="AI11" s="16"/>
+      <c r="AJ11" s="16"/>
+      <c r="AK11" s="16"/>
+      <c r="AL11" s="16"/>
+      <c r="AM11" s="16"/>
+      <c r="AN11" s="16"/>
+      <c r="AO11" s="16"/>
+      <c r="AP11" s="17"/>
     </row>
     <row r="12" spans="1:42">
-      <c r="A12" s="16"/>
+      <c r="A12" s="19"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="17"/>
-      <c r="R12" s="17"/>
-      <c r="S12" s="17"/>
-      <c r="T12" s="17"/>
-      <c r="U12" s="17"/>
-      <c r="V12" s="17"/>
-      <c r="W12" s="17"/>
-      <c r="X12" s="17"/>
-      <c r="Y12" s="17"/>
-      <c r="Z12" s="17"/>
-      <c r="AA12" s="17"/>
-      <c r="AB12" s="17"/>
-      <c r="AC12" s="17"/>
-      <c r="AD12" s="17"/>
-      <c r="AE12" s="17"/>
-      <c r="AF12" s="17"/>
-      <c r="AG12" s="17"/>
-      <c r="AH12" s="17"/>
-      <c r="AI12" s="17"/>
-      <c r="AJ12" s="17"/>
-      <c r="AK12" s="17"/>
-      <c r="AL12" s="17"/>
-      <c r="AM12" s="17"/>
-      <c r="AN12" s="17"/>
-      <c r="AO12" s="17"/>
-      <c r="AP12" s="14"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="16"/>
+      <c r="T12" s="16"/>
+      <c r="U12" s="16"/>
+      <c r="V12" s="16"/>
+      <c r="W12" s="16"/>
+      <c r="X12" s="16"/>
+      <c r="Y12" s="16"/>
+      <c r="Z12" s="16"/>
+      <c r="AA12" s="16"/>
+      <c r="AB12" s="16"/>
+      <c r="AC12" s="16"/>
+      <c r="AD12" s="16"/>
+      <c r="AE12" s="16"/>
+      <c r="AF12" s="16"/>
+      <c r="AG12" s="16"/>
+      <c r="AH12" s="16"/>
+      <c r="AI12" s="16"/>
+      <c r="AJ12" s="16"/>
+      <c r="AK12" s="16"/>
+      <c r="AL12" s="16"/>
+      <c r="AM12" s="16"/>
+      <c r="AN12" s="16"/>
+      <c r="AO12" s="16"/>
+      <c r="AP12" s="17"/>
     </row>
     <row r="13" spans="1:42">
-      <c r="A13" s="16"/>
+      <c r="A13" s="19"/>
       <c r="B13" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="17"/>
-      <c r="R13" s="17"/>
-      <c r="S13" s="17"/>
-      <c r="T13" s="17"/>
-      <c r="U13" s="17"/>
-      <c r="V13" s="17"/>
-      <c r="W13" s="17"/>
-      <c r="X13" s="17"/>
-      <c r="Y13" s="17"/>
-      <c r="Z13" s="17"/>
-      <c r="AA13" s="17"/>
-      <c r="AB13" s="17"/>
-      <c r="AC13" s="17"/>
-      <c r="AD13" s="17"/>
-      <c r="AE13" s="17"/>
-      <c r="AF13" s="17"/>
-      <c r="AG13" s="17"/>
-      <c r="AH13" s="17"/>
-      <c r="AI13" s="17"/>
-      <c r="AJ13" s="17"/>
-      <c r="AK13" s="17"/>
-      <c r="AL13" s="17"/>
-      <c r="AM13" s="17"/>
-      <c r="AN13" s="17"/>
-      <c r="AO13" s="17"/>
-      <c r="AP13" s="14"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="16"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="16"/>
+      <c r="R13" s="16"/>
+      <c r="S13" s="16"/>
+      <c r="T13" s="16"/>
+      <c r="U13" s="16"/>
+      <c r="V13" s="16"/>
+      <c r="W13" s="16"/>
+      <c r="X13" s="16"/>
+      <c r="Y13" s="16"/>
+      <c r="Z13" s="16"/>
+      <c r="AA13" s="16"/>
+      <c r="AB13" s="16"/>
+      <c r="AC13" s="16"/>
+      <c r="AD13" s="16"/>
+      <c r="AE13" s="16"/>
+      <c r="AF13" s="16"/>
+      <c r="AG13" s="16"/>
+      <c r="AH13" s="16"/>
+      <c r="AI13" s="16"/>
+      <c r="AJ13" s="16"/>
+      <c r="AK13" s="16"/>
+      <c r="AL13" s="16"/>
+      <c r="AM13" s="16"/>
+      <c r="AN13" s="16"/>
+      <c r="AO13" s="16"/>
+      <c r="AP13" s="17"/>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" s="2">
@@ -4506,33 +4538,6 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="AO11:AO13"/>
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="AN11:AN13"/>
-    <mergeCell ref="AE11:AE13"/>
-    <mergeCell ref="AF11:AF13"/>
-    <mergeCell ref="AG11:AG13"/>
-    <mergeCell ref="AH11:AH13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="Z11:Z13"/>
-    <mergeCell ref="AA11:AA13"/>
-    <mergeCell ref="AB11:AB13"/>
-    <mergeCell ref="AC11:AC13"/>
-    <mergeCell ref="AD11:AD13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="V11:V13"/>
-    <mergeCell ref="W11:W13"/>
-    <mergeCell ref="X11:X13"/>
-    <mergeCell ref="Y11:Y13"/>
-    <mergeCell ref="P11:P13"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="T11:T13"/>
     <mergeCell ref="A1:AP1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A11:A13"/>
@@ -4549,6 +4554,33 @@
     <mergeCell ref="M11:M13"/>
     <mergeCell ref="N11:N13"/>
     <mergeCell ref="O11:O13"/>
+    <mergeCell ref="P11:P13"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="T11:T13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="V11:V13"/>
+    <mergeCell ref="W11:W13"/>
+    <mergeCell ref="X11:X13"/>
+    <mergeCell ref="Y11:Y13"/>
+    <mergeCell ref="Z11:Z13"/>
+    <mergeCell ref="AA11:AA13"/>
+    <mergeCell ref="AB11:AB13"/>
+    <mergeCell ref="AC11:AC13"/>
+    <mergeCell ref="AD11:AD13"/>
+    <mergeCell ref="AE11:AE13"/>
+    <mergeCell ref="AF11:AF13"/>
+    <mergeCell ref="AG11:AG13"/>
+    <mergeCell ref="AH11:AH13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="AO11:AO13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
+    <mergeCell ref="AN11:AN13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ТКИ-341_Реверс_Инжиниринг.xlsx
+++ b/ТКИ-341_Реверс_Инжиниринг.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\Reverse_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9422486-19A0-44D9-A049-A8C94251E87D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F905EE3-EEDC-47A3-B2EA-F1321C22099F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="55">
   <si>
     <t>ВЕДОМОСТЬ ПОСЕЩАЕМОСТИ ЗАНЯТИЙ СТУДЕНТАМИ ГРУППЫ ТКИ "Компьютерная безопасность" ИТТСУ РУТ (МИИТ)</t>
   </si>
@@ -221,6 +221,9 @@
   </si>
   <si>
     <t>расчет потенциальной энергии пружины</t>
+  </si>
+  <si>
+    <t>расчет геометрической прогрессии</t>
   </si>
 </sst>
 </file>
@@ -331,10 +334,10 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -628,51 +631,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="14.45" customHeight="1">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
+      <c r="B1" s="16"/>
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="17"/>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17"/>
-      <c r="AD1" s="17"/>
-      <c r="AE1" s="17"/>
-      <c r="AF1" s="17"/>
-      <c r="AG1" s="17"/>
-      <c r="AH1" s="17"/>
-      <c r="AI1" s="17"/>
-      <c r="AJ1" s="17"/>
-      <c r="AK1" s="17"/>
-      <c r="AL1" s="17"/>
-      <c r="AM1" s="17"/>
-      <c r="AN1" s="17"/>
-      <c r="AO1" s="17"/>
-      <c r="AP1" s="17"/>
-      <c r="AQ1" s="17"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+      <c r="S1" s="16"/>
+      <c r="T1" s="16"/>
+      <c r="U1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="16"/>
+      <c r="Y1" s="16"/>
+      <c r="Z1" s="16"/>
+      <c r="AA1" s="16"/>
+      <c r="AB1" s="16"/>
+      <c r="AC1" s="16"/>
+      <c r="AD1" s="16"/>
+      <c r="AE1" s="16"/>
+      <c r="AF1" s="16"/>
+      <c r="AG1" s="16"/>
+      <c r="AH1" s="16"/>
+      <c r="AI1" s="16"/>
+      <c r="AJ1" s="16"/>
+      <c r="AK1" s="16"/>
+      <c r="AL1" s="16"/>
+      <c r="AM1" s="16"/>
+      <c r="AN1" s="16"/>
+      <c r="AO1" s="16"/>
+      <c r="AP1" s="16"/>
+      <c r="AQ1" s="16"/>
     </row>
     <row r="2" spans="1:43" ht="27.6" customHeight="1">
       <c r="A2" s="19" t="s">
@@ -933,7 +936,9 @@
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
       <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
+      <c r="U6" s="14">
+        <v>46072</v>
+      </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
@@ -1226,23 +1231,23 @@
       <c r="X11" s="12"/>
       <c r="Y11" s="12"/>
       <c r="Z11" s="12"/>
-      <c r="AA11" s="16"/>
-      <c r="AB11" s="16"/>
-      <c r="AC11" s="16"/>
-      <c r="AD11" s="16"/>
-      <c r="AE11" s="16"/>
-      <c r="AF11" s="16"/>
-      <c r="AG11" s="16"/>
-      <c r="AH11" s="16"/>
-      <c r="AI11" s="16"/>
-      <c r="AJ11" s="16"/>
-      <c r="AK11" s="16"/>
-      <c r="AL11" s="16"/>
-      <c r="AM11" s="16"/>
-      <c r="AN11" s="16"/>
-      <c r="AO11" s="16"/>
-      <c r="AP11" s="16"/>
-      <c r="AQ11" s="17"/>
+      <c r="AA11" s="17"/>
+      <c r="AB11" s="17"/>
+      <c r="AC11" s="17"/>
+      <c r="AD11" s="17"/>
+      <c r="AE11" s="17"/>
+      <c r="AF11" s="17"/>
+      <c r="AG11" s="17"/>
+      <c r="AH11" s="17"/>
+      <c r="AI11" s="17"/>
+      <c r="AJ11" s="17"/>
+      <c r="AK11" s="17"/>
+      <c r="AL11" s="17"/>
+      <c r="AM11" s="17"/>
+      <c r="AN11" s="17"/>
+      <c r="AO11" s="17"/>
+      <c r="AP11" s="17"/>
+      <c r="AQ11" s="16"/>
     </row>
     <row r="12" spans="1:43">
       <c r="A12" s="2">
@@ -1287,23 +1292,23 @@
       <c r="X12" s="12"/>
       <c r="Y12" s="12"/>
       <c r="Z12" s="12"/>
-      <c r="AA12" s="16"/>
-      <c r="AB12" s="16"/>
-      <c r="AC12" s="16"/>
-      <c r="AD12" s="16"/>
-      <c r="AE12" s="16"/>
-      <c r="AF12" s="16"/>
-      <c r="AG12" s="16"/>
-      <c r="AH12" s="16"/>
-      <c r="AI12" s="16"/>
-      <c r="AJ12" s="16"/>
-      <c r="AK12" s="16"/>
-      <c r="AL12" s="16"/>
-      <c r="AM12" s="16"/>
-      <c r="AN12" s="16"/>
-      <c r="AO12" s="16"/>
-      <c r="AP12" s="16"/>
-      <c r="AQ12" s="17"/>
+      <c r="AA12" s="17"/>
+      <c r="AB12" s="17"/>
+      <c r="AC12" s="17"/>
+      <c r="AD12" s="17"/>
+      <c r="AE12" s="17"/>
+      <c r="AF12" s="17"/>
+      <c r="AG12" s="17"/>
+      <c r="AH12" s="17"/>
+      <c r="AI12" s="17"/>
+      <c r="AJ12" s="17"/>
+      <c r="AK12" s="17"/>
+      <c r="AL12" s="17"/>
+      <c r="AM12" s="17"/>
+      <c r="AN12" s="17"/>
+      <c r="AO12" s="17"/>
+      <c r="AP12" s="17"/>
+      <c r="AQ12" s="16"/>
     </row>
     <row r="13" spans="1:43">
       <c r="A13" s="2">
@@ -1348,23 +1353,23 @@
       <c r="X13" s="12"/>
       <c r="Y13" s="12"/>
       <c r="Z13" s="12"/>
-      <c r="AA13" s="16"/>
-      <c r="AB13" s="16"/>
-      <c r="AC13" s="16"/>
-      <c r="AD13" s="16"/>
-      <c r="AE13" s="16"/>
-      <c r="AF13" s="16"/>
-      <c r="AG13" s="16"/>
-      <c r="AH13" s="16"/>
-      <c r="AI13" s="16"/>
-      <c r="AJ13" s="16"/>
-      <c r="AK13" s="16"/>
-      <c r="AL13" s="16"/>
-      <c r="AM13" s="16"/>
-      <c r="AN13" s="16"/>
-      <c r="AO13" s="16"/>
-      <c r="AP13" s="16"/>
-      <c r="AQ13" s="17"/>
+      <c r="AA13" s="17"/>
+      <c r="AB13" s="17"/>
+      <c r="AC13" s="17"/>
+      <c r="AD13" s="17"/>
+      <c r="AE13" s="17"/>
+      <c r="AF13" s="17"/>
+      <c r="AG13" s="17"/>
+      <c r="AH13" s="17"/>
+      <c r="AI13" s="17"/>
+      <c r="AJ13" s="17"/>
+      <c r="AK13" s="17"/>
+      <c r="AL13" s="17"/>
+      <c r="AM13" s="17"/>
+      <c r="AN13" s="17"/>
+      <c r="AO13" s="17"/>
+      <c r="AP13" s="17"/>
+      <c r="AQ13" s="16"/>
     </row>
     <row r="14" spans="1:43">
       <c r="A14" s="2">
@@ -2359,13 +2364,15 @@
       <c r="A31" s="2">
         <v>28</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="15" t="s">
         <v>35</v>
       </c>
       <c r="C31" s="9">
         <v>3</v>
       </c>
-      <c r="D31" s="9"/>
+      <c r="D31" s="9" t="s">
+        <v>54</v>
+      </c>
       <c r="E31" s="2" t="s">
         <v>7</v>
       </c>
@@ -2388,7 +2395,9 @@
       <c r="R31" s="3"/>
       <c r="S31" s="3"/>
       <c r="T31" s="3"/>
-      <c r="U31" s="3"/>
+      <c r="U31" s="14">
+        <v>46072</v>
+      </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
@@ -2739,12 +2748,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="AQ11:AQ13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
     <mergeCell ref="A1:AQ1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="AA11:AA13"/>
@@ -2758,6 +2761,12 @@
     <mergeCell ref="AN11:AN13"/>
     <mergeCell ref="AO11:AO13"/>
     <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AQ11:AQ13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2769,50 +2778,50 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="17"/>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17"/>
-      <c r="AD1" s="17"/>
-      <c r="AE1" s="17"/>
-      <c r="AF1" s="17"/>
-      <c r="AG1" s="17"/>
-      <c r="AH1" s="17"/>
-      <c r="AI1" s="17"/>
-      <c r="AJ1" s="17"/>
-      <c r="AK1" s="17"/>
-      <c r="AL1" s="17"/>
-      <c r="AM1" s="17"/>
-      <c r="AN1" s="17"/>
-      <c r="AO1" s="17"/>
-      <c r="AP1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+      <c r="S1" s="16"/>
+      <c r="T1" s="16"/>
+      <c r="U1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="16"/>
+      <c r="Y1" s="16"/>
+      <c r="Z1" s="16"/>
+      <c r="AA1" s="16"/>
+      <c r="AB1" s="16"/>
+      <c r="AC1" s="16"/>
+      <c r="AD1" s="16"/>
+      <c r="AE1" s="16"/>
+      <c r="AF1" s="16"/>
+      <c r="AG1" s="16"/>
+      <c r="AH1" s="16"/>
+      <c r="AI1" s="16"/>
+      <c r="AJ1" s="16"/>
+      <c r="AK1" s="16"/>
+      <c r="AL1" s="16"/>
+      <c r="AM1" s="16"/>
+      <c r="AN1" s="16"/>
+      <c r="AO1" s="16"/>
+      <c r="AP1" s="16"/>
     </row>
     <row r="2" spans="1:42" ht="30">
       <c r="A2" s="19" t="s">
@@ -3262,37 +3271,37 @@
       <c r="I11" s="19"/>
       <c r="J11" s="19"/>
       <c r="K11" s="19"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="16"/>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="16"/>
-      <c r="R11" s="16"/>
-      <c r="S11" s="16"/>
-      <c r="T11" s="16"/>
-      <c r="U11" s="16"/>
-      <c r="V11" s="16"/>
-      <c r="W11" s="16"/>
-      <c r="X11" s="16"/>
-      <c r="Y11" s="16"/>
-      <c r="Z11" s="16"/>
-      <c r="AA11" s="16"/>
-      <c r="AB11" s="16"/>
-      <c r="AC11" s="16"/>
-      <c r="AD11" s="16"/>
-      <c r="AE11" s="16"/>
-      <c r="AF11" s="16"/>
-      <c r="AG11" s="16"/>
-      <c r="AH11" s="16"/>
-      <c r="AI11" s="16"/>
-      <c r="AJ11" s="16"/>
-      <c r="AK11" s="16"/>
-      <c r="AL11" s="16"/>
-      <c r="AM11" s="16"/>
-      <c r="AN11" s="16"/>
-      <c r="AO11" s="16"/>
-      <c r="AP11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="17"/>
+      <c r="U11" s="17"/>
+      <c r="V11" s="17"/>
+      <c r="W11" s="17"/>
+      <c r="X11" s="17"/>
+      <c r="Y11" s="17"/>
+      <c r="Z11" s="17"/>
+      <c r="AA11" s="17"/>
+      <c r="AB11" s="17"/>
+      <c r="AC11" s="17"/>
+      <c r="AD11" s="17"/>
+      <c r="AE11" s="17"/>
+      <c r="AF11" s="17"/>
+      <c r="AG11" s="17"/>
+      <c r="AH11" s="17"/>
+      <c r="AI11" s="17"/>
+      <c r="AJ11" s="17"/>
+      <c r="AK11" s="17"/>
+      <c r="AL11" s="17"/>
+      <c r="AM11" s="17"/>
+      <c r="AN11" s="17"/>
+      <c r="AO11" s="17"/>
+      <c r="AP11" s="16"/>
     </row>
     <row r="12" spans="1:42">
       <c r="A12" s="19"/>
@@ -3306,37 +3315,37 @@
       <c r="I12" s="19"/>
       <c r="J12" s="19"/>
       <c r="K12" s="19"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="16"/>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="16"/>
-      <c r="R12" s="16"/>
-      <c r="S12" s="16"/>
-      <c r="T12" s="16"/>
-      <c r="U12" s="16"/>
-      <c r="V12" s="16"/>
-      <c r="W12" s="16"/>
-      <c r="X12" s="16"/>
-      <c r="Y12" s="16"/>
-      <c r="Z12" s="16"/>
-      <c r="AA12" s="16"/>
-      <c r="AB12" s="16"/>
-      <c r="AC12" s="16"/>
-      <c r="AD12" s="16"/>
-      <c r="AE12" s="16"/>
-      <c r="AF12" s="16"/>
-      <c r="AG12" s="16"/>
-      <c r="AH12" s="16"/>
-      <c r="AI12" s="16"/>
-      <c r="AJ12" s="16"/>
-      <c r="AK12" s="16"/>
-      <c r="AL12" s="16"/>
-      <c r="AM12" s="16"/>
-      <c r="AN12" s="16"/>
-      <c r="AO12" s="16"/>
-      <c r="AP12" s="17"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="17"/>
+      <c r="S12" s="17"/>
+      <c r="T12" s="17"/>
+      <c r="U12" s="17"/>
+      <c r="V12" s="17"/>
+      <c r="W12" s="17"/>
+      <c r="X12" s="17"/>
+      <c r="Y12" s="17"/>
+      <c r="Z12" s="17"/>
+      <c r="AA12" s="17"/>
+      <c r="AB12" s="17"/>
+      <c r="AC12" s="17"/>
+      <c r="AD12" s="17"/>
+      <c r="AE12" s="17"/>
+      <c r="AF12" s="17"/>
+      <c r="AG12" s="17"/>
+      <c r="AH12" s="17"/>
+      <c r="AI12" s="17"/>
+      <c r="AJ12" s="17"/>
+      <c r="AK12" s="17"/>
+      <c r="AL12" s="17"/>
+      <c r="AM12" s="17"/>
+      <c r="AN12" s="17"/>
+      <c r="AO12" s="17"/>
+      <c r="AP12" s="16"/>
     </row>
     <row r="13" spans="1:42">
       <c r="A13" s="19"/>
@@ -3352,37 +3361,37 @@
       <c r="I13" s="19"/>
       <c r="J13" s="19"/>
       <c r="K13" s="19"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="16"/>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="16"/>
-      <c r="R13" s="16"/>
-      <c r="S13" s="16"/>
-      <c r="T13" s="16"/>
-      <c r="U13" s="16"/>
-      <c r="V13" s="16"/>
-      <c r="W13" s="16"/>
-      <c r="X13" s="16"/>
-      <c r="Y13" s="16"/>
-      <c r="Z13" s="16"/>
-      <c r="AA13" s="16"/>
-      <c r="AB13" s="16"/>
-      <c r="AC13" s="16"/>
-      <c r="AD13" s="16"/>
-      <c r="AE13" s="16"/>
-      <c r="AF13" s="16"/>
-      <c r="AG13" s="16"/>
-      <c r="AH13" s="16"/>
-      <c r="AI13" s="16"/>
-      <c r="AJ13" s="16"/>
-      <c r="AK13" s="16"/>
-      <c r="AL13" s="16"/>
-      <c r="AM13" s="16"/>
-      <c r="AN13" s="16"/>
-      <c r="AO13" s="16"/>
-      <c r="AP13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="17"/>
+      <c r="S13" s="17"/>
+      <c r="T13" s="17"/>
+      <c r="U13" s="17"/>
+      <c r="V13" s="17"/>
+      <c r="W13" s="17"/>
+      <c r="X13" s="17"/>
+      <c r="Y13" s="17"/>
+      <c r="Z13" s="17"/>
+      <c r="AA13" s="17"/>
+      <c r="AB13" s="17"/>
+      <c r="AC13" s="17"/>
+      <c r="AD13" s="17"/>
+      <c r="AE13" s="17"/>
+      <c r="AF13" s="17"/>
+      <c r="AG13" s="17"/>
+      <c r="AH13" s="17"/>
+      <c r="AI13" s="17"/>
+      <c r="AJ13" s="17"/>
+      <c r="AK13" s="17"/>
+      <c r="AL13" s="17"/>
+      <c r="AM13" s="17"/>
+      <c r="AN13" s="17"/>
+      <c r="AO13" s="17"/>
+      <c r="AP13" s="16"/>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" s="2">
@@ -4538,6 +4547,33 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="AO11:AO13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
+    <mergeCell ref="AN11:AN13"/>
+    <mergeCell ref="AE11:AE13"/>
+    <mergeCell ref="AF11:AF13"/>
+    <mergeCell ref="AG11:AG13"/>
+    <mergeCell ref="AH11:AH13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="Z11:Z13"/>
+    <mergeCell ref="AA11:AA13"/>
+    <mergeCell ref="AB11:AB13"/>
+    <mergeCell ref="AC11:AC13"/>
+    <mergeCell ref="AD11:AD13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="V11:V13"/>
+    <mergeCell ref="W11:W13"/>
+    <mergeCell ref="X11:X13"/>
+    <mergeCell ref="Y11:Y13"/>
+    <mergeCell ref="P11:P13"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="T11:T13"/>
     <mergeCell ref="A1:AP1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A11:A13"/>
@@ -4554,33 +4590,6 @@
     <mergeCell ref="M11:M13"/>
     <mergeCell ref="N11:N13"/>
     <mergeCell ref="O11:O13"/>
-    <mergeCell ref="P11:P13"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="T11:T13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="V11:V13"/>
-    <mergeCell ref="W11:W13"/>
-    <mergeCell ref="X11:X13"/>
-    <mergeCell ref="Y11:Y13"/>
-    <mergeCell ref="Z11:Z13"/>
-    <mergeCell ref="AA11:AA13"/>
-    <mergeCell ref="AB11:AB13"/>
-    <mergeCell ref="AC11:AC13"/>
-    <mergeCell ref="AD11:AD13"/>
-    <mergeCell ref="AE11:AE13"/>
-    <mergeCell ref="AF11:AF13"/>
-    <mergeCell ref="AG11:AG13"/>
-    <mergeCell ref="AH11:AH13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="AO11:AO13"/>
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="AN11:AN13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ТКИ-341_Реверс_Инжиниринг.xlsx
+++ b/ТКИ-341_Реверс_Инжиниринг.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\Reverse_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F905EE3-EEDC-47A3-B2EA-F1321C22099F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F168DCD-973B-45C7-B320-53EB41BBC070}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="60">
   <si>
     <t>ВЕДОМОСТЬ ПОСЕЩАЕМОСТИ ЗАНЯТИЙ СТУДЕНТАМИ ГРУППЫ ТКИ "Компьютерная безопасность" ИТТСУ РУТ (МИИТ)</t>
   </si>
@@ -224,6 +224,21 @@
   </si>
   <si>
     <t>расчет геометрической прогрессии</t>
+  </si>
+  <si>
+    <t>кусочно-</t>
+  </si>
+  <si>
+    <t>2 лаба</t>
+  </si>
+  <si>
+    <t>1 лаба</t>
+  </si>
+  <si>
+    <t>перевод из радиан в градусы</t>
+  </si>
+  <si>
+    <t>_1/2</t>
   </si>
 </sst>
 </file>
@@ -296,7 +311,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -334,15 +349,27 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -620,68 +647,68 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AQ37"/>
+  <dimension ref="A1:AQ39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="37.28515625" customWidth="1"/>
     <col min="3" max="4" width="9" style="8"/>
     <col min="5" max="5" width="10.85546875"/>
-    <col min="6" max="7" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="14.45" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
-      <c r="S1" s="16"/>
-      <c r="T1" s="16"/>
-      <c r="U1" s="16"/>
-      <c r="V1" s="16"/>
-      <c r="W1" s="16"/>
-      <c r="X1" s="16"/>
-      <c r="Y1" s="16"/>
-      <c r="Z1" s="16"/>
-      <c r="AA1" s="16"/>
-      <c r="AB1" s="16"/>
-      <c r="AC1" s="16"/>
-      <c r="AD1" s="16"/>
-      <c r="AE1" s="16"/>
-      <c r="AF1" s="16"/>
-      <c r="AG1" s="16"/>
-      <c r="AH1" s="16"/>
-      <c r="AI1" s="16"/>
-      <c r="AJ1" s="16"/>
-      <c r="AK1" s="16"/>
-      <c r="AL1" s="16"/>
-      <c r="AM1" s="16"/>
-      <c r="AN1" s="16"/>
-      <c r="AO1" s="16"/>
-      <c r="AP1" s="16"/>
-      <c r="AQ1" s="16"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="20"/>
+      <c r="Z1" s="20"/>
+      <c r="AA1" s="20"/>
+      <c r="AB1" s="20"/>
+      <c r="AC1" s="20"/>
+      <c r="AD1" s="20"/>
+      <c r="AE1" s="20"/>
+      <c r="AF1" s="20"/>
+      <c r="AG1" s="20"/>
+      <c r="AH1" s="20"/>
+      <c r="AI1" s="20"/>
+      <c r="AJ1" s="20"/>
+      <c r="AK1" s="20"/>
+      <c r="AL1" s="20"/>
+      <c r="AM1" s="20"/>
+      <c r="AN1" s="20"/>
+      <c r="AO1" s="20"/>
+      <c r="AP1" s="20"/>
+      <c r="AQ1" s="20"/>
     </row>
     <row r="2" spans="1:43" ht="27.6" customHeight="1">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="19"/>
+      <c r="B2" s="22"/>
       <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
@@ -697,7 +724,9 @@
       <c r="G2" s="10">
         <v>46072</v>
       </c>
-      <c r="H2" s="2"/>
+      <c r="H2" s="10">
+        <v>46079</v>
+      </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -809,7 +838,9 @@
       <c r="G4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="2"/>
+      <c r="H4" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -866,7 +897,9 @@
       <c r="G5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="2"/>
+      <c r="H5" s="18" t="s">
+        <v>7</v>
+      </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -923,7 +956,9 @@
       <c r="G6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="2"/>
+      <c r="H6" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -982,7 +1017,9 @@
       <c r="G7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="2"/>
+      <c r="H7" s="18" t="s">
+        <v>7</v>
+      </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -1039,7 +1076,9 @@
       <c r="G8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="2"/>
+      <c r="H8" s="23" t="s">
+        <v>59</v>
+      </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -1096,7 +1135,9 @@
       <c r="G9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="2"/>
+      <c r="H9" s="18" t="s">
+        <v>7</v>
+      </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -1137,7 +1178,7 @@
       <c r="A10" s="2">
         <v>7</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="15" t="s">
         <v>13</v>
       </c>
       <c r="C10" s="9">
@@ -1155,7 +1196,9 @@
       <c r="G10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="2"/>
+      <c r="H10" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -1168,7 +1211,9 @@
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
       <c r="T10" s="3"/>
-      <c r="U10" s="3"/>
+      <c r="U10" s="14">
+        <v>46079</v>
+      </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
@@ -1212,7 +1257,9 @@
       <c r="G11" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="H11" s="11"/>
+      <c r="H11" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="I11" s="11"/>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
@@ -1225,29 +1272,31 @@
       <c r="R11" s="12"/>
       <c r="S11" s="12"/>
       <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
+      <c r="U11" s="14">
+        <v>46079</v>
+      </c>
       <c r="V11" s="12"/>
       <c r="W11" s="12"/>
       <c r="X11" s="12"/>
       <c r="Y11" s="12"/>
       <c r="Z11" s="12"/>
-      <c r="AA11" s="17"/>
-      <c r="AB11" s="17"/>
-      <c r="AC11" s="17"/>
-      <c r="AD11" s="17"/>
-      <c r="AE11" s="17"/>
-      <c r="AF11" s="17"/>
-      <c r="AG11" s="17"/>
-      <c r="AH11" s="17"/>
-      <c r="AI11" s="17"/>
-      <c r="AJ11" s="17"/>
-      <c r="AK11" s="17"/>
-      <c r="AL11" s="17"/>
-      <c r="AM11" s="17"/>
-      <c r="AN11" s="17"/>
-      <c r="AO11" s="17"/>
-      <c r="AP11" s="17"/>
-      <c r="AQ11" s="16"/>
+      <c r="AA11" s="19"/>
+      <c r="AB11" s="19"/>
+      <c r="AC11" s="19"/>
+      <c r="AD11" s="19"/>
+      <c r="AE11" s="19"/>
+      <c r="AF11" s="19"/>
+      <c r="AG11" s="19"/>
+      <c r="AH11" s="19"/>
+      <c r="AI11" s="19"/>
+      <c r="AJ11" s="19"/>
+      <c r="AK11" s="19"/>
+      <c r="AL11" s="19"/>
+      <c r="AM11" s="19"/>
+      <c r="AN11" s="19"/>
+      <c r="AO11" s="19"/>
+      <c r="AP11" s="19"/>
+      <c r="AQ11" s="20"/>
     </row>
     <row r="12" spans="1:43">
       <c r="A12" s="2">
@@ -1271,7 +1320,9 @@
       <c r="G12" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="11"/>
+      <c r="H12" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="I12" s="11"/>
       <c r="J12" s="11"/>
       <c r="K12" s="11"/>
@@ -1292,23 +1343,23 @@
       <c r="X12" s="12"/>
       <c r="Y12" s="12"/>
       <c r="Z12" s="12"/>
-      <c r="AA12" s="17"/>
-      <c r="AB12" s="17"/>
-      <c r="AC12" s="17"/>
-      <c r="AD12" s="17"/>
-      <c r="AE12" s="17"/>
-      <c r="AF12" s="17"/>
-      <c r="AG12" s="17"/>
-      <c r="AH12" s="17"/>
-      <c r="AI12" s="17"/>
-      <c r="AJ12" s="17"/>
-      <c r="AK12" s="17"/>
-      <c r="AL12" s="17"/>
-      <c r="AM12" s="17"/>
-      <c r="AN12" s="17"/>
-      <c r="AO12" s="17"/>
-      <c r="AP12" s="17"/>
-      <c r="AQ12" s="16"/>
+      <c r="AA12" s="19"/>
+      <c r="AB12" s="19"/>
+      <c r="AC12" s="19"/>
+      <c r="AD12" s="19"/>
+      <c r="AE12" s="19"/>
+      <c r="AF12" s="19"/>
+      <c r="AG12" s="19"/>
+      <c r="AH12" s="19"/>
+      <c r="AI12" s="19"/>
+      <c r="AJ12" s="19"/>
+      <c r="AK12" s="19"/>
+      <c r="AL12" s="19"/>
+      <c r="AM12" s="19"/>
+      <c r="AN12" s="19"/>
+      <c r="AO12" s="19"/>
+      <c r="AP12" s="19"/>
+      <c r="AQ12" s="20"/>
     </row>
     <row r="13" spans="1:43">
       <c r="A13" s="2">
@@ -1332,7 +1383,9 @@
       <c r="G13" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="H13" s="11"/>
+      <c r="H13" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="I13" s="11"/>
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
@@ -1353,23 +1406,23 @@
       <c r="X13" s="12"/>
       <c r="Y13" s="12"/>
       <c r="Z13" s="12"/>
-      <c r="AA13" s="17"/>
-      <c r="AB13" s="17"/>
-      <c r="AC13" s="17"/>
-      <c r="AD13" s="17"/>
-      <c r="AE13" s="17"/>
-      <c r="AF13" s="17"/>
-      <c r="AG13" s="17"/>
-      <c r="AH13" s="17"/>
-      <c r="AI13" s="17"/>
-      <c r="AJ13" s="17"/>
-      <c r="AK13" s="17"/>
-      <c r="AL13" s="17"/>
-      <c r="AM13" s="17"/>
-      <c r="AN13" s="17"/>
-      <c r="AO13" s="17"/>
-      <c r="AP13" s="17"/>
-      <c r="AQ13" s="16"/>
+      <c r="AA13" s="19"/>
+      <c r="AB13" s="19"/>
+      <c r="AC13" s="19"/>
+      <c r="AD13" s="19"/>
+      <c r="AE13" s="19"/>
+      <c r="AF13" s="19"/>
+      <c r="AG13" s="19"/>
+      <c r="AH13" s="19"/>
+      <c r="AI13" s="19"/>
+      <c r="AJ13" s="19"/>
+      <c r="AK13" s="19"/>
+      <c r="AL13" s="19"/>
+      <c r="AM13" s="19"/>
+      <c r="AN13" s="19"/>
+      <c r="AO13" s="19"/>
+      <c r="AP13" s="19"/>
+      <c r="AQ13" s="20"/>
     </row>
     <row r="14" spans="1:43">
       <c r="A14" s="2">
@@ -1391,7 +1444,9 @@
       <c r="G14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H14" s="2"/>
+      <c r="H14" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -1432,13 +1487,15 @@
       <c r="A15" s="2">
         <v>12</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="15" t="s">
         <v>18</v>
       </c>
       <c r="C15" s="9">
         <v>8</v>
       </c>
-      <c r="D15" s="9"/>
+      <c r="D15" s="9" t="s">
+        <v>55</v>
+      </c>
       <c r="E15" s="2" t="s">
         <v>7</v>
       </c>
@@ -1448,7 +1505,9 @@
       <c r="G15" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H15" s="2"/>
+      <c r="H15" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -1461,7 +1520,9 @@
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
       <c r="T15" s="3"/>
-      <c r="U15" s="3"/>
+      <c r="U15" s="14">
+        <v>46079</v>
+      </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
@@ -1505,7 +1566,9 @@
       <c r="G16" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H16" s="2"/>
+      <c r="H16" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -1566,7 +1629,9 @@
       <c r="G17" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H17" s="2"/>
+      <c r="H17" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -1625,7 +1690,9 @@
       <c r="G18" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H18" s="2"/>
+      <c r="H18" s="18" t="s">
+        <v>7</v>
+      </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -1682,7 +1749,9 @@
       <c r="G19" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H19" s="2"/>
+      <c r="H19" s="18" t="s">
+        <v>7</v>
+      </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -1739,7 +1808,9 @@
       <c r="G20" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H20" s="2"/>
+      <c r="H20" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -1796,7 +1867,9 @@
       <c r="G21" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H21" s="2"/>
+      <c r="H21" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
@@ -1853,7 +1926,9 @@
       <c r="G22" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H22" s="2"/>
+      <c r="H22" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
@@ -1914,7 +1989,9 @@
       <c r="G23" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H23" s="2"/>
+      <c r="H23" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -1963,7 +2040,9 @@
       <c r="C24" s="9">
         <v>15</v>
       </c>
-      <c r="D24" s="9"/>
+      <c r="D24" s="9" t="s">
+        <v>58</v>
+      </c>
       <c r="E24" s="2" t="s">
         <v>7</v>
       </c>
@@ -1973,7 +2052,9 @@
       <c r="G24" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H24" s="2"/>
+      <c r="H24" s="18" t="s">
+        <v>7</v>
+      </c>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -2030,7 +2111,9 @@
       <c r="G25" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H25" s="2"/>
+      <c r="H25" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -2089,7 +2172,9 @@
       <c r="G26" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H26" s="2"/>
+      <c r="H26" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -2146,7 +2231,9 @@
       <c r="G27" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H27" s="2"/>
+      <c r="H27" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -2203,7 +2290,9 @@
       <c r="G28" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H28" s="2"/>
+      <c r="H28" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
@@ -2260,7 +2349,9 @@
       <c r="G29" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H29" s="2"/>
+      <c r="H29" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
@@ -2321,7 +2412,9 @@
       <c r="G30" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H30" s="2"/>
+      <c r="H30" s="18" t="s">
+        <v>7</v>
+      </c>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
@@ -2382,7 +2475,9 @@
       <c r="G31" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H31" s="2"/>
+      <c r="H31" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
@@ -2441,7 +2536,9 @@
       <c r="G32" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H32" s="2"/>
+      <c r="H32" s="18" t="s">
+        <v>7</v>
+      </c>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
@@ -2498,7 +2595,9 @@
       <c r="G33" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H33" s="2"/>
+      <c r="H33" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
@@ -2511,7 +2610,9 @@
       <c r="R33" s="3"/>
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
-      <c r="U33" s="3"/>
+      <c r="U33" s="14">
+        <v>46079</v>
+      </c>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
       <c r="X33" s="3"/>
@@ -2555,7 +2656,9 @@
       <c r="G34" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H34" s="2"/>
+      <c r="H34" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
@@ -2614,7 +2717,9 @@
       <c r="G35" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H35" s="2"/>
+      <c r="H35" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
@@ -2709,7 +2814,9 @@
       <c r="G37" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="H37" s="2"/>
+      <c r="H37" s="16" t="s">
+        <v>43</v>
+      </c>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
@@ -2746,8 +2853,45 @@
       <c r="AP37" s="3"/>
       <c r="AQ37" s="1"/>
     </row>
+    <row r="38" spans="1:43">
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38">
+        <v>2</v>
+      </c>
+      <c r="H38">
+        <v>3</v>
+      </c>
+      <c r="I38">
+        <v>4</v>
+      </c>
+      <c r="J38">
+        <v>5</v>
+      </c>
+      <c r="K38">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:43">
+      <c r="E39" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="G39" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="AQ11:AQ13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
     <mergeCell ref="A1:AQ1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="AA11:AA13"/>
@@ -2761,12 +2905,6 @@
     <mergeCell ref="AN11:AN13"/>
     <mergeCell ref="AO11:AO13"/>
     <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AQ11:AQ13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2778,56 +2916,56 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
-      <c r="S1" s="16"/>
-      <c r="T1" s="16"/>
-      <c r="U1" s="16"/>
-      <c r="V1" s="16"/>
-      <c r="W1" s="16"/>
-      <c r="X1" s="16"/>
-      <c r="Y1" s="16"/>
-      <c r="Z1" s="16"/>
-      <c r="AA1" s="16"/>
-      <c r="AB1" s="16"/>
-      <c r="AC1" s="16"/>
-      <c r="AD1" s="16"/>
-      <c r="AE1" s="16"/>
-      <c r="AF1" s="16"/>
-      <c r="AG1" s="16"/>
-      <c r="AH1" s="16"/>
-      <c r="AI1" s="16"/>
-      <c r="AJ1" s="16"/>
-      <c r="AK1" s="16"/>
-      <c r="AL1" s="16"/>
-      <c r="AM1" s="16"/>
-      <c r="AN1" s="16"/>
-      <c r="AO1" s="16"/>
-      <c r="AP1" s="16"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="20"/>
+      <c r="Z1" s="20"/>
+      <c r="AA1" s="20"/>
+      <c r="AB1" s="20"/>
+      <c r="AC1" s="20"/>
+      <c r="AD1" s="20"/>
+      <c r="AE1" s="20"/>
+      <c r="AF1" s="20"/>
+      <c r="AG1" s="20"/>
+      <c r="AH1" s="20"/>
+      <c r="AI1" s="20"/>
+      <c r="AJ1" s="20"/>
+      <c r="AK1" s="20"/>
+      <c r="AL1" s="20"/>
+      <c r="AM1" s="20"/>
+      <c r="AN1" s="20"/>
+      <c r="AO1" s="20"/>
+      <c r="AP1" s="20"/>
     </row>
     <row r="2" spans="1:42" ht="30">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="19"/>
+      <c r="B2" s="22"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -3256,142 +3394,142 @@
       <c r="AP10" s="1"/>
     </row>
     <row r="11" spans="1:42">
-      <c r="A11" s="19">
+      <c r="A11" s="22">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="17"/>
-      <c r="Q11" s="17"/>
-      <c r="R11" s="17"/>
-      <c r="S11" s="17"/>
-      <c r="T11" s="17"/>
-      <c r="U11" s="17"/>
-      <c r="V11" s="17"/>
-      <c r="W11" s="17"/>
-      <c r="X11" s="17"/>
-      <c r="Y11" s="17"/>
-      <c r="Z11" s="17"/>
-      <c r="AA11" s="17"/>
-      <c r="AB11" s="17"/>
-      <c r="AC11" s="17"/>
-      <c r="AD11" s="17"/>
-      <c r="AE11" s="17"/>
-      <c r="AF11" s="17"/>
-      <c r="AG11" s="17"/>
-      <c r="AH11" s="17"/>
-      <c r="AI11" s="17"/>
-      <c r="AJ11" s="17"/>
-      <c r="AK11" s="17"/>
-      <c r="AL11" s="17"/>
-      <c r="AM11" s="17"/>
-      <c r="AN11" s="17"/>
-      <c r="AO11" s="17"/>
-      <c r="AP11" s="16"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="19"/>
+      <c r="Y11" s="19"/>
+      <c r="Z11" s="19"/>
+      <c r="AA11" s="19"/>
+      <c r="AB11" s="19"/>
+      <c r="AC11" s="19"/>
+      <c r="AD11" s="19"/>
+      <c r="AE11" s="19"/>
+      <c r="AF11" s="19"/>
+      <c r="AG11" s="19"/>
+      <c r="AH11" s="19"/>
+      <c r="AI11" s="19"/>
+      <c r="AJ11" s="19"/>
+      <c r="AK11" s="19"/>
+      <c r="AL11" s="19"/>
+      <c r="AM11" s="19"/>
+      <c r="AN11" s="19"/>
+      <c r="AO11" s="19"/>
+      <c r="AP11" s="20"/>
     </row>
     <row r="12" spans="1:42">
-      <c r="A12" s="19"/>
+      <c r="A12" s="22"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="17"/>
-      <c r="R12" s="17"/>
-      <c r="S12" s="17"/>
-      <c r="T12" s="17"/>
-      <c r="U12" s="17"/>
-      <c r="V12" s="17"/>
-      <c r="W12" s="17"/>
-      <c r="X12" s="17"/>
-      <c r="Y12" s="17"/>
-      <c r="Z12" s="17"/>
-      <c r="AA12" s="17"/>
-      <c r="AB12" s="17"/>
-      <c r="AC12" s="17"/>
-      <c r="AD12" s="17"/>
-      <c r="AE12" s="17"/>
-      <c r="AF12" s="17"/>
-      <c r="AG12" s="17"/>
-      <c r="AH12" s="17"/>
-      <c r="AI12" s="17"/>
-      <c r="AJ12" s="17"/>
-      <c r="AK12" s="17"/>
-      <c r="AL12" s="17"/>
-      <c r="AM12" s="17"/>
-      <c r="AN12" s="17"/>
-      <c r="AO12" s="17"/>
-      <c r="AP12" s="16"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="19"/>
+      <c r="Y12" s="19"/>
+      <c r="Z12" s="19"/>
+      <c r="AA12" s="19"/>
+      <c r="AB12" s="19"/>
+      <c r="AC12" s="19"/>
+      <c r="AD12" s="19"/>
+      <c r="AE12" s="19"/>
+      <c r="AF12" s="19"/>
+      <c r="AG12" s="19"/>
+      <c r="AH12" s="19"/>
+      <c r="AI12" s="19"/>
+      <c r="AJ12" s="19"/>
+      <c r="AK12" s="19"/>
+      <c r="AL12" s="19"/>
+      <c r="AM12" s="19"/>
+      <c r="AN12" s="19"/>
+      <c r="AO12" s="19"/>
+      <c r="AP12" s="20"/>
     </row>
     <row r="13" spans="1:42">
-      <c r="A13" s="19"/>
+      <c r="A13" s="22"/>
       <c r="B13" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="17"/>
-      <c r="R13" s="17"/>
-      <c r="S13" s="17"/>
-      <c r="T13" s="17"/>
-      <c r="U13" s="17"/>
-      <c r="V13" s="17"/>
-      <c r="W13" s="17"/>
-      <c r="X13" s="17"/>
-      <c r="Y13" s="17"/>
-      <c r="Z13" s="17"/>
-      <c r="AA13" s="17"/>
-      <c r="AB13" s="17"/>
-      <c r="AC13" s="17"/>
-      <c r="AD13" s="17"/>
-      <c r="AE13" s="17"/>
-      <c r="AF13" s="17"/>
-      <c r="AG13" s="17"/>
-      <c r="AH13" s="17"/>
-      <c r="AI13" s="17"/>
-      <c r="AJ13" s="17"/>
-      <c r="AK13" s="17"/>
-      <c r="AL13" s="17"/>
-      <c r="AM13" s="17"/>
-      <c r="AN13" s="17"/>
-      <c r="AO13" s="17"/>
-      <c r="AP13" s="16"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="19"/>
+      <c r="Y13" s="19"/>
+      <c r="Z13" s="19"/>
+      <c r="AA13" s="19"/>
+      <c r="AB13" s="19"/>
+      <c r="AC13" s="19"/>
+      <c r="AD13" s="19"/>
+      <c r="AE13" s="19"/>
+      <c r="AF13" s="19"/>
+      <c r="AG13" s="19"/>
+      <c r="AH13" s="19"/>
+      <c r="AI13" s="19"/>
+      <c r="AJ13" s="19"/>
+      <c r="AK13" s="19"/>
+      <c r="AL13" s="19"/>
+      <c r="AM13" s="19"/>
+      <c r="AN13" s="19"/>
+      <c r="AO13" s="19"/>
+      <c r="AP13" s="20"/>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" s="2">

--- a/ТКИ-341_Реверс_Инжиниринг.xlsx
+++ b/ТКИ-341_Реверс_Инжиниринг.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\Reverse_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F168DCD-973B-45C7-B320-53EB41BBC070}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21B72AF-76FA-494F-8852-AE153DFEC240}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="135" windowWidth="19410" windowHeight="14895" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="64">
   <si>
     <t>ВЕДОМОСТЬ ПОСЕЩАЕМОСТИ ЗАНЯТИЙ СТУДЕНТАМИ ГРУППЫ ТКИ "Компьютерная безопасность" ИТТСУ РУТ (МИИТ)</t>
   </si>
@@ -239,6 +239,18 @@
   </si>
   <si>
     <t>_1/2</t>
+  </si>
+  <si>
+    <t>kNN</t>
+  </si>
+  <si>
+    <t>текстовый квест</t>
+  </si>
+  <si>
+    <t>С#</t>
+  </si>
+  <si>
+    <t>Python</t>
   </si>
 </sst>
 </file>
@@ -311,7 +323,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -354,14 +366,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -369,7 +378,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -654,61 +672,62 @@
     <col min="3" max="4" width="9" style="8"/>
     <col min="5" max="5" width="10.85546875"/>
     <col min="6" max="8" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="14.45" customHeight="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20"/>
-      <c r="W1" s="20"/>
-      <c r="X1" s="20"/>
-      <c r="Y1" s="20"/>
-      <c r="Z1" s="20"/>
-      <c r="AA1" s="20"/>
-      <c r="AB1" s="20"/>
-      <c r="AC1" s="20"/>
-      <c r="AD1" s="20"/>
-      <c r="AE1" s="20"/>
-      <c r="AF1" s="20"/>
-      <c r="AG1" s="20"/>
-      <c r="AH1" s="20"/>
-      <c r="AI1" s="20"/>
-      <c r="AJ1" s="20"/>
-      <c r="AK1" s="20"/>
-      <c r="AL1" s="20"/>
-      <c r="AM1" s="20"/>
-      <c r="AN1" s="20"/>
-      <c r="AO1" s="20"/>
-      <c r="AP1" s="20"/>
-      <c r="AQ1" s="20"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
+      <c r="S1" s="18"/>
+      <c r="T1" s="18"/>
+      <c r="U1" s="18"/>
+      <c r="V1" s="18"/>
+      <c r="W1" s="18"/>
+      <c r="X1" s="18"/>
+      <c r="Y1" s="18"/>
+      <c r="Z1" s="18"/>
+      <c r="AA1" s="18"/>
+      <c r="AB1" s="18"/>
+      <c r="AC1" s="18"/>
+      <c r="AD1" s="18"/>
+      <c r="AE1" s="18"/>
+      <c r="AF1" s="18"/>
+      <c r="AG1" s="18"/>
+      <c r="AH1" s="18"/>
+      <c r="AI1" s="18"/>
+      <c r="AJ1" s="18"/>
+      <c r="AK1" s="18"/>
+      <c r="AL1" s="18"/>
+      <c r="AM1" s="18"/>
+      <c r="AN1" s="18"/>
+      <c r="AO1" s="18"/>
+      <c r="AP1" s="18"/>
+      <c r="AQ1" s="18"/>
     </row>
     <row r="2" spans="1:43" ht="27.6" customHeight="1">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22"/>
+      <c r="B2" s="21"/>
       <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
@@ -727,7 +746,9 @@
       <c r="H2" s="10">
         <v>46079</v>
       </c>
-      <c r="I2" s="2"/>
+      <c r="I2" s="22">
+        <v>46086</v>
+      </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -747,9 +768,13 @@
         <v>47</v>
       </c>
       <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
+      <c r="Y2" s="3" t="s">
+        <v>62</v>
+      </c>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="3"/>
+      <c r="AA2" s="3" t="s">
+        <v>63</v>
+      </c>
       <c r="AB2" s="3"/>
       <c r="AC2" s="3"/>
       <c r="AD2" s="3"/>
@@ -822,26 +847,30 @@
       <c r="A4" s="2">
         <v>1</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="9">
         <v>1</v>
       </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I4" s="2"/>
+      <c r="D4" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>7</v>
+      </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -853,7 +882,9 @@
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
-      <c r="U4" s="3"/>
+      <c r="U4" s="25">
+        <v>46086</v>
+      </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
@@ -888,19 +919,21 @@
         <v>2</v>
       </c>
       <c r="D5" s="9"/>
-      <c r="E5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H5" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="I5" s="2"/>
+      <c r="E5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -947,19 +980,21 @@
         <v>3</v>
       </c>
       <c r="D6" s="9"/>
-      <c r="E6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I6" s="2"/>
+      <c r="E6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -1007,20 +1042,24 @@
       <c r="C7" s="9">
         <v>4</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H7" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="I7" s="2"/>
+      <c r="D7" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
@@ -1067,19 +1106,21 @@
         <v>5</v>
       </c>
       <c r="D8" s="9"/>
-      <c r="E8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="E8" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="23" t="s">
+      <c r="H8" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="I8" s="2"/>
+      <c r="I8" s="23" t="s">
+        <v>7</v>
+      </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
@@ -1126,19 +1167,21 @@
         <v>6</v>
       </c>
       <c r="D9" s="9"/>
-      <c r="E9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H9" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="I9" s="2"/>
+      <c r="E9" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H9" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
@@ -1187,19 +1230,21 @@
       <c r="D10" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I10" s="2"/>
+      <c r="E10" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
@@ -1248,19 +1293,21 @@
         <v>8</v>
       </c>
       <c r="D11" s="9"/>
-      <c r="E11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="I11" s="11"/>
+      <c r="E11" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
       <c r="L11" s="11"/>
@@ -1296,7 +1343,7 @@
       <c r="AN11" s="19"/>
       <c r="AO11" s="19"/>
       <c r="AP11" s="19"/>
-      <c r="AQ11" s="20"/>
+      <c r="AQ11" s="18"/>
     </row>
     <row r="12" spans="1:43">
       <c r="A12" s="2">
@@ -1311,19 +1358,21 @@
       <c r="D12" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="I12" s="11"/>
+      <c r="E12" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="J12" s="11"/>
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
@@ -1359,7 +1408,7 @@
       <c r="AN12" s="19"/>
       <c r="AO12" s="19"/>
       <c r="AP12" s="19"/>
-      <c r="AQ12" s="20"/>
+      <c r="AQ12" s="18"/>
     </row>
     <row r="13" spans="1:43">
       <c r="A13" s="2">
@@ -1374,19 +1423,21 @@
       <c r="D13" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="I13" s="11"/>
+      <c r="E13" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
@@ -1422,7 +1473,7 @@
       <c r="AN13" s="19"/>
       <c r="AO13" s="19"/>
       <c r="AP13" s="19"/>
-      <c r="AQ13" s="20"/>
+      <c r="AQ13" s="18"/>
     </row>
     <row r="14" spans="1:43">
       <c r="A14" s="2">
@@ -1435,19 +1486,21 @@
         <v>11</v>
       </c>
       <c r="D14" s="9"/>
-      <c r="E14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H14" s="2" t="s">
+      <c r="E14" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H14" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I14" s="2"/>
+      <c r="I14" s="23" t="s">
+        <v>7</v>
+      </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
@@ -1496,19 +1549,21 @@
       <c r="D15" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="E15" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I15" s="2"/>
+      <c r="H15" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
@@ -1557,19 +1612,21 @@
         <v>12</v>
       </c>
       <c r="D16" s="9"/>
-      <c r="E16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I16" s="2"/>
+      <c r="E16" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
@@ -1620,19 +1677,21 @@
       <c r="D17" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I17" s="2"/>
+      <c r="E17" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
@@ -1680,20 +1739,24 @@
       <c r="C18" s="9">
         <v>4</v>
       </c>
-      <c r="D18" s="9"/>
-      <c r="E18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H18" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="I18" s="2"/>
+      <c r="D18" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H18" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
@@ -1740,19 +1803,21 @@
         <v>6</v>
       </c>
       <c r="D19" s="9"/>
-      <c r="E19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H19" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="I19" s="2"/>
+      <c r="E19" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H19" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
@@ -1799,19 +1864,21 @@
         <v>16</v>
       </c>
       <c r="D20" s="9"/>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H20" s="2" t="s">
+      <c r="G20" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H20" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I20" s="2"/>
+      <c r="I20" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
@@ -1858,19 +1925,21 @@
         <v>5</v>
       </c>
       <c r="D21" s="9"/>
-      <c r="E21" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I21" s="2"/>
+      <c r="E21" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I21" s="23" t="s">
+        <v>7</v>
+      </c>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
@@ -1917,19 +1986,21 @@
         <v>14</v>
       </c>
       <c r="D22" s="9"/>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I22" s="2"/>
+      <c r="F22" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
@@ -1980,19 +2051,21 @@
       <c r="D23" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I23" s="2"/>
+      <c r="E23" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
@@ -2043,19 +2116,21 @@
       <c r="D24" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H24" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="I24" s="2"/>
+      <c r="E24" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H24" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
@@ -2102,19 +2177,21 @@
         <v>9</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I25" s="2"/>
+      <c r="E25" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
@@ -2163,19 +2240,21 @@
         <v>16</v>
       </c>
       <c r="D26" s="9"/>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="G26" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="H26" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I26" s="2"/>
+      <c r="I26" s="9" t="s">
+        <v>24</v>
+      </c>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
@@ -2222,19 +2301,21 @@
         <v>2</v>
       </c>
       <c r="D27" s="9"/>
-      <c r="E27" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G27" s="2" t="s">
+      <c r="E27" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G27" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H27" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I27" s="2"/>
+      <c r="H27" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
@@ -2280,20 +2361,24 @@
       <c r="C28" s="9">
         <v>1</v>
       </c>
-      <c r="D28" s="9"/>
-      <c r="E28" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I28" s="2"/>
+      <c r="D28" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I28" s="23" t="s">
+        <v>7</v>
+      </c>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
@@ -2305,7 +2390,9 @@
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
       <c r="T28" s="3"/>
-      <c r="U28" s="3"/>
+      <c r="U28" s="25">
+        <v>46086</v>
+      </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
@@ -2340,19 +2427,21 @@
         <v>13</v>
       </c>
       <c r="D29" s="9"/>
-      <c r="E29" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I29" s="2"/>
+      <c r="E29" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
@@ -2403,19 +2492,21 @@
       <c r="D30" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H30" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="I30" s="2"/>
+      <c r="E30" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H30" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
@@ -2466,19 +2557,21 @@
       <c r="D31" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I31" s="2"/>
+      <c r="E31" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
@@ -2527,19 +2620,21 @@
         <v>15</v>
       </c>
       <c r="D32" s="9"/>
-      <c r="E32" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G32" s="2" t="s">
+      <c r="E32" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G32" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H32" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="I32" s="2"/>
+      <c r="H32" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
@@ -2586,19 +2681,21 @@
         <v>7</v>
       </c>
       <c r="D33" s="9"/>
-      <c r="E33" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I33" s="2"/>
+      <c r="E33" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
@@ -2647,19 +2744,21 @@
         <v>10</v>
       </c>
       <c r="D34" s="9"/>
-      <c r="E34" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I34" s="2"/>
+      <c r="E34" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
@@ -2708,19 +2807,21 @@
         <v>11</v>
       </c>
       <c r="D35" s="9"/>
-      <c r="E35" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H35" s="2" t="s">
+      <c r="E35" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H35" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I35" s="2"/>
+      <c r="I35" s="23" t="s">
+        <v>7</v>
+      </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
@@ -2886,12 +2987,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="AQ11:AQ13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
     <mergeCell ref="A1:AQ1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="AA11:AA13"/>
@@ -2905,6 +3000,12 @@
     <mergeCell ref="AN11:AN13"/>
     <mergeCell ref="AO11:AO13"/>
     <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AQ11:AQ13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2916,56 +3017,56 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20"/>
-      <c r="W1" s="20"/>
-      <c r="X1" s="20"/>
-      <c r="Y1" s="20"/>
-      <c r="Z1" s="20"/>
-      <c r="AA1" s="20"/>
-      <c r="AB1" s="20"/>
-      <c r="AC1" s="20"/>
-      <c r="AD1" s="20"/>
-      <c r="AE1" s="20"/>
-      <c r="AF1" s="20"/>
-      <c r="AG1" s="20"/>
-      <c r="AH1" s="20"/>
-      <c r="AI1" s="20"/>
-      <c r="AJ1" s="20"/>
-      <c r="AK1" s="20"/>
-      <c r="AL1" s="20"/>
-      <c r="AM1" s="20"/>
-      <c r="AN1" s="20"/>
-      <c r="AO1" s="20"/>
-      <c r="AP1" s="20"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
+      <c r="S1" s="18"/>
+      <c r="T1" s="18"/>
+      <c r="U1" s="18"/>
+      <c r="V1" s="18"/>
+      <c r="W1" s="18"/>
+      <c r="X1" s="18"/>
+      <c r="Y1" s="18"/>
+      <c r="Z1" s="18"/>
+      <c r="AA1" s="18"/>
+      <c r="AB1" s="18"/>
+      <c r="AC1" s="18"/>
+      <c r="AD1" s="18"/>
+      <c r="AE1" s="18"/>
+      <c r="AF1" s="18"/>
+      <c r="AG1" s="18"/>
+      <c r="AH1" s="18"/>
+      <c r="AI1" s="18"/>
+      <c r="AJ1" s="18"/>
+      <c r="AK1" s="18"/>
+      <c r="AL1" s="18"/>
+      <c r="AM1" s="18"/>
+      <c r="AN1" s="18"/>
+      <c r="AO1" s="18"/>
+      <c r="AP1" s="18"/>
     </row>
     <row r="2" spans="1:42" ht="30">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22"/>
+      <c r="B2" s="21"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -3394,21 +3495,21 @@
       <c r="AP10" s="1"/>
     </row>
     <row r="11" spans="1:42">
-      <c r="A11" s="22">
+      <c r="A11" s="21">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="21"/>
       <c r="L11" s="19"/>
       <c r="M11" s="19"/>
       <c r="N11" s="19"/>
@@ -3439,20 +3540,20 @@
       <c r="AM11" s="19"/>
       <c r="AN11" s="19"/>
       <c r="AO11" s="19"/>
-      <c r="AP11" s="20"/>
+      <c r="AP11" s="18"/>
     </row>
     <row r="12" spans="1:42">
-      <c r="A12" s="22"/>
+      <c r="A12" s="21"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
       <c r="L12" s="19"/>
       <c r="M12" s="19"/>
       <c r="N12" s="19"/>
@@ -3483,22 +3584,22 @@
       <c r="AM12" s="19"/>
       <c r="AN12" s="19"/>
       <c r="AO12" s="19"/>
-      <c r="AP12" s="20"/>
+      <c r="AP12" s="18"/>
     </row>
     <row r="13" spans="1:42">
-      <c r="A13" s="22"/>
+      <c r="A13" s="21"/>
       <c r="B13" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="22"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
       <c r="L13" s="19"/>
       <c r="M13" s="19"/>
       <c r="N13" s="19"/>
@@ -3529,7 +3630,7 @@
       <c r="AM13" s="19"/>
       <c r="AN13" s="19"/>
       <c r="AO13" s="19"/>
-      <c r="AP13" s="20"/>
+      <c r="AP13" s="18"/>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" s="2">
@@ -4685,33 +4786,6 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="AO11:AO13"/>
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="AN11:AN13"/>
-    <mergeCell ref="AE11:AE13"/>
-    <mergeCell ref="AF11:AF13"/>
-    <mergeCell ref="AG11:AG13"/>
-    <mergeCell ref="AH11:AH13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="Z11:Z13"/>
-    <mergeCell ref="AA11:AA13"/>
-    <mergeCell ref="AB11:AB13"/>
-    <mergeCell ref="AC11:AC13"/>
-    <mergeCell ref="AD11:AD13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="V11:V13"/>
-    <mergeCell ref="W11:W13"/>
-    <mergeCell ref="X11:X13"/>
-    <mergeCell ref="Y11:Y13"/>
-    <mergeCell ref="P11:P13"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="T11:T13"/>
     <mergeCell ref="A1:AP1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A11:A13"/>
@@ -4728,6 +4802,33 @@
     <mergeCell ref="M11:M13"/>
     <mergeCell ref="N11:N13"/>
     <mergeCell ref="O11:O13"/>
+    <mergeCell ref="P11:P13"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="T11:T13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="V11:V13"/>
+    <mergeCell ref="W11:W13"/>
+    <mergeCell ref="X11:X13"/>
+    <mergeCell ref="Y11:Y13"/>
+    <mergeCell ref="Z11:Z13"/>
+    <mergeCell ref="AA11:AA13"/>
+    <mergeCell ref="AB11:AB13"/>
+    <mergeCell ref="AC11:AC13"/>
+    <mergeCell ref="AD11:AD13"/>
+    <mergeCell ref="AE11:AE13"/>
+    <mergeCell ref="AF11:AF13"/>
+    <mergeCell ref="AG11:AG13"/>
+    <mergeCell ref="AH11:AH13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="AO11:AO13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
+    <mergeCell ref="AN11:AN13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ТКИ-341_Реверс_Инжиниринг.xlsx
+++ b/ТКИ-341_Реверс_Инжиниринг.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\Reverse_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21B72AF-76FA-494F-8852-AE153DFEC240}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F66168-3507-4D51-BCF8-BB46C387EB23}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="135" windowWidth="19410" windowHeight="14895" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="64">
   <si>
     <t>ВЕДОМОСТЬ ПОСЕЩАЕМОСТИ ЗАНЯТИЙ СТУДЕНТАМИ ГРУППЫ ТКИ "Компьютерная безопасность" ИТТСУ РУТ (МИИТ)</t>
   </si>
@@ -205,9 +205,6 @@
     <t>С, С++</t>
   </si>
   <si>
-    <t>сопротивление параллельного соединения</t>
-  </si>
-  <si>
     <t>расстояние между двумя точками на плоскости</t>
   </si>
   <si>
@@ -251,6 +248,9 @@
   </si>
   <si>
     <t>Python</t>
+  </si>
+  <si>
+    <t>сопротивление параллельного соединения в 1 ЛР, дальше пример 1.14.1 из книги</t>
   </si>
 </sst>
 </file>
@@ -282,7 +282,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -292,6 +292,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -323,7 +329,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -366,18 +372,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -389,6 +383,30 @@
     </xf>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -672,62 +690,63 @@
     <col min="3" max="4" width="9" style="8"/>
     <col min="5" max="5" width="10.85546875"/>
     <col min="6" max="8" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="14.45" customHeight="1">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="18"/>
-      <c r="S1" s="18"/>
-      <c r="T1" s="18"/>
-      <c r="U1" s="18"/>
-      <c r="V1" s="18"/>
-      <c r="W1" s="18"/>
-      <c r="X1" s="18"/>
-      <c r="Y1" s="18"/>
-      <c r="Z1" s="18"/>
-      <c r="AA1" s="18"/>
-      <c r="AB1" s="18"/>
-      <c r="AC1" s="18"/>
-      <c r="AD1" s="18"/>
-      <c r="AE1" s="18"/>
-      <c r="AF1" s="18"/>
-      <c r="AG1" s="18"/>
-      <c r="AH1" s="18"/>
-      <c r="AI1" s="18"/>
-      <c r="AJ1" s="18"/>
-      <c r="AK1" s="18"/>
-      <c r="AL1" s="18"/>
-      <c r="AM1" s="18"/>
-      <c r="AN1" s="18"/>
-      <c r="AO1" s="18"/>
-      <c r="AP1" s="18"/>
-      <c r="AQ1" s="18"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
+      <c r="Y1" s="22"/>
+      <c r="Z1" s="22"/>
+      <c r="AA1" s="22"/>
+      <c r="AB1" s="22"/>
+      <c r="AC1" s="22"/>
+      <c r="AD1" s="22"/>
+      <c r="AE1" s="22"/>
+      <c r="AF1" s="22"/>
+      <c r="AG1" s="22"/>
+      <c r="AH1" s="22"/>
+      <c r="AI1" s="22"/>
+      <c r="AJ1" s="22"/>
+      <c r="AK1" s="22"/>
+      <c r="AL1" s="22"/>
+      <c r="AM1" s="22"/>
+      <c r="AN1" s="22"/>
+      <c r="AO1" s="22"/>
+      <c r="AP1" s="22"/>
+      <c r="AQ1" s="22"/>
     </row>
     <row r="2" spans="1:43" ht="27.6" customHeight="1">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21"/>
+      <c r="B2" s="24"/>
       <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
@@ -746,10 +765,12 @@
       <c r="H2" s="10">
         <v>46079</v>
       </c>
-      <c r="I2" s="22">
+      <c r="I2" s="18">
         <v>46086</v>
       </c>
-      <c r="J2" s="2"/>
+      <c r="J2" s="18">
+        <v>46093</v>
+      </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="3"/>
@@ -769,11 +790,11 @@
       </c>
       <c r="X2" s="3"/>
       <c r="Y2" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Z2" s="3"/>
       <c r="AA2" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AB2" s="3"/>
       <c r="AC2" s="3"/>
@@ -795,53 +816,53 @@
       </c>
     </row>
     <row r="3" spans="1:43">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
-      <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="3"/>
-      <c r="AB3" s="3"/>
-      <c r="AC3" s="3"/>
-      <c r="AD3" s="3"/>
-      <c r="AE3" s="3"/>
-      <c r="AF3" s="3"/>
-      <c r="AG3" s="3"/>
-      <c r="AH3" s="3"/>
-      <c r="AI3" s="3"/>
-      <c r="AJ3" s="3"/>
-      <c r="AK3" s="3"/>
-      <c r="AL3" s="3"/>
-      <c r="AM3" s="3"/>
-      <c r="AN3" s="3"/>
-      <c r="AO3" s="3"/>
-      <c r="AP3" s="3"/>
-      <c r="AQ3" s="1"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="27"/>
+      <c r="R3" s="27"/>
+      <c r="S3" s="27"/>
+      <c r="T3" s="27"/>
+      <c r="U3" s="27"/>
+      <c r="V3" s="27"/>
+      <c r="W3" s="27"/>
+      <c r="X3" s="27"/>
+      <c r="Y3" s="27"/>
+      <c r="Z3" s="27"/>
+      <c r="AA3" s="27"/>
+      <c r="AB3" s="27"/>
+      <c r="AC3" s="27"/>
+      <c r="AD3" s="27"/>
+      <c r="AE3" s="27"/>
+      <c r="AF3" s="27"/>
+      <c r="AG3" s="27"/>
+      <c r="AH3" s="27"/>
+      <c r="AI3" s="27"/>
+      <c r="AJ3" s="27"/>
+      <c r="AK3" s="27"/>
+      <c r="AL3" s="27"/>
+      <c r="AM3" s="27"/>
+      <c r="AN3" s="27"/>
+      <c r="AO3" s="27"/>
+      <c r="AP3" s="27"/>
+      <c r="AQ3" s="29"/>
     </row>
     <row r="4" spans="1:43">
       <c r="A4" s="2">
@@ -854,7 +875,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>7</v>
@@ -868,10 +889,12 @@
       <c r="H4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="J4" s="2"/>
+      <c r="I4" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="3"/>
@@ -882,7 +905,7 @@
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
-      <c r="U4" s="25">
+      <c r="U4" s="21">
         <v>46086</v>
       </c>
       <c r="V4" s="3"/>
@@ -928,13 +951,15 @@
       <c r="G5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="23" t="s">
+      <c r="H5" s="19" t="s">
         <v>7</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="2"/>
+      <c r="J5" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="3"/>
@@ -995,7 +1020,9 @@
       <c r="I6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J6" s="2"/>
+      <c r="J6" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="3"/>
@@ -1043,7 +1070,7 @@
         <v>4</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>7</v>
@@ -1054,13 +1081,15 @@
       <c r="G7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="H7" s="19" t="s">
         <v>7</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="2"/>
+      <c r="J7" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="3"/>
@@ -1115,13 +1144,15 @@
       <c r="G8" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="I8" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="J8" s="2"/>
+      <c r="H8" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="I8" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>24</v>
+      </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="3"/>
@@ -1176,13 +1207,15 @@
       <c r="G9" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="23" t="s">
+      <c r="H9" s="19" t="s">
         <v>7</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J9" s="2"/>
+      <c r="J9" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="3"/>
@@ -1228,7 +1261,7 @@
         <v>7</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>7</v>
@@ -1245,7 +1278,9 @@
       <c r="I10" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J10" s="2"/>
+      <c r="J10" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="3"/>
@@ -1308,7 +1343,9 @@
       <c r="I11" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J11" s="11"/>
+      <c r="J11" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="K11" s="11"/>
       <c r="L11" s="11"/>
       <c r="M11" s="12"/>
@@ -1327,23 +1364,23 @@
       <c r="X11" s="12"/>
       <c r="Y11" s="12"/>
       <c r="Z11" s="12"/>
-      <c r="AA11" s="19"/>
-      <c r="AB11" s="19"/>
-      <c r="AC11" s="19"/>
-      <c r="AD11" s="19"/>
-      <c r="AE11" s="19"/>
-      <c r="AF11" s="19"/>
-      <c r="AG11" s="19"/>
-      <c r="AH11" s="19"/>
-      <c r="AI11" s="19"/>
-      <c r="AJ11" s="19"/>
-      <c r="AK11" s="19"/>
-      <c r="AL11" s="19"/>
-      <c r="AM11" s="19"/>
-      <c r="AN11" s="19"/>
-      <c r="AO11" s="19"/>
-      <c r="AP11" s="19"/>
-      <c r="AQ11" s="18"/>
+      <c r="AA11" s="25"/>
+      <c r="AB11" s="25"/>
+      <c r="AC11" s="25"/>
+      <c r="AD11" s="25"/>
+      <c r="AE11" s="25"/>
+      <c r="AF11" s="25"/>
+      <c r="AG11" s="25"/>
+      <c r="AH11" s="25"/>
+      <c r="AI11" s="25"/>
+      <c r="AJ11" s="25"/>
+      <c r="AK11" s="25"/>
+      <c r="AL11" s="25"/>
+      <c r="AM11" s="25"/>
+      <c r="AN11" s="25"/>
+      <c r="AO11" s="25"/>
+      <c r="AP11" s="25"/>
+      <c r="AQ11" s="22"/>
     </row>
     <row r="12" spans="1:43">
       <c r="A12" s="2">
@@ -1356,7 +1393,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>7</v>
@@ -1373,7 +1410,9 @@
       <c r="I12" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J12" s="11"/>
+      <c r="J12" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
       <c r="M12" s="12"/>
@@ -1392,23 +1431,23 @@
       <c r="X12" s="12"/>
       <c r="Y12" s="12"/>
       <c r="Z12" s="12"/>
-      <c r="AA12" s="19"/>
-      <c r="AB12" s="19"/>
-      <c r="AC12" s="19"/>
-      <c r="AD12" s="19"/>
-      <c r="AE12" s="19"/>
-      <c r="AF12" s="19"/>
-      <c r="AG12" s="19"/>
-      <c r="AH12" s="19"/>
-      <c r="AI12" s="19"/>
-      <c r="AJ12" s="19"/>
-      <c r="AK12" s="19"/>
-      <c r="AL12" s="19"/>
-      <c r="AM12" s="19"/>
-      <c r="AN12" s="19"/>
-      <c r="AO12" s="19"/>
-      <c r="AP12" s="19"/>
-      <c r="AQ12" s="18"/>
+      <c r="AA12" s="25"/>
+      <c r="AB12" s="25"/>
+      <c r="AC12" s="25"/>
+      <c r="AD12" s="25"/>
+      <c r="AE12" s="25"/>
+      <c r="AF12" s="25"/>
+      <c r="AG12" s="25"/>
+      <c r="AH12" s="25"/>
+      <c r="AI12" s="25"/>
+      <c r="AJ12" s="25"/>
+      <c r="AK12" s="25"/>
+      <c r="AL12" s="25"/>
+      <c r="AM12" s="25"/>
+      <c r="AN12" s="25"/>
+      <c r="AO12" s="25"/>
+      <c r="AP12" s="25"/>
+      <c r="AQ12" s="22"/>
     </row>
     <row r="13" spans="1:43">
       <c r="A13" s="2">
@@ -1421,7 +1460,7 @@
         <v>10</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>7</v>
@@ -1438,7 +1477,9 @@
       <c r="I13" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J13" s="11"/>
+      <c r="J13" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
       <c r="M13" s="12"/>
@@ -1453,27 +1494,29 @@
         <v>46072</v>
       </c>
       <c r="V13" s="12"/>
-      <c r="W13" s="12"/>
+      <c r="W13" s="21">
+        <v>46093</v>
+      </c>
       <c r="X13" s="12"/>
       <c r="Y13" s="12"/>
       <c r="Z13" s="12"/>
-      <c r="AA13" s="19"/>
-      <c r="AB13" s="19"/>
-      <c r="AC13" s="19"/>
-      <c r="AD13" s="19"/>
-      <c r="AE13" s="19"/>
-      <c r="AF13" s="19"/>
-      <c r="AG13" s="19"/>
-      <c r="AH13" s="19"/>
-      <c r="AI13" s="19"/>
-      <c r="AJ13" s="19"/>
-      <c r="AK13" s="19"/>
-      <c r="AL13" s="19"/>
-      <c r="AM13" s="19"/>
-      <c r="AN13" s="19"/>
-      <c r="AO13" s="19"/>
-      <c r="AP13" s="19"/>
-      <c r="AQ13" s="18"/>
+      <c r="AA13" s="25"/>
+      <c r="AB13" s="25"/>
+      <c r="AC13" s="25"/>
+      <c r="AD13" s="25"/>
+      <c r="AE13" s="25"/>
+      <c r="AF13" s="25"/>
+      <c r="AG13" s="25"/>
+      <c r="AH13" s="25"/>
+      <c r="AI13" s="25"/>
+      <c r="AJ13" s="25"/>
+      <c r="AK13" s="25"/>
+      <c r="AL13" s="25"/>
+      <c r="AM13" s="25"/>
+      <c r="AN13" s="25"/>
+      <c r="AO13" s="25"/>
+      <c r="AP13" s="25"/>
+      <c r="AQ13" s="22"/>
     </row>
     <row r="14" spans="1:43">
       <c r="A14" s="2">
@@ -1498,10 +1541,12 @@
       <c r="H14" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I14" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="J14" s="2"/>
+      <c r="I14" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="3"/>
@@ -1547,7 +1592,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>7</v>
@@ -1564,7 +1609,9 @@
       <c r="I15" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J15" s="2"/>
+      <c r="J15" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="3"/>
@@ -1627,7 +1674,9 @@
       <c r="I16" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J16" s="2"/>
+      <c r="J16" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="3"/>
@@ -1675,7 +1724,7 @@
         <v>13</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>7</v>
@@ -1692,7 +1741,9 @@
       <c r="I17" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J17" s="2"/>
+      <c r="J17" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="3"/>
@@ -1740,7 +1791,7 @@
         <v>4</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>7</v>
@@ -1751,13 +1802,15 @@
       <c r="G18" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H18" s="23" t="s">
+      <c r="H18" s="19" t="s">
         <v>7</v>
       </c>
       <c r="I18" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J18" s="2"/>
+      <c r="J18" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="3"/>
@@ -1812,13 +1865,15 @@
       <c r="G19" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H19" s="23" t="s">
+      <c r="H19" s="19" t="s">
         <v>7</v>
       </c>
       <c r="I19" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J19" s="2"/>
+      <c r="J19" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="3"/>
@@ -1879,7 +1934,9 @@
       <c r="I20" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J20" s="2"/>
+      <c r="J20" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="3"/>
@@ -1937,10 +1994,12 @@
       <c r="H21" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I21" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="J21" s="2"/>
+      <c r="I21" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>24</v>
+      </c>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="3"/>
@@ -2001,7 +2060,9 @@
       <c r="I22" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J22" s="2"/>
+      <c r="J22" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="3"/>
@@ -2049,7 +2110,7 @@
         <v>14</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>7</v>
@@ -2066,7 +2127,9 @@
       <c r="I23" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J23" s="2"/>
+      <c r="J23" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
       <c r="M23" s="3"/>
@@ -2114,7 +2177,7 @@
         <v>15</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>7</v>
@@ -2125,13 +2188,15 @@
       <c r="G24" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H24" s="23" t="s">
+      <c r="H24" s="19" t="s">
         <v>7</v>
       </c>
       <c r="I24" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J24" s="2"/>
+      <c r="J24" s="9" t="s">
+        <v>24</v>
+      </c>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="3"/>
@@ -2192,7 +2257,9 @@
       <c r="I25" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J25" s="2"/>
+      <c r="J25" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="3"/>
@@ -2255,7 +2322,9 @@
       <c r="I26" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="J26" s="2"/>
+      <c r="J26" s="9" t="s">
+        <v>24</v>
+      </c>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="3"/>
@@ -2316,7 +2385,9 @@
       <c r="I27" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J27" s="2"/>
+      <c r="J27" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="3"/>
@@ -2362,7 +2433,7 @@
         <v>1</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>7</v>
@@ -2376,10 +2447,12 @@
       <c r="H28" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I28" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="J28" s="2"/>
+      <c r="I28" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="3"/>
@@ -2390,7 +2463,7 @@
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
       <c r="T28" s="3"/>
-      <c r="U28" s="25">
+      <c r="U28" s="21">
         <v>46086</v>
       </c>
       <c r="V28" s="3"/>
@@ -2442,7 +2515,9 @@
       <c r="I29" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J29" s="2"/>
+      <c r="J29" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
       <c r="M29" s="3"/>
@@ -2490,7 +2565,7 @@
         <v>12</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>7</v>
@@ -2501,13 +2576,15 @@
       <c r="G30" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H30" s="23" t="s">
+      <c r="H30" s="19" t="s">
         <v>7</v>
       </c>
       <c r="I30" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J30" s="2"/>
+      <c r="J30" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
       <c r="M30" s="3"/>
@@ -2555,7 +2632,7 @@
         <v>3</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>7</v>
@@ -2572,7 +2649,9 @@
       <c r="I31" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J31" s="2"/>
+      <c r="J31" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
       <c r="M31" s="3"/>
@@ -2629,13 +2708,15 @@
       <c r="G32" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H32" s="23" t="s">
+      <c r="H32" s="19" t="s">
         <v>7</v>
       </c>
       <c r="I32" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J32" s="2"/>
+      <c r="J32" s="9" t="s">
+        <v>24</v>
+      </c>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
       <c r="M32" s="3"/>
@@ -2696,7 +2777,9 @@
       <c r="I33" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J33" s="2"/>
+      <c r="J33" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
       <c r="M33" s="3"/>
@@ -2759,7 +2842,9 @@
       <c r="I34" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J34" s="2"/>
+      <c r="J34" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
       <c r="M34" s="3"/>
@@ -2774,7 +2859,9 @@
         <v>46072</v>
       </c>
       <c r="V34" s="3"/>
-      <c r="W34" s="3"/>
+      <c r="W34" s="21">
+        <v>46093</v>
+      </c>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
       <c r="Z34" s="3"/>
@@ -2819,10 +2906,12 @@
       <c r="H35" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I35" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="J35" s="2"/>
+      <c r="I35" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>24</v>
+      </c>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
       <c r="M35" s="3"/>
@@ -2865,7 +2954,7 @@
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
+      <c r="J36" s="9"/>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
       <c r="M36" s="3"/>
@@ -2919,7 +3008,7 @@
         <v>43</v>
       </c>
       <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
+      <c r="J37" s="9"/>
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
       <c r="M37" s="3"/>
@@ -2979,14 +3068,17 @@
     </row>
     <row r="39" spans="1:43">
       <c r="E39" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G39" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
     <mergeCell ref="A1:AQ1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="AA11:AA13"/>
@@ -3003,9 +3095,6 @@
     <mergeCell ref="AQ11:AQ13"/>
     <mergeCell ref="AI11:AI13"/>
     <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3017,56 +3106,56 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="18"/>
-      <c r="S1" s="18"/>
-      <c r="T1" s="18"/>
-      <c r="U1" s="18"/>
-      <c r="V1" s="18"/>
-      <c r="W1" s="18"/>
-      <c r="X1" s="18"/>
-      <c r="Y1" s="18"/>
-      <c r="Z1" s="18"/>
-      <c r="AA1" s="18"/>
-      <c r="AB1" s="18"/>
-      <c r="AC1" s="18"/>
-      <c r="AD1" s="18"/>
-      <c r="AE1" s="18"/>
-      <c r="AF1" s="18"/>
-      <c r="AG1" s="18"/>
-      <c r="AH1" s="18"/>
-      <c r="AI1" s="18"/>
-      <c r="AJ1" s="18"/>
-      <c r="AK1" s="18"/>
-      <c r="AL1" s="18"/>
-      <c r="AM1" s="18"/>
-      <c r="AN1" s="18"/>
-      <c r="AO1" s="18"/>
-      <c r="AP1" s="18"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
+      <c r="Y1" s="22"/>
+      <c r="Z1" s="22"/>
+      <c r="AA1" s="22"/>
+      <c r="AB1" s="22"/>
+      <c r="AC1" s="22"/>
+      <c r="AD1" s="22"/>
+      <c r="AE1" s="22"/>
+      <c r="AF1" s="22"/>
+      <c r="AG1" s="22"/>
+      <c r="AH1" s="22"/>
+      <c r="AI1" s="22"/>
+      <c r="AJ1" s="22"/>
+      <c r="AK1" s="22"/>
+      <c r="AL1" s="22"/>
+      <c r="AM1" s="22"/>
+      <c r="AN1" s="22"/>
+      <c r="AO1" s="22"/>
+      <c r="AP1" s="22"/>
     </row>
     <row r="2" spans="1:42" ht="30">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21"/>
+      <c r="B2" s="24"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -3495,142 +3584,142 @@
       <c r="AP10" s="1"/>
     </row>
     <row r="11" spans="1:42">
-      <c r="A11" s="21">
+      <c r="A11" s="24">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19"/>
-      <c r="P11" s="19"/>
-      <c r="Q11" s="19"/>
-      <c r="R11" s="19"/>
-      <c r="S11" s="19"/>
-      <c r="T11" s="19"/>
-      <c r="U11" s="19"/>
-      <c r="V11" s="19"/>
-      <c r="W11" s="19"/>
-      <c r="X11" s="19"/>
-      <c r="Y11" s="19"/>
-      <c r="Z11" s="19"/>
-      <c r="AA11" s="19"/>
-      <c r="AB11" s="19"/>
-      <c r="AC11" s="19"/>
-      <c r="AD11" s="19"/>
-      <c r="AE11" s="19"/>
-      <c r="AF11" s="19"/>
-      <c r="AG11" s="19"/>
-      <c r="AH11" s="19"/>
-      <c r="AI11" s="19"/>
-      <c r="AJ11" s="19"/>
-      <c r="AK11" s="19"/>
-      <c r="AL11" s="19"/>
-      <c r="AM11" s="19"/>
-      <c r="AN11" s="19"/>
-      <c r="AO11" s="19"/>
-      <c r="AP11" s="18"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="25"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="25"/>
+      <c r="P11" s="25"/>
+      <c r="Q11" s="25"/>
+      <c r="R11" s="25"/>
+      <c r="S11" s="25"/>
+      <c r="T11" s="25"/>
+      <c r="U11" s="25"/>
+      <c r="V11" s="25"/>
+      <c r="W11" s="25"/>
+      <c r="X11" s="25"/>
+      <c r="Y11" s="25"/>
+      <c r="Z11" s="25"/>
+      <c r="AA11" s="25"/>
+      <c r="AB11" s="25"/>
+      <c r="AC11" s="25"/>
+      <c r="AD11" s="25"/>
+      <c r="AE11" s="25"/>
+      <c r="AF11" s="25"/>
+      <c r="AG11" s="25"/>
+      <c r="AH11" s="25"/>
+      <c r="AI11" s="25"/>
+      <c r="AJ11" s="25"/>
+      <c r="AK11" s="25"/>
+      <c r="AL11" s="25"/>
+      <c r="AM11" s="25"/>
+      <c r="AN11" s="25"/>
+      <c r="AO11" s="25"/>
+      <c r="AP11" s="22"/>
     </row>
     <row r="12" spans="1:42">
-      <c r="A12" s="21"/>
+      <c r="A12" s="24"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="19"/>
-      <c r="Q12" s="19"/>
-      <c r="R12" s="19"/>
-      <c r="S12" s="19"/>
-      <c r="T12" s="19"/>
-      <c r="U12" s="19"/>
-      <c r="V12" s="19"/>
-      <c r="W12" s="19"/>
-      <c r="X12" s="19"/>
-      <c r="Y12" s="19"/>
-      <c r="Z12" s="19"/>
-      <c r="AA12" s="19"/>
-      <c r="AB12" s="19"/>
-      <c r="AC12" s="19"/>
-      <c r="AD12" s="19"/>
-      <c r="AE12" s="19"/>
-      <c r="AF12" s="19"/>
-      <c r="AG12" s="19"/>
-      <c r="AH12" s="19"/>
-      <c r="AI12" s="19"/>
-      <c r="AJ12" s="19"/>
-      <c r="AK12" s="19"/>
-      <c r="AL12" s="19"/>
-      <c r="AM12" s="19"/>
-      <c r="AN12" s="19"/>
-      <c r="AO12" s="19"/>
-      <c r="AP12" s="18"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="25"/>
+      <c r="M12" s="25"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="25"/>
+      <c r="P12" s="25"/>
+      <c r="Q12" s="25"/>
+      <c r="R12" s="25"/>
+      <c r="S12" s="25"/>
+      <c r="T12" s="25"/>
+      <c r="U12" s="25"/>
+      <c r="V12" s="25"/>
+      <c r="W12" s="25"/>
+      <c r="X12" s="25"/>
+      <c r="Y12" s="25"/>
+      <c r="Z12" s="25"/>
+      <c r="AA12" s="25"/>
+      <c r="AB12" s="25"/>
+      <c r="AC12" s="25"/>
+      <c r="AD12" s="25"/>
+      <c r="AE12" s="25"/>
+      <c r="AF12" s="25"/>
+      <c r="AG12" s="25"/>
+      <c r="AH12" s="25"/>
+      <c r="AI12" s="25"/>
+      <c r="AJ12" s="25"/>
+      <c r="AK12" s="25"/>
+      <c r="AL12" s="25"/>
+      <c r="AM12" s="25"/>
+      <c r="AN12" s="25"/>
+      <c r="AO12" s="25"/>
+      <c r="AP12" s="22"/>
     </row>
     <row r="13" spans="1:42">
-      <c r="A13" s="21"/>
+      <c r="A13" s="24"/>
       <c r="B13" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="19"/>
-      <c r="O13" s="19"/>
-      <c r="P13" s="19"/>
-      <c r="Q13" s="19"/>
-      <c r="R13" s="19"/>
-      <c r="S13" s="19"/>
-      <c r="T13" s="19"/>
-      <c r="U13" s="19"/>
-      <c r="V13" s="19"/>
-      <c r="W13" s="19"/>
-      <c r="X13" s="19"/>
-      <c r="Y13" s="19"/>
-      <c r="Z13" s="19"/>
-      <c r="AA13" s="19"/>
-      <c r="AB13" s="19"/>
-      <c r="AC13" s="19"/>
-      <c r="AD13" s="19"/>
-      <c r="AE13" s="19"/>
-      <c r="AF13" s="19"/>
-      <c r="AG13" s="19"/>
-      <c r="AH13" s="19"/>
-      <c r="AI13" s="19"/>
-      <c r="AJ13" s="19"/>
-      <c r="AK13" s="19"/>
-      <c r="AL13" s="19"/>
-      <c r="AM13" s="19"/>
-      <c r="AN13" s="19"/>
-      <c r="AO13" s="19"/>
-      <c r="AP13" s="18"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="24"/>
+      <c r="K13" s="24"/>
+      <c r="L13" s="25"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="25"/>
+      <c r="O13" s="25"/>
+      <c r="P13" s="25"/>
+      <c r="Q13" s="25"/>
+      <c r="R13" s="25"/>
+      <c r="S13" s="25"/>
+      <c r="T13" s="25"/>
+      <c r="U13" s="25"/>
+      <c r="V13" s="25"/>
+      <c r="W13" s="25"/>
+      <c r="X13" s="25"/>
+      <c r="Y13" s="25"/>
+      <c r="Z13" s="25"/>
+      <c r="AA13" s="25"/>
+      <c r="AB13" s="25"/>
+      <c r="AC13" s="25"/>
+      <c r="AD13" s="25"/>
+      <c r="AE13" s="25"/>
+      <c r="AF13" s="25"/>
+      <c r="AG13" s="25"/>
+      <c r="AH13" s="25"/>
+      <c r="AI13" s="25"/>
+      <c r="AJ13" s="25"/>
+      <c r="AK13" s="25"/>
+      <c r="AL13" s="25"/>
+      <c r="AM13" s="25"/>
+      <c r="AN13" s="25"/>
+      <c r="AO13" s="25"/>
+      <c r="AP13" s="22"/>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" s="2">
@@ -4786,6 +4875,33 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="AO11:AO13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
+    <mergeCell ref="AN11:AN13"/>
+    <mergeCell ref="AE11:AE13"/>
+    <mergeCell ref="AF11:AF13"/>
+    <mergeCell ref="AG11:AG13"/>
+    <mergeCell ref="AH11:AH13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="Z11:Z13"/>
+    <mergeCell ref="AA11:AA13"/>
+    <mergeCell ref="AB11:AB13"/>
+    <mergeCell ref="AC11:AC13"/>
+    <mergeCell ref="AD11:AD13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="V11:V13"/>
+    <mergeCell ref="W11:W13"/>
+    <mergeCell ref="X11:X13"/>
+    <mergeCell ref="Y11:Y13"/>
+    <mergeCell ref="P11:P13"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="T11:T13"/>
     <mergeCell ref="A1:AP1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A11:A13"/>
@@ -4802,33 +4918,6 @@
     <mergeCell ref="M11:M13"/>
     <mergeCell ref="N11:N13"/>
     <mergeCell ref="O11:O13"/>
-    <mergeCell ref="P11:P13"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="T11:T13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="V11:V13"/>
-    <mergeCell ref="W11:W13"/>
-    <mergeCell ref="X11:X13"/>
-    <mergeCell ref="Y11:Y13"/>
-    <mergeCell ref="Z11:Z13"/>
-    <mergeCell ref="AA11:AA13"/>
-    <mergeCell ref="AB11:AB13"/>
-    <mergeCell ref="AC11:AC13"/>
-    <mergeCell ref="AD11:AD13"/>
-    <mergeCell ref="AE11:AE13"/>
-    <mergeCell ref="AF11:AF13"/>
-    <mergeCell ref="AG11:AG13"/>
-    <mergeCell ref="AH11:AH13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="AO11:AO13"/>
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="AN11:AN13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ТКИ-341_Реверс_Инжиниринг.xlsx
+++ b/ТКИ-341_Реверс_Инжиниринг.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\Reverse_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F66168-3507-4D51-BCF8-BB46C387EB23}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{032432B6-9CCF-4F8C-904F-7F62ECE280EA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="71">
   <si>
     <t>ВЕДОМОСТЬ ПОСЕЩАЕМОСТИ ЗАНЯТИЙ СТУДЕНТАМИ ГРУППЫ ТКИ "Компьютерная безопасность" ИТТСУ РУТ (МИИТ)</t>
   </si>
@@ -252,6 +252,27 @@
   <si>
     <t>сопротивление параллельного соединения в 1 ЛР, дальше пример 1.14.1 из книги</t>
   </si>
+  <si>
+    <t>решение квадратного уравнения</t>
+  </si>
+  <si>
+    <t>проверка числа на простоту</t>
+  </si>
+  <si>
+    <t>Santa</t>
+  </si>
+  <si>
+    <t>Регулярные выражения</t>
+  </si>
+  <si>
+    <t>Творческое</t>
+  </si>
+  <si>
+    <t>периметр и площадь прямоугольного треугольника</t>
+  </si>
+  <si>
+    <t>иетрационно элементы увеличиваем на 4 и умножаем на 2</t>
+  </si>
 </sst>
 </file>
 
@@ -282,7 +303,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -298,6 +319,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -329,7 +362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -385,15 +418,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -407,6 +431,24 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -683,70 +725,75 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AQ39"/>
+  <dimension ref="A1:AS39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="37.28515625" customWidth="1"/>
-    <col min="3" max="4" width="9" style="8"/>
+    <col min="3" max="3" width="9" style="8"/>
+    <col min="4" max="4" width="29" style="8" customWidth="1"/>
     <col min="5" max="5" width="10.85546875"/>
     <col min="6" max="8" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="15" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11" customWidth="1"/>
+    <col min="17" max="21" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="14.45" customHeight="1">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:45" ht="14.45" customHeight="1">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
-      <c r="S1" s="22"/>
-      <c r="T1" s="22"/>
-      <c r="U1" s="22"/>
-      <c r="V1" s="22"/>
-      <c r="W1" s="22"/>
-      <c r="X1" s="22"/>
-      <c r="Y1" s="22"/>
-      <c r="Z1" s="22"/>
-      <c r="AA1" s="22"/>
-      <c r="AB1" s="22"/>
-      <c r="AC1" s="22"/>
-      <c r="AD1" s="22"/>
-      <c r="AE1" s="22"/>
-      <c r="AF1" s="22"/>
-      <c r="AG1" s="22"/>
-      <c r="AH1" s="22"/>
-      <c r="AI1" s="22"/>
-      <c r="AJ1" s="22"/>
-      <c r="AK1" s="22"/>
-      <c r="AL1" s="22"/>
-      <c r="AM1" s="22"/>
-      <c r="AN1" s="22"/>
-      <c r="AO1" s="22"/>
-      <c r="AP1" s="22"/>
-      <c r="AQ1" s="22"/>
-    </row>
-    <row r="2" spans="1:43" ht="27.6" customHeight="1">
-      <c r="A2" s="24" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
+      <c r="Y1" s="28"/>
+      <c r="Z1" s="28"/>
+      <c r="AA1" s="28"/>
+      <c r="AB1" s="28"/>
+      <c r="AC1" s="28"/>
+      <c r="AD1" s="28"/>
+      <c r="AE1" s="28"/>
+      <c r="AF1" s="28"/>
+      <c r="AG1" s="28"/>
+      <c r="AH1" s="28"/>
+      <c r="AI1" s="28"/>
+      <c r="AJ1" s="28"/>
+      <c r="AK1" s="28"/>
+      <c r="AL1" s="28"/>
+      <c r="AM1" s="28"/>
+      <c r="AN1" s="28"/>
+      <c r="AO1" s="28"/>
+      <c r="AP1" s="28"/>
+      <c r="AQ1" s="28"/>
+      <c r="AR1" s="28"/>
+      <c r="AS1" s="28"/>
+    </row>
+    <row r="2" spans="1:45" ht="27.6" customHeight="1">
+      <c r="A2" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="24"/>
+      <c r="B2" s="30"/>
       <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
@@ -771,39 +818,67 @@
       <c r="J2" s="18">
         <v>46093</v>
       </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3" t="s">
+      <c r="K2" s="18">
+        <v>46100</v>
+      </c>
+      <c r="L2" s="18">
+        <v>46107</v>
+      </c>
+      <c r="M2" s="18">
+        <v>46114</v>
+      </c>
+      <c r="N2" s="18">
+        <v>46121</v>
+      </c>
+      <c r="O2" s="18">
+        <v>46128</v>
+      </c>
+      <c r="P2" s="18">
+        <v>46135</v>
+      </c>
+      <c r="Q2" s="18">
+        <v>46142</v>
+      </c>
+      <c r="R2" s="18">
+        <v>46149</v>
+      </c>
+      <c r="S2" s="18">
+        <v>46156</v>
+      </c>
+      <c r="T2" s="18">
+        <v>46163</v>
+      </c>
+      <c r="U2" s="18">
+        <v>46170</v>
+      </c>
+      <c r="V2" s="22"/>
+      <c r="W2" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="V2" s="3"/>
-      <c r="W2" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="X2" s="3"/>
       <c r="Y2" s="3" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="Z2" s="3"/>
       <c r="AA2" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB2" s="3"/>
+      <c r="AC2" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="AB2" s="3"/>
-      <c r="AC2" s="3"/>
       <c r="AD2" s="3"/>
-      <c r="AE2" s="3"/>
+      <c r="AE2" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="AF2" s="3"/>
-      <c r="AG2" s="3"/>
+      <c r="AG2" s="3" t="s">
+        <v>67</v>
+      </c>
       <c r="AH2" s="3"/>
-      <c r="AI2" s="3"/>
+      <c r="AI2" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="AJ2" s="3"/>
       <c r="AK2" s="3"/>
       <c r="AL2" s="3"/>
@@ -811,60 +886,64 @@
       <c r="AN2" s="3"/>
       <c r="AO2" s="3"/>
       <c r="AP2" s="3"/>
-      <c r="AQ2" s="1" t="s">
+      <c r="AQ2" s="3"/>
+      <c r="AR2" s="3"/>
+      <c r="AS2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:43">
-      <c r="A3" s="26" t="s">
+    <row r="3" spans="1:45">
+      <c r="A3" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="27"/>
-      <c r="N3" s="27"/>
-      <c r="O3" s="27"/>
-      <c r="P3" s="27"/>
-      <c r="Q3" s="27"/>
-      <c r="R3" s="27"/>
-      <c r="S3" s="27"/>
-      <c r="T3" s="27"/>
-      <c r="U3" s="27"/>
-      <c r="V3" s="27"/>
-      <c r="W3" s="27"/>
-      <c r="X3" s="27"/>
-      <c r="Y3" s="27"/>
-      <c r="Z3" s="27"/>
-      <c r="AA3" s="27"/>
-      <c r="AB3" s="27"/>
-      <c r="AC3" s="27"/>
-      <c r="AD3" s="27"/>
-      <c r="AE3" s="27"/>
-      <c r="AF3" s="27"/>
-      <c r="AG3" s="27"/>
-      <c r="AH3" s="27"/>
-      <c r="AI3" s="27"/>
-      <c r="AJ3" s="27"/>
-      <c r="AK3" s="27"/>
-      <c r="AL3" s="27"/>
-      <c r="AM3" s="27"/>
-      <c r="AN3" s="27"/>
-      <c r="AO3" s="27"/>
-      <c r="AP3" s="27"/>
-      <c r="AQ3" s="29"/>
-    </row>
-    <row r="4" spans="1:43">
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
+      <c r="S3" s="24"/>
+      <c r="T3" s="24"/>
+      <c r="U3" s="24"/>
+      <c r="V3" s="24"/>
+      <c r="W3" s="24"/>
+      <c r="X3" s="24"/>
+      <c r="Y3" s="24"/>
+      <c r="Z3" s="24"/>
+      <c r="AA3" s="24"/>
+      <c r="AB3" s="24"/>
+      <c r="AC3" s="24"/>
+      <c r="AD3" s="24"/>
+      <c r="AE3" s="24"/>
+      <c r="AF3" s="24"/>
+      <c r="AG3" s="24"/>
+      <c r="AH3" s="24"/>
+      <c r="AI3" s="24"/>
+      <c r="AJ3" s="24"/>
+      <c r="AK3" s="24"/>
+      <c r="AL3" s="24"/>
+      <c r="AM3" s="24"/>
+      <c r="AN3" s="24"/>
+      <c r="AO3" s="24"/>
+      <c r="AP3" s="24"/>
+      <c r="AQ3" s="24"/>
+      <c r="AR3" s="24"/>
+      <c r="AS3" s="26"/>
+    </row>
+    <row r="4" spans="1:45">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -895,7 +974,9 @@
       <c r="J4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="2"/>
+      <c r="K4" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="L4" s="2"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -905,11 +986,11 @@
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
-      <c r="U4" s="21">
+      <c r="U4" s="22"/>
+      <c r="V4" s="22"/>
+      <c r="W4" s="21">
         <v>46086</v>
       </c>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
@@ -929,9 +1010,11 @@
       <c r="AN4" s="3"/>
       <c r="AO4" s="3"/>
       <c r="AP4" s="3"/>
-      <c r="AQ4" s="1"/>
-    </row>
-    <row r="5" spans="1:43">
+      <c r="AQ4" s="3"/>
+      <c r="AR4" s="3"/>
+      <c r="AS4" s="1"/>
+    </row>
+    <row r="5" spans="1:45">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -941,7 +1024,9 @@
       <c r="C5" s="9">
         <v>2</v>
       </c>
-      <c r="D5" s="9"/>
+      <c r="D5" s="9" t="s">
+        <v>65</v>
+      </c>
       <c r="E5" s="9" t="s">
         <v>7</v>
       </c>
@@ -960,7 +1045,9 @@
       <c r="J5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="2"/>
+      <c r="K5" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="L5" s="2"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
@@ -970,11 +1057,15 @@
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
       <c r="T5" s="3"/>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
-      <c r="W5" s="3"/>
+      <c r="U5" s="22"/>
+      <c r="V5" s="22"/>
+      <c r="W5" s="14">
+        <v>46100</v>
+      </c>
       <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
+      <c r="Y5" s="14">
+        <v>46100</v>
+      </c>
       <c r="Z5" s="3"/>
       <c r="AA5" s="3"/>
       <c r="AB5" s="3"/>
@@ -992,9 +1083,11 @@
       <c r="AN5" s="3"/>
       <c r="AO5" s="3"/>
       <c r="AP5" s="3"/>
-      <c r="AQ5" s="1"/>
-    </row>
-    <row r="6" spans="1:43">
+      <c r="AQ5" s="3"/>
+      <c r="AR5" s="3"/>
+      <c r="AS5" s="1"/>
+    </row>
+    <row r="6" spans="1:45">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1023,7 +1116,9 @@
       <c r="J6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K6" s="2"/>
+      <c r="K6" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="L6" s="2"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
@@ -1033,11 +1128,11 @@
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
       <c r="T6" s="3"/>
-      <c r="U6" s="14">
+      <c r="U6" s="22"/>
+      <c r="V6" s="22"/>
+      <c r="W6" s="14">
         <v>46072</v>
       </c>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
@@ -1057,9 +1152,11 @@
       <c r="AN6" s="3"/>
       <c r="AO6" s="3"/>
       <c r="AP6" s="3"/>
-      <c r="AQ6" s="1"/>
-    </row>
-    <row r="7" spans="1:43">
+      <c r="AQ6" s="3"/>
+      <c r="AR6" s="3"/>
+      <c r="AS6" s="1"/>
+    </row>
+    <row r="7" spans="1:45">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -1090,7 +1187,9 @@
       <c r="J7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K7" s="2"/>
+      <c r="K7" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="L7" s="2"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
@@ -1100,11 +1199,15 @@
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
       <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
+      <c r="U7" s="22"/>
+      <c r="V7" s="22"/>
+      <c r="W7" s="31">
+        <v>46100</v>
+      </c>
       <c r="X7" s="3"/>
-      <c r="Y7" s="3"/>
+      <c r="Y7" s="14">
+        <v>46100</v>
+      </c>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3"/>
       <c r="AB7" s="3"/>
@@ -1122,9 +1225,11 @@
       <c r="AN7" s="3"/>
       <c r="AO7" s="3"/>
       <c r="AP7" s="3"/>
-      <c r="AQ7" s="1"/>
-    </row>
-    <row r="8" spans="1:43" ht="18" customHeight="1">
+      <c r="AQ7" s="3"/>
+      <c r="AR7" s="3"/>
+      <c r="AS7" s="1"/>
+    </row>
+    <row r="8" spans="1:45" ht="18" customHeight="1">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -1153,7 +1258,9 @@
       <c r="J8" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K8" s="2"/>
+      <c r="K8" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="L8" s="2"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
@@ -1163,9 +1270,11 @@
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
+      <c r="U8" s="22"/>
+      <c r="V8" s="22"/>
+      <c r="W8" s="14">
+        <v>46100</v>
+      </c>
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
@@ -1185,9 +1294,11 @@
       <c r="AN8" s="3"/>
       <c r="AO8" s="3"/>
       <c r="AP8" s="3"/>
-      <c r="AQ8" s="1"/>
-    </row>
-    <row r="9" spans="1:43">
+      <c r="AQ8" s="3"/>
+      <c r="AR8" s="3"/>
+      <c r="AS8" s="1"/>
+    </row>
+    <row r="9" spans="1:45">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -1197,7 +1308,9 @@
       <c r="C9" s="9">
         <v>6</v>
       </c>
-      <c r="D9" s="9"/>
+      <c r="D9" s="9" t="s">
+        <v>70</v>
+      </c>
       <c r="E9" s="9" t="s">
         <v>7</v>
       </c>
@@ -1216,7 +1329,9 @@
       <c r="J9" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K9" s="2"/>
+      <c r="K9" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="L9" s="2"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
@@ -1226,9 +1341,11 @@
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
       <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
+      <c r="U9" s="22"/>
+      <c r="V9" s="22"/>
+      <c r="W9" s="14">
+        <v>46100</v>
+      </c>
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
@@ -1248,9 +1365,11 @@
       <c r="AN9" s="3"/>
       <c r="AO9" s="3"/>
       <c r="AP9" s="3"/>
-      <c r="AQ9" s="1"/>
-    </row>
-    <row r="10" spans="1:43">
+      <c r="AQ9" s="3"/>
+      <c r="AR9" s="3"/>
+      <c r="AS9" s="1"/>
+    </row>
+    <row r="10" spans="1:45">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -1281,7 +1400,9 @@
       <c r="J10" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K10" s="2"/>
+      <c r="K10" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="L10" s="2"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
@@ -1291,11 +1412,11 @@
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
       <c r="T10" s="3"/>
-      <c r="U10" s="14">
+      <c r="U10" s="22"/>
+      <c r="V10" s="22"/>
+      <c r="W10" s="14">
         <v>46079</v>
       </c>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
@@ -1315,9 +1436,11 @@
       <c r="AN10" s="3"/>
       <c r="AO10" s="3"/>
       <c r="AP10" s="3"/>
-      <c r="AQ10" s="1"/>
-    </row>
-    <row r="11" spans="1:43" ht="14.45" customHeight="1">
+      <c r="AQ10" s="3"/>
+      <c r="AR10" s="3"/>
+      <c r="AS10" s="1"/>
+    </row>
+    <row r="11" spans="1:45" ht="14.45" customHeight="1">
       <c r="A11" s="2">
         <v>8</v>
       </c>
@@ -1346,7 +1469,9 @@
       <c r="J11" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K11" s="11"/>
+      <c r="K11" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="L11" s="11"/>
       <c r="M11" s="12"/>
       <c r="N11" s="12"/>
@@ -1356,33 +1481,35 @@
       <c r="R11" s="12"/>
       <c r="S11" s="12"/>
       <c r="T11" s="12"/>
-      <c r="U11" s="14">
+      <c r="U11" s="12"/>
+      <c r="V11" s="12"/>
+      <c r="W11" s="14">
         <v>46079</v>
       </c>
-      <c r="V11" s="12"/>
-      <c r="W11" s="12"/>
       <c r="X11" s="12"/>
       <c r="Y11" s="12"/>
       <c r="Z11" s="12"/>
-      <c r="AA11" s="25"/>
-      <c r="AB11" s="25"/>
-      <c r="AC11" s="25"/>
-      <c r="AD11" s="25"/>
-      <c r="AE11" s="25"/>
-      <c r="AF11" s="25"/>
-      <c r="AG11" s="25"/>
-      <c r="AH11" s="25"/>
-      <c r="AI11" s="25"/>
-      <c r="AJ11" s="25"/>
-      <c r="AK11" s="25"/>
-      <c r="AL11" s="25"/>
-      <c r="AM11" s="25"/>
-      <c r="AN11" s="25"/>
-      <c r="AO11" s="25"/>
-      <c r="AP11" s="25"/>
-      <c r="AQ11" s="22"/>
-    </row>
-    <row r="12" spans="1:43">
+      <c r="AA11" s="12"/>
+      <c r="AB11" s="12"/>
+      <c r="AC11" s="27"/>
+      <c r="AD11" s="27"/>
+      <c r="AE11" s="27"/>
+      <c r="AF11" s="27"/>
+      <c r="AG11" s="27"/>
+      <c r="AH11" s="27"/>
+      <c r="AI11" s="27"/>
+      <c r="AJ11" s="27"/>
+      <c r="AK11" s="27"/>
+      <c r="AL11" s="27"/>
+      <c r="AM11" s="27"/>
+      <c r="AN11" s="27"/>
+      <c r="AO11" s="27"/>
+      <c r="AP11" s="27"/>
+      <c r="AQ11" s="27"/>
+      <c r="AR11" s="27"/>
+      <c r="AS11" s="28"/>
+    </row>
+    <row r="12" spans="1:45">
       <c r="A12" s="2">
         <v>9</v>
       </c>
@@ -1413,7 +1540,9 @@
       <c r="J12" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K12" s="11"/>
+      <c r="K12" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="L12" s="11"/>
       <c r="M12" s="12"/>
       <c r="N12" s="12"/>
@@ -1423,33 +1552,35 @@
       <c r="R12" s="12"/>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
-      <c r="U12" s="14">
+      <c r="U12" s="12"/>
+      <c r="V12" s="12"/>
+      <c r="W12" s="14">
         <v>46072</v>
       </c>
-      <c r="V12" s="12"/>
-      <c r="W12" s="12"/>
       <c r="X12" s="12"/>
       <c r="Y12" s="12"/>
       <c r="Z12" s="12"/>
-      <c r="AA12" s="25"/>
-      <c r="AB12" s="25"/>
-      <c r="AC12" s="25"/>
-      <c r="AD12" s="25"/>
-      <c r="AE12" s="25"/>
-      <c r="AF12" s="25"/>
-      <c r="AG12" s="25"/>
-      <c r="AH12" s="25"/>
-      <c r="AI12" s="25"/>
-      <c r="AJ12" s="25"/>
-      <c r="AK12" s="25"/>
-      <c r="AL12" s="25"/>
-      <c r="AM12" s="25"/>
-      <c r="AN12" s="25"/>
-      <c r="AO12" s="25"/>
-      <c r="AP12" s="25"/>
-      <c r="AQ12" s="22"/>
-    </row>
-    <row r="13" spans="1:43">
+      <c r="AA12" s="12"/>
+      <c r="AB12" s="12"/>
+      <c r="AC12" s="27"/>
+      <c r="AD12" s="27"/>
+      <c r="AE12" s="27"/>
+      <c r="AF12" s="27"/>
+      <c r="AG12" s="27"/>
+      <c r="AH12" s="27"/>
+      <c r="AI12" s="27"/>
+      <c r="AJ12" s="27"/>
+      <c r="AK12" s="27"/>
+      <c r="AL12" s="27"/>
+      <c r="AM12" s="27"/>
+      <c r="AN12" s="27"/>
+      <c r="AO12" s="27"/>
+      <c r="AP12" s="27"/>
+      <c r="AQ12" s="27"/>
+      <c r="AR12" s="27"/>
+      <c r="AS12" s="28"/>
+    </row>
+    <row r="13" spans="1:45">
       <c r="A13" s="2">
         <v>10</v>
       </c>
@@ -1480,7 +1611,9 @@
       <c r="J13" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K13" s="11"/>
+      <c r="K13" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="L13" s="11"/>
       <c r="M13" s="12"/>
       <c r="N13" s="12"/>
@@ -1490,35 +1623,37 @@
       <c r="R13" s="12"/>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
-      <c r="U13" s="14">
+      <c r="U13" s="12"/>
+      <c r="V13" s="12"/>
+      <c r="W13" s="14">
         <v>46072</v>
       </c>
-      <c r="V13" s="12"/>
-      <c r="W13" s="21">
+      <c r="X13" s="12"/>
+      <c r="Y13" s="21">
         <v>46093</v>
       </c>
-      <c r="X13" s="12"/>
-      <c r="Y13" s="12"/>
       <c r="Z13" s="12"/>
-      <c r="AA13" s="25"/>
-      <c r="AB13" s="25"/>
-      <c r="AC13" s="25"/>
-      <c r="AD13" s="25"/>
-      <c r="AE13" s="25"/>
-      <c r="AF13" s="25"/>
-      <c r="AG13" s="25"/>
-      <c r="AH13" s="25"/>
-      <c r="AI13" s="25"/>
-      <c r="AJ13" s="25"/>
-      <c r="AK13" s="25"/>
-      <c r="AL13" s="25"/>
-      <c r="AM13" s="25"/>
-      <c r="AN13" s="25"/>
-      <c r="AO13" s="25"/>
-      <c r="AP13" s="25"/>
-      <c r="AQ13" s="22"/>
-    </row>
-    <row r="14" spans="1:43">
+      <c r="AA13" s="12"/>
+      <c r="AB13" s="12"/>
+      <c r="AC13" s="27"/>
+      <c r="AD13" s="27"/>
+      <c r="AE13" s="27"/>
+      <c r="AF13" s="27"/>
+      <c r="AG13" s="27"/>
+      <c r="AH13" s="27"/>
+      <c r="AI13" s="27"/>
+      <c r="AJ13" s="27"/>
+      <c r="AK13" s="27"/>
+      <c r="AL13" s="27"/>
+      <c r="AM13" s="27"/>
+      <c r="AN13" s="27"/>
+      <c r="AO13" s="27"/>
+      <c r="AP13" s="27"/>
+      <c r="AQ13" s="27"/>
+      <c r="AR13" s="27"/>
+      <c r="AS13" s="28"/>
+    </row>
+    <row r="14" spans="1:45">
       <c r="A14" s="2">
         <v>11</v>
       </c>
@@ -1547,7 +1682,9 @@
       <c r="J14" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K14" s="2"/>
+      <c r="K14" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="L14" s="2"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
@@ -1557,8 +1694,8 @@
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
-      <c r="U14" s="3"/>
-      <c r="V14" s="3"/>
+      <c r="U14" s="22"/>
+      <c r="V14" s="22"/>
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
@@ -1579,9 +1716,11 @@
       <c r="AN14" s="3"/>
       <c r="AO14" s="3"/>
       <c r="AP14" s="3"/>
-      <c r="AQ14" s="1"/>
-    </row>
-    <row r="15" spans="1:43">
+      <c r="AQ14" s="3"/>
+      <c r="AR14" s="3"/>
+      <c r="AS14" s="1"/>
+    </row>
+    <row r="15" spans="1:45">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -1612,7 +1751,9 @@
       <c r="J15" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K15" s="2"/>
+      <c r="K15" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="L15" s="2"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
@@ -1622,11 +1763,11 @@
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
       <c r="T15" s="3"/>
-      <c r="U15" s="14">
+      <c r="U15" s="22"/>
+      <c r="V15" s="22"/>
+      <c r="W15" s="14">
         <v>46079</v>
       </c>
-      <c r="V15" s="3"/>
-      <c r="W15" s="3"/>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
@@ -1646,9 +1787,11 @@
       <c r="AN15" s="3"/>
       <c r="AO15" s="3"/>
       <c r="AP15" s="3"/>
-      <c r="AQ15" s="1"/>
-    </row>
-    <row r="16" spans="1:43">
+      <c r="AQ15" s="3"/>
+      <c r="AR15" s="3"/>
+      <c r="AS15" s="1"/>
+    </row>
+    <row r="16" spans="1:45">
       <c r="A16" s="2">
         <v>13</v>
       </c>
@@ -1677,7 +1820,9 @@
       <c r="J16" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K16" s="2"/>
+      <c r="K16" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="L16" s="2"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
@@ -1687,11 +1832,11 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-      <c r="U16" s="14">
+      <c r="U16" s="22"/>
+      <c r="V16" s="22"/>
+      <c r="W16" s="14">
         <v>46072</v>
       </c>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
@@ -1711,9 +1856,11 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
-      <c r="AQ16" s="1"/>
-    </row>
-    <row r="17" spans="1:43">
+      <c r="AQ16" s="3"/>
+      <c r="AR16" s="3"/>
+      <c r="AS16" s="1"/>
+    </row>
+    <row r="17" spans="1:45">
       <c r="A17" s="2">
         <v>14</v>
       </c>
@@ -1744,7 +1891,9 @@
       <c r="J17" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K17" s="2"/>
+      <c r="K17" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="L17" s="2"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
@@ -1754,13 +1903,15 @@
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
       <c r="T17" s="3"/>
-      <c r="U17" s="14">
+      <c r="U17" s="22"/>
+      <c r="V17" s="22"/>
+      <c r="W17" s="14">
         <v>46072</v>
       </c>
-      <c r="V17" s="3"/>
-      <c r="W17" s="3"/>
       <c r="X17" s="3"/>
-      <c r="Y17" s="3"/>
+      <c r="Y17" s="14">
+        <v>46100</v>
+      </c>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3"/>
       <c r="AB17" s="3"/>
@@ -1778,9 +1929,11 @@
       <c r="AN17" s="3"/>
       <c r="AO17" s="3"/>
       <c r="AP17" s="3"/>
-      <c r="AQ17" s="1"/>
-    </row>
-    <row r="18" spans="1:43">
+      <c r="AQ17" s="3"/>
+      <c r="AR17" s="3"/>
+      <c r="AS17" s="1"/>
+    </row>
+    <row r="18" spans="1:45">
       <c r="A18" s="2">
         <v>15</v>
       </c>
@@ -1811,7 +1964,9 @@
       <c r="J18" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K18" s="2"/>
+      <c r="K18" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="L18" s="2"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
@@ -1821,11 +1976,15 @@
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
       <c r="T18" s="3"/>
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
+      <c r="U18" s="22"/>
+      <c r="V18" s="22"/>
+      <c r="W18" s="31">
+        <v>46100</v>
+      </c>
       <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
+      <c r="Y18" s="14">
+        <v>46100</v>
+      </c>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3"/>
       <c r="AB18" s="3"/>
@@ -1843,13 +2002,15 @@
       <c r="AN18" s="3"/>
       <c r="AO18" s="3"/>
       <c r="AP18" s="3"/>
-      <c r="AQ18" s="1"/>
-    </row>
-    <row r="19" spans="1:43">
+      <c r="AQ18" s="3"/>
+      <c r="AR18" s="3"/>
+      <c r="AS18" s="1"/>
+    </row>
+    <row r="19" spans="1:45">
       <c r="A19" s="2">
         <v>16</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="15" t="s">
         <v>22</v>
       </c>
       <c r="C19" s="9">
@@ -1874,7 +2035,9 @@
       <c r="J19" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K19" s="2"/>
+      <c r="K19" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="L19" s="2"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
@@ -1884,9 +2047,11 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
+      <c r="U19" s="22"/>
+      <c r="V19" s="22"/>
+      <c r="W19" s="14">
+        <v>46100</v>
+      </c>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
@@ -1906,9 +2071,11 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
-      <c r="AQ19" s="1"/>
-    </row>
-    <row r="20" spans="1:43">
+      <c r="AQ19" s="3"/>
+      <c r="AR19" s="3"/>
+      <c r="AS19" s="1"/>
+    </row>
+    <row r="20" spans="1:45">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -1918,7 +2085,9 @@
       <c r="C20" s="9">
         <v>16</v>
       </c>
-      <c r="D20" s="9"/>
+      <c r="D20" s="9" t="s">
+        <v>64</v>
+      </c>
       <c r="E20" s="9" t="s">
         <v>24</v>
       </c>
@@ -1937,7 +2106,9 @@
       <c r="J20" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K20" s="2"/>
+      <c r="K20" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="L20" s="2"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
@@ -1947,8 +2118,8 @@
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
       <c r="T20" s="3"/>
-      <c r="U20" s="3"/>
-      <c r="V20" s="3"/>
+      <c r="U20" s="22"/>
+      <c r="V20" s="22"/>
       <c r="W20" s="3"/>
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
@@ -1969,9 +2140,11 @@
       <c r="AN20" s="3"/>
       <c r="AO20" s="3"/>
       <c r="AP20" s="3"/>
-      <c r="AQ20" s="1"/>
-    </row>
-    <row r="21" spans="1:43">
+      <c r="AQ20" s="3"/>
+      <c r="AR20" s="3"/>
+      <c r="AS20" s="1"/>
+    </row>
+    <row r="21" spans="1:45">
       <c r="A21" s="2">
         <v>18</v>
       </c>
@@ -1981,7 +2154,9 @@
       <c r="C21" s="9">
         <v>5</v>
       </c>
-      <c r="D21" s="9"/>
+      <c r="D21" s="9" t="s">
+        <v>69</v>
+      </c>
       <c r="E21" s="9" t="s">
         <v>7</v>
       </c>
@@ -2000,7 +2175,9 @@
       <c r="J21" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K21" s="2"/>
+      <c r="K21" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="L21" s="2"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
@@ -2010,9 +2187,11 @@
       <c r="R21" s="3"/>
       <c r="S21" s="3"/>
       <c r="T21" s="3"/>
-      <c r="U21" s="3"/>
-      <c r="V21" s="3"/>
-      <c r="W21" s="3"/>
+      <c r="U21" s="22"/>
+      <c r="V21" s="22"/>
+      <c r="W21" s="14">
+        <v>46100</v>
+      </c>
       <c r="X21" s="3"/>
       <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
@@ -2032,9 +2211,11 @@
       <c r="AN21" s="3"/>
       <c r="AO21" s="3"/>
       <c r="AP21" s="3"/>
-      <c r="AQ21" s="1"/>
-    </row>
-    <row r="22" spans="1:43">
+      <c r="AQ21" s="3"/>
+      <c r="AR21" s="3"/>
+      <c r="AS21" s="1"/>
+    </row>
+    <row r="22" spans="1:45">
       <c r="A22" s="2">
         <v>19</v>
       </c>
@@ -2063,7 +2244,9 @@
       <c r="J22" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K22" s="2"/>
+      <c r="K22" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="L22" s="2"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
@@ -2073,13 +2256,15 @@
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
       <c r="T22" s="3"/>
-      <c r="U22" s="14">
+      <c r="U22" s="22"/>
+      <c r="V22" s="22"/>
+      <c r="W22" s="14">
         <v>46072</v>
       </c>
-      <c r="V22" s="3"/>
-      <c r="W22" s="3"/>
       <c r="X22" s="3"/>
-      <c r="Y22" s="3"/>
+      <c r="Y22" s="14">
+        <v>46100</v>
+      </c>
       <c r="Z22" s="3"/>
       <c r="AA22" s="3"/>
       <c r="AB22" s="3"/>
@@ -2097,9 +2282,11 @@
       <c r="AN22" s="3"/>
       <c r="AO22" s="3"/>
       <c r="AP22" s="3"/>
-      <c r="AQ22" s="1"/>
-    </row>
-    <row r="23" spans="1:43">
+      <c r="AQ22" s="3"/>
+      <c r="AR22" s="3"/>
+      <c r="AS22" s="1"/>
+    </row>
+    <row r="23" spans="1:45">
       <c r="A23" s="2">
         <v>20</v>
       </c>
@@ -2130,7 +2317,9 @@
       <c r="J23" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K23" s="2"/>
+      <c r="K23" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="L23" s="2"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
@@ -2140,13 +2329,15 @@
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
-      <c r="U23" s="14">
+      <c r="U23" s="22"/>
+      <c r="V23" s="22"/>
+      <c r="W23" s="14">
         <v>46072</v>
       </c>
-      <c r="V23" s="3"/>
-      <c r="W23" s="3"/>
       <c r="X23" s="3"/>
-      <c r="Y23" s="3"/>
+      <c r="Y23" s="14">
+        <v>46100</v>
+      </c>
       <c r="Z23" s="3"/>
       <c r="AA23" s="3"/>
       <c r="AB23" s="3"/>
@@ -2164,9 +2355,11 @@
       <c r="AN23" s="3"/>
       <c r="AO23" s="3"/>
       <c r="AP23" s="3"/>
-      <c r="AQ23" s="1"/>
-    </row>
-    <row r="24" spans="1:43">
+      <c r="AQ23" s="3"/>
+      <c r="AR23" s="3"/>
+      <c r="AS23" s="1"/>
+    </row>
+    <row r="24" spans="1:45">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -2197,7 +2390,9 @@
       <c r="J24" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K24" s="2"/>
+      <c r="K24" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="L24" s="2"/>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
@@ -2207,8 +2402,8 @@
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
       <c r="T24" s="3"/>
-      <c r="U24" s="3"/>
-      <c r="V24" s="3"/>
+      <c r="U24" s="22"/>
+      <c r="V24" s="22"/>
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
@@ -2229,9 +2424,11 @@
       <c r="AN24" s="3"/>
       <c r="AO24" s="3"/>
       <c r="AP24" s="3"/>
-      <c r="AQ24" s="1"/>
-    </row>
-    <row r="25" spans="1:43">
+      <c r="AQ24" s="3"/>
+      <c r="AR24" s="3"/>
+      <c r="AS24" s="1"/>
+    </row>
+    <row r="25" spans="1:45">
       <c r="A25" s="2">
         <v>22</v>
       </c>
@@ -2260,7 +2457,9 @@
       <c r="J25" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K25" s="2"/>
+      <c r="K25" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="L25" s="2"/>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
@@ -2270,11 +2469,11 @@
       <c r="R25" s="3"/>
       <c r="S25" s="3"/>
       <c r="T25" s="3"/>
-      <c r="U25" s="14">
+      <c r="U25" s="22"/>
+      <c r="V25" s="22"/>
+      <c r="W25" s="14">
         <v>46072</v>
       </c>
-      <c r="V25" s="3"/>
-      <c r="W25" s="3"/>
       <c r="X25" s="3"/>
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
@@ -2294,9 +2493,11 @@
       <c r="AN25" s="3"/>
       <c r="AO25" s="3"/>
       <c r="AP25" s="3"/>
-      <c r="AQ25" s="1"/>
-    </row>
-    <row r="26" spans="1:43">
+      <c r="AQ25" s="3"/>
+      <c r="AR25" s="3"/>
+      <c r="AS25" s="1"/>
+    </row>
+    <row r="26" spans="1:45">
       <c r="A26" s="2">
         <v>23</v>
       </c>
@@ -2325,7 +2526,9 @@
       <c r="J26" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K26" s="2"/>
+      <c r="K26" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="L26" s="2"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
@@ -2335,8 +2538,8 @@
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
       <c r="T26" s="3"/>
-      <c r="U26" s="3"/>
-      <c r="V26" s="3"/>
+      <c r="U26" s="22"/>
+      <c r="V26" s="22"/>
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
       <c r="Y26" s="3"/>
@@ -2357,9 +2560,11 @@
       <c r="AN26" s="3"/>
       <c r="AO26" s="3"/>
       <c r="AP26" s="3"/>
-      <c r="AQ26" s="1"/>
-    </row>
-    <row r="27" spans="1:43">
+      <c r="AQ26" s="3"/>
+      <c r="AR26" s="3"/>
+      <c r="AS26" s="1"/>
+    </row>
+    <row r="27" spans="1:45">
       <c r="A27" s="2">
         <v>24</v>
       </c>
@@ -2369,7 +2574,9 @@
       <c r="C27" s="9">
         <v>2</v>
       </c>
-      <c r="D27" s="9"/>
+      <c r="D27" s="9" t="s">
+        <v>65</v>
+      </c>
       <c r="E27" s="9" t="s">
         <v>7</v>
       </c>
@@ -2388,7 +2595,9 @@
       <c r="J27" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K27" s="2"/>
+      <c r="K27" s="32" t="s">
+        <v>7</v>
+      </c>
       <c r="L27" s="2"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
@@ -2398,11 +2607,15 @@
       <c r="R27" s="3"/>
       <c r="S27" s="3"/>
       <c r="T27" s="3"/>
-      <c r="U27" s="3"/>
-      <c r="V27" s="3"/>
-      <c r="W27" s="3"/>
+      <c r="U27" s="22"/>
+      <c r="V27" s="22"/>
+      <c r="W27" s="14">
+        <v>46100</v>
+      </c>
       <c r="X27" s="3"/>
-      <c r="Y27" s="3"/>
+      <c r="Y27" s="14">
+        <v>46100</v>
+      </c>
       <c r="Z27" s="3"/>
       <c r="AA27" s="3"/>
       <c r="AB27" s="3"/>
@@ -2420,9 +2633,11 @@
       <c r="AN27" s="3"/>
       <c r="AO27" s="3"/>
       <c r="AP27" s="3"/>
-      <c r="AQ27" s="1"/>
-    </row>
-    <row r="28" spans="1:43">
+      <c r="AQ27" s="3"/>
+      <c r="AR27" s="3"/>
+      <c r="AS27" s="1"/>
+    </row>
+    <row r="28" spans="1:45">
       <c r="A28" s="2">
         <v>25</v>
       </c>
@@ -2453,7 +2668,9 @@
       <c r="J28" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K28" s="2"/>
+      <c r="K28" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="L28" s="2"/>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
@@ -2463,11 +2680,11 @@
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
       <c r="T28" s="3"/>
-      <c r="U28" s="21">
+      <c r="U28" s="22"/>
+      <c r="V28" s="22"/>
+      <c r="W28" s="21">
         <v>46086</v>
       </c>
-      <c r="V28" s="3"/>
-      <c r="W28" s="3"/>
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
@@ -2487,9 +2704,11 @@
       <c r="AN28" s="3"/>
       <c r="AO28" s="3"/>
       <c r="AP28" s="3"/>
-      <c r="AQ28" s="1"/>
-    </row>
-    <row r="29" spans="1:43">
+      <c r="AQ28" s="3"/>
+      <c r="AR28" s="3"/>
+      <c r="AS28" s="1"/>
+    </row>
+    <row r="29" spans="1:45">
       <c r="A29" s="2">
         <v>26</v>
       </c>
@@ -2518,7 +2737,9 @@
       <c r="J29" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K29" s="2"/>
+      <c r="K29" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="L29" s="2"/>
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
@@ -2528,13 +2749,15 @@
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
-      <c r="U29" s="14">
+      <c r="U29" s="22"/>
+      <c r="V29" s="22"/>
+      <c r="W29" s="14">
         <v>46072</v>
       </c>
-      <c r="V29" s="3"/>
-      <c r="W29" s="3"/>
       <c r="X29" s="3"/>
-      <c r="Y29" s="3"/>
+      <c r="Y29" s="14">
+        <v>46100</v>
+      </c>
       <c r="Z29" s="3"/>
       <c r="AA29" s="3"/>
       <c r="AB29" s="3"/>
@@ -2552,9 +2775,11 @@
       <c r="AN29" s="3"/>
       <c r="AO29" s="3"/>
       <c r="AP29" s="3"/>
-      <c r="AQ29" s="1"/>
-    </row>
-    <row r="30" spans="1:43">
+      <c r="AQ29" s="3"/>
+      <c r="AR29" s="3"/>
+      <c r="AS29" s="1"/>
+    </row>
+    <row r="30" spans="1:45">
       <c r="A30" s="2">
         <v>27</v>
       </c>
@@ -2585,7 +2810,9 @@
       <c r="J30" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K30" s="2"/>
+      <c r="K30" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="L30" s="2"/>
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
@@ -2595,11 +2822,11 @@
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
-      <c r="U30" s="14">
+      <c r="U30" s="22"/>
+      <c r="V30" s="22"/>
+      <c r="W30" s="14">
         <v>46072</v>
       </c>
-      <c r="V30" s="3"/>
-      <c r="W30" s="3"/>
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
       <c r="Z30" s="3"/>
@@ -2619,9 +2846,11 @@
       <c r="AN30" s="3"/>
       <c r="AO30" s="3"/>
       <c r="AP30" s="3"/>
-      <c r="AQ30" s="1"/>
-    </row>
-    <row r="31" spans="1:43">
+      <c r="AQ30" s="3"/>
+      <c r="AR30" s="3"/>
+      <c r="AS30" s="1"/>
+    </row>
+    <row r="31" spans="1:45">
       <c r="A31" s="2">
         <v>28</v>
       </c>
@@ -2652,7 +2881,9 @@
       <c r="J31" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K31" s="2"/>
+      <c r="K31" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="L31" s="2"/>
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
@@ -2662,11 +2893,11 @@
       <c r="R31" s="3"/>
       <c r="S31" s="3"/>
       <c r="T31" s="3"/>
-      <c r="U31" s="14">
+      <c r="U31" s="22"/>
+      <c r="V31" s="22"/>
+      <c r="W31" s="14">
         <v>46072</v>
       </c>
-      <c r="V31" s="3"/>
-      <c r="W31" s="3"/>
       <c r="X31" s="3"/>
       <c r="Y31" s="3"/>
       <c r="Z31" s="3"/>
@@ -2686,9 +2917,11 @@
       <c r="AN31" s="3"/>
       <c r="AO31" s="3"/>
       <c r="AP31" s="3"/>
-      <c r="AQ31" s="1"/>
-    </row>
-    <row r="32" spans="1:43">
+      <c r="AQ31" s="3"/>
+      <c r="AR31" s="3"/>
+      <c r="AS31" s="1"/>
+    </row>
+    <row r="32" spans="1:45">
       <c r="A32" s="2">
         <v>29</v>
       </c>
@@ -2717,7 +2950,9 @@
       <c r="J32" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K32" s="2"/>
+      <c r="K32" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="L32" s="2"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
@@ -2727,8 +2962,8 @@
       <c r="R32" s="3"/>
       <c r="S32" s="3"/>
       <c r="T32" s="3"/>
-      <c r="U32" s="3"/>
-      <c r="V32" s="3"/>
+      <c r="U32" s="22"/>
+      <c r="V32" s="22"/>
       <c r="W32" s="3"/>
       <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
@@ -2749,9 +2984,11 @@
       <c r="AN32" s="3"/>
       <c r="AO32" s="3"/>
       <c r="AP32" s="3"/>
-      <c r="AQ32" s="1"/>
-    </row>
-    <row r="33" spans="1:43">
+      <c r="AQ32" s="3"/>
+      <c r="AR32" s="3"/>
+      <c r="AS32" s="1"/>
+    </row>
+    <row r="33" spans="1:45">
       <c r="A33" s="2">
         <v>30</v>
       </c>
@@ -2780,7 +3017,9 @@
       <c r="J33" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K33" s="2"/>
+      <c r="K33" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="L33" s="2"/>
       <c r="M33" s="3"/>
       <c r="N33" s="3"/>
@@ -2790,11 +3029,11 @@
       <c r="R33" s="3"/>
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
-      <c r="U33" s="14">
+      <c r="U33" s="22"/>
+      <c r="V33" s="22"/>
+      <c r="W33" s="14">
         <v>46079</v>
       </c>
-      <c r="V33" s="3"/>
-      <c r="W33" s="3"/>
       <c r="X33" s="3"/>
       <c r="Y33" s="3"/>
       <c r="Z33" s="3"/>
@@ -2814,9 +3053,11 @@
       <c r="AN33" s="3"/>
       <c r="AO33" s="3"/>
       <c r="AP33" s="3"/>
-      <c r="AQ33" s="1"/>
-    </row>
-    <row r="34" spans="1:43">
+      <c r="AQ33" s="3"/>
+      <c r="AR33" s="3"/>
+      <c r="AS33" s="1"/>
+    </row>
+    <row r="34" spans="1:45">
       <c r="A34" s="2">
         <v>31</v>
       </c>
@@ -2845,7 +3086,9 @@
       <c r="J34" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K34" s="2"/>
+      <c r="K34" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="L34" s="2"/>
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
@@ -2855,15 +3098,15 @@
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
-      <c r="U34" s="14">
+      <c r="U34" s="22"/>
+      <c r="V34" s="22"/>
+      <c r="W34" s="14">
         <v>46072</v>
       </c>
-      <c r="V34" s="3"/>
-      <c r="W34" s="21">
+      <c r="X34" s="3"/>
+      <c r="Y34" s="21">
         <v>46093</v>
       </c>
-      <c r="X34" s="3"/>
-      <c r="Y34" s="3"/>
       <c r="Z34" s="3"/>
       <c r="AA34" s="3"/>
       <c r="AB34" s="3"/>
@@ -2881,9 +3124,11 @@
       <c r="AN34" s="3"/>
       <c r="AO34" s="3"/>
       <c r="AP34" s="3"/>
-      <c r="AQ34" s="1"/>
-    </row>
-    <row r="35" spans="1:43">
+      <c r="AQ34" s="3"/>
+      <c r="AR34" s="3"/>
+      <c r="AS34" s="1"/>
+    </row>
+    <row r="35" spans="1:45">
       <c r="A35" s="2">
         <v>32</v>
       </c>
@@ -2912,7 +3157,9 @@
       <c r="J35" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K35" s="2"/>
+      <c r="K35" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="L35" s="2"/>
       <c r="M35" s="3"/>
       <c r="N35" s="3"/>
@@ -2922,8 +3169,8 @@
       <c r="R35" s="3"/>
       <c r="S35" s="3"/>
       <c r="T35" s="3"/>
-      <c r="U35" s="3"/>
-      <c r="V35" s="3"/>
+      <c r="U35" s="22"/>
+      <c r="V35" s="22"/>
       <c r="W35" s="3"/>
       <c r="X35" s="3"/>
       <c r="Y35" s="3"/>
@@ -2944,9 +3191,11 @@
       <c r="AN35" s="3"/>
       <c r="AO35" s="3"/>
       <c r="AP35" s="3"/>
-      <c r="AQ35" s="1"/>
-    </row>
-    <row r="36" spans="1:43">
+      <c r="AQ35" s="3"/>
+      <c r="AR35" s="3"/>
+      <c r="AS35" s="1"/>
+    </row>
+    <row r="36" spans="1:45">
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="2"/>
@@ -2965,8 +3214,8 @@
       <c r="R36" s="3"/>
       <c r="S36" s="3"/>
       <c r="T36" s="3"/>
-      <c r="U36" s="3"/>
-      <c r="V36" s="3"/>
+      <c r="U36" s="22"/>
+      <c r="V36" s="22"/>
       <c r="W36" s="3"/>
       <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
@@ -2987,9 +3236,11 @@
       <c r="AN36" s="3"/>
       <c r="AO36" s="3"/>
       <c r="AP36" s="3"/>
-      <c r="AQ36" s="1"/>
-    </row>
-    <row r="37" spans="1:43">
+      <c r="AQ36" s="3"/>
+      <c r="AR36" s="3"/>
+      <c r="AS36" s="1"/>
+    </row>
+    <row r="37" spans="1:45">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -3019,8 +3270,8 @@
       <c r="R37" s="3"/>
       <c r="S37" s="3"/>
       <c r="T37" s="3"/>
-      <c r="U37" s="3"/>
-      <c r="V37" s="3"/>
+      <c r="U37" s="22"/>
+      <c r="V37" s="22"/>
       <c r="W37" s="3"/>
       <c r="X37" s="3"/>
       <c r="Y37" s="3"/>
@@ -3041,9 +3292,11 @@
       <c r="AN37" s="3"/>
       <c r="AO37" s="3"/>
       <c r="AP37" s="3"/>
-      <c r="AQ37" s="1"/>
-    </row>
-    <row r="38" spans="1:43">
+      <c r="AQ37" s="3"/>
+      <c r="AR37" s="3"/>
+      <c r="AS37" s="1"/>
+    </row>
+    <row r="38" spans="1:45">
       <c r="E38">
         <v>1</v>
       </c>
@@ -3065,8 +3318,38 @@
       <c r="K38">
         <v>6</v>
       </c>
-    </row>
-    <row r="39" spans="1:43">
+      <c r="L38">
+        <v>7</v>
+      </c>
+      <c r="M38">
+        <v>8</v>
+      </c>
+      <c r="N38">
+        <v>9</v>
+      </c>
+      <c r="O38">
+        <v>10</v>
+      </c>
+      <c r="P38">
+        <v>11</v>
+      </c>
+      <c r="Q38">
+        <v>12</v>
+      </c>
+      <c r="R38">
+        <v>13</v>
+      </c>
+      <c r="S38">
+        <v>14</v>
+      </c>
+      <c r="T38">
+        <v>15</v>
+      </c>
+      <c r="U38">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:45">
       <c r="E39" s="17" t="s">
         <v>56</v>
       </c>
@@ -3076,25 +3359,25 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="AS11:AS13"/>
     <mergeCell ref="AK11:AK13"/>
     <mergeCell ref="AL11:AL13"/>
     <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="A1:AQ1"/>
+    <mergeCell ref="AN11:AN13"/>
+    <mergeCell ref="AO11:AO13"/>
+    <mergeCell ref="A1:AS1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="AA11:AA13"/>
-    <mergeCell ref="AB11:AB13"/>
     <mergeCell ref="AC11:AC13"/>
     <mergeCell ref="AD11:AD13"/>
     <mergeCell ref="AE11:AE13"/>
     <mergeCell ref="AF11:AF13"/>
     <mergeCell ref="AG11:AG13"/>
     <mergeCell ref="AH11:AH13"/>
-    <mergeCell ref="AN11:AN13"/>
-    <mergeCell ref="AO11:AO13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="AJ11:AJ13"/>
     <mergeCell ref="AP11:AP13"/>
     <mergeCell ref="AQ11:AQ13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AR11:AR13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3106,56 +3389,56 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
-      <c r="S1" s="22"/>
-      <c r="T1" s="22"/>
-      <c r="U1" s="22"/>
-      <c r="V1" s="22"/>
-      <c r="W1" s="22"/>
-      <c r="X1" s="22"/>
-      <c r="Y1" s="22"/>
-      <c r="Z1" s="22"/>
-      <c r="AA1" s="22"/>
-      <c r="AB1" s="22"/>
-      <c r="AC1" s="22"/>
-      <c r="AD1" s="22"/>
-      <c r="AE1" s="22"/>
-      <c r="AF1" s="22"/>
-      <c r="AG1" s="22"/>
-      <c r="AH1" s="22"/>
-      <c r="AI1" s="22"/>
-      <c r="AJ1" s="22"/>
-      <c r="AK1" s="22"/>
-      <c r="AL1" s="22"/>
-      <c r="AM1" s="22"/>
-      <c r="AN1" s="22"/>
-      <c r="AO1" s="22"/>
-      <c r="AP1" s="22"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
+      <c r="Y1" s="28"/>
+      <c r="Z1" s="28"/>
+      <c r="AA1" s="28"/>
+      <c r="AB1" s="28"/>
+      <c r="AC1" s="28"/>
+      <c r="AD1" s="28"/>
+      <c r="AE1" s="28"/>
+      <c r="AF1" s="28"/>
+      <c r="AG1" s="28"/>
+      <c r="AH1" s="28"/>
+      <c r="AI1" s="28"/>
+      <c r="AJ1" s="28"/>
+      <c r="AK1" s="28"/>
+      <c r="AL1" s="28"/>
+      <c r="AM1" s="28"/>
+      <c r="AN1" s="28"/>
+      <c r="AO1" s="28"/>
+      <c r="AP1" s="28"/>
     </row>
     <row r="2" spans="1:42" ht="30">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="24"/>
+      <c r="B2" s="30"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -3584,142 +3867,142 @@
       <c r="AP10" s="1"/>
     </row>
     <row r="11" spans="1:42">
-      <c r="A11" s="24">
+      <c r="A11" s="30">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="25"/>
-      <c r="O11" s="25"/>
-      <c r="P11" s="25"/>
-      <c r="Q11" s="25"/>
-      <c r="R11" s="25"/>
-      <c r="S11" s="25"/>
-      <c r="T11" s="25"/>
-      <c r="U11" s="25"/>
-      <c r="V11" s="25"/>
-      <c r="W11" s="25"/>
-      <c r="X11" s="25"/>
-      <c r="Y11" s="25"/>
-      <c r="Z11" s="25"/>
-      <c r="AA11" s="25"/>
-      <c r="AB11" s="25"/>
-      <c r="AC11" s="25"/>
-      <c r="AD11" s="25"/>
-      <c r="AE11" s="25"/>
-      <c r="AF11" s="25"/>
-      <c r="AG11" s="25"/>
-      <c r="AH11" s="25"/>
-      <c r="AI11" s="25"/>
-      <c r="AJ11" s="25"/>
-      <c r="AK11" s="25"/>
-      <c r="AL11" s="25"/>
-      <c r="AM11" s="25"/>
-      <c r="AN11" s="25"/>
-      <c r="AO11" s="25"/>
-      <c r="AP11" s="22"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="27"/>
+      <c r="P11" s="27"/>
+      <c r="Q11" s="27"/>
+      <c r="R11" s="27"/>
+      <c r="S11" s="27"/>
+      <c r="T11" s="27"/>
+      <c r="U11" s="27"/>
+      <c r="V11" s="27"/>
+      <c r="W11" s="27"/>
+      <c r="X11" s="27"/>
+      <c r="Y11" s="27"/>
+      <c r="Z11" s="27"/>
+      <c r="AA11" s="27"/>
+      <c r="AB11" s="27"/>
+      <c r="AC11" s="27"/>
+      <c r="AD11" s="27"/>
+      <c r="AE11" s="27"/>
+      <c r="AF11" s="27"/>
+      <c r="AG11" s="27"/>
+      <c r="AH11" s="27"/>
+      <c r="AI11" s="27"/>
+      <c r="AJ11" s="27"/>
+      <c r="AK11" s="27"/>
+      <c r="AL11" s="27"/>
+      <c r="AM11" s="27"/>
+      <c r="AN11" s="27"/>
+      <c r="AO11" s="27"/>
+      <c r="AP11" s="28"/>
     </row>
     <row r="12" spans="1:42">
-      <c r="A12" s="24"/>
+      <c r="A12" s="30"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="24"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="25"/>
-      <c r="M12" s="25"/>
-      <c r="N12" s="25"/>
-      <c r="O12" s="25"/>
-      <c r="P12" s="25"/>
-      <c r="Q12" s="25"/>
-      <c r="R12" s="25"/>
-      <c r="S12" s="25"/>
-      <c r="T12" s="25"/>
-      <c r="U12" s="25"/>
-      <c r="V12" s="25"/>
-      <c r="W12" s="25"/>
-      <c r="X12" s="25"/>
-      <c r="Y12" s="25"/>
-      <c r="Z12" s="25"/>
-      <c r="AA12" s="25"/>
-      <c r="AB12" s="25"/>
-      <c r="AC12" s="25"/>
-      <c r="AD12" s="25"/>
-      <c r="AE12" s="25"/>
-      <c r="AF12" s="25"/>
-      <c r="AG12" s="25"/>
-      <c r="AH12" s="25"/>
-      <c r="AI12" s="25"/>
-      <c r="AJ12" s="25"/>
-      <c r="AK12" s="25"/>
-      <c r="AL12" s="25"/>
-      <c r="AM12" s="25"/>
-      <c r="AN12" s="25"/>
-      <c r="AO12" s="25"/>
-      <c r="AP12" s="22"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="27"/>
+      <c r="N12" s="27"/>
+      <c r="O12" s="27"/>
+      <c r="P12" s="27"/>
+      <c r="Q12" s="27"/>
+      <c r="R12" s="27"/>
+      <c r="S12" s="27"/>
+      <c r="T12" s="27"/>
+      <c r="U12" s="27"/>
+      <c r="V12" s="27"/>
+      <c r="W12" s="27"/>
+      <c r="X12" s="27"/>
+      <c r="Y12" s="27"/>
+      <c r="Z12" s="27"/>
+      <c r="AA12" s="27"/>
+      <c r="AB12" s="27"/>
+      <c r="AC12" s="27"/>
+      <c r="AD12" s="27"/>
+      <c r="AE12" s="27"/>
+      <c r="AF12" s="27"/>
+      <c r="AG12" s="27"/>
+      <c r="AH12" s="27"/>
+      <c r="AI12" s="27"/>
+      <c r="AJ12" s="27"/>
+      <c r="AK12" s="27"/>
+      <c r="AL12" s="27"/>
+      <c r="AM12" s="27"/>
+      <c r="AN12" s="27"/>
+      <c r="AO12" s="27"/>
+      <c r="AP12" s="28"/>
     </row>
     <row r="13" spans="1:42">
-      <c r="A13" s="24"/>
+      <c r="A13" s="30"/>
       <c r="B13" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="24"/>
-      <c r="K13" s="24"/>
-      <c r="L13" s="25"/>
-      <c r="M13" s="25"/>
-      <c r="N13" s="25"/>
-      <c r="O13" s="25"/>
-      <c r="P13" s="25"/>
-      <c r="Q13" s="25"/>
-      <c r="R13" s="25"/>
-      <c r="S13" s="25"/>
-      <c r="T13" s="25"/>
-      <c r="U13" s="25"/>
-      <c r="V13" s="25"/>
-      <c r="W13" s="25"/>
-      <c r="X13" s="25"/>
-      <c r="Y13" s="25"/>
-      <c r="Z13" s="25"/>
-      <c r="AA13" s="25"/>
-      <c r="AB13" s="25"/>
-      <c r="AC13" s="25"/>
-      <c r="AD13" s="25"/>
-      <c r="AE13" s="25"/>
-      <c r="AF13" s="25"/>
-      <c r="AG13" s="25"/>
-      <c r="AH13" s="25"/>
-      <c r="AI13" s="25"/>
-      <c r="AJ13" s="25"/>
-      <c r="AK13" s="25"/>
-      <c r="AL13" s="25"/>
-      <c r="AM13" s="25"/>
-      <c r="AN13" s="25"/>
-      <c r="AO13" s="25"/>
-      <c r="AP13" s="22"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="30"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="27"/>
+      <c r="N13" s="27"/>
+      <c r="O13" s="27"/>
+      <c r="P13" s="27"/>
+      <c r="Q13" s="27"/>
+      <c r="R13" s="27"/>
+      <c r="S13" s="27"/>
+      <c r="T13" s="27"/>
+      <c r="U13" s="27"/>
+      <c r="V13" s="27"/>
+      <c r="W13" s="27"/>
+      <c r="X13" s="27"/>
+      <c r="Y13" s="27"/>
+      <c r="Z13" s="27"/>
+      <c r="AA13" s="27"/>
+      <c r="AB13" s="27"/>
+      <c r="AC13" s="27"/>
+      <c r="AD13" s="27"/>
+      <c r="AE13" s="27"/>
+      <c r="AF13" s="27"/>
+      <c r="AG13" s="27"/>
+      <c r="AH13" s="27"/>
+      <c r="AI13" s="27"/>
+      <c r="AJ13" s="27"/>
+      <c r="AK13" s="27"/>
+      <c r="AL13" s="27"/>
+      <c r="AM13" s="27"/>
+      <c r="AN13" s="27"/>
+      <c r="AO13" s="27"/>
+      <c r="AP13" s="28"/>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" s="2">
@@ -4875,33 +5158,6 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="AO11:AO13"/>
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="AN11:AN13"/>
-    <mergeCell ref="AE11:AE13"/>
-    <mergeCell ref="AF11:AF13"/>
-    <mergeCell ref="AG11:AG13"/>
-    <mergeCell ref="AH11:AH13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="Z11:Z13"/>
-    <mergeCell ref="AA11:AA13"/>
-    <mergeCell ref="AB11:AB13"/>
-    <mergeCell ref="AC11:AC13"/>
-    <mergeCell ref="AD11:AD13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="V11:V13"/>
-    <mergeCell ref="W11:W13"/>
-    <mergeCell ref="X11:X13"/>
-    <mergeCell ref="Y11:Y13"/>
-    <mergeCell ref="P11:P13"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="T11:T13"/>
     <mergeCell ref="A1:AP1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A11:A13"/>
@@ -4918,6 +5174,33 @@
     <mergeCell ref="M11:M13"/>
     <mergeCell ref="N11:N13"/>
     <mergeCell ref="O11:O13"/>
+    <mergeCell ref="P11:P13"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="T11:T13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="V11:V13"/>
+    <mergeCell ref="W11:W13"/>
+    <mergeCell ref="X11:X13"/>
+    <mergeCell ref="Y11:Y13"/>
+    <mergeCell ref="Z11:Z13"/>
+    <mergeCell ref="AA11:AA13"/>
+    <mergeCell ref="AB11:AB13"/>
+    <mergeCell ref="AC11:AC13"/>
+    <mergeCell ref="AD11:AD13"/>
+    <mergeCell ref="AE11:AE13"/>
+    <mergeCell ref="AF11:AF13"/>
+    <mergeCell ref="AG11:AG13"/>
+    <mergeCell ref="AH11:AH13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="AO11:AO13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
+    <mergeCell ref="AN11:AN13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ТКИ-341_Реверс_Инжиниринг.xlsx
+++ b/ТКИ-341_Реверс_Инжиниринг.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22527"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\Reverse_Engineering\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\safronov\Documents\Reverse_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{032432B6-9CCF-4F8C-904F-7F62ECE280EA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -277,7 +276,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
@@ -362,7 +361,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -433,10 +432,19 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -444,11 +452,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -724,7 +732,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AS39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -738,62 +746,63 @@
     <col min="17" max="21" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="14.45" customHeight="1">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="28"/>
-      <c r="AA1" s="28"/>
-      <c r="AB1" s="28"/>
-      <c r="AC1" s="28"/>
-      <c r="AD1" s="28"/>
-      <c r="AE1" s="28"/>
-      <c r="AF1" s="28"/>
-      <c r="AG1" s="28"/>
-      <c r="AH1" s="28"/>
-      <c r="AI1" s="28"/>
-      <c r="AJ1" s="28"/>
-      <c r="AK1" s="28"/>
-      <c r="AL1" s="28"/>
-      <c r="AM1" s="28"/>
-      <c r="AN1" s="28"/>
-      <c r="AO1" s="28"/>
-      <c r="AP1" s="28"/>
-      <c r="AQ1" s="28"/>
-      <c r="AR1" s="28"/>
-      <c r="AS1" s="28"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="30"/>
+      <c r="R1" s="30"/>
+      <c r="S1" s="30"/>
+      <c r="T1" s="30"/>
+      <c r="U1" s="30"/>
+      <c r="V1" s="30"/>
+      <c r="W1" s="30"/>
+      <c r="X1" s="30"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="30"/>
+      <c r="AA1" s="30"/>
+      <c r="AB1" s="30"/>
+      <c r="AC1" s="30"/>
+      <c r="AD1" s="30"/>
+      <c r="AE1" s="30"/>
+      <c r="AF1" s="30"/>
+      <c r="AG1" s="30"/>
+      <c r="AH1" s="30"/>
+      <c r="AI1" s="30"/>
+      <c r="AJ1" s="30"/>
+      <c r="AK1" s="30"/>
+      <c r="AL1" s="30"/>
+      <c r="AM1" s="30"/>
+      <c r="AN1" s="30"/>
+      <c r="AO1" s="30"/>
+      <c r="AP1" s="30"/>
+      <c r="AQ1" s="30"/>
+      <c r="AR1" s="30"/>
+      <c r="AS1" s="30"/>
     </row>
     <row r="2" spans="1:45" ht="27.6" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="30"/>
+      <c r="B2" s="33"/>
       <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1201,7 +1210,7 @@
       <c r="T7" s="3"/>
       <c r="U7" s="22"/>
       <c r="V7" s="22"/>
-      <c r="W7" s="31">
+      <c r="W7" s="28">
         <v>46100</v>
       </c>
       <c r="X7" s="3"/>
@@ -1209,7 +1218,9 @@
         <v>46100</v>
       </c>
       <c r="Z7" s="3"/>
-      <c r="AA7" s="3"/>
+      <c r="AA7" s="34">
+        <v>46100</v>
+      </c>
       <c r="AB7" s="3"/>
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
@@ -1469,7 +1480,7 @@
       <c r="J11" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="K11" s="27" t="s">
         <v>7</v>
       </c>
       <c r="L11" s="11"/>
@@ -1487,27 +1498,29 @@
         <v>46079</v>
       </c>
       <c r="X11" s="12"/>
-      <c r="Y11" s="12"/>
+      <c r="Y11" s="35">
+        <v>46100</v>
+      </c>
       <c r="Z11" s="12"/>
       <c r="AA11" s="12"/>
       <c r="AB11" s="12"/>
-      <c r="AC11" s="27"/>
-      <c r="AD11" s="27"/>
-      <c r="AE11" s="27"/>
-      <c r="AF11" s="27"/>
-      <c r="AG11" s="27"/>
-      <c r="AH11" s="27"/>
-      <c r="AI11" s="27"/>
-      <c r="AJ11" s="27"/>
-      <c r="AK11" s="27"/>
-      <c r="AL11" s="27"/>
-      <c r="AM11" s="27"/>
-      <c r="AN11" s="27"/>
-      <c r="AO11" s="27"/>
-      <c r="AP11" s="27"/>
-      <c r="AQ11" s="27"/>
-      <c r="AR11" s="27"/>
-      <c r="AS11" s="28"/>
+      <c r="AC11" s="31"/>
+      <c r="AD11" s="31"/>
+      <c r="AE11" s="31"/>
+      <c r="AF11" s="31"/>
+      <c r="AG11" s="31"/>
+      <c r="AH11" s="31"/>
+      <c r="AI11" s="31"/>
+      <c r="AJ11" s="31"/>
+      <c r="AK11" s="31"/>
+      <c r="AL11" s="31"/>
+      <c r="AM11" s="31"/>
+      <c r="AN11" s="31"/>
+      <c r="AO11" s="31"/>
+      <c r="AP11" s="31"/>
+      <c r="AQ11" s="31"/>
+      <c r="AR11" s="31"/>
+      <c r="AS11" s="30"/>
     </row>
     <row r="12" spans="1:45">
       <c r="A12" s="2">
@@ -1540,7 +1553,7 @@
       <c r="J12" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="K12" s="27" t="s">
         <v>7</v>
       </c>
       <c r="L12" s="11"/>
@@ -1558,27 +1571,29 @@
         <v>46072</v>
       </c>
       <c r="X12" s="12"/>
-      <c r="Y12" s="12"/>
+      <c r="Y12" s="35">
+        <v>46100</v>
+      </c>
       <c r="Z12" s="12"/>
       <c r="AA12" s="12"/>
       <c r="AB12" s="12"/>
-      <c r="AC12" s="27"/>
-      <c r="AD12" s="27"/>
-      <c r="AE12" s="27"/>
-      <c r="AF12" s="27"/>
-      <c r="AG12" s="27"/>
-      <c r="AH12" s="27"/>
-      <c r="AI12" s="27"/>
-      <c r="AJ12" s="27"/>
-      <c r="AK12" s="27"/>
-      <c r="AL12" s="27"/>
-      <c r="AM12" s="27"/>
-      <c r="AN12" s="27"/>
-      <c r="AO12" s="27"/>
-      <c r="AP12" s="27"/>
-      <c r="AQ12" s="27"/>
-      <c r="AR12" s="27"/>
-      <c r="AS12" s="28"/>
+      <c r="AC12" s="31"/>
+      <c r="AD12" s="31"/>
+      <c r="AE12" s="31"/>
+      <c r="AF12" s="31"/>
+      <c r="AG12" s="31"/>
+      <c r="AH12" s="31"/>
+      <c r="AI12" s="31"/>
+      <c r="AJ12" s="31"/>
+      <c r="AK12" s="31"/>
+      <c r="AL12" s="31"/>
+      <c r="AM12" s="31"/>
+      <c r="AN12" s="31"/>
+      <c r="AO12" s="31"/>
+      <c r="AP12" s="31"/>
+      <c r="AQ12" s="31"/>
+      <c r="AR12" s="31"/>
+      <c r="AS12" s="30"/>
     </row>
     <row r="13" spans="1:45">
       <c r="A13" s="2">
@@ -1611,7 +1626,7 @@
       <c r="J13" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K13" s="11" t="s">
+      <c r="K13" s="27" t="s">
         <v>7</v>
       </c>
       <c r="L13" s="11"/>
@@ -1635,23 +1650,23 @@
       <c r="Z13" s="12"/>
       <c r="AA13" s="12"/>
       <c r="AB13" s="12"/>
-      <c r="AC13" s="27"/>
-      <c r="AD13" s="27"/>
-      <c r="AE13" s="27"/>
-      <c r="AF13" s="27"/>
-      <c r="AG13" s="27"/>
-      <c r="AH13" s="27"/>
-      <c r="AI13" s="27"/>
-      <c r="AJ13" s="27"/>
-      <c r="AK13" s="27"/>
-      <c r="AL13" s="27"/>
-      <c r="AM13" s="27"/>
-      <c r="AN13" s="27"/>
-      <c r="AO13" s="27"/>
-      <c r="AP13" s="27"/>
-      <c r="AQ13" s="27"/>
-      <c r="AR13" s="27"/>
-      <c r="AS13" s="28"/>
+      <c r="AC13" s="31"/>
+      <c r="AD13" s="31"/>
+      <c r="AE13" s="31"/>
+      <c r="AF13" s="31"/>
+      <c r="AG13" s="31"/>
+      <c r="AH13" s="31"/>
+      <c r="AI13" s="31"/>
+      <c r="AJ13" s="31"/>
+      <c r="AK13" s="31"/>
+      <c r="AL13" s="31"/>
+      <c r="AM13" s="31"/>
+      <c r="AN13" s="31"/>
+      <c r="AO13" s="31"/>
+      <c r="AP13" s="31"/>
+      <c r="AQ13" s="31"/>
+      <c r="AR13" s="31"/>
+      <c r="AS13" s="30"/>
     </row>
     <row r="14" spans="1:45">
       <c r="A14" s="2">
@@ -1769,7 +1784,9 @@
         <v>46079</v>
       </c>
       <c r="X15" s="3"/>
-      <c r="Y15" s="3"/>
+      <c r="Y15" s="34">
+        <v>46100</v>
+      </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
       <c r="AB15" s="3"/>
@@ -1838,7 +1855,9 @@
         <v>46072</v>
       </c>
       <c r="X16" s="3"/>
-      <c r="Y16" s="3"/>
+      <c r="Y16" s="34">
+        <v>46100</v>
+      </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
@@ -1978,7 +1997,7 @@
       <c r="T18" s="3"/>
       <c r="U18" s="22"/>
       <c r="V18" s="22"/>
-      <c r="W18" s="31">
+      <c r="W18" s="28">
         <v>46100</v>
       </c>
       <c r="X18" s="3"/>
@@ -1986,7 +2005,9 @@
         <v>46100</v>
       </c>
       <c r="Z18" s="3"/>
-      <c r="AA18" s="3"/>
+      <c r="AA18" s="34">
+        <v>46100</v>
+      </c>
       <c r="AB18" s="3"/>
       <c r="AC18" s="3"/>
       <c r="AD18" s="3"/>
@@ -2475,7 +2496,9 @@
         <v>46072</v>
       </c>
       <c r="X25" s="3"/>
-      <c r="Y25" s="3"/>
+      <c r="Y25" s="34">
+        <v>46100</v>
+      </c>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3"/>
       <c r="AB25" s="3"/>
@@ -2595,7 +2618,7 @@
       <c r="J27" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K27" s="32" t="s">
+      <c r="K27" s="29" t="s">
         <v>7</v>
       </c>
       <c r="L27" s="2"/>
@@ -2828,7 +2851,9 @@
         <v>46072</v>
       </c>
       <c r="X30" s="3"/>
-      <c r="Y30" s="3"/>
+      <c r="Y30" s="34">
+        <v>46100</v>
+      </c>
       <c r="Z30" s="3"/>
       <c r="AA30" s="3"/>
       <c r="AB30" s="3"/>
@@ -3359,12 +3384,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="AS11:AS13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="AN11:AN13"/>
-    <mergeCell ref="AO11:AO13"/>
     <mergeCell ref="A1:AS1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="AC11:AC13"/>
@@ -3378,67 +3397,73 @@
     <mergeCell ref="AP11:AP13"/>
     <mergeCell ref="AQ11:AQ13"/>
     <mergeCell ref="AR11:AR13"/>
+    <mergeCell ref="AS11:AS13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
+    <mergeCell ref="AN11:AN13"/>
+    <mergeCell ref="AO11:AO13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AP37"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="28"/>
-      <c r="AA1" s="28"/>
-      <c r="AB1" s="28"/>
-      <c r="AC1" s="28"/>
-      <c r="AD1" s="28"/>
-      <c r="AE1" s="28"/>
-      <c r="AF1" s="28"/>
-      <c r="AG1" s="28"/>
-      <c r="AH1" s="28"/>
-      <c r="AI1" s="28"/>
-      <c r="AJ1" s="28"/>
-      <c r="AK1" s="28"/>
-      <c r="AL1" s="28"/>
-      <c r="AM1" s="28"/>
-      <c r="AN1" s="28"/>
-      <c r="AO1" s="28"/>
-      <c r="AP1" s="28"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="30"/>
+      <c r="R1" s="30"/>
+      <c r="S1" s="30"/>
+      <c r="T1" s="30"/>
+      <c r="U1" s="30"/>
+      <c r="V1" s="30"/>
+      <c r="W1" s="30"/>
+      <c r="X1" s="30"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="30"/>
+      <c r="AA1" s="30"/>
+      <c r="AB1" s="30"/>
+      <c r="AC1" s="30"/>
+      <c r="AD1" s="30"/>
+      <c r="AE1" s="30"/>
+      <c r="AF1" s="30"/>
+      <c r="AG1" s="30"/>
+      <c r="AH1" s="30"/>
+      <c r="AI1" s="30"/>
+      <c r="AJ1" s="30"/>
+      <c r="AK1" s="30"/>
+      <c r="AL1" s="30"/>
+      <c r="AM1" s="30"/>
+      <c r="AN1" s="30"/>
+      <c r="AO1" s="30"/>
+      <c r="AP1" s="30"/>
     </row>
     <row r="2" spans="1:42" ht="30">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="30"/>
+      <c r="B2" s="33"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -3867,142 +3892,142 @@
       <c r="AP10" s="1"/>
     </row>
     <row r="11" spans="1:42">
-      <c r="A11" s="30">
+      <c r="A11" s="33">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="27"/>
-      <c r="M11" s="27"/>
-      <c r="N11" s="27"/>
-      <c r="O11" s="27"/>
-      <c r="P11" s="27"/>
-      <c r="Q11" s="27"/>
-      <c r="R11" s="27"/>
-      <c r="S11" s="27"/>
-      <c r="T11" s="27"/>
-      <c r="U11" s="27"/>
-      <c r="V11" s="27"/>
-      <c r="W11" s="27"/>
-      <c r="X11" s="27"/>
-      <c r="Y11" s="27"/>
-      <c r="Z11" s="27"/>
-      <c r="AA11" s="27"/>
-      <c r="AB11" s="27"/>
-      <c r="AC11" s="27"/>
-      <c r="AD11" s="27"/>
-      <c r="AE11" s="27"/>
-      <c r="AF11" s="27"/>
-      <c r="AG11" s="27"/>
-      <c r="AH11" s="27"/>
-      <c r="AI11" s="27"/>
-      <c r="AJ11" s="27"/>
-      <c r="AK11" s="27"/>
-      <c r="AL11" s="27"/>
-      <c r="AM11" s="27"/>
-      <c r="AN11" s="27"/>
-      <c r="AO11" s="27"/>
-      <c r="AP11" s="28"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="31"/>
+      <c r="M11" s="31"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="31"/>
+      <c r="P11" s="31"/>
+      <c r="Q11" s="31"/>
+      <c r="R11" s="31"/>
+      <c r="S11" s="31"/>
+      <c r="T11" s="31"/>
+      <c r="U11" s="31"/>
+      <c r="V11" s="31"/>
+      <c r="W11" s="31"/>
+      <c r="X11" s="31"/>
+      <c r="Y11" s="31"/>
+      <c r="Z11" s="31"/>
+      <c r="AA11" s="31"/>
+      <c r="AB11" s="31"/>
+      <c r="AC11" s="31"/>
+      <c r="AD11" s="31"/>
+      <c r="AE11" s="31"/>
+      <c r="AF11" s="31"/>
+      <c r="AG11" s="31"/>
+      <c r="AH11" s="31"/>
+      <c r="AI11" s="31"/>
+      <c r="AJ11" s="31"/>
+      <c r="AK11" s="31"/>
+      <c r="AL11" s="31"/>
+      <c r="AM11" s="31"/>
+      <c r="AN11" s="31"/>
+      <c r="AO11" s="31"/>
+      <c r="AP11" s="30"/>
     </row>
     <row r="12" spans="1:42">
-      <c r="A12" s="30"/>
+      <c r="A12" s="33"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="30"/>
-      <c r="L12" s="27"/>
-      <c r="M12" s="27"/>
-      <c r="N12" s="27"/>
-      <c r="O12" s="27"/>
-      <c r="P12" s="27"/>
-      <c r="Q12" s="27"/>
-      <c r="R12" s="27"/>
-      <c r="S12" s="27"/>
-      <c r="T12" s="27"/>
-      <c r="U12" s="27"/>
-      <c r="V12" s="27"/>
-      <c r="W12" s="27"/>
-      <c r="X12" s="27"/>
-      <c r="Y12" s="27"/>
-      <c r="Z12" s="27"/>
-      <c r="AA12" s="27"/>
-      <c r="AB12" s="27"/>
-      <c r="AC12" s="27"/>
-      <c r="AD12" s="27"/>
-      <c r="AE12" s="27"/>
-      <c r="AF12" s="27"/>
-      <c r="AG12" s="27"/>
-      <c r="AH12" s="27"/>
-      <c r="AI12" s="27"/>
-      <c r="AJ12" s="27"/>
-      <c r="AK12" s="27"/>
-      <c r="AL12" s="27"/>
-      <c r="AM12" s="27"/>
-      <c r="AN12" s="27"/>
-      <c r="AO12" s="27"/>
-      <c r="AP12" s="28"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="33"/>
+      <c r="K12" s="33"/>
+      <c r="L12" s="31"/>
+      <c r="M12" s="31"/>
+      <c r="N12" s="31"/>
+      <c r="O12" s="31"/>
+      <c r="P12" s="31"/>
+      <c r="Q12" s="31"/>
+      <c r="R12" s="31"/>
+      <c r="S12" s="31"/>
+      <c r="T12" s="31"/>
+      <c r="U12" s="31"/>
+      <c r="V12" s="31"/>
+      <c r="W12" s="31"/>
+      <c r="X12" s="31"/>
+      <c r="Y12" s="31"/>
+      <c r="Z12" s="31"/>
+      <c r="AA12" s="31"/>
+      <c r="AB12" s="31"/>
+      <c r="AC12" s="31"/>
+      <c r="AD12" s="31"/>
+      <c r="AE12" s="31"/>
+      <c r="AF12" s="31"/>
+      <c r="AG12" s="31"/>
+      <c r="AH12" s="31"/>
+      <c r="AI12" s="31"/>
+      <c r="AJ12" s="31"/>
+      <c r="AK12" s="31"/>
+      <c r="AL12" s="31"/>
+      <c r="AM12" s="31"/>
+      <c r="AN12" s="31"/>
+      <c r="AO12" s="31"/>
+      <c r="AP12" s="30"/>
     </row>
     <row r="13" spans="1:42">
-      <c r="A13" s="30"/>
+      <c r="A13" s="33"/>
       <c r="B13" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="30"/>
-      <c r="L13" s="27"/>
-      <c r="M13" s="27"/>
-      <c r="N13" s="27"/>
-      <c r="O13" s="27"/>
-      <c r="P13" s="27"/>
-      <c r="Q13" s="27"/>
-      <c r="R13" s="27"/>
-      <c r="S13" s="27"/>
-      <c r="T13" s="27"/>
-      <c r="U13" s="27"/>
-      <c r="V13" s="27"/>
-      <c r="W13" s="27"/>
-      <c r="X13" s="27"/>
-      <c r="Y13" s="27"/>
-      <c r="Z13" s="27"/>
-      <c r="AA13" s="27"/>
-      <c r="AB13" s="27"/>
-      <c r="AC13" s="27"/>
-      <c r="AD13" s="27"/>
-      <c r="AE13" s="27"/>
-      <c r="AF13" s="27"/>
-      <c r="AG13" s="27"/>
-      <c r="AH13" s="27"/>
-      <c r="AI13" s="27"/>
-      <c r="AJ13" s="27"/>
-      <c r="AK13" s="27"/>
-      <c r="AL13" s="27"/>
-      <c r="AM13" s="27"/>
-      <c r="AN13" s="27"/>
-      <c r="AO13" s="27"/>
-      <c r="AP13" s="28"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="33"/>
+      <c r="K13" s="33"/>
+      <c r="L13" s="31"/>
+      <c r="M13" s="31"/>
+      <c r="N13" s="31"/>
+      <c r="O13" s="31"/>
+      <c r="P13" s="31"/>
+      <c r="Q13" s="31"/>
+      <c r="R13" s="31"/>
+      <c r="S13" s="31"/>
+      <c r="T13" s="31"/>
+      <c r="U13" s="31"/>
+      <c r="V13" s="31"/>
+      <c r="W13" s="31"/>
+      <c r="X13" s="31"/>
+      <c r="Y13" s="31"/>
+      <c r="Z13" s="31"/>
+      <c r="AA13" s="31"/>
+      <c r="AB13" s="31"/>
+      <c r="AC13" s="31"/>
+      <c r="AD13" s="31"/>
+      <c r="AE13" s="31"/>
+      <c r="AF13" s="31"/>
+      <c r="AG13" s="31"/>
+      <c r="AH13" s="31"/>
+      <c r="AI13" s="31"/>
+      <c r="AJ13" s="31"/>
+      <c r="AK13" s="31"/>
+      <c r="AL13" s="31"/>
+      <c r="AM13" s="31"/>
+      <c r="AN13" s="31"/>
+      <c r="AO13" s="31"/>
+      <c r="AP13" s="30"/>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" s="2">
@@ -5158,6 +5183,33 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="AO11:AO13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
+    <mergeCell ref="AN11:AN13"/>
+    <mergeCell ref="AE11:AE13"/>
+    <mergeCell ref="AF11:AF13"/>
+    <mergeCell ref="AG11:AG13"/>
+    <mergeCell ref="AH11:AH13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="Z11:Z13"/>
+    <mergeCell ref="AA11:AA13"/>
+    <mergeCell ref="AB11:AB13"/>
+    <mergeCell ref="AC11:AC13"/>
+    <mergeCell ref="AD11:AD13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="V11:V13"/>
+    <mergeCell ref="W11:W13"/>
+    <mergeCell ref="X11:X13"/>
+    <mergeCell ref="Y11:Y13"/>
+    <mergeCell ref="P11:P13"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="T11:T13"/>
     <mergeCell ref="A1:AP1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A11:A13"/>
@@ -5174,33 +5226,6 @@
     <mergeCell ref="M11:M13"/>
     <mergeCell ref="N11:N13"/>
     <mergeCell ref="O11:O13"/>
-    <mergeCell ref="P11:P13"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="T11:T13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="V11:V13"/>
-    <mergeCell ref="W11:W13"/>
-    <mergeCell ref="X11:X13"/>
-    <mergeCell ref="Y11:Y13"/>
-    <mergeCell ref="Z11:Z13"/>
-    <mergeCell ref="AA11:AA13"/>
-    <mergeCell ref="AB11:AB13"/>
-    <mergeCell ref="AC11:AC13"/>
-    <mergeCell ref="AD11:AD13"/>
-    <mergeCell ref="AE11:AE13"/>
-    <mergeCell ref="AF11:AF13"/>
-    <mergeCell ref="AG11:AG13"/>
-    <mergeCell ref="AH11:AH13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="AO11:AO13"/>
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="AN11:AN13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ТКИ-341_Реверс_Инжиниринг.xlsx
+++ b/ТКИ-341_Реверс_Инжиниринг.xlsx
@@ -1,34 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\safronov\Documents\Reverse_Engineering\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Сидоренко\Reverse_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8144D8E-C7DA-4711-B784-C97A1A2E2CB8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="73">
   <si>
     <t>ВЕДОМОСТЬ ПОСЕЩАЕМОСТИ ЗАНЯТИЙ СТУДЕНТАМИ ГРУППЫ ТКИ "Компьютерная безопасность" ИТТСУ РУТ (МИИТ)</t>
   </si>
@@ -222,9 +215,6 @@
     <t>расчет геометрической прогрессии</t>
   </si>
   <si>
-    <t>кусочно-</t>
-  </si>
-  <si>
     <t>2 лаба</t>
   </si>
   <si>
@@ -271,12 +261,21 @@
   </si>
   <si>
     <t>иетрационно элементы увеличиваем на 4 и умножаем на 2</t>
+  </si>
+  <si>
+    <t>4 лаба</t>
+  </si>
+  <si>
+    <t>3 лаба</t>
+  </si>
+  <si>
+    <t>кусочно-линейная функция</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
@@ -361,7 +360,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -441,13 +440,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -457,6 +450,18 @@
     </xf>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -732,8 +737,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AS39"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AX39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="37.28515625" customWidth="1"/>
@@ -741,68 +746,82 @@
     <col min="4" max="4" width="29" style="8" customWidth="1"/>
     <col min="5" max="5" width="10.85546875"/>
     <col min="6" max="8" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="15" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="21" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.7109375" customWidth="1"/>
+    <col min="19" max="19" width="11" customWidth="1"/>
+    <col min="20" max="20" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.7109375" customWidth="1"/>
+    <col min="22" max="23" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.7109375" customWidth="1"/>
+    <col min="25" max="26" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" ht="14.45" customHeight="1">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:50" ht="14.45" customHeight="1">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="30"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="30"/>
-      <c r="AA1" s="30"/>
-      <c r="AB1" s="30"/>
-      <c r="AC1" s="30"/>
-      <c r="AD1" s="30"/>
-      <c r="AE1" s="30"/>
-      <c r="AF1" s="30"/>
-      <c r="AG1" s="30"/>
-      <c r="AH1" s="30"/>
-      <c r="AI1" s="30"/>
-      <c r="AJ1" s="30"/>
-      <c r="AK1" s="30"/>
-      <c r="AL1" s="30"/>
-      <c r="AM1" s="30"/>
-      <c r="AN1" s="30"/>
-      <c r="AO1" s="30"/>
-      <c r="AP1" s="30"/>
-      <c r="AQ1" s="30"/>
-      <c r="AR1" s="30"/>
-      <c r="AS1" s="30"/>
-    </row>
-    <row r="2" spans="1:45" ht="27.6" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="34"/>
+      <c r="AA1" s="34"/>
+      <c r="AB1" s="34"/>
+      <c r="AC1" s="34"/>
+      <c r="AD1" s="34"/>
+      <c r="AE1" s="34"/>
+      <c r="AF1" s="34"/>
+      <c r="AG1" s="34"/>
+      <c r="AH1" s="34"/>
+      <c r="AI1" s="34"/>
+      <c r="AJ1" s="34"/>
+      <c r="AK1" s="34"/>
+      <c r="AL1" s="34"/>
+      <c r="AM1" s="34"/>
+      <c r="AN1" s="34"/>
+      <c r="AO1" s="34"/>
+      <c r="AP1" s="34"/>
+      <c r="AQ1" s="34"/>
+      <c r="AR1" s="34"/>
+      <c r="AS1" s="34"/>
+      <c r="AT1" s="34"/>
+      <c r="AU1" s="34"/>
+      <c r="AV1" s="34"/>
+      <c r="AW1" s="34"/>
+      <c r="AX1" s="34"/>
+    </row>
+    <row r="2" spans="1:50" ht="27.6" customHeight="1">
+      <c r="A2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="33"/>
+      <c r="B2" s="36"/>
       <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
@@ -831,77 +850,86 @@
         <v>46100</v>
       </c>
       <c r="L2" s="18">
+        <v>46104</v>
+      </c>
+      <c r="M2" s="18">
         <v>46107</v>
       </c>
-      <c r="M2" s="18">
+      <c r="N2" s="18">
         <v>46114</v>
       </c>
-      <c r="N2" s="18">
+      <c r="O2" s="18">
+        <v>46117</v>
+      </c>
+      <c r="P2" s="18">
         <v>46121</v>
       </c>
-      <c r="O2" s="18">
+      <c r="Q2" s="18">
         <v>46128</v>
       </c>
-      <c r="P2" s="18">
+      <c r="R2" s="18"/>
+      <c r="S2" s="18">
         <v>46135</v>
       </c>
-      <c r="Q2" s="18">
+      <c r="T2" s="18">
         <v>46142</v>
       </c>
-      <c r="R2" s="18">
+      <c r="U2" s="18"/>
+      <c r="V2" s="18">
         <v>46149</v>
       </c>
-      <c r="S2" s="18">
+      <c r="W2" s="18">
         <v>46156</v>
       </c>
-      <c r="T2" s="18">
+      <c r="X2" s="18"/>
+      <c r="Y2" s="18">
         <v>46163</v>
       </c>
-      <c r="U2" s="18">
+      <c r="Z2" s="18">
         <v>46170</v>
       </c>
-      <c r="V2" s="22"/>
-      <c r="W2" s="3" t="s">
+      <c r="AA2" s="22"/>
+      <c r="AB2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3" t="s">
+      <c r="AC2" s="3"/>
+      <c r="AD2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="Z2" s="3"/>
-      <c r="AA2" s="3" t="s">
+      <c r="AE2" s="3"/>
+      <c r="AF2" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AG2" s="3"/>
+      <c r="AH2" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="AB2" s="3"/>
-      <c r="AC2" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="AD2" s="3"/>
-      <c r="AE2" s="3" t="s">
+      <c r="AI2" s="3"/>
+      <c r="AJ2" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK2" s="3"/>
+      <c r="AL2" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="AF2" s="3"/>
-      <c r="AG2" s="3" t="s">
+      <c r="AM2" s="3"/>
+      <c r="AN2" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="AH2" s="3"/>
-      <c r="AI2" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="AJ2" s="3"/>
-      <c r="AK2" s="3"/>
-      <c r="AL2" s="3"/>
-      <c r="AM2" s="3"/>
-      <c r="AN2" s="3"/>
       <c r="AO2" s="3"/>
       <c r="AP2" s="3"/>
       <c r="AQ2" s="3"/>
       <c r="AR2" s="3"/>
-      <c r="AS2" s="1" t="s">
+      <c r="AS2" s="3"/>
+      <c r="AT2" s="3"/>
+      <c r="AU2" s="3"/>
+      <c r="AV2" s="3"/>
+      <c r="AW2" s="3"/>
+      <c r="AX2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:45">
+    <row r="3" spans="1:50">
       <c r="A3" s="23" t="s">
         <v>4</v>
       </c>
@@ -918,7 +946,7 @@
       <c r="J3" s="23"/>
       <c r="K3" s="23"/>
       <c r="L3" s="23"/>
-      <c r="M3" s="24"/>
+      <c r="M3" s="23"/>
       <c r="N3" s="24"/>
       <c r="O3" s="24"/>
       <c r="P3" s="24"/>
@@ -950,9 +978,14 @@
       <c r="AP3" s="24"/>
       <c r="AQ3" s="24"/>
       <c r="AR3" s="24"/>
-      <c r="AS3" s="26"/>
-    </row>
-    <row r="4" spans="1:45">
+      <c r="AS3" s="24"/>
+      <c r="AT3" s="24"/>
+      <c r="AU3" s="24"/>
+      <c r="AV3" s="24"/>
+      <c r="AW3" s="24"/>
+      <c r="AX3" s="26"/>
+    </row>
+    <row r="4" spans="1:50">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -963,7 +996,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>7</v>
@@ -986,25 +1019,27 @@
       <c r="K4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L4" s="2"/>
-      <c r="M4" s="3"/>
+      <c r="L4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="31"/>
       <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
+      <c r="O4" s="30"/>
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
+      <c r="R4" s="30"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
-      <c r="U4" s="22"/>
-      <c r="V4" s="22"/>
-      <c r="W4" s="21">
+      <c r="U4" s="30"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="30"/>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="22"/>
+      <c r="AA4" s="22"/>
+      <c r="AB4" s="21">
         <v>46086</v>
       </c>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="3"/>
-      <c r="AA4" s="3"/>
-      <c r="AB4" s="3"/>
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3"/>
@@ -1021,9 +1056,14 @@
       <c r="AP4" s="3"/>
       <c r="AQ4" s="3"/>
       <c r="AR4" s="3"/>
-      <c r="AS4" s="1"/>
-    </row>
-    <row r="5" spans="1:45">
+      <c r="AS4" s="3"/>
+      <c r="AT4" s="3"/>
+      <c r="AU4" s="3"/>
+      <c r="AV4" s="3"/>
+      <c r="AW4" s="3"/>
+      <c r="AX4" s="1"/>
+    </row>
+    <row r="5" spans="1:50">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1034,7 +1074,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>7</v>
@@ -1057,29 +1097,31 @@
       <c r="K5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L5" s="2"/>
-      <c r="M5" s="3"/>
+      <c r="L5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" s="31"/>
       <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
+      <c r="O5" s="30"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
+      <c r="R5" s="30"/>
       <c r="S5" s="3"/>
       <c r="T5" s="3"/>
-      <c r="U5" s="22"/>
-      <c r="V5" s="22"/>
-      <c r="W5" s="14">
+      <c r="U5" s="30"/>
+      <c r="V5" s="3"/>
+      <c r="W5" s="3"/>
+      <c r="X5" s="30"/>
+      <c r="Y5" s="3"/>
+      <c r="Z5" s="22"/>
+      <c r="AA5" s="22"/>
+      <c r="AB5" s="14">
         <v>46100</v>
       </c>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="14">
+      <c r="AC5" s="3"/>
+      <c r="AD5" s="14">
         <v>46100</v>
       </c>
-      <c r="Z5" s="3"/>
-      <c r="AA5" s="3"/>
-      <c r="AB5" s="3"/>
-      <c r="AC5" s="3"/>
-      <c r="AD5" s="3"/>
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
       <c r="AG5" s="3"/>
@@ -1094,9 +1136,14 @@
       <c r="AP5" s="3"/>
       <c r="AQ5" s="3"/>
       <c r="AR5" s="3"/>
-      <c r="AS5" s="1"/>
-    </row>
-    <row r="6" spans="1:45">
+      <c r="AS5" s="3"/>
+      <c r="AT5" s="3"/>
+      <c r="AU5" s="3"/>
+      <c r="AV5" s="3"/>
+      <c r="AW5" s="3"/>
+      <c r="AX5" s="1"/>
+    </row>
+    <row r="6" spans="1:50">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1128,25 +1175,27 @@
       <c r="K6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L6" s="2"/>
-      <c r="M6" s="3"/>
+      <c r="L6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M6" s="31"/>
       <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
+      <c r="O6" s="30"/>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
+      <c r="R6" s="30"/>
       <c r="S6" s="3"/>
       <c r="T6" s="3"/>
-      <c r="U6" s="22"/>
-      <c r="V6" s="22"/>
-      <c r="W6" s="14">
+      <c r="U6" s="30"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3"/>
+      <c r="X6" s="30"/>
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="22"/>
+      <c r="AA6" s="22"/>
+      <c r="AB6" s="14">
         <v>46072</v>
       </c>
-      <c r="X6" s="3"/>
-      <c r="Y6" s="3"/>
-      <c r="Z6" s="3"/>
-      <c r="AA6" s="3"/>
-      <c r="AB6" s="3"/>
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
       <c r="AE6" s="3"/>
@@ -1163,9 +1212,14 @@
       <c r="AP6" s="3"/>
       <c r="AQ6" s="3"/>
       <c r="AR6" s="3"/>
-      <c r="AS6" s="1"/>
-    </row>
-    <row r="7" spans="1:45">
+      <c r="AS6" s="3"/>
+      <c r="AT6" s="3"/>
+      <c r="AU6" s="3"/>
+      <c r="AV6" s="3"/>
+      <c r="AW6" s="3"/>
+      <c r="AX6" s="1"/>
+    </row>
+    <row r="7" spans="1:50">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -1176,7 +1230,7 @@
         <v>4</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>7</v>
@@ -1199,33 +1253,35 @@
       <c r="K7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L7" s="2"/>
-      <c r="M7" s="3"/>
+      <c r="L7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M7" s="31"/>
       <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
+      <c r="O7" s="30"/>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
+      <c r="R7" s="30"/>
       <c r="S7" s="3"/>
       <c r="T7" s="3"/>
-      <c r="U7" s="22"/>
-      <c r="V7" s="22"/>
-      <c r="W7" s="28">
+      <c r="U7" s="30"/>
+      <c r="V7" s="3"/>
+      <c r="W7" s="3"/>
+      <c r="X7" s="30"/>
+      <c r="Y7" s="3"/>
+      <c r="Z7" s="22"/>
+      <c r="AA7" s="22"/>
+      <c r="AB7" s="28">
         <v>46100</v>
       </c>
-      <c r="X7" s="3"/>
-      <c r="Y7" s="14">
+      <c r="AC7" s="3"/>
+      <c r="AD7" s="14">
         <v>46100</v>
       </c>
-      <c r="Z7" s="3"/>
-      <c r="AA7" s="34">
+      <c r="AE7" s="3"/>
+      <c r="AF7" s="32">
         <v>46100</v>
       </c>
-      <c r="AB7" s="3"/>
-      <c r="AC7" s="3"/>
-      <c r="AD7" s="3"/>
-      <c r="AE7" s="3"/>
-      <c r="AF7" s="3"/>
       <c r="AG7" s="3"/>
       <c r="AH7" s="3"/>
       <c r="AI7" s="3"/>
@@ -1238,9 +1294,14 @@
       <c r="AP7" s="3"/>
       <c r="AQ7" s="3"/>
       <c r="AR7" s="3"/>
-      <c r="AS7" s="1"/>
-    </row>
-    <row r="8" spans="1:45" ht="18" customHeight="1">
+      <c r="AS7" s="3"/>
+      <c r="AT7" s="3"/>
+      <c r="AU7" s="3"/>
+      <c r="AV7" s="3"/>
+      <c r="AW7" s="3"/>
+      <c r="AX7" s="1"/>
+    </row>
+    <row r="8" spans="1:50" ht="18" customHeight="1">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -1261,7 +1322,7 @@
         <v>24</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I8" s="19" t="s">
         <v>7</v>
@@ -1272,25 +1333,27 @@
       <c r="K8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L8" s="2"/>
-      <c r="M8" s="3"/>
+      <c r="L8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M8" s="31"/>
       <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
+      <c r="O8" s="30"/>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
+      <c r="R8" s="30"/>
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
-      <c r="U8" s="22"/>
-      <c r="V8" s="22"/>
-      <c r="W8" s="14">
+      <c r="U8" s="30"/>
+      <c r="V8" s="3"/>
+      <c r="W8" s="3"/>
+      <c r="X8" s="30"/>
+      <c r="Y8" s="3"/>
+      <c r="Z8" s="22"/>
+      <c r="AA8" s="22"/>
+      <c r="AB8" s="14">
         <v>46100</v>
       </c>
-      <c r="X8" s="3"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="3"/>
-      <c r="AA8" s="3"/>
-      <c r="AB8" s="3"/>
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3"/>
@@ -1307,9 +1370,14 @@
       <c r="AP8" s="3"/>
       <c r="AQ8" s="3"/>
       <c r="AR8" s="3"/>
-      <c r="AS8" s="1"/>
-    </row>
-    <row r="9" spans="1:45">
+      <c r="AS8" s="3"/>
+      <c r="AT8" s="3"/>
+      <c r="AU8" s="3"/>
+      <c r="AV8" s="3"/>
+      <c r="AW8" s="3"/>
+      <c r="AX8" s="1"/>
+    </row>
+    <row r="9" spans="1:50">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -1320,7 +1388,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>7</v>
@@ -1343,25 +1411,27 @@
       <c r="K9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L9" s="2"/>
-      <c r="M9" s="3"/>
+      <c r="L9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M9" s="31"/>
       <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
+      <c r="O9" s="30"/>
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
+      <c r="R9" s="30"/>
       <c r="S9" s="3"/>
       <c r="T9" s="3"/>
-      <c r="U9" s="22"/>
-      <c r="V9" s="22"/>
-      <c r="W9" s="14">
+      <c r="U9" s="30"/>
+      <c r="V9" s="3"/>
+      <c r="W9" s="3"/>
+      <c r="X9" s="30"/>
+      <c r="Y9" s="3"/>
+      <c r="Z9" s="22"/>
+      <c r="AA9" s="22"/>
+      <c r="AB9" s="14">
         <v>46100</v>
       </c>
-      <c r="X9" s="3"/>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="3"/>
-      <c r="AA9" s="3"/>
-      <c r="AB9" s="3"/>
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3"/>
@@ -1378,9 +1448,14 @@
       <c r="AP9" s="3"/>
       <c r="AQ9" s="3"/>
       <c r="AR9" s="3"/>
-      <c r="AS9" s="1"/>
-    </row>
-    <row r="10" spans="1:45">
+      <c r="AS9" s="3"/>
+      <c r="AT9" s="3"/>
+      <c r="AU9" s="3"/>
+      <c r="AV9" s="3"/>
+      <c r="AW9" s="3"/>
+      <c r="AX9" s="1"/>
+    </row>
+    <row r="10" spans="1:50">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -1414,25 +1489,27 @@
       <c r="K10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L10" s="2"/>
-      <c r="M10" s="3"/>
+      <c r="L10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M10" s="31"/>
       <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
+      <c r="O10" s="30"/>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
+      <c r="R10" s="30"/>
       <c r="S10" s="3"/>
       <c r="T10" s="3"/>
-      <c r="U10" s="22"/>
-      <c r="V10" s="22"/>
-      <c r="W10" s="14">
+      <c r="U10" s="30"/>
+      <c r="V10" s="3"/>
+      <c r="W10" s="3"/>
+      <c r="X10" s="30"/>
+      <c r="Y10" s="3"/>
+      <c r="Z10" s="22"/>
+      <c r="AA10" s="22"/>
+      <c r="AB10" s="14">
         <v>46079</v>
       </c>
-      <c r="X10" s="3"/>
-      <c r="Y10" s="3"/>
-      <c r="Z10" s="3"/>
-      <c r="AA10" s="3"/>
-      <c r="AB10" s="3"/>
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3"/>
@@ -1449,9 +1526,14 @@
       <c r="AP10" s="3"/>
       <c r="AQ10" s="3"/>
       <c r="AR10" s="3"/>
-      <c r="AS10" s="1"/>
-    </row>
-    <row r="11" spans="1:45" ht="14.45" customHeight="1">
+      <c r="AS10" s="3"/>
+      <c r="AT10" s="3"/>
+      <c r="AU10" s="3"/>
+      <c r="AV10" s="3"/>
+      <c r="AW10" s="3"/>
+      <c r="AX10" s="1"/>
+    </row>
+    <row r="11" spans="1:50" ht="14.45" customHeight="1">
       <c r="A11" s="2">
         <v>8</v>
       </c>
@@ -1483,8 +1565,10 @@
       <c r="K11" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="L11" s="11"/>
-      <c r="M11" s="12"/>
+      <c r="L11" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="M11" s="11"/>
       <c r="N11" s="12"/>
       <c r="O11" s="12"/>
       <c r="P11" s="12"/>
@@ -1494,35 +1578,40 @@
       <c r="T11" s="12"/>
       <c r="U11" s="12"/>
       <c r="V11" s="12"/>
-      <c r="W11" s="14">
-        <v>46079</v>
-      </c>
+      <c r="W11" s="12"/>
       <c r="X11" s="12"/>
-      <c r="Y11" s="35">
-        <v>46100</v>
-      </c>
+      <c r="Y11" s="12"/>
       <c r="Z11" s="12"/>
       <c r="AA11" s="12"/>
-      <c r="AB11" s="12"/>
-      <c r="AC11" s="31"/>
-      <c r="AD11" s="31"/>
-      <c r="AE11" s="31"/>
-      <c r="AF11" s="31"/>
-      <c r="AG11" s="31"/>
-      <c r="AH11" s="31"/>
-      <c r="AI11" s="31"/>
-      <c r="AJ11" s="31"/>
-      <c r="AK11" s="31"/>
-      <c r="AL11" s="31"/>
-      <c r="AM11" s="31"/>
-      <c r="AN11" s="31"/>
-      <c r="AO11" s="31"/>
-      <c r="AP11" s="31"/>
-      <c r="AQ11" s="31"/>
-      <c r="AR11" s="31"/>
-      <c r="AS11" s="30"/>
-    </row>
-    <row r="12" spans="1:45">
+      <c r="AB11" s="14">
+        <v>46079</v>
+      </c>
+      <c r="AC11" s="12"/>
+      <c r="AD11" s="33">
+        <v>46100</v>
+      </c>
+      <c r="AE11" s="12"/>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="37"/>
+      <c r="AI11" s="37"/>
+      <c r="AJ11" s="37"/>
+      <c r="AK11" s="37"/>
+      <c r="AL11" s="37"/>
+      <c r="AM11" s="37"/>
+      <c r="AN11" s="37"/>
+      <c r="AO11" s="37"/>
+      <c r="AP11" s="37"/>
+      <c r="AQ11" s="37"/>
+      <c r="AR11" s="37"/>
+      <c r="AS11" s="37"/>
+      <c r="AT11" s="37"/>
+      <c r="AU11" s="37"/>
+      <c r="AV11" s="37"/>
+      <c r="AW11" s="37"/>
+      <c r="AX11" s="34"/>
+    </row>
+    <row r="12" spans="1:50">
       <c r="A12" s="2">
         <v>9</v>
       </c>
@@ -1556,8 +1645,10 @@
       <c r="K12" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="L12" s="11"/>
-      <c r="M12" s="12"/>
+      <c r="L12" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="M12" s="11"/>
       <c r="N12" s="12"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
@@ -1567,35 +1658,40 @@
       <c r="T12" s="12"/>
       <c r="U12" s="12"/>
       <c r="V12" s="12"/>
-      <c r="W12" s="14">
-        <v>46072</v>
-      </c>
+      <c r="W12" s="12"/>
       <c r="X12" s="12"/>
-      <c r="Y12" s="35">
-        <v>46100</v>
-      </c>
+      <c r="Y12" s="12"/>
       <c r="Z12" s="12"/>
       <c r="AA12" s="12"/>
-      <c r="AB12" s="12"/>
-      <c r="AC12" s="31"/>
-      <c r="AD12" s="31"/>
-      <c r="AE12" s="31"/>
-      <c r="AF12" s="31"/>
-      <c r="AG12" s="31"/>
-      <c r="AH12" s="31"/>
-      <c r="AI12" s="31"/>
-      <c r="AJ12" s="31"/>
-      <c r="AK12" s="31"/>
-      <c r="AL12" s="31"/>
-      <c r="AM12" s="31"/>
-      <c r="AN12" s="31"/>
-      <c r="AO12" s="31"/>
-      <c r="AP12" s="31"/>
-      <c r="AQ12" s="31"/>
-      <c r="AR12" s="31"/>
-      <c r="AS12" s="30"/>
-    </row>
-    <row r="13" spans="1:45">
+      <c r="AB12" s="14">
+        <v>46072</v>
+      </c>
+      <c r="AC12" s="12"/>
+      <c r="AD12" s="33">
+        <v>46100</v>
+      </c>
+      <c r="AE12" s="12"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="37"/>
+      <c r="AI12" s="37"/>
+      <c r="AJ12" s="37"/>
+      <c r="AK12" s="37"/>
+      <c r="AL12" s="37"/>
+      <c r="AM12" s="37"/>
+      <c r="AN12" s="37"/>
+      <c r="AO12" s="37"/>
+      <c r="AP12" s="37"/>
+      <c r="AQ12" s="37"/>
+      <c r="AR12" s="37"/>
+      <c r="AS12" s="37"/>
+      <c r="AT12" s="37"/>
+      <c r="AU12" s="37"/>
+      <c r="AV12" s="37"/>
+      <c r="AW12" s="37"/>
+      <c r="AX12" s="34"/>
+    </row>
+    <row r="13" spans="1:50">
       <c r="A13" s="2">
         <v>10</v>
       </c>
@@ -1629,8 +1725,10 @@
       <c r="K13" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="L13" s="11"/>
-      <c r="M13" s="12"/>
+      <c r="L13" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="M13" s="11"/>
       <c r="N13" s="12"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
@@ -1640,35 +1738,40 @@
       <c r="T13" s="12"/>
       <c r="U13" s="12"/>
       <c r="V13" s="12"/>
-      <c r="W13" s="14">
-        <v>46072</v>
-      </c>
+      <c r="W13" s="12"/>
       <c r="X13" s="12"/>
-      <c r="Y13" s="21">
-        <v>46093</v>
-      </c>
+      <c r="Y13" s="12"/>
       <c r="Z13" s="12"/>
       <c r="AA13" s="12"/>
-      <c r="AB13" s="12"/>
-      <c r="AC13" s="31"/>
-      <c r="AD13" s="31"/>
-      <c r="AE13" s="31"/>
-      <c r="AF13" s="31"/>
-      <c r="AG13" s="31"/>
-      <c r="AH13" s="31"/>
-      <c r="AI13" s="31"/>
-      <c r="AJ13" s="31"/>
-      <c r="AK13" s="31"/>
-      <c r="AL13" s="31"/>
-      <c r="AM13" s="31"/>
-      <c r="AN13" s="31"/>
-      <c r="AO13" s="31"/>
-      <c r="AP13" s="31"/>
-      <c r="AQ13" s="31"/>
-      <c r="AR13" s="31"/>
-      <c r="AS13" s="30"/>
-    </row>
-    <row r="14" spans="1:45">
+      <c r="AB13" s="14">
+        <v>46072</v>
+      </c>
+      <c r="AC13" s="12"/>
+      <c r="AD13" s="21">
+        <v>46093</v>
+      </c>
+      <c r="AE13" s="12"/>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="37"/>
+      <c r="AI13" s="37"/>
+      <c r="AJ13" s="37"/>
+      <c r="AK13" s="37"/>
+      <c r="AL13" s="37"/>
+      <c r="AM13" s="37"/>
+      <c r="AN13" s="37"/>
+      <c r="AO13" s="37"/>
+      <c r="AP13" s="37"/>
+      <c r="AQ13" s="37"/>
+      <c r="AR13" s="37"/>
+      <c r="AS13" s="37"/>
+      <c r="AT13" s="37"/>
+      <c r="AU13" s="37"/>
+      <c r="AV13" s="37"/>
+      <c r="AW13" s="37"/>
+      <c r="AX13" s="34"/>
+    </row>
+    <row r="14" spans="1:50">
       <c r="A14" s="2">
         <v>11</v>
       </c>
@@ -1700,22 +1803,24 @@
       <c r="K14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L14" s="2"/>
-      <c r="M14" s="3"/>
+      <c r="L14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M14" s="31"/>
       <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
+      <c r="O14" s="30"/>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
+      <c r="R14" s="30"/>
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
-      <c r="U14" s="22"/>
-      <c r="V14" s="22"/>
+      <c r="U14" s="30"/>
+      <c r="V14" s="3"/>
       <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
+      <c r="X14" s="30"/>
       <c r="Y14" s="3"/>
-      <c r="Z14" s="3"/>
-      <c r="AA14" s="3"/>
+      <c r="Z14" s="22"/>
+      <c r="AA14" s="22"/>
       <c r="AB14" s="3"/>
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
@@ -1733,9 +1838,14 @@
       <c r="AP14" s="3"/>
       <c r="AQ14" s="3"/>
       <c r="AR14" s="3"/>
-      <c r="AS14" s="1"/>
-    </row>
-    <row r="15" spans="1:45">
+      <c r="AS14" s="3"/>
+      <c r="AT14" s="3"/>
+      <c r="AU14" s="3"/>
+      <c r="AV14" s="3"/>
+      <c r="AW14" s="3"/>
+      <c r="AX14" s="1"/>
+    </row>
+    <row r="15" spans="1:50">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -1746,7 +1856,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>7</v>
@@ -1769,29 +1879,31 @@
       <c r="K15" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L15" s="2"/>
-      <c r="M15" s="3"/>
+      <c r="L15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M15" s="31"/>
       <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
+      <c r="O15" s="30"/>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
+      <c r="R15" s="30"/>
       <c r="S15" s="3"/>
       <c r="T15" s="3"/>
-      <c r="U15" s="22"/>
-      <c r="V15" s="22"/>
-      <c r="W15" s="14">
+      <c r="U15" s="30"/>
+      <c r="V15" s="3"/>
+      <c r="W15" s="3"/>
+      <c r="X15" s="30"/>
+      <c r="Y15" s="3"/>
+      <c r="Z15" s="22"/>
+      <c r="AA15" s="22"/>
+      <c r="AB15" s="14">
         <v>46079</v>
       </c>
-      <c r="X15" s="3"/>
-      <c r="Y15" s="34">
+      <c r="AC15" s="3"/>
+      <c r="AD15" s="32">
         <v>46100</v>
       </c>
-      <c r="Z15" s="3"/>
-      <c r="AA15" s="3"/>
-      <c r="AB15" s="3"/>
-      <c r="AC15" s="3"/>
-      <c r="AD15" s="3"/>
       <c r="AE15" s="3"/>
       <c r="AF15" s="3"/>
       <c r="AG15" s="3"/>
@@ -1806,9 +1918,14 @@
       <c r="AP15" s="3"/>
       <c r="AQ15" s="3"/>
       <c r="AR15" s="3"/>
-      <c r="AS15" s="1"/>
-    </row>
-    <row r="16" spans="1:45">
+      <c r="AS15" s="3"/>
+      <c r="AT15" s="3"/>
+      <c r="AU15" s="3"/>
+      <c r="AV15" s="3"/>
+      <c r="AW15" s="3"/>
+      <c r="AX15" s="1"/>
+    </row>
+    <row r="16" spans="1:50">
       <c r="A16" s="2">
         <v>13</v>
       </c>
@@ -1840,31 +1957,35 @@
       <c r="K16" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L16" s="2"/>
-      <c r="M16" s="3"/>
+      <c r="L16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M16" s="31"/>
       <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
+      <c r="O16" s="30"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
+      <c r="R16" s="30"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-      <c r="U16" s="22"/>
-      <c r="V16" s="22"/>
-      <c r="W16" s="14">
+      <c r="U16" s="30"/>
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+      <c r="X16" s="30"/>
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="22"/>
+      <c r="AA16" s="22"/>
+      <c r="AB16" s="14">
         <v>46072</v>
       </c>
-      <c r="X16" s="3"/>
-      <c r="Y16" s="34">
+      <c r="AC16" s="3"/>
+      <c r="AD16" s="32">
         <v>46100</v>
       </c>
-      <c r="Z16" s="3"/>
-      <c r="AA16" s="3"/>
-      <c r="AB16" s="3"/>
-      <c r="AC16" s="3"/>
-      <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-      <c r="AF16" s="3"/>
+      <c r="AF16" s="32">
+        <v>46104</v>
+      </c>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
@@ -1877,9 +1998,14 @@
       <c r="AP16" s="3"/>
       <c r="AQ16" s="3"/>
       <c r="AR16" s="3"/>
-      <c r="AS16" s="1"/>
-    </row>
-    <row r="17" spans="1:45">
+      <c r="AS16" s="3"/>
+      <c r="AT16" s="3"/>
+      <c r="AU16" s="3"/>
+      <c r="AV16" s="3"/>
+      <c r="AW16" s="3"/>
+      <c r="AX16" s="1"/>
+    </row>
+    <row r="17" spans="1:50">
       <c r="A17" s="2">
         <v>14</v>
       </c>
@@ -1913,29 +2039,31 @@
       <c r="K17" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L17" s="2"/>
-      <c r="M17" s="3"/>
+      <c r="L17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M17" s="31"/>
       <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
+      <c r="O17" s="30"/>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
+      <c r="R17" s="30"/>
       <c r="S17" s="3"/>
       <c r="T17" s="3"/>
-      <c r="U17" s="22"/>
-      <c r="V17" s="22"/>
-      <c r="W17" s="14">
+      <c r="U17" s="30"/>
+      <c r="V17" s="3"/>
+      <c r="W17" s="3"/>
+      <c r="X17" s="30"/>
+      <c r="Y17" s="3"/>
+      <c r="Z17" s="22"/>
+      <c r="AA17" s="22"/>
+      <c r="AB17" s="14">
         <v>46072</v>
       </c>
-      <c r="X17" s="3"/>
-      <c r="Y17" s="14">
+      <c r="AC17" s="3"/>
+      <c r="AD17" s="14">
         <v>46100</v>
       </c>
-      <c r="Z17" s="3"/>
-      <c r="AA17" s="3"/>
-      <c r="AB17" s="3"/>
-      <c r="AC17" s="3"/>
-      <c r="AD17" s="3"/>
       <c r="AE17" s="3"/>
       <c r="AF17" s="3"/>
       <c r="AG17" s="3"/>
@@ -1950,9 +2078,14 @@
       <c r="AP17" s="3"/>
       <c r="AQ17" s="3"/>
       <c r="AR17" s="3"/>
-      <c r="AS17" s="1"/>
-    </row>
-    <row r="18" spans="1:45">
+      <c r="AS17" s="3"/>
+      <c r="AT17" s="3"/>
+      <c r="AU17" s="3"/>
+      <c r="AV17" s="3"/>
+      <c r="AW17" s="3"/>
+      <c r="AX17" s="1"/>
+    </row>
+    <row r="18" spans="1:50">
       <c r="A18" s="2">
         <v>15</v>
       </c>
@@ -1963,7 +2096,7 @@
         <v>4</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>7</v>
@@ -1986,33 +2119,35 @@
       <c r="K18" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L18" s="2"/>
-      <c r="M18" s="3"/>
+      <c r="L18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M18" s="31"/>
       <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
+      <c r="O18" s="30"/>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
+      <c r="R18" s="30"/>
       <c r="S18" s="3"/>
       <c r="T18" s="3"/>
-      <c r="U18" s="22"/>
-      <c r="V18" s="22"/>
-      <c r="W18" s="28">
+      <c r="U18" s="30"/>
+      <c r="V18" s="3"/>
+      <c r="W18" s="3"/>
+      <c r="X18" s="30"/>
+      <c r="Y18" s="3"/>
+      <c r="Z18" s="22"/>
+      <c r="AA18" s="22"/>
+      <c r="AB18" s="28">
         <v>46100</v>
       </c>
-      <c r="X18" s="3"/>
-      <c r="Y18" s="14">
+      <c r="AC18" s="3"/>
+      <c r="AD18" s="14">
         <v>46100</v>
       </c>
-      <c r="Z18" s="3"/>
-      <c r="AA18" s="34">
+      <c r="AE18" s="3"/>
+      <c r="AF18" s="32">
         <v>46100</v>
       </c>
-      <c r="AB18" s="3"/>
-      <c r="AC18" s="3"/>
-      <c r="AD18" s="3"/>
-      <c r="AE18" s="3"/>
-      <c r="AF18" s="3"/>
       <c r="AG18" s="3"/>
       <c r="AH18" s="3"/>
       <c r="AI18" s="3"/>
@@ -2025,9 +2160,14 @@
       <c r="AP18" s="3"/>
       <c r="AQ18" s="3"/>
       <c r="AR18" s="3"/>
-      <c r="AS18" s="1"/>
-    </row>
-    <row r="19" spans="1:45">
+      <c r="AS18" s="3"/>
+      <c r="AT18" s="3"/>
+      <c r="AU18" s="3"/>
+      <c r="AV18" s="3"/>
+      <c r="AW18" s="3"/>
+      <c r="AX18" s="1"/>
+    </row>
+    <row r="19" spans="1:50">
       <c r="A19" s="2">
         <v>16</v>
       </c>
@@ -2059,25 +2199,27 @@
       <c r="K19" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L19" s="2"/>
-      <c r="M19" s="3"/>
+      <c r="L19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M19" s="31"/>
       <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
+      <c r="O19" s="30"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
+      <c r="R19" s="30"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-      <c r="U19" s="22"/>
-      <c r="V19" s="22"/>
-      <c r="W19" s="14">
+      <c r="U19" s="30"/>
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+      <c r="X19" s="30"/>
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="22"/>
+      <c r="AA19" s="22"/>
+      <c r="AB19" s="14">
         <v>46100</v>
       </c>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
-      <c r="Z19" s="3"/>
-      <c r="AA19" s="3"/>
-      <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
@@ -2094,9 +2236,14 @@
       <c r="AP19" s="3"/>
       <c r="AQ19" s="3"/>
       <c r="AR19" s="3"/>
-      <c r="AS19" s="1"/>
-    </row>
-    <row r="20" spans="1:45">
+      <c r="AS19" s="3"/>
+      <c r="AT19" s="3"/>
+      <c r="AU19" s="3"/>
+      <c r="AV19" s="3"/>
+      <c r="AW19" s="3"/>
+      <c r="AX19" s="1"/>
+    </row>
+    <row r="20" spans="1:50">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -2107,7 +2254,7 @@
         <v>16</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>24</v>
@@ -2130,22 +2277,24 @@
       <c r="K20" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L20" s="2"/>
-      <c r="M20" s="3"/>
+      <c r="L20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M20" s="31"/>
       <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
+      <c r="O20" s="30"/>
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
-      <c r="R20" s="3"/>
+      <c r="R20" s="30"/>
       <c r="S20" s="3"/>
       <c r="T20" s="3"/>
-      <c r="U20" s="22"/>
-      <c r="V20" s="22"/>
+      <c r="U20" s="30"/>
+      <c r="V20" s="3"/>
       <c r="W20" s="3"/>
-      <c r="X20" s="3"/>
+      <c r="X20" s="30"/>
       <c r="Y20" s="3"/>
-      <c r="Z20" s="3"/>
-      <c r="AA20" s="3"/>
+      <c r="Z20" s="22"/>
+      <c r="AA20" s="22"/>
       <c r="AB20" s="3"/>
       <c r="AC20" s="3"/>
       <c r="AD20" s="3"/>
@@ -2163,9 +2312,14 @@
       <c r="AP20" s="3"/>
       <c r="AQ20" s="3"/>
       <c r="AR20" s="3"/>
-      <c r="AS20" s="1"/>
-    </row>
-    <row r="21" spans="1:45">
+      <c r="AS20" s="3"/>
+      <c r="AT20" s="3"/>
+      <c r="AU20" s="3"/>
+      <c r="AV20" s="3"/>
+      <c r="AW20" s="3"/>
+      <c r="AX20" s="1"/>
+    </row>
+    <row r="21" spans="1:50">
       <c r="A21" s="2">
         <v>18</v>
       </c>
@@ -2176,7 +2330,7 @@
         <v>5</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>7</v>
@@ -2199,25 +2353,27 @@
       <c r="K21" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L21" s="2"/>
-      <c r="M21" s="3"/>
+      <c r="L21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M21" s="31"/>
       <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
+      <c r="O21" s="30"/>
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
-      <c r="R21" s="3"/>
+      <c r="R21" s="30"/>
       <c r="S21" s="3"/>
       <c r="T21" s="3"/>
-      <c r="U21" s="22"/>
-      <c r="V21" s="22"/>
-      <c r="W21" s="14">
+      <c r="U21" s="30"/>
+      <c r="V21" s="3"/>
+      <c r="W21" s="3"/>
+      <c r="X21" s="30"/>
+      <c r="Y21" s="3"/>
+      <c r="Z21" s="22"/>
+      <c r="AA21" s="22"/>
+      <c r="AB21" s="14">
         <v>46100</v>
       </c>
-      <c r="X21" s="3"/>
-      <c r="Y21" s="3"/>
-      <c r="Z21" s="3"/>
-      <c r="AA21" s="3"/>
-      <c r="AB21" s="3"/>
       <c r="AC21" s="3"/>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3"/>
@@ -2234,9 +2390,14 @@
       <c r="AP21" s="3"/>
       <c r="AQ21" s="3"/>
       <c r="AR21" s="3"/>
-      <c r="AS21" s="1"/>
-    </row>
-    <row r="22" spans="1:45">
+      <c r="AS21" s="3"/>
+      <c r="AT21" s="3"/>
+      <c r="AU21" s="3"/>
+      <c r="AV21" s="3"/>
+      <c r="AW21" s="3"/>
+      <c r="AX21" s="1"/>
+    </row>
+    <row r="22" spans="1:50">
       <c r="A22" s="2">
         <v>19</v>
       </c>
@@ -2268,29 +2429,31 @@
       <c r="K22" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L22" s="2"/>
-      <c r="M22" s="3"/>
+      <c r="L22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M22" s="31"/>
       <c r="N22" s="3"/>
-      <c r="O22" s="3"/>
+      <c r="O22" s="30"/>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
-      <c r="R22" s="3"/>
+      <c r="R22" s="30"/>
       <c r="S22" s="3"/>
       <c r="T22" s="3"/>
-      <c r="U22" s="22"/>
-      <c r="V22" s="22"/>
-      <c r="W22" s="14">
+      <c r="U22" s="30"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+      <c r="X22" s="30"/>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="22"/>
+      <c r="AA22" s="22"/>
+      <c r="AB22" s="14">
         <v>46072</v>
       </c>
-      <c r="X22" s="3"/>
-      <c r="Y22" s="14">
+      <c r="AC22" s="3"/>
+      <c r="AD22" s="14">
         <v>46100</v>
       </c>
-      <c r="Z22" s="3"/>
-      <c r="AA22" s="3"/>
-      <c r="AB22" s="3"/>
-      <c r="AC22" s="3"/>
-      <c r="AD22" s="3"/>
       <c r="AE22" s="3"/>
       <c r="AF22" s="3"/>
       <c r="AG22" s="3"/>
@@ -2305,9 +2468,14 @@
       <c r="AP22" s="3"/>
       <c r="AQ22" s="3"/>
       <c r="AR22" s="3"/>
-      <c r="AS22" s="1"/>
-    </row>
-    <row r="23" spans="1:45">
+      <c r="AS22" s="3"/>
+      <c r="AT22" s="3"/>
+      <c r="AU22" s="3"/>
+      <c r="AV22" s="3"/>
+      <c r="AW22" s="3"/>
+      <c r="AX22" s="1"/>
+    </row>
+    <row r="23" spans="1:50">
       <c r="A23" s="2">
         <v>20</v>
       </c>
@@ -2318,7 +2486,7 @@
         <v>14</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>7</v>
@@ -2341,29 +2509,31 @@
       <c r="K23" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L23" s="2"/>
-      <c r="M23" s="3"/>
+      <c r="L23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M23" s="31"/>
       <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
+      <c r="O23" s="30"/>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
-      <c r="R23" s="3"/>
+      <c r="R23" s="30"/>
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
-      <c r="U23" s="22"/>
-      <c r="V23" s="22"/>
-      <c r="W23" s="14">
+      <c r="U23" s="30"/>
+      <c r="V23" s="3"/>
+      <c r="W23" s="3"/>
+      <c r="X23" s="30"/>
+      <c r="Y23" s="3"/>
+      <c r="Z23" s="22"/>
+      <c r="AA23" s="22"/>
+      <c r="AB23" s="14">
         <v>46072</v>
       </c>
-      <c r="X23" s="3"/>
-      <c r="Y23" s="14">
+      <c r="AC23" s="3"/>
+      <c r="AD23" s="14">
         <v>46100</v>
       </c>
-      <c r="Z23" s="3"/>
-      <c r="AA23" s="3"/>
-      <c r="AB23" s="3"/>
-      <c r="AC23" s="3"/>
-      <c r="AD23" s="3"/>
       <c r="AE23" s="3"/>
       <c r="AF23" s="3"/>
       <c r="AG23" s="3"/>
@@ -2378,9 +2548,14 @@
       <c r="AP23" s="3"/>
       <c r="AQ23" s="3"/>
       <c r="AR23" s="3"/>
-      <c r="AS23" s="1"/>
-    </row>
-    <row r="24" spans="1:45">
+      <c r="AS23" s="3"/>
+      <c r="AT23" s="3"/>
+      <c r="AU23" s="3"/>
+      <c r="AV23" s="3"/>
+      <c r="AW23" s="3"/>
+      <c r="AX23" s="1"/>
+    </row>
+    <row r="24" spans="1:50">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -2391,7 +2566,7 @@
         <v>15</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>7</v>
@@ -2414,22 +2589,24 @@
       <c r="K24" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L24" s="2"/>
-      <c r="M24" s="3"/>
+      <c r="L24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M24" s="31"/>
       <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
+      <c r="O24" s="30"/>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
-      <c r="R24" s="3"/>
+      <c r="R24" s="30"/>
       <c r="S24" s="3"/>
       <c r="T24" s="3"/>
-      <c r="U24" s="22"/>
-      <c r="V24" s="22"/>
+      <c r="U24" s="30"/>
+      <c r="V24" s="3"/>
       <c r="W24" s="3"/>
-      <c r="X24" s="3"/>
+      <c r="X24" s="30"/>
       <c r="Y24" s="3"/>
-      <c r="Z24" s="3"/>
-      <c r="AA24" s="3"/>
+      <c r="Z24" s="22"/>
+      <c r="AA24" s="22"/>
       <c r="AB24" s="3"/>
       <c r="AC24" s="3"/>
       <c r="AD24" s="3"/>
@@ -2447,9 +2624,14 @@
       <c r="AP24" s="3"/>
       <c r="AQ24" s="3"/>
       <c r="AR24" s="3"/>
-      <c r="AS24" s="1"/>
-    </row>
-    <row r="25" spans="1:45">
+      <c r="AS24" s="3"/>
+      <c r="AT24" s="3"/>
+      <c r="AU24" s="3"/>
+      <c r="AV24" s="3"/>
+      <c r="AW24" s="3"/>
+      <c r="AX24" s="1"/>
+    </row>
+    <row r="25" spans="1:50">
       <c r="A25" s="2">
         <v>22</v>
       </c>
@@ -2481,29 +2663,31 @@
       <c r="K25" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L25" s="2"/>
-      <c r="M25" s="3"/>
+      <c r="L25" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M25" s="31"/>
       <c r="N25" s="3"/>
-      <c r="O25" s="3"/>
+      <c r="O25" s="30"/>
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
+      <c r="R25" s="30"/>
       <c r="S25" s="3"/>
       <c r="T25" s="3"/>
-      <c r="U25" s="22"/>
-      <c r="V25" s="22"/>
-      <c r="W25" s="14">
+      <c r="U25" s="30"/>
+      <c r="V25" s="3"/>
+      <c r="W25" s="3"/>
+      <c r="X25" s="30"/>
+      <c r="Y25" s="3"/>
+      <c r="Z25" s="22"/>
+      <c r="AA25" s="22"/>
+      <c r="AB25" s="14">
         <v>46072</v>
       </c>
-      <c r="X25" s="3"/>
-      <c r="Y25" s="34">
+      <c r="AC25" s="3"/>
+      <c r="AD25" s="32">
         <v>46100</v>
       </c>
-      <c r="Z25" s="3"/>
-      <c r="AA25" s="3"/>
-      <c r="AB25" s="3"/>
-      <c r="AC25" s="3"/>
-      <c r="AD25" s="3"/>
       <c r="AE25" s="3"/>
       <c r="AF25" s="3"/>
       <c r="AG25" s="3"/>
@@ -2518,9 +2702,14 @@
       <c r="AP25" s="3"/>
       <c r="AQ25" s="3"/>
       <c r="AR25" s="3"/>
-      <c r="AS25" s="1"/>
-    </row>
-    <row r="26" spans="1:45">
+      <c r="AS25" s="3"/>
+      <c r="AT25" s="3"/>
+      <c r="AU25" s="3"/>
+      <c r="AV25" s="3"/>
+      <c r="AW25" s="3"/>
+      <c r="AX25" s="1"/>
+    </row>
+    <row r="26" spans="1:50">
       <c r="A26" s="2">
         <v>23</v>
       </c>
@@ -2552,22 +2741,24 @@
       <c r="K26" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L26" s="2"/>
-      <c r="M26" s="3"/>
+      <c r="L26" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M26" s="31"/>
       <c r="N26" s="3"/>
-      <c r="O26" s="3"/>
+      <c r="O26" s="30"/>
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
-      <c r="R26" s="3"/>
+      <c r="R26" s="30"/>
       <c r="S26" s="3"/>
       <c r="T26" s="3"/>
-      <c r="U26" s="22"/>
-      <c r="V26" s="22"/>
+      <c r="U26" s="30"/>
+      <c r="V26" s="3"/>
       <c r="W26" s="3"/>
-      <c r="X26" s="3"/>
+      <c r="X26" s="30"/>
       <c r="Y26" s="3"/>
-      <c r="Z26" s="3"/>
-      <c r="AA26" s="3"/>
+      <c r="Z26" s="22"/>
+      <c r="AA26" s="22"/>
       <c r="AB26" s="3"/>
       <c r="AC26" s="3"/>
       <c r="AD26" s="3"/>
@@ -2585,9 +2776,14 @@
       <c r="AP26" s="3"/>
       <c r="AQ26" s="3"/>
       <c r="AR26" s="3"/>
-      <c r="AS26" s="1"/>
-    </row>
-    <row r="27" spans="1:45">
+      <c r="AS26" s="3"/>
+      <c r="AT26" s="3"/>
+      <c r="AU26" s="3"/>
+      <c r="AV26" s="3"/>
+      <c r="AW26" s="3"/>
+      <c r="AX26" s="1"/>
+    </row>
+    <row r="27" spans="1:50">
       <c r="A27" s="2">
         <v>24</v>
       </c>
@@ -2598,7 +2794,7 @@
         <v>2</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>7</v>
@@ -2621,29 +2817,31 @@
       <c r="K27" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="L27" s="2"/>
-      <c r="M27" s="3"/>
+      <c r="L27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M27" s="31"/>
       <c r="N27" s="3"/>
-      <c r="O27" s="3"/>
+      <c r="O27" s="30"/>
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
-      <c r="R27" s="3"/>
+      <c r="R27" s="30"/>
       <c r="S27" s="3"/>
       <c r="T27" s="3"/>
-      <c r="U27" s="22"/>
-      <c r="V27" s="22"/>
-      <c r="W27" s="14">
+      <c r="U27" s="30"/>
+      <c r="V27" s="3"/>
+      <c r="W27" s="3"/>
+      <c r="X27" s="30"/>
+      <c r="Y27" s="3"/>
+      <c r="Z27" s="22"/>
+      <c r="AA27" s="22"/>
+      <c r="AB27" s="14">
         <v>46100</v>
       </c>
-      <c r="X27" s="3"/>
-      <c r="Y27" s="14">
+      <c r="AC27" s="3"/>
+      <c r="AD27" s="14">
         <v>46100</v>
       </c>
-      <c r="Z27" s="3"/>
-      <c r="AA27" s="3"/>
-      <c r="AB27" s="3"/>
-      <c r="AC27" s="3"/>
-      <c r="AD27" s="3"/>
       <c r="AE27" s="3"/>
       <c r="AF27" s="3"/>
       <c r="AG27" s="3"/>
@@ -2658,9 +2856,14 @@
       <c r="AP27" s="3"/>
       <c r="AQ27" s="3"/>
       <c r="AR27" s="3"/>
-      <c r="AS27" s="1"/>
-    </row>
-    <row r="28" spans="1:45">
+      <c r="AS27" s="3"/>
+      <c r="AT27" s="3"/>
+      <c r="AU27" s="3"/>
+      <c r="AV27" s="3"/>
+      <c r="AW27" s="3"/>
+      <c r="AX27" s="1"/>
+    </row>
+    <row r="28" spans="1:50">
       <c r="A28" s="2">
         <v>25</v>
       </c>
@@ -2671,7 +2874,7 @@
         <v>1</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>7</v>
@@ -2694,25 +2897,27 @@
       <c r="K28" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L28" s="2"/>
-      <c r="M28" s="3"/>
+      <c r="L28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M28" s="31"/>
       <c r="N28" s="3"/>
-      <c r="O28" s="3"/>
+      <c r="O28" s="30"/>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
-      <c r="R28" s="3"/>
+      <c r="R28" s="30"/>
       <c r="S28" s="3"/>
       <c r="T28" s="3"/>
-      <c r="U28" s="22"/>
-      <c r="V28" s="22"/>
-      <c r="W28" s="21">
+      <c r="U28" s="30"/>
+      <c r="V28" s="3"/>
+      <c r="W28" s="3"/>
+      <c r="X28" s="30"/>
+      <c r="Y28" s="3"/>
+      <c r="Z28" s="22"/>
+      <c r="AA28" s="22"/>
+      <c r="AB28" s="21">
         <v>46086</v>
       </c>
-      <c r="X28" s="3"/>
-      <c r="Y28" s="3"/>
-      <c r="Z28" s="3"/>
-      <c r="AA28" s="3"/>
-      <c r="AB28" s="3"/>
       <c r="AC28" s="3"/>
       <c r="AD28" s="3"/>
       <c r="AE28" s="3"/>
@@ -2729,9 +2934,14 @@
       <c r="AP28" s="3"/>
       <c r="AQ28" s="3"/>
       <c r="AR28" s="3"/>
-      <c r="AS28" s="1"/>
-    </row>
-    <row r="29" spans="1:45">
+      <c r="AS28" s="3"/>
+      <c r="AT28" s="3"/>
+      <c r="AU28" s="3"/>
+      <c r="AV28" s="3"/>
+      <c r="AW28" s="3"/>
+      <c r="AX28" s="1"/>
+    </row>
+    <row r="29" spans="1:50">
       <c r="A29" s="2">
         <v>26</v>
       </c>
@@ -2763,29 +2973,31 @@
       <c r="K29" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L29" s="2"/>
-      <c r="M29" s="3"/>
+      <c r="L29" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M29" s="31"/>
       <c r="N29" s="3"/>
-      <c r="O29" s="3"/>
+      <c r="O29" s="30"/>
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
-      <c r="R29" s="3"/>
+      <c r="R29" s="30"/>
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
-      <c r="U29" s="22"/>
-      <c r="V29" s="22"/>
-      <c r="W29" s="14">
+      <c r="U29" s="30"/>
+      <c r="V29" s="3"/>
+      <c r="W29" s="3"/>
+      <c r="X29" s="30"/>
+      <c r="Y29" s="3"/>
+      <c r="Z29" s="22"/>
+      <c r="AA29" s="22"/>
+      <c r="AB29" s="14">
         <v>46072</v>
       </c>
-      <c r="X29" s="3"/>
-      <c r="Y29" s="14">
+      <c r="AC29" s="3"/>
+      <c r="AD29" s="14">
         <v>46100</v>
       </c>
-      <c r="Z29" s="3"/>
-      <c r="AA29" s="3"/>
-      <c r="AB29" s="3"/>
-      <c r="AC29" s="3"/>
-      <c r="AD29" s="3"/>
       <c r="AE29" s="3"/>
       <c r="AF29" s="3"/>
       <c r="AG29" s="3"/>
@@ -2800,9 +3012,14 @@
       <c r="AP29" s="3"/>
       <c r="AQ29" s="3"/>
       <c r="AR29" s="3"/>
-      <c r="AS29" s="1"/>
-    </row>
-    <row r="30" spans="1:45">
+      <c r="AS29" s="3"/>
+      <c r="AT29" s="3"/>
+      <c r="AU29" s="3"/>
+      <c r="AV29" s="3"/>
+      <c r="AW29" s="3"/>
+      <c r="AX29" s="1"/>
+    </row>
+    <row r="30" spans="1:50">
       <c r="A30" s="2">
         <v>27</v>
       </c>
@@ -2836,31 +3053,35 @@
       <c r="K30" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L30" s="2"/>
-      <c r="M30" s="3"/>
+      <c r="L30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M30" s="31"/>
       <c r="N30" s="3"/>
-      <c r="O30" s="3"/>
+      <c r="O30" s="30"/>
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
-      <c r="R30" s="3"/>
+      <c r="R30" s="30"/>
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
-      <c r="U30" s="22"/>
-      <c r="V30" s="22"/>
-      <c r="W30" s="14">
+      <c r="U30" s="30"/>
+      <c r="V30" s="3"/>
+      <c r="W30" s="3"/>
+      <c r="X30" s="30"/>
+      <c r="Y30" s="3"/>
+      <c r="Z30" s="22"/>
+      <c r="AA30" s="22"/>
+      <c r="AB30" s="14">
         <v>46072</v>
       </c>
-      <c r="X30" s="3"/>
-      <c r="Y30" s="34">
+      <c r="AC30" s="3"/>
+      <c r="AD30" s="32">
         <v>46100</v>
       </c>
-      <c r="Z30" s="3"/>
-      <c r="AA30" s="3"/>
-      <c r="AB30" s="3"/>
-      <c r="AC30" s="3"/>
-      <c r="AD30" s="3"/>
       <c r="AE30" s="3"/>
-      <c r="AF30" s="3"/>
+      <c r="AF30" s="32">
+        <v>46104</v>
+      </c>
       <c r="AG30" s="3"/>
       <c r="AH30" s="3"/>
       <c r="AI30" s="3"/>
@@ -2873,9 +3094,14 @@
       <c r="AP30" s="3"/>
       <c r="AQ30" s="3"/>
       <c r="AR30" s="3"/>
-      <c r="AS30" s="1"/>
-    </row>
-    <row r="31" spans="1:45">
+      <c r="AS30" s="3"/>
+      <c r="AT30" s="3"/>
+      <c r="AU30" s="3"/>
+      <c r="AV30" s="3"/>
+      <c r="AW30" s="3"/>
+      <c r="AX30" s="1"/>
+    </row>
+    <row r="31" spans="1:50">
       <c r="A31" s="2">
         <v>28</v>
       </c>
@@ -2909,25 +3135,27 @@
       <c r="K31" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L31" s="2"/>
-      <c r="M31" s="3"/>
+      <c r="L31" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M31" s="31"/>
       <c r="N31" s="3"/>
-      <c r="O31" s="3"/>
+      <c r="O31" s="30"/>
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
-      <c r="R31" s="3"/>
+      <c r="R31" s="30"/>
       <c r="S31" s="3"/>
       <c r="T31" s="3"/>
-      <c r="U31" s="22"/>
-      <c r="V31" s="22"/>
-      <c r="W31" s="14">
+      <c r="U31" s="30"/>
+      <c r="V31" s="3"/>
+      <c r="W31" s="3"/>
+      <c r="X31" s="30"/>
+      <c r="Y31" s="3"/>
+      <c r="Z31" s="22"/>
+      <c r="AA31" s="22"/>
+      <c r="AB31" s="14">
         <v>46072</v>
       </c>
-      <c r="X31" s="3"/>
-      <c r="Y31" s="3"/>
-      <c r="Z31" s="3"/>
-      <c r="AA31" s="3"/>
-      <c r="AB31" s="3"/>
       <c r="AC31" s="3"/>
       <c r="AD31" s="3"/>
       <c r="AE31" s="3"/>
@@ -2944,9 +3172,14 @@
       <c r="AP31" s="3"/>
       <c r="AQ31" s="3"/>
       <c r="AR31" s="3"/>
-      <c r="AS31" s="1"/>
-    </row>
-    <row r="32" spans="1:45">
+      <c r="AS31" s="3"/>
+      <c r="AT31" s="3"/>
+      <c r="AU31" s="3"/>
+      <c r="AV31" s="3"/>
+      <c r="AW31" s="3"/>
+      <c r="AX31" s="1"/>
+    </row>
+    <row r="32" spans="1:50">
       <c r="A32" s="2">
         <v>29</v>
       </c>
@@ -2978,22 +3211,24 @@
       <c r="K32" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L32" s="2"/>
-      <c r="M32" s="3"/>
+      <c r="L32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M32" s="31"/>
       <c r="N32" s="3"/>
-      <c r="O32" s="3"/>
+      <c r="O32" s="30"/>
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
-      <c r="R32" s="3"/>
+      <c r="R32" s="30"/>
       <c r="S32" s="3"/>
       <c r="T32" s="3"/>
-      <c r="U32" s="22"/>
-      <c r="V32" s="22"/>
+      <c r="U32" s="30"/>
+      <c r="V32" s="3"/>
       <c r="W32" s="3"/>
-      <c r="X32" s="3"/>
+      <c r="X32" s="30"/>
       <c r="Y32" s="3"/>
-      <c r="Z32" s="3"/>
-      <c r="AA32" s="3"/>
+      <c r="Z32" s="22"/>
+      <c r="AA32" s="22"/>
       <c r="AB32" s="3"/>
       <c r="AC32" s="3"/>
       <c r="AD32" s="3"/>
@@ -3011,9 +3246,14 @@
       <c r="AP32" s="3"/>
       <c r="AQ32" s="3"/>
       <c r="AR32" s="3"/>
-      <c r="AS32" s="1"/>
-    </row>
-    <row r="33" spans="1:45">
+      <c r="AS32" s="3"/>
+      <c r="AT32" s="3"/>
+      <c r="AU32" s="3"/>
+      <c r="AV32" s="3"/>
+      <c r="AW32" s="3"/>
+      <c r="AX32" s="1"/>
+    </row>
+    <row r="33" spans="1:50">
       <c r="A33" s="2">
         <v>30</v>
       </c>
@@ -3045,25 +3285,27 @@
       <c r="K33" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L33" s="2"/>
-      <c r="M33" s="3"/>
+      <c r="L33" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M33" s="31"/>
       <c r="N33" s="3"/>
-      <c r="O33" s="3"/>
+      <c r="O33" s="30"/>
       <c r="P33" s="3"/>
       <c r="Q33" s="3"/>
-      <c r="R33" s="3"/>
+      <c r="R33" s="30"/>
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
-      <c r="U33" s="22"/>
-      <c r="V33" s="22"/>
-      <c r="W33" s="14">
+      <c r="U33" s="30"/>
+      <c r="V33" s="3"/>
+      <c r="W33" s="3"/>
+      <c r="X33" s="30"/>
+      <c r="Y33" s="3"/>
+      <c r="Z33" s="22"/>
+      <c r="AA33" s="22"/>
+      <c r="AB33" s="14">
         <v>46079</v>
       </c>
-      <c r="X33" s="3"/>
-      <c r="Y33" s="3"/>
-      <c r="Z33" s="3"/>
-      <c r="AA33" s="3"/>
-      <c r="AB33" s="3"/>
       <c r="AC33" s="3"/>
       <c r="AD33" s="3"/>
       <c r="AE33" s="3"/>
@@ -3080,9 +3322,14 @@
       <c r="AP33" s="3"/>
       <c r="AQ33" s="3"/>
       <c r="AR33" s="3"/>
-      <c r="AS33" s="1"/>
-    </row>
-    <row r="34" spans="1:45">
+      <c r="AS33" s="3"/>
+      <c r="AT33" s="3"/>
+      <c r="AU33" s="3"/>
+      <c r="AV33" s="3"/>
+      <c r="AW33" s="3"/>
+      <c r="AX33" s="1"/>
+    </row>
+    <row r="34" spans="1:50">
       <c r="A34" s="2">
         <v>31</v>
       </c>
@@ -3114,29 +3361,31 @@
       <c r="K34" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L34" s="2"/>
-      <c r="M34" s="3"/>
+      <c r="L34" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M34" s="31"/>
       <c r="N34" s="3"/>
-      <c r="O34" s="3"/>
+      <c r="O34" s="30"/>
       <c r="P34" s="3"/>
       <c r="Q34" s="3"/>
-      <c r="R34" s="3"/>
+      <c r="R34" s="30"/>
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
-      <c r="U34" s="22"/>
-      <c r="V34" s="22"/>
-      <c r="W34" s="14">
+      <c r="U34" s="30"/>
+      <c r="V34" s="3"/>
+      <c r="W34" s="3"/>
+      <c r="X34" s="30"/>
+      <c r="Y34" s="3"/>
+      <c r="Z34" s="22"/>
+      <c r="AA34" s="22"/>
+      <c r="AB34" s="14">
         <v>46072</v>
       </c>
-      <c r="X34" s="3"/>
-      <c r="Y34" s="21">
+      <c r="AC34" s="3"/>
+      <c r="AD34" s="21">
         <v>46093</v>
       </c>
-      <c r="Z34" s="3"/>
-      <c r="AA34" s="3"/>
-      <c r="AB34" s="3"/>
-      <c r="AC34" s="3"/>
-      <c r="AD34" s="3"/>
       <c r="AE34" s="3"/>
       <c r="AF34" s="3"/>
       <c r="AG34" s="3"/>
@@ -3151,9 +3400,14 @@
       <c r="AP34" s="3"/>
       <c r="AQ34" s="3"/>
       <c r="AR34" s="3"/>
-      <c r="AS34" s="1"/>
-    </row>
-    <row r="35" spans="1:45">
+      <c r="AS34" s="3"/>
+      <c r="AT34" s="3"/>
+      <c r="AU34" s="3"/>
+      <c r="AV34" s="3"/>
+      <c r="AW34" s="3"/>
+      <c r="AX34" s="1"/>
+    </row>
+    <row r="35" spans="1:50">
       <c r="A35" s="2">
         <v>32</v>
       </c>
@@ -3185,22 +3439,24 @@
       <c r="K35" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L35" s="2"/>
-      <c r="M35" s="3"/>
+      <c r="L35" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M35" s="31"/>
       <c r="N35" s="3"/>
-      <c r="O35" s="3"/>
+      <c r="O35" s="30"/>
       <c r="P35" s="3"/>
       <c r="Q35" s="3"/>
-      <c r="R35" s="3"/>
+      <c r="R35" s="30"/>
       <c r="S35" s="3"/>
       <c r="T35" s="3"/>
-      <c r="U35" s="22"/>
-      <c r="V35" s="22"/>
+      <c r="U35" s="30"/>
+      <c r="V35" s="3"/>
       <c r="W35" s="3"/>
-      <c r="X35" s="3"/>
+      <c r="X35" s="30"/>
       <c r="Y35" s="3"/>
-      <c r="Z35" s="3"/>
-      <c r="AA35" s="3"/>
+      <c r="Z35" s="22"/>
+      <c r="AA35" s="22"/>
       <c r="AB35" s="3"/>
       <c r="AC35" s="3"/>
       <c r="AD35" s="3"/>
@@ -3218,9 +3474,14 @@
       <c r="AP35" s="3"/>
       <c r="AQ35" s="3"/>
       <c r="AR35" s="3"/>
-      <c r="AS35" s="1"/>
-    </row>
-    <row r="36" spans="1:45">
+      <c r="AS35" s="3"/>
+      <c r="AT35" s="3"/>
+      <c r="AU35" s="3"/>
+      <c r="AV35" s="3"/>
+      <c r="AW35" s="3"/>
+      <c r="AX35" s="1"/>
+    </row>
+    <row r="36" spans="1:50">
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="2"/>
@@ -3231,21 +3492,21 @@
       <c r="J36" s="9"/>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
-      <c r="M36" s="3"/>
+      <c r="M36" s="31"/>
       <c r="N36" s="3"/>
-      <c r="O36" s="3"/>
+      <c r="O36" s="30"/>
       <c r="P36" s="3"/>
       <c r="Q36" s="3"/>
-      <c r="R36" s="3"/>
+      <c r="R36" s="30"/>
       <c r="S36" s="3"/>
       <c r="T36" s="3"/>
-      <c r="U36" s="22"/>
-      <c r="V36" s="22"/>
+      <c r="U36" s="30"/>
+      <c r="V36" s="3"/>
       <c r="W36" s="3"/>
-      <c r="X36" s="3"/>
+      <c r="X36" s="30"/>
       <c r="Y36" s="3"/>
-      <c r="Z36" s="3"/>
-      <c r="AA36" s="3"/>
+      <c r="Z36" s="22"/>
+      <c r="AA36" s="22"/>
       <c r="AB36" s="3"/>
       <c r="AC36" s="3"/>
       <c r="AD36" s="3"/>
@@ -3263,9 +3524,14 @@
       <c r="AP36" s="3"/>
       <c r="AQ36" s="3"/>
       <c r="AR36" s="3"/>
-      <c r="AS36" s="1"/>
-    </row>
-    <row r="37" spans="1:45">
+      <c r="AS36" s="3"/>
+      <c r="AT36" s="3"/>
+      <c r="AU36" s="3"/>
+      <c r="AV36" s="3"/>
+      <c r="AW36" s="3"/>
+      <c r="AX36" s="1"/>
+    </row>
+    <row r="37" spans="1:50">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -3283,25 +3549,61 @@
       <c r="H37" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="I37" s="2"/>
-      <c r="J37" s="9"/>
-      <c r="K37" s="2"/>
-      <c r="L37" s="2"/>
-      <c r="M37" s="3"/>
-      <c r="N37" s="3"/>
-      <c r="O37" s="3"/>
-      <c r="P37" s="3"/>
-      <c r="Q37" s="3"/>
-      <c r="R37" s="3"/>
-      <c r="S37" s="3"/>
-      <c r="T37" s="3"/>
-      <c r="U37" s="22"/>
-      <c r="V37" s="22"/>
-      <c r="W37" s="3"/>
-      <c r="X37" s="3"/>
-      <c r="Y37" s="3"/>
-      <c r="Z37" s="3"/>
-      <c r="AA37" s="3"/>
+      <c r="I37" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="J37" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="K37" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="L37" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="M37" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="N37" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="O37" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="P37" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q37" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="R37" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="S37" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="T37" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="U37" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="V37" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="W37" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="X37" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y37" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z37" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA37" s="22"/>
       <c r="AB37" s="3"/>
       <c r="AC37" s="3"/>
       <c r="AD37" s="3"/>
@@ -3319,9 +3621,14 @@
       <c r="AP37" s="3"/>
       <c r="AQ37" s="3"/>
       <c r="AR37" s="3"/>
-      <c r="AS37" s="1"/>
-    </row>
-    <row r="38" spans="1:45">
+      <c r="AS37" s="3"/>
+      <c r="AT37" s="3"/>
+      <c r="AU37" s="3"/>
+      <c r="AV37" s="3"/>
+      <c r="AW37" s="3"/>
+      <c r="AX37" s="1"/>
+    </row>
+    <row r="38" spans="1:50">
       <c r="E38">
         <v>1</v>
       </c>
@@ -3347,123 +3654,135 @@
         <v>7</v>
       </c>
       <c r="M38">
+        <v>7</v>
+      </c>
+      <c r="N38">
         <v>8</v>
       </c>
-      <c r="N38">
+      <c r="O38">
         <v>9</v>
       </c>
-      <c r="O38">
+      <c r="P38">
+        <v>9</v>
+      </c>
+      <c r="Q38">
         <v>10</v>
       </c>
-      <c r="P38">
+      <c r="S38">
         <v>11</v>
       </c>
-      <c r="Q38">
+      <c r="T38">
         <v>12</v>
       </c>
-      <c r="R38">
+      <c r="V38">
         <v>13</v>
       </c>
-      <c r="S38">
+      <c r="W38">
         <v>14</v>
       </c>
-      <c r="T38">
+      <c r="Y38">
         <v>15</v>
       </c>
-      <c r="U38">
+      <c r="Z38">
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:45">
+    <row r="39" spans="1:50">
       <c r="E39" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G39" s="17" t="s">
-        <v>55</v>
+        <v>54</v>
+      </c>
+      <c r="I39" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="L39" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A1:AS1"/>
+    <mergeCell ref="AR11:AR13"/>
+    <mergeCell ref="AS11:AS13"/>
+    <mergeCell ref="AT11:AT13"/>
+    <mergeCell ref="A1:AX1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="AC11:AC13"/>
-    <mergeCell ref="AD11:AD13"/>
-    <mergeCell ref="AE11:AE13"/>
-    <mergeCell ref="AF11:AF13"/>
-    <mergeCell ref="AG11:AG13"/>
     <mergeCell ref="AH11:AH13"/>
     <mergeCell ref="AI11:AI13"/>
     <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AQ11:AQ13"/>
-    <mergeCell ref="AR11:AR13"/>
-    <mergeCell ref="AS11:AS13"/>
     <mergeCell ref="AK11:AK13"/>
     <mergeCell ref="AL11:AL13"/>
     <mergeCell ref="AM11:AM13"/>
     <mergeCell ref="AN11:AN13"/>
     <mergeCell ref="AO11:AO13"/>
+    <mergeCell ref="AU11:AU13"/>
+    <mergeCell ref="AV11:AV13"/>
+    <mergeCell ref="AW11:AW13"/>
+    <mergeCell ref="AX11:AX13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AQ11:AQ13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AP37"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="30"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="30"/>
-      <c r="AA1" s="30"/>
-      <c r="AB1" s="30"/>
-      <c r="AC1" s="30"/>
-      <c r="AD1" s="30"/>
-      <c r="AE1" s="30"/>
-      <c r="AF1" s="30"/>
-      <c r="AG1" s="30"/>
-      <c r="AH1" s="30"/>
-      <c r="AI1" s="30"/>
-      <c r="AJ1" s="30"/>
-      <c r="AK1" s="30"/>
-      <c r="AL1" s="30"/>
-      <c r="AM1" s="30"/>
-      <c r="AN1" s="30"/>
-      <c r="AO1" s="30"/>
-      <c r="AP1" s="30"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="34"/>
+      <c r="AA1" s="34"/>
+      <c r="AB1" s="34"/>
+      <c r="AC1" s="34"/>
+      <c r="AD1" s="34"/>
+      <c r="AE1" s="34"/>
+      <c r="AF1" s="34"/>
+      <c r="AG1" s="34"/>
+      <c r="AH1" s="34"/>
+      <c r="AI1" s="34"/>
+      <c r="AJ1" s="34"/>
+      <c r="AK1" s="34"/>
+      <c r="AL1" s="34"/>
+      <c r="AM1" s="34"/>
+      <c r="AN1" s="34"/>
+      <c r="AO1" s="34"/>
+      <c r="AP1" s="34"/>
     </row>
     <row r="2" spans="1:42" ht="30">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="33"/>
+      <c r="B2" s="36"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -3892,142 +4211,142 @@
       <c r="AP10" s="1"/>
     </row>
     <row r="11" spans="1:42">
-      <c r="A11" s="33">
+      <c r="A11" s="36">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="31"/>
-      <c r="M11" s="31"/>
-      <c r="N11" s="31"/>
-      <c r="O11" s="31"/>
-      <c r="P11" s="31"/>
-      <c r="Q11" s="31"/>
-      <c r="R11" s="31"/>
-      <c r="S11" s="31"/>
-      <c r="T11" s="31"/>
-      <c r="U11" s="31"/>
-      <c r="V11" s="31"/>
-      <c r="W11" s="31"/>
-      <c r="X11" s="31"/>
-      <c r="Y11" s="31"/>
-      <c r="Z11" s="31"/>
-      <c r="AA11" s="31"/>
-      <c r="AB11" s="31"/>
-      <c r="AC11" s="31"/>
-      <c r="AD11" s="31"/>
-      <c r="AE11" s="31"/>
-      <c r="AF11" s="31"/>
-      <c r="AG11" s="31"/>
-      <c r="AH11" s="31"/>
-      <c r="AI11" s="31"/>
-      <c r="AJ11" s="31"/>
-      <c r="AK11" s="31"/>
-      <c r="AL11" s="31"/>
-      <c r="AM11" s="31"/>
-      <c r="AN11" s="31"/>
-      <c r="AO11" s="31"/>
-      <c r="AP11" s="30"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="36"/>
+      <c r="K11" s="36"/>
+      <c r="L11" s="37"/>
+      <c r="M11" s="37"/>
+      <c r="N11" s="37"/>
+      <c r="O11" s="37"/>
+      <c r="P11" s="37"/>
+      <c r="Q11" s="37"/>
+      <c r="R11" s="37"/>
+      <c r="S11" s="37"/>
+      <c r="T11" s="37"/>
+      <c r="U11" s="37"/>
+      <c r="V11" s="37"/>
+      <c r="W11" s="37"/>
+      <c r="X11" s="37"/>
+      <c r="Y11" s="37"/>
+      <c r="Z11" s="37"/>
+      <c r="AA11" s="37"/>
+      <c r="AB11" s="37"/>
+      <c r="AC11" s="37"/>
+      <c r="AD11" s="37"/>
+      <c r="AE11" s="37"/>
+      <c r="AF11" s="37"/>
+      <c r="AG11" s="37"/>
+      <c r="AH11" s="37"/>
+      <c r="AI11" s="37"/>
+      <c r="AJ11" s="37"/>
+      <c r="AK11" s="37"/>
+      <c r="AL11" s="37"/>
+      <c r="AM11" s="37"/>
+      <c r="AN11" s="37"/>
+      <c r="AO11" s="37"/>
+      <c r="AP11" s="34"/>
     </row>
     <row r="12" spans="1:42">
-      <c r="A12" s="33"/>
+      <c r="A12" s="36"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="31"/>
-      <c r="M12" s="31"/>
-      <c r="N12" s="31"/>
-      <c r="O12" s="31"/>
-      <c r="P12" s="31"/>
-      <c r="Q12" s="31"/>
-      <c r="R12" s="31"/>
-      <c r="S12" s="31"/>
-      <c r="T12" s="31"/>
-      <c r="U12" s="31"/>
-      <c r="V12" s="31"/>
-      <c r="W12" s="31"/>
-      <c r="X12" s="31"/>
-      <c r="Y12" s="31"/>
-      <c r="Z12" s="31"/>
-      <c r="AA12" s="31"/>
-      <c r="AB12" s="31"/>
-      <c r="AC12" s="31"/>
-      <c r="AD12" s="31"/>
-      <c r="AE12" s="31"/>
-      <c r="AF12" s="31"/>
-      <c r="AG12" s="31"/>
-      <c r="AH12" s="31"/>
-      <c r="AI12" s="31"/>
-      <c r="AJ12" s="31"/>
-      <c r="AK12" s="31"/>
-      <c r="AL12" s="31"/>
-      <c r="AM12" s="31"/>
-      <c r="AN12" s="31"/>
-      <c r="AO12" s="31"/>
-      <c r="AP12" s="30"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="36"/>
+      <c r="K12" s="36"/>
+      <c r="L12" s="37"/>
+      <c r="M12" s="37"/>
+      <c r="N12" s="37"/>
+      <c r="O12" s="37"/>
+      <c r="P12" s="37"/>
+      <c r="Q12" s="37"/>
+      <c r="R12" s="37"/>
+      <c r="S12" s="37"/>
+      <c r="T12" s="37"/>
+      <c r="U12" s="37"/>
+      <c r="V12" s="37"/>
+      <c r="W12" s="37"/>
+      <c r="X12" s="37"/>
+      <c r="Y12" s="37"/>
+      <c r="Z12" s="37"/>
+      <c r="AA12" s="37"/>
+      <c r="AB12" s="37"/>
+      <c r="AC12" s="37"/>
+      <c r="AD12" s="37"/>
+      <c r="AE12" s="37"/>
+      <c r="AF12" s="37"/>
+      <c r="AG12" s="37"/>
+      <c r="AH12" s="37"/>
+      <c r="AI12" s="37"/>
+      <c r="AJ12" s="37"/>
+      <c r="AK12" s="37"/>
+      <c r="AL12" s="37"/>
+      <c r="AM12" s="37"/>
+      <c r="AN12" s="37"/>
+      <c r="AO12" s="37"/>
+      <c r="AP12" s="34"/>
     </row>
     <row r="13" spans="1:42">
-      <c r="A13" s="33"/>
+      <c r="A13" s="36"/>
       <c r="B13" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="33"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="31"/>
-      <c r="M13" s="31"/>
-      <c r="N13" s="31"/>
-      <c r="O13" s="31"/>
-      <c r="P13" s="31"/>
-      <c r="Q13" s="31"/>
-      <c r="R13" s="31"/>
-      <c r="S13" s="31"/>
-      <c r="T13" s="31"/>
-      <c r="U13" s="31"/>
-      <c r="V13" s="31"/>
-      <c r="W13" s="31"/>
-      <c r="X13" s="31"/>
-      <c r="Y13" s="31"/>
-      <c r="Z13" s="31"/>
-      <c r="AA13" s="31"/>
-      <c r="AB13" s="31"/>
-      <c r="AC13" s="31"/>
-      <c r="AD13" s="31"/>
-      <c r="AE13" s="31"/>
-      <c r="AF13" s="31"/>
-      <c r="AG13" s="31"/>
-      <c r="AH13" s="31"/>
-      <c r="AI13" s="31"/>
-      <c r="AJ13" s="31"/>
-      <c r="AK13" s="31"/>
-      <c r="AL13" s="31"/>
-      <c r="AM13" s="31"/>
-      <c r="AN13" s="31"/>
-      <c r="AO13" s="31"/>
-      <c r="AP13" s="30"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="36"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="37"/>
+      <c r="M13" s="37"/>
+      <c r="N13" s="37"/>
+      <c r="O13" s="37"/>
+      <c r="P13" s="37"/>
+      <c r="Q13" s="37"/>
+      <c r="R13" s="37"/>
+      <c r="S13" s="37"/>
+      <c r="T13" s="37"/>
+      <c r="U13" s="37"/>
+      <c r="V13" s="37"/>
+      <c r="W13" s="37"/>
+      <c r="X13" s="37"/>
+      <c r="Y13" s="37"/>
+      <c r="Z13" s="37"/>
+      <c r="AA13" s="37"/>
+      <c r="AB13" s="37"/>
+      <c r="AC13" s="37"/>
+      <c r="AD13" s="37"/>
+      <c r="AE13" s="37"/>
+      <c r="AF13" s="37"/>
+      <c r="AG13" s="37"/>
+      <c r="AH13" s="37"/>
+      <c r="AI13" s="37"/>
+      <c r="AJ13" s="37"/>
+      <c r="AK13" s="37"/>
+      <c r="AL13" s="37"/>
+      <c r="AM13" s="37"/>
+      <c r="AN13" s="37"/>
+      <c r="AO13" s="37"/>
+      <c r="AP13" s="34"/>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" s="2">
@@ -5183,33 +5502,6 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="AO11:AO13"/>
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="AN11:AN13"/>
-    <mergeCell ref="AE11:AE13"/>
-    <mergeCell ref="AF11:AF13"/>
-    <mergeCell ref="AG11:AG13"/>
-    <mergeCell ref="AH11:AH13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="Z11:Z13"/>
-    <mergeCell ref="AA11:AA13"/>
-    <mergeCell ref="AB11:AB13"/>
-    <mergeCell ref="AC11:AC13"/>
-    <mergeCell ref="AD11:AD13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="V11:V13"/>
-    <mergeCell ref="W11:W13"/>
-    <mergeCell ref="X11:X13"/>
-    <mergeCell ref="Y11:Y13"/>
-    <mergeCell ref="P11:P13"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="T11:T13"/>
     <mergeCell ref="A1:AP1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A11:A13"/>
@@ -5226,6 +5518,33 @@
     <mergeCell ref="M11:M13"/>
     <mergeCell ref="N11:N13"/>
     <mergeCell ref="O11:O13"/>
+    <mergeCell ref="P11:P13"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="T11:T13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="V11:V13"/>
+    <mergeCell ref="W11:W13"/>
+    <mergeCell ref="X11:X13"/>
+    <mergeCell ref="Y11:Y13"/>
+    <mergeCell ref="Z11:Z13"/>
+    <mergeCell ref="AA11:AA13"/>
+    <mergeCell ref="AB11:AB13"/>
+    <mergeCell ref="AC11:AC13"/>
+    <mergeCell ref="AD11:AD13"/>
+    <mergeCell ref="AE11:AE13"/>
+    <mergeCell ref="AF11:AF13"/>
+    <mergeCell ref="AG11:AG13"/>
+    <mergeCell ref="AH11:AH13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="AO11:AO13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
+    <mergeCell ref="AN11:AN13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ТКИ-341_Реверс_Инжиниринг.xlsx
+++ b/ТКИ-341_Реверс_Инжиниринг.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Сидоренко\Reverse_Engineering\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\Reverse_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8144D8E-C7DA-4711-B784-C97A1A2E2CB8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A11380D-C8C9-42AB-88CF-934ABF9B0EC6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="73">
   <si>
     <t>ВЕДОМОСТЬ ПОСЕЩАЕМОСТИ ЗАНЯТИЙ СТУДЕНТАМИ ГРУППЫ ТКИ "Компьютерная безопасность" ИТТСУ РУТ (МИИТ)</t>
   </si>
@@ -452,6 +452,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -459,9 +462,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -764,64 +764,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="14.45" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
-      <c r="T1" s="34"/>
-      <c r="U1" s="34"/>
-      <c r="V1" s="34"/>
-      <c r="W1" s="34"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="34"/>
-      <c r="Z1" s="34"/>
-      <c r="AA1" s="34"/>
-      <c r="AB1" s="34"/>
-      <c r="AC1" s="34"/>
-      <c r="AD1" s="34"/>
-      <c r="AE1" s="34"/>
-      <c r="AF1" s="34"/>
-      <c r="AG1" s="34"/>
-      <c r="AH1" s="34"/>
-      <c r="AI1" s="34"/>
-      <c r="AJ1" s="34"/>
-      <c r="AK1" s="34"/>
-      <c r="AL1" s="34"/>
-      <c r="AM1" s="34"/>
-      <c r="AN1" s="34"/>
-      <c r="AO1" s="34"/>
-      <c r="AP1" s="34"/>
-      <c r="AQ1" s="34"/>
-      <c r="AR1" s="34"/>
-      <c r="AS1" s="34"/>
-      <c r="AT1" s="34"/>
-      <c r="AU1" s="34"/>
-      <c r="AV1" s="34"/>
-      <c r="AW1" s="34"/>
-      <c r="AX1" s="34"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="35"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="35"/>
+      <c r="AA1" s="35"/>
+      <c r="AB1" s="35"/>
+      <c r="AC1" s="35"/>
+      <c r="AD1" s="35"/>
+      <c r="AE1" s="35"/>
+      <c r="AF1" s="35"/>
+      <c r="AG1" s="35"/>
+      <c r="AH1" s="35"/>
+      <c r="AI1" s="35"/>
+      <c r="AJ1" s="35"/>
+      <c r="AK1" s="35"/>
+      <c r="AL1" s="35"/>
+      <c r="AM1" s="35"/>
+      <c r="AN1" s="35"/>
+      <c r="AO1" s="35"/>
+      <c r="AP1" s="35"/>
+      <c r="AQ1" s="35"/>
+      <c r="AR1" s="35"/>
+      <c r="AS1" s="35"/>
+      <c r="AT1" s="35"/>
+      <c r="AU1" s="35"/>
+      <c r="AV1" s="35"/>
+      <c r="AW1" s="35"/>
+      <c r="AX1" s="35"/>
     </row>
     <row r="2" spans="1:50" ht="27.6" customHeight="1">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="36"/>
+      <c r="B2" s="37"/>
       <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1019,10 +1019,12 @@
       <c r="K4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M4" s="31"/>
+      <c r="L4" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="31" t="s">
+        <v>7</v>
+      </c>
       <c r="N4" s="3"/>
       <c r="O4" s="30"/>
       <c r="P4" s="3"/>
@@ -1097,10 +1099,12 @@
       <c r="K5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="L5" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="M5" s="31"/>
+      <c r="M5" s="31" t="s">
+        <v>24</v>
+      </c>
       <c r="N5" s="3"/>
       <c r="O5" s="30"/>
       <c r="P5" s="3"/>
@@ -1175,10 +1179,12 @@
       <c r="K6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M6" s="31"/>
+      <c r="L6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="M6" s="31" t="s">
+        <v>7</v>
+      </c>
       <c r="N6" s="3"/>
       <c r="O6" s="30"/>
       <c r="P6" s="3"/>
@@ -1253,10 +1259,12 @@
       <c r="K7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M7" s="31"/>
+      <c r="L7" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="M7" s="31" t="s">
+        <v>7</v>
+      </c>
       <c r="N7" s="3"/>
       <c r="O7" s="30"/>
       <c r="P7" s="3"/>
@@ -1333,10 +1341,12 @@
       <c r="K8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="L8" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="M8" s="31"/>
+      <c r="M8" s="31" t="s">
+        <v>24</v>
+      </c>
       <c r="N8" s="3"/>
       <c r="O8" s="30"/>
       <c r="P8" s="3"/>
@@ -1411,10 +1421,12 @@
       <c r="K9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="L9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="M9" s="31"/>
+      <c r="M9" s="31" t="s">
+        <v>24</v>
+      </c>
       <c r="N9" s="3"/>
       <c r="O9" s="30"/>
       <c r="P9" s="3"/>
@@ -1489,10 +1501,12 @@
       <c r="K10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="L10" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="M10" s="31"/>
+      <c r="M10" s="31" t="s">
+        <v>7</v>
+      </c>
       <c r="N10" s="3"/>
       <c r="O10" s="30"/>
       <c r="P10" s="3"/>
@@ -1565,10 +1579,12 @@
       <c r="K11" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="L11" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="M11" s="11"/>
+      <c r="L11" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="N11" s="12"/>
       <c r="O11" s="12"/>
       <c r="P11" s="12"/>
@@ -1593,23 +1609,23 @@
       <c r="AE11" s="12"/>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
-      <c r="AH11" s="37"/>
-      <c r="AI11" s="37"/>
-      <c r="AJ11" s="37"/>
-      <c r="AK11" s="37"/>
-      <c r="AL11" s="37"/>
-      <c r="AM11" s="37"/>
-      <c r="AN11" s="37"/>
-      <c r="AO11" s="37"/>
-      <c r="AP11" s="37"/>
-      <c r="AQ11" s="37"/>
-      <c r="AR11" s="37"/>
-      <c r="AS11" s="37"/>
-      <c r="AT11" s="37"/>
-      <c r="AU11" s="37"/>
-      <c r="AV11" s="37"/>
-      <c r="AW11" s="37"/>
-      <c r="AX11" s="34"/>
+      <c r="AH11" s="34"/>
+      <c r="AI11" s="34"/>
+      <c r="AJ11" s="34"/>
+      <c r="AK11" s="34"/>
+      <c r="AL11" s="34"/>
+      <c r="AM11" s="34"/>
+      <c r="AN11" s="34"/>
+      <c r="AO11" s="34"/>
+      <c r="AP11" s="34"/>
+      <c r="AQ11" s="34"/>
+      <c r="AR11" s="34"/>
+      <c r="AS11" s="34"/>
+      <c r="AT11" s="34"/>
+      <c r="AU11" s="34"/>
+      <c r="AV11" s="34"/>
+      <c r="AW11" s="34"/>
+      <c r="AX11" s="35"/>
     </row>
     <row r="12" spans="1:50">
       <c r="A12" s="2">
@@ -1645,10 +1661,12 @@
       <c r="K12" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="L12" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="M12" s="11"/>
+      <c r="L12" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="N12" s="12"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
@@ -1673,23 +1691,23 @@
       <c r="AE12" s="12"/>
       <c r="AF12" s="12"/>
       <c r="AG12" s="12"/>
-      <c r="AH12" s="37"/>
-      <c r="AI12" s="37"/>
-      <c r="AJ12" s="37"/>
-      <c r="AK12" s="37"/>
-      <c r="AL12" s="37"/>
-      <c r="AM12" s="37"/>
-      <c r="AN12" s="37"/>
-      <c r="AO12" s="37"/>
-      <c r="AP12" s="37"/>
-      <c r="AQ12" s="37"/>
-      <c r="AR12" s="37"/>
-      <c r="AS12" s="37"/>
-      <c r="AT12" s="37"/>
-      <c r="AU12" s="37"/>
-      <c r="AV12" s="37"/>
-      <c r="AW12" s="37"/>
-      <c r="AX12" s="34"/>
+      <c r="AH12" s="34"/>
+      <c r="AI12" s="34"/>
+      <c r="AJ12" s="34"/>
+      <c r="AK12" s="34"/>
+      <c r="AL12" s="34"/>
+      <c r="AM12" s="34"/>
+      <c r="AN12" s="34"/>
+      <c r="AO12" s="34"/>
+      <c r="AP12" s="34"/>
+      <c r="AQ12" s="34"/>
+      <c r="AR12" s="34"/>
+      <c r="AS12" s="34"/>
+      <c r="AT12" s="34"/>
+      <c r="AU12" s="34"/>
+      <c r="AV12" s="34"/>
+      <c r="AW12" s="34"/>
+      <c r="AX12" s="35"/>
     </row>
     <row r="13" spans="1:50">
       <c r="A13" s="2">
@@ -1725,10 +1743,12 @@
       <c r="K13" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="L13" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="M13" s="11"/>
+      <c r="L13" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="N13" s="12"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
@@ -1753,23 +1773,23 @@
       <c r="AE13" s="12"/>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
-      <c r="AH13" s="37"/>
-      <c r="AI13" s="37"/>
-      <c r="AJ13" s="37"/>
-      <c r="AK13" s="37"/>
-      <c r="AL13" s="37"/>
-      <c r="AM13" s="37"/>
-      <c r="AN13" s="37"/>
-      <c r="AO13" s="37"/>
-      <c r="AP13" s="37"/>
-      <c r="AQ13" s="37"/>
-      <c r="AR13" s="37"/>
-      <c r="AS13" s="37"/>
-      <c r="AT13" s="37"/>
-      <c r="AU13" s="37"/>
-      <c r="AV13" s="37"/>
-      <c r="AW13" s="37"/>
-      <c r="AX13" s="34"/>
+      <c r="AH13" s="34"/>
+      <c r="AI13" s="34"/>
+      <c r="AJ13" s="34"/>
+      <c r="AK13" s="34"/>
+      <c r="AL13" s="34"/>
+      <c r="AM13" s="34"/>
+      <c r="AN13" s="34"/>
+      <c r="AO13" s="34"/>
+      <c r="AP13" s="34"/>
+      <c r="AQ13" s="34"/>
+      <c r="AR13" s="34"/>
+      <c r="AS13" s="34"/>
+      <c r="AT13" s="34"/>
+      <c r="AU13" s="34"/>
+      <c r="AV13" s="34"/>
+      <c r="AW13" s="34"/>
+      <c r="AX13" s="35"/>
     </row>
     <row r="14" spans="1:50">
       <c r="A14" s="2">
@@ -1803,10 +1823,12 @@
       <c r="K14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M14" s="31"/>
+      <c r="L14" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="M14" s="31" t="s">
+        <v>7</v>
+      </c>
       <c r="N14" s="3"/>
       <c r="O14" s="30"/>
       <c r="P14" s="3"/>
@@ -1879,10 +1901,12 @@
       <c r="K15" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L15" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M15" s="31"/>
+      <c r="L15" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="M15" s="31" t="s">
+        <v>24</v>
+      </c>
       <c r="N15" s="3"/>
       <c r="O15" s="30"/>
       <c r="P15" s="3"/>
@@ -1957,10 +1981,12 @@
       <c r="K16" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M16" s="31"/>
+      <c r="L16" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="M16" s="31" t="s">
+        <v>7</v>
+      </c>
       <c r="N16" s="3"/>
       <c r="O16" s="30"/>
       <c r="P16" s="3"/>
@@ -2039,10 +2065,12 @@
       <c r="K17" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M17" s="31"/>
+      <c r="L17" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="M17" s="31" t="s">
+        <v>7</v>
+      </c>
       <c r="N17" s="3"/>
       <c r="O17" s="30"/>
       <c r="P17" s="3"/>
@@ -2119,10 +2147,12 @@
       <c r="K18" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M18" s="31"/>
+      <c r="L18" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="M18" s="31" t="s">
+        <v>24</v>
+      </c>
       <c r="N18" s="3"/>
       <c r="O18" s="30"/>
       <c r="P18" s="3"/>
@@ -2199,10 +2229,12 @@
       <c r="K19" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M19" s="31"/>
+      <c r="L19" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="M19" s="31" t="s">
+        <v>7</v>
+      </c>
       <c r="N19" s="3"/>
       <c r="O19" s="30"/>
       <c r="P19" s="3"/>
@@ -2277,10 +2309,12 @@
       <c r="K20" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M20" s="31"/>
+      <c r="L20" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="M20" s="31" t="s">
+        <v>24</v>
+      </c>
       <c r="N20" s="3"/>
       <c r="O20" s="30"/>
       <c r="P20" s="3"/>
@@ -2353,10 +2387,12 @@
       <c r="K21" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L21" s="2" t="s">
+      <c r="L21" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="M21" s="31"/>
+      <c r="M21" s="31" t="s">
+        <v>7</v>
+      </c>
       <c r="N21" s="3"/>
       <c r="O21" s="30"/>
       <c r="P21" s="3"/>
@@ -2429,10 +2465,12 @@
       <c r="K22" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M22" s="31"/>
+      <c r="L22" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="M22" s="31" t="s">
+        <v>24</v>
+      </c>
       <c r="N22" s="3"/>
       <c r="O22" s="30"/>
       <c r="P22" s="3"/>
@@ -2509,10 +2547,12 @@
       <c r="K23" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L23" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M23" s="31"/>
+      <c r="L23" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="M23" s="31" t="s">
+        <v>7</v>
+      </c>
       <c r="N23" s="3"/>
       <c r="O23" s="30"/>
       <c r="P23" s="3"/>
@@ -2589,10 +2629,12 @@
       <c r="K24" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L24" s="2" t="s">
+      <c r="L24" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="31"/>
+      <c r="M24" s="31" t="s">
+        <v>7</v>
+      </c>
       <c r="N24" s="3"/>
       <c r="O24" s="30"/>
       <c r="P24" s="3"/>
@@ -2663,10 +2705,12 @@
       <c r="K25" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L25" s="2" t="s">
+      <c r="L25" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="M25" s="31"/>
+      <c r="M25" s="31" t="s">
+        <v>24</v>
+      </c>
       <c r="N25" s="3"/>
       <c r="O25" s="30"/>
       <c r="P25" s="3"/>
@@ -2741,10 +2785,12 @@
       <c r="K26" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L26" s="2" t="s">
+      <c r="L26" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="M26" s="31"/>
+      <c r="M26" s="31" t="s">
+        <v>24</v>
+      </c>
       <c r="N26" s="3"/>
       <c r="O26" s="30"/>
       <c r="P26" s="3"/>
@@ -2817,10 +2863,12 @@
       <c r="K27" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="L27" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M27" s="31"/>
+      <c r="L27" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="M27" s="31" t="s">
+        <v>7</v>
+      </c>
       <c r="N27" s="3"/>
       <c r="O27" s="30"/>
       <c r="P27" s="3"/>
@@ -2897,10 +2945,12 @@
       <c r="K28" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L28" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M28" s="31"/>
+      <c r="L28" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="M28" s="31" t="s">
+        <v>7</v>
+      </c>
       <c r="N28" s="3"/>
       <c r="O28" s="30"/>
       <c r="P28" s="3"/>
@@ -2973,10 +3023,12 @@
       <c r="K29" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L29" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M29" s="31"/>
+      <c r="L29" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="M29" s="31" t="s">
+        <v>7</v>
+      </c>
       <c r="N29" s="3"/>
       <c r="O29" s="30"/>
       <c r="P29" s="3"/>
@@ -3053,10 +3105,12 @@
       <c r="K30" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L30" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M30" s="31"/>
+      <c r="L30" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="M30" s="31" t="s">
+        <v>7</v>
+      </c>
       <c r="N30" s="3"/>
       <c r="O30" s="30"/>
       <c r="P30" s="3"/>
@@ -3135,10 +3189,12 @@
       <c r="K31" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L31" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M31" s="31"/>
+      <c r="L31" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="M31" s="31" t="s">
+        <v>7</v>
+      </c>
       <c r="N31" s="3"/>
       <c r="O31" s="30"/>
       <c r="P31" s="3"/>
@@ -3211,10 +3267,12 @@
       <c r="K32" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L32" s="2" t="s">
+      <c r="L32" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="M32" s="31"/>
+      <c r="M32" s="31" t="s">
+        <v>7</v>
+      </c>
       <c r="N32" s="3"/>
       <c r="O32" s="30"/>
       <c r="P32" s="3"/>
@@ -3285,10 +3343,12 @@
       <c r="K33" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L33" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M33" s="31"/>
+      <c r="L33" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="M33" s="31" t="s">
+        <v>7</v>
+      </c>
       <c r="N33" s="3"/>
       <c r="O33" s="30"/>
       <c r="P33" s="3"/>
@@ -3361,10 +3421,12 @@
       <c r="K34" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L34" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M34" s="31"/>
+      <c r="L34" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="M34" s="31" t="s">
+        <v>7</v>
+      </c>
       <c r="N34" s="3"/>
       <c r="O34" s="30"/>
       <c r="P34" s="3"/>
@@ -3439,10 +3501,12 @@
       <c r="K35" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L35" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M35" s="31"/>
+      <c r="L35" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="M35" s="31" t="s">
+        <v>7</v>
+      </c>
       <c r="N35" s="3"/>
       <c r="O35" s="30"/>
       <c r="P35" s="3"/>
@@ -3703,6 +3767,9 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="AX11:AX13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AQ11:AQ13"/>
     <mergeCell ref="AR11:AR13"/>
     <mergeCell ref="AS11:AS13"/>
     <mergeCell ref="AT11:AT13"/>
@@ -3719,9 +3786,6 @@
     <mergeCell ref="AU11:AU13"/>
     <mergeCell ref="AV11:AV13"/>
     <mergeCell ref="AW11:AW13"/>
-    <mergeCell ref="AX11:AX13"/>
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AQ11:AQ13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3733,56 +3797,56 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
-      <c r="T1" s="34"/>
-      <c r="U1" s="34"/>
-      <c r="V1" s="34"/>
-      <c r="W1" s="34"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="34"/>
-      <c r="Z1" s="34"/>
-      <c r="AA1" s="34"/>
-      <c r="AB1" s="34"/>
-      <c r="AC1" s="34"/>
-      <c r="AD1" s="34"/>
-      <c r="AE1" s="34"/>
-      <c r="AF1" s="34"/>
-      <c r="AG1" s="34"/>
-      <c r="AH1" s="34"/>
-      <c r="AI1" s="34"/>
-      <c r="AJ1" s="34"/>
-      <c r="AK1" s="34"/>
-      <c r="AL1" s="34"/>
-      <c r="AM1" s="34"/>
-      <c r="AN1" s="34"/>
-      <c r="AO1" s="34"/>
-      <c r="AP1" s="34"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="35"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="35"/>
+      <c r="AA1" s="35"/>
+      <c r="AB1" s="35"/>
+      <c r="AC1" s="35"/>
+      <c r="AD1" s="35"/>
+      <c r="AE1" s="35"/>
+      <c r="AF1" s="35"/>
+      <c r="AG1" s="35"/>
+      <c r="AH1" s="35"/>
+      <c r="AI1" s="35"/>
+      <c r="AJ1" s="35"/>
+      <c r="AK1" s="35"/>
+      <c r="AL1" s="35"/>
+      <c r="AM1" s="35"/>
+      <c r="AN1" s="35"/>
+      <c r="AO1" s="35"/>
+      <c r="AP1" s="35"/>
     </row>
     <row r="2" spans="1:42" ht="30">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="36"/>
+      <c r="B2" s="37"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -4211,142 +4275,142 @@
       <c r="AP10" s="1"/>
     </row>
     <row r="11" spans="1:42">
-      <c r="A11" s="36">
+      <c r="A11" s="37">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="36"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="37"/>
-      <c r="M11" s="37"/>
-      <c r="N11" s="37"/>
-      <c r="O11" s="37"/>
-      <c r="P11" s="37"/>
-      <c r="Q11" s="37"/>
-      <c r="R11" s="37"/>
-      <c r="S11" s="37"/>
-      <c r="T11" s="37"/>
-      <c r="U11" s="37"/>
-      <c r="V11" s="37"/>
-      <c r="W11" s="37"/>
-      <c r="X11" s="37"/>
-      <c r="Y11" s="37"/>
-      <c r="Z11" s="37"/>
-      <c r="AA11" s="37"/>
-      <c r="AB11" s="37"/>
-      <c r="AC11" s="37"/>
-      <c r="AD11" s="37"/>
-      <c r="AE11" s="37"/>
-      <c r="AF11" s="37"/>
-      <c r="AG11" s="37"/>
-      <c r="AH11" s="37"/>
-      <c r="AI11" s="37"/>
-      <c r="AJ11" s="37"/>
-      <c r="AK11" s="37"/>
-      <c r="AL11" s="37"/>
-      <c r="AM11" s="37"/>
-      <c r="AN11" s="37"/>
-      <c r="AO11" s="37"/>
-      <c r="AP11" s="34"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="37"/>
+      <c r="H11" s="37"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="37"/>
+      <c r="K11" s="37"/>
+      <c r="L11" s="34"/>
+      <c r="M11" s="34"/>
+      <c r="N11" s="34"/>
+      <c r="O11" s="34"/>
+      <c r="P11" s="34"/>
+      <c r="Q11" s="34"/>
+      <c r="R11" s="34"/>
+      <c r="S11" s="34"/>
+      <c r="T11" s="34"/>
+      <c r="U11" s="34"/>
+      <c r="V11" s="34"/>
+      <c r="W11" s="34"/>
+      <c r="X11" s="34"/>
+      <c r="Y11" s="34"/>
+      <c r="Z11" s="34"/>
+      <c r="AA11" s="34"/>
+      <c r="AB11" s="34"/>
+      <c r="AC11" s="34"/>
+      <c r="AD11" s="34"/>
+      <c r="AE11" s="34"/>
+      <c r="AF11" s="34"/>
+      <c r="AG11" s="34"/>
+      <c r="AH11" s="34"/>
+      <c r="AI11" s="34"/>
+      <c r="AJ11" s="34"/>
+      <c r="AK11" s="34"/>
+      <c r="AL11" s="34"/>
+      <c r="AM11" s="34"/>
+      <c r="AN11" s="34"/>
+      <c r="AO11" s="34"/>
+      <c r="AP11" s="35"/>
     </row>
     <row r="12" spans="1:42">
-      <c r="A12" s="36"/>
+      <c r="A12" s="37"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="36"/>
-      <c r="J12" s="36"/>
-      <c r="K12" s="36"/>
-      <c r="L12" s="37"/>
-      <c r="M12" s="37"/>
-      <c r="N12" s="37"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="37"/>
-      <c r="Q12" s="37"/>
-      <c r="R12" s="37"/>
-      <c r="S12" s="37"/>
-      <c r="T12" s="37"/>
-      <c r="U12" s="37"/>
-      <c r="V12" s="37"/>
-      <c r="W12" s="37"/>
-      <c r="X12" s="37"/>
-      <c r="Y12" s="37"/>
-      <c r="Z12" s="37"/>
-      <c r="AA12" s="37"/>
-      <c r="AB12" s="37"/>
-      <c r="AC12" s="37"/>
-      <c r="AD12" s="37"/>
-      <c r="AE12" s="37"/>
-      <c r="AF12" s="37"/>
-      <c r="AG12" s="37"/>
-      <c r="AH12" s="37"/>
-      <c r="AI12" s="37"/>
-      <c r="AJ12" s="37"/>
-      <c r="AK12" s="37"/>
-      <c r="AL12" s="37"/>
-      <c r="AM12" s="37"/>
-      <c r="AN12" s="37"/>
-      <c r="AO12" s="37"/>
-      <c r="AP12" s="34"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="37"/>
+      <c r="G12" s="37"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="37"/>
+      <c r="K12" s="37"/>
+      <c r="L12" s="34"/>
+      <c r="M12" s="34"/>
+      <c r="N12" s="34"/>
+      <c r="O12" s="34"/>
+      <c r="P12" s="34"/>
+      <c r="Q12" s="34"/>
+      <c r="R12" s="34"/>
+      <c r="S12" s="34"/>
+      <c r="T12" s="34"/>
+      <c r="U12" s="34"/>
+      <c r="V12" s="34"/>
+      <c r="W12" s="34"/>
+      <c r="X12" s="34"/>
+      <c r="Y12" s="34"/>
+      <c r="Z12" s="34"/>
+      <c r="AA12" s="34"/>
+      <c r="AB12" s="34"/>
+      <c r="AC12" s="34"/>
+      <c r="AD12" s="34"/>
+      <c r="AE12" s="34"/>
+      <c r="AF12" s="34"/>
+      <c r="AG12" s="34"/>
+      <c r="AH12" s="34"/>
+      <c r="AI12" s="34"/>
+      <c r="AJ12" s="34"/>
+      <c r="AK12" s="34"/>
+      <c r="AL12" s="34"/>
+      <c r="AM12" s="34"/>
+      <c r="AN12" s="34"/>
+      <c r="AO12" s="34"/>
+      <c r="AP12" s="35"/>
     </row>
     <row r="13" spans="1:42">
-      <c r="A13" s="36"/>
+      <c r="A13" s="37"/>
       <c r="B13" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="36"/>
-      <c r="J13" s="36"/>
-      <c r="K13" s="36"/>
-      <c r="L13" s="37"/>
-      <c r="M13" s="37"/>
-      <c r="N13" s="37"/>
-      <c r="O13" s="37"/>
-      <c r="P13" s="37"/>
-      <c r="Q13" s="37"/>
-      <c r="R13" s="37"/>
-      <c r="S13" s="37"/>
-      <c r="T13" s="37"/>
-      <c r="U13" s="37"/>
-      <c r="V13" s="37"/>
-      <c r="W13" s="37"/>
-      <c r="X13" s="37"/>
-      <c r="Y13" s="37"/>
-      <c r="Z13" s="37"/>
-      <c r="AA13" s="37"/>
-      <c r="AB13" s="37"/>
-      <c r="AC13" s="37"/>
-      <c r="AD13" s="37"/>
-      <c r="AE13" s="37"/>
-      <c r="AF13" s="37"/>
-      <c r="AG13" s="37"/>
-      <c r="AH13" s="37"/>
-      <c r="AI13" s="37"/>
-      <c r="AJ13" s="37"/>
-      <c r="AK13" s="37"/>
-      <c r="AL13" s="37"/>
-      <c r="AM13" s="37"/>
-      <c r="AN13" s="37"/>
-      <c r="AO13" s="37"/>
-      <c r="AP13" s="34"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="37"/>
+      <c r="G13" s="37"/>
+      <c r="H13" s="37"/>
+      <c r="I13" s="37"/>
+      <c r="J13" s="37"/>
+      <c r="K13" s="37"/>
+      <c r="L13" s="34"/>
+      <c r="M13" s="34"/>
+      <c r="N13" s="34"/>
+      <c r="O13" s="34"/>
+      <c r="P13" s="34"/>
+      <c r="Q13" s="34"/>
+      <c r="R13" s="34"/>
+      <c r="S13" s="34"/>
+      <c r="T13" s="34"/>
+      <c r="U13" s="34"/>
+      <c r="V13" s="34"/>
+      <c r="W13" s="34"/>
+      <c r="X13" s="34"/>
+      <c r="Y13" s="34"/>
+      <c r="Z13" s="34"/>
+      <c r="AA13" s="34"/>
+      <c r="AB13" s="34"/>
+      <c r="AC13" s="34"/>
+      <c r="AD13" s="34"/>
+      <c r="AE13" s="34"/>
+      <c r="AF13" s="34"/>
+      <c r="AG13" s="34"/>
+      <c r="AH13" s="34"/>
+      <c r="AI13" s="34"/>
+      <c r="AJ13" s="34"/>
+      <c r="AK13" s="34"/>
+      <c r="AL13" s="34"/>
+      <c r="AM13" s="34"/>
+      <c r="AN13" s="34"/>
+      <c r="AO13" s="34"/>
+      <c r="AP13" s="35"/>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" s="2">
@@ -5502,6 +5566,33 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="AO11:AO13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
+    <mergeCell ref="AN11:AN13"/>
+    <mergeCell ref="AE11:AE13"/>
+    <mergeCell ref="AF11:AF13"/>
+    <mergeCell ref="AG11:AG13"/>
+    <mergeCell ref="AH11:AH13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="Z11:Z13"/>
+    <mergeCell ref="AA11:AA13"/>
+    <mergeCell ref="AB11:AB13"/>
+    <mergeCell ref="AC11:AC13"/>
+    <mergeCell ref="AD11:AD13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="V11:V13"/>
+    <mergeCell ref="W11:W13"/>
+    <mergeCell ref="X11:X13"/>
+    <mergeCell ref="Y11:Y13"/>
+    <mergeCell ref="P11:P13"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="T11:T13"/>
     <mergeCell ref="A1:AP1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A11:A13"/>
@@ -5518,33 +5609,6 @@
     <mergeCell ref="M11:M13"/>
     <mergeCell ref="N11:N13"/>
     <mergeCell ref="O11:O13"/>
-    <mergeCell ref="P11:P13"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="T11:T13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="V11:V13"/>
-    <mergeCell ref="W11:W13"/>
-    <mergeCell ref="X11:X13"/>
-    <mergeCell ref="Y11:Y13"/>
-    <mergeCell ref="Z11:Z13"/>
-    <mergeCell ref="AA11:AA13"/>
-    <mergeCell ref="AB11:AB13"/>
-    <mergeCell ref="AC11:AC13"/>
-    <mergeCell ref="AD11:AD13"/>
-    <mergeCell ref="AE11:AE13"/>
-    <mergeCell ref="AF11:AF13"/>
-    <mergeCell ref="AG11:AG13"/>
-    <mergeCell ref="AH11:AH13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="AO11:AO13"/>
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="AN11:AN13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ТКИ-341_Реверс_Инжиниринг.xlsx
+++ b/ТКИ-341_Реверс_Инжиниринг.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\Reverse_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A11380D-C8C9-42AB-88CF-934ABF9B0EC6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3439937F-6D27-4126-81B8-AA5BD1BA10DF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -452,10 +452,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -738,7 +738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AX39"/>
+  <dimension ref="A1:AX42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="37.28515625" customWidth="1"/>
@@ -761,61 +761,62 @@
     <col min="28" max="28" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="14.45" customHeight="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
+      <c r="B1" s="34"/>
       <c r="C1" s="36"/>
       <c r="D1" s="36"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="35"/>
-      <c r="AA1" s="35"/>
-      <c r="AB1" s="35"/>
-      <c r="AC1" s="35"/>
-      <c r="AD1" s="35"/>
-      <c r="AE1" s="35"/>
-      <c r="AF1" s="35"/>
-      <c r="AG1" s="35"/>
-      <c r="AH1" s="35"/>
-      <c r="AI1" s="35"/>
-      <c r="AJ1" s="35"/>
-      <c r="AK1" s="35"/>
-      <c r="AL1" s="35"/>
-      <c r="AM1" s="35"/>
-      <c r="AN1" s="35"/>
-      <c r="AO1" s="35"/>
-      <c r="AP1" s="35"/>
-      <c r="AQ1" s="35"/>
-      <c r="AR1" s="35"/>
-      <c r="AS1" s="35"/>
-      <c r="AT1" s="35"/>
-      <c r="AU1" s="35"/>
-      <c r="AV1" s="35"/>
-      <c r="AW1" s="35"/>
-      <c r="AX1" s="35"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="34"/>
+      <c r="AA1" s="34"/>
+      <c r="AB1" s="34"/>
+      <c r="AC1" s="34"/>
+      <c r="AD1" s="34"/>
+      <c r="AE1" s="34"/>
+      <c r="AF1" s="34"/>
+      <c r="AG1" s="34"/>
+      <c r="AH1" s="34"/>
+      <c r="AI1" s="34"/>
+      <c r="AJ1" s="34"/>
+      <c r="AK1" s="34"/>
+      <c r="AL1" s="34"/>
+      <c r="AM1" s="34"/>
+      <c r="AN1" s="34"/>
+      <c r="AO1" s="34"/>
+      <c r="AP1" s="34"/>
+      <c r="AQ1" s="34"/>
+      <c r="AR1" s="34"/>
+      <c r="AS1" s="34"/>
+      <c r="AT1" s="34"/>
+      <c r="AU1" s="34"/>
+      <c r="AV1" s="34"/>
+      <c r="AW1" s="34"/>
+      <c r="AX1" s="34"/>
     </row>
     <row r="2" spans="1:50" ht="27.6" customHeight="1">
       <c r="A2" s="37" t="s">
@@ -1023,7 +1024,7 @@
         <v>7</v>
       </c>
       <c r="M4" s="31" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="N4" s="3"/>
       <c r="O4" s="30"/>
@@ -1425,7 +1426,7 @@
         <v>24</v>
       </c>
       <c r="M9" s="31" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="N9" s="3"/>
       <c r="O9" s="30"/>
@@ -1609,23 +1610,23 @@
       <c r="AE11" s="12"/>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
-      <c r="AH11" s="34"/>
-      <c r="AI11" s="34"/>
-      <c r="AJ11" s="34"/>
-      <c r="AK11" s="34"/>
-      <c r="AL11" s="34"/>
-      <c r="AM11" s="34"/>
-      <c r="AN11" s="34"/>
-      <c r="AO11" s="34"/>
-      <c r="AP11" s="34"/>
-      <c r="AQ11" s="34"/>
-      <c r="AR11" s="34"/>
-      <c r="AS11" s="34"/>
-      <c r="AT11" s="34"/>
-      <c r="AU11" s="34"/>
-      <c r="AV11" s="34"/>
-      <c r="AW11" s="34"/>
-      <c r="AX11" s="35"/>
+      <c r="AH11" s="35"/>
+      <c r="AI11" s="35"/>
+      <c r="AJ11" s="35"/>
+      <c r="AK11" s="35"/>
+      <c r="AL11" s="35"/>
+      <c r="AM11" s="35"/>
+      <c r="AN11" s="35"/>
+      <c r="AO11" s="35"/>
+      <c r="AP11" s="35"/>
+      <c r="AQ11" s="35"/>
+      <c r="AR11" s="35"/>
+      <c r="AS11" s="35"/>
+      <c r="AT11" s="35"/>
+      <c r="AU11" s="35"/>
+      <c r="AV11" s="35"/>
+      <c r="AW11" s="35"/>
+      <c r="AX11" s="34"/>
     </row>
     <row r="12" spans="1:50">
       <c r="A12" s="2">
@@ -1689,25 +1690,27 @@
         <v>46100</v>
       </c>
       <c r="AE12" s="12"/>
-      <c r="AF12" s="12"/>
+      <c r="AF12" s="32">
+        <v>46107</v>
+      </c>
       <c r="AG12" s="12"/>
-      <c r="AH12" s="34"/>
-      <c r="AI12" s="34"/>
-      <c r="AJ12" s="34"/>
-      <c r="AK12" s="34"/>
-      <c r="AL12" s="34"/>
-      <c r="AM12" s="34"/>
-      <c r="AN12" s="34"/>
-      <c r="AO12" s="34"/>
-      <c r="AP12" s="34"/>
-      <c r="AQ12" s="34"/>
-      <c r="AR12" s="34"/>
-      <c r="AS12" s="34"/>
-      <c r="AT12" s="34"/>
-      <c r="AU12" s="34"/>
-      <c r="AV12" s="34"/>
-      <c r="AW12" s="34"/>
-      <c r="AX12" s="35"/>
+      <c r="AH12" s="35"/>
+      <c r="AI12" s="35"/>
+      <c r="AJ12" s="35"/>
+      <c r="AK12" s="35"/>
+      <c r="AL12" s="35"/>
+      <c r="AM12" s="35"/>
+      <c r="AN12" s="35"/>
+      <c r="AO12" s="35"/>
+      <c r="AP12" s="35"/>
+      <c r="AQ12" s="35"/>
+      <c r="AR12" s="35"/>
+      <c r="AS12" s="35"/>
+      <c r="AT12" s="35"/>
+      <c r="AU12" s="35"/>
+      <c r="AV12" s="35"/>
+      <c r="AW12" s="35"/>
+      <c r="AX12" s="34"/>
     </row>
     <row r="13" spans="1:50">
       <c r="A13" s="2">
@@ -1773,23 +1776,23 @@
       <c r="AE13" s="12"/>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
-      <c r="AH13" s="34"/>
-      <c r="AI13" s="34"/>
-      <c r="AJ13" s="34"/>
-      <c r="AK13" s="34"/>
-      <c r="AL13" s="34"/>
-      <c r="AM13" s="34"/>
-      <c r="AN13" s="34"/>
-      <c r="AO13" s="34"/>
-      <c r="AP13" s="34"/>
-      <c r="AQ13" s="34"/>
-      <c r="AR13" s="34"/>
-      <c r="AS13" s="34"/>
-      <c r="AT13" s="34"/>
-      <c r="AU13" s="34"/>
-      <c r="AV13" s="34"/>
-      <c r="AW13" s="34"/>
-      <c r="AX13" s="35"/>
+      <c r="AH13" s="35"/>
+      <c r="AI13" s="35"/>
+      <c r="AJ13" s="35"/>
+      <c r="AK13" s="35"/>
+      <c r="AL13" s="35"/>
+      <c r="AM13" s="35"/>
+      <c r="AN13" s="35"/>
+      <c r="AO13" s="35"/>
+      <c r="AP13" s="35"/>
+      <c r="AQ13" s="35"/>
+      <c r="AR13" s="35"/>
+      <c r="AS13" s="35"/>
+      <c r="AT13" s="35"/>
+      <c r="AU13" s="35"/>
+      <c r="AV13" s="35"/>
+      <c r="AW13" s="35"/>
+      <c r="AX13" s="34"/>
     </row>
     <row r="14" spans="1:50">
       <c r="A14" s="2">
@@ -2013,7 +2016,9 @@
         <v>46104</v>
       </c>
       <c r="AG16" s="3"/>
-      <c r="AH16" s="3"/>
+      <c r="AH16" s="32">
+        <v>46107</v>
+      </c>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
@@ -2151,7 +2156,7 @@
         <v>7</v>
       </c>
       <c r="M18" s="31" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="N18" s="3"/>
       <c r="O18" s="30"/>
@@ -2469,7 +2474,7 @@
         <v>7</v>
       </c>
       <c r="M22" s="31" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="N22" s="3"/>
       <c r="O22" s="30"/>
@@ -2493,7 +2498,9 @@
         <v>46100</v>
       </c>
       <c r="AE22" s="3"/>
-      <c r="AF22" s="3"/>
+      <c r="AF22" s="32">
+        <v>46107</v>
+      </c>
       <c r="AG22" s="3"/>
       <c r="AH22" s="3"/>
       <c r="AI22" s="3"/>
@@ -2575,7 +2582,9 @@
         <v>46100</v>
       </c>
       <c r="AE23" s="3"/>
-      <c r="AF23" s="3"/>
+      <c r="AF23" s="32">
+        <v>46107</v>
+      </c>
       <c r="AG23" s="3"/>
       <c r="AH23" s="3"/>
       <c r="AI23" s="3"/>
@@ -2633,7 +2642,7 @@
         <v>24</v>
       </c>
       <c r="M24" s="31" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="N24" s="3"/>
       <c r="O24" s="30"/>
@@ -2709,7 +2718,7 @@
         <v>24</v>
       </c>
       <c r="M25" s="31" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="N25" s="3"/>
       <c r="O25" s="30"/>
@@ -2733,7 +2742,9 @@
         <v>46100</v>
       </c>
       <c r="AE25" s="3"/>
-      <c r="AF25" s="3"/>
+      <c r="AF25" s="32">
+        <v>46107</v>
+      </c>
       <c r="AG25" s="3"/>
       <c r="AH25" s="3"/>
       <c r="AI25" s="3"/>
@@ -2949,7 +2960,7 @@
         <v>7</v>
       </c>
       <c r="M28" s="31" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="30"/>
@@ -3137,7 +3148,9 @@
         <v>46104</v>
       </c>
       <c r="AG30" s="3"/>
-      <c r="AH30" s="3"/>
+      <c r="AH30" s="32">
+        <v>46107</v>
+      </c>
       <c r="AI30" s="3"/>
       <c r="AJ30" s="3"/>
       <c r="AK30" s="3"/>
@@ -3765,14 +3778,9 @@
         <v>70</v>
       </c>
     </row>
+    <row r="42" spans="1:50" ht="9.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="AX11:AX13"/>
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AQ11:AQ13"/>
-    <mergeCell ref="AR11:AR13"/>
-    <mergeCell ref="AS11:AS13"/>
-    <mergeCell ref="AT11:AT13"/>
     <mergeCell ref="A1:AX1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="AH11:AH13"/>
@@ -3786,6 +3794,12 @@
     <mergeCell ref="AU11:AU13"/>
     <mergeCell ref="AV11:AV13"/>
     <mergeCell ref="AW11:AW13"/>
+    <mergeCell ref="AX11:AX13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AQ11:AQ13"/>
+    <mergeCell ref="AR11:AR13"/>
+    <mergeCell ref="AS11:AS13"/>
+    <mergeCell ref="AT11:AT13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3797,50 +3811,50 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="35"/>
-      <c r="AA1" s="35"/>
-      <c r="AB1" s="35"/>
-      <c r="AC1" s="35"/>
-      <c r="AD1" s="35"/>
-      <c r="AE1" s="35"/>
-      <c r="AF1" s="35"/>
-      <c r="AG1" s="35"/>
-      <c r="AH1" s="35"/>
-      <c r="AI1" s="35"/>
-      <c r="AJ1" s="35"/>
-      <c r="AK1" s="35"/>
-      <c r="AL1" s="35"/>
-      <c r="AM1" s="35"/>
-      <c r="AN1" s="35"/>
-      <c r="AO1" s="35"/>
-      <c r="AP1" s="35"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="34"/>
+      <c r="AA1" s="34"/>
+      <c r="AB1" s="34"/>
+      <c r="AC1" s="34"/>
+      <c r="AD1" s="34"/>
+      <c r="AE1" s="34"/>
+      <c r="AF1" s="34"/>
+      <c r="AG1" s="34"/>
+      <c r="AH1" s="34"/>
+      <c r="AI1" s="34"/>
+      <c r="AJ1" s="34"/>
+      <c r="AK1" s="34"/>
+      <c r="AL1" s="34"/>
+      <c r="AM1" s="34"/>
+      <c r="AN1" s="34"/>
+      <c r="AO1" s="34"/>
+      <c r="AP1" s="34"/>
     </row>
     <row r="2" spans="1:42" ht="30">
       <c r="A2" s="37" t="s">
@@ -4290,37 +4304,37 @@
       <c r="I11" s="37"/>
       <c r="J11" s="37"/>
       <c r="K11" s="37"/>
-      <c r="L11" s="34"/>
-      <c r="M11" s="34"/>
-      <c r="N11" s="34"/>
-      <c r="O11" s="34"/>
-      <c r="P11" s="34"/>
-      <c r="Q11" s="34"/>
-      <c r="R11" s="34"/>
-      <c r="S11" s="34"/>
-      <c r="T11" s="34"/>
-      <c r="U11" s="34"/>
-      <c r="V11" s="34"/>
-      <c r="W11" s="34"/>
-      <c r="X11" s="34"/>
-      <c r="Y11" s="34"/>
-      <c r="Z11" s="34"/>
-      <c r="AA11" s="34"/>
-      <c r="AB11" s="34"/>
-      <c r="AC11" s="34"/>
-      <c r="AD11" s="34"/>
-      <c r="AE11" s="34"/>
-      <c r="AF11" s="34"/>
-      <c r="AG11" s="34"/>
-      <c r="AH11" s="34"/>
-      <c r="AI11" s="34"/>
-      <c r="AJ11" s="34"/>
-      <c r="AK11" s="34"/>
-      <c r="AL11" s="34"/>
-      <c r="AM11" s="34"/>
-      <c r="AN11" s="34"/>
-      <c r="AO11" s="34"/>
-      <c r="AP11" s="35"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="35"/>
+      <c r="N11" s="35"/>
+      <c r="O11" s="35"/>
+      <c r="P11" s="35"/>
+      <c r="Q11" s="35"/>
+      <c r="R11" s="35"/>
+      <c r="S11" s="35"/>
+      <c r="T11" s="35"/>
+      <c r="U11" s="35"/>
+      <c r="V11" s="35"/>
+      <c r="W11" s="35"/>
+      <c r="X11" s="35"/>
+      <c r="Y11" s="35"/>
+      <c r="Z11" s="35"/>
+      <c r="AA11" s="35"/>
+      <c r="AB11" s="35"/>
+      <c r="AC11" s="35"/>
+      <c r="AD11" s="35"/>
+      <c r="AE11" s="35"/>
+      <c r="AF11" s="35"/>
+      <c r="AG11" s="35"/>
+      <c r="AH11" s="35"/>
+      <c r="AI11" s="35"/>
+      <c r="AJ11" s="35"/>
+      <c r="AK11" s="35"/>
+      <c r="AL11" s="35"/>
+      <c r="AM11" s="35"/>
+      <c r="AN11" s="35"/>
+      <c r="AO11" s="35"/>
+      <c r="AP11" s="34"/>
     </row>
     <row r="12" spans="1:42">
       <c r="A12" s="37"/>
@@ -4334,37 +4348,37 @@
       <c r="I12" s="37"/>
       <c r="J12" s="37"/>
       <c r="K12" s="37"/>
-      <c r="L12" s="34"/>
-      <c r="M12" s="34"/>
-      <c r="N12" s="34"/>
-      <c r="O12" s="34"/>
-      <c r="P12" s="34"/>
-      <c r="Q12" s="34"/>
-      <c r="R12" s="34"/>
-      <c r="S12" s="34"/>
-      <c r="T12" s="34"/>
-      <c r="U12" s="34"/>
-      <c r="V12" s="34"/>
-      <c r="W12" s="34"/>
-      <c r="X12" s="34"/>
-      <c r="Y12" s="34"/>
-      <c r="Z12" s="34"/>
-      <c r="AA12" s="34"/>
-      <c r="AB12" s="34"/>
-      <c r="AC12" s="34"/>
-      <c r="AD12" s="34"/>
-      <c r="AE12" s="34"/>
-      <c r="AF12" s="34"/>
-      <c r="AG12" s="34"/>
-      <c r="AH12" s="34"/>
-      <c r="AI12" s="34"/>
-      <c r="AJ12" s="34"/>
-      <c r="AK12" s="34"/>
-      <c r="AL12" s="34"/>
-      <c r="AM12" s="34"/>
-      <c r="AN12" s="34"/>
-      <c r="AO12" s="34"/>
-      <c r="AP12" s="35"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="35"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="35"/>
+      <c r="P12" s="35"/>
+      <c r="Q12" s="35"/>
+      <c r="R12" s="35"/>
+      <c r="S12" s="35"/>
+      <c r="T12" s="35"/>
+      <c r="U12" s="35"/>
+      <c r="V12" s="35"/>
+      <c r="W12" s="35"/>
+      <c r="X12" s="35"/>
+      <c r="Y12" s="35"/>
+      <c r="Z12" s="35"/>
+      <c r="AA12" s="35"/>
+      <c r="AB12" s="35"/>
+      <c r="AC12" s="35"/>
+      <c r="AD12" s="35"/>
+      <c r="AE12" s="35"/>
+      <c r="AF12" s="35"/>
+      <c r="AG12" s="35"/>
+      <c r="AH12" s="35"/>
+      <c r="AI12" s="35"/>
+      <c r="AJ12" s="35"/>
+      <c r="AK12" s="35"/>
+      <c r="AL12" s="35"/>
+      <c r="AM12" s="35"/>
+      <c r="AN12" s="35"/>
+      <c r="AO12" s="35"/>
+      <c r="AP12" s="34"/>
     </row>
     <row r="13" spans="1:42">
       <c r="A13" s="37"/>
@@ -4380,37 +4394,37 @@
       <c r="I13" s="37"/>
       <c r="J13" s="37"/>
       <c r="K13" s="37"/>
-      <c r="L13" s="34"/>
-      <c r="M13" s="34"/>
-      <c r="N13" s="34"/>
-      <c r="O13" s="34"/>
-      <c r="P13" s="34"/>
-      <c r="Q13" s="34"/>
-      <c r="R13" s="34"/>
-      <c r="S13" s="34"/>
-      <c r="T13" s="34"/>
-      <c r="U13" s="34"/>
-      <c r="V13" s="34"/>
-      <c r="W13" s="34"/>
-      <c r="X13" s="34"/>
-      <c r="Y13" s="34"/>
-      <c r="Z13" s="34"/>
-      <c r="AA13" s="34"/>
-      <c r="AB13" s="34"/>
-      <c r="AC13" s="34"/>
-      <c r="AD13" s="34"/>
-      <c r="AE13" s="34"/>
-      <c r="AF13" s="34"/>
-      <c r="AG13" s="34"/>
-      <c r="AH13" s="34"/>
-      <c r="AI13" s="34"/>
-      <c r="AJ13" s="34"/>
-      <c r="AK13" s="34"/>
-      <c r="AL13" s="34"/>
-      <c r="AM13" s="34"/>
-      <c r="AN13" s="34"/>
-      <c r="AO13" s="34"/>
-      <c r="AP13" s="35"/>
+      <c r="L13" s="35"/>
+      <c r="M13" s="35"/>
+      <c r="N13" s="35"/>
+      <c r="O13" s="35"/>
+      <c r="P13" s="35"/>
+      <c r="Q13" s="35"/>
+      <c r="R13" s="35"/>
+      <c r="S13" s="35"/>
+      <c r="T13" s="35"/>
+      <c r="U13" s="35"/>
+      <c r="V13" s="35"/>
+      <c r="W13" s="35"/>
+      <c r="X13" s="35"/>
+      <c r="Y13" s="35"/>
+      <c r="Z13" s="35"/>
+      <c r="AA13" s="35"/>
+      <c r="AB13" s="35"/>
+      <c r="AC13" s="35"/>
+      <c r="AD13" s="35"/>
+      <c r="AE13" s="35"/>
+      <c r="AF13" s="35"/>
+      <c r="AG13" s="35"/>
+      <c r="AH13" s="35"/>
+      <c r="AI13" s="35"/>
+      <c r="AJ13" s="35"/>
+      <c r="AK13" s="35"/>
+      <c r="AL13" s="35"/>
+      <c r="AM13" s="35"/>
+      <c r="AN13" s="35"/>
+      <c r="AO13" s="35"/>
+      <c r="AP13" s="34"/>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" s="2">
@@ -5566,33 +5580,6 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="AO11:AO13"/>
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="AN11:AN13"/>
-    <mergeCell ref="AE11:AE13"/>
-    <mergeCell ref="AF11:AF13"/>
-    <mergeCell ref="AG11:AG13"/>
-    <mergeCell ref="AH11:AH13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="Z11:Z13"/>
-    <mergeCell ref="AA11:AA13"/>
-    <mergeCell ref="AB11:AB13"/>
-    <mergeCell ref="AC11:AC13"/>
-    <mergeCell ref="AD11:AD13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="V11:V13"/>
-    <mergeCell ref="W11:W13"/>
-    <mergeCell ref="X11:X13"/>
-    <mergeCell ref="Y11:Y13"/>
-    <mergeCell ref="P11:P13"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="T11:T13"/>
     <mergeCell ref="A1:AP1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A11:A13"/>
@@ -5609,6 +5596,33 @@
     <mergeCell ref="M11:M13"/>
     <mergeCell ref="N11:N13"/>
     <mergeCell ref="O11:O13"/>
+    <mergeCell ref="P11:P13"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="T11:T13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="V11:V13"/>
+    <mergeCell ref="W11:W13"/>
+    <mergeCell ref="X11:X13"/>
+    <mergeCell ref="Y11:Y13"/>
+    <mergeCell ref="Z11:Z13"/>
+    <mergeCell ref="AA11:AA13"/>
+    <mergeCell ref="AB11:AB13"/>
+    <mergeCell ref="AC11:AC13"/>
+    <mergeCell ref="AD11:AD13"/>
+    <mergeCell ref="AE11:AE13"/>
+    <mergeCell ref="AF11:AF13"/>
+    <mergeCell ref="AG11:AG13"/>
+    <mergeCell ref="AH11:AH13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="AO11:AO13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
+    <mergeCell ref="AN11:AN13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ТКИ-341_Реверс_Инжиниринг.xlsx
+++ b/ТКИ-341_Реверс_Инжиниринг.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\Reverse_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3439937F-6D27-4126-81B8-AA5BD1BA10DF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C4525E-2219-43AC-90A3-9E1A15F095D1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="74">
   <si>
     <t>ВЕДОМОСТЬ ПОСЕЩАЕМОСТИ ЗАНЯТИЙ СТУДЕНТАМИ ГРУППЫ ТКИ "Компьютерная безопасность" ИТТСУ РУТ (МИИТ)</t>
   </si>
@@ -270,6 +270,9 @@
   </si>
   <si>
     <t>кусочно-линейная функция</t>
+  </si>
+  <si>
+    <t>Горковец Анна Сергеевна</t>
   </si>
 </sst>
 </file>
@@ -360,7 +363,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -386,7 +389,6 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -452,16 +454,25 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -765,58 +776,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="14.45" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
+      <c r="B1" s="35"/>
       <c r="C1" s="36"/>
       <c r="D1" s="36"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
-      <c r="T1" s="34"/>
-      <c r="U1" s="34"/>
-      <c r="V1" s="34"/>
-      <c r="W1" s="34"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="34"/>
-      <c r="Z1" s="34"/>
-      <c r="AA1" s="34"/>
-      <c r="AB1" s="34"/>
-      <c r="AC1" s="34"/>
-      <c r="AD1" s="34"/>
-      <c r="AE1" s="34"/>
-      <c r="AF1" s="34"/>
-      <c r="AG1" s="34"/>
-      <c r="AH1" s="34"/>
-      <c r="AI1" s="34"/>
-      <c r="AJ1" s="34"/>
-      <c r="AK1" s="34"/>
-      <c r="AL1" s="34"/>
-      <c r="AM1" s="34"/>
-      <c r="AN1" s="34"/>
-      <c r="AO1" s="34"/>
-      <c r="AP1" s="34"/>
-      <c r="AQ1" s="34"/>
-      <c r="AR1" s="34"/>
-      <c r="AS1" s="34"/>
-      <c r="AT1" s="34"/>
-      <c r="AU1" s="34"/>
-      <c r="AV1" s="34"/>
-      <c r="AW1" s="34"/>
-      <c r="AX1" s="34"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="35"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="35"/>
+      <c r="AA1" s="35"/>
+      <c r="AB1" s="35"/>
+      <c r="AC1" s="35"/>
+      <c r="AD1" s="35"/>
+      <c r="AE1" s="35"/>
+      <c r="AF1" s="35"/>
+      <c r="AG1" s="35"/>
+      <c r="AH1" s="35"/>
+      <c r="AI1" s="35"/>
+      <c r="AJ1" s="35"/>
+      <c r="AK1" s="35"/>
+      <c r="AL1" s="35"/>
+      <c r="AM1" s="35"/>
+      <c r="AN1" s="35"/>
+      <c r="AO1" s="35"/>
+      <c r="AP1" s="35"/>
+      <c r="AQ1" s="35"/>
+      <c r="AR1" s="35"/>
+      <c r="AS1" s="35"/>
+      <c r="AT1" s="35"/>
+      <c r="AU1" s="35"/>
+      <c r="AV1" s="35"/>
+      <c r="AW1" s="35"/>
+      <c r="AX1" s="35"/>
     </row>
     <row r="2" spans="1:50" ht="27.6" customHeight="1">
       <c r="A2" s="37" t="s">
@@ -841,55 +852,55 @@
       <c r="H2" s="10">
         <v>46079</v>
       </c>
-      <c r="I2" s="18">
+      <c r="I2" s="17">
         <v>46086</v>
       </c>
-      <c r="J2" s="18">
+      <c r="J2" s="17">
         <v>46093</v>
       </c>
-      <c r="K2" s="18">
+      <c r="K2" s="17">
         <v>46100</v>
       </c>
-      <c r="L2" s="18">
+      <c r="L2" s="17">
         <v>46104</v>
       </c>
-      <c r="M2" s="18">
+      <c r="M2" s="17">
         <v>46107</v>
       </c>
-      <c r="N2" s="18">
+      <c r="N2" s="17">
         <v>46114</v>
       </c>
-      <c r="O2" s="18">
+      <c r="O2" s="17">
         <v>46117</v>
       </c>
-      <c r="P2" s="18">
+      <c r="P2" s="17">
         <v>46121</v>
       </c>
-      <c r="Q2" s="18">
+      <c r="Q2" s="17">
         <v>46128</v>
       </c>
-      <c r="R2" s="18"/>
-      <c r="S2" s="18">
+      <c r="R2" s="17"/>
+      <c r="S2" s="17">
         <v>46135</v>
       </c>
-      <c r="T2" s="18">
+      <c r="T2" s="17">
         <v>46142</v>
       </c>
-      <c r="U2" s="18"/>
-      <c r="V2" s="18">
+      <c r="U2" s="17"/>
+      <c r="V2" s="17">
         <v>46149</v>
       </c>
-      <c r="W2" s="18">
+      <c r="W2" s="17">
         <v>46156</v>
       </c>
-      <c r="X2" s="18"/>
-      <c r="Y2" s="18">
+      <c r="X2" s="17"/>
+      <c r="Y2" s="17">
         <v>46163</v>
       </c>
-      <c r="Z2" s="18">
+      <c r="Z2" s="17">
         <v>46170</v>
       </c>
-      <c r="AA2" s="22"/>
+      <c r="AA2" s="21"/>
       <c r="AB2" s="3" t="s">
         <v>45</v>
       </c>
@@ -931,66 +942,66 @@
       </c>
     </row>
     <row r="3" spans="1:50">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="23"/>
-      <c r="M3" s="23"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
-      <c r="S3" s="24"/>
-      <c r="T3" s="24"/>
-      <c r="U3" s="24"/>
-      <c r="V3" s="24"/>
-      <c r="W3" s="24"/>
-      <c r="X3" s="24"/>
-      <c r="Y3" s="24"/>
-      <c r="Z3" s="24"/>
-      <c r="AA3" s="24"/>
-      <c r="AB3" s="24"/>
-      <c r="AC3" s="24"/>
-      <c r="AD3" s="24"/>
-      <c r="AE3" s="24"/>
-      <c r="AF3" s="24"/>
-      <c r="AG3" s="24"/>
-      <c r="AH3" s="24"/>
-      <c r="AI3" s="24"/>
-      <c r="AJ3" s="24"/>
-      <c r="AK3" s="24"/>
-      <c r="AL3" s="24"/>
-      <c r="AM3" s="24"/>
-      <c r="AN3" s="24"/>
-      <c r="AO3" s="24"/>
-      <c r="AP3" s="24"/>
-      <c r="AQ3" s="24"/>
-      <c r="AR3" s="24"/>
-      <c r="AS3" s="24"/>
-      <c r="AT3" s="24"/>
-      <c r="AU3" s="24"/>
-      <c r="AV3" s="24"/>
-      <c r="AW3" s="24"/>
-      <c r="AX3" s="26"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="22"/>
+      <c r="M3" s="22"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23"/>
+      <c r="T3" s="23"/>
+      <c r="U3" s="23"/>
+      <c r="V3" s="23"/>
+      <c r="W3" s="23"/>
+      <c r="X3" s="23"/>
+      <c r="Y3" s="23"/>
+      <c r="Z3" s="23"/>
+      <c r="AA3" s="23"/>
+      <c r="AB3" s="23"/>
+      <c r="AC3" s="23"/>
+      <c r="AD3" s="23"/>
+      <c r="AE3" s="23"/>
+      <c r="AF3" s="23"/>
+      <c r="AG3" s="23"/>
+      <c r="AH3" s="23"/>
+      <c r="AI3" s="23"/>
+      <c r="AJ3" s="23"/>
+      <c r="AK3" s="23"/>
+      <c r="AL3" s="23"/>
+      <c r="AM3" s="23"/>
+      <c r="AN3" s="23"/>
+      <c r="AO3" s="23"/>
+      <c r="AP3" s="23"/>
+      <c r="AQ3" s="23"/>
+      <c r="AR3" s="23"/>
+      <c r="AS3" s="23"/>
+      <c r="AT3" s="23"/>
+      <c r="AU3" s="23"/>
+      <c r="AV3" s="23"/>
+      <c r="AW3" s="23"/>
+      <c r="AX3" s="25"/>
     </row>
     <row r="4" spans="1:50">
       <c r="A4" s="2">
         <v>1</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="14" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="9">
@@ -1011,7 +1022,7 @@
       <c r="H4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="19" t="s">
+      <c r="I4" s="18" t="s">
         <v>7</v>
       </c>
       <c r="J4" s="9" t="s">
@@ -1023,24 +1034,26 @@
       <c r="L4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="31" t="s">
+      <c r="M4" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="N4" s="3"/>
-      <c r="O4" s="30"/>
+      <c r="N4" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="O4" s="29"/>
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
-      <c r="R4" s="30"/>
+      <c r="R4" s="29"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
-      <c r="U4" s="30"/>
+      <c r="U4" s="29"/>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
-      <c r="X4" s="30"/>
+      <c r="X4" s="29"/>
       <c r="Y4" s="3"/>
-      <c r="Z4" s="22"/>
-      <c r="AA4" s="22"/>
-      <c r="AB4" s="21">
+      <c r="Z4" s="21"/>
+      <c r="AA4" s="21"/>
+      <c r="AB4" s="20">
         <v>46086</v>
       </c>
       <c r="AC4" s="3"/>
@@ -1049,7 +1062,9 @@
       <c r="AF4" s="3"/>
       <c r="AG4" s="3"/>
       <c r="AH4" s="3"/>
-      <c r="AI4" s="3"/>
+      <c r="AI4" s="33">
+        <v>3</v>
+      </c>
       <c r="AJ4" s="3"/>
       <c r="AK4" s="3"/>
       <c r="AL4" s="3"/>
@@ -1088,7 +1103,7 @@
       <c r="G5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="18" t="s">
         <v>7</v>
       </c>
       <c r="I5" s="9" t="s">
@@ -1103,35 +1118,39 @@
       <c r="L5" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="M5" s="31" t="s">
+      <c r="M5" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="N5" s="3"/>
-      <c r="O5" s="30"/>
+      <c r="N5" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="O5" s="29"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
-      <c r="R5" s="30"/>
+      <c r="R5" s="29"/>
       <c r="S5" s="3"/>
       <c r="T5" s="3"/>
-      <c r="U5" s="30"/>
+      <c r="U5" s="29"/>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
-      <c r="X5" s="30"/>
+      <c r="X5" s="29"/>
       <c r="Y5" s="3"/>
-      <c r="Z5" s="22"/>
-      <c r="AA5" s="22"/>
-      <c r="AB5" s="14">
+      <c r="Z5" s="21"/>
+      <c r="AA5" s="21"/>
+      <c r="AB5" s="13">
         <v>46100</v>
       </c>
       <c r="AC5" s="3"/>
-      <c r="AD5" s="14">
+      <c r="AD5" s="13">
         <v>46100</v>
       </c>
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
       <c r="AG5" s="3"/>
       <c r="AH5" s="3"/>
-      <c r="AI5" s="3"/>
+      <c r="AI5" s="33">
+        <v>4</v>
+      </c>
       <c r="AJ5" s="3"/>
       <c r="AK5" s="3"/>
       <c r="AL5" s="3"/>
@@ -1183,24 +1202,26 @@
       <c r="L6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="M6" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="N6" s="3"/>
-      <c r="O6" s="30"/>
+      <c r="M6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N6" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="O6" s="29"/>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
-      <c r="R6" s="30"/>
+      <c r="R6" s="29"/>
       <c r="S6" s="3"/>
       <c r="T6" s="3"/>
-      <c r="U6" s="30"/>
+      <c r="U6" s="29"/>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
-      <c r="X6" s="30"/>
+      <c r="X6" s="29"/>
       <c r="Y6" s="3"/>
-      <c r="Z6" s="22"/>
-      <c r="AA6" s="22"/>
-      <c r="AB6" s="14">
+      <c r="Z6" s="21"/>
+      <c r="AA6" s="21"/>
+      <c r="AB6" s="13">
         <v>46072</v>
       </c>
       <c r="AC6" s="3"/>
@@ -1209,7 +1230,9 @@
       <c r="AF6" s="3"/>
       <c r="AG6" s="3"/>
       <c r="AH6" s="3"/>
-      <c r="AI6" s="3"/>
+      <c r="AI6" s="33">
+        <v>3</v>
+      </c>
       <c r="AJ6" s="3"/>
       <c r="AK6" s="3"/>
       <c r="AL6" s="3"/>
@@ -1248,7 +1271,7 @@
       <c r="G7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="18" t="s">
         <v>7</v>
       </c>
       <c r="I7" s="9" t="s">
@@ -1263,37 +1286,43 @@
       <c r="L7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="M7" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="N7" s="3"/>
-      <c r="O7" s="30"/>
+      <c r="M7" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N7" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="O7" s="29"/>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
-      <c r="R7" s="30"/>
+      <c r="R7" s="29"/>
       <c r="S7" s="3"/>
       <c r="T7" s="3"/>
-      <c r="U7" s="30"/>
+      <c r="U7" s="29"/>
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
-      <c r="X7" s="30"/>
+      <c r="X7" s="29"/>
       <c r="Y7" s="3"/>
-      <c r="Z7" s="22"/>
-      <c r="AA7" s="22"/>
-      <c r="AB7" s="28">
+      <c r="Z7" s="21"/>
+      <c r="AA7" s="21"/>
+      <c r="AB7" s="27">
         <v>46100</v>
       </c>
       <c r="AC7" s="3"/>
-      <c r="AD7" s="14">
+      <c r="AD7" s="13">
         <v>46100</v>
       </c>
       <c r="AE7" s="3"/>
-      <c r="AF7" s="32">
+      <c r="AF7" s="31">
         <v>46100</v>
       </c>
       <c r="AG7" s="3"/>
-      <c r="AH7" s="3"/>
-      <c r="AI7" s="3"/>
+      <c r="AH7" s="31">
+        <v>46114</v>
+      </c>
+      <c r="AI7" s="33">
+        <v>5</v>
+      </c>
       <c r="AJ7" s="3"/>
       <c r="AK7" s="3"/>
       <c r="AL7" s="3"/>
@@ -1330,10 +1359,10 @@
       <c r="G8" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="H8" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="I8" s="19" t="s">
+      <c r="I8" s="18" t="s">
         <v>7</v>
       </c>
       <c r="J8" s="9" t="s">
@@ -1345,24 +1374,26 @@
       <c r="L8" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="M8" s="31" t="s">
+      <c r="M8" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="N8" s="3"/>
-      <c r="O8" s="30"/>
+      <c r="N8" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="O8" s="29"/>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
-      <c r="R8" s="30"/>
+      <c r="R8" s="29"/>
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
-      <c r="U8" s="30"/>
+      <c r="U8" s="29"/>
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
-      <c r="X8" s="30"/>
+      <c r="X8" s="29"/>
       <c r="Y8" s="3"/>
-      <c r="Z8" s="22"/>
-      <c r="AA8" s="22"/>
-      <c r="AB8" s="14">
+      <c r="Z8" s="21"/>
+      <c r="AA8" s="21"/>
+      <c r="AB8" s="13">
         <v>46100</v>
       </c>
       <c r="AC8" s="3"/>
@@ -1371,7 +1402,9 @@
       <c r="AF8" s="3"/>
       <c r="AG8" s="3"/>
       <c r="AH8" s="3"/>
-      <c r="AI8" s="3"/>
+      <c r="AI8" s="33">
+        <v>3</v>
+      </c>
       <c r="AJ8" s="3"/>
       <c r="AK8" s="3"/>
       <c r="AL8" s="3"/>
@@ -1410,7 +1443,7 @@
       <c r="G9" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="19" t="s">
+      <c r="H9" s="18" t="s">
         <v>7</v>
       </c>
       <c r="I9" s="9" t="s">
@@ -1425,24 +1458,26 @@
       <c r="L9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="M9" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="N9" s="3"/>
-      <c r="O9" s="30"/>
+      <c r="M9" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N9" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="O9" s="29"/>
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
-      <c r="R9" s="30"/>
+      <c r="R9" s="29"/>
       <c r="S9" s="3"/>
       <c r="T9" s="3"/>
-      <c r="U9" s="30"/>
+      <c r="U9" s="29"/>
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
-      <c r="X9" s="30"/>
+      <c r="X9" s="29"/>
       <c r="Y9" s="3"/>
-      <c r="Z9" s="22"/>
-      <c r="AA9" s="22"/>
-      <c r="AB9" s="14">
+      <c r="Z9" s="21"/>
+      <c r="AA9" s="21"/>
+      <c r="AB9" s="13">
         <v>46100</v>
       </c>
       <c r="AC9" s="3"/>
@@ -1451,7 +1486,9 @@
       <c r="AF9" s="3"/>
       <c r="AG9" s="3"/>
       <c r="AH9" s="3"/>
-      <c r="AI9" s="3"/>
+      <c r="AI9" s="33">
+        <v>3</v>
+      </c>
       <c r="AJ9" s="3"/>
       <c r="AK9" s="3"/>
       <c r="AL9" s="3"/>
@@ -1472,7 +1509,7 @@
       <c r="A10" s="2">
         <v>7</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C10" s="9">
@@ -1505,24 +1542,26 @@
       <c r="L10" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="M10" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="N10" s="3"/>
-      <c r="O10" s="30"/>
+      <c r="M10" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N10" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="O10" s="29"/>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
-      <c r="R10" s="30"/>
+      <c r="R10" s="29"/>
       <c r="S10" s="3"/>
       <c r="T10" s="3"/>
-      <c r="U10" s="30"/>
+      <c r="U10" s="29"/>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
-      <c r="X10" s="30"/>
+      <c r="X10" s="29"/>
       <c r="Y10" s="3"/>
-      <c r="Z10" s="22"/>
-      <c r="AA10" s="22"/>
-      <c r="AB10" s="14">
+      <c r="Z10" s="21"/>
+      <c r="AA10" s="21"/>
+      <c r="AB10" s="13">
         <v>46079</v>
       </c>
       <c r="AC10" s="3"/>
@@ -1531,7 +1570,9 @@
       <c r="AF10" s="3"/>
       <c r="AG10" s="3"/>
       <c r="AH10" s="3"/>
-      <c r="AI10" s="3"/>
+      <c r="AI10" s="33">
+        <v>3</v>
+      </c>
       <c r="AJ10" s="3"/>
       <c r="AK10" s="3"/>
       <c r="AL10" s="3"/>
@@ -1577,62 +1618,66 @@
       <c r="J11" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K11" s="27" t="s">
+      <c r="K11" s="26" t="s">
         <v>7</v>
       </c>
       <c r="L11" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="M11" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="N11" s="12"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
-      <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="12"/>
-      <c r="W11" s="12"/>
-      <c r="X11" s="12"/>
-      <c r="Y11" s="12"/>
-      <c r="Z11" s="12"/>
-      <c r="AA11" s="12"/>
-      <c r="AB11" s="14">
+      <c r="M11" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N11" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11"/>
+      <c r="R11" s="11"/>
+      <c r="S11" s="11"/>
+      <c r="T11" s="11"/>
+      <c r="U11" s="11"/>
+      <c r="V11" s="11"/>
+      <c r="W11" s="11"/>
+      <c r="X11" s="11"/>
+      <c r="Y11" s="11"/>
+      <c r="Z11" s="11"/>
+      <c r="AA11" s="11"/>
+      <c r="AB11" s="13">
         <v>46079</v>
       </c>
-      <c r="AC11" s="12"/>
-      <c r="AD11" s="33">
+      <c r="AC11" s="11"/>
+      <c r="AD11" s="32">
         <v>46100</v>
       </c>
-      <c r="AE11" s="12"/>
-      <c r="AF11" s="12"/>
-      <c r="AG11" s="12"/>
-      <c r="AH11" s="35"/>
-      <c r="AI11" s="35"/>
-      <c r="AJ11" s="35"/>
-      <c r="AK11" s="35"/>
-      <c r="AL11" s="35"/>
-      <c r="AM11" s="35"/>
-      <c r="AN11" s="35"/>
-      <c r="AO11" s="35"/>
-      <c r="AP11" s="35"/>
-      <c r="AQ11" s="35"/>
-      <c r="AR11" s="35"/>
-      <c r="AS11" s="35"/>
-      <c r="AT11" s="35"/>
-      <c r="AU11" s="35"/>
-      <c r="AV11" s="35"/>
-      <c r="AW11" s="35"/>
-      <c r="AX11" s="34"/>
+      <c r="AE11" s="11"/>
+      <c r="AF11" s="11"/>
+      <c r="AG11" s="11"/>
+      <c r="AH11" s="38"/>
+      <c r="AI11" s="11">
+        <v>4</v>
+      </c>
+      <c r="AJ11" s="38"/>
+      <c r="AK11" s="38"/>
+      <c r="AL11" s="38"/>
+      <c r="AM11" s="38"/>
+      <c r="AN11" s="38"/>
+      <c r="AO11" s="38"/>
+      <c r="AP11" s="38"/>
+      <c r="AQ11" s="38"/>
+      <c r="AR11" s="38"/>
+      <c r="AS11" s="38"/>
+      <c r="AT11" s="38"/>
+      <c r="AU11" s="38"/>
+      <c r="AV11" s="38"/>
+      <c r="AW11" s="38"/>
+      <c r="AX11" s="35"/>
     </row>
     <row r="12" spans="1:50">
       <c r="A12" s="2">
         <v>9</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="14" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="9">
@@ -1659,64 +1704,68 @@
       <c r="J12" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K12" s="27" t="s">
+      <c r="K12" s="26" t="s">
         <v>7</v>
       </c>
       <c r="L12" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="M12" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="N12" s="12"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="12"/>
-      <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
-      <c r="V12" s="12"/>
-      <c r="W12" s="12"/>
-      <c r="X12" s="12"/>
-      <c r="Y12" s="12"/>
-      <c r="Z12" s="12"/>
-      <c r="AA12" s="12"/>
-      <c r="AB12" s="14">
+      <c r="M12" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N12" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="11"/>
+      <c r="V12" s="11"/>
+      <c r="W12" s="11"/>
+      <c r="X12" s="11"/>
+      <c r="Y12" s="11"/>
+      <c r="Z12" s="11"/>
+      <c r="AA12" s="11"/>
+      <c r="AB12" s="13">
         <v>46072</v>
       </c>
-      <c r="AC12" s="12"/>
-      <c r="AD12" s="33">
+      <c r="AC12" s="11"/>
+      <c r="AD12" s="32">
         <v>46100</v>
       </c>
-      <c r="AE12" s="12"/>
-      <c r="AF12" s="32">
+      <c r="AE12" s="11"/>
+      <c r="AF12" s="31">
         <v>46107</v>
       </c>
-      <c r="AG12" s="12"/>
-      <c r="AH12" s="35"/>
-      <c r="AI12" s="35"/>
-      <c r="AJ12" s="35"/>
-      <c r="AK12" s="35"/>
-      <c r="AL12" s="35"/>
-      <c r="AM12" s="35"/>
-      <c r="AN12" s="35"/>
-      <c r="AO12" s="35"/>
-      <c r="AP12" s="35"/>
-      <c r="AQ12" s="35"/>
-      <c r="AR12" s="35"/>
-      <c r="AS12" s="35"/>
-      <c r="AT12" s="35"/>
-      <c r="AU12" s="35"/>
-      <c r="AV12" s="35"/>
-      <c r="AW12" s="35"/>
-      <c r="AX12" s="34"/>
+      <c r="AG12" s="11"/>
+      <c r="AH12" s="38"/>
+      <c r="AI12" s="11">
+        <v>5</v>
+      </c>
+      <c r="AJ12" s="38"/>
+      <c r="AK12" s="38"/>
+      <c r="AL12" s="38"/>
+      <c r="AM12" s="38"/>
+      <c r="AN12" s="38"/>
+      <c r="AO12" s="38"/>
+      <c r="AP12" s="38"/>
+      <c r="AQ12" s="38"/>
+      <c r="AR12" s="38"/>
+      <c r="AS12" s="38"/>
+      <c r="AT12" s="38"/>
+      <c r="AU12" s="38"/>
+      <c r="AV12" s="38"/>
+      <c r="AW12" s="38"/>
+      <c r="AX12" s="35"/>
     </row>
     <row r="13" spans="1:50">
       <c r="A13" s="2">
         <v>10</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="9">
@@ -1743,56 +1792,60 @@
       <c r="J13" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K13" s="27" t="s">
+      <c r="K13" s="26" t="s">
         <v>7</v>
       </c>
       <c r="L13" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="M13" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="N13" s="12"/>
-      <c r="O13" s="12"/>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="12"/>
-      <c r="S13" s="12"/>
-      <c r="T13" s="12"/>
-      <c r="U13" s="12"/>
-      <c r="V13" s="12"/>
-      <c r="W13" s="12"/>
-      <c r="X13" s="12"/>
-      <c r="Y13" s="12"/>
-      <c r="Z13" s="12"/>
-      <c r="AA13" s="12"/>
-      <c r="AB13" s="14">
+      <c r="M13" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N13" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="11"/>
+      <c r="T13" s="11"/>
+      <c r="U13" s="11"/>
+      <c r="V13" s="11"/>
+      <c r="W13" s="11"/>
+      <c r="X13" s="11"/>
+      <c r="Y13" s="11"/>
+      <c r="Z13" s="11"/>
+      <c r="AA13" s="11"/>
+      <c r="AB13" s="13">
         <v>46072</v>
       </c>
-      <c r="AC13" s="12"/>
-      <c r="AD13" s="21">
+      <c r="AC13" s="11"/>
+      <c r="AD13" s="20">
         <v>46093</v>
       </c>
-      <c r="AE13" s="12"/>
-      <c r="AF13" s="12"/>
-      <c r="AG13" s="12"/>
-      <c r="AH13" s="35"/>
-      <c r="AI13" s="35"/>
-      <c r="AJ13" s="35"/>
-      <c r="AK13" s="35"/>
-      <c r="AL13" s="35"/>
-      <c r="AM13" s="35"/>
-      <c r="AN13" s="35"/>
-      <c r="AO13" s="35"/>
-      <c r="AP13" s="35"/>
-      <c r="AQ13" s="35"/>
-      <c r="AR13" s="35"/>
-      <c r="AS13" s="35"/>
-      <c r="AT13" s="35"/>
-      <c r="AU13" s="35"/>
-      <c r="AV13" s="35"/>
-      <c r="AW13" s="35"/>
-      <c r="AX13" s="34"/>
+      <c r="AE13" s="11"/>
+      <c r="AF13" s="11"/>
+      <c r="AG13" s="11"/>
+      <c r="AH13" s="38"/>
+      <c r="AI13" s="11">
+        <v>4</v>
+      </c>
+      <c r="AJ13" s="38"/>
+      <c r="AK13" s="38"/>
+      <c r="AL13" s="38"/>
+      <c r="AM13" s="38"/>
+      <c r="AN13" s="38"/>
+      <c r="AO13" s="38"/>
+      <c r="AP13" s="38"/>
+      <c r="AQ13" s="38"/>
+      <c r="AR13" s="38"/>
+      <c r="AS13" s="38"/>
+      <c r="AT13" s="38"/>
+      <c r="AU13" s="38"/>
+      <c r="AV13" s="38"/>
+      <c r="AW13" s="38"/>
+      <c r="AX13" s="35"/>
     </row>
     <row r="14" spans="1:50">
       <c r="A14" s="2">
@@ -1817,7 +1870,7 @@
       <c r="H14" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I14" s="19" t="s">
+      <c r="I14" s="18" t="s">
         <v>7</v>
       </c>
       <c r="J14" s="9" t="s">
@@ -1829,23 +1882,25 @@
       <c r="L14" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="M14" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="N14" s="3"/>
-      <c r="O14" s="30"/>
+      <c r="M14" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N14" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="O14" s="29"/>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
-      <c r="R14" s="30"/>
+      <c r="R14" s="29"/>
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
-      <c r="U14" s="30"/>
+      <c r="U14" s="29"/>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
-      <c r="X14" s="30"/>
+      <c r="X14" s="29"/>
       <c r="Y14" s="3"/>
-      <c r="Z14" s="22"/>
-      <c r="AA14" s="22"/>
+      <c r="Z14" s="21"/>
+      <c r="AA14" s="21"/>
       <c r="AB14" s="3"/>
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
@@ -1853,7 +1908,9 @@
       <c r="AF14" s="3"/>
       <c r="AG14" s="3"/>
       <c r="AH14" s="3"/>
-      <c r="AI14" s="3"/>
+      <c r="AI14" s="33">
+        <v>2</v>
+      </c>
       <c r="AJ14" s="3"/>
       <c r="AK14" s="3"/>
       <c r="AL14" s="3"/>
@@ -1874,8 +1931,8 @@
       <c r="A15" s="2">
         <v>12</v>
       </c>
-      <c r="B15" s="15" t="s">
-        <v>18</v>
+      <c r="B15" s="14" t="s">
+        <v>73</v>
       </c>
       <c r="C15" s="9">
         <v>8</v>
@@ -1907,35 +1964,39 @@
       <c r="L15" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="M15" s="31" t="s">
+      <c r="M15" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="N15" s="3"/>
-      <c r="O15" s="30"/>
+      <c r="N15" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="O15" s="29"/>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
-      <c r="R15" s="30"/>
+      <c r="R15" s="29"/>
       <c r="S15" s="3"/>
       <c r="T15" s="3"/>
-      <c r="U15" s="30"/>
+      <c r="U15" s="29"/>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
-      <c r="X15" s="30"/>
+      <c r="X15" s="29"/>
       <c r="Y15" s="3"/>
-      <c r="Z15" s="22"/>
-      <c r="AA15" s="22"/>
-      <c r="AB15" s="14">
+      <c r="Z15" s="21"/>
+      <c r="AA15" s="21"/>
+      <c r="AB15" s="13">
         <v>46079</v>
       </c>
       <c r="AC15" s="3"/>
-      <c r="AD15" s="32">
+      <c r="AD15" s="31">
         <v>46100</v>
       </c>
       <c r="AE15" s="3"/>
       <c r="AF15" s="3"/>
       <c r="AG15" s="3"/>
       <c r="AH15" s="3"/>
-      <c r="AI15" s="3"/>
+      <c r="AI15" s="3">
+        <v>4</v>
+      </c>
       <c r="AJ15" s="3"/>
       <c r="AK15" s="3"/>
       <c r="AL15" s="3"/>
@@ -1987,39 +2048,43 @@
       <c r="L16" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="M16" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="N16" s="3"/>
-      <c r="O16" s="30"/>
+      <c r="M16" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N16" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="O16" s="29"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-      <c r="R16" s="30"/>
+      <c r="R16" s="29"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-      <c r="U16" s="30"/>
+      <c r="U16" s="29"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-      <c r="X16" s="30"/>
+      <c r="X16" s="29"/>
       <c r="Y16" s="3"/>
-      <c r="Z16" s="22"/>
-      <c r="AA16" s="22"/>
-      <c r="AB16" s="14">
+      <c r="Z16" s="21"/>
+      <c r="AA16" s="21"/>
+      <c r="AB16" s="13">
         <v>46072</v>
       </c>
       <c r="AC16" s="3"/>
-      <c r="AD16" s="32">
+      <c r="AD16" s="31">
         <v>46100</v>
       </c>
       <c r="AE16" s="3"/>
-      <c r="AF16" s="32">
+      <c r="AF16" s="31">
         <v>46104</v>
       </c>
       <c r="AG16" s="3"/>
-      <c r="AH16" s="32">
+      <c r="AH16" s="31">
         <v>46107</v>
       </c>
-      <c r="AI16" s="3"/>
+      <c r="AI16" s="3">
+        <v>5</v>
+      </c>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
@@ -2040,7 +2105,7 @@
       <c r="A17" s="2">
         <v>14</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C17" s="9">
@@ -2073,35 +2138,39 @@
       <c r="L17" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="M17" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="N17" s="3"/>
-      <c r="O17" s="30"/>
+      <c r="M17" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N17" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="O17" s="29"/>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
-      <c r="R17" s="30"/>
+      <c r="R17" s="29"/>
       <c r="S17" s="3"/>
       <c r="T17" s="3"/>
-      <c r="U17" s="30"/>
+      <c r="U17" s="29"/>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
-      <c r="X17" s="30"/>
+      <c r="X17" s="29"/>
       <c r="Y17" s="3"/>
-      <c r="Z17" s="22"/>
-      <c r="AA17" s="22"/>
-      <c r="AB17" s="14">
+      <c r="Z17" s="21"/>
+      <c r="AA17" s="21"/>
+      <c r="AB17" s="13">
         <v>46072</v>
       </c>
       <c r="AC17" s="3"/>
-      <c r="AD17" s="14">
+      <c r="AD17" s="13">
         <v>46100</v>
       </c>
       <c r="AE17" s="3"/>
       <c r="AF17" s="3"/>
       <c r="AG17" s="3"/>
       <c r="AH17" s="3"/>
-      <c r="AI17" s="3"/>
+      <c r="AI17" s="3">
+        <v>4</v>
+      </c>
       <c r="AJ17" s="3"/>
       <c r="AK17" s="3"/>
       <c r="AL17" s="3"/>
@@ -2140,7 +2209,7 @@
       <c r="G18" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H18" s="19" t="s">
+      <c r="H18" s="18" t="s">
         <v>7</v>
       </c>
       <c r="I18" s="9" t="s">
@@ -2155,37 +2224,43 @@
       <c r="L18" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="M18" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="N18" s="3"/>
-      <c r="O18" s="30"/>
+      <c r="M18" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N18" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="O18" s="29"/>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
-      <c r="R18" s="30"/>
+      <c r="R18" s="29"/>
       <c r="S18" s="3"/>
       <c r="T18" s="3"/>
-      <c r="U18" s="30"/>
+      <c r="U18" s="29"/>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
-      <c r="X18" s="30"/>
+      <c r="X18" s="29"/>
       <c r="Y18" s="3"/>
-      <c r="Z18" s="22"/>
-      <c r="AA18" s="22"/>
-      <c r="AB18" s="28">
+      <c r="Z18" s="21"/>
+      <c r="AA18" s="21"/>
+      <c r="AB18" s="27">
         <v>46100</v>
       </c>
       <c r="AC18" s="3"/>
-      <c r="AD18" s="14">
+      <c r="AD18" s="13">
         <v>46100</v>
       </c>
       <c r="AE18" s="3"/>
-      <c r="AF18" s="32">
+      <c r="AF18" s="31">
         <v>46100</v>
       </c>
       <c r="AG18" s="3"/>
-      <c r="AH18" s="3"/>
-      <c r="AI18" s="3"/>
+      <c r="AH18" s="31">
+        <v>46114</v>
+      </c>
+      <c r="AI18" s="3">
+        <v>5</v>
+      </c>
       <c r="AJ18" s="3"/>
       <c r="AK18" s="3"/>
       <c r="AL18" s="3"/>
@@ -2206,7 +2281,7 @@
       <c r="A19" s="2">
         <v>16</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="14" t="s">
         <v>22</v>
       </c>
       <c r="C19" s="9">
@@ -2222,7 +2297,7 @@
       <c r="G19" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H19" s="19" t="s">
+      <c r="H19" s="18" t="s">
         <v>7</v>
       </c>
       <c r="I19" s="9" t="s">
@@ -2237,24 +2312,26 @@
       <c r="L19" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="M19" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="N19" s="3"/>
-      <c r="O19" s="30"/>
+      <c r="M19" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N19" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="O19" s="29"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-      <c r="R19" s="30"/>
+      <c r="R19" s="29"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-      <c r="U19" s="30"/>
+      <c r="U19" s="29"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-      <c r="X19" s="30"/>
+      <c r="X19" s="29"/>
       <c r="Y19" s="3"/>
-      <c r="Z19" s="22"/>
-      <c r="AA19" s="22"/>
-      <c r="AB19" s="14">
+      <c r="Z19" s="21"/>
+      <c r="AA19" s="21"/>
+      <c r="AB19" s="13">
         <v>46100</v>
       </c>
       <c r="AC19" s="3"/>
@@ -2263,7 +2340,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-      <c r="AI19" s="3"/>
+      <c r="AI19" s="3">
+        <v>3</v>
+      </c>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
@@ -2317,23 +2396,25 @@
       <c r="L20" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="M20" s="31" t="s">
+      <c r="M20" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="N20" s="3"/>
-      <c r="O20" s="30"/>
+      <c r="N20" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="O20" s="29"/>
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
-      <c r="R20" s="30"/>
+      <c r="R20" s="29"/>
       <c r="S20" s="3"/>
       <c r="T20" s="3"/>
-      <c r="U20" s="30"/>
+      <c r="U20" s="29"/>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
-      <c r="X20" s="30"/>
+      <c r="X20" s="29"/>
       <c r="Y20" s="3"/>
-      <c r="Z20" s="22"/>
-      <c r="AA20" s="22"/>
+      <c r="Z20" s="21"/>
+      <c r="AA20" s="21"/>
       <c r="AB20" s="3"/>
       <c r="AC20" s="3"/>
       <c r="AD20" s="3"/>
@@ -2341,7 +2422,9 @@
       <c r="AF20" s="3"/>
       <c r="AG20" s="3"/>
       <c r="AH20" s="3"/>
-      <c r="AI20" s="3"/>
+      <c r="AI20" s="3">
+        <v>2</v>
+      </c>
       <c r="AJ20" s="3"/>
       <c r="AK20" s="3"/>
       <c r="AL20" s="3"/>
@@ -2383,7 +2466,7 @@
       <c r="H21" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I21" s="19" t="s">
+      <c r="I21" s="18" t="s">
         <v>7</v>
       </c>
       <c r="J21" s="9" t="s">
@@ -2395,24 +2478,26 @@
       <c r="L21" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="M21" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="N21" s="3"/>
-      <c r="O21" s="30"/>
+      <c r="M21" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N21" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="O21" s="29"/>
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
-      <c r="R21" s="30"/>
+      <c r="R21" s="29"/>
       <c r="S21" s="3"/>
       <c r="T21" s="3"/>
-      <c r="U21" s="30"/>
+      <c r="U21" s="29"/>
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
-      <c r="X21" s="30"/>
+      <c r="X21" s="29"/>
       <c r="Y21" s="3"/>
-      <c r="Z21" s="22"/>
-      <c r="AA21" s="22"/>
-      <c r="AB21" s="14">
+      <c r="Z21" s="21"/>
+      <c r="AA21" s="21"/>
+      <c r="AB21" s="13">
         <v>46100</v>
       </c>
       <c r="AC21" s="3"/>
@@ -2421,7 +2506,9 @@
       <c r="AF21" s="3"/>
       <c r="AG21" s="3"/>
       <c r="AH21" s="3"/>
-      <c r="AI21" s="3"/>
+      <c r="AI21" s="3">
+        <v>3</v>
+      </c>
       <c r="AJ21" s="3"/>
       <c r="AK21" s="3"/>
       <c r="AL21" s="3"/>
@@ -2473,37 +2560,41 @@
       <c r="L22" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="M22" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="N22" s="3"/>
-      <c r="O22" s="30"/>
+      <c r="M22" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N22" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="O22" s="29"/>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
-      <c r="R22" s="30"/>
+      <c r="R22" s="29"/>
       <c r="S22" s="3"/>
       <c r="T22" s="3"/>
-      <c r="U22" s="30"/>
+      <c r="U22" s="29"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
-      <c r="X22" s="30"/>
+      <c r="X22" s="29"/>
       <c r="Y22" s="3"/>
-      <c r="Z22" s="22"/>
-      <c r="AA22" s="22"/>
-      <c r="AB22" s="14">
+      <c r="Z22" s="21"/>
+      <c r="AA22" s="21"/>
+      <c r="AB22" s="13">
         <v>46072</v>
       </c>
       <c r="AC22" s="3"/>
-      <c r="AD22" s="14">
+      <c r="AD22" s="13">
         <v>46100</v>
       </c>
       <c r="AE22" s="3"/>
-      <c r="AF22" s="32">
+      <c r="AF22" s="31">
         <v>46107</v>
       </c>
       <c r="AG22" s="3"/>
       <c r="AH22" s="3"/>
-      <c r="AI22" s="3"/>
+      <c r="AI22" s="3">
+        <v>5</v>
+      </c>
       <c r="AJ22" s="3"/>
       <c r="AK22" s="3"/>
       <c r="AL22" s="3"/>
@@ -2524,7 +2615,7 @@
       <c r="A23" s="2">
         <v>20</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C23" s="9">
@@ -2557,37 +2648,41 @@
       <c r="L23" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="M23" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="N23" s="3"/>
-      <c r="O23" s="30"/>
+      <c r="M23" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N23" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="O23" s="29"/>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
-      <c r="R23" s="30"/>
+      <c r="R23" s="29"/>
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
-      <c r="U23" s="30"/>
+      <c r="U23" s="29"/>
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
-      <c r="X23" s="30"/>
+      <c r="X23" s="29"/>
       <c r="Y23" s="3"/>
-      <c r="Z23" s="22"/>
-      <c r="AA23" s="22"/>
-      <c r="AB23" s="14">
+      <c r="Z23" s="21"/>
+      <c r="AA23" s="21"/>
+      <c r="AB23" s="13">
         <v>46072</v>
       </c>
       <c r="AC23" s="3"/>
-      <c r="AD23" s="14">
+      <c r="AD23" s="13">
         <v>46100</v>
       </c>
       <c r="AE23" s="3"/>
-      <c r="AF23" s="32">
+      <c r="AF23" s="31">
         <v>46107</v>
       </c>
       <c r="AG23" s="3"/>
       <c r="AH23" s="3"/>
-      <c r="AI23" s="3"/>
+      <c r="AI23" s="3">
+        <v>5</v>
+      </c>
       <c r="AJ23" s="3"/>
       <c r="AK23" s="3"/>
       <c r="AL23" s="3"/>
@@ -2626,7 +2721,7 @@
       <c r="G24" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H24" s="19" t="s">
+      <c r="H24" s="18" t="s">
         <v>7</v>
       </c>
       <c r="I24" s="9" t="s">
@@ -2641,23 +2736,25 @@
       <c r="L24" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="31" t="s">
+      <c r="M24" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="N24" s="3"/>
-      <c r="O24" s="30"/>
+      <c r="N24" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="O24" s="29"/>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
-      <c r="R24" s="30"/>
+      <c r="R24" s="29"/>
       <c r="S24" s="3"/>
       <c r="T24" s="3"/>
-      <c r="U24" s="30"/>
+      <c r="U24" s="29"/>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
-      <c r="X24" s="30"/>
+      <c r="X24" s="29"/>
       <c r="Y24" s="3"/>
-      <c r="Z24" s="22"/>
-      <c r="AA24" s="22"/>
+      <c r="Z24" s="21"/>
+      <c r="AA24" s="21"/>
       <c r="AB24" s="3"/>
       <c r="AC24" s="3"/>
       <c r="AD24" s="3"/>
@@ -2665,7 +2762,9 @@
       <c r="AF24" s="3"/>
       <c r="AG24" s="3"/>
       <c r="AH24" s="3"/>
-      <c r="AI24" s="3"/>
+      <c r="AI24" s="3">
+        <v>2</v>
+      </c>
       <c r="AJ24" s="3"/>
       <c r="AK24" s="3"/>
       <c r="AL24" s="3"/>
@@ -2717,37 +2816,41 @@
       <c r="L25" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="M25" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="N25" s="3"/>
-      <c r="O25" s="30"/>
+      <c r="M25" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N25" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="O25" s="29"/>
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
-      <c r="R25" s="30"/>
+      <c r="R25" s="29"/>
       <c r="S25" s="3"/>
       <c r="T25" s="3"/>
-      <c r="U25" s="30"/>
+      <c r="U25" s="29"/>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
-      <c r="X25" s="30"/>
+      <c r="X25" s="29"/>
       <c r="Y25" s="3"/>
-      <c r="Z25" s="22"/>
-      <c r="AA25" s="22"/>
-      <c r="AB25" s="14">
+      <c r="Z25" s="21"/>
+      <c r="AA25" s="21"/>
+      <c r="AB25" s="13">
         <v>46072</v>
       </c>
       <c r="AC25" s="3"/>
-      <c r="AD25" s="32">
+      <c r="AD25" s="31">
         <v>46100</v>
       </c>
       <c r="AE25" s="3"/>
-      <c r="AF25" s="32">
+      <c r="AF25" s="31">
         <v>46107</v>
       </c>
       <c r="AG25" s="3"/>
       <c r="AH25" s="3"/>
-      <c r="AI25" s="3"/>
+      <c r="AI25" s="3">
+        <v>5</v>
+      </c>
       <c r="AJ25" s="3"/>
       <c r="AK25" s="3"/>
       <c r="AL25" s="3"/>
@@ -2799,23 +2902,25 @@
       <c r="L26" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="M26" s="31" t="s">
+      <c r="M26" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="N26" s="3"/>
-      <c r="O26" s="30"/>
+      <c r="N26" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="O26" s="29"/>
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
-      <c r="R26" s="30"/>
+      <c r="R26" s="29"/>
       <c r="S26" s="3"/>
       <c r="T26" s="3"/>
-      <c r="U26" s="30"/>
+      <c r="U26" s="29"/>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
-      <c r="X26" s="30"/>
+      <c r="X26" s="29"/>
       <c r="Y26" s="3"/>
-      <c r="Z26" s="22"/>
-      <c r="AA26" s="22"/>
+      <c r="Z26" s="21"/>
+      <c r="AA26" s="21"/>
       <c r="AB26" s="3"/>
       <c r="AC26" s="3"/>
       <c r="AD26" s="3"/>
@@ -2823,7 +2928,9 @@
       <c r="AF26" s="3"/>
       <c r="AG26" s="3"/>
       <c r="AH26" s="3"/>
-      <c r="AI26" s="3"/>
+      <c r="AI26" s="3">
+        <v>0</v>
+      </c>
       <c r="AJ26" s="3"/>
       <c r="AK26" s="3"/>
       <c r="AL26" s="3"/>
@@ -2871,41 +2978,45 @@
       <c r="J27" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K27" s="29" t="s">
+      <c r="K27" s="28" t="s">
         <v>7</v>
       </c>
       <c r="L27" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="M27" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="N27" s="3"/>
-      <c r="O27" s="30"/>
+      <c r="M27" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N27" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="O27" s="29"/>
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
-      <c r="R27" s="30"/>
+      <c r="R27" s="29"/>
       <c r="S27" s="3"/>
       <c r="T27" s="3"/>
-      <c r="U27" s="30"/>
+      <c r="U27" s="29"/>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
-      <c r="X27" s="30"/>
+      <c r="X27" s="29"/>
       <c r="Y27" s="3"/>
-      <c r="Z27" s="22"/>
-      <c r="AA27" s="22"/>
-      <c r="AB27" s="14">
+      <c r="Z27" s="21"/>
+      <c r="AA27" s="21"/>
+      <c r="AB27" s="13">
         <v>46100</v>
       </c>
       <c r="AC27" s="3"/>
-      <c r="AD27" s="14">
+      <c r="AD27" s="13">
         <v>46100</v>
       </c>
       <c r="AE27" s="3"/>
       <c r="AF27" s="3"/>
       <c r="AG27" s="3"/>
       <c r="AH27" s="3"/>
-      <c r="AI27" s="3"/>
+      <c r="AI27" s="3">
+        <v>4</v>
+      </c>
       <c r="AJ27" s="3"/>
       <c r="AK27" s="3"/>
       <c r="AL27" s="3"/>
@@ -2947,7 +3058,7 @@
       <c r="H28" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I28" s="19" t="s">
+      <c r="I28" s="18" t="s">
         <v>7</v>
       </c>
       <c r="J28" s="9" t="s">
@@ -2959,24 +3070,26 @@
       <c r="L28" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="M28" s="31" t="s">
+      <c r="M28" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="N28" s="3"/>
-      <c r="O28" s="30"/>
+      <c r="N28" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="O28" s="29"/>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
-      <c r="R28" s="30"/>
+      <c r="R28" s="29"/>
       <c r="S28" s="3"/>
       <c r="T28" s="3"/>
-      <c r="U28" s="30"/>
+      <c r="U28" s="29"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
-      <c r="X28" s="30"/>
+      <c r="X28" s="29"/>
       <c r="Y28" s="3"/>
-      <c r="Z28" s="22"/>
-      <c r="AA28" s="22"/>
-      <c r="AB28" s="21">
+      <c r="Z28" s="21"/>
+      <c r="AA28" s="21"/>
+      <c r="AB28" s="20">
         <v>46086</v>
       </c>
       <c r="AC28" s="3"/>
@@ -2985,7 +3098,9 @@
       <c r="AF28" s="3"/>
       <c r="AG28" s="3"/>
       <c r="AH28" s="3"/>
-      <c r="AI28" s="3"/>
+      <c r="AI28" s="3">
+        <v>3</v>
+      </c>
       <c r="AJ28" s="3"/>
       <c r="AK28" s="3"/>
       <c r="AL28" s="3"/>
@@ -3037,35 +3152,39 @@
       <c r="L29" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="M29" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="N29" s="3"/>
-      <c r="O29" s="30"/>
+      <c r="M29" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N29" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="O29" s="29"/>
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
-      <c r="R29" s="30"/>
+      <c r="R29" s="29"/>
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
-      <c r="U29" s="30"/>
+      <c r="U29" s="29"/>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
-      <c r="X29" s="30"/>
+      <c r="X29" s="29"/>
       <c r="Y29" s="3"/>
-      <c r="Z29" s="22"/>
-      <c r="AA29" s="22"/>
-      <c r="AB29" s="14">
+      <c r="Z29" s="21"/>
+      <c r="AA29" s="21"/>
+      <c r="AB29" s="13">
         <v>46072</v>
       </c>
       <c r="AC29" s="3"/>
-      <c r="AD29" s="14">
+      <c r="AD29" s="13">
         <v>46100</v>
       </c>
       <c r="AE29" s="3"/>
       <c r="AF29" s="3"/>
       <c r="AG29" s="3"/>
       <c r="AH29" s="3"/>
-      <c r="AI29" s="3"/>
+      <c r="AI29" s="3">
+        <v>4</v>
+      </c>
       <c r="AJ29" s="3"/>
       <c r="AK29" s="3"/>
       <c r="AL29" s="3"/>
@@ -3086,7 +3205,7 @@
       <c r="A30" s="2">
         <v>27</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="14" t="s">
         <v>34</v>
       </c>
       <c r="C30" s="9">
@@ -3104,7 +3223,7 @@
       <c r="G30" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H30" s="19" t="s">
+      <c r="H30" s="18" t="s">
         <v>7</v>
       </c>
       <c r="I30" s="9" t="s">
@@ -3119,39 +3238,43 @@
       <c r="L30" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="M30" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="N30" s="3"/>
-      <c r="O30" s="30"/>
+      <c r="M30" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N30" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="O30" s="29"/>
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
-      <c r="R30" s="30"/>
+      <c r="R30" s="29"/>
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
-      <c r="U30" s="30"/>
+      <c r="U30" s="29"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
-      <c r="X30" s="30"/>
+      <c r="X30" s="29"/>
       <c r="Y30" s="3"/>
-      <c r="Z30" s="22"/>
-      <c r="AA30" s="22"/>
-      <c r="AB30" s="14">
+      <c r="Z30" s="21"/>
+      <c r="AA30" s="21"/>
+      <c r="AB30" s="13">
         <v>46072</v>
       </c>
       <c r="AC30" s="3"/>
-      <c r="AD30" s="32">
+      <c r="AD30" s="31">
         <v>46100</v>
       </c>
       <c r="AE30" s="3"/>
-      <c r="AF30" s="32">
+      <c r="AF30" s="31">
         <v>46104</v>
       </c>
       <c r="AG30" s="3"/>
-      <c r="AH30" s="32">
+      <c r="AH30" s="31">
         <v>46107</v>
       </c>
-      <c r="AI30" s="3"/>
+      <c r="AI30" s="3">
+        <v>5</v>
+      </c>
       <c r="AJ30" s="3"/>
       <c r="AK30" s="3"/>
       <c r="AL30" s="3"/>
@@ -3172,7 +3295,7 @@
       <c r="A31" s="2">
         <v>28</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="14" t="s">
         <v>35</v>
       </c>
       <c r="C31" s="9">
@@ -3205,24 +3328,26 @@
       <c r="L31" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="M31" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="N31" s="3"/>
-      <c r="O31" s="30"/>
+      <c r="M31" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N31" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="O31" s="29"/>
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
-      <c r="R31" s="30"/>
+      <c r="R31" s="29"/>
       <c r="S31" s="3"/>
       <c r="T31" s="3"/>
-      <c r="U31" s="30"/>
+      <c r="U31" s="29"/>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
-      <c r="X31" s="30"/>
+      <c r="X31" s="29"/>
       <c r="Y31" s="3"/>
-      <c r="Z31" s="22"/>
-      <c r="AA31" s="22"/>
-      <c r="AB31" s="14">
+      <c r="Z31" s="21"/>
+      <c r="AA31" s="21"/>
+      <c r="AB31" s="13">
         <v>46072</v>
       </c>
       <c r="AC31" s="3"/>
@@ -3231,7 +3356,9 @@
       <c r="AF31" s="3"/>
       <c r="AG31" s="3"/>
       <c r="AH31" s="3"/>
-      <c r="AI31" s="3"/>
+      <c r="AI31" s="3">
+        <v>3</v>
+      </c>
       <c r="AJ31" s="3"/>
       <c r="AK31" s="3"/>
       <c r="AL31" s="3"/>
@@ -3268,7 +3395,7 @@
       <c r="G32" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H32" s="19" t="s">
+      <c r="H32" s="18" t="s">
         <v>7</v>
       </c>
       <c r="I32" s="9" t="s">
@@ -3283,23 +3410,25 @@
       <c r="L32" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="M32" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="N32" s="3"/>
-      <c r="O32" s="30"/>
+      <c r="M32" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N32" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="O32" s="29"/>
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
-      <c r="R32" s="30"/>
+      <c r="R32" s="29"/>
       <c r="S32" s="3"/>
       <c r="T32" s="3"/>
-      <c r="U32" s="30"/>
+      <c r="U32" s="29"/>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
-      <c r="X32" s="30"/>
+      <c r="X32" s="29"/>
       <c r="Y32" s="3"/>
-      <c r="Z32" s="22"/>
-      <c r="AA32" s="22"/>
+      <c r="Z32" s="21"/>
+      <c r="AA32" s="21"/>
       <c r="AB32" s="3"/>
       <c r="AC32" s="3"/>
       <c r="AD32" s="3"/>
@@ -3307,7 +3436,9 @@
       <c r="AF32" s="3"/>
       <c r="AG32" s="3"/>
       <c r="AH32" s="3"/>
-      <c r="AI32" s="3"/>
+      <c r="AI32" s="3">
+        <v>2</v>
+      </c>
       <c r="AJ32" s="3"/>
       <c r="AK32" s="3"/>
       <c r="AL32" s="3"/>
@@ -3359,24 +3490,26 @@
       <c r="L33" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="M33" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="N33" s="3"/>
-      <c r="O33" s="30"/>
+      <c r="M33" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N33" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="O33" s="29"/>
       <c r="P33" s="3"/>
       <c r="Q33" s="3"/>
-      <c r="R33" s="30"/>
+      <c r="R33" s="29"/>
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
-      <c r="U33" s="30"/>
+      <c r="U33" s="29"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
-      <c r="X33" s="30"/>
+      <c r="X33" s="29"/>
       <c r="Y33" s="3"/>
-      <c r="Z33" s="22"/>
-      <c r="AA33" s="22"/>
-      <c r="AB33" s="14">
+      <c r="Z33" s="21"/>
+      <c r="AA33" s="21"/>
+      <c r="AB33" s="13">
         <v>46079</v>
       </c>
       <c r="AC33" s="3"/>
@@ -3385,7 +3518,9 @@
       <c r="AF33" s="3"/>
       <c r="AG33" s="3"/>
       <c r="AH33" s="3"/>
-      <c r="AI33" s="3"/>
+      <c r="AI33" s="3">
+        <v>3</v>
+      </c>
       <c r="AJ33" s="3"/>
       <c r="AK33" s="3"/>
       <c r="AL33" s="3"/>
@@ -3437,35 +3572,39 @@
       <c r="L34" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="M34" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="N34" s="3"/>
-      <c r="O34" s="30"/>
+      <c r="M34" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N34" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="O34" s="29"/>
       <c r="P34" s="3"/>
       <c r="Q34" s="3"/>
-      <c r="R34" s="30"/>
+      <c r="R34" s="29"/>
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
-      <c r="U34" s="30"/>
+      <c r="U34" s="29"/>
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
-      <c r="X34" s="30"/>
+      <c r="X34" s="29"/>
       <c r="Y34" s="3"/>
-      <c r="Z34" s="22"/>
-      <c r="AA34" s="22"/>
-      <c r="AB34" s="14">
+      <c r="Z34" s="21"/>
+      <c r="AA34" s="21"/>
+      <c r="AB34" s="13">
         <v>46072</v>
       </c>
       <c r="AC34" s="3"/>
-      <c r="AD34" s="21">
+      <c r="AD34" s="20">
         <v>46093</v>
       </c>
       <c r="AE34" s="3"/>
       <c r="AF34" s="3"/>
       <c r="AG34" s="3"/>
       <c r="AH34" s="3"/>
-      <c r="AI34" s="3"/>
+      <c r="AI34" s="3">
+        <v>4</v>
+      </c>
       <c r="AJ34" s="3"/>
       <c r="AK34" s="3"/>
       <c r="AL34" s="3"/>
@@ -3505,7 +3644,7 @@
       <c r="H35" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I35" s="19" t="s">
+      <c r="I35" s="18" t="s">
         <v>7</v>
       </c>
       <c r="J35" s="9" t="s">
@@ -3517,23 +3656,25 @@
       <c r="L35" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="M35" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="N35" s="3"/>
-      <c r="O35" s="30"/>
+      <c r="M35" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N35" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="O35" s="29"/>
       <c r="P35" s="3"/>
       <c r="Q35" s="3"/>
-      <c r="R35" s="30"/>
+      <c r="R35" s="29"/>
       <c r="S35" s="3"/>
       <c r="T35" s="3"/>
-      <c r="U35" s="30"/>
+      <c r="U35" s="29"/>
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
-      <c r="X35" s="30"/>
+      <c r="X35" s="29"/>
       <c r="Y35" s="3"/>
-      <c r="Z35" s="22"/>
-      <c r="AA35" s="22"/>
+      <c r="Z35" s="21"/>
+      <c r="AA35" s="21"/>
       <c r="AB35" s="3"/>
       <c r="AC35" s="3"/>
       <c r="AD35" s="3"/>
@@ -3541,7 +3682,9 @@
       <c r="AF35" s="3"/>
       <c r="AG35" s="3"/>
       <c r="AH35" s="3"/>
-      <c r="AI35" s="3"/>
+      <c r="AI35" s="3">
+        <v>2</v>
+      </c>
       <c r="AJ35" s="3"/>
       <c r="AK35" s="3"/>
       <c r="AL35" s="3"/>
@@ -3569,21 +3712,21 @@
       <c r="J36" s="9"/>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
-      <c r="M36" s="31"/>
+      <c r="M36" s="30"/>
       <c r="N36" s="3"/>
-      <c r="O36" s="30"/>
+      <c r="O36" s="29"/>
       <c r="P36" s="3"/>
       <c r="Q36" s="3"/>
-      <c r="R36" s="30"/>
+      <c r="R36" s="29"/>
       <c r="S36" s="3"/>
       <c r="T36" s="3"/>
-      <c r="U36" s="30"/>
+      <c r="U36" s="29"/>
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
-      <c r="X36" s="30"/>
+      <c r="X36" s="29"/>
       <c r="Y36" s="3"/>
-      <c r="Z36" s="22"/>
-      <c r="AA36" s="22"/>
+      <c r="Z36" s="21"/>
+      <c r="AA36" s="21"/>
       <c r="AB36" s="3"/>
       <c r="AC36" s="3"/>
       <c r="AD36" s="3"/>
@@ -3620,67 +3763,67 @@
       <c r="F37" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G37" s="13" t="s">
+      <c r="G37" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="H37" s="16" t="s">
+      <c r="H37" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="I37" s="31" t="s">
+      <c r="I37" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="J37" s="31" t="s">
+      <c r="J37" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="K37" s="31" t="s">
+      <c r="K37" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="L37" s="31" t="s">
+      <c r="L37" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="M37" s="31" t="s">
+      <c r="M37" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="N37" s="31" t="s">
+      <c r="N37" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="O37" s="31" t="s">
+      <c r="O37" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="P37" s="31" t="s">
+      <c r="P37" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="Q37" s="31" t="s">
+      <c r="Q37" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="R37" s="31" t="s">
+      <c r="R37" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="S37" s="31" t="s">
+      <c r="S37" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="T37" s="31" t="s">
+      <c r="T37" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="U37" s="31" t="s">
+      <c r="U37" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="V37" s="31" t="s">
+      <c r="V37" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="W37" s="31" t="s">
+      <c r="W37" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="X37" s="31" t="s">
+      <c r="X37" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="Y37" s="31" t="s">
+      <c r="Y37" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="Z37" s="31" t="s">
+      <c r="Z37" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="AA37" s="22"/>
+      <c r="AA37" s="21"/>
       <c r="AB37" s="3"/>
       <c r="AC37" s="3"/>
       <c r="AD37" s="3"/>
@@ -3765,13 +3908,13 @@
       </c>
     </row>
     <row r="39" spans="1:50">
-      <c r="E39" s="17" t="s">
+      <c r="E39" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="G39" s="17" t="s">
+      <c r="G39" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="I39" s="17" t="s">
+      <c r="I39" s="16" t="s">
         <v>71</v>
       </c>
       <c r="L39" t="s">
@@ -3780,11 +3923,13 @@
     </row>
     <row r="42" spans="1:50" ht="9.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="18">
+    <mergeCell ref="AR11:AR13"/>
+    <mergeCell ref="AS11:AS13"/>
+    <mergeCell ref="AT11:AT13"/>
     <mergeCell ref="A1:AX1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="AH11:AH13"/>
-    <mergeCell ref="AI11:AI13"/>
     <mergeCell ref="AJ11:AJ13"/>
     <mergeCell ref="AK11:AK13"/>
     <mergeCell ref="AL11:AL13"/>
@@ -3797,9 +3942,6 @@
     <mergeCell ref="AX11:AX13"/>
     <mergeCell ref="AP11:AP13"/>
     <mergeCell ref="AQ11:AQ13"/>
-    <mergeCell ref="AR11:AR13"/>
-    <mergeCell ref="AS11:AS13"/>
-    <mergeCell ref="AT11:AT13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3811,50 +3953,50 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
-      <c r="T1" s="34"/>
-      <c r="U1" s="34"/>
-      <c r="V1" s="34"/>
-      <c r="W1" s="34"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="34"/>
-      <c r="Z1" s="34"/>
-      <c r="AA1" s="34"/>
-      <c r="AB1" s="34"/>
-      <c r="AC1" s="34"/>
-      <c r="AD1" s="34"/>
-      <c r="AE1" s="34"/>
-      <c r="AF1" s="34"/>
-      <c r="AG1" s="34"/>
-      <c r="AH1" s="34"/>
-      <c r="AI1" s="34"/>
-      <c r="AJ1" s="34"/>
-      <c r="AK1" s="34"/>
-      <c r="AL1" s="34"/>
-      <c r="AM1" s="34"/>
-      <c r="AN1" s="34"/>
-      <c r="AO1" s="34"/>
-      <c r="AP1" s="34"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="35"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="35"/>
+      <c r="AA1" s="35"/>
+      <c r="AB1" s="35"/>
+      <c r="AC1" s="35"/>
+      <c r="AD1" s="35"/>
+      <c r="AE1" s="35"/>
+      <c r="AF1" s="35"/>
+      <c r="AG1" s="35"/>
+      <c r="AH1" s="35"/>
+      <c r="AI1" s="35"/>
+      <c r="AJ1" s="35"/>
+      <c r="AK1" s="35"/>
+      <c r="AL1" s="35"/>
+      <c r="AM1" s="35"/>
+      <c r="AN1" s="35"/>
+      <c r="AO1" s="35"/>
+      <c r="AP1" s="35"/>
     </row>
     <row r="2" spans="1:42" ht="30">
       <c r="A2" s="37" t="s">
@@ -4304,37 +4446,37 @@
       <c r="I11" s="37"/>
       <c r="J11" s="37"/>
       <c r="K11" s="37"/>
-      <c r="L11" s="35"/>
-      <c r="M11" s="35"/>
-      <c r="N11" s="35"/>
-      <c r="O11" s="35"/>
-      <c r="P11" s="35"/>
-      <c r="Q11" s="35"/>
-      <c r="R11" s="35"/>
-      <c r="S11" s="35"/>
-      <c r="T11" s="35"/>
-      <c r="U11" s="35"/>
-      <c r="V11" s="35"/>
-      <c r="W11" s="35"/>
-      <c r="X11" s="35"/>
-      <c r="Y11" s="35"/>
-      <c r="Z11" s="35"/>
-      <c r="AA11" s="35"/>
-      <c r="AB11" s="35"/>
-      <c r="AC11" s="35"/>
-      <c r="AD11" s="35"/>
-      <c r="AE11" s="35"/>
-      <c r="AF11" s="35"/>
-      <c r="AG11" s="35"/>
-      <c r="AH11" s="35"/>
-      <c r="AI11" s="35"/>
-      <c r="AJ11" s="35"/>
-      <c r="AK11" s="35"/>
-      <c r="AL11" s="35"/>
-      <c r="AM11" s="35"/>
-      <c r="AN11" s="35"/>
-      <c r="AO11" s="35"/>
-      <c r="AP11" s="34"/>
+      <c r="L11" s="38"/>
+      <c r="M11" s="38"/>
+      <c r="N11" s="38"/>
+      <c r="O11" s="38"/>
+      <c r="P11" s="38"/>
+      <c r="Q11" s="38"/>
+      <c r="R11" s="38"/>
+      <c r="S11" s="38"/>
+      <c r="T11" s="38"/>
+      <c r="U11" s="38"/>
+      <c r="V11" s="38"/>
+      <c r="W11" s="38"/>
+      <c r="X11" s="38"/>
+      <c r="Y11" s="38"/>
+      <c r="Z11" s="38"/>
+      <c r="AA11" s="38"/>
+      <c r="AB11" s="38"/>
+      <c r="AC11" s="38"/>
+      <c r="AD11" s="38"/>
+      <c r="AE11" s="38"/>
+      <c r="AF11" s="38"/>
+      <c r="AG11" s="38"/>
+      <c r="AH11" s="38"/>
+      <c r="AI11" s="38"/>
+      <c r="AJ11" s="38"/>
+      <c r="AK11" s="38"/>
+      <c r="AL11" s="38"/>
+      <c r="AM11" s="38"/>
+      <c r="AN11" s="38"/>
+      <c r="AO11" s="38"/>
+      <c r="AP11" s="35"/>
     </row>
     <row r="12" spans="1:42">
       <c r="A12" s="37"/>
@@ -4348,37 +4490,37 @@
       <c r="I12" s="37"/>
       <c r="J12" s="37"/>
       <c r="K12" s="37"/>
-      <c r="L12" s="35"/>
-      <c r="M12" s="35"/>
-      <c r="N12" s="35"/>
-      <c r="O12" s="35"/>
-      <c r="P12" s="35"/>
-      <c r="Q12" s="35"/>
-      <c r="R12" s="35"/>
-      <c r="S12" s="35"/>
-      <c r="T12" s="35"/>
-      <c r="U12" s="35"/>
-      <c r="V12" s="35"/>
-      <c r="W12" s="35"/>
-      <c r="X12" s="35"/>
-      <c r="Y12" s="35"/>
-      <c r="Z12" s="35"/>
-      <c r="AA12" s="35"/>
-      <c r="AB12" s="35"/>
-      <c r="AC12" s="35"/>
-      <c r="AD12" s="35"/>
-      <c r="AE12" s="35"/>
-      <c r="AF12" s="35"/>
-      <c r="AG12" s="35"/>
-      <c r="AH12" s="35"/>
-      <c r="AI12" s="35"/>
-      <c r="AJ12" s="35"/>
-      <c r="AK12" s="35"/>
-      <c r="AL12" s="35"/>
-      <c r="AM12" s="35"/>
-      <c r="AN12" s="35"/>
-      <c r="AO12" s="35"/>
-      <c r="AP12" s="34"/>
+      <c r="L12" s="38"/>
+      <c r="M12" s="38"/>
+      <c r="N12" s="38"/>
+      <c r="O12" s="38"/>
+      <c r="P12" s="38"/>
+      <c r="Q12" s="38"/>
+      <c r="R12" s="38"/>
+      <c r="S12" s="38"/>
+      <c r="T12" s="38"/>
+      <c r="U12" s="38"/>
+      <c r="V12" s="38"/>
+      <c r="W12" s="38"/>
+      <c r="X12" s="38"/>
+      <c r="Y12" s="38"/>
+      <c r="Z12" s="38"/>
+      <c r="AA12" s="38"/>
+      <c r="AB12" s="38"/>
+      <c r="AC12" s="38"/>
+      <c r="AD12" s="38"/>
+      <c r="AE12" s="38"/>
+      <c r="AF12" s="38"/>
+      <c r="AG12" s="38"/>
+      <c r="AH12" s="38"/>
+      <c r="AI12" s="38"/>
+      <c r="AJ12" s="38"/>
+      <c r="AK12" s="38"/>
+      <c r="AL12" s="38"/>
+      <c r="AM12" s="38"/>
+      <c r="AN12" s="38"/>
+      <c r="AO12" s="38"/>
+      <c r="AP12" s="35"/>
     </row>
     <row r="13" spans="1:42">
       <c r="A13" s="37"/>
@@ -4394,37 +4536,37 @@
       <c r="I13" s="37"/>
       <c r="J13" s="37"/>
       <c r="K13" s="37"/>
-      <c r="L13" s="35"/>
-      <c r="M13" s="35"/>
-      <c r="N13" s="35"/>
-      <c r="O13" s="35"/>
-      <c r="P13" s="35"/>
-      <c r="Q13" s="35"/>
-      <c r="R13" s="35"/>
-      <c r="S13" s="35"/>
-      <c r="T13" s="35"/>
-      <c r="U13" s="35"/>
-      <c r="V13" s="35"/>
-      <c r="W13" s="35"/>
-      <c r="X13" s="35"/>
-      <c r="Y13" s="35"/>
-      <c r="Z13" s="35"/>
-      <c r="AA13" s="35"/>
-      <c r="AB13" s="35"/>
-      <c r="AC13" s="35"/>
-      <c r="AD13" s="35"/>
-      <c r="AE13" s="35"/>
-      <c r="AF13" s="35"/>
-      <c r="AG13" s="35"/>
-      <c r="AH13" s="35"/>
-      <c r="AI13" s="35"/>
-      <c r="AJ13" s="35"/>
-      <c r="AK13" s="35"/>
-      <c r="AL13" s="35"/>
-      <c r="AM13" s="35"/>
-      <c r="AN13" s="35"/>
-      <c r="AO13" s="35"/>
-      <c r="AP13" s="34"/>
+      <c r="L13" s="38"/>
+      <c r="M13" s="38"/>
+      <c r="N13" s="38"/>
+      <c r="O13" s="38"/>
+      <c r="P13" s="38"/>
+      <c r="Q13" s="38"/>
+      <c r="R13" s="38"/>
+      <c r="S13" s="38"/>
+      <c r="T13" s="38"/>
+      <c r="U13" s="38"/>
+      <c r="V13" s="38"/>
+      <c r="W13" s="38"/>
+      <c r="X13" s="38"/>
+      <c r="Y13" s="38"/>
+      <c r="Z13" s="38"/>
+      <c r="AA13" s="38"/>
+      <c r="AB13" s="38"/>
+      <c r="AC13" s="38"/>
+      <c r="AD13" s="38"/>
+      <c r="AE13" s="38"/>
+      <c r="AF13" s="38"/>
+      <c r="AG13" s="38"/>
+      <c r="AH13" s="38"/>
+      <c r="AI13" s="38"/>
+      <c r="AJ13" s="38"/>
+      <c r="AK13" s="38"/>
+      <c r="AL13" s="38"/>
+      <c r="AM13" s="38"/>
+      <c r="AN13" s="38"/>
+      <c r="AO13" s="38"/>
+      <c r="AP13" s="35"/>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" s="2">
@@ -5580,6 +5722,33 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="AO11:AO13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
+    <mergeCell ref="AN11:AN13"/>
+    <mergeCell ref="AE11:AE13"/>
+    <mergeCell ref="AF11:AF13"/>
+    <mergeCell ref="AG11:AG13"/>
+    <mergeCell ref="AH11:AH13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="Z11:Z13"/>
+    <mergeCell ref="AA11:AA13"/>
+    <mergeCell ref="AB11:AB13"/>
+    <mergeCell ref="AC11:AC13"/>
+    <mergeCell ref="AD11:AD13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="V11:V13"/>
+    <mergeCell ref="W11:W13"/>
+    <mergeCell ref="X11:X13"/>
+    <mergeCell ref="Y11:Y13"/>
+    <mergeCell ref="P11:P13"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="T11:T13"/>
     <mergeCell ref="A1:AP1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A11:A13"/>
@@ -5596,33 +5765,6 @@
     <mergeCell ref="M11:M13"/>
     <mergeCell ref="N11:N13"/>
     <mergeCell ref="O11:O13"/>
-    <mergeCell ref="P11:P13"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="T11:T13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="V11:V13"/>
-    <mergeCell ref="W11:W13"/>
-    <mergeCell ref="X11:X13"/>
-    <mergeCell ref="Y11:Y13"/>
-    <mergeCell ref="Z11:Z13"/>
-    <mergeCell ref="AA11:AA13"/>
-    <mergeCell ref="AB11:AB13"/>
-    <mergeCell ref="AC11:AC13"/>
-    <mergeCell ref="AD11:AD13"/>
-    <mergeCell ref="AE11:AE13"/>
-    <mergeCell ref="AF11:AF13"/>
-    <mergeCell ref="AG11:AG13"/>
-    <mergeCell ref="AH11:AH13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="AO11:AO13"/>
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="AN11:AN13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ТКИ-341_Реверс_Инжиниринг.xlsx
+++ b/ТКИ-341_Реверс_Инжиниринг.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\Reverse_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C4525E-2219-43AC-90A3-9E1A15F095D1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73D695DD-E9C4-4DB4-9860-ADC08D7E34FB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -363,7 +363,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -460,6 +460,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -467,12 +476,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -776,64 +779,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="14.45" customHeight="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="35"/>
-      <c r="AA1" s="35"/>
-      <c r="AB1" s="35"/>
-      <c r="AC1" s="35"/>
-      <c r="AD1" s="35"/>
-      <c r="AE1" s="35"/>
-      <c r="AF1" s="35"/>
-      <c r="AG1" s="35"/>
-      <c r="AH1" s="35"/>
-      <c r="AI1" s="35"/>
-      <c r="AJ1" s="35"/>
-      <c r="AK1" s="35"/>
-      <c r="AL1" s="35"/>
-      <c r="AM1" s="35"/>
-      <c r="AN1" s="35"/>
-      <c r="AO1" s="35"/>
-      <c r="AP1" s="35"/>
-      <c r="AQ1" s="35"/>
-      <c r="AR1" s="35"/>
-      <c r="AS1" s="35"/>
-      <c r="AT1" s="35"/>
-      <c r="AU1" s="35"/>
-      <c r="AV1" s="35"/>
-      <c r="AW1" s="35"/>
-      <c r="AX1" s="35"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
+      <c r="X1" s="38"/>
+      <c r="Y1" s="38"/>
+      <c r="Z1" s="38"/>
+      <c r="AA1" s="38"/>
+      <c r="AB1" s="38"/>
+      <c r="AC1" s="38"/>
+      <c r="AD1" s="38"/>
+      <c r="AE1" s="38"/>
+      <c r="AF1" s="38"/>
+      <c r="AG1" s="38"/>
+      <c r="AH1" s="38"/>
+      <c r="AI1" s="38"/>
+      <c r="AJ1" s="38"/>
+      <c r="AK1" s="38"/>
+      <c r="AL1" s="38"/>
+      <c r="AM1" s="38"/>
+      <c r="AN1" s="38"/>
+      <c r="AO1" s="38"/>
+      <c r="AP1" s="38"/>
+      <c r="AQ1" s="38"/>
+      <c r="AR1" s="38"/>
+      <c r="AS1" s="38"/>
+      <c r="AT1" s="38"/>
+      <c r="AU1" s="38"/>
+      <c r="AV1" s="38"/>
+      <c r="AW1" s="38"/>
+      <c r="AX1" s="38"/>
     </row>
     <row r="2" spans="1:50" ht="27.6" customHeight="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="37"/>
+      <c r="B2" s="40"/>
       <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1121,7 +1124,7 @@
       <c r="M5" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="N5" s="39" t="s">
+      <c r="N5" s="36" t="s">
         <v>7</v>
       </c>
       <c r="O5" s="29"/>
@@ -1145,11 +1148,13 @@
         <v>46100</v>
       </c>
       <c r="AE5" s="3"/>
-      <c r="AF5" s="3"/>
+      <c r="AF5" s="31">
+        <v>46114</v>
+      </c>
       <c r="AG5" s="3"/>
-      <c r="AH5" s="3"/>
+      <c r="AH5" s="35"/>
       <c r="AI5" s="33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ5" s="3"/>
       <c r="AK5" s="3"/>
@@ -1651,27 +1656,31 @@
         <v>46100</v>
       </c>
       <c r="AE11" s="11"/>
-      <c r="AF11" s="11"/>
+      <c r="AF11" s="13">
+        <v>46107</v>
+      </c>
       <c r="AG11" s="11"/>
-      <c r="AH11" s="38"/>
+      <c r="AH11" s="31">
+        <v>46114</v>
+      </c>
       <c r="AI11" s="11">
-        <v>4</v>
-      </c>
-      <c r="AJ11" s="38"/>
-      <c r="AK11" s="38"/>
-      <c r="AL11" s="38"/>
-      <c r="AM11" s="38"/>
-      <c r="AN11" s="38"/>
-      <c r="AO11" s="38"/>
-      <c r="AP11" s="38"/>
-      <c r="AQ11" s="38"/>
-      <c r="AR11" s="38"/>
-      <c r="AS11" s="38"/>
-      <c r="AT11" s="38"/>
-      <c r="AU11" s="38"/>
-      <c r="AV11" s="38"/>
-      <c r="AW11" s="38"/>
-      <c r="AX11" s="35"/>
+        <v>5</v>
+      </c>
+      <c r="AJ11" s="37"/>
+      <c r="AK11" s="37"/>
+      <c r="AL11" s="37"/>
+      <c r="AM11" s="37"/>
+      <c r="AN11" s="37"/>
+      <c r="AO11" s="37"/>
+      <c r="AP11" s="37"/>
+      <c r="AQ11" s="37"/>
+      <c r="AR11" s="37"/>
+      <c r="AS11" s="37"/>
+      <c r="AT11" s="37"/>
+      <c r="AU11" s="37"/>
+      <c r="AV11" s="37"/>
+      <c r="AW11" s="37"/>
+      <c r="AX11" s="38"/>
     </row>
     <row r="12" spans="1:50">
       <c r="A12" s="2">
@@ -1741,25 +1750,27 @@
         <v>46107</v>
       </c>
       <c r="AG12" s="11"/>
-      <c r="AH12" s="38"/>
+      <c r="AH12" s="31">
+        <v>46114</v>
+      </c>
       <c r="AI12" s="11">
         <v>5</v>
       </c>
-      <c r="AJ12" s="38"/>
-      <c r="AK12" s="38"/>
-      <c r="AL12" s="38"/>
-      <c r="AM12" s="38"/>
-      <c r="AN12" s="38"/>
-      <c r="AO12" s="38"/>
-      <c r="AP12" s="38"/>
-      <c r="AQ12" s="38"/>
-      <c r="AR12" s="38"/>
-      <c r="AS12" s="38"/>
-      <c r="AT12" s="38"/>
-      <c r="AU12" s="38"/>
-      <c r="AV12" s="38"/>
-      <c r="AW12" s="38"/>
-      <c r="AX12" s="35"/>
+      <c r="AJ12" s="37"/>
+      <c r="AK12" s="37"/>
+      <c r="AL12" s="37"/>
+      <c r="AM12" s="37"/>
+      <c r="AN12" s="37"/>
+      <c r="AO12" s="37"/>
+      <c r="AP12" s="37"/>
+      <c r="AQ12" s="37"/>
+      <c r="AR12" s="37"/>
+      <c r="AS12" s="37"/>
+      <c r="AT12" s="37"/>
+      <c r="AU12" s="37"/>
+      <c r="AV12" s="37"/>
+      <c r="AW12" s="37"/>
+      <c r="AX12" s="38"/>
     </row>
     <row r="13" spans="1:50">
       <c r="A13" s="2">
@@ -1827,25 +1838,25 @@
       <c r="AE13" s="11"/>
       <c r="AF13" s="11"/>
       <c r="AG13" s="11"/>
-      <c r="AH13" s="38"/>
+      <c r="AH13" s="11"/>
       <c r="AI13" s="11">
         <v>4</v>
       </c>
-      <c r="AJ13" s="38"/>
-      <c r="AK13" s="38"/>
-      <c r="AL13" s="38"/>
-      <c r="AM13" s="38"/>
-      <c r="AN13" s="38"/>
-      <c r="AO13" s="38"/>
-      <c r="AP13" s="38"/>
-      <c r="AQ13" s="38"/>
-      <c r="AR13" s="38"/>
-      <c r="AS13" s="38"/>
-      <c r="AT13" s="38"/>
-      <c r="AU13" s="38"/>
-      <c r="AV13" s="38"/>
-      <c r="AW13" s="38"/>
-      <c r="AX13" s="35"/>
+      <c r="AJ13" s="37"/>
+      <c r="AK13" s="37"/>
+      <c r="AL13" s="37"/>
+      <c r="AM13" s="37"/>
+      <c r="AN13" s="37"/>
+      <c r="AO13" s="37"/>
+      <c r="AP13" s="37"/>
+      <c r="AQ13" s="37"/>
+      <c r="AR13" s="37"/>
+      <c r="AS13" s="37"/>
+      <c r="AT13" s="37"/>
+      <c r="AU13" s="37"/>
+      <c r="AV13" s="37"/>
+      <c r="AW13" s="37"/>
+      <c r="AX13" s="38"/>
     </row>
     <row r="14" spans="1:50">
       <c r="A14" s="2">
@@ -1991,11 +2002,15 @@
         <v>46100</v>
       </c>
       <c r="AE15" s="3"/>
-      <c r="AF15" s="3"/>
+      <c r="AF15" s="13">
+        <v>46107</v>
+      </c>
       <c r="AG15" s="3"/>
-      <c r="AH15" s="3"/>
+      <c r="AH15" s="31">
+        <v>46114</v>
+      </c>
       <c r="AI15" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ15" s="3"/>
       <c r="AK15" s="3"/>
@@ -2141,7 +2156,7 @@
       <c r="M17" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="N17" s="39" t="s">
+      <c r="N17" s="36" t="s">
         <v>7</v>
       </c>
       <c r="O17" s="29"/>
@@ -2165,11 +2180,13 @@
         <v>46100</v>
       </c>
       <c r="AE17" s="3"/>
-      <c r="AF17" s="3"/>
+      <c r="AF17" s="31">
+        <v>46114</v>
+      </c>
       <c r="AG17" s="3"/>
       <c r="AH17" s="3"/>
       <c r="AI17" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ17" s="3"/>
       <c r="AK17" s="3"/>
@@ -2591,7 +2608,9 @@
         <v>46107</v>
       </c>
       <c r="AG22" s="3"/>
-      <c r="AH22" s="3"/>
+      <c r="AH22" s="31">
+        <v>46114</v>
+      </c>
       <c r="AI22" s="3">
         <v>5</v>
       </c>
@@ -2679,7 +2698,9 @@
         <v>46107</v>
       </c>
       <c r="AG23" s="3"/>
-      <c r="AH23" s="3"/>
+      <c r="AH23" s="31">
+        <v>46114</v>
+      </c>
       <c r="AI23" s="3">
         <v>5</v>
       </c>
@@ -2847,7 +2868,9 @@
         <v>46107</v>
       </c>
       <c r="AG25" s="3"/>
-      <c r="AH25" s="3"/>
+      <c r="AH25" s="31">
+        <v>46114</v>
+      </c>
       <c r="AI25" s="3">
         <v>5</v>
       </c>
@@ -2987,7 +3010,7 @@
       <c r="M27" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="N27" s="39" t="s">
+      <c r="N27" s="36" t="s">
         <v>7</v>
       </c>
       <c r="O27" s="29"/>
@@ -3011,11 +3034,13 @@
         <v>46100</v>
       </c>
       <c r="AE27" s="3"/>
-      <c r="AF27" s="3"/>
-      <c r="AG27" s="3"/>
+      <c r="AF27" s="31">
+        <v>46114</v>
+      </c>
+      <c r="AG27" s="35"/>
       <c r="AH27" s="3"/>
       <c r="AI27" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ27" s="3"/>
       <c r="AK27" s="3"/>
@@ -3155,7 +3180,7 @@
       <c r="M29" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="N29" s="39" t="s">
+      <c r="N29" s="36" t="s">
         <v>7</v>
       </c>
       <c r="O29" s="29"/>
@@ -3179,11 +3204,13 @@
         <v>46100</v>
       </c>
       <c r="AE29" s="3"/>
-      <c r="AF29" s="3"/>
+      <c r="AF29" s="31">
+        <v>46114</v>
+      </c>
       <c r="AG29" s="3"/>
       <c r="AH29" s="3"/>
       <c r="AI29" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ29" s="3"/>
       <c r="AK29" s="3"/>
@@ -3923,13 +3950,14 @@
     </row>
     <row r="42" spans="1:50" ht="9.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="17">
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AQ11:AQ13"/>
     <mergeCell ref="AR11:AR13"/>
     <mergeCell ref="AS11:AS13"/>
     <mergeCell ref="AT11:AT13"/>
     <mergeCell ref="A1:AX1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="AH11:AH13"/>
     <mergeCell ref="AJ11:AJ13"/>
     <mergeCell ref="AK11:AK13"/>
     <mergeCell ref="AL11:AL13"/>
@@ -3940,8 +3968,6 @@
     <mergeCell ref="AV11:AV13"/>
     <mergeCell ref="AW11:AW13"/>
     <mergeCell ref="AX11:AX13"/>
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AQ11:AQ13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3953,56 +3979,56 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="35"/>
-      <c r="AA1" s="35"/>
-      <c r="AB1" s="35"/>
-      <c r="AC1" s="35"/>
-      <c r="AD1" s="35"/>
-      <c r="AE1" s="35"/>
-      <c r="AF1" s="35"/>
-      <c r="AG1" s="35"/>
-      <c r="AH1" s="35"/>
-      <c r="AI1" s="35"/>
-      <c r="AJ1" s="35"/>
-      <c r="AK1" s="35"/>
-      <c r="AL1" s="35"/>
-      <c r="AM1" s="35"/>
-      <c r="AN1" s="35"/>
-      <c r="AO1" s="35"/>
-      <c r="AP1" s="35"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
+      <c r="X1" s="38"/>
+      <c r="Y1" s="38"/>
+      <c r="Z1" s="38"/>
+      <c r="AA1" s="38"/>
+      <c r="AB1" s="38"/>
+      <c r="AC1" s="38"/>
+      <c r="AD1" s="38"/>
+      <c r="AE1" s="38"/>
+      <c r="AF1" s="38"/>
+      <c r="AG1" s="38"/>
+      <c r="AH1" s="38"/>
+      <c r="AI1" s="38"/>
+      <c r="AJ1" s="38"/>
+      <c r="AK1" s="38"/>
+      <c r="AL1" s="38"/>
+      <c r="AM1" s="38"/>
+      <c r="AN1" s="38"/>
+      <c r="AO1" s="38"/>
+      <c r="AP1" s="38"/>
     </row>
     <row r="2" spans="1:42" ht="30">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="37"/>
+      <c r="B2" s="40"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -4431,142 +4457,142 @@
       <c r="AP10" s="1"/>
     </row>
     <row r="11" spans="1:42">
-      <c r="A11" s="37">
+      <c r="A11" s="40">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
-      <c r="J11" s="37"/>
-      <c r="K11" s="37"/>
-      <c r="L11" s="38"/>
-      <c r="M11" s="38"/>
-      <c r="N11" s="38"/>
-      <c r="O11" s="38"/>
-      <c r="P11" s="38"/>
-      <c r="Q11" s="38"/>
-      <c r="R11" s="38"/>
-      <c r="S11" s="38"/>
-      <c r="T11" s="38"/>
-      <c r="U11" s="38"/>
-      <c r="V11" s="38"/>
-      <c r="W11" s="38"/>
-      <c r="X11" s="38"/>
-      <c r="Y11" s="38"/>
-      <c r="Z11" s="38"/>
-      <c r="AA11" s="38"/>
-      <c r="AB11" s="38"/>
-      <c r="AC11" s="38"/>
-      <c r="AD11" s="38"/>
-      <c r="AE11" s="38"/>
-      <c r="AF11" s="38"/>
-      <c r="AG11" s="38"/>
-      <c r="AH11" s="38"/>
-      <c r="AI11" s="38"/>
-      <c r="AJ11" s="38"/>
-      <c r="AK11" s="38"/>
-      <c r="AL11" s="38"/>
-      <c r="AM11" s="38"/>
-      <c r="AN11" s="38"/>
-      <c r="AO11" s="38"/>
-      <c r="AP11" s="35"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="40"/>
+      <c r="K11" s="40"/>
+      <c r="L11" s="37"/>
+      <c r="M11" s="37"/>
+      <c r="N11" s="37"/>
+      <c r="O11" s="37"/>
+      <c r="P11" s="37"/>
+      <c r="Q11" s="37"/>
+      <c r="R11" s="37"/>
+      <c r="S11" s="37"/>
+      <c r="T11" s="37"/>
+      <c r="U11" s="37"/>
+      <c r="V11" s="37"/>
+      <c r="W11" s="37"/>
+      <c r="X11" s="37"/>
+      <c r="Y11" s="37"/>
+      <c r="Z11" s="37"/>
+      <c r="AA11" s="37"/>
+      <c r="AB11" s="37"/>
+      <c r="AC11" s="37"/>
+      <c r="AD11" s="37"/>
+      <c r="AE11" s="37"/>
+      <c r="AF11" s="37"/>
+      <c r="AG11" s="37"/>
+      <c r="AH11" s="37"/>
+      <c r="AI11" s="37"/>
+      <c r="AJ11" s="37"/>
+      <c r="AK11" s="37"/>
+      <c r="AL11" s="37"/>
+      <c r="AM11" s="37"/>
+      <c r="AN11" s="37"/>
+      <c r="AO11" s="37"/>
+      <c r="AP11" s="38"/>
     </row>
     <row r="12" spans="1:42">
-      <c r="A12" s="37"/>
+      <c r="A12" s="40"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="37"/>
-      <c r="J12" s="37"/>
-      <c r="K12" s="37"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="38"/>
-      <c r="P12" s="38"/>
-      <c r="Q12" s="38"/>
-      <c r="R12" s="38"/>
-      <c r="S12" s="38"/>
-      <c r="T12" s="38"/>
-      <c r="U12" s="38"/>
-      <c r="V12" s="38"/>
-      <c r="W12" s="38"/>
-      <c r="X12" s="38"/>
-      <c r="Y12" s="38"/>
-      <c r="Z12" s="38"/>
-      <c r="AA12" s="38"/>
-      <c r="AB12" s="38"/>
-      <c r="AC12" s="38"/>
-      <c r="AD12" s="38"/>
-      <c r="AE12" s="38"/>
-      <c r="AF12" s="38"/>
-      <c r="AG12" s="38"/>
-      <c r="AH12" s="38"/>
-      <c r="AI12" s="38"/>
-      <c r="AJ12" s="38"/>
-      <c r="AK12" s="38"/>
-      <c r="AL12" s="38"/>
-      <c r="AM12" s="38"/>
-      <c r="AN12" s="38"/>
-      <c r="AO12" s="38"/>
-      <c r="AP12" s="35"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="37"/>
+      <c r="M12" s="37"/>
+      <c r="N12" s="37"/>
+      <c r="O12" s="37"/>
+      <c r="P12" s="37"/>
+      <c r="Q12" s="37"/>
+      <c r="R12" s="37"/>
+      <c r="S12" s="37"/>
+      <c r="T12" s="37"/>
+      <c r="U12" s="37"/>
+      <c r="V12" s="37"/>
+      <c r="W12" s="37"/>
+      <c r="X12" s="37"/>
+      <c r="Y12" s="37"/>
+      <c r="Z12" s="37"/>
+      <c r="AA12" s="37"/>
+      <c r="AB12" s="37"/>
+      <c r="AC12" s="37"/>
+      <c r="AD12" s="37"/>
+      <c r="AE12" s="37"/>
+      <c r="AF12" s="37"/>
+      <c r="AG12" s="37"/>
+      <c r="AH12" s="37"/>
+      <c r="AI12" s="37"/>
+      <c r="AJ12" s="37"/>
+      <c r="AK12" s="37"/>
+      <c r="AL12" s="37"/>
+      <c r="AM12" s="37"/>
+      <c r="AN12" s="37"/>
+      <c r="AO12" s="37"/>
+      <c r="AP12" s="38"/>
     </row>
     <row r="13" spans="1:42">
-      <c r="A13" s="37"/>
+      <c r="A13" s="40"/>
       <c r="B13" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="37"/>
-      <c r="J13" s="37"/>
-      <c r="K13" s="37"/>
-      <c r="L13" s="38"/>
-      <c r="M13" s="38"/>
-      <c r="N13" s="38"/>
-      <c r="O13" s="38"/>
-      <c r="P13" s="38"/>
-      <c r="Q13" s="38"/>
-      <c r="R13" s="38"/>
-      <c r="S13" s="38"/>
-      <c r="T13" s="38"/>
-      <c r="U13" s="38"/>
-      <c r="V13" s="38"/>
-      <c r="W13" s="38"/>
-      <c r="X13" s="38"/>
-      <c r="Y13" s="38"/>
-      <c r="Z13" s="38"/>
-      <c r="AA13" s="38"/>
-      <c r="AB13" s="38"/>
-      <c r="AC13" s="38"/>
-      <c r="AD13" s="38"/>
-      <c r="AE13" s="38"/>
-      <c r="AF13" s="38"/>
-      <c r="AG13" s="38"/>
-      <c r="AH13" s="38"/>
-      <c r="AI13" s="38"/>
-      <c r="AJ13" s="38"/>
-      <c r="AK13" s="38"/>
-      <c r="AL13" s="38"/>
-      <c r="AM13" s="38"/>
-      <c r="AN13" s="38"/>
-      <c r="AO13" s="38"/>
-      <c r="AP13" s="35"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="40"/>
+      <c r="K13" s="40"/>
+      <c r="L13" s="37"/>
+      <c r="M13" s="37"/>
+      <c r="N13" s="37"/>
+      <c r="O13" s="37"/>
+      <c r="P13" s="37"/>
+      <c r="Q13" s="37"/>
+      <c r="R13" s="37"/>
+      <c r="S13" s="37"/>
+      <c r="T13" s="37"/>
+      <c r="U13" s="37"/>
+      <c r="V13" s="37"/>
+      <c r="W13" s="37"/>
+      <c r="X13" s="37"/>
+      <c r="Y13" s="37"/>
+      <c r="Z13" s="37"/>
+      <c r="AA13" s="37"/>
+      <c r="AB13" s="37"/>
+      <c r="AC13" s="37"/>
+      <c r="AD13" s="37"/>
+      <c r="AE13" s="37"/>
+      <c r="AF13" s="37"/>
+      <c r="AG13" s="37"/>
+      <c r="AH13" s="37"/>
+      <c r="AI13" s="37"/>
+      <c r="AJ13" s="37"/>
+      <c r="AK13" s="37"/>
+      <c r="AL13" s="37"/>
+      <c r="AM13" s="37"/>
+      <c r="AN13" s="37"/>
+      <c r="AO13" s="37"/>
+      <c r="AP13" s="38"/>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" s="2">
@@ -5722,33 +5748,6 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="AO11:AO13"/>
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="AN11:AN13"/>
-    <mergeCell ref="AE11:AE13"/>
-    <mergeCell ref="AF11:AF13"/>
-    <mergeCell ref="AG11:AG13"/>
-    <mergeCell ref="AH11:AH13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="Z11:Z13"/>
-    <mergeCell ref="AA11:AA13"/>
-    <mergeCell ref="AB11:AB13"/>
-    <mergeCell ref="AC11:AC13"/>
-    <mergeCell ref="AD11:AD13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="V11:V13"/>
-    <mergeCell ref="W11:W13"/>
-    <mergeCell ref="X11:X13"/>
-    <mergeCell ref="Y11:Y13"/>
-    <mergeCell ref="P11:P13"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="T11:T13"/>
     <mergeCell ref="A1:AP1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A11:A13"/>
@@ -5765,6 +5764,33 @@
     <mergeCell ref="M11:M13"/>
     <mergeCell ref="N11:N13"/>
     <mergeCell ref="O11:O13"/>
+    <mergeCell ref="P11:P13"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="T11:T13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="V11:V13"/>
+    <mergeCell ref="W11:W13"/>
+    <mergeCell ref="X11:X13"/>
+    <mergeCell ref="Y11:Y13"/>
+    <mergeCell ref="Z11:Z13"/>
+    <mergeCell ref="AA11:AA13"/>
+    <mergeCell ref="AB11:AB13"/>
+    <mergeCell ref="AC11:AC13"/>
+    <mergeCell ref="AD11:AD13"/>
+    <mergeCell ref="AE11:AE13"/>
+    <mergeCell ref="AF11:AF13"/>
+    <mergeCell ref="AG11:AG13"/>
+    <mergeCell ref="AH11:AH13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="AO11:AO13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
+    <mergeCell ref="AN11:AN13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ТКИ-341_Реверс_Инжиниринг.xlsx
+++ b/ТКИ-341_Реверс_Инжиниринг.xlsx
@@ -1,27 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22527"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\Reverse_Engineering\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\flash\Documents\GIT\Reverse_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73D695DD-E9C4-4DB4-9860-ADC08D7E34FB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="82">
   <si>
     <t>ВЕДОМОСТЬ ПОСЕЩАЕМОСТИ ЗАНЯТИЙ СТУДЕНТАМИ ГРУППЫ ТКИ "Компьютерная безопасность" ИТТСУ РУТ (МИИТ)</t>
   </si>
@@ -274,11 +273,35 @@
   <si>
     <t>Горковец Анна Сергеевна</t>
   </si>
+  <si>
+    <t>Задание 1</t>
+  </si>
+  <si>
+    <t>Задание 2</t>
+  </si>
+  <si>
+    <t>Задание 3</t>
+  </si>
+  <si>
+    <t>Задание 4</t>
+  </si>
+  <si>
+    <t>ПК</t>
+  </si>
+  <si>
+    <t>Задание 5</t>
+  </si>
+  <si>
+    <t>Задание 6</t>
+  </si>
+  <si>
+    <t>Задание 7</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
@@ -363,7 +386,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -466,6 +489,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -476,6 +505,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -751,7 +786,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AX42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -776,67 +811,70 @@
     <col min="30" max="30" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="9.85546875" customWidth="1"/>
+    <col min="38" max="38" width="12" customWidth="1"/>
+    <col min="40" max="40" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="14.45" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="38"/>
-      <c r="R1" s="38"/>
-      <c r="S1" s="38"/>
-      <c r="T1" s="38"/>
-      <c r="U1" s="38"/>
-      <c r="V1" s="38"/>
-      <c r="W1" s="38"/>
-      <c r="X1" s="38"/>
-      <c r="Y1" s="38"/>
-      <c r="Z1" s="38"/>
-      <c r="AA1" s="38"/>
-      <c r="AB1" s="38"/>
-      <c r="AC1" s="38"/>
-      <c r="AD1" s="38"/>
-      <c r="AE1" s="38"/>
-      <c r="AF1" s="38"/>
-      <c r="AG1" s="38"/>
-      <c r="AH1" s="38"/>
-      <c r="AI1" s="38"/>
-      <c r="AJ1" s="38"/>
-      <c r="AK1" s="38"/>
-      <c r="AL1" s="38"/>
-      <c r="AM1" s="38"/>
-      <c r="AN1" s="38"/>
-      <c r="AO1" s="38"/>
-      <c r="AP1" s="38"/>
-      <c r="AQ1" s="38"/>
-      <c r="AR1" s="38"/>
-      <c r="AS1" s="38"/>
-      <c r="AT1" s="38"/>
-      <c r="AU1" s="38"/>
-      <c r="AV1" s="38"/>
-      <c r="AW1" s="38"/>
-      <c r="AX1" s="38"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40"/>
+      <c r="Q1" s="40"/>
+      <c r="R1" s="40"/>
+      <c r="S1" s="40"/>
+      <c r="T1" s="40"/>
+      <c r="U1" s="40"/>
+      <c r="V1" s="40"/>
+      <c r="W1" s="40"/>
+      <c r="X1" s="40"/>
+      <c r="Y1" s="40"/>
+      <c r="Z1" s="40"/>
+      <c r="AA1" s="40"/>
+      <c r="AB1" s="40"/>
+      <c r="AC1" s="40"/>
+      <c r="AD1" s="40"/>
+      <c r="AE1" s="40"/>
+      <c r="AF1" s="40"/>
+      <c r="AG1" s="40"/>
+      <c r="AH1" s="40"/>
+      <c r="AI1" s="40"/>
+      <c r="AJ1" s="40"/>
+      <c r="AK1" s="40"/>
+      <c r="AL1" s="40"/>
+      <c r="AM1" s="40"/>
+      <c r="AN1" s="40"/>
+      <c r="AO1" s="40"/>
+      <c r="AP1" s="40"/>
+      <c r="AQ1" s="40"/>
+      <c r="AR1" s="40"/>
+      <c r="AS1" s="40"/>
+      <c r="AT1" s="40"/>
+      <c r="AU1" s="40"/>
+      <c r="AV1" s="40"/>
+      <c r="AW1" s="40"/>
+      <c r="AX1" s="40"/>
     </row>
     <row r="2" spans="1:50" ht="27.6" customHeight="1">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="40"/>
+      <c r="B2" s="42"/>
       <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
@@ -874,7 +912,7 @@
         <v>46114</v>
       </c>
       <c r="O2" s="17">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="P2" s="17">
         <v>46121</v>
@@ -919,7 +957,9 @@
       <c r="AH2" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="AI2" s="3"/>
+      <c r="AI2" s="3" t="s">
+        <v>78</v>
+      </c>
       <c r="AJ2" s="3" t="s">
         <v>65</v>
       </c>
@@ -976,19 +1016,33 @@
       <c r="Y3" s="23"/>
       <c r="Z3" s="23"/>
       <c r="AA3" s="23"/>
-      <c r="AB3" s="23"/>
+      <c r="AB3" s="23" t="s">
+        <v>74</v>
+      </c>
       <c r="AC3" s="23"/>
-      <c r="AD3" s="23"/>
+      <c r="AD3" s="23" t="s">
+        <v>75</v>
+      </c>
       <c r="AE3" s="23"/>
-      <c r="AF3" s="23"/>
+      <c r="AF3" s="23" t="s">
+        <v>76</v>
+      </c>
       <c r="AG3" s="23"/>
-      <c r="AH3" s="23"/>
+      <c r="AH3" s="23" t="s">
+        <v>77</v>
+      </c>
       <c r="AI3" s="23"/>
-      <c r="AJ3" s="23"/>
+      <c r="AJ3" s="23" t="s">
+        <v>79</v>
+      </c>
       <c r="AK3" s="23"/>
-      <c r="AL3" s="23"/>
+      <c r="AL3" s="23" t="s">
+        <v>80</v>
+      </c>
       <c r="AM3" s="23"/>
-      <c r="AN3" s="23"/>
+      <c r="AN3" s="23" t="s">
+        <v>81</v>
+      </c>
       <c r="AO3" s="23"/>
       <c r="AP3" s="23"/>
       <c r="AQ3" s="23"/>
@@ -1043,7 +1097,9 @@
       <c r="N4" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="O4" s="29"/>
+      <c r="O4" s="29" t="s">
+        <v>7</v>
+      </c>
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
       <c r="R4" s="29"/>
@@ -1213,7 +1269,9 @@
       <c r="N6" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="O6" s="29"/>
+      <c r="O6" s="29" t="s">
+        <v>7</v>
+      </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="29"/>
@@ -1297,7 +1355,9 @@
       <c r="N7" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="O7" s="29"/>
+      <c r="O7" s="43" t="s">
+        <v>7</v>
+      </c>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="29"/>
@@ -1332,7 +1392,9 @@
       <c r="AK7" s="3"/>
       <c r="AL7" s="3"/>
       <c r="AM7" s="3"/>
-      <c r="AN7" s="3"/>
+      <c r="AN7" s="31">
+        <v>46118</v>
+      </c>
       <c r="AO7" s="3"/>
       <c r="AP7" s="3"/>
       <c r="AQ7" s="3"/>
@@ -1469,7 +1531,9 @@
       <c r="N9" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="O9" s="29"/>
+      <c r="O9" s="43" t="s">
+        <v>7</v>
+      </c>
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="29"/>
@@ -1553,7 +1617,9 @@
       <c r="N10" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="O10" s="29"/>
+      <c r="O10" s="43" t="s">
+        <v>7</v>
+      </c>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="29"/>
@@ -1635,7 +1701,9 @@
       <c r="N11" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="O11" s="11"/>
+      <c r="O11" s="38" t="s">
+        <v>7</v>
+      </c>
       <c r="P11" s="11"/>
       <c r="Q11" s="11"/>
       <c r="R11" s="11"/>
@@ -1663,24 +1731,24 @@
       <c r="AH11" s="31">
         <v>46114</v>
       </c>
-      <c r="AI11" s="11">
+      <c r="AI11" s="37">
         <v>5</v>
       </c>
-      <c r="AJ11" s="37"/>
-      <c r="AK11" s="37"/>
-      <c r="AL11" s="37"/>
-      <c r="AM11" s="37"/>
-      <c r="AN11" s="37"/>
-      <c r="AO11" s="37"/>
-      <c r="AP11" s="37"/>
-      <c r="AQ11" s="37"/>
-      <c r="AR11" s="37"/>
-      <c r="AS11" s="37"/>
-      <c r="AT11" s="37"/>
-      <c r="AU11" s="37"/>
-      <c r="AV11" s="37"/>
-      <c r="AW11" s="37"/>
-      <c r="AX11" s="38"/>
+      <c r="AJ11" s="39"/>
+      <c r="AK11" s="39"/>
+      <c r="AL11" s="39"/>
+      <c r="AM11" s="39"/>
+      <c r="AN11" s="39"/>
+      <c r="AO11" s="39"/>
+      <c r="AP11" s="39"/>
+      <c r="AQ11" s="39"/>
+      <c r="AR11" s="39"/>
+      <c r="AS11" s="39"/>
+      <c r="AT11" s="39"/>
+      <c r="AU11" s="39"/>
+      <c r="AV11" s="39"/>
+      <c r="AW11" s="39"/>
+      <c r="AX11" s="40"/>
     </row>
     <row r="12" spans="1:50">
       <c r="A12" s="2">
@@ -1725,7 +1793,9 @@
       <c r="N12" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="O12" s="11"/>
+      <c r="O12" s="38" t="s">
+        <v>7</v>
+      </c>
       <c r="P12" s="11"/>
       <c r="Q12" s="11"/>
       <c r="R12" s="11"/>
@@ -1753,24 +1823,24 @@
       <c r="AH12" s="31">
         <v>46114</v>
       </c>
-      <c r="AI12" s="11">
+      <c r="AI12" s="37">
         <v>5</v>
       </c>
-      <c r="AJ12" s="37"/>
-      <c r="AK12" s="37"/>
-      <c r="AL12" s="37"/>
-      <c r="AM12" s="37"/>
-      <c r="AN12" s="37"/>
-      <c r="AO12" s="37"/>
-      <c r="AP12" s="37"/>
-      <c r="AQ12" s="37"/>
-      <c r="AR12" s="37"/>
-      <c r="AS12" s="37"/>
-      <c r="AT12" s="37"/>
-      <c r="AU12" s="37"/>
-      <c r="AV12" s="37"/>
-      <c r="AW12" s="37"/>
-      <c r="AX12" s="38"/>
+      <c r="AJ12" s="39"/>
+      <c r="AK12" s="39"/>
+      <c r="AL12" s="39"/>
+      <c r="AM12" s="39"/>
+      <c r="AN12" s="39"/>
+      <c r="AO12" s="39"/>
+      <c r="AP12" s="39"/>
+      <c r="AQ12" s="39"/>
+      <c r="AR12" s="39"/>
+      <c r="AS12" s="39"/>
+      <c r="AT12" s="39"/>
+      <c r="AU12" s="39"/>
+      <c r="AV12" s="39"/>
+      <c r="AW12" s="39"/>
+      <c r="AX12" s="40"/>
     </row>
     <row r="13" spans="1:50">
       <c r="A13" s="2">
@@ -1815,7 +1885,9 @@
       <c r="N13" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="O13" s="11"/>
+      <c r="O13" s="36" t="s">
+        <v>7</v>
+      </c>
       <c r="P13" s="11"/>
       <c r="Q13" s="11"/>
       <c r="R13" s="11"/>
@@ -1836,27 +1908,31 @@
         <v>46093</v>
       </c>
       <c r="AE13" s="11"/>
-      <c r="AF13" s="11"/>
+      <c r="AF13" s="44">
+        <v>46118</v>
+      </c>
       <c r="AG13" s="11"/>
-      <c r="AH13" s="11"/>
-      <c r="AI13" s="11">
+      <c r="AH13" s="32">
+        <v>46118</v>
+      </c>
+      <c r="AI13" s="37">
         <v>4</v>
       </c>
-      <c r="AJ13" s="37"/>
-      <c r="AK13" s="37"/>
-      <c r="AL13" s="37"/>
-      <c r="AM13" s="37"/>
-      <c r="AN13" s="37"/>
-      <c r="AO13" s="37"/>
-      <c r="AP13" s="37"/>
-      <c r="AQ13" s="37"/>
-      <c r="AR13" s="37"/>
-      <c r="AS13" s="37"/>
-      <c r="AT13" s="37"/>
-      <c r="AU13" s="37"/>
-      <c r="AV13" s="37"/>
-      <c r="AW13" s="37"/>
-      <c r="AX13" s="38"/>
+      <c r="AJ13" s="39"/>
+      <c r="AK13" s="39"/>
+      <c r="AL13" s="39"/>
+      <c r="AM13" s="39"/>
+      <c r="AN13" s="39"/>
+      <c r="AO13" s="39"/>
+      <c r="AP13" s="39"/>
+      <c r="AQ13" s="39"/>
+      <c r="AR13" s="39"/>
+      <c r="AS13" s="39"/>
+      <c r="AT13" s="39"/>
+      <c r="AU13" s="39"/>
+      <c r="AV13" s="39"/>
+      <c r="AW13" s="39"/>
+      <c r="AX13" s="40"/>
     </row>
     <row r="14" spans="1:50">
       <c r="A14" s="2">
@@ -1981,7 +2057,9 @@
       <c r="N15" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="O15" s="29"/>
+      <c r="O15" s="29" t="s">
+        <v>7</v>
+      </c>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="29"/>
@@ -2069,7 +2147,9 @@
       <c r="N16" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="O16" s="29"/>
+      <c r="O16" s="43" t="s">
+        <v>7</v>
+      </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="29"/>
@@ -2104,7 +2184,9 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
-      <c r="AN16" s="3"/>
+      <c r="AN16" s="31">
+        <v>46118</v>
+      </c>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
       <c r="AQ16" s="3"/>
@@ -2159,7 +2241,9 @@
       <c r="N17" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="O17" s="29"/>
+      <c r="O17" s="29" t="s">
+        <v>7</v>
+      </c>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="29"/>
@@ -2247,7 +2331,9 @@
       <c r="N18" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="O18" s="29"/>
+      <c r="O18" s="43" t="s">
+        <v>7</v>
+      </c>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="29"/>
@@ -2335,7 +2421,9 @@
       <c r="N19" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="O19" s="29"/>
+      <c r="O19" s="43" t="s">
+        <v>7</v>
+      </c>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="29"/>
@@ -2419,7 +2507,9 @@
       <c r="N20" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="O20" s="29"/>
+      <c r="O20" s="29" t="s">
+        <v>7</v>
+      </c>
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
       <c r="R20" s="29"/>
@@ -2583,7 +2673,9 @@
       <c r="N22" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="O22" s="29"/>
+      <c r="O22" s="29" t="s">
+        <v>7</v>
+      </c>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
       <c r="R22" s="29"/>
@@ -2673,7 +2765,9 @@
       <c r="N23" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="O23" s="29"/>
+      <c r="O23" s="29" t="s">
+        <v>7</v>
+      </c>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
       <c r="R23" s="29"/>
@@ -2763,7 +2857,9 @@
       <c r="N24" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="O24" s="29"/>
+      <c r="O24" s="29" t="s">
+        <v>7</v>
+      </c>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
       <c r="R24" s="29"/>
@@ -2931,7 +3027,9 @@
       <c r="N26" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="O26" s="29"/>
+      <c r="O26" s="29" t="s">
+        <v>24</v>
+      </c>
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
       <c r="R26" s="29"/>
@@ -3101,7 +3199,9 @@
       <c r="N28" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="O28" s="29"/>
+      <c r="O28" s="29" t="s">
+        <v>7</v>
+      </c>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
       <c r="R28" s="29"/>
@@ -3183,7 +3283,9 @@
       <c r="N29" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="O29" s="29"/>
+      <c r="O29" s="29" t="s">
+        <v>7</v>
+      </c>
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
       <c r="R29" s="29"/>
@@ -3271,7 +3373,9 @@
       <c r="N30" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="O30" s="29"/>
+      <c r="O30" s="43" t="s">
+        <v>7</v>
+      </c>
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
       <c r="R30" s="29"/>
@@ -3306,7 +3410,9 @@
       <c r="AK30" s="3"/>
       <c r="AL30" s="3"/>
       <c r="AM30" s="3"/>
-      <c r="AN30" s="3"/>
+      <c r="AN30" s="31">
+        <v>46118</v>
+      </c>
       <c r="AO30" s="3"/>
       <c r="AP30" s="3"/>
       <c r="AQ30" s="3"/>
@@ -3361,7 +3467,9 @@
       <c r="N31" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="O31" s="29"/>
+      <c r="O31" s="29" t="s">
+        <v>7</v>
+      </c>
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
       <c r="R31" s="29"/>
@@ -3443,7 +3551,9 @@
       <c r="N32" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="O32" s="29"/>
+      <c r="O32" s="29" t="s">
+        <v>7</v>
+      </c>
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
       <c r="R32" s="29"/>
@@ -3605,7 +3715,9 @@
       <c r="N34" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="O34" s="29"/>
+      <c r="O34" s="43" t="s">
+        <v>7</v>
+      </c>
       <c r="P34" s="3"/>
       <c r="Q34" s="3"/>
       <c r="R34" s="29"/>
@@ -3626,9 +3738,13 @@
         <v>46093</v>
       </c>
       <c r="AE34" s="3"/>
-      <c r="AF34" s="3"/>
+      <c r="AF34" s="31">
+        <v>46118</v>
+      </c>
       <c r="AG34" s="3"/>
-      <c r="AH34" s="3"/>
+      <c r="AH34" s="31">
+        <v>46118</v>
+      </c>
       <c r="AI34" s="3">
         <v>4</v>
       </c>
@@ -3636,7 +3752,9 @@
       <c r="AK34" s="3"/>
       <c r="AL34" s="3"/>
       <c r="AM34" s="3"/>
-      <c r="AN34" s="3"/>
+      <c r="AN34" s="31">
+        <v>46118</v>
+      </c>
       <c r="AO34" s="3"/>
       <c r="AP34" s="3"/>
       <c r="AQ34" s="3"/>
@@ -3951,11 +4069,6 @@
     <row r="42" spans="1:50" ht="9.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AQ11:AQ13"/>
-    <mergeCell ref="AR11:AR13"/>
-    <mergeCell ref="AS11:AS13"/>
-    <mergeCell ref="AT11:AT13"/>
     <mergeCell ref="A1:AX1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="AJ11:AJ13"/>
@@ -3968,67 +4081,72 @@
     <mergeCell ref="AV11:AV13"/>
     <mergeCell ref="AW11:AW13"/>
     <mergeCell ref="AX11:AX13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AQ11:AQ13"/>
+    <mergeCell ref="AR11:AR13"/>
+    <mergeCell ref="AS11:AS13"/>
+    <mergeCell ref="AT11:AT13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AP37"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="38"/>
-      <c r="R1" s="38"/>
-      <c r="S1" s="38"/>
-      <c r="T1" s="38"/>
-      <c r="U1" s="38"/>
-      <c r="V1" s="38"/>
-      <c r="W1" s="38"/>
-      <c r="X1" s="38"/>
-      <c r="Y1" s="38"/>
-      <c r="Z1" s="38"/>
-      <c r="AA1" s="38"/>
-      <c r="AB1" s="38"/>
-      <c r="AC1" s="38"/>
-      <c r="AD1" s="38"/>
-      <c r="AE1" s="38"/>
-      <c r="AF1" s="38"/>
-      <c r="AG1" s="38"/>
-      <c r="AH1" s="38"/>
-      <c r="AI1" s="38"/>
-      <c r="AJ1" s="38"/>
-      <c r="AK1" s="38"/>
-      <c r="AL1" s="38"/>
-      <c r="AM1" s="38"/>
-      <c r="AN1" s="38"/>
-      <c r="AO1" s="38"/>
-      <c r="AP1" s="38"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40"/>
+      <c r="Q1" s="40"/>
+      <c r="R1" s="40"/>
+      <c r="S1" s="40"/>
+      <c r="T1" s="40"/>
+      <c r="U1" s="40"/>
+      <c r="V1" s="40"/>
+      <c r="W1" s="40"/>
+      <c r="X1" s="40"/>
+      <c r="Y1" s="40"/>
+      <c r="Z1" s="40"/>
+      <c r="AA1" s="40"/>
+      <c r="AB1" s="40"/>
+      <c r="AC1" s="40"/>
+      <c r="AD1" s="40"/>
+      <c r="AE1" s="40"/>
+      <c r="AF1" s="40"/>
+      <c r="AG1" s="40"/>
+      <c r="AH1" s="40"/>
+      <c r="AI1" s="40"/>
+      <c r="AJ1" s="40"/>
+      <c r="AK1" s="40"/>
+      <c r="AL1" s="40"/>
+      <c r="AM1" s="40"/>
+      <c r="AN1" s="40"/>
+      <c r="AO1" s="40"/>
+      <c r="AP1" s="40"/>
     </row>
     <row r="2" spans="1:42" ht="30">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="40"/>
+      <c r="B2" s="42"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -4457,142 +4575,142 @@
       <c r="AP10" s="1"/>
     </row>
     <row r="11" spans="1:42">
-      <c r="A11" s="40">
+      <c r="A11" s="42">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="40"/>
-      <c r="I11" s="40"/>
-      <c r="J11" s="40"/>
-      <c r="K11" s="40"/>
-      <c r="L11" s="37"/>
-      <c r="M11" s="37"/>
-      <c r="N11" s="37"/>
-      <c r="O11" s="37"/>
-      <c r="P11" s="37"/>
-      <c r="Q11" s="37"/>
-      <c r="R11" s="37"/>
-      <c r="S11" s="37"/>
-      <c r="T11" s="37"/>
-      <c r="U11" s="37"/>
-      <c r="V11" s="37"/>
-      <c r="W11" s="37"/>
-      <c r="X11" s="37"/>
-      <c r="Y11" s="37"/>
-      <c r="Z11" s="37"/>
-      <c r="AA11" s="37"/>
-      <c r="AB11" s="37"/>
-      <c r="AC11" s="37"/>
-      <c r="AD11" s="37"/>
-      <c r="AE11" s="37"/>
-      <c r="AF11" s="37"/>
-      <c r="AG11" s="37"/>
-      <c r="AH11" s="37"/>
-      <c r="AI11" s="37"/>
-      <c r="AJ11" s="37"/>
-      <c r="AK11" s="37"/>
-      <c r="AL11" s="37"/>
-      <c r="AM11" s="37"/>
-      <c r="AN11" s="37"/>
-      <c r="AO11" s="37"/>
-      <c r="AP11" s="38"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="39"/>
+      <c r="M11" s="39"/>
+      <c r="N11" s="39"/>
+      <c r="O11" s="39"/>
+      <c r="P11" s="39"/>
+      <c r="Q11" s="39"/>
+      <c r="R11" s="39"/>
+      <c r="S11" s="39"/>
+      <c r="T11" s="39"/>
+      <c r="U11" s="39"/>
+      <c r="V11" s="39"/>
+      <c r="W11" s="39"/>
+      <c r="X11" s="39"/>
+      <c r="Y11" s="39"/>
+      <c r="Z11" s="39"/>
+      <c r="AA11" s="39"/>
+      <c r="AB11" s="39"/>
+      <c r="AC11" s="39"/>
+      <c r="AD11" s="39"/>
+      <c r="AE11" s="39"/>
+      <c r="AF11" s="39"/>
+      <c r="AG11" s="39"/>
+      <c r="AH11" s="39"/>
+      <c r="AI11" s="39"/>
+      <c r="AJ11" s="39"/>
+      <c r="AK11" s="39"/>
+      <c r="AL11" s="39"/>
+      <c r="AM11" s="39"/>
+      <c r="AN11" s="39"/>
+      <c r="AO11" s="39"/>
+      <c r="AP11" s="40"/>
     </row>
     <row r="12" spans="1:42">
-      <c r="A12" s="40"/>
+      <c r="A12" s="42"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="40"/>
-      <c r="K12" s="40"/>
-      <c r="L12" s="37"/>
-      <c r="M12" s="37"/>
-      <c r="N12" s="37"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="37"/>
-      <c r="Q12" s="37"/>
-      <c r="R12" s="37"/>
-      <c r="S12" s="37"/>
-      <c r="T12" s="37"/>
-      <c r="U12" s="37"/>
-      <c r="V12" s="37"/>
-      <c r="W12" s="37"/>
-      <c r="X12" s="37"/>
-      <c r="Y12" s="37"/>
-      <c r="Z12" s="37"/>
-      <c r="AA12" s="37"/>
-      <c r="AB12" s="37"/>
-      <c r="AC12" s="37"/>
-      <c r="AD12" s="37"/>
-      <c r="AE12" s="37"/>
-      <c r="AF12" s="37"/>
-      <c r="AG12" s="37"/>
-      <c r="AH12" s="37"/>
-      <c r="AI12" s="37"/>
-      <c r="AJ12" s="37"/>
-      <c r="AK12" s="37"/>
-      <c r="AL12" s="37"/>
-      <c r="AM12" s="37"/>
-      <c r="AN12" s="37"/>
-      <c r="AO12" s="37"/>
-      <c r="AP12" s="38"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="42"/>
+      <c r="L12" s="39"/>
+      <c r="M12" s="39"/>
+      <c r="N12" s="39"/>
+      <c r="O12" s="39"/>
+      <c r="P12" s="39"/>
+      <c r="Q12" s="39"/>
+      <c r="R12" s="39"/>
+      <c r="S12" s="39"/>
+      <c r="T12" s="39"/>
+      <c r="U12" s="39"/>
+      <c r="V12" s="39"/>
+      <c r="W12" s="39"/>
+      <c r="X12" s="39"/>
+      <c r="Y12" s="39"/>
+      <c r="Z12" s="39"/>
+      <c r="AA12" s="39"/>
+      <c r="AB12" s="39"/>
+      <c r="AC12" s="39"/>
+      <c r="AD12" s="39"/>
+      <c r="AE12" s="39"/>
+      <c r="AF12" s="39"/>
+      <c r="AG12" s="39"/>
+      <c r="AH12" s="39"/>
+      <c r="AI12" s="39"/>
+      <c r="AJ12" s="39"/>
+      <c r="AK12" s="39"/>
+      <c r="AL12" s="39"/>
+      <c r="AM12" s="39"/>
+      <c r="AN12" s="39"/>
+      <c r="AO12" s="39"/>
+      <c r="AP12" s="40"/>
     </row>
     <row r="13" spans="1:42">
-      <c r="A13" s="40"/>
+      <c r="A13" s="42"/>
       <c r="B13" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="40"/>
-      <c r="I13" s="40"/>
-      <c r="J13" s="40"/>
-      <c r="K13" s="40"/>
-      <c r="L13" s="37"/>
-      <c r="M13" s="37"/>
-      <c r="N13" s="37"/>
-      <c r="O13" s="37"/>
-      <c r="P13" s="37"/>
-      <c r="Q13" s="37"/>
-      <c r="R13" s="37"/>
-      <c r="S13" s="37"/>
-      <c r="T13" s="37"/>
-      <c r="U13" s="37"/>
-      <c r="V13" s="37"/>
-      <c r="W13" s="37"/>
-      <c r="X13" s="37"/>
-      <c r="Y13" s="37"/>
-      <c r="Z13" s="37"/>
-      <c r="AA13" s="37"/>
-      <c r="AB13" s="37"/>
-      <c r="AC13" s="37"/>
-      <c r="AD13" s="37"/>
-      <c r="AE13" s="37"/>
-      <c r="AF13" s="37"/>
-      <c r="AG13" s="37"/>
-      <c r="AH13" s="37"/>
-      <c r="AI13" s="37"/>
-      <c r="AJ13" s="37"/>
-      <c r="AK13" s="37"/>
-      <c r="AL13" s="37"/>
-      <c r="AM13" s="37"/>
-      <c r="AN13" s="37"/>
-      <c r="AO13" s="37"/>
-      <c r="AP13" s="38"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="42"/>
+      <c r="L13" s="39"/>
+      <c r="M13" s="39"/>
+      <c r="N13" s="39"/>
+      <c r="O13" s="39"/>
+      <c r="P13" s="39"/>
+      <c r="Q13" s="39"/>
+      <c r="R13" s="39"/>
+      <c r="S13" s="39"/>
+      <c r="T13" s="39"/>
+      <c r="U13" s="39"/>
+      <c r="V13" s="39"/>
+      <c r="W13" s="39"/>
+      <c r="X13" s="39"/>
+      <c r="Y13" s="39"/>
+      <c r="Z13" s="39"/>
+      <c r="AA13" s="39"/>
+      <c r="AB13" s="39"/>
+      <c r="AC13" s="39"/>
+      <c r="AD13" s="39"/>
+      <c r="AE13" s="39"/>
+      <c r="AF13" s="39"/>
+      <c r="AG13" s="39"/>
+      <c r="AH13" s="39"/>
+      <c r="AI13" s="39"/>
+      <c r="AJ13" s="39"/>
+      <c r="AK13" s="39"/>
+      <c r="AL13" s="39"/>
+      <c r="AM13" s="39"/>
+      <c r="AN13" s="39"/>
+      <c r="AO13" s="39"/>
+      <c r="AP13" s="40"/>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" s="2">
@@ -5748,6 +5866,33 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="AO11:AO13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
+    <mergeCell ref="AN11:AN13"/>
+    <mergeCell ref="AE11:AE13"/>
+    <mergeCell ref="AF11:AF13"/>
+    <mergeCell ref="AG11:AG13"/>
+    <mergeCell ref="AH11:AH13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="Z11:Z13"/>
+    <mergeCell ref="AA11:AA13"/>
+    <mergeCell ref="AB11:AB13"/>
+    <mergeCell ref="AC11:AC13"/>
+    <mergeCell ref="AD11:AD13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="V11:V13"/>
+    <mergeCell ref="W11:W13"/>
+    <mergeCell ref="X11:X13"/>
+    <mergeCell ref="Y11:Y13"/>
+    <mergeCell ref="P11:P13"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="T11:T13"/>
     <mergeCell ref="A1:AP1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A11:A13"/>
@@ -5764,33 +5909,6 @@
     <mergeCell ref="M11:M13"/>
     <mergeCell ref="N11:N13"/>
     <mergeCell ref="O11:O13"/>
-    <mergeCell ref="P11:P13"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="T11:T13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="V11:V13"/>
-    <mergeCell ref="W11:W13"/>
-    <mergeCell ref="X11:X13"/>
-    <mergeCell ref="Y11:Y13"/>
-    <mergeCell ref="Z11:Z13"/>
-    <mergeCell ref="AA11:AA13"/>
-    <mergeCell ref="AB11:AB13"/>
-    <mergeCell ref="AC11:AC13"/>
-    <mergeCell ref="AD11:AD13"/>
-    <mergeCell ref="AE11:AE13"/>
-    <mergeCell ref="AF11:AF13"/>
-    <mergeCell ref="AG11:AG13"/>
-    <mergeCell ref="AH11:AH13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="AO11:AO13"/>
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="AN11:AN13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ТКИ-341_Реверс_Инжиниринг.xlsx
+++ b/ТКИ-341_Реверс_Инжиниринг.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\Reverse_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3919E602-50D1-4D3C-AC3A-4ABC15DFFE83}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC11F6B-B280-4BE5-90C7-56960BDAC510}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="96">
   <si>
     <t>ВЕДОМОСТЬ ПОСЕЩАЕМОСТИ ЗАНЯТИЙ СТУДЕНТАМИ ГРУППЫ ТКИ "Компьютерная безопасность" ИТТСУ РУТ (МИИТ)</t>
   </si>
@@ -342,6 +342,15 @@
   </si>
   <si>
     <t>Разобраться с графовой БД</t>
+  </si>
+  <si>
+    <t>KodusAI</t>
+  </si>
+  <si>
+    <t>Joern/CPG</t>
+  </si>
+  <si>
+    <t>Gitinspector</t>
   </si>
 </sst>
 </file>
@@ -518,6 +527,13 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -530,13 +546,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -836,68 +845,68 @@
     <col min="30" max="30" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="9" style="36"/>
+    <col min="42" max="42" width="9" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="14.45" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="30"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="30"/>
-      <c r="AA1" s="30"/>
-      <c r="AB1" s="30"/>
-      <c r="AC1" s="30"/>
-      <c r="AD1" s="30"/>
-      <c r="AE1" s="30"/>
-      <c r="AF1" s="30"/>
-      <c r="AG1" s="30"/>
-      <c r="AH1" s="30"/>
-      <c r="AI1" s="30"/>
-      <c r="AJ1" s="30"/>
-      <c r="AK1" s="30"/>
-      <c r="AL1" s="30"/>
-      <c r="AM1" s="30"/>
-      <c r="AN1" s="30"/>
-      <c r="AO1" s="30"/>
-      <c r="AP1" s="30"/>
-      <c r="AQ1" s="30"/>
-      <c r="AR1" s="30"/>
-      <c r="AS1" s="30"/>
-      <c r="AT1" s="30"/>
-      <c r="AU1" s="30"/>
-      <c r="AV1" s="30"/>
-      <c r="AW1" s="30"/>
-      <c r="AX1" s="30"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="33"/>
+      <c r="R1" s="33"/>
+      <c r="S1" s="33"/>
+      <c r="T1" s="33"/>
+      <c r="U1" s="33"/>
+      <c r="V1" s="33"/>
+      <c r="W1" s="33"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="33"/>
+      <c r="AA1" s="33"/>
+      <c r="AB1" s="33"/>
+      <c r="AC1" s="33"/>
+      <c r="AD1" s="33"/>
+      <c r="AE1" s="33"/>
+      <c r="AF1" s="33"/>
+      <c r="AG1" s="33"/>
+      <c r="AH1" s="33"/>
+      <c r="AI1" s="33"/>
+      <c r="AJ1" s="33"/>
+      <c r="AK1" s="33"/>
+      <c r="AL1" s="33"/>
+      <c r="AM1" s="33"/>
+      <c r="AN1" s="33"/>
+      <c r="AO1" s="33"/>
+      <c r="AP1" s="33"/>
+      <c r="AQ1" s="33"/>
+      <c r="AR1" s="33"/>
+      <c r="AS1" s="33"/>
+      <c r="AT1" s="33"/>
+      <c r="AU1" s="33"/>
+      <c r="AV1" s="33"/>
+      <c r="AW1" s="33"/>
+      <c r="AX1" s="33"/>
     </row>
     <row r="2" spans="1:50" ht="27.6" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="32"/>
+      <c r="B2" s="35"/>
       <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
@@ -996,7 +1005,7 @@
       </c>
       <c r="AM2" s="3"/>
       <c r="AO2" s="3"/>
-      <c r="AP2" s="34" t="s">
+      <c r="AP2" s="30" t="s">
         <v>10</v>
       </c>
       <c r="AQ2" s="3"/>
@@ -1056,7 +1065,7 @@
       <c r="AM3" s="19"/>
       <c r="AN3" s="19"/>
       <c r="AO3" s="19"/>
-      <c r="AP3" s="34"/>
+      <c r="AP3" s="30"/>
       <c r="AQ3" s="19"/>
       <c r="AR3" s="19"/>
       <c r="AS3" s="19"/>
@@ -1150,7 +1159,7 @@
         <v>74</v>
       </c>
       <c r="AO4" s="3"/>
-      <c r="AP4" s="34"/>
+      <c r="AP4" s="30"/>
       <c r="AQ4" s="3"/>
       <c r="AR4" s="3"/>
       <c r="AS4" s="3"/>
@@ -1207,7 +1216,7 @@
         <v>17</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
@@ -1246,7 +1255,7 @@
       </c>
       <c r="AN5" s="3"/>
       <c r="AO5" s="3"/>
-      <c r="AP5" s="34"/>
+      <c r="AP5" s="30"/>
       <c r="AQ5" s="3"/>
       <c r="AR5" s="3"/>
       <c r="AS5" s="3"/>
@@ -1342,7 +1351,7 @@
         <v>77</v>
       </c>
       <c r="AO6" s="3"/>
-      <c r="AP6" s="34"/>
+      <c r="AP6" s="30"/>
       <c r="AQ6" s="3"/>
       <c r="AR6" s="3"/>
       <c r="AS6" s="3"/>
@@ -1440,10 +1449,12 @@
       </c>
       <c r="AN7" s="3"/>
       <c r="AO7" s="3"/>
-      <c r="AP7" s="34" t="s">
+      <c r="AP7" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="AQ7" s="3"/>
+      <c r="AQ7" s="3" t="s">
+        <v>94</v>
+      </c>
       <c r="AR7" s="3"/>
       <c r="AS7" s="3"/>
       <c r="AT7" s="3"/>
@@ -1534,7 +1545,7 @@
         <v>79</v>
       </c>
       <c r="AO8" s="3"/>
-      <c r="AP8" s="34"/>
+      <c r="AP8" s="30"/>
       <c r="AQ8" s="3"/>
       <c r="AR8" s="3"/>
       <c r="AS8" s="3"/>
@@ -1626,7 +1637,7 @@
       </c>
       <c r="AN9" s="3"/>
       <c r="AO9" s="3"/>
-      <c r="AP9" s="34"/>
+      <c r="AP9" s="30"/>
       <c r="AQ9" s="3"/>
       <c r="AR9" s="3"/>
       <c r="AS9" s="3"/>
@@ -1704,7 +1715,9 @@
         <v>46118</v>
       </c>
       <c r="AE10" s="3"/>
-      <c r="AF10" s="3"/>
+      <c r="AF10" s="24">
+        <v>46121</v>
+      </c>
       <c r="AG10" s="3"/>
       <c r="AH10" s="3"/>
       <c r="AI10" s="3">
@@ -1722,7 +1735,7 @@
         <v>81</v>
       </c>
       <c r="AO10" s="3"/>
-      <c r="AP10" s="34"/>
+      <c r="AP10" s="30"/>
       <c r="AQ10" s="3"/>
       <c r="AR10" s="3"/>
       <c r="AS10" s="3"/>
@@ -1818,8 +1831,10 @@
       </c>
       <c r="AN11" s="5"/>
       <c r="AO11" s="5"/>
-      <c r="AP11" s="35"/>
-      <c r="AQ11" s="5"/>
+      <c r="AP11" s="31"/>
+      <c r="AQ11" s="5" t="s">
+        <v>95</v>
+      </c>
       <c r="AR11" s="5"/>
       <c r="AS11" s="5"/>
       <c r="AT11" s="5"/>
@@ -1918,7 +1933,7 @@
         <v>83</v>
       </c>
       <c r="AO12" s="5"/>
-      <c r="AP12" s="35"/>
+      <c r="AP12" s="31"/>
       <c r="AQ12" s="5"/>
       <c r="AR12" s="5"/>
       <c r="AS12" s="5"/>
@@ -2016,7 +2031,7 @@
       </c>
       <c r="AN13" s="28"/>
       <c r="AO13" s="5"/>
-      <c r="AP13" s="35"/>
+      <c r="AP13" s="31"/>
       <c r="AQ13" s="5"/>
       <c r="AR13" s="5"/>
       <c r="AS13" s="5"/>
@@ -2106,7 +2121,7 @@
         <v>85</v>
       </c>
       <c r="AO14" s="3"/>
-      <c r="AP14" s="34"/>
+      <c r="AP14" s="30"/>
       <c r="AQ14" s="3"/>
       <c r="AR14" s="3"/>
       <c r="AS14" s="3"/>
@@ -2200,7 +2215,7 @@
       <c r="AM15" s="3"/>
       <c r="AN15" s="3"/>
       <c r="AO15" s="3"/>
-      <c r="AP15" s="34"/>
+      <c r="AP15" s="30"/>
       <c r="AQ15" s="3"/>
       <c r="AR15" s="3"/>
       <c r="AS15" s="3"/>
@@ -2296,10 +2311,12 @@
       </c>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
-      <c r="AP16" s="34" t="s">
+      <c r="AP16" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="AQ16" s="3"/>
+      <c r="AQ16" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="AR16" s="3"/>
       <c r="AS16" s="3"/>
       <c r="AT16" s="3"/>
@@ -2396,7 +2413,7 @@
         <v>87</v>
       </c>
       <c r="AO17" s="3"/>
-      <c r="AP17" s="34"/>
+      <c r="AP17" s="30"/>
       <c r="AQ17" s="3"/>
       <c r="AR17" s="3"/>
       <c r="AS17" s="3"/>
@@ -2490,7 +2507,7 @@
       <c r="AM18" s="3"/>
       <c r="AN18" s="3"/>
       <c r="AO18" s="3"/>
-      <c r="AP18" s="34"/>
+      <c r="AP18" s="30"/>
       <c r="AQ18" s="3"/>
       <c r="AR18" s="3"/>
       <c r="AS18" s="3"/>
@@ -2576,7 +2593,7 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
-      <c r="AP19" s="34"/>
+      <c r="AP19" s="30"/>
       <c r="AQ19" s="3"/>
       <c r="AR19" s="3"/>
       <c r="AS19" s="3"/>
@@ -2664,7 +2681,7 @@
       <c r="AM20" s="3"/>
       <c r="AN20" s="3"/>
       <c r="AO20" s="3"/>
-      <c r="AP20" s="34"/>
+      <c r="AP20" s="30"/>
       <c r="AQ20" s="3"/>
       <c r="AR20" s="3"/>
       <c r="AS20" s="3"/>
@@ -2752,7 +2769,7 @@
       <c r="AM21" s="3"/>
       <c r="AN21" s="3"/>
       <c r="AO21" s="3"/>
-      <c r="AP21" s="34"/>
+      <c r="AP21" s="30"/>
       <c r="AQ21" s="3"/>
       <c r="AR21" s="3"/>
       <c r="AS21" s="3"/>
@@ -2848,7 +2865,7 @@
       </c>
       <c r="AN22" s="3"/>
       <c r="AO22" s="3"/>
-      <c r="AP22" s="34"/>
+      <c r="AP22" s="30"/>
       <c r="AQ22" s="3"/>
       <c r="AR22" s="3"/>
       <c r="AS22" s="3"/>
@@ -2942,7 +2959,7 @@
       <c r="AM23" s="3"/>
       <c r="AN23" s="3"/>
       <c r="AO23" s="3"/>
-      <c r="AP23" s="34"/>
+      <c r="AP23" s="30"/>
       <c r="AQ23" s="3"/>
       <c r="AR23" s="3"/>
       <c r="AS23" s="3"/>
@@ -3028,7 +3045,7 @@
       <c r="AM24" s="3"/>
       <c r="AN24" s="3"/>
       <c r="AO24" s="3"/>
-      <c r="AP24" s="34"/>
+      <c r="AP24" s="30"/>
       <c r="AQ24" s="3"/>
       <c r="AR24" s="3"/>
       <c r="AS24" s="3"/>
@@ -3120,7 +3137,7 @@
       <c r="AM25" s="3"/>
       <c r="AN25" s="3"/>
       <c r="AO25" s="3"/>
-      <c r="AP25" s="34"/>
+      <c r="AP25" s="30"/>
       <c r="AQ25" s="3"/>
       <c r="AR25" s="3"/>
       <c r="AS25" s="3"/>
@@ -3204,7 +3221,7 @@
       <c r="AM26" s="3"/>
       <c r="AN26" s="3"/>
       <c r="AO26" s="3"/>
-      <c r="AP26" s="34"/>
+      <c r="AP26" s="30"/>
       <c r="AQ26" s="3"/>
       <c r="AR26" s="3"/>
       <c r="AS26" s="3"/>
@@ -3296,7 +3313,7 @@
       <c r="AM27" s="3"/>
       <c r="AN27" s="3"/>
       <c r="AO27" s="3"/>
-      <c r="AP27" s="34"/>
+      <c r="AP27" s="30"/>
       <c r="AQ27" s="3"/>
       <c r="AR27" s="3"/>
       <c r="AS27" s="3"/>
@@ -3384,7 +3401,7 @@
       <c r="AM28" s="3"/>
       <c r="AN28" s="3"/>
       <c r="AO28" s="3"/>
-      <c r="AP28" s="34"/>
+      <c r="AP28" s="30"/>
       <c r="AQ28" s="3"/>
       <c r="AR28" s="3"/>
       <c r="AS28" s="3"/>
@@ -3474,7 +3491,7 @@
       <c r="AM29" s="3"/>
       <c r="AN29" s="3"/>
       <c r="AO29" s="3"/>
-      <c r="AP29" s="34"/>
+      <c r="AP29" s="30"/>
       <c r="AQ29" s="3"/>
       <c r="AR29" s="3"/>
       <c r="AS29" s="3"/>
@@ -3568,7 +3585,7 @@
       <c r="AM30" s="3"/>
       <c r="AN30" s="3"/>
       <c r="AO30" s="3"/>
-      <c r="AP30" s="34"/>
+      <c r="AP30" s="30"/>
       <c r="AQ30" s="3"/>
       <c r="AR30" s="3"/>
       <c r="AS30" s="3"/>
@@ -3642,6 +3659,9 @@
         <v>46072</v>
       </c>
       <c r="AC31" s="3"/>
+      <c r="AD31" s="24">
+        <v>46121</v>
+      </c>
       <c r="AE31" s="3"/>
       <c r="AF31" s="3"/>
       <c r="AG31" s="3"/>
@@ -3655,7 +3675,7 @@
       <c r="AM31" s="3"/>
       <c r="AN31" s="3"/>
       <c r="AO31" s="3"/>
-      <c r="AP31" s="34"/>
+      <c r="AP31" s="30"/>
       <c r="AQ31" s="3"/>
       <c r="AR31" s="3"/>
       <c r="AS31" s="3"/>
@@ -3739,7 +3759,7 @@
       <c r="AM32" s="3"/>
       <c r="AN32" s="3"/>
       <c r="AO32" s="3"/>
-      <c r="AP32" s="34"/>
+      <c r="AP32" s="30"/>
       <c r="AQ32" s="3"/>
       <c r="AR32" s="3"/>
       <c r="AS32" s="3"/>
@@ -3815,7 +3835,9 @@
         <v>46118</v>
       </c>
       <c r="AE33" s="3"/>
-      <c r="AF33" s="3"/>
+      <c r="AF33" s="24">
+        <v>46121</v>
+      </c>
       <c r="AG33" s="3"/>
       <c r="AH33" s="3"/>
       <c r="AI33" s="3">
@@ -3827,7 +3849,7 @@
       <c r="AM33" s="3"/>
       <c r="AN33" s="3"/>
       <c r="AO33" s="3"/>
-      <c r="AP33" s="34"/>
+      <c r="AP33" s="30"/>
       <c r="AQ33" s="3"/>
       <c r="AR33" s="3"/>
       <c r="AS33" s="3"/>
@@ -3919,7 +3941,7 @@
       <c r="AM34" s="3"/>
       <c r="AN34" s="3"/>
       <c r="AO34" s="3"/>
-      <c r="AP34" s="34"/>
+      <c r="AP34" s="30"/>
       <c r="AQ34" s="3"/>
       <c r="AR34" s="3"/>
       <c r="AS34" s="3"/>
@@ -4003,7 +4025,7 @@
       <c r="AM35" s="3"/>
       <c r="AN35" s="3"/>
       <c r="AO35" s="3"/>
-      <c r="AP35" s="34"/>
+      <c r="AP35" s="30"/>
       <c r="AQ35" s="3"/>
       <c r="AR35" s="3"/>
       <c r="AS35" s="3"/>
@@ -4053,7 +4075,7 @@
       <c r="AM36" s="3"/>
       <c r="AN36" s="3"/>
       <c r="AO36" s="3"/>
-      <c r="AP36" s="34"/>
+      <c r="AP36" s="30"/>
       <c r="AQ36" s="3"/>
       <c r="AR36" s="3"/>
       <c r="AS36" s="3"/>
@@ -4150,7 +4172,7 @@
       <c r="AM37" s="3"/>
       <c r="AN37" s="3"/>
       <c r="AO37" s="3"/>
-      <c r="AP37" s="34"/>
+      <c r="AP37" s="30"/>
       <c r="AQ37" s="3"/>
       <c r="AR37" s="3"/>
       <c r="AS37" s="3"/>
@@ -4382,56 +4404,56 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="30"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="30"/>
-      <c r="AA1" s="30"/>
-      <c r="AB1" s="30"/>
-      <c r="AC1" s="30"/>
-      <c r="AD1" s="30"/>
-      <c r="AE1" s="30"/>
-      <c r="AF1" s="30"/>
-      <c r="AG1" s="30"/>
-      <c r="AH1" s="30"/>
-      <c r="AI1" s="30"/>
-      <c r="AJ1" s="30"/>
-      <c r="AK1" s="30"/>
-      <c r="AL1" s="30"/>
-      <c r="AM1" s="30"/>
-      <c r="AN1" s="30"/>
-      <c r="AO1" s="30"/>
-      <c r="AP1" s="30"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="33"/>
+      <c r="R1" s="33"/>
+      <c r="S1" s="33"/>
+      <c r="T1" s="33"/>
+      <c r="U1" s="33"/>
+      <c r="V1" s="33"/>
+      <c r="W1" s="33"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="33"/>
+      <c r="AA1" s="33"/>
+      <c r="AB1" s="33"/>
+      <c r="AC1" s="33"/>
+      <c r="AD1" s="33"/>
+      <c r="AE1" s="33"/>
+      <c r="AF1" s="33"/>
+      <c r="AG1" s="33"/>
+      <c r="AH1" s="33"/>
+      <c r="AI1" s="33"/>
+      <c r="AJ1" s="33"/>
+      <c r="AK1" s="33"/>
+      <c r="AL1" s="33"/>
+      <c r="AM1" s="33"/>
+      <c r="AN1" s="33"/>
+      <c r="AO1" s="33"/>
+      <c r="AP1" s="33"/>
     </row>
     <row r="2" spans="1:42" ht="30">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="32"/>
+      <c r="B2" s="35"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -4860,142 +4882,142 @@
       <c r="AP10" s="1"/>
     </row>
     <row r="11" spans="1:42">
-      <c r="A11" s="32">
+      <c r="A11" s="35">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-      <c r="K11" s="32"/>
-      <c r="L11" s="33"/>
-      <c r="M11" s="33"/>
-      <c r="N11" s="33"/>
-      <c r="O11" s="33"/>
-      <c r="P11" s="33"/>
-      <c r="Q11" s="33"/>
-      <c r="R11" s="33"/>
-      <c r="S11" s="33"/>
-      <c r="T11" s="33"/>
-      <c r="U11" s="33"/>
-      <c r="V11" s="33"/>
-      <c r="W11" s="33"/>
-      <c r="X11" s="33"/>
-      <c r="Y11" s="33"/>
-      <c r="Z11" s="33"/>
-      <c r="AA11" s="33"/>
-      <c r="AB11" s="33"/>
-      <c r="AC11" s="33"/>
-      <c r="AD11" s="33"/>
-      <c r="AE11" s="33"/>
-      <c r="AF11" s="33"/>
-      <c r="AG11" s="33"/>
-      <c r="AH11" s="33"/>
-      <c r="AI11" s="33"/>
-      <c r="AJ11" s="33"/>
-      <c r="AK11" s="33"/>
-      <c r="AL11" s="33"/>
-      <c r="AM11" s="33"/>
-      <c r="AN11" s="33"/>
-      <c r="AO11" s="33"/>
-      <c r="AP11" s="30"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="35"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="35"/>
+      <c r="L11" s="36"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="36"/>
+      <c r="S11" s="36"/>
+      <c r="T11" s="36"/>
+      <c r="U11" s="36"/>
+      <c r="V11" s="36"/>
+      <c r="W11" s="36"/>
+      <c r="X11" s="36"/>
+      <c r="Y11" s="36"/>
+      <c r="Z11" s="36"/>
+      <c r="AA11" s="36"/>
+      <c r="AB11" s="36"/>
+      <c r="AC11" s="36"/>
+      <c r="AD11" s="36"/>
+      <c r="AE11" s="36"/>
+      <c r="AF11" s="36"/>
+      <c r="AG11" s="36"/>
+      <c r="AH11" s="36"/>
+      <c r="AI11" s="36"/>
+      <c r="AJ11" s="36"/>
+      <c r="AK11" s="36"/>
+      <c r="AL11" s="36"/>
+      <c r="AM11" s="36"/>
+      <c r="AN11" s="36"/>
+      <c r="AO11" s="36"/>
+      <c r="AP11" s="33"/>
     </row>
     <row r="12" spans="1:42">
-      <c r="A12" s="32"/>
+      <c r="A12" s="35"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="32"/>
-      <c r="K12" s="32"/>
-      <c r="L12" s="33"/>
-      <c r="M12" s="33"/>
-      <c r="N12" s="33"/>
-      <c r="O12" s="33"/>
-      <c r="P12" s="33"/>
-      <c r="Q12" s="33"/>
-      <c r="R12" s="33"/>
-      <c r="S12" s="33"/>
-      <c r="T12" s="33"/>
-      <c r="U12" s="33"/>
-      <c r="V12" s="33"/>
-      <c r="W12" s="33"/>
-      <c r="X12" s="33"/>
-      <c r="Y12" s="33"/>
-      <c r="Z12" s="33"/>
-      <c r="AA12" s="33"/>
-      <c r="AB12" s="33"/>
-      <c r="AC12" s="33"/>
-      <c r="AD12" s="33"/>
-      <c r="AE12" s="33"/>
-      <c r="AF12" s="33"/>
-      <c r="AG12" s="33"/>
-      <c r="AH12" s="33"/>
-      <c r="AI12" s="33"/>
-      <c r="AJ12" s="33"/>
-      <c r="AK12" s="33"/>
-      <c r="AL12" s="33"/>
-      <c r="AM12" s="33"/>
-      <c r="AN12" s="33"/>
-      <c r="AO12" s="33"/>
-      <c r="AP12" s="30"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="36"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
+      <c r="S12" s="36"/>
+      <c r="T12" s="36"/>
+      <c r="U12" s="36"/>
+      <c r="V12" s="36"/>
+      <c r="W12" s="36"/>
+      <c r="X12" s="36"/>
+      <c r="Y12" s="36"/>
+      <c r="Z12" s="36"/>
+      <c r="AA12" s="36"/>
+      <c r="AB12" s="36"/>
+      <c r="AC12" s="36"/>
+      <c r="AD12" s="36"/>
+      <c r="AE12" s="36"/>
+      <c r="AF12" s="36"/>
+      <c r="AG12" s="36"/>
+      <c r="AH12" s="36"/>
+      <c r="AI12" s="36"/>
+      <c r="AJ12" s="36"/>
+      <c r="AK12" s="36"/>
+      <c r="AL12" s="36"/>
+      <c r="AM12" s="36"/>
+      <c r="AN12" s="36"/>
+      <c r="AO12" s="36"/>
+      <c r="AP12" s="33"/>
     </row>
     <row r="13" spans="1:42">
-      <c r="A13" s="32"/>
+      <c r="A13" s="35"/>
       <c r="B13" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32"/>
-      <c r="L13" s="33"/>
-      <c r="M13" s="33"/>
-      <c r="N13" s="33"/>
-      <c r="O13" s="33"/>
-      <c r="P13" s="33"/>
-      <c r="Q13" s="33"/>
-      <c r="R13" s="33"/>
-      <c r="S13" s="33"/>
-      <c r="T13" s="33"/>
-      <c r="U13" s="33"/>
-      <c r="V13" s="33"/>
-      <c r="W13" s="33"/>
-      <c r="X13" s="33"/>
-      <c r="Y13" s="33"/>
-      <c r="Z13" s="33"/>
-      <c r="AA13" s="33"/>
-      <c r="AB13" s="33"/>
-      <c r="AC13" s="33"/>
-      <c r="AD13" s="33"/>
-      <c r="AE13" s="33"/>
-      <c r="AF13" s="33"/>
-      <c r="AG13" s="33"/>
-      <c r="AH13" s="33"/>
-      <c r="AI13" s="33"/>
-      <c r="AJ13" s="33"/>
-      <c r="AK13" s="33"/>
-      <c r="AL13" s="33"/>
-      <c r="AM13" s="33"/>
-      <c r="AN13" s="33"/>
-      <c r="AO13" s="33"/>
-      <c r="AP13" s="30"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="35"/>
+      <c r="K13" s="35"/>
+      <c r="L13" s="36"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
+      <c r="S13" s="36"/>
+      <c r="T13" s="36"/>
+      <c r="U13" s="36"/>
+      <c r="V13" s="36"/>
+      <c r="W13" s="36"/>
+      <c r="X13" s="36"/>
+      <c r="Y13" s="36"/>
+      <c r="Z13" s="36"/>
+      <c r="AA13" s="36"/>
+      <c r="AB13" s="36"/>
+      <c r="AC13" s="36"/>
+      <c r="AD13" s="36"/>
+      <c r="AE13" s="36"/>
+      <c r="AF13" s="36"/>
+      <c r="AG13" s="36"/>
+      <c r="AH13" s="36"/>
+      <c r="AI13" s="36"/>
+      <c r="AJ13" s="36"/>
+      <c r="AK13" s="36"/>
+      <c r="AL13" s="36"/>
+      <c r="AM13" s="36"/>
+      <c r="AN13" s="36"/>
+      <c r="AO13" s="36"/>
+      <c r="AP13" s="33"/>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" s="2">
@@ -6151,33 +6173,6 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="AO11:AO13"/>
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="AN11:AN13"/>
-    <mergeCell ref="AE11:AE13"/>
-    <mergeCell ref="AF11:AF13"/>
-    <mergeCell ref="AG11:AG13"/>
-    <mergeCell ref="AH11:AH13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="Z11:Z13"/>
-    <mergeCell ref="AA11:AA13"/>
-    <mergeCell ref="AB11:AB13"/>
-    <mergeCell ref="AC11:AC13"/>
-    <mergeCell ref="AD11:AD13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="V11:V13"/>
-    <mergeCell ref="W11:W13"/>
-    <mergeCell ref="X11:X13"/>
-    <mergeCell ref="Y11:Y13"/>
-    <mergeCell ref="P11:P13"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="T11:T13"/>
     <mergeCell ref="A1:AP1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A11:A13"/>
@@ -6194,6 +6189,33 @@
     <mergeCell ref="M11:M13"/>
     <mergeCell ref="N11:N13"/>
     <mergeCell ref="O11:O13"/>
+    <mergeCell ref="P11:P13"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="T11:T13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="V11:V13"/>
+    <mergeCell ref="W11:W13"/>
+    <mergeCell ref="X11:X13"/>
+    <mergeCell ref="Y11:Y13"/>
+    <mergeCell ref="Z11:Z13"/>
+    <mergeCell ref="AA11:AA13"/>
+    <mergeCell ref="AB11:AB13"/>
+    <mergeCell ref="AC11:AC13"/>
+    <mergeCell ref="AD11:AD13"/>
+    <mergeCell ref="AE11:AE13"/>
+    <mergeCell ref="AF11:AF13"/>
+    <mergeCell ref="AG11:AG13"/>
+    <mergeCell ref="AH11:AH13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="AO11:AO13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
+    <mergeCell ref="AN11:AN13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ТКИ-341_Реверс_Инжиниринг.xlsx
+++ b/ТКИ-341_Реверс_Инжиниринг.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\Reverse_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC11F6B-B280-4BE5-90C7-56960BDAC510}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB183EA-6108-419C-A255-ECC02A8B1EA1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="99">
   <si>
     <t>ВЕДОМОСТЬ ПОСЕЩАЕМОСТИ ЗАНЯТИЙ СТУДЕНТАМИ ГРУППЫ ТКИ "Компьютерная безопасность" ИТТСУ РУТ (МИИТ)</t>
   </si>
@@ -352,6 +352,15 @@
   <si>
     <t>Gitinspector</t>
   </si>
+  <si>
+    <t>Санта</t>
+  </si>
+  <si>
+    <t>Новый инструментарий</t>
+  </si>
+  <si>
+    <t>VPN</t>
+  </si>
 </sst>
 </file>
 
@@ -383,7 +392,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -420,6 +429,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -448,7 +463,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -534,6 +549,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -845,68 +867,69 @@
     <col min="30" max="30" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="42" max="42" width="9" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="14.45" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="33"/>
-      <c r="R1" s="33"/>
-      <c r="S1" s="33"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="33"/>
-      <c r="V1" s="33"/>
-      <c r="W1" s="33"/>
-      <c r="X1" s="33"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="33"/>
-      <c r="AA1" s="33"/>
-      <c r="AB1" s="33"/>
-      <c r="AC1" s="33"/>
-      <c r="AD1" s="33"/>
-      <c r="AE1" s="33"/>
-      <c r="AF1" s="33"/>
-      <c r="AG1" s="33"/>
-      <c r="AH1" s="33"/>
-      <c r="AI1" s="33"/>
-      <c r="AJ1" s="33"/>
-      <c r="AK1" s="33"/>
-      <c r="AL1" s="33"/>
-      <c r="AM1" s="33"/>
-      <c r="AN1" s="33"/>
-      <c r="AO1" s="33"/>
-      <c r="AP1" s="33"/>
-      <c r="AQ1" s="33"/>
-      <c r="AR1" s="33"/>
-      <c r="AS1" s="33"/>
-      <c r="AT1" s="33"/>
-      <c r="AU1" s="33"/>
-      <c r="AV1" s="33"/>
-      <c r="AW1" s="33"/>
-      <c r="AX1" s="33"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="36"/>
+      <c r="R1" s="36"/>
+      <c r="S1" s="36"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="36"/>
+      <c r="V1" s="36"/>
+      <c r="W1" s="36"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="36"/>
+      <c r="Z1" s="36"/>
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="36"/>
+      <c r="AC1" s="36"/>
+      <c r="AD1" s="36"/>
+      <c r="AE1" s="36"/>
+      <c r="AF1" s="36"/>
+      <c r="AG1" s="36"/>
+      <c r="AH1" s="36"/>
+      <c r="AI1" s="36"/>
+      <c r="AJ1" s="36"/>
+      <c r="AK1" s="36"/>
+      <c r="AL1" s="36"/>
+      <c r="AM1" s="36"/>
+      <c r="AN1" s="36"/>
+      <c r="AO1" s="36"/>
+      <c r="AP1" s="36"/>
+      <c r="AQ1" s="36"/>
+      <c r="AR1" s="36"/>
+      <c r="AS1" s="36"/>
+      <c r="AT1" s="36"/>
+      <c r="AU1" s="36"/>
+      <c r="AV1" s="36"/>
+      <c r="AW1" s="36"/>
+      <c r="AX1" s="36"/>
     </row>
     <row r="2" spans="1:50" ht="27.6" customHeight="1">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="35"/>
+      <c r="B2" s="38"/>
       <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1124,7 +1147,9 @@
       <c r="P4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q4" s="3"/>
+      <c r="Q4" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
@@ -1218,7 +1243,9 @@
       <c r="P5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q5" s="3"/>
+      <c r="Q5" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
       <c r="T5" s="3"/>
@@ -1241,7 +1268,9 @@
         <v>46114</v>
       </c>
       <c r="AG5" s="3"/>
-      <c r="AH5" s="3"/>
+      <c r="AH5" s="24">
+        <v>46128</v>
+      </c>
       <c r="AI5" s="3">
         <v>5</v>
       </c>
@@ -1314,7 +1343,9 @@
       <c r="P6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q6" s="3"/>
+      <c r="Q6" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
       <c r="T6" s="3"/>
@@ -1410,7 +1441,9 @@
       <c r="P7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q7" s="3"/>
+      <c r="Q7" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
       <c r="T7" s="3"/>
@@ -1455,7 +1488,7 @@
       <c r="AQ7" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="AR7" s="3"/>
+      <c r="AR7" s="33"/>
       <c r="AS7" s="3"/>
       <c r="AT7" s="3"/>
       <c r="AU7" s="3"/>
@@ -1510,7 +1543,9 @@
       <c r="P8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q8" s="3"/>
+      <c r="Q8" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
@@ -1604,7 +1639,9 @@
       <c r="P9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q9" s="3"/>
+      <c r="Q9" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
       <c r="T9" s="3"/>
@@ -1696,7 +1733,9 @@
       <c r="P10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q10" s="3"/>
+      <c r="Q10" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
       <c r="T10" s="3"/>
@@ -1792,7 +1831,9 @@
       <c r="P11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="Q11" s="5"/>
+      <c r="Q11" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="R11" s="5"/>
       <c r="S11" s="5"/>
       <c r="T11" s="5"/>
@@ -1830,12 +1871,14 @@
         <v>82</v>
       </c>
       <c r="AN11" s="5"/>
-      <c r="AO11" s="5"/>
+      <c r="AO11" s="24">
+        <v>46128</v>
+      </c>
       <c r="AP11" s="31"/>
       <c r="AQ11" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="AR11" s="5"/>
+      <c r="AR11" s="34"/>
       <c r="AS11" s="5"/>
       <c r="AT11" s="5"/>
       <c r="AU11" s="5"/>
@@ -1892,7 +1935,9 @@
       <c r="P12" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="Q12" s="5"/>
+      <c r="Q12" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="R12" s="5"/>
       <c r="S12" s="5"/>
       <c r="T12" s="5"/>
@@ -1992,7 +2037,9 @@
       <c r="P13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="Q13" s="5"/>
+      <c r="Q13" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="R13" s="5"/>
       <c r="S13" s="5"/>
       <c r="T13" s="5"/>
@@ -2030,7 +2077,9 @@
         <v>84</v>
       </c>
       <c r="AN13" s="28"/>
-      <c r="AO13" s="5"/>
+      <c r="AO13" s="24">
+        <v>46128</v>
+      </c>
       <c r="AP13" s="31"/>
       <c r="AQ13" s="5"/>
       <c r="AR13" s="5"/>
@@ -2088,7 +2137,9 @@
       <c r="P14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q14" s="3"/>
+      <c r="Q14" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
@@ -2180,7 +2231,9 @@
       <c r="P15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q15" s="3"/>
+      <c r="Q15" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
       <c r="T15" s="3"/>
@@ -2214,7 +2267,9 @@
       <c r="AL15" s="3"/>
       <c r="AM15" s="3"/>
       <c r="AN15" s="3"/>
-      <c r="AO15" s="3"/>
+      <c r="AO15" s="24">
+        <v>46128</v>
+      </c>
       <c r="AP15" s="30"/>
       <c r="AQ15" s="3"/>
       <c r="AR15" s="3"/>
@@ -2272,7 +2327,9 @@
       <c r="P16" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q16" s="3"/>
+      <c r="Q16" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
@@ -2317,7 +2374,7 @@
       <c r="AQ16" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="AR16" s="3"/>
+      <c r="AR16" s="33"/>
       <c r="AS16" s="3"/>
       <c r="AT16" s="3"/>
       <c r="AU16" s="3"/>
@@ -2374,7 +2431,9 @@
       <c r="P17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q17" s="3"/>
+      <c r="Q17" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
       <c r="T17" s="3"/>
@@ -2397,7 +2456,9 @@
         <v>46114</v>
       </c>
       <c r="AG17" s="3"/>
-      <c r="AH17" s="3"/>
+      <c r="AH17" s="24">
+        <v>46128</v>
+      </c>
       <c r="AI17" s="3">
         <v>5</v>
       </c>
@@ -2472,7 +2533,9 @@
       <c r="P18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q18" s="3"/>
+      <c r="Q18" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
       <c r="T18" s="3"/>
@@ -2564,7 +2627,9 @@
       <c r="P19" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q19" s="3"/>
+      <c r="Q19" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
@@ -2652,7 +2717,9 @@
       <c r="P20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q20" s="3"/>
+      <c r="Q20" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
       <c r="T20" s="3"/>
@@ -2740,7 +2807,9 @@
       <c r="P21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q21" s="3"/>
+      <c r="Q21" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="R21" s="3"/>
       <c r="S21" s="3"/>
       <c r="T21" s="3"/>
@@ -2826,7 +2895,9 @@
       <c r="P22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q22" s="3"/>
+      <c r="Q22" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
       <c r="T22" s="3"/>
@@ -2864,7 +2935,9 @@
         <v>80</v>
       </c>
       <c r="AN22" s="3"/>
-      <c r="AO22" s="3"/>
+      <c r="AO22" s="24">
+        <v>46128</v>
+      </c>
       <c r="AP22" s="30"/>
       <c r="AQ22" s="3"/>
       <c r="AR22" s="3"/>
@@ -2924,7 +2997,9 @@
       <c r="P23" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q23" s="3"/>
+      <c r="Q23" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
@@ -2958,7 +3033,9 @@
       <c r="AL23" s="3"/>
       <c r="AM23" s="3"/>
       <c r="AN23" s="3"/>
-      <c r="AO23" s="3"/>
+      <c r="AO23" s="24">
+        <v>46128</v>
+      </c>
       <c r="AP23" s="30"/>
       <c r="AQ23" s="3"/>
       <c r="AR23" s="3"/>
@@ -3018,7 +3095,9 @@
       <c r="P24" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q24" s="3"/>
+      <c r="Q24" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
       <c r="T24" s="3"/>
@@ -3102,7 +3181,9 @@
       <c r="P25" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q25" s="3"/>
+      <c r="Q25" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="R25" s="3"/>
       <c r="S25" s="3"/>
       <c r="T25" s="3"/>
@@ -3194,7 +3275,9 @@
       <c r="P26" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q26" s="3"/>
+      <c r="Q26" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
       <c r="T26" s="3"/>
@@ -3280,7 +3363,9 @@
       <c r="P27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q27" s="3"/>
+      <c r="Q27" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="R27" s="3"/>
       <c r="S27" s="3"/>
       <c r="T27" s="3"/>
@@ -3303,7 +3388,9 @@
         <v>46114</v>
       </c>
       <c r="AG27" s="3"/>
-      <c r="AH27" s="3"/>
+      <c r="AH27" s="24">
+        <v>46128</v>
+      </c>
       <c r="AI27" s="3">
         <v>5</v>
       </c>
@@ -3372,7 +3459,9 @@
       <c r="P28" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="3"/>
+      <c r="Q28" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
       <c r="T28" s="3"/>
@@ -3458,7 +3547,9 @@
       <c r="P29" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q29" s="3"/>
+      <c r="Q29" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
@@ -3481,7 +3572,9 @@
         <v>46114</v>
       </c>
       <c r="AG29" s="3"/>
-      <c r="AH29" s="3"/>
+      <c r="AH29" s="24">
+        <v>46128</v>
+      </c>
       <c r="AI29" s="3">
         <v>5</v>
       </c>
@@ -3550,7 +3643,9 @@
       <c r="P30" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q30" s="3"/>
+      <c r="Q30" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
@@ -3587,7 +3682,9 @@
       <c r="AO30" s="3"/>
       <c r="AP30" s="30"/>
       <c r="AQ30" s="3"/>
-      <c r="AR30" s="3"/>
+      <c r="AR30" s="33" t="s">
+        <v>98</v>
+      </c>
       <c r="AS30" s="3"/>
       <c r="AT30" s="3"/>
       <c r="AU30" s="3"/>
@@ -3644,7 +3741,9 @@
       <c r="P31" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q31" s="3"/>
+      <c r="Q31" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="R31" s="3"/>
       <c r="S31" s="3"/>
       <c r="T31" s="3"/>
@@ -3732,7 +3831,9 @@
       <c r="P32" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q32" s="3"/>
+      <c r="Q32" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="R32" s="3"/>
       <c r="S32" s="3"/>
       <c r="T32" s="3"/>
@@ -3816,7 +3917,9 @@
       <c r="P33" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q33" s="3"/>
+      <c r="Q33" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="R33" s="3"/>
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
@@ -3906,7 +4009,9 @@
       <c r="P34" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q34" s="3"/>
+      <c r="Q34" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
@@ -3940,7 +4045,9 @@
       <c r="AL34" s="3"/>
       <c r="AM34" s="3"/>
       <c r="AN34" s="3"/>
-      <c r="AO34" s="3"/>
+      <c r="AO34" s="24">
+        <v>46128</v>
+      </c>
       <c r="AP34" s="30"/>
       <c r="AQ34" s="3"/>
       <c r="AR34" s="3"/>
@@ -3998,7 +4105,9 @@
       <c r="P35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q35" s="3"/>
+      <c r="Q35" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="R35" s="3"/>
       <c r="S35" s="3"/>
       <c r="T35" s="3"/>
@@ -4323,6 +4432,14 @@
         <v>22</v>
       </c>
     </row>
+    <row r="41" spans="1:50">
+      <c r="W41" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="X41" s="35" t="s">
+        <v>97</v>
+      </c>
+    </row>
     <row r="42" spans="1:50" ht="9.75" customHeight="1"/>
     <row r="57" spans="31:33">
       <c r="AE57" s="28"/>
@@ -4404,56 +4521,56 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="33"/>
-      <c r="R1" s="33"/>
-      <c r="S1" s="33"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="33"/>
-      <c r="V1" s="33"/>
-      <c r="W1" s="33"/>
-      <c r="X1" s="33"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="33"/>
-      <c r="AA1" s="33"/>
-      <c r="AB1" s="33"/>
-      <c r="AC1" s="33"/>
-      <c r="AD1" s="33"/>
-      <c r="AE1" s="33"/>
-      <c r="AF1" s="33"/>
-      <c r="AG1" s="33"/>
-      <c r="AH1" s="33"/>
-      <c r="AI1" s="33"/>
-      <c r="AJ1" s="33"/>
-      <c r="AK1" s="33"/>
-      <c r="AL1" s="33"/>
-      <c r="AM1" s="33"/>
-      <c r="AN1" s="33"/>
-      <c r="AO1" s="33"/>
-      <c r="AP1" s="33"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="36"/>
+      <c r="R1" s="36"/>
+      <c r="S1" s="36"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="36"/>
+      <c r="V1" s="36"/>
+      <c r="W1" s="36"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="36"/>
+      <c r="Z1" s="36"/>
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="36"/>
+      <c r="AC1" s="36"/>
+      <c r="AD1" s="36"/>
+      <c r="AE1" s="36"/>
+      <c r="AF1" s="36"/>
+      <c r="AG1" s="36"/>
+      <c r="AH1" s="36"/>
+      <c r="AI1" s="36"/>
+      <c r="AJ1" s="36"/>
+      <c r="AK1" s="36"/>
+      <c r="AL1" s="36"/>
+      <c r="AM1" s="36"/>
+      <c r="AN1" s="36"/>
+      <c r="AO1" s="36"/>
+      <c r="AP1" s="36"/>
     </row>
     <row r="2" spans="1:42" ht="30">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="35"/>
+      <c r="B2" s="38"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -4882,142 +4999,142 @@
       <c r="AP10" s="1"/>
     </row>
     <row r="11" spans="1:42">
-      <c r="A11" s="35">
+      <c r="A11" s="38">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="35"/>
-      <c r="J11" s="35"/>
-      <c r="K11" s="35"/>
-      <c r="L11" s="36"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="36"/>
-      <c r="S11" s="36"/>
-      <c r="T11" s="36"/>
-      <c r="U11" s="36"/>
-      <c r="V11" s="36"/>
-      <c r="W11" s="36"/>
-      <c r="X11" s="36"/>
-      <c r="Y11" s="36"/>
-      <c r="Z11" s="36"/>
-      <c r="AA11" s="36"/>
-      <c r="AB11" s="36"/>
-      <c r="AC11" s="36"/>
-      <c r="AD11" s="36"/>
-      <c r="AE11" s="36"/>
-      <c r="AF11" s="36"/>
-      <c r="AG11" s="36"/>
-      <c r="AH11" s="36"/>
-      <c r="AI11" s="36"/>
-      <c r="AJ11" s="36"/>
-      <c r="AK11" s="36"/>
-      <c r="AL11" s="36"/>
-      <c r="AM11" s="36"/>
-      <c r="AN11" s="36"/>
-      <c r="AO11" s="36"/>
-      <c r="AP11" s="33"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="L11" s="39"/>
+      <c r="M11" s="39"/>
+      <c r="N11" s="39"/>
+      <c r="O11" s="39"/>
+      <c r="P11" s="39"/>
+      <c r="Q11" s="39"/>
+      <c r="R11" s="39"/>
+      <c r="S11" s="39"/>
+      <c r="T11" s="39"/>
+      <c r="U11" s="39"/>
+      <c r="V11" s="39"/>
+      <c r="W11" s="39"/>
+      <c r="X11" s="39"/>
+      <c r="Y11" s="39"/>
+      <c r="Z11" s="39"/>
+      <c r="AA11" s="39"/>
+      <c r="AB11" s="39"/>
+      <c r="AC11" s="39"/>
+      <c r="AD11" s="39"/>
+      <c r="AE11" s="39"/>
+      <c r="AF11" s="39"/>
+      <c r="AG11" s="39"/>
+      <c r="AH11" s="39"/>
+      <c r="AI11" s="39"/>
+      <c r="AJ11" s="39"/>
+      <c r="AK11" s="39"/>
+      <c r="AL11" s="39"/>
+      <c r="AM11" s="39"/>
+      <c r="AN11" s="39"/>
+      <c r="AO11" s="39"/>
+      <c r="AP11" s="36"/>
     </row>
     <row r="12" spans="1:42">
-      <c r="A12" s="35"/>
+      <c r="A12" s="38"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="35"/>
-      <c r="J12" s="35"/>
-      <c r="K12" s="35"/>
-      <c r="L12" s="36"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="36"/>
-      <c r="S12" s="36"/>
-      <c r="T12" s="36"/>
-      <c r="U12" s="36"/>
-      <c r="V12" s="36"/>
-      <c r="W12" s="36"/>
-      <c r="X12" s="36"/>
-      <c r="Y12" s="36"/>
-      <c r="Z12" s="36"/>
-      <c r="AA12" s="36"/>
-      <c r="AB12" s="36"/>
-      <c r="AC12" s="36"/>
-      <c r="AD12" s="36"/>
-      <c r="AE12" s="36"/>
-      <c r="AF12" s="36"/>
-      <c r="AG12" s="36"/>
-      <c r="AH12" s="36"/>
-      <c r="AI12" s="36"/>
-      <c r="AJ12" s="36"/>
-      <c r="AK12" s="36"/>
-      <c r="AL12" s="36"/>
-      <c r="AM12" s="36"/>
-      <c r="AN12" s="36"/>
-      <c r="AO12" s="36"/>
-      <c r="AP12" s="33"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="L12" s="39"/>
+      <c r="M12" s="39"/>
+      <c r="N12" s="39"/>
+      <c r="O12" s="39"/>
+      <c r="P12" s="39"/>
+      <c r="Q12" s="39"/>
+      <c r="R12" s="39"/>
+      <c r="S12" s="39"/>
+      <c r="T12" s="39"/>
+      <c r="U12" s="39"/>
+      <c r="V12" s="39"/>
+      <c r="W12" s="39"/>
+      <c r="X12" s="39"/>
+      <c r="Y12" s="39"/>
+      <c r="Z12" s="39"/>
+      <c r="AA12" s="39"/>
+      <c r="AB12" s="39"/>
+      <c r="AC12" s="39"/>
+      <c r="AD12" s="39"/>
+      <c r="AE12" s="39"/>
+      <c r="AF12" s="39"/>
+      <c r="AG12" s="39"/>
+      <c r="AH12" s="39"/>
+      <c r="AI12" s="39"/>
+      <c r="AJ12" s="39"/>
+      <c r="AK12" s="39"/>
+      <c r="AL12" s="39"/>
+      <c r="AM12" s="39"/>
+      <c r="AN12" s="39"/>
+      <c r="AO12" s="39"/>
+      <c r="AP12" s="36"/>
     </row>
     <row r="13" spans="1:42">
-      <c r="A13" s="35"/>
+      <c r="A13" s="38"/>
       <c r="B13" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="35"/>
-      <c r="K13" s="35"/>
-      <c r="L13" s="36"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="36"/>
-      <c r="S13" s="36"/>
-      <c r="T13" s="36"/>
-      <c r="U13" s="36"/>
-      <c r="V13" s="36"/>
-      <c r="W13" s="36"/>
-      <c r="X13" s="36"/>
-      <c r="Y13" s="36"/>
-      <c r="Z13" s="36"/>
-      <c r="AA13" s="36"/>
-      <c r="AB13" s="36"/>
-      <c r="AC13" s="36"/>
-      <c r="AD13" s="36"/>
-      <c r="AE13" s="36"/>
-      <c r="AF13" s="36"/>
-      <c r="AG13" s="36"/>
-      <c r="AH13" s="36"/>
-      <c r="AI13" s="36"/>
-      <c r="AJ13" s="36"/>
-      <c r="AK13" s="36"/>
-      <c r="AL13" s="36"/>
-      <c r="AM13" s="36"/>
-      <c r="AN13" s="36"/>
-      <c r="AO13" s="36"/>
-      <c r="AP13" s="33"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="L13" s="39"/>
+      <c r="M13" s="39"/>
+      <c r="N13" s="39"/>
+      <c r="O13" s="39"/>
+      <c r="P13" s="39"/>
+      <c r="Q13" s="39"/>
+      <c r="R13" s="39"/>
+      <c r="S13" s="39"/>
+      <c r="T13" s="39"/>
+      <c r="U13" s="39"/>
+      <c r="V13" s="39"/>
+      <c r="W13" s="39"/>
+      <c r="X13" s="39"/>
+      <c r="Y13" s="39"/>
+      <c r="Z13" s="39"/>
+      <c r="AA13" s="39"/>
+      <c r="AB13" s="39"/>
+      <c r="AC13" s="39"/>
+      <c r="AD13" s="39"/>
+      <c r="AE13" s="39"/>
+      <c r="AF13" s="39"/>
+      <c r="AG13" s="39"/>
+      <c r="AH13" s="39"/>
+      <c r="AI13" s="39"/>
+      <c r="AJ13" s="39"/>
+      <c r="AK13" s="39"/>
+      <c r="AL13" s="39"/>
+      <c r="AM13" s="39"/>
+      <c r="AN13" s="39"/>
+      <c r="AO13" s="39"/>
+      <c r="AP13" s="36"/>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" s="2">

--- a/ТКИ-341_Реверс_Инжиниринг.xlsx
+++ b/ТКИ-341_Реверс_Инжиниринг.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\Reverse_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB183EA-6108-419C-A255-ECC02A8B1EA1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E38A76B-6F5F-44C0-BF55-CB9B92ECC966}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="103">
   <si>
     <t>ВЕДОМОСТЬ ПОСЕЩАЕМОСТИ ЗАНЯТИЙ СТУДЕНТАМИ ГРУППЫ ТКИ "Компьютерная безопасность" ИТТСУ РУТ (МИИТ)</t>
   </si>
@@ -360,6 +360,18 @@
   </si>
   <si>
     <t>VPN</t>
+  </si>
+  <si>
+    <t>Боди Иштан</t>
+  </si>
+  <si>
+    <t>Конференция</t>
+  </si>
+  <si>
+    <t>Зачет</t>
+  </si>
+  <si>
+    <t>Зачет по проектной деятельности</t>
   </si>
 </sst>
 </file>
@@ -463,7 +475,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -557,6 +569,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -566,6 +581,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -872,64 +891,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="14.45" customHeight="1">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="36"/>
-      <c r="R1" s="36"/>
-      <c r="S1" s="36"/>
-      <c r="T1" s="36"/>
-      <c r="U1" s="36"/>
-      <c r="V1" s="36"/>
-      <c r="W1" s="36"/>
-      <c r="X1" s="36"/>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="36"/>
-      <c r="AA1" s="36"/>
-      <c r="AB1" s="36"/>
-      <c r="AC1" s="36"/>
-      <c r="AD1" s="36"/>
-      <c r="AE1" s="36"/>
-      <c r="AF1" s="36"/>
-      <c r="AG1" s="36"/>
-      <c r="AH1" s="36"/>
-      <c r="AI1" s="36"/>
-      <c r="AJ1" s="36"/>
-      <c r="AK1" s="36"/>
-      <c r="AL1" s="36"/>
-      <c r="AM1" s="36"/>
-      <c r="AN1" s="36"/>
-      <c r="AO1" s="36"/>
-      <c r="AP1" s="36"/>
-      <c r="AQ1" s="36"/>
-      <c r="AR1" s="36"/>
-      <c r="AS1" s="36"/>
-      <c r="AT1" s="36"/>
-      <c r="AU1" s="36"/>
-      <c r="AV1" s="36"/>
-      <c r="AW1" s="36"/>
-      <c r="AX1" s="36"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37"/>
+      <c r="S1" s="37"/>
+      <c r="T1" s="37"/>
+      <c r="U1" s="37"/>
+      <c r="V1" s="37"/>
+      <c r="W1" s="37"/>
+      <c r="X1" s="37"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="37"/>
+      <c r="AA1" s="37"/>
+      <c r="AB1" s="37"/>
+      <c r="AC1" s="37"/>
+      <c r="AD1" s="37"/>
+      <c r="AE1" s="37"/>
+      <c r="AF1" s="37"/>
+      <c r="AG1" s="37"/>
+      <c r="AH1" s="37"/>
+      <c r="AI1" s="37"/>
+      <c r="AJ1" s="37"/>
+      <c r="AK1" s="37"/>
+      <c r="AL1" s="37"/>
+      <c r="AM1" s="37"/>
+      <c r="AN1" s="37"/>
+      <c r="AO1" s="37"/>
+      <c r="AP1" s="37"/>
+      <c r="AQ1" s="37"/>
+      <c r="AR1" s="37"/>
+      <c r="AS1" s="37"/>
+      <c r="AT1" s="37"/>
+      <c r="AU1" s="37"/>
+      <c r="AV1" s="37"/>
+      <c r="AW1" s="37"/>
+      <c r="AX1" s="37"/>
     </row>
     <row r="2" spans="1:50" ht="27.6" customHeight="1">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="38"/>
+      <c r="B2" s="39"/>
       <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1150,8 +1169,12 @@
       <c r="Q4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
+      <c r="R4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
@@ -1246,8 +1269,12 @@
       <c r="Q5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
+      <c r="R5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
@@ -1283,7 +1310,9 @@
         <v>76</v>
       </c>
       <c r="AN5" s="3"/>
-      <c r="AO5" s="3"/>
+      <c r="AO5" s="24">
+        <v>46135</v>
+      </c>
       <c r="AP5" s="30"/>
       <c r="AQ5" s="3"/>
       <c r="AR5" s="3"/>
@@ -1346,8 +1375,12 @@
       <c r="Q6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
+      <c r="R6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S6" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
@@ -1364,9 +1397,13 @@
         <v>46121</v>
       </c>
       <c r="AE6" s="3"/>
-      <c r="AF6" s="3"/>
+      <c r="AF6" s="24">
+        <v>46135</v>
+      </c>
       <c r="AG6" s="3"/>
-      <c r="AH6" s="3"/>
+      <c r="AH6" s="24">
+        <v>46135</v>
+      </c>
       <c r="AI6" s="3">
         <v>3</v>
       </c>
@@ -1444,8 +1481,12 @@
       <c r="Q7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
+      <c r="R7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S7" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
       <c r="V7" s="3"/>
@@ -1481,7 +1522,9 @@
         <v>78</v>
       </c>
       <c r="AN7" s="3"/>
-      <c r="AO7" s="3"/>
+      <c r="AO7" s="24">
+        <v>46135</v>
+      </c>
       <c r="AP7" s="30" t="s">
         <v>92</v>
       </c>
@@ -1546,8 +1589,12 @@
       <c r="Q8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
+      <c r="R8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
@@ -1562,7 +1609,9 @@
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3"/>
-      <c r="AF8" s="3"/>
+      <c r="AF8" s="24">
+        <v>46135</v>
+      </c>
       <c r="AG8" s="3"/>
       <c r="AH8" s="3"/>
       <c r="AI8" s="3">
@@ -1642,8 +1691,12 @@
       <c r="Q9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
+      <c r="R9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
@@ -1656,7 +1709,9 @@
         <v>46100</v>
       </c>
       <c r="AC9" s="3"/>
-      <c r="AD9" s="3"/>
+      <c r="AD9" s="24">
+        <v>46135</v>
+      </c>
       <c r="AE9" s="3"/>
       <c r="AF9" s="3"/>
       <c r="AG9" s="3"/>
@@ -1736,8 +1791,12 @@
       <c r="Q10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
+      <c r="R10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
@@ -1758,7 +1817,9 @@
         <v>46121</v>
       </c>
       <c r="AG10" s="3"/>
-      <c r="AH10" s="3"/>
+      <c r="AH10" s="24">
+        <v>46135</v>
+      </c>
       <c r="AI10" s="3">
         <v>4</v>
       </c>
@@ -1834,8 +1895,12 @@
       <c r="Q11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R11" s="5"/>
-      <c r="S11" s="5"/>
+      <c r="R11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="S11" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="T11" s="5"/>
       <c r="U11" s="5"/>
       <c r="V11" s="5"/>
@@ -1938,8 +2003,12 @@
       <c r="Q12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R12" s="5"/>
-      <c r="S12" s="5"/>
+      <c r="R12" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="S12" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="T12" s="5"/>
       <c r="U12" s="5"/>
       <c r="V12" s="5"/>
@@ -1977,10 +2046,12 @@
       <c r="AN12" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="AO12" s="5"/>
+      <c r="AO12" s="24">
+        <v>46135</v>
+      </c>
       <c r="AP12" s="31"/>
       <c r="AQ12" s="5"/>
-      <c r="AR12" s="5"/>
+      <c r="AR12" s="34"/>
       <c r="AS12" s="5"/>
       <c r="AT12" s="5"/>
       <c r="AU12" s="5"/>
@@ -2040,8 +2111,12 @@
       <c r="Q13" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R13" s="5"/>
-      <c r="S13" s="5"/>
+      <c r="R13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="S13" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="T13" s="5"/>
       <c r="U13" s="5"/>
       <c r="V13" s="5"/>
@@ -2140,8 +2215,12 @@
       <c r="Q14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
+      <c r="R14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
       <c r="V14" s="3"/>
@@ -2156,7 +2235,7 @@
       <c r="AE14" s="3"/>
       <c r="AF14" s="3"/>
       <c r="AG14" s="3"/>
-      <c r="AH14" s="3"/>
+      <c r="AH14" s="42"/>
       <c r="AI14" s="3">
         <v>2</v>
       </c>
@@ -2234,8 +2313,12 @@
       <c r="Q15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
+      <c r="R15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
       <c r="V15" s="3"/>
@@ -2330,8 +2413,12 @@
       <c r="Q16" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
+      <c r="R16" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
@@ -2367,7 +2454,9 @@
         <v>86</v>
       </c>
       <c r="AN16" s="3"/>
-      <c r="AO16" s="3"/>
+      <c r="AO16" s="24">
+        <v>46135</v>
+      </c>
       <c r="AP16" s="30" t="s">
         <v>91</v>
       </c>
@@ -2434,8 +2523,12 @@
       <c r="Q17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
+      <c r="R17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>
@@ -2473,7 +2566,9 @@
       <c r="AN17" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="AO17" s="3"/>
+      <c r="AO17" s="24">
+        <v>46135</v>
+      </c>
       <c r="AP17" s="30"/>
       <c r="AQ17" s="3"/>
       <c r="AR17" s="3"/>
@@ -2536,8 +2631,12 @@
       <c r="Q18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
+      <c r="R18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="T18" s="3"/>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
@@ -2569,10 +2668,12 @@
       <c r="AL18" s="3"/>
       <c r="AM18" s="3"/>
       <c r="AN18" s="3"/>
-      <c r="AO18" s="3"/>
+      <c r="AO18" s="24">
+        <v>46135</v>
+      </c>
       <c r="AP18" s="30"/>
       <c r="AQ18" s="3"/>
-      <c r="AR18" s="3"/>
+      <c r="AR18" s="33"/>
       <c r="AS18" s="3"/>
       <c r="AT18" s="3"/>
       <c r="AU18" s="3"/>
@@ -2630,8 +2731,12 @@
       <c r="Q19" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
+      <c r="R19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S19" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
@@ -2644,7 +2749,9 @@
         <v>46100</v>
       </c>
       <c r="AC19" s="3"/>
-      <c r="AD19" s="3"/>
+      <c r="AD19" s="24">
+        <v>46135</v>
+      </c>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
@@ -2720,8 +2827,12 @@
       <c r="Q20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R20" s="3"/>
-      <c r="S20" s="3"/>
+      <c r="R20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
@@ -2810,8 +2921,12 @@
       <c r="Q21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R21" s="3"/>
-      <c r="S21" s="3"/>
+      <c r="R21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="T21" s="3"/>
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
@@ -2826,7 +2941,9 @@
       <c r="AC21" s="3"/>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3"/>
-      <c r="AF21" s="3"/>
+      <c r="AF21" s="24">
+        <v>46135</v>
+      </c>
       <c r="AG21" s="3"/>
       <c r="AH21" s="3"/>
       <c r="AI21" s="3">
@@ -2898,8 +3015,12 @@
       <c r="Q22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R22" s="3"/>
-      <c r="S22" s="3"/>
+      <c r="R22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="T22" s="3"/>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
@@ -3000,8 +3121,12 @@
       <c r="Q23" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R23" s="3"/>
-      <c r="S23" s="3"/>
+      <c r="R23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
       <c r="V23" s="3"/>
@@ -3098,8 +3223,12 @@
       <c r="Q24" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R24" s="3"/>
-      <c r="S24" s="3"/>
+      <c r="R24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
@@ -3184,8 +3313,12 @@
       <c r="Q25" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
+      <c r="R25" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S25" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="T25" s="3"/>
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
@@ -3217,7 +3350,9 @@
       <c r="AL25" s="3"/>
       <c r="AM25" s="3"/>
       <c r="AN25" s="3"/>
-      <c r="AO25" s="3"/>
+      <c r="AO25" s="24">
+        <v>46135</v>
+      </c>
       <c r="AP25" s="30"/>
       <c r="AQ25" s="3"/>
       <c r="AR25" s="3"/>
@@ -3278,8 +3413,12 @@
       <c r="Q26" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R26" s="3"/>
-      <c r="S26" s="3"/>
+      <c r="R26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
@@ -3366,8 +3505,12 @@
       <c r="Q27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R27" s="3"/>
-      <c r="S27" s="3"/>
+      <c r="R27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
       <c r="V27" s="3"/>
@@ -3399,7 +3542,9 @@
       <c r="AL27" s="3"/>
       <c r="AM27" s="3"/>
       <c r="AN27" s="3"/>
-      <c r="AO27" s="3"/>
+      <c r="AO27" s="24">
+        <v>46135</v>
+      </c>
       <c r="AP27" s="30"/>
       <c r="AQ27" s="3"/>
       <c r="AR27" s="3"/>
@@ -3462,8 +3607,12 @@
       <c r="Q28" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R28" s="3"/>
-      <c r="S28" s="3"/>
+      <c r="R28" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S28" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
@@ -3550,8 +3699,12 @@
       <c r="Q29" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R29" s="3"/>
-      <c r="S29" s="3"/>
+      <c r="R29" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="T29" s="3"/>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
@@ -3583,7 +3736,9 @@
       <c r="AL29" s="3"/>
       <c r="AM29" s="3"/>
       <c r="AN29" s="3"/>
-      <c r="AO29" s="3"/>
+      <c r="AO29" s="24">
+        <v>46135</v>
+      </c>
       <c r="AP29" s="30"/>
       <c r="AQ29" s="3"/>
       <c r="AR29" s="3"/>
@@ -3646,8 +3801,12 @@
       <c r="Q30" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R30" s="3"/>
-      <c r="S30" s="3"/>
+      <c r="R30" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S30" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
@@ -3679,7 +3838,9 @@
       <c r="AL30" s="3"/>
       <c r="AM30" s="3"/>
       <c r="AN30" s="3"/>
-      <c r="AO30" s="3"/>
+      <c r="AO30" s="24">
+        <v>46135</v>
+      </c>
       <c r="AP30" s="30"/>
       <c r="AQ30" s="3"/>
       <c r="AR30" s="33" t="s">
@@ -3744,8 +3905,12 @@
       <c r="Q31" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R31" s="3"/>
-      <c r="S31" s="3"/>
+      <c r="R31" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S31" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="T31" s="3"/>
       <c r="U31" s="3"/>
       <c r="V31" s="3"/>
@@ -3762,9 +3927,13 @@
         <v>46121</v>
       </c>
       <c r="AE31" s="3"/>
-      <c r="AF31" s="3"/>
+      <c r="AF31" s="24">
+        <v>46135</v>
+      </c>
       <c r="AG31" s="3"/>
-      <c r="AH31" s="3"/>
+      <c r="AH31" s="24">
+        <v>46135</v>
+      </c>
       <c r="AI31" s="3">
         <v>3</v>
       </c>
@@ -3834,8 +4003,12 @@
       <c r="Q32" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R32" s="3"/>
-      <c r="S32" s="3"/>
+      <c r="R32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
@@ -3920,8 +4093,12 @@
       <c r="Q33" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R33" s="3"/>
-      <c r="S33" s="3"/>
+      <c r="R33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
@@ -3942,7 +4119,9 @@
         <v>46121</v>
       </c>
       <c r="AG33" s="3"/>
-      <c r="AH33" s="3"/>
+      <c r="AH33" s="24">
+        <v>46135</v>
+      </c>
       <c r="AI33" s="3">
         <v>4</v>
       </c>
@@ -4012,8 +4191,12 @@
       <c r="Q34" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R34" s="3"/>
-      <c r="S34" s="3"/>
+      <c r="R34" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S34" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="T34" s="3"/>
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
@@ -4108,8 +4291,12 @@
       <c r="Q35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R35" s="3"/>
-      <c r="S35" s="3"/>
+      <c r="R35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="T35" s="3"/>
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
@@ -4124,7 +4311,7 @@
       <c r="AE35" s="3"/>
       <c r="AF35" s="3"/>
       <c r="AG35" s="3"/>
-      <c r="AH35" s="3"/>
+      <c r="AH35" s="42"/>
       <c r="AI35" s="3">
         <v>2</v>
       </c>
@@ -4145,23 +4332,61 @@
       <c r="AX35" s="1"/>
     </row>
     <row r="36" spans="1:50">
-      <c r="C36" s="9"/>
+      <c r="A36" s="36">
+        <v>33</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C36" s="9">
+        <v>17</v>
+      </c>
       <c r="D36" s="9"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="9"/>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
-      <c r="N36" s="3"/>
-      <c r="O36" s="3"/>
-      <c r="P36" s="3"/>
-      <c r="Q36" s="3"/>
-      <c r="R36" s="3"/>
-      <c r="S36" s="3"/>
+      <c r="E36" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F36" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="G36" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="H36" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="I36" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="K36" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="L36" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="M36" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="N36" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="O36" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="P36" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q36" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="R36" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S36" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="T36" s="3"/>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
@@ -4439,8 +4664,21 @@
       <c r="X41" s="35" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="42" spans="1:50" ht="9.75" customHeight="1"/>
+      <c r="Y41" s="41" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="42" spans="1:50" ht="9.75" customHeight="1">
+      <c r="W42" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z42" s="41" t="s">
+        <v>102</v>
+      </c>
+    </row>
     <row r="57" spans="31:33">
       <c r="AE57" s="28"/>
       <c r="AF57" s="29"/>
@@ -4521,56 +4759,56 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="36"/>
-      <c r="R1" s="36"/>
-      <c r="S1" s="36"/>
-      <c r="T1" s="36"/>
-      <c r="U1" s="36"/>
-      <c r="V1" s="36"/>
-      <c r="W1" s="36"/>
-      <c r="X1" s="36"/>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="36"/>
-      <c r="AA1" s="36"/>
-      <c r="AB1" s="36"/>
-      <c r="AC1" s="36"/>
-      <c r="AD1" s="36"/>
-      <c r="AE1" s="36"/>
-      <c r="AF1" s="36"/>
-      <c r="AG1" s="36"/>
-      <c r="AH1" s="36"/>
-      <c r="AI1" s="36"/>
-      <c r="AJ1" s="36"/>
-      <c r="AK1" s="36"/>
-      <c r="AL1" s="36"/>
-      <c r="AM1" s="36"/>
-      <c r="AN1" s="36"/>
-      <c r="AO1" s="36"/>
-      <c r="AP1" s="36"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37"/>
+      <c r="S1" s="37"/>
+      <c r="T1" s="37"/>
+      <c r="U1" s="37"/>
+      <c r="V1" s="37"/>
+      <c r="W1" s="37"/>
+      <c r="X1" s="37"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="37"/>
+      <c r="AA1" s="37"/>
+      <c r="AB1" s="37"/>
+      <c r="AC1" s="37"/>
+      <c r="AD1" s="37"/>
+      <c r="AE1" s="37"/>
+      <c r="AF1" s="37"/>
+      <c r="AG1" s="37"/>
+      <c r="AH1" s="37"/>
+      <c r="AI1" s="37"/>
+      <c r="AJ1" s="37"/>
+      <c r="AK1" s="37"/>
+      <c r="AL1" s="37"/>
+      <c r="AM1" s="37"/>
+      <c r="AN1" s="37"/>
+      <c r="AO1" s="37"/>
+      <c r="AP1" s="37"/>
     </row>
     <row r="2" spans="1:42" ht="30">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="38"/>
+      <c r="B2" s="39"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -4999,142 +5237,142 @@
       <c r="AP10" s="1"/>
     </row>
     <row r="11" spans="1:42">
-      <c r="A11" s="38">
+      <c r="A11" s="39">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="38"/>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="L11" s="39"/>
-      <c r="M11" s="39"/>
-      <c r="N11" s="39"/>
-      <c r="O11" s="39"/>
-      <c r="P11" s="39"/>
-      <c r="Q11" s="39"/>
-      <c r="R11" s="39"/>
-      <c r="S11" s="39"/>
-      <c r="T11" s="39"/>
-      <c r="U11" s="39"/>
-      <c r="V11" s="39"/>
-      <c r="W11" s="39"/>
-      <c r="X11" s="39"/>
-      <c r="Y11" s="39"/>
-      <c r="Z11" s="39"/>
-      <c r="AA11" s="39"/>
-      <c r="AB11" s="39"/>
-      <c r="AC11" s="39"/>
-      <c r="AD11" s="39"/>
-      <c r="AE11" s="39"/>
-      <c r="AF11" s="39"/>
-      <c r="AG11" s="39"/>
-      <c r="AH11" s="39"/>
-      <c r="AI11" s="39"/>
-      <c r="AJ11" s="39"/>
-      <c r="AK11" s="39"/>
-      <c r="AL11" s="39"/>
-      <c r="AM11" s="39"/>
-      <c r="AN11" s="39"/>
-      <c r="AO11" s="39"/>
-      <c r="AP11" s="36"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="40"/>
+      <c r="M11" s="40"/>
+      <c r="N11" s="40"/>
+      <c r="O11" s="40"/>
+      <c r="P11" s="40"/>
+      <c r="Q11" s="40"/>
+      <c r="R11" s="40"/>
+      <c r="S11" s="40"/>
+      <c r="T11" s="40"/>
+      <c r="U11" s="40"/>
+      <c r="V11" s="40"/>
+      <c r="W11" s="40"/>
+      <c r="X11" s="40"/>
+      <c r="Y11" s="40"/>
+      <c r="Z11" s="40"/>
+      <c r="AA11" s="40"/>
+      <c r="AB11" s="40"/>
+      <c r="AC11" s="40"/>
+      <c r="AD11" s="40"/>
+      <c r="AE11" s="40"/>
+      <c r="AF11" s="40"/>
+      <c r="AG11" s="40"/>
+      <c r="AH11" s="40"/>
+      <c r="AI11" s="40"/>
+      <c r="AJ11" s="40"/>
+      <c r="AK11" s="40"/>
+      <c r="AL11" s="40"/>
+      <c r="AM11" s="40"/>
+      <c r="AN11" s="40"/>
+      <c r="AO11" s="40"/>
+      <c r="AP11" s="37"/>
     </row>
     <row r="12" spans="1:42">
-      <c r="A12" s="38"/>
+      <c r="A12" s="39"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="39"/>
-      <c r="M12" s="39"/>
-      <c r="N12" s="39"/>
-      <c r="O12" s="39"/>
-      <c r="P12" s="39"/>
-      <c r="Q12" s="39"/>
-      <c r="R12" s="39"/>
-      <c r="S12" s="39"/>
-      <c r="T12" s="39"/>
-      <c r="U12" s="39"/>
-      <c r="V12" s="39"/>
-      <c r="W12" s="39"/>
-      <c r="X12" s="39"/>
-      <c r="Y12" s="39"/>
-      <c r="Z12" s="39"/>
-      <c r="AA12" s="39"/>
-      <c r="AB12" s="39"/>
-      <c r="AC12" s="39"/>
-      <c r="AD12" s="39"/>
-      <c r="AE12" s="39"/>
-      <c r="AF12" s="39"/>
-      <c r="AG12" s="39"/>
-      <c r="AH12" s="39"/>
-      <c r="AI12" s="39"/>
-      <c r="AJ12" s="39"/>
-      <c r="AK12" s="39"/>
-      <c r="AL12" s="39"/>
-      <c r="AM12" s="39"/>
-      <c r="AN12" s="39"/>
-      <c r="AO12" s="39"/>
-      <c r="AP12" s="36"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="39"/>
+      <c r="K12" s="39"/>
+      <c r="L12" s="40"/>
+      <c r="M12" s="40"/>
+      <c r="N12" s="40"/>
+      <c r="O12" s="40"/>
+      <c r="P12" s="40"/>
+      <c r="Q12" s="40"/>
+      <c r="R12" s="40"/>
+      <c r="S12" s="40"/>
+      <c r="T12" s="40"/>
+      <c r="U12" s="40"/>
+      <c r="V12" s="40"/>
+      <c r="W12" s="40"/>
+      <c r="X12" s="40"/>
+      <c r="Y12" s="40"/>
+      <c r="Z12" s="40"/>
+      <c r="AA12" s="40"/>
+      <c r="AB12" s="40"/>
+      <c r="AC12" s="40"/>
+      <c r="AD12" s="40"/>
+      <c r="AE12" s="40"/>
+      <c r="AF12" s="40"/>
+      <c r="AG12" s="40"/>
+      <c r="AH12" s="40"/>
+      <c r="AI12" s="40"/>
+      <c r="AJ12" s="40"/>
+      <c r="AK12" s="40"/>
+      <c r="AL12" s="40"/>
+      <c r="AM12" s="40"/>
+      <c r="AN12" s="40"/>
+      <c r="AO12" s="40"/>
+      <c r="AP12" s="37"/>
     </row>
     <row r="13" spans="1:42">
-      <c r="A13" s="38"/>
+      <c r="A13" s="39"/>
       <c r="B13" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="38"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="L13" s="39"/>
-      <c r="M13" s="39"/>
-      <c r="N13" s="39"/>
-      <c r="O13" s="39"/>
-      <c r="P13" s="39"/>
-      <c r="Q13" s="39"/>
-      <c r="R13" s="39"/>
-      <c r="S13" s="39"/>
-      <c r="T13" s="39"/>
-      <c r="U13" s="39"/>
-      <c r="V13" s="39"/>
-      <c r="W13" s="39"/>
-      <c r="X13" s="39"/>
-      <c r="Y13" s="39"/>
-      <c r="Z13" s="39"/>
-      <c r="AA13" s="39"/>
-      <c r="AB13" s="39"/>
-      <c r="AC13" s="39"/>
-      <c r="AD13" s="39"/>
-      <c r="AE13" s="39"/>
-      <c r="AF13" s="39"/>
-      <c r="AG13" s="39"/>
-      <c r="AH13" s="39"/>
-      <c r="AI13" s="39"/>
-      <c r="AJ13" s="39"/>
-      <c r="AK13" s="39"/>
-      <c r="AL13" s="39"/>
-      <c r="AM13" s="39"/>
-      <c r="AN13" s="39"/>
-      <c r="AO13" s="39"/>
-      <c r="AP13" s="36"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="39"/>
+      <c r="L13" s="40"/>
+      <c r="M13" s="40"/>
+      <c r="N13" s="40"/>
+      <c r="O13" s="40"/>
+      <c r="P13" s="40"/>
+      <c r="Q13" s="40"/>
+      <c r="R13" s="40"/>
+      <c r="S13" s="40"/>
+      <c r="T13" s="40"/>
+      <c r="U13" s="40"/>
+      <c r="V13" s="40"/>
+      <c r="W13" s="40"/>
+      <c r="X13" s="40"/>
+      <c r="Y13" s="40"/>
+      <c r="Z13" s="40"/>
+      <c r="AA13" s="40"/>
+      <c r="AB13" s="40"/>
+      <c r="AC13" s="40"/>
+      <c r="AD13" s="40"/>
+      <c r="AE13" s="40"/>
+      <c r="AF13" s="40"/>
+      <c r="AG13" s="40"/>
+      <c r="AH13" s="40"/>
+      <c r="AI13" s="40"/>
+      <c r="AJ13" s="40"/>
+      <c r="AK13" s="40"/>
+      <c r="AL13" s="40"/>
+      <c r="AM13" s="40"/>
+      <c r="AN13" s="40"/>
+      <c r="AO13" s="40"/>
+      <c r="AP13" s="37"/>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" s="2">
@@ -6290,6 +6528,33 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="AO11:AO13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
+    <mergeCell ref="AN11:AN13"/>
+    <mergeCell ref="AE11:AE13"/>
+    <mergeCell ref="AF11:AF13"/>
+    <mergeCell ref="AG11:AG13"/>
+    <mergeCell ref="AH11:AH13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="Z11:Z13"/>
+    <mergeCell ref="AA11:AA13"/>
+    <mergeCell ref="AB11:AB13"/>
+    <mergeCell ref="AC11:AC13"/>
+    <mergeCell ref="AD11:AD13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="V11:V13"/>
+    <mergeCell ref="W11:W13"/>
+    <mergeCell ref="X11:X13"/>
+    <mergeCell ref="Y11:Y13"/>
+    <mergeCell ref="P11:P13"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="T11:T13"/>
     <mergeCell ref="A1:AP1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A11:A13"/>
@@ -6306,33 +6571,6 @@
     <mergeCell ref="M11:M13"/>
     <mergeCell ref="N11:N13"/>
     <mergeCell ref="O11:O13"/>
-    <mergeCell ref="P11:P13"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="T11:T13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="V11:V13"/>
-    <mergeCell ref="W11:W13"/>
-    <mergeCell ref="X11:X13"/>
-    <mergeCell ref="Y11:Y13"/>
-    <mergeCell ref="Z11:Z13"/>
-    <mergeCell ref="AA11:AA13"/>
-    <mergeCell ref="AB11:AB13"/>
-    <mergeCell ref="AC11:AC13"/>
-    <mergeCell ref="AD11:AD13"/>
-    <mergeCell ref="AE11:AE13"/>
-    <mergeCell ref="AF11:AF13"/>
-    <mergeCell ref="AG11:AG13"/>
-    <mergeCell ref="AH11:AH13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="AO11:AO13"/>
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="AN11:AN13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ТКИ-341_Реверс_Инжиниринг.xlsx
+++ b/ТКИ-341_Реверс_Инжиниринг.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\Reverse_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E38A76B-6F5F-44C0-BF55-CB9B92ECC966}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B77C032-7E55-41AA-B287-8C65D0FDEF30}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="108">
   <si>
     <t>ВЕДОМОСТЬ ПОСЕЩАЕМОСТИ ЗАНЯТИЙ СТУДЕНТАМИ ГРУППЫ ТКИ "Компьютерная безопасность" ИТТСУ РУТ (МИИТ)</t>
   </si>
@@ -372,6 +372,21 @@
   </si>
   <si>
     <t>Зачет по проектной деятельности</t>
+  </si>
+  <si>
+    <t>Иконников, Наседкин (13)</t>
+  </si>
+  <si>
+    <t>сумма элементов массива с нечетными значениями</t>
+  </si>
+  <si>
+    <t>Кручинин, Дамир (5)</t>
+  </si>
+  <si>
+    <t>площадь или периметр треугольника</t>
+  </si>
+  <si>
+    <t>потенциальная энергия пружины</t>
   </si>
 </sst>
 </file>
@@ -475,7 +490,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -572,6 +587,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -583,8 +605,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -862,7 +883,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AX63"/>
+  <dimension ref="A1:BA63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="37.28515625" customWidth="1"/>
@@ -886,69 +907,74 @@
     <col min="30" max="30" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="9" style="32"/>
+    <col min="36" max="36" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="9" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" ht="14.45" customHeight="1">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:53" ht="14.45" customHeight="1">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="37"/>
-      <c r="R1" s="37"/>
-      <c r="S1" s="37"/>
-      <c r="T1" s="37"/>
-      <c r="U1" s="37"/>
-      <c r="V1" s="37"/>
-      <c r="W1" s="37"/>
-      <c r="X1" s="37"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="37"/>
-      <c r="AA1" s="37"/>
-      <c r="AB1" s="37"/>
-      <c r="AC1" s="37"/>
-      <c r="AD1" s="37"/>
-      <c r="AE1" s="37"/>
-      <c r="AF1" s="37"/>
-      <c r="AG1" s="37"/>
-      <c r="AH1" s="37"/>
-      <c r="AI1" s="37"/>
-      <c r="AJ1" s="37"/>
-      <c r="AK1" s="37"/>
-      <c r="AL1" s="37"/>
-      <c r="AM1" s="37"/>
-      <c r="AN1" s="37"/>
-      <c r="AO1" s="37"/>
-      <c r="AP1" s="37"/>
-      <c r="AQ1" s="37"/>
-      <c r="AR1" s="37"/>
-      <c r="AS1" s="37"/>
-      <c r="AT1" s="37"/>
-      <c r="AU1" s="37"/>
-      <c r="AV1" s="37"/>
-      <c r="AW1" s="37"/>
-      <c r="AX1" s="37"/>
-    </row>
-    <row r="2" spans="1:50" ht="27.6" customHeight="1">
-      <c r="A2" s="39" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40"/>
+      <c r="Q1" s="40"/>
+      <c r="R1" s="40"/>
+      <c r="S1" s="40"/>
+      <c r="T1" s="40"/>
+      <c r="U1" s="40"/>
+      <c r="V1" s="40"/>
+      <c r="W1" s="40"/>
+      <c r="X1" s="40"/>
+      <c r="Y1" s="40"/>
+      <c r="Z1" s="40"/>
+      <c r="AA1" s="40"/>
+      <c r="AB1" s="40"/>
+      <c r="AC1" s="40"/>
+      <c r="AD1" s="40"/>
+      <c r="AE1" s="40"/>
+      <c r="AF1" s="40"/>
+      <c r="AG1" s="40"/>
+      <c r="AH1" s="40"/>
+      <c r="AI1" s="40"/>
+      <c r="AJ1" s="40"/>
+      <c r="AK1" s="40"/>
+      <c r="AL1" s="40"/>
+      <c r="AM1" s="40"/>
+      <c r="AN1" s="40"/>
+      <c r="AO1" s="40"/>
+      <c r="AP1" s="40"/>
+      <c r="AQ1" s="40"/>
+      <c r="AR1" s="40"/>
+      <c r="AS1" s="40"/>
+      <c r="AT1" s="40"/>
+      <c r="AU1" s="40"/>
+      <c r="AV1" s="40"/>
+      <c r="AW1" s="40"/>
+      <c r="AX1" s="40"/>
+      <c r="AY1" s="40"/>
+      <c r="AZ1" s="40"/>
+      <c r="BA1" s="40"/>
+    </row>
+    <row r="2" spans="1:53" ht="27.6" customHeight="1">
+      <c r="A2" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="39"/>
+      <c r="B2" s="42"/>
       <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1041,27 +1067,30 @@
       <c r="AJ2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK2" s="3"/>
-      <c r="AL2" s="3" t="s">
+      <c r="AK2" s="37"/>
+      <c r="AL2" s="3"/>
+      <c r="AM2" s="37"/>
+      <c r="AN2" s="37"/>
+      <c r="AO2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="AM2" s="3"/>
-      <c r="AO2" s="3"/>
-      <c r="AP2" s="30" t="s">
+      <c r="AP2" s="3"/>
+      <c r="AR2" s="3"/>
+      <c r="AS2" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="AQ2" s="3"/>
-      <c r="AR2" s="3"/>
-      <c r="AS2" s="3"/>
       <c r="AT2" s="3"/>
       <c r="AU2" s="3"/>
       <c r="AV2" s="3"/>
       <c r="AW2" s="3"/>
-      <c r="AX2" s="1" t="s">
+      <c r="AX2" s="3"/>
+      <c r="AY2" s="3"/>
+      <c r="AZ2" s="3"/>
+      <c r="BA2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:50">
+    <row r="3" spans="1:53">
       <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
@@ -1107,17 +1136,20 @@
       <c r="AM3" s="19"/>
       <c r="AN3" s="19"/>
       <c r="AO3" s="19"/>
-      <c r="AP3" s="30"/>
+      <c r="AP3" s="19"/>
       <c r="AQ3" s="19"/>
       <c r="AR3" s="19"/>
-      <c r="AS3" s="19"/>
+      <c r="AS3" s="30"/>
       <c r="AT3" s="19"/>
       <c r="AU3" s="19"/>
       <c r="AV3" s="19"/>
       <c r="AW3" s="19"/>
-      <c r="AX3" s="21"/>
-    </row>
-    <row r="4" spans="1:50" ht="105">
+      <c r="AX3" s="19"/>
+      <c r="AY3" s="19"/>
+      <c r="AZ3" s="19"/>
+      <c r="BA3" s="21"/>
+    </row>
+    <row r="4" spans="1:53" ht="105">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -1196,28 +1228,31 @@
         <v>3</v>
       </c>
       <c r="AJ4" s="3"/>
-      <c r="AK4" s="3"/>
-      <c r="AL4" s="28" t="s">
+      <c r="AK4" s="37"/>
+      <c r="AL4" s="3"/>
+      <c r="AM4" s="37"/>
+      <c r="AN4" s="37"/>
+      <c r="AO4" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="AM4" s="29" t="s">
+      <c r="AP4" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="AN4" s="28" t="s">
+      <c r="AQ4" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="AO4" s="3"/>
-      <c r="AP4" s="30"/>
-      <c r="AQ4" s="3"/>
       <c r="AR4" s="3"/>
-      <c r="AS4" s="3"/>
+      <c r="AS4" s="30"/>
       <c r="AT4" s="3"/>
       <c r="AU4" s="3"/>
       <c r="AV4" s="3"/>
       <c r="AW4" s="3"/>
-      <c r="AX4" s="1"/>
-    </row>
-    <row r="5" spans="1:50">
+      <c r="AX4" s="3"/>
+      <c r="AY4" s="3"/>
+      <c r="AZ4" s="3"/>
+      <c r="BA4" s="1"/>
+    </row>
+    <row r="5" spans="1:53">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1273,7 +1308,7 @@
         <v>17</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
@@ -1302,28 +1337,31 @@
         <v>5</v>
       </c>
       <c r="AJ5" s="3"/>
-      <c r="AK5" s="3"/>
-      <c r="AL5" s="28" t="s">
+      <c r="AK5" s="37"/>
+      <c r="AL5" s="3"/>
+      <c r="AM5" s="37"/>
+      <c r="AN5" s="37"/>
+      <c r="AO5" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="AM5" s="28" t="s">
+      <c r="AP5" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="AN5" s="3"/>
-      <c r="AO5" s="24">
+      <c r="AQ5" s="3"/>
+      <c r="AR5" s="24">
         <v>46135</v>
       </c>
-      <c r="AP5" s="30"/>
-      <c r="AQ5" s="3"/>
-      <c r="AR5" s="3"/>
-      <c r="AS5" s="3"/>
+      <c r="AS5" s="30"/>
       <c r="AT5" s="3"/>
       <c r="AU5" s="3"/>
       <c r="AV5" s="3"/>
       <c r="AW5" s="3"/>
-      <c r="AX5" s="1"/>
-    </row>
-    <row r="6" spans="1:50" ht="105">
+      <c r="AX5" s="3"/>
+      <c r="AY5" s="3"/>
+      <c r="AZ5" s="3"/>
+      <c r="BA5" s="1"/>
+    </row>
+    <row r="6" spans="1:53" ht="105">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1408,28 +1446,31 @@
         <v>3</v>
       </c>
       <c r="AJ6" s="3"/>
-      <c r="AK6" s="3"/>
-      <c r="AL6" s="28" t="s">
+      <c r="AK6" s="37"/>
+      <c r="AL6" s="3"/>
+      <c r="AM6" s="37"/>
+      <c r="AN6" s="37"/>
+      <c r="AO6" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="AM6" s="29" t="s">
+      <c r="AP6" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="AN6" s="28" t="s">
+      <c r="AQ6" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="AO6" s="3"/>
-      <c r="AP6" s="30"/>
-      <c r="AQ6" s="3"/>
       <c r="AR6" s="3"/>
-      <c r="AS6" s="3"/>
+      <c r="AS6" s="30"/>
       <c r="AT6" s="3"/>
       <c r="AU6" s="3"/>
       <c r="AV6" s="3"/>
       <c r="AW6" s="3"/>
-      <c r="AX6" s="1"/>
-    </row>
-    <row r="7" spans="1:50" ht="60">
+      <c r="AX6" s="3"/>
+      <c r="AY6" s="3"/>
+      <c r="AZ6" s="3"/>
+      <c r="BA6" s="1"/>
+    </row>
+    <row r="7" spans="1:53" ht="90">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -1513,33 +1554,44 @@
       <c r="AI7" s="3">
         <v>5</v>
       </c>
-      <c r="AJ7" s="3"/>
-      <c r="AK7" s="3"/>
-      <c r="AL7" s="28" t="s">
+      <c r="AJ7" s="44">
+        <v>46135</v>
+      </c>
+      <c r="AK7" s="34">
+        <v>12</v>
+      </c>
+      <c r="AL7" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="AM7" s="5"/>
+      <c r="AN7" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="AO7" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="AM7" s="29" t="s">
+      <c r="AP7" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="AN7" s="3"/>
-      <c r="AO7" s="24">
+      <c r="AQ7" s="3"/>
+      <c r="AR7" s="24">
         <v>46135</v>
       </c>
-      <c r="AP7" s="30" t="s">
+      <c r="AS7" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="AQ7" s="3" t="s">
+      <c r="AT7" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="AR7" s="33"/>
-      <c r="AS7" s="3"/>
-      <c r="AT7" s="3"/>
-      <c r="AU7" s="3"/>
+      <c r="AU7" s="33"/>
       <c r="AV7" s="3"/>
       <c r="AW7" s="3"/>
-      <c r="AX7" s="1"/>
-    </row>
-    <row r="8" spans="1:50" ht="18" customHeight="1">
+      <c r="AX7" s="3"/>
+      <c r="AY7" s="3"/>
+      <c r="AZ7" s="3"/>
+      <c r="BA7" s="1"/>
+    </row>
+    <row r="8" spans="1:53" ht="105">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -1618,28 +1670,35 @@
         <v>3</v>
       </c>
       <c r="AJ8" s="3"/>
-      <c r="AK8" s="3"/>
-      <c r="AL8" s="28" t="s">
+      <c r="AK8" s="37"/>
+      <c r="AL8" s="3"/>
+      <c r="AM8" s="24">
+        <v>46135</v>
+      </c>
+      <c r="AN8" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="AO8" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="AM8" s="29" t="s">
+      <c r="AP8" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="AN8" s="28" t="s">
+      <c r="AQ8" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="AO8" s="3"/>
-      <c r="AP8" s="30"/>
-      <c r="AQ8" s="3"/>
       <c r="AR8" s="3"/>
-      <c r="AS8" s="3"/>
+      <c r="AS8" s="30"/>
       <c r="AT8" s="3"/>
       <c r="AU8" s="3"/>
       <c r="AV8" s="3"/>
       <c r="AW8" s="3"/>
-      <c r="AX8" s="1"/>
-    </row>
-    <row r="9" spans="1:50" ht="45">
+      <c r="AX8" s="3"/>
+      <c r="AY8" s="3"/>
+      <c r="AZ8" s="3"/>
+      <c r="BA8" s="1"/>
+    </row>
+    <row r="9" spans="1:53" ht="45">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -1719,27 +1778,30 @@
       <c r="AI9" s="3">
         <v>3</v>
       </c>
-      <c r="AJ9" s="3"/>
-      <c r="AK9" s="3"/>
-      <c r="AL9" s="28" t="s">
+      <c r="AJ9" s="33"/>
+      <c r="AK9" s="33"/>
+      <c r="AL9" s="3"/>
+      <c r="AM9" s="37"/>
+      <c r="AN9" s="37"/>
+      <c r="AO9" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="AM9" s="29" t="s">
+      <c r="AP9" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="AN9" s="3"/>
-      <c r="AO9" s="3"/>
-      <c r="AP9" s="30"/>
       <c r="AQ9" s="3"/>
       <c r="AR9" s="3"/>
-      <c r="AS9" s="3"/>
+      <c r="AS9" s="30"/>
       <c r="AT9" s="3"/>
       <c r="AU9" s="3"/>
       <c r="AV9" s="3"/>
       <c r="AW9" s="3"/>
-      <c r="AX9" s="1"/>
-    </row>
-    <row r="10" spans="1:50" ht="105">
+      <c r="AX9" s="3"/>
+      <c r="AY9" s="3"/>
+      <c r="AZ9" s="3"/>
+      <c r="BA9" s="1"/>
+    </row>
+    <row r="10" spans="1:53" ht="105">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -1824,28 +1886,31 @@
         <v>4</v>
       </c>
       <c r="AJ10" s="3"/>
-      <c r="AK10" s="3"/>
-      <c r="AL10" s="28" t="s">
+      <c r="AK10" s="37"/>
+      <c r="AL10" s="3"/>
+      <c r="AM10" s="37"/>
+      <c r="AN10" s="37"/>
+      <c r="AO10" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="AM10" s="29" t="s">
+      <c r="AP10" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="AN10" s="28" t="s">
+      <c r="AQ10" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="AO10" s="3"/>
-      <c r="AP10" s="30"/>
-      <c r="AQ10" s="3"/>
       <c r="AR10" s="3"/>
-      <c r="AS10" s="3"/>
+      <c r="AS10" s="30"/>
       <c r="AT10" s="3"/>
       <c r="AU10" s="3"/>
       <c r="AV10" s="3"/>
       <c r="AW10" s="3"/>
-      <c r="AX10" s="1"/>
-    </row>
-    <row r="11" spans="1:50" ht="14.45" customHeight="1">
+      <c r="AX10" s="3"/>
+      <c r="AY10" s="3"/>
+      <c r="AZ10" s="3"/>
+      <c r="BA10" s="1"/>
+    </row>
+    <row r="11" spans="1:53" ht="14.45" customHeight="1">
       <c r="A11" s="2">
         <v>8</v>
       </c>
@@ -1929,29 +1994,32 @@
       </c>
       <c r="AJ11" s="5"/>
       <c r="AK11" s="5"/>
-      <c r="AL11" s="28" t="s">
+      <c r="AL11" s="5"/>
+      <c r="AM11" s="5"/>
+      <c r="AN11" s="5"/>
+      <c r="AO11" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="AM11" s="29" t="s">
+      <c r="AP11" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="AN11" s="5"/>
-      <c r="AO11" s="24">
+      <c r="AQ11" s="5"/>
+      <c r="AR11" s="24">
         <v>46128</v>
       </c>
-      <c r="AP11" s="31"/>
-      <c r="AQ11" s="5" t="s">
+      <c r="AS11" s="31"/>
+      <c r="AT11" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="AR11" s="34"/>
-      <c r="AS11" s="5"/>
-      <c r="AT11" s="5"/>
-      <c r="AU11" s="5"/>
+      <c r="AU11" s="34"/>
       <c r="AV11" s="5"/>
       <c r="AW11" s="5"/>
       <c r="AX11" s="5"/>
-    </row>
-    <row r="12" spans="1:50" ht="105">
+      <c r="AY11" s="5"/>
+      <c r="AZ11" s="5"/>
+      <c r="BA11" s="5"/>
+    </row>
+    <row r="12" spans="1:53" ht="105">
       <c r="A12" s="2">
         <v>9</v>
       </c>
@@ -2037,29 +2105,32 @@
       </c>
       <c r="AJ12" s="5"/>
       <c r="AK12" s="5"/>
-      <c r="AL12" s="28" t="s">
+      <c r="AL12" s="5"/>
+      <c r="AM12" s="5"/>
+      <c r="AN12" s="5"/>
+      <c r="AO12" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="AM12" s="29" t="s">
+      <c r="AP12" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="AN12" s="28" t="s">
+      <c r="AQ12" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="AO12" s="24">
+      <c r="AR12" s="24">
         <v>46135</v>
       </c>
-      <c r="AP12" s="31"/>
-      <c r="AQ12" s="5"/>
-      <c r="AR12" s="34"/>
-      <c r="AS12" s="5"/>
+      <c r="AS12" s="31"/>
       <c r="AT12" s="5"/>
-      <c r="AU12" s="5"/>
+      <c r="AU12" s="34"/>
       <c r="AV12" s="5"/>
       <c r="AW12" s="5"/>
       <c r="AX12" s="5"/>
-    </row>
-    <row r="13" spans="1:50" ht="120">
+      <c r="AY12" s="5"/>
+      <c r="AZ12" s="5"/>
+      <c r="BA12" s="5"/>
+    </row>
+    <row r="13" spans="1:53" ht="135">
       <c r="A13" s="2">
         <v>10</v>
       </c>
@@ -2143,29 +2214,40 @@
       <c r="AI13" s="5">
         <v>5</v>
       </c>
-      <c r="AJ13" s="5"/>
-      <c r="AK13" s="5"/>
-      <c r="AL13" s="28" t="s">
+      <c r="AJ13" s="44">
+        <v>46135</v>
+      </c>
+      <c r="AK13" s="34">
+        <v>11</v>
+      </c>
+      <c r="AL13" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AM13" s="5"/>
+      <c r="AN13" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="AO13" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="AM13" s="29" t="s">
+      <c r="AP13" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="AN13" s="28"/>
-      <c r="AO13" s="24">
+      <c r="AQ13" s="28"/>
+      <c r="AR13" s="24">
         <v>46128</v>
       </c>
-      <c r="AP13" s="31"/>
-      <c r="AQ13" s="5"/>
-      <c r="AR13" s="5"/>
-      <c r="AS13" s="5"/>
+      <c r="AS13" s="31"/>
       <c r="AT13" s="5"/>
       <c r="AU13" s="5"/>
       <c r="AV13" s="5"/>
       <c r="AW13" s="5"/>
       <c r="AX13" s="5"/>
-    </row>
-    <row r="14" spans="1:50" ht="105">
+      <c r="AY13" s="5"/>
+      <c r="AZ13" s="5"/>
+      <c r="BA13" s="5"/>
+    </row>
+    <row r="14" spans="1:53" ht="105">
       <c r="A14" s="2">
         <v>11</v>
       </c>
@@ -2235,33 +2317,36 @@
       <c r="AE14" s="3"/>
       <c r="AF14" s="3"/>
       <c r="AG14" s="3"/>
-      <c r="AH14" s="42"/>
+      <c r="AH14" s="39"/>
       <c r="AI14" s="3">
         <v>2</v>
       </c>
       <c r="AJ14" s="3"/>
-      <c r="AK14" s="3"/>
-      <c r="AL14" s="28" t="s">
+      <c r="AK14" s="37"/>
+      <c r="AL14" s="3"/>
+      <c r="AM14" s="37"/>
+      <c r="AN14" s="37"/>
+      <c r="AO14" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="AM14" s="29" t="s">
+      <c r="AP14" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="AN14" s="28" t="s">
+      <c r="AQ14" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="AO14" s="3"/>
-      <c r="AP14" s="30"/>
-      <c r="AQ14" s="3"/>
       <c r="AR14" s="3"/>
-      <c r="AS14" s="3"/>
+      <c r="AS14" s="30"/>
       <c r="AT14" s="3"/>
       <c r="AU14" s="3"/>
       <c r="AV14" s="3"/>
       <c r="AW14" s="3"/>
-      <c r="AX14" s="1"/>
-    </row>
-    <row r="15" spans="1:50">
+      <c r="AX14" s="3"/>
+      <c r="AY14" s="3"/>
+      <c r="AZ14" s="3"/>
+      <c r="BA14" s="1"/>
+    </row>
+    <row r="15" spans="1:53">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -2346,24 +2431,27 @@
         <v>5</v>
       </c>
       <c r="AJ15" s="3"/>
-      <c r="AK15" s="3"/>
+      <c r="AK15" s="37"/>
       <c r="AL15" s="3"/>
-      <c r="AM15" s="3"/>
-      <c r="AN15" s="3"/>
-      <c r="AO15" s="24">
+      <c r="AM15" s="37"/>
+      <c r="AN15" s="37"/>
+      <c r="AO15" s="3"/>
+      <c r="AP15" s="3"/>
+      <c r="AQ15" s="3"/>
+      <c r="AR15" s="24">
         <v>46128</v>
       </c>
-      <c r="AP15" s="30"/>
-      <c r="AQ15" s="3"/>
-      <c r="AR15" s="3"/>
-      <c r="AS15" s="3"/>
+      <c r="AS15" s="30"/>
       <c r="AT15" s="3"/>
       <c r="AU15" s="3"/>
       <c r="AV15" s="3"/>
       <c r="AW15" s="3"/>
-      <c r="AX15" s="1"/>
-    </row>
-    <row r="16" spans="1:50" ht="330">
+      <c r="AX15" s="3"/>
+      <c r="AY15" s="3"/>
+      <c r="AZ15" s="3"/>
+      <c r="BA15" s="1"/>
+    </row>
+    <row r="16" spans="1:53" ht="330">
       <c r="A16" s="2">
         <v>13</v>
       </c>
@@ -2445,33 +2533,42 @@
       <c r="AI16" s="3">
         <v>5</v>
       </c>
-      <c r="AJ16" s="3"/>
-      <c r="AK16" s="3"/>
-      <c r="AL16" s="28" t="s">
+      <c r="AJ16" s="44">
+        <v>46135</v>
+      </c>
+      <c r="AK16" s="37">
+        <v>7</v>
+      </c>
+      <c r="AL16" s="38"/>
+      <c r="AM16" s="37"/>
+      <c r="AN16" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="AO16" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="AM16" s="29" t="s">
+      <c r="AP16" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="AN16" s="3"/>
-      <c r="AO16" s="24">
+      <c r="AQ16" s="3"/>
+      <c r="AR16" s="24">
         <v>46135</v>
       </c>
-      <c r="AP16" s="30" t="s">
+      <c r="AS16" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="AQ16" s="3" t="s">
+      <c r="AT16" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="AR16" s="33"/>
-      <c r="AS16" s="3"/>
-      <c r="AT16" s="3"/>
-      <c r="AU16" s="3"/>
+      <c r="AU16" s="33"/>
       <c r="AV16" s="3"/>
       <c r="AW16" s="3"/>
-      <c r="AX16" s="1"/>
-    </row>
-    <row r="17" spans="1:50" ht="105">
+      <c r="AX16" s="3"/>
+      <c r="AY16" s="3"/>
+      <c r="AZ16" s="3"/>
+      <c r="BA16" s="1"/>
+    </row>
+    <row r="17" spans="1:53" ht="135">
       <c r="A17" s="2">
         <v>14</v>
       </c>
@@ -2556,30 +2653,37 @@
         <v>5</v>
       </c>
       <c r="AJ17" s="3"/>
-      <c r="AK17" s="3"/>
-      <c r="AL17" s="28" t="s">
+      <c r="AK17" s="37"/>
+      <c r="AL17" s="3"/>
+      <c r="AM17" s="24">
+        <v>46135</v>
+      </c>
+      <c r="AN17" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="AO17" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="AM17" s="29" t="s">
+      <c r="AP17" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="AN17" s="28" t="s">
+      <c r="AQ17" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="AO17" s="24">
+      <c r="AR17" s="24">
         <v>46135</v>
       </c>
-      <c r="AP17" s="30"/>
-      <c r="AQ17" s="3"/>
-      <c r="AR17" s="3"/>
-      <c r="AS17" s="3"/>
+      <c r="AS17" s="30"/>
       <c r="AT17" s="3"/>
       <c r="AU17" s="3"/>
       <c r="AV17" s="3"/>
       <c r="AW17" s="3"/>
-      <c r="AX17" s="1"/>
-    </row>
-    <row r="18" spans="1:50">
+      <c r="AX17" s="3"/>
+      <c r="AY17" s="3"/>
+      <c r="AZ17" s="3"/>
+      <c r="BA17" s="1"/>
+    </row>
+    <row r="18" spans="1:53" ht="90">
       <c r="A18" s="2">
         <v>15</v>
       </c>
@@ -2663,25 +2767,36 @@
       <c r="AI18" s="3">
         <v>5</v>
       </c>
-      <c r="AJ18" s="3"/>
-      <c r="AK18" s="3"/>
-      <c r="AL18" s="3"/>
-      <c r="AM18" s="3"/>
-      <c r="AN18" s="3"/>
-      <c r="AO18" s="24">
+      <c r="AJ18" s="44">
         <v>46135</v>
       </c>
-      <c r="AP18" s="30"/>
+      <c r="AK18" s="34">
+        <v>12</v>
+      </c>
+      <c r="AL18" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="AM18" s="5"/>
+      <c r="AN18" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="AO18" s="3"/>
+      <c r="AP18" s="3"/>
       <c r="AQ18" s="3"/>
-      <c r="AR18" s="33"/>
-      <c r="AS18" s="3"/>
+      <c r="AR18" s="24">
+        <v>46135</v>
+      </c>
+      <c r="AS18" s="30"/>
       <c r="AT18" s="3"/>
-      <c r="AU18" s="3"/>
+      <c r="AU18" s="33"/>
       <c r="AV18" s="3"/>
       <c r="AW18" s="3"/>
-      <c r="AX18" s="1"/>
-    </row>
-    <row r="19" spans="1:50">
+      <c r="AX18" s="3"/>
+      <c r="AY18" s="3"/>
+      <c r="AZ18" s="3"/>
+      <c r="BA18" s="1"/>
+    </row>
+    <row r="19" spans="1:53">
       <c r="A19" s="2">
         <v>16</v>
       </c>
@@ -2760,22 +2875,25 @@
         <v>3</v>
       </c>
       <c r="AJ19" s="3"/>
-      <c r="AK19" s="3"/>
+      <c r="AK19" s="37"/>
       <c r="AL19" s="3"/>
-      <c r="AM19" s="3"/>
-      <c r="AN19" s="3"/>
+      <c r="AM19" s="37"/>
+      <c r="AN19" s="37"/>
       <c r="AO19" s="3"/>
-      <c r="AP19" s="30"/>
+      <c r="AP19" s="3"/>
       <c r="AQ19" s="3"/>
       <c r="AR19" s="3"/>
-      <c r="AS19" s="3"/>
+      <c r="AS19" s="30"/>
       <c r="AT19" s="3"/>
       <c r="AU19" s="3"/>
       <c r="AV19" s="3"/>
       <c r="AW19" s="3"/>
-      <c r="AX19" s="1"/>
-    </row>
-    <row r="20" spans="1:50">
+      <c r="AX19" s="3"/>
+      <c r="AY19" s="3"/>
+      <c r="AZ19" s="3"/>
+      <c r="BA19" s="1"/>
+    </row>
+    <row r="20" spans="1:53">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -2831,7 +2949,7 @@
         <v>17</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
@@ -2854,22 +2972,25 @@
         <v>2</v>
       </c>
       <c r="AJ20" s="3"/>
-      <c r="AK20" s="3"/>
+      <c r="AK20" s="37"/>
       <c r="AL20" s="3"/>
-      <c r="AM20" s="3"/>
-      <c r="AN20" s="3"/>
+      <c r="AM20" s="37"/>
+      <c r="AN20" s="37"/>
       <c r="AO20" s="3"/>
-      <c r="AP20" s="30"/>
+      <c r="AP20" s="3"/>
       <c r="AQ20" s="3"/>
       <c r="AR20" s="3"/>
-      <c r="AS20" s="3"/>
+      <c r="AS20" s="30"/>
       <c r="AT20" s="3"/>
       <c r="AU20" s="3"/>
       <c r="AV20" s="3"/>
       <c r="AW20" s="3"/>
-      <c r="AX20" s="1"/>
-    </row>
-    <row r="21" spans="1:50">
+      <c r="AX20" s="3"/>
+      <c r="AY20" s="3"/>
+      <c r="AZ20" s="3"/>
+      <c r="BA20" s="1"/>
+    </row>
+    <row r="21" spans="1:53" ht="90">
       <c r="A21" s="2">
         <v>18</v>
       </c>
@@ -2950,22 +3071,29 @@
         <v>3</v>
       </c>
       <c r="AJ21" s="3"/>
-      <c r="AK21" s="3"/>
+      <c r="AK21" s="37"/>
       <c r="AL21" s="3"/>
-      <c r="AM21" s="3"/>
-      <c r="AN21" s="3"/>
+      <c r="AM21" s="24">
+        <v>46135</v>
+      </c>
+      <c r="AN21" s="37" t="s">
+        <v>106</v>
+      </c>
       <c r="AO21" s="3"/>
-      <c r="AP21" s="30"/>
+      <c r="AP21" s="3"/>
       <c r="AQ21" s="3"/>
       <c r="AR21" s="3"/>
-      <c r="AS21" s="3"/>
+      <c r="AS21" s="30"/>
       <c r="AT21" s="3"/>
       <c r="AU21" s="3"/>
       <c r="AV21" s="3"/>
       <c r="AW21" s="3"/>
-      <c r="AX21" s="1"/>
-    </row>
-    <row r="22" spans="1:50" ht="45">
+      <c r="AX21" s="3"/>
+      <c r="AY21" s="3"/>
+      <c r="AZ21" s="3"/>
+      <c r="BA21" s="1"/>
+    </row>
+    <row r="22" spans="1:53" ht="45">
       <c r="A22" s="2">
         <v>19</v>
       </c>
@@ -3048,28 +3176,31 @@
         <v>5</v>
       </c>
       <c r="AJ22" s="3"/>
-      <c r="AK22" s="3"/>
-      <c r="AL22" s="28" t="s">
+      <c r="AK22" s="37"/>
+      <c r="AL22" s="3"/>
+      <c r="AM22" s="37"/>
+      <c r="AN22" s="37"/>
+      <c r="AO22" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="AM22" s="29" t="s">
+      <c r="AP22" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="AN22" s="3"/>
-      <c r="AO22" s="24">
+      <c r="AQ22" s="3"/>
+      <c r="AR22" s="24">
         <v>46128</v>
       </c>
-      <c r="AP22" s="30"/>
-      <c r="AQ22" s="3"/>
-      <c r="AR22" s="3"/>
-      <c r="AS22" s="3"/>
+      <c r="AS22" s="30"/>
       <c r="AT22" s="3"/>
       <c r="AU22" s="3"/>
       <c r="AV22" s="3"/>
       <c r="AW22" s="3"/>
-      <c r="AX22" s="1"/>
-    </row>
-    <row r="23" spans="1:50">
+      <c r="AX22" s="3"/>
+      <c r="AY22" s="3"/>
+      <c r="AZ22" s="3"/>
+      <c r="BA22" s="1"/>
+    </row>
+    <row r="23" spans="1:53">
       <c r="A23" s="2">
         <v>20</v>
       </c>
@@ -3154,24 +3285,27 @@
         <v>5</v>
       </c>
       <c r="AJ23" s="3"/>
-      <c r="AK23" s="3"/>
+      <c r="AK23" s="37"/>
       <c r="AL23" s="3"/>
-      <c r="AM23" s="3"/>
-      <c r="AN23" s="3"/>
-      <c r="AO23" s="24">
+      <c r="AM23" s="37"/>
+      <c r="AN23" s="37"/>
+      <c r="AO23" s="3"/>
+      <c r="AP23" s="3"/>
+      <c r="AQ23" s="3"/>
+      <c r="AR23" s="24">
         <v>46128</v>
       </c>
-      <c r="AP23" s="30"/>
-      <c r="AQ23" s="3"/>
-      <c r="AR23" s="3"/>
-      <c r="AS23" s="3"/>
+      <c r="AS23" s="30"/>
       <c r="AT23" s="3"/>
       <c r="AU23" s="3"/>
       <c r="AV23" s="3"/>
       <c r="AW23" s="3"/>
-      <c r="AX23" s="1"/>
-    </row>
-    <row r="24" spans="1:50">
+      <c r="AX23" s="3"/>
+      <c r="AY23" s="3"/>
+      <c r="AZ23" s="3"/>
+      <c r="BA23" s="1"/>
+    </row>
+    <row r="24" spans="1:53">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -3248,22 +3382,25 @@
         <v>2</v>
       </c>
       <c r="AJ24" s="3"/>
-      <c r="AK24" s="3"/>
+      <c r="AK24" s="37"/>
       <c r="AL24" s="3"/>
-      <c r="AM24" s="3"/>
-      <c r="AN24" s="3"/>
+      <c r="AM24" s="37"/>
+      <c r="AN24" s="37"/>
       <c r="AO24" s="3"/>
-      <c r="AP24" s="30"/>
+      <c r="AP24" s="3"/>
       <c r="AQ24" s="3"/>
       <c r="AR24" s="3"/>
-      <c r="AS24" s="3"/>
+      <c r="AS24" s="30"/>
       <c r="AT24" s="3"/>
       <c r="AU24" s="3"/>
       <c r="AV24" s="3"/>
       <c r="AW24" s="3"/>
-      <c r="AX24" s="1"/>
-    </row>
-    <row r="25" spans="1:50">
+      <c r="AX24" s="3"/>
+      <c r="AY24" s="3"/>
+      <c r="AZ24" s="3"/>
+      <c r="BA24" s="1"/>
+    </row>
+    <row r="25" spans="1:53">
       <c r="A25" s="2">
         <v>22</v>
       </c>
@@ -3346,24 +3483,27 @@
         <v>5</v>
       </c>
       <c r="AJ25" s="3"/>
-      <c r="AK25" s="3"/>
+      <c r="AK25" s="37"/>
       <c r="AL25" s="3"/>
-      <c r="AM25" s="3"/>
-      <c r="AN25" s="3"/>
-      <c r="AO25" s="24">
+      <c r="AM25" s="37"/>
+      <c r="AN25" s="37"/>
+      <c r="AO25" s="3"/>
+      <c r="AP25" s="3"/>
+      <c r="AQ25" s="3"/>
+      <c r="AR25" s="24">
         <v>46135</v>
       </c>
-      <c r="AP25" s="30"/>
-      <c r="AQ25" s="3"/>
-      <c r="AR25" s="3"/>
-      <c r="AS25" s="3"/>
+      <c r="AS25" s="30"/>
       <c r="AT25" s="3"/>
       <c r="AU25" s="3"/>
       <c r="AV25" s="3"/>
       <c r="AW25" s="3"/>
-      <c r="AX25" s="1"/>
-    </row>
-    <row r="26" spans="1:50">
+      <c r="AX25" s="3"/>
+      <c r="AY25" s="3"/>
+      <c r="AZ25" s="3"/>
+      <c r="BA25" s="1"/>
+    </row>
+    <row r="26" spans="1:53">
       <c r="A26" s="2">
         <v>23</v>
       </c>
@@ -3438,22 +3578,25 @@
         <v>0</v>
       </c>
       <c r="AJ26" s="3"/>
-      <c r="AK26" s="3"/>
+      <c r="AK26" s="37"/>
       <c r="AL26" s="3"/>
-      <c r="AM26" s="3"/>
-      <c r="AN26" s="3"/>
+      <c r="AM26" s="37"/>
+      <c r="AN26" s="37"/>
       <c r="AO26" s="3"/>
-      <c r="AP26" s="30"/>
+      <c r="AP26" s="3"/>
       <c r="AQ26" s="3"/>
       <c r="AR26" s="3"/>
-      <c r="AS26" s="3"/>
+      <c r="AS26" s="30"/>
       <c r="AT26" s="3"/>
       <c r="AU26" s="3"/>
       <c r="AV26" s="3"/>
       <c r="AW26" s="3"/>
-      <c r="AX26" s="1"/>
-    </row>
-    <row r="27" spans="1:50">
+      <c r="AX26" s="3"/>
+      <c r="AY26" s="3"/>
+      <c r="AZ26" s="3"/>
+      <c r="BA26" s="1"/>
+    </row>
+    <row r="27" spans="1:53">
       <c r="A27" s="2">
         <v>24</v>
       </c>
@@ -3538,24 +3681,27 @@
         <v>5</v>
       </c>
       <c r="AJ27" s="3"/>
-      <c r="AK27" s="3"/>
+      <c r="AK27" s="37"/>
       <c r="AL27" s="3"/>
-      <c r="AM27" s="3"/>
-      <c r="AN27" s="3"/>
-      <c r="AO27" s="24">
+      <c r="AM27" s="37"/>
+      <c r="AN27" s="37"/>
+      <c r="AO27" s="3"/>
+      <c r="AP27" s="3"/>
+      <c r="AQ27" s="3"/>
+      <c r="AR27" s="24">
         <v>46135</v>
       </c>
-      <c r="AP27" s="30"/>
-      <c r="AQ27" s="3"/>
-      <c r="AR27" s="3"/>
-      <c r="AS27" s="3"/>
+      <c r="AS27" s="30"/>
       <c r="AT27" s="3"/>
       <c r="AU27" s="3"/>
       <c r="AV27" s="3"/>
       <c r="AW27" s="3"/>
-      <c r="AX27" s="1"/>
-    </row>
-    <row r="28" spans="1:50">
+      <c r="AX27" s="3"/>
+      <c r="AY27" s="3"/>
+      <c r="AZ27" s="3"/>
+      <c r="BA27" s="1"/>
+    </row>
+    <row r="28" spans="1:53">
       <c r="A28" s="2">
         <v>25</v>
       </c>
@@ -3634,22 +3780,25 @@
         <v>3</v>
       </c>
       <c r="AJ28" s="3"/>
-      <c r="AK28" s="3"/>
+      <c r="AK28" s="37"/>
       <c r="AL28" s="3"/>
-      <c r="AM28" s="3"/>
-      <c r="AN28" s="3"/>
+      <c r="AM28" s="37"/>
+      <c r="AN28" s="37"/>
       <c r="AO28" s="3"/>
-      <c r="AP28" s="30"/>
+      <c r="AP28" s="3"/>
       <c r="AQ28" s="3"/>
       <c r="AR28" s="3"/>
-      <c r="AS28" s="3"/>
+      <c r="AS28" s="30"/>
       <c r="AT28" s="3"/>
       <c r="AU28" s="3"/>
       <c r="AV28" s="3"/>
       <c r="AW28" s="3"/>
-      <c r="AX28" s="1"/>
-    </row>
-    <row r="29" spans="1:50">
+      <c r="AX28" s="3"/>
+      <c r="AY28" s="3"/>
+      <c r="AZ28" s="3"/>
+      <c r="BA28" s="1"/>
+    </row>
+    <row r="29" spans="1:53" ht="135">
       <c r="A29" s="2">
         <v>26</v>
       </c>
@@ -3732,24 +3881,31 @@
         <v>5</v>
       </c>
       <c r="AJ29" s="3"/>
-      <c r="AK29" s="3"/>
+      <c r="AK29" s="37"/>
       <c r="AL29" s="3"/>
-      <c r="AM29" s="3"/>
-      <c r="AN29" s="3"/>
-      <c r="AO29" s="24">
+      <c r="AM29" s="24">
         <v>46135</v>
       </c>
-      <c r="AP29" s="30"/>
+      <c r="AN29" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="AO29" s="3"/>
+      <c r="AP29" s="3"/>
       <c r="AQ29" s="3"/>
-      <c r="AR29" s="3"/>
-      <c r="AS29" s="3"/>
+      <c r="AR29" s="24">
+        <v>46135</v>
+      </c>
+      <c r="AS29" s="30"/>
       <c r="AT29" s="3"/>
       <c r="AU29" s="3"/>
       <c r="AV29" s="3"/>
       <c r="AW29" s="3"/>
-      <c r="AX29" s="1"/>
-    </row>
-    <row r="30" spans="1:50">
+      <c r="AX29" s="3"/>
+      <c r="AY29" s="3"/>
+      <c r="AZ29" s="3"/>
+      <c r="BA29" s="1"/>
+    </row>
+    <row r="30" spans="1:53" ht="60">
       <c r="A30" s="2">
         <v>27</v>
       </c>
@@ -3833,27 +3989,36 @@
       <c r="AI30" s="3">
         <v>5</v>
       </c>
-      <c r="AJ30" s="3"/>
-      <c r="AK30" s="3"/>
-      <c r="AL30" s="3"/>
-      <c r="AM30" s="3"/>
-      <c r="AN30" s="3"/>
-      <c r="AO30" s="24">
+      <c r="AJ30" s="44">
         <v>46135</v>
       </c>
-      <c r="AP30" s="30"/>
+      <c r="AK30" s="37">
+        <v>7</v>
+      </c>
+      <c r="AL30" s="38"/>
+      <c r="AM30" s="37"/>
+      <c r="AN30" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="AO30" s="3"/>
+      <c r="AP30" s="3"/>
       <c r="AQ30" s="3"/>
-      <c r="AR30" s="33" t="s">
+      <c r="AR30" s="24">
+        <v>46135</v>
+      </c>
+      <c r="AS30" s="30"/>
+      <c r="AT30" s="3"/>
+      <c r="AU30" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="AS30" s="3"/>
-      <c r="AT30" s="3"/>
-      <c r="AU30" s="3"/>
       <c r="AV30" s="3"/>
       <c r="AW30" s="3"/>
-      <c r="AX30" s="1"/>
-    </row>
-    <row r="31" spans="1:50">
+      <c r="AX30" s="3"/>
+      <c r="AY30" s="3"/>
+      <c r="AZ30" s="3"/>
+      <c r="BA30" s="1"/>
+    </row>
+    <row r="31" spans="1:53">
       <c r="A31" s="2">
         <v>28</v>
       </c>
@@ -3938,22 +4103,25 @@
         <v>3</v>
       </c>
       <c r="AJ31" s="3"/>
-      <c r="AK31" s="3"/>
+      <c r="AK31" s="37"/>
       <c r="AL31" s="3"/>
-      <c r="AM31" s="3"/>
-      <c r="AN31" s="3"/>
+      <c r="AM31" s="37"/>
+      <c r="AN31" s="37"/>
       <c r="AO31" s="3"/>
-      <c r="AP31" s="30"/>
+      <c r="AP31" s="3"/>
       <c r="AQ31" s="3"/>
       <c r="AR31" s="3"/>
-      <c r="AS31" s="3"/>
+      <c r="AS31" s="30"/>
       <c r="AT31" s="3"/>
       <c r="AU31" s="3"/>
       <c r="AV31" s="3"/>
       <c r="AW31" s="3"/>
-      <c r="AX31" s="1"/>
-    </row>
-    <row r="32" spans="1:50">
+      <c r="AX31" s="3"/>
+      <c r="AY31" s="3"/>
+      <c r="AZ31" s="3"/>
+      <c r="BA31" s="1"/>
+    </row>
+    <row r="32" spans="1:53">
       <c r="A32" s="2">
         <v>29</v>
       </c>
@@ -4028,22 +4196,25 @@
         <v>2</v>
       </c>
       <c r="AJ32" s="3"/>
-      <c r="AK32" s="3"/>
+      <c r="AK32" s="37"/>
       <c r="AL32" s="3"/>
-      <c r="AM32" s="3"/>
-      <c r="AN32" s="3"/>
+      <c r="AM32" s="37"/>
+      <c r="AN32" s="37"/>
       <c r="AO32" s="3"/>
-      <c r="AP32" s="30"/>
+      <c r="AP32" s="3"/>
       <c r="AQ32" s="3"/>
       <c r="AR32" s="3"/>
-      <c r="AS32" s="3"/>
+      <c r="AS32" s="30"/>
       <c r="AT32" s="3"/>
       <c r="AU32" s="3"/>
       <c r="AV32" s="3"/>
       <c r="AW32" s="3"/>
-      <c r="AX32" s="1"/>
-    </row>
-    <row r="33" spans="1:50">
+      <c r="AX32" s="3"/>
+      <c r="AY32" s="3"/>
+      <c r="AZ32" s="3"/>
+      <c r="BA32" s="1"/>
+    </row>
+    <row r="33" spans="1:53">
       <c r="A33" s="2">
         <v>30</v>
       </c>
@@ -4126,22 +4297,25 @@
         <v>4</v>
       </c>
       <c r="AJ33" s="3"/>
-      <c r="AK33" s="3"/>
+      <c r="AK33" s="37"/>
       <c r="AL33" s="3"/>
-      <c r="AM33" s="3"/>
-      <c r="AN33" s="3"/>
+      <c r="AM33" s="37"/>
+      <c r="AN33" s="37"/>
       <c r="AO33" s="3"/>
-      <c r="AP33" s="30"/>
+      <c r="AP33" s="3"/>
       <c r="AQ33" s="3"/>
       <c r="AR33" s="3"/>
-      <c r="AS33" s="3"/>
+      <c r="AS33" s="30"/>
       <c r="AT33" s="3"/>
       <c r="AU33" s="3"/>
       <c r="AV33" s="3"/>
       <c r="AW33" s="3"/>
-      <c r="AX33" s="1"/>
-    </row>
-    <row r="34" spans="1:50">
+      <c r="AX33" s="3"/>
+      <c r="AY33" s="3"/>
+      <c r="AZ33" s="3"/>
+      <c r="BA33" s="1"/>
+    </row>
+    <row r="34" spans="1:53" ht="135">
       <c r="A34" s="2">
         <v>31</v>
       </c>
@@ -4223,25 +4397,36 @@
       <c r="AI34" s="5">
         <v>5</v>
       </c>
-      <c r="AJ34" s="3"/>
-      <c r="AK34" s="3"/>
-      <c r="AL34" s="3"/>
-      <c r="AM34" s="3"/>
-      <c r="AN34" s="3"/>
-      <c r="AO34" s="24">
+      <c r="AJ34" s="44">
+        <v>46135</v>
+      </c>
+      <c r="AK34" s="34">
+        <v>11</v>
+      </c>
+      <c r="AL34" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AM34" s="5"/>
+      <c r="AN34" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="AO34" s="3"/>
+      <c r="AP34" s="3"/>
+      <c r="AQ34" s="3"/>
+      <c r="AR34" s="24">
         <v>46128</v>
       </c>
-      <c r="AP34" s="30"/>
-      <c r="AQ34" s="3"/>
-      <c r="AR34" s="3"/>
-      <c r="AS34" s="3"/>
+      <c r="AS34" s="30"/>
       <c r="AT34" s="3"/>
       <c r="AU34" s="3"/>
       <c r="AV34" s="3"/>
       <c r="AW34" s="3"/>
-      <c r="AX34" s="1"/>
-    </row>
-    <row r="35" spans="1:50">
+      <c r="AX34" s="3"/>
+      <c r="AY34" s="3"/>
+      <c r="AZ34" s="3"/>
+      <c r="BA34" s="1"/>
+    </row>
+    <row r="35" spans="1:53">
       <c r="A35" s="2">
         <v>32</v>
       </c>
@@ -4311,27 +4496,30 @@
       <c r="AE35" s="3"/>
       <c r="AF35" s="3"/>
       <c r="AG35" s="3"/>
-      <c r="AH35" s="42"/>
+      <c r="AH35" s="39"/>
       <c r="AI35" s="3">
         <v>2</v>
       </c>
       <c r="AJ35" s="3"/>
-      <c r="AK35" s="3"/>
+      <c r="AK35" s="37"/>
       <c r="AL35" s="3"/>
-      <c r="AM35" s="3"/>
-      <c r="AN35" s="3"/>
+      <c r="AM35" s="37"/>
+      <c r="AN35" s="37"/>
       <c r="AO35" s="3"/>
-      <c r="AP35" s="30"/>
+      <c r="AP35" s="3"/>
       <c r="AQ35" s="3"/>
       <c r="AR35" s="3"/>
-      <c r="AS35" s="3"/>
+      <c r="AS35" s="30"/>
       <c r="AT35" s="3"/>
       <c r="AU35" s="3"/>
       <c r="AV35" s="3"/>
       <c r="AW35" s="3"/>
-      <c r="AX35" s="1"/>
-    </row>
-    <row r="36" spans="1:50">
+      <c r="AX35" s="3"/>
+      <c r="AY35" s="3"/>
+      <c r="AZ35" s="3"/>
+      <c r="BA35" s="1"/>
+    </row>
+    <row r="36" spans="1:53">
       <c r="A36" s="36">
         <v>33</v>
       </c>
@@ -4404,22 +4592,25 @@
       <c r="AH36" s="3"/>
       <c r="AI36" s="3"/>
       <c r="AJ36" s="3"/>
-      <c r="AK36" s="3"/>
+      <c r="AK36" s="37"/>
       <c r="AL36" s="3"/>
-      <c r="AM36" s="3"/>
-      <c r="AN36" s="3"/>
+      <c r="AM36" s="37"/>
+      <c r="AN36" s="37"/>
       <c r="AO36" s="3"/>
-      <c r="AP36" s="30"/>
+      <c r="AP36" s="3"/>
       <c r="AQ36" s="3"/>
       <c r="AR36" s="3"/>
-      <c r="AS36" s="3"/>
+      <c r="AS36" s="30"/>
       <c r="AT36" s="3"/>
       <c r="AU36" s="3"/>
       <c r="AV36" s="3"/>
       <c r="AW36" s="3"/>
-      <c r="AX36" s="1"/>
-    </row>
-    <row r="37" spans="1:50">
+      <c r="AX36" s="3"/>
+      <c r="AY36" s="3"/>
+      <c r="AZ36" s="3"/>
+      <c r="BA36" s="1"/>
+    </row>
+    <row r="37" spans="1:53">
       <c r="A37" t="s">
         <v>65</v>
       </c>
@@ -4501,22 +4692,25 @@
       <c r="AH37" s="3"/>
       <c r="AI37" s="3"/>
       <c r="AJ37" s="3"/>
-      <c r="AK37" s="3"/>
+      <c r="AK37" s="37"/>
       <c r="AL37" s="3"/>
-      <c r="AM37" s="3"/>
-      <c r="AN37" s="3"/>
+      <c r="AM37" s="37"/>
+      <c r="AN37" s="37"/>
       <c r="AO37" s="3"/>
-      <c r="AP37" s="30"/>
+      <c r="AP37" s="3"/>
       <c r="AQ37" s="3"/>
       <c r="AR37" s="3"/>
-      <c r="AS37" s="3"/>
+      <c r="AS37" s="30"/>
       <c r="AT37" s="3"/>
       <c r="AU37" s="3"/>
       <c r="AV37" s="3"/>
       <c r="AW37" s="3"/>
-      <c r="AX37" s="1"/>
-    </row>
-    <row r="38" spans="1:50">
+      <c r="AX37" s="3"/>
+      <c r="AY37" s="3"/>
+      <c r="AZ37" s="3"/>
+      <c r="BA37" s="1"/>
+    </row>
+    <row r="38" spans="1:53">
       <c r="E38">
         <v>1</v>
       </c>
@@ -4575,7 +4769,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:50">
+    <row r="39" spans="1:53">
       <c r="E39" s="13" t="s">
         <v>68</v>
       </c>
@@ -4589,7 +4783,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="40" spans="1:50">
+    <row r="40" spans="1:53">
       <c r="E40">
         <v>1</v>
       </c>
@@ -4657,25 +4851,25 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="1:50">
+    <row r="41" spans="1:53">
       <c r="W41" s="35" t="s">
         <v>96</v>
       </c>
       <c r="X41" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="Y41" s="41" t="s">
+      <c r="Y41" s="38" t="s">
         <v>100</v>
       </c>
       <c r="Z41" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="42" spans="1:50" ht="9.75" customHeight="1">
-      <c r="W42" s="41" t="s">
+    <row r="42" spans="1:53" ht="9.75" customHeight="1">
+      <c r="W42" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="Z42" s="41" t="s">
+      <c r="Z42" s="38" t="s">
         <v>102</v>
       </c>
     </row>
@@ -4746,7 +4940,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:AX1"/>
+    <mergeCell ref="A1:BA1"/>
     <mergeCell ref="A2:B2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4759,56 +4953,56 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="37"/>
-      <c r="R1" s="37"/>
-      <c r="S1" s="37"/>
-      <c r="T1" s="37"/>
-      <c r="U1" s="37"/>
-      <c r="V1" s="37"/>
-      <c r="W1" s="37"/>
-      <c r="X1" s="37"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="37"/>
-      <c r="AA1" s="37"/>
-      <c r="AB1" s="37"/>
-      <c r="AC1" s="37"/>
-      <c r="AD1" s="37"/>
-      <c r="AE1" s="37"/>
-      <c r="AF1" s="37"/>
-      <c r="AG1" s="37"/>
-      <c r="AH1" s="37"/>
-      <c r="AI1" s="37"/>
-      <c r="AJ1" s="37"/>
-      <c r="AK1" s="37"/>
-      <c r="AL1" s="37"/>
-      <c r="AM1" s="37"/>
-      <c r="AN1" s="37"/>
-      <c r="AO1" s="37"/>
-      <c r="AP1" s="37"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40"/>
+      <c r="Q1" s="40"/>
+      <c r="R1" s="40"/>
+      <c r="S1" s="40"/>
+      <c r="T1" s="40"/>
+      <c r="U1" s="40"/>
+      <c r="V1" s="40"/>
+      <c r="W1" s="40"/>
+      <c r="X1" s="40"/>
+      <c r="Y1" s="40"/>
+      <c r="Z1" s="40"/>
+      <c r="AA1" s="40"/>
+      <c r="AB1" s="40"/>
+      <c r="AC1" s="40"/>
+      <c r="AD1" s="40"/>
+      <c r="AE1" s="40"/>
+      <c r="AF1" s="40"/>
+      <c r="AG1" s="40"/>
+      <c r="AH1" s="40"/>
+      <c r="AI1" s="40"/>
+      <c r="AJ1" s="40"/>
+      <c r="AK1" s="40"/>
+      <c r="AL1" s="40"/>
+      <c r="AM1" s="40"/>
+      <c r="AN1" s="40"/>
+      <c r="AO1" s="40"/>
+      <c r="AP1" s="40"/>
     </row>
     <row r="2" spans="1:42" ht="30">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="39"/>
+      <c r="B2" s="42"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -5237,142 +5431,142 @@
       <c r="AP10" s="1"/>
     </row>
     <row r="11" spans="1:42">
-      <c r="A11" s="39">
+      <c r="A11" s="42">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="40"/>
-      <c r="M11" s="40"/>
-      <c r="N11" s="40"/>
-      <c r="O11" s="40"/>
-      <c r="P11" s="40"/>
-      <c r="Q11" s="40"/>
-      <c r="R11" s="40"/>
-      <c r="S11" s="40"/>
-      <c r="T11" s="40"/>
-      <c r="U11" s="40"/>
-      <c r="V11" s="40"/>
-      <c r="W11" s="40"/>
-      <c r="X11" s="40"/>
-      <c r="Y11" s="40"/>
-      <c r="Z11" s="40"/>
-      <c r="AA11" s="40"/>
-      <c r="AB11" s="40"/>
-      <c r="AC11" s="40"/>
-      <c r="AD11" s="40"/>
-      <c r="AE11" s="40"/>
-      <c r="AF11" s="40"/>
-      <c r="AG11" s="40"/>
-      <c r="AH11" s="40"/>
-      <c r="AI11" s="40"/>
-      <c r="AJ11" s="40"/>
-      <c r="AK11" s="40"/>
-      <c r="AL11" s="40"/>
-      <c r="AM11" s="40"/>
-      <c r="AN11" s="40"/>
-      <c r="AO11" s="40"/>
-      <c r="AP11" s="37"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="43"/>
+      <c r="M11" s="43"/>
+      <c r="N11" s="43"/>
+      <c r="O11" s="43"/>
+      <c r="P11" s="43"/>
+      <c r="Q11" s="43"/>
+      <c r="R11" s="43"/>
+      <c r="S11" s="43"/>
+      <c r="T11" s="43"/>
+      <c r="U11" s="43"/>
+      <c r="V11" s="43"/>
+      <c r="W11" s="43"/>
+      <c r="X11" s="43"/>
+      <c r="Y11" s="43"/>
+      <c r="Z11" s="43"/>
+      <c r="AA11" s="43"/>
+      <c r="AB11" s="43"/>
+      <c r="AC11" s="43"/>
+      <c r="AD11" s="43"/>
+      <c r="AE11" s="43"/>
+      <c r="AF11" s="43"/>
+      <c r="AG11" s="43"/>
+      <c r="AH11" s="43"/>
+      <c r="AI11" s="43"/>
+      <c r="AJ11" s="43"/>
+      <c r="AK11" s="43"/>
+      <c r="AL11" s="43"/>
+      <c r="AM11" s="43"/>
+      <c r="AN11" s="43"/>
+      <c r="AO11" s="43"/>
+      <c r="AP11" s="40"/>
     </row>
     <row r="12" spans="1:42">
-      <c r="A12" s="39"/>
+      <c r="A12" s="42"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="40"/>
-      <c r="M12" s="40"/>
-      <c r="N12" s="40"/>
-      <c r="O12" s="40"/>
-      <c r="P12" s="40"/>
-      <c r="Q12" s="40"/>
-      <c r="R12" s="40"/>
-      <c r="S12" s="40"/>
-      <c r="T12" s="40"/>
-      <c r="U12" s="40"/>
-      <c r="V12" s="40"/>
-      <c r="W12" s="40"/>
-      <c r="X12" s="40"/>
-      <c r="Y12" s="40"/>
-      <c r="Z12" s="40"/>
-      <c r="AA12" s="40"/>
-      <c r="AB12" s="40"/>
-      <c r="AC12" s="40"/>
-      <c r="AD12" s="40"/>
-      <c r="AE12" s="40"/>
-      <c r="AF12" s="40"/>
-      <c r="AG12" s="40"/>
-      <c r="AH12" s="40"/>
-      <c r="AI12" s="40"/>
-      <c r="AJ12" s="40"/>
-      <c r="AK12" s="40"/>
-      <c r="AL12" s="40"/>
-      <c r="AM12" s="40"/>
-      <c r="AN12" s="40"/>
-      <c r="AO12" s="40"/>
-      <c r="AP12" s="37"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="42"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="43"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="43"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="43"/>
+      <c r="S12" s="43"/>
+      <c r="T12" s="43"/>
+      <c r="U12" s="43"/>
+      <c r="V12" s="43"/>
+      <c r="W12" s="43"/>
+      <c r="X12" s="43"/>
+      <c r="Y12" s="43"/>
+      <c r="Z12" s="43"/>
+      <c r="AA12" s="43"/>
+      <c r="AB12" s="43"/>
+      <c r="AC12" s="43"/>
+      <c r="AD12" s="43"/>
+      <c r="AE12" s="43"/>
+      <c r="AF12" s="43"/>
+      <c r="AG12" s="43"/>
+      <c r="AH12" s="43"/>
+      <c r="AI12" s="43"/>
+      <c r="AJ12" s="43"/>
+      <c r="AK12" s="43"/>
+      <c r="AL12" s="43"/>
+      <c r="AM12" s="43"/>
+      <c r="AN12" s="43"/>
+      <c r="AO12" s="43"/>
+      <c r="AP12" s="40"/>
     </row>
     <row r="13" spans="1:42">
-      <c r="A13" s="39"/>
+      <c r="A13" s="42"/>
       <c r="B13" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="39"/>
-      <c r="L13" s="40"/>
-      <c r="M13" s="40"/>
-      <c r="N13" s="40"/>
-      <c r="O13" s="40"/>
-      <c r="P13" s="40"/>
-      <c r="Q13" s="40"/>
-      <c r="R13" s="40"/>
-      <c r="S13" s="40"/>
-      <c r="T13" s="40"/>
-      <c r="U13" s="40"/>
-      <c r="V13" s="40"/>
-      <c r="W13" s="40"/>
-      <c r="X13" s="40"/>
-      <c r="Y13" s="40"/>
-      <c r="Z13" s="40"/>
-      <c r="AA13" s="40"/>
-      <c r="AB13" s="40"/>
-      <c r="AC13" s="40"/>
-      <c r="AD13" s="40"/>
-      <c r="AE13" s="40"/>
-      <c r="AF13" s="40"/>
-      <c r="AG13" s="40"/>
-      <c r="AH13" s="40"/>
-      <c r="AI13" s="40"/>
-      <c r="AJ13" s="40"/>
-      <c r="AK13" s="40"/>
-      <c r="AL13" s="40"/>
-      <c r="AM13" s="40"/>
-      <c r="AN13" s="40"/>
-      <c r="AO13" s="40"/>
-      <c r="AP13" s="37"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="42"/>
+      <c r="L13" s="43"/>
+      <c r="M13" s="43"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="43"/>
+      <c r="T13" s="43"/>
+      <c r="U13" s="43"/>
+      <c r="V13" s="43"/>
+      <c r="W13" s="43"/>
+      <c r="X13" s="43"/>
+      <c r="Y13" s="43"/>
+      <c r="Z13" s="43"/>
+      <c r="AA13" s="43"/>
+      <c r="AB13" s="43"/>
+      <c r="AC13" s="43"/>
+      <c r="AD13" s="43"/>
+      <c r="AE13" s="43"/>
+      <c r="AF13" s="43"/>
+      <c r="AG13" s="43"/>
+      <c r="AH13" s="43"/>
+      <c r="AI13" s="43"/>
+      <c r="AJ13" s="43"/>
+      <c r="AK13" s="43"/>
+      <c r="AL13" s="43"/>
+      <c r="AM13" s="43"/>
+      <c r="AN13" s="43"/>
+      <c r="AO13" s="43"/>
+      <c r="AP13" s="40"/>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" s="2">
@@ -6528,33 +6722,6 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="AO11:AO13"/>
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="AN11:AN13"/>
-    <mergeCell ref="AE11:AE13"/>
-    <mergeCell ref="AF11:AF13"/>
-    <mergeCell ref="AG11:AG13"/>
-    <mergeCell ref="AH11:AH13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="Z11:Z13"/>
-    <mergeCell ref="AA11:AA13"/>
-    <mergeCell ref="AB11:AB13"/>
-    <mergeCell ref="AC11:AC13"/>
-    <mergeCell ref="AD11:AD13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="V11:V13"/>
-    <mergeCell ref="W11:W13"/>
-    <mergeCell ref="X11:X13"/>
-    <mergeCell ref="Y11:Y13"/>
-    <mergeCell ref="P11:P13"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="T11:T13"/>
     <mergeCell ref="A1:AP1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A11:A13"/>
@@ -6571,6 +6738,33 @@
     <mergeCell ref="M11:M13"/>
     <mergeCell ref="N11:N13"/>
     <mergeCell ref="O11:O13"/>
+    <mergeCell ref="P11:P13"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="T11:T13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="V11:V13"/>
+    <mergeCell ref="W11:W13"/>
+    <mergeCell ref="X11:X13"/>
+    <mergeCell ref="Y11:Y13"/>
+    <mergeCell ref="Z11:Z13"/>
+    <mergeCell ref="AA11:AA13"/>
+    <mergeCell ref="AB11:AB13"/>
+    <mergeCell ref="AC11:AC13"/>
+    <mergeCell ref="AD11:AD13"/>
+    <mergeCell ref="AE11:AE13"/>
+    <mergeCell ref="AF11:AF13"/>
+    <mergeCell ref="AG11:AG13"/>
+    <mergeCell ref="AH11:AH13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="AO11:AO13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
+    <mergeCell ref="AN11:AN13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ТКИ-341_Реверс_Инжиниринг.xlsx
+++ b/ТКИ-341_Реверс_Инжиниринг.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\Reverse_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B77C032-7E55-41AA-B287-8C65D0FDEF30}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94A88632-7980-4E72-AC39-CB097B2A77D2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="108">
   <si>
     <t>ВЕДОМОСТЬ ПОСЕЩАЕМОСТИ ЗАНЯТИЙ СТУДЕНТАМИ ГРУППЫ ТКИ "Компьютерная безопасность" ИТТСУ РУТ (МИИТ)</t>
   </si>
@@ -593,6 +593,9 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -603,9 +606,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -914,67 +914,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:53" ht="14.45" customHeight="1">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
-      <c r="N1" s="40"/>
-      <c r="O1" s="40"/>
-      <c r="P1" s="40"/>
-      <c r="Q1" s="40"/>
-      <c r="R1" s="40"/>
-      <c r="S1" s="40"/>
-      <c r="T1" s="40"/>
-      <c r="U1" s="40"/>
-      <c r="V1" s="40"/>
-      <c r="W1" s="40"/>
-      <c r="X1" s="40"/>
-      <c r="Y1" s="40"/>
-      <c r="Z1" s="40"/>
-      <c r="AA1" s="40"/>
-      <c r="AB1" s="40"/>
-      <c r="AC1" s="40"/>
-      <c r="AD1" s="40"/>
-      <c r="AE1" s="40"/>
-      <c r="AF1" s="40"/>
-      <c r="AG1" s="40"/>
-      <c r="AH1" s="40"/>
-      <c r="AI1" s="40"/>
-      <c r="AJ1" s="40"/>
-      <c r="AK1" s="40"/>
-      <c r="AL1" s="40"/>
-      <c r="AM1" s="40"/>
-      <c r="AN1" s="40"/>
-      <c r="AO1" s="40"/>
-      <c r="AP1" s="40"/>
-      <c r="AQ1" s="40"/>
-      <c r="AR1" s="40"/>
-      <c r="AS1" s="40"/>
-      <c r="AT1" s="40"/>
-      <c r="AU1" s="40"/>
-      <c r="AV1" s="40"/>
-      <c r="AW1" s="40"/>
-      <c r="AX1" s="40"/>
-      <c r="AY1" s="40"/>
-      <c r="AZ1" s="40"/>
-      <c r="BA1" s="40"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="41"/>
+      <c r="T1" s="41"/>
+      <c r="U1" s="41"/>
+      <c r="V1" s="41"/>
+      <c r="W1" s="41"/>
+      <c r="X1" s="41"/>
+      <c r="Y1" s="41"/>
+      <c r="Z1" s="41"/>
+      <c r="AA1" s="41"/>
+      <c r="AB1" s="41"/>
+      <c r="AC1" s="41"/>
+      <c r="AD1" s="41"/>
+      <c r="AE1" s="41"/>
+      <c r="AF1" s="41"/>
+      <c r="AG1" s="41"/>
+      <c r="AH1" s="41"/>
+      <c r="AI1" s="41"/>
+      <c r="AJ1" s="41"/>
+      <c r="AK1" s="41"/>
+      <c r="AL1" s="41"/>
+      <c r="AM1" s="41"/>
+      <c r="AN1" s="41"/>
+      <c r="AO1" s="41"/>
+      <c r="AP1" s="41"/>
+      <c r="AQ1" s="41"/>
+      <c r="AR1" s="41"/>
+      <c r="AS1" s="41"/>
+      <c r="AT1" s="41"/>
+      <c r="AU1" s="41"/>
+      <c r="AV1" s="41"/>
+      <c r="AW1" s="41"/>
+      <c r="AX1" s="41"/>
+      <c r="AY1" s="41"/>
+      <c r="AZ1" s="41"/>
+      <c r="BA1" s="41"/>
     </row>
     <row r="2" spans="1:53" ht="27.6" customHeight="1">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="42"/>
+      <c r="B2" s="43"/>
       <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1207,7 +1207,9 @@
       <c r="S4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T4" s="3"/>
+      <c r="T4" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
@@ -1310,7 +1312,9 @@
       <c r="S5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="T5" s="3"/>
+      <c r="T5" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
@@ -1419,7 +1423,9 @@
       <c r="S6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T6" s="3"/>
+      <c r="T6" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
@@ -1528,7 +1534,9 @@
       <c r="S7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T7" s="3"/>
+      <c r="T7" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="U7" s="3"/>
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
@@ -1554,7 +1562,7 @@
       <c r="AI7" s="3">
         <v>5</v>
       </c>
-      <c r="AJ7" s="44">
+      <c r="AJ7" s="40">
         <v>46135</v>
       </c>
       <c r="AK7" s="34">
@@ -1647,7 +1655,9 @@
       <c r="S8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="T8" s="3"/>
+      <c r="T8" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
@@ -1756,7 +1766,9 @@
       <c r="S9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T9" s="3"/>
+      <c r="T9" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
@@ -1859,7 +1871,9 @@
       <c r="S10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T10" s="3"/>
+      <c r="T10" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
@@ -1966,7 +1980,9 @@
       <c r="S11" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="T11" s="5"/>
+      <c r="T11" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="U11" s="5"/>
       <c r="V11" s="5"/>
       <c r="W11" s="5"/>
@@ -2077,7 +2093,9 @@
       <c r="S12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="T12" s="5"/>
+      <c r="T12" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="U12" s="5"/>
       <c r="V12" s="5"/>
       <c r="W12" s="5"/>
@@ -2188,7 +2206,9 @@
       <c r="S13" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="T13" s="5"/>
+      <c r="T13" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="U13" s="5"/>
       <c r="V13" s="5"/>
       <c r="W13" s="5"/>
@@ -2214,7 +2234,7 @@
       <c r="AI13" s="5">
         <v>5</v>
       </c>
-      <c r="AJ13" s="44">
+      <c r="AJ13" s="40">
         <v>46135</v>
       </c>
       <c r="AK13" s="34">
@@ -2303,7 +2323,9 @@
       <c r="S14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="T14" s="3"/>
+      <c r="T14" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="U14" s="3"/>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
@@ -2404,7 +2426,9 @@
       <c r="S15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="T15" s="3"/>
+      <c r="T15" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="U15" s="3"/>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
@@ -2507,7 +2531,9 @@
       <c r="S16" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T16" s="3"/>
+      <c r="T16" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
@@ -2533,7 +2559,7 @@
       <c r="AI16" s="3">
         <v>5</v>
       </c>
-      <c r="AJ16" s="44">
+      <c r="AJ16" s="40">
         <v>46135</v>
       </c>
       <c r="AK16" s="37">
@@ -2626,7 +2652,9 @@
       <c r="S17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T17" s="3"/>
+      <c r="T17" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
@@ -2741,7 +2769,9 @@
       <c r="S18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T18" s="3"/>
+      <c r="T18" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
@@ -2767,7 +2797,7 @@
       <c r="AI18" s="3">
         <v>5</v>
       </c>
-      <c r="AJ18" s="44">
+      <c r="AJ18" s="40">
         <v>46135</v>
       </c>
       <c r="AK18" s="34">
@@ -2852,7 +2882,9 @@
       <c r="S19" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T19" s="3"/>
+      <c r="T19" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
@@ -2951,7 +2983,9 @@
       <c r="S20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="T20" s="3"/>
+      <c r="T20" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
@@ -3048,7 +3082,9 @@
       <c r="S21" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="T21" s="3"/>
+      <c r="T21" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
@@ -3149,7 +3185,9 @@
       <c r="S22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T22" s="3"/>
+      <c r="T22" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
@@ -3258,7 +3296,9 @@
       <c r="S23" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T23" s="3"/>
+      <c r="T23" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="U23" s="3"/>
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
@@ -3363,7 +3403,9 @@
       <c r="S24" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T24" s="3"/>
+      <c r="T24" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
@@ -3456,7 +3498,9 @@
       <c r="S25" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="T25" s="3"/>
+      <c r="T25" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
@@ -3511,7 +3555,7 @@
         <v>53</v>
       </c>
       <c r="C26" s="9">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D26" s="9"/>
       <c r="E26" s="9" t="s">
@@ -3559,7 +3603,9 @@
       <c r="S26" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="T26" s="3"/>
+      <c r="T26" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
@@ -3654,7 +3700,9 @@
       <c r="S27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T27" s="3"/>
+      <c r="T27" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="U27" s="3"/>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
@@ -3759,7 +3807,9 @@
       <c r="S28" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T28" s="3"/>
+      <c r="T28" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
@@ -3854,7 +3904,9 @@
       <c r="S29" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T29" s="3"/>
+      <c r="T29" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
@@ -3963,7 +4015,9 @@
       <c r="S30" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T30" s="3"/>
+      <c r="T30" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
@@ -3989,7 +4043,7 @@
       <c r="AI30" s="3">
         <v>5</v>
       </c>
-      <c r="AJ30" s="44">
+      <c r="AJ30" s="40">
         <v>46135</v>
       </c>
       <c r="AK30" s="37">
@@ -4076,7 +4130,9 @@
       <c r="S31" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T31" s="3"/>
+      <c r="T31" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="U31" s="3"/>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
@@ -4177,7 +4233,9 @@
       <c r="S32" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T32" s="3"/>
+      <c r="T32" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
@@ -4270,7 +4328,9 @@
       <c r="S33" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T33" s="3"/>
+      <c r="T33" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
@@ -4371,7 +4431,9 @@
       <c r="S34" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T34" s="3"/>
+      <c r="T34" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
@@ -4397,7 +4459,7 @@
       <c r="AI34" s="5">
         <v>5</v>
       </c>
-      <c r="AJ34" s="44">
+      <c r="AJ34" s="40">
         <v>46135</v>
       </c>
       <c r="AK34" s="34">
@@ -4482,7 +4544,9 @@
       <c r="S35" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="T35" s="3"/>
+      <c r="T35" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
@@ -4575,7 +4639,9 @@
       <c r="S36" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="T36" s="3"/>
+      <c r="T36" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
@@ -4953,56 +5019,56 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
-      <c r="N1" s="40"/>
-      <c r="O1" s="40"/>
-      <c r="P1" s="40"/>
-      <c r="Q1" s="40"/>
-      <c r="R1" s="40"/>
-      <c r="S1" s="40"/>
-      <c r="T1" s="40"/>
-      <c r="U1" s="40"/>
-      <c r="V1" s="40"/>
-      <c r="W1" s="40"/>
-      <c r="X1" s="40"/>
-      <c r="Y1" s="40"/>
-      <c r="Z1" s="40"/>
-      <c r="AA1" s="40"/>
-      <c r="AB1" s="40"/>
-      <c r="AC1" s="40"/>
-      <c r="AD1" s="40"/>
-      <c r="AE1" s="40"/>
-      <c r="AF1" s="40"/>
-      <c r="AG1" s="40"/>
-      <c r="AH1" s="40"/>
-      <c r="AI1" s="40"/>
-      <c r="AJ1" s="40"/>
-      <c r="AK1" s="40"/>
-      <c r="AL1" s="40"/>
-      <c r="AM1" s="40"/>
-      <c r="AN1" s="40"/>
-      <c r="AO1" s="40"/>
-      <c r="AP1" s="40"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="41"/>
+      <c r="T1" s="41"/>
+      <c r="U1" s="41"/>
+      <c r="V1" s="41"/>
+      <c r="W1" s="41"/>
+      <c r="X1" s="41"/>
+      <c r="Y1" s="41"/>
+      <c r="Z1" s="41"/>
+      <c r="AA1" s="41"/>
+      <c r="AB1" s="41"/>
+      <c r="AC1" s="41"/>
+      <c r="AD1" s="41"/>
+      <c r="AE1" s="41"/>
+      <c r="AF1" s="41"/>
+      <c r="AG1" s="41"/>
+      <c r="AH1" s="41"/>
+      <c r="AI1" s="41"/>
+      <c r="AJ1" s="41"/>
+      <c r="AK1" s="41"/>
+      <c r="AL1" s="41"/>
+      <c r="AM1" s="41"/>
+      <c r="AN1" s="41"/>
+      <c r="AO1" s="41"/>
+      <c r="AP1" s="41"/>
     </row>
     <row r="2" spans="1:42" ht="30">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="42"/>
+      <c r="B2" s="43"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -5431,142 +5497,142 @@
       <c r="AP10" s="1"/>
     </row>
     <row r="11" spans="1:42">
-      <c r="A11" s="42">
+      <c r="A11" s="43">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="42"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="43"/>
-      <c r="M11" s="43"/>
-      <c r="N11" s="43"/>
-      <c r="O11" s="43"/>
-      <c r="P11" s="43"/>
-      <c r="Q11" s="43"/>
-      <c r="R11" s="43"/>
-      <c r="S11" s="43"/>
-      <c r="T11" s="43"/>
-      <c r="U11" s="43"/>
-      <c r="V11" s="43"/>
-      <c r="W11" s="43"/>
-      <c r="X11" s="43"/>
-      <c r="Y11" s="43"/>
-      <c r="Z11" s="43"/>
-      <c r="AA11" s="43"/>
-      <c r="AB11" s="43"/>
-      <c r="AC11" s="43"/>
-      <c r="AD11" s="43"/>
-      <c r="AE11" s="43"/>
-      <c r="AF11" s="43"/>
-      <c r="AG11" s="43"/>
-      <c r="AH11" s="43"/>
-      <c r="AI11" s="43"/>
-      <c r="AJ11" s="43"/>
-      <c r="AK11" s="43"/>
-      <c r="AL11" s="43"/>
-      <c r="AM11" s="43"/>
-      <c r="AN11" s="43"/>
-      <c r="AO11" s="43"/>
-      <c r="AP11" s="40"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="43"/>
+      <c r="L11" s="44"/>
+      <c r="M11" s="44"/>
+      <c r="N11" s="44"/>
+      <c r="O11" s="44"/>
+      <c r="P11" s="44"/>
+      <c r="Q11" s="44"/>
+      <c r="R11" s="44"/>
+      <c r="S11" s="44"/>
+      <c r="T11" s="44"/>
+      <c r="U11" s="44"/>
+      <c r="V11" s="44"/>
+      <c r="W11" s="44"/>
+      <c r="X11" s="44"/>
+      <c r="Y11" s="44"/>
+      <c r="Z11" s="44"/>
+      <c r="AA11" s="44"/>
+      <c r="AB11" s="44"/>
+      <c r="AC11" s="44"/>
+      <c r="AD11" s="44"/>
+      <c r="AE11" s="44"/>
+      <c r="AF11" s="44"/>
+      <c r="AG11" s="44"/>
+      <c r="AH11" s="44"/>
+      <c r="AI11" s="44"/>
+      <c r="AJ11" s="44"/>
+      <c r="AK11" s="44"/>
+      <c r="AL11" s="44"/>
+      <c r="AM11" s="44"/>
+      <c r="AN11" s="44"/>
+      <c r="AO11" s="44"/>
+      <c r="AP11" s="41"/>
     </row>
     <row r="12" spans="1:42">
-      <c r="A12" s="42"/>
+      <c r="A12" s="43"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="42"/>
-      <c r="K12" s="42"/>
-      <c r="L12" s="43"/>
-      <c r="M12" s="43"/>
-      <c r="N12" s="43"/>
-      <c r="O12" s="43"/>
-      <c r="P12" s="43"/>
-      <c r="Q12" s="43"/>
-      <c r="R12" s="43"/>
-      <c r="S12" s="43"/>
-      <c r="T12" s="43"/>
-      <c r="U12" s="43"/>
-      <c r="V12" s="43"/>
-      <c r="W12" s="43"/>
-      <c r="X12" s="43"/>
-      <c r="Y12" s="43"/>
-      <c r="Z12" s="43"/>
-      <c r="AA12" s="43"/>
-      <c r="AB12" s="43"/>
-      <c r="AC12" s="43"/>
-      <c r="AD12" s="43"/>
-      <c r="AE12" s="43"/>
-      <c r="AF12" s="43"/>
-      <c r="AG12" s="43"/>
-      <c r="AH12" s="43"/>
-      <c r="AI12" s="43"/>
-      <c r="AJ12" s="43"/>
-      <c r="AK12" s="43"/>
-      <c r="AL12" s="43"/>
-      <c r="AM12" s="43"/>
-      <c r="AN12" s="43"/>
-      <c r="AO12" s="43"/>
-      <c r="AP12" s="40"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="44"/>
+      <c r="M12" s="44"/>
+      <c r="N12" s="44"/>
+      <c r="O12" s="44"/>
+      <c r="P12" s="44"/>
+      <c r="Q12" s="44"/>
+      <c r="R12" s="44"/>
+      <c r="S12" s="44"/>
+      <c r="T12" s="44"/>
+      <c r="U12" s="44"/>
+      <c r="V12" s="44"/>
+      <c r="W12" s="44"/>
+      <c r="X12" s="44"/>
+      <c r="Y12" s="44"/>
+      <c r="Z12" s="44"/>
+      <c r="AA12" s="44"/>
+      <c r="AB12" s="44"/>
+      <c r="AC12" s="44"/>
+      <c r="AD12" s="44"/>
+      <c r="AE12" s="44"/>
+      <c r="AF12" s="44"/>
+      <c r="AG12" s="44"/>
+      <c r="AH12" s="44"/>
+      <c r="AI12" s="44"/>
+      <c r="AJ12" s="44"/>
+      <c r="AK12" s="44"/>
+      <c r="AL12" s="44"/>
+      <c r="AM12" s="44"/>
+      <c r="AN12" s="44"/>
+      <c r="AO12" s="44"/>
+      <c r="AP12" s="41"/>
     </row>
     <row r="13" spans="1:42">
-      <c r="A13" s="42"/>
+      <c r="A13" s="43"/>
       <c r="B13" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="42"/>
-      <c r="K13" s="42"/>
-      <c r="L13" s="43"/>
-      <c r="M13" s="43"/>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="43"/>
-      <c r="T13" s="43"/>
-      <c r="U13" s="43"/>
-      <c r="V13" s="43"/>
-      <c r="W13" s="43"/>
-      <c r="X13" s="43"/>
-      <c r="Y13" s="43"/>
-      <c r="Z13" s="43"/>
-      <c r="AA13" s="43"/>
-      <c r="AB13" s="43"/>
-      <c r="AC13" s="43"/>
-      <c r="AD13" s="43"/>
-      <c r="AE13" s="43"/>
-      <c r="AF13" s="43"/>
-      <c r="AG13" s="43"/>
-      <c r="AH13" s="43"/>
-      <c r="AI13" s="43"/>
-      <c r="AJ13" s="43"/>
-      <c r="AK13" s="43"/>
-      <c r="AL13" s="43"/>
-      <c r="AM13" s="43"/>
-      <c r="AN13" s="43"/>
-      <c r="AO13" s="43"/>
-      <c r="AP13" s="40"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="43"/>
+      <c r="L13" s="44"/>
+      <c r="M13" s="44"/>
+      <c r="N13" s="44"/>
+      <c r="O13" s="44"/>
+      <c r="P13" s="44"/>
+      <c r="Q13" s="44"/>
+      <c r="R13" s="44"/>
+      <c r="S13" s="44"/>
+      <c r="T13" s="44"/>
+      <c r="U13" s="44"/>
+      <c r="V13" s="44"/>
+      <c r="W13" s="44"/>
+      <c r="X13" s="44"/>
+      <c r="Y13" s="44"/>
+      <c r="Z13" s="44"/>
+      <c r="AA13" s="44"/>
+      <c r="AB13" s="44"/>
+      <c r="AC13" s="44"/>
+      <c r="AD13" s="44"/>
+      <c r="AE13" s="44"/>
+      <c r="AF13" s="44"/>
+      <c r="AG13" s="44"/>
+      <c r="AH13" s="44"/>
+      <c r="AI13" s="44"/>
+      <c r="AJ13" s="44"/>
+      <c r="AK13" s="44"/>
+      <c r="AL13" s="44"/>
+      <c r="AM13" s="44"/>
+      <c r="AN13" s="44"/>
+      <c r="AO13" s="44"/>
+      <c r="AP13" s="41"/>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" s="2">
@@ -6722,6 +6788,33 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="AO11:AO13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
+    <mergeCell ref="AN11:AN13"/>
+    <mergeCell ref="AE11:AE13"/>
+    <mergeCell ref="AF11:AF13"/>
+    <mergeCell ref="AG11:AG13"/>
+    <mergeCell ref="AH11:AH13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="Z11:Z13"/>
+    <mergeCell ref="AA11:AA13"/>
+    <mergeCell ref="AB11:AB13"/>
+    <mergeCell ref="AC11:AC13"/>
+    <mergeCell ref="AD11:AD13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="V11:V13"/>
+    <mergeCell ref="W11:W13"/>
+    <mergeCell ref="X11:X13"/>
+    <mergeCell ref="Y11:Y13"/>
+    <mergeCell ref="P11:P13"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="T11:T13"/>
     <mergeCell ref="A1:AP1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A11:A13"/>
@@ -6738,33 +6831,6 @@
     <mergeCell ref="M11:M13"/>
     <mergeCell ref="N11:N13"/>
     <mergeCell ref="O11:O13"/>
-    <mergeCell ref="P11:P13"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="T11:T13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="V11:V13"/>
-    <mergeCell ref="W11:W13"/>
-    <mergeCell ref="X11:X13"/>
-    <mergeCell ref="Y11:Y13"/>
-    <mergeCell ref="Z11:Z13"/>
-    <mergeCell ref="AA11:AA13"/>
-    <mergeCell ref="AB11:AB13"/>
-    <mergeCell ref="AC11:AC13"/>
-    <mergeCell ref="AD11:AD13"/>
-    <mergeCell ref="AE11:AE13"/>
-    <mergeCell ref="AF11:AF13"/>
-    <mergeCell ref="AG11:AG13"/>
-    <mergeCell ref="AH11:AH13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="AO11:AO13"/>
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="AN11:AN13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ТКИ-341_Реверс_Инжиниринг.xlsx
+++ b/ТКИ-341_Реверс_Инжиниринг.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\Reverse_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94A88632-7980-4E72-AC39-CB097B2A77D2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09247BD0-6704-459F-998B-80211BAE764F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="120">
   <si>
     <t>ВЕДОМОСТЬ ПОСЕЩАЕМОСТИ ЗАНЯТИЙ СТУДЕНТАМИ ГРУППЫ ТКИ "Компьютерная безопасность" ИТТСУ РУТ (МИИТ)</t>
   </si>
@@ -380,13 +380,49 @@
     <t>сумма элементов массива с нечетными значениями</t>
   </si>
   <si>
-    <t>Кручинин, Дамир (5)</t>
-  </si>
-  <si>
     <t>площадь или периметр треугольника</t>
   </si>
   <si>
     <t>потенциальная энергия пружины</t>
+  </si>
+  <si>
+    <t>Чью задачу решали</t>
+  </si>
+  <si>
+    <t>Кому досталась их задача</t>
+  </si>
+  <si>
+    <t>16 - решение квадратного уравения (Буланый, Горковец)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Крецу (16) </t>
+  </si>
+  <si>
+    <t>Иконников, Наседкин</t>
+  </si>
+  <si>
+    <t>Небоваренков Степан (4)</t>
+  </si>
+  <si>
+    <t>площадь и периметрпрямоугольника</t>
+  </si>
+  <si>
+    <t>Рина (5)</t>
+  </si>
+  <si>
+    <t>генератор случайных чисел</t>
+  </si>
+  <si>
+    <t>Кручинин, Дамир (12)</t>
+  </si>
+  <si>
+    <t>разложение на множители</t>
+  </si>
+  <si>
+    <t>площадь или периметр треугольника (Беймель, 12)</t>
+  </si>
+  <si>
+    <t>9-Хоптий, Бойков</t>
   </si>
 </sst>
 </file>
@@ -419,7 +455,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -462,6 +498,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -490,7 +532,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -593,7 +635,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -607,6 +649,13 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -907,10 +956,12 @@
     <col min="30" max="30" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="10.5703125" style="32" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="9" style="32"/>
     <col min="44" max="44" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="9" style="32"/>
+    <col min="47" max="47" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:53" ht="14.45" customHeight="1">
@@ -1064,14 +1115,18 @@
         <v>7</v>
       </c>
       <c r="AI2" s="3"/>
-      <c r="AJ2" s="3" t="s">
+      <c r="AJ2" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="AK2" s="37"/>
-      <c r="AL2" s="3"/>
+      <c r="AK2" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="AL2" s="3" t="s">
+        <v>107</v>
+      </c>
       <c r="AM2" s="37"/>
       <c r="AN2" s="37"/>
-      <c r="AO2" s="3" t="s">
+      <c r="AO2" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AP2" s="3"/>
@@ -1082,7 +1137,9 @@
       <c r="AT2" s="3"/>
       <c r="AU2" s="3"/>
       <c r="AV2" s="3"/>
-      <c r="AW2" s="3"/>
+      <c r="AW2" s="3" t="s">
+        <v>101</v>
+      </c>
       <c r="AX2" s="3"/>
       <c r="AY2" s="3"/>
       <c r="AZ2" s="3"/>
@@ -1130,12 +1187,12 @@
       <c r="AG3" s="19"/>
       <c r="AH3" s="19"/>
       <c r="AI3" s="19"/>
-      <c r="AJ3" s="19"/>
+      <c r="AJ3" s="30"/>
       <c r="AK3" s="19"/>
       <c r="AL3" s="19"/>
       <c r="AM3" s="19"/>
       <c r="AN3" s="19"/>
-      <c r="AO3" s="19"/>
+      <c r="AO3" s="30"/>
       <c r="AP3" s="19"/>
       <c r="AQ3" s="19"/>
       <c r="AR3" s="19"/>
@@ -1210,8 +1267,12 @@
       <c r="T4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
+      <c r="U4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
@@ -1221,20 +1282,28 @@
         <v>46086</v>
       </c>
       <c r="AC4" s="3"/>
-      <c r="AD4" s="3"/>
+      <c r="AD4" s="24">
+        <v>46149</v>
+      </c>
       <c r="AE4" s="3"/>
-      <c r="AF4" s="3"/>
+      <c r="AF4" s="24">
+        <v>46149</v>
+      </c>
       <c r="AG4" s="3"/>
-      <c r="AH4" s="3"/>
+      <c r="AH4" s="24">
+        <v>46149</v>
+      </c>
       <c r="AI4" s="3">
         <v>3</v>
       </c>
-      <c r="AJ4" s="3"/>
+      <c r="AJ4" s="30"/>
       <c r="AK4" s="37"/>
-      <c r="AL4" s="3"/>
+      <c r="AL4" s="3">
+        <v>15</v>
+      </c>
       <c r="AM4" s="37"/>
       <c r="AN4" s="37"/>
-      <c r="AO4" s="28" t="s">
+      <c r="AO4" s="45" t="s">
         <v>72</v>
       </c>
       <c r="AP4" s="29" t="s">
@@ -1315,8 +1384,12 @@
       <c r="T5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
+      <c r="U5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="V5" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
@@ -1340,12 +1413,14 @@
       <c r="AI5" s="3">
         <v>5</v>
       </c>
-      <c r="AJ5" s="3"/>
+      <c r="AJ5" s="30"/>
       <c r="AK5" s="37"/>
-      <c r="AL5" s="3"/>
+      <c r="AL5" s="3">
+        <v>13</v>
+      </c>
       <c r="AM5" s="37"/>
       <c r="AN5" s="37"/>
-      <c r="AO5" s="28" t="s">
+      <c r="AO5" s="45" t="s">
         <v>75</v>
       </c>
       <c r="AP5" s="28" t="s">
@@ -1426,8 +1501,12 @@
       <c r="T6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
+      <c r="U6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V6" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
@@ -1451,12 +1530,18 @@
       <c r="AI6" s="3">
         <v>3</v>
       </c>
-      <c r="AJ6" s="3"/>
+      <c r="AJ6" s="30"/>
       <c r="AK6" s="37"/>
-      <c r="AL6" s="3"/>
-      <c r="AM6" s="37"/>
-      <c r="AN6" s="37"/>
-      <c r="AO6" s="28" t="s">
+      <c r="AL6" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AM6" s="24">
+        <v>46149</v>
+      </c>
+      <c r="AN6" s="37" t="s">
+        <v>115</v>
+      </c>
+      <c r="AO6" s="45" t="s">
         <v>72</v>
       </c>
       <c r="AP6" s="29" t="s">
@@ -1537,8 +1622,12 @@
       <c r="T7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
+      <c r="U7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V7" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
@@ -1562,20 +1651,22 @@
       <c r="AI7" s="3">
         <v>5</v>
       </c>
-      <c r="AJ7" s="40">
+      <c r="AJ7" s="46">
         <v>46135</v>
       </c>
       <c r="AK7" s="34">
         <v>12</v>
       </c>
       <c r="AL7" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM7" s="24">
+        <v>46135</v>
+      </c>
+      <c r="AN7" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="AM7" s="5"/>
-      <c r="AN7" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="AO7" s="28" t="s">
+      <c r="AO7" s="45" t="s">
         <v>75</v>
       </c>
       <c r="AP7" s="29" t="s">
@@ -1591,7 +1682,9 @@
       <c r="AT7" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="AU7" s="33"/>
+      <c r="AU7" s="24">
+        <v>46149</v>
+      </c>
       <c r="AV7" s="3"/>
       <c r="AW7" s="3"/>
       <c r="AX7" s="3"/>
@@ -1599,7 +1692,7 @@
       <c r="AZ7" s="3"/>
       <c r="BA7" s="1"/>
     </row>
-    <row r="8" spans="1:53" ht="105">
+    <row r="8" spans="1:53" ht="120">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -1658,8 +1751,12 @@
       <c r="T8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
+      <c r="U8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
@@ -1679,16 +1776,17 @@
       <c r="AI8" s="3">
         <v>3</v>
       </c>
-      <c r="AJ8" s="3"/>
-      <c r="AK8" s="37"/>
-      <c r="AL8" s="3"/>
+      <c r="AJ8" s="30"/>
+      <c r="AK8" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL8" s="3">
+        <v>17</v>
+      </c>
       <c r="AM8" s="24">
         <v>46135</v>
       </c>
-      <c r="AN8" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="AO8" s="28" t="s">
+      <c r="AO8" s="45" t="s">
         <v>72</v>
       </c>
       <c r="AP8" s="29" t="s">
@@ -1708,7 +1806,7 @@
       <c r="AZ8" s="3"/>
       <c r="BA8" s="1"/>
     </row>
-    <row r="9" spans="1:53" ht="45">
+    <row r="9" spans="1:53" ht="75">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -1769,8 +1867,12 @@
       <c r="T9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
+      <c r="U9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
@@ -1790,12 +1892,18 @@
       <c r="AI9" s="3">
         <v>3</v>
       </c>
-      <c r="AJ9" s="33"/>
+      <c r="AJ9" s="30"/>
       <c r="AK9" s="33"/>
-      <c r="AL9" s="3"/>
-      <c r="AM9" s="37"/>
-      <c r="AN9" s="37"/>
-      <c r="AO9" s="28" t="s">
+      <c r="AL9" s="40">
+        <v>14</v>
+      </c>
+      <c r="AM9" s="24">
+        <v>46149</v>
+      </c>
+      <c r="AN9" s="40" t="s">
+        <v>113</v>
+      </c>
+      <c r="AO9" s="45" t="s">
         <v>75</v>
       </c>
       <c r="AP9" s="29" t="s">
@@ -1874,8 +1982,12 @@
       <c r="T10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
+      <c r="U10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
@@ -1899,12 +2011,16 @@
       <c r="AI10" s="3">
         <v>4</v>
       </c>
-      <c r="AJ10" s="3"/>
+      <c r="AJ10" s="30"/>
       <c r="AK10" s="37"/>
-      <c r="AL10" s="3"/>
-      <c r="AM10" s="37"/>
+      <c r="AL10" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AM10" s="24">
+        <v>46149</v>
+      </c>
       <c r="AN10" s="37"/>
-      <c r="AO10" s="28" t="s">
+      <c r="AO10" s="45" t="s">
         <v>72</v>
       </c>
       <c r="AP10" s="29" t="s">
@@ -1924,7 +2040,7 @@
       <c r="AZ10" s="3"/>
       <c r="BA10" s="1"/>
     </row>
-    <row r="11" spans="1:53" ht="14.45" customHeight="1">
+    <row r="11" spans="1:53" ht="89.25" customHeight="1">
       <c r="A11" s="2">
         <v>8</v>
       </c>
@@ -1983,8 +2099,12 @@
       <c r="T11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="U11" s="5"/>
-      <c r="V11" s="5"/>
+      <c r="U11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="V11" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="W11" s="5"/>
       <c r="X11" s="5"/>
       <c r="Y11" s="5"/>
@@ -2008,12 +2128,20 @@
       <c r="AI11" s="5">
         <v>5</v>
       </c>
-      <c r="AJ11" s="5"/>
-      <c r="AK11" s="5"/>
-      <c r="AL11" s="5"/>
-      <c r="AM11" s="5"/>
-      <c r="AN11" s="5"/>
-      <c r="AO11" s="28" t="s">
+      <c r="AJ11" s="31"/>
+      <c r="AK11" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="AL11" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="AM11" s="24">
+        <v>46149</v>
+      </c>
+      <c r="AN11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AO11" s="45" t="s">
         <v>72</v>
       </c>
       <c r="AP11" s="29" t="s">
@@ -2096,8 +2224,12 @@
       <c r="T12" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="U12" s="5"/>
-      <c r="V12" s="5"/>
+      <c r="U12" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="V12" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="W12" s="5"/>
       <c r="X12" s="5"/>
       <c r="Y12" s="5"/>
@@ -2121,12 +2253,14 @@
       <c r="AI12" s="5">
         <v>5</v>
       </c>
-      <c r="AJ12" s="5"/>
+      <c r="AJ12" s="31"/>
       <c r="AK12" s="5"/>
-      <c r="AL12" s="5"/>
+      <c r="AL12" s="5">
+        <v>10</v>
+      </c>
       <c r="AM12" s="5"/>
       <c r="AN12" s="5"/>
-      <c r="AO12" s="28" t="s">
+      <c r="AO12" s="45" t="s">
         <v>72</v>
       </c>
       <c r="AP12" s="29" t="s">
@@ -2209,8 +2343,12 @@
       <c r="T13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="U13" s="5"/>
-      <c r="V13" s="5"/>
+      <c r="U13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="V13" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="W13" s="5"/>
       <c r="X13" s="5"/>
       <c r="Y13" s="5"/>
@@ -2234,20 +2372,17 @@
       <c r="AI13" s="5">
         <v>5</v>
       </c>
-      <c r="AJ13" s="40">
+      <c r="AJ13" s="46">
         <v>46135</v>
       </c>
       <c r="AK13" s="34">
         <v>11</v>
-      </c>
-      <c r="AL13" s="5" t="s">
-        <v>103</v>
       </c>
       <c r="AM13" s="5"/>
       <c r="AN13" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="AO13" s="28" t="s">
+      <c r="AO13" s="45" t="s">
         <v>72</v>
       </c>
       <c r="AP13" s="29" t="s">
@@ -2326,8 +2461,12 @@
       <c r="T14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="U14" s="3"/>
-      <c r="V14" s="3"/>
+      <c r="U14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
@@ -2343,12 +2482,14 @@
       <c r="AI14" s="3">
         <v>2</v>
       </c>
-      <c r="AJ14" s="3"/>
+      <c r="AJ14" s="30"/>
       <c r="AK14" s="37"/>
-      <c r="AL14" s="3"/>
+      <c r="AL14" s="3">
+        <v>3</v>
+      </c>
       <c r="AM14" s="37"/>
       <c r="AN14" s="37"/>
-      <c r="AO14" s="28" t="s">
+      <c r="AO14" s="45" t="s">
         <v>72</v>
       </c>
       <c r="AP14" s="29" t="s">
@@ -2368,7 +2509,7 @@
       <c r="AZ14" s="3"/>
       <c r="BA14" s="1"/>
     </row>
-    <row r="15" spans="1:53">
+    <row r="15" spans="1:53" ht="75">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -2429,8 +2570,12 @@
       <c r="T15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="U15" s="3"/>
-      <c r="V15" s="3"/>
+      <c r="U15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
@@ -2454,12 +2599,18 @@
       <c r="AI15" s="3">
         <v>5</v>
       </c>
-      <c r="AJ15" s="3"/>
+      <c r="AJ15" s="30"/>
       <c r="AK15" s="37"/>
-      <c r="AL15" s="3"/>
-      <c r="AM15" s="37"/>
-      <c r="AN15" s="37"/>
-      <c r="AO15" s="3"/>
+      <c r="AL15" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="AM15" s="24">
+        <v>46149</v>
+      </c>
+      <c r="AN15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AO15" s="30"/>
       <c r="AP15" s="3"/>
       <c r="AQ15" s="3"/>
       <c r="AR15" s="24">
@@ -2534,8 +2685,12 @@
       <c r="T16" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
+      <c r="U16" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V16" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
@@ -2559,18 +2714,18 @@
       <c r="AI16" s="3">
         <v>5</v>
       </c>
-      <c r="AJ16" s="40">
+      <c r="AJ16" s="46">
         <v>46135</v>
       </c>
-      <c r="AK16" s="37">
+      <c r="AK16" s="37"/>
+      <c r="AL16" s="38">
         <v>7</v>
       </c>
-      <c r="AL16" s="38"/>
       <c r="AM16" s="37"/>
       <c r="AN16" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="AO16" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="AO16" s="45" t="s">
         <v>72</v>
       </c>
       <c r="AP16" s="29" t="s">
@@ -2655,8 +2810,12 @@
       <c r="T17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U17" s="3"/>
-      <c r="V17" s="3"/>
+      <c r="U17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="W17" s="3"/>
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
@@ -2680,16 +2839,20 @@
       <c r="AI17" s="3">
         <v>5</v>
       </c>
-      <c r="AJ17" s="3"/>
-      <c r="AK17" s="37"/>
-      <c r="AL17" s="3"/>
+      <c r="AJ17" s="30"/>
+      <c r="AK17" s="37">
+        <v>13</v>
+      </c>
+      <c r="AL17" s="47">
+        <v>1</v>
+      </c>
       <c r="AM17" s="24">
         <v>46135</v>
       </c>
       <c r="AN17" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="AO17" s="28" t="s">
+      <c r="AO17" s="45" t="s">
         <v>72</v>
       </c>
       <c r="AP17" s="29" t="s">
@@ -2772,8 +2935,12 @@
       <c r="T18" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
+      <c r="U18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
@@ -2797,20 +2964,18 @@
       <c r="AI18" s="3">
         <v>5</v>
       </c>
-      <c r="AJ18" s="40">
-        <v>46135</v>
-      </c>
+      <c r="AJ18" s="46"/>
       <c r="AK18" s="34">
         <v>12</v>
       </c>
-      <c r="AL18" s="5" t="s">
+      <c r="AL18" s="5"/>
+      <c r="AM18" s="24">
+        <v>46135</v>
+      </c>
+      <c r="AN18" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="AM18" s="5"/>
-      <c r="AN18" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="AO18" s="3"/>
+      <c r="AO18" s="30"/>
       <c r="AP18" s="3"/>
       <c r="AQ18" s="3"/>
       <c r="AR18" s="24">
@@ -2818,7 +2983,9 @@
       </c>
       <c r="AS18" s="30"/>
       <c r="AT18" s="3"/>
-      <c r="AU18" s="33"/>
+      <c r="AU18" s="24">
+        <v>46149</v>
+      </c>
       <c r="AV18" s="3"/>
       <c r="AW18" s="3"/>
       <c r="AX18" s="3"/>
@@ -2826,7 +2993,7 @@
       <c r="AZ18" s="3"/>
       <c r="BA18" s="1"/>
     </row>
-    <row r="19" spans="1:53">
+    <row r="19" spans="1:53" ht="75">
       <c r="A19" s="2">
         <v>16</v>
       </c>
@@ -2885,8 +3052,12 @@
       <c r="T19" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
+      <c r="U19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V19" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
@@ -2906,12 +3077,18 @@
       <c r="AI19" s="3">
         <v>3</v>
       </c>
-      <c r="AJ19" s="3"/>
+      <c r="AJ19" s="30"/>
       <c r="AK19" s="37"/>
-      <c r="AL19" s="3"/>
-      <c r="AM19" s="37"/>
-      <c r="AN19" s="37"/>
-      <c r="AO19" s="3"/>
+      <c r="AL19" s="40">
+        <v>14</v>
+      </c>
+      <c r="AM19" s="24">
+        <v>46149</v>
+      </c>
+      <c r="AN19" s="40" t="s">
+        <v>113</v>
+      </c>
+      <c r="AO19" s="30"/>
       <c r="AP19" s="3"/>
       <c r="AQ19" s="3"/>
       <c r="AR19" s="3"/>
@@ -2925,7 +3102,7 @@
       <c r="AZ19" s="3"/>
       <c r="BA19" s="1"/>
     </row>
-    <row r="20" spans="1:53">
+    <row r="20" spans="1:53" ht="135">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -2986,8 +3163,12 @@
       <c r="T20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U20" s="3"/>
-      <c r="V20" s="3"/>
+      <c r="U20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="W20" s="3"/>
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
@@ -3005,12 +3186,16 @@
       <c r="AI20" s="3">
         <v>2</v>
       </c>
-      <c r="AJ20" s="3"/>
-      <c r="AK20" s="37"/>
-      <c r="AL20" s="3"/>
+      <c r="AJ20" s="30"/>
+      <c r="AK20" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="AL20" s="3">
+        <v>6</v>
+      </c>
       <c r="AM20" s="37"/>
       <c r="AN20" s="37"/>
-      <c r="AO20" s="3"/>
+      <c r="AO20" s="30"/>
       <c r="AP20" s="3"/>
       <c r="AQ20" s="3"/>
       <c r="AR20" s="3"/>
@@ -3085,8 +3270,12 @@
       <c r="T21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U21" s="3"/>
-      <c r="V21" s="3"/>
+      <c r="U21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="W21" s="3"/>
       <c r="X21" s="3"/>
       <c r="Y21" s="3"/>
@@ -3106,16 +3295,16 @@
       <c r="AI21" s="3">
         <v>3</v>
       </c>
-      <c r="AJ21" s="3"/>
+      <c r="AJ21" s="30"/>
       <c r="AK21" s="37"/>
       <c r="AL21" s="3"/>
       <c r="AM21" s="24">
         <v>46135</v>
       </c>
       <c r="AN21" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="AO21" s="3"/>
+        <v>105</v>
+      </c>
+      <c r="AO21" s="30"/>
       <c r="AP21" s="3"/>
       <c r="AQ21" s="3"/>
       <c r="AR21" s="3"/>
@@ -3129,7 +3318,7 @@
       <c r="AZ21" s="3"/>
       <c r="BA21" s="1"/>
     </row>
-    <row r="22" spans="1:53" ht="45">
+    <row r="22" spans="1:53" ht="60">
       <c r="A22" s="2">
         <v>19</v>
       </c>
@@ -3188,8 +3377,12 @@
       <c r="T22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="U22" s="3"/>
-      <c r="V22" s="3"/>
+      <c r="U22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
@@ -3213,12 +3406,18 @@
       <c r="AI22" s="3">
         <v>5</v>
       </c>
-      <c r="AJ22" s="3"/>
+      <c r="AJ22" s="30"/>
       <c r="AK22" s="37"/>
-      <c r="AL22" s="3"/>
-      <c r="AM22" s="37"/>
-      <c r="AN22" s="37"/>
-      <c r="AO22" s="28" t="s">
+      <c r="AL22" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AM22" s="24">
+        <v>46135</v>
+      </c>
+      <c r="AN22" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="AO22" s="45" t="s">
         <v>75</v>
       </c>
       <c r="AP22" s="29" t="s">
@@ -3238,7 +3437,7 @@
       <c r="AZ22" s="3"/>
       <c r="BA22" s="1"/>
     </row>
-    <row r="23" spans="1:53">
+    <row r="23" spans="1:53" ht="60">
       <c r="A23" s="2">
         <v>20</v>
       </c>
@@ -3299,8 +3498,12 @@
       <c r="T23" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U23" s="3"/>
-      <c r="V23" s="3"/>
+      <c r="U23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V23" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="W23" s="3"/>
       <c r="X23" s="3"/>
       <c r="Y23" s="3"/>
@@ -3324,12 +3527,18 @@
       <c r="AI23" s="3">
         <v>5</v>
       </c>
-      <c r="AJ23" s="3"/>
+      <c r="AJ23" s="30"/>
       <c r="AK23" s="37"/>
-      <c r="AL23" s="3"/>
-      <c r="AM23" s="37"/>
-      <c r="AN23" s="37"/>
-      <c r="AO23" s="3"/>
+      <c r="AL23" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="AM23" s="24">
+        <v>46135</v>
+      </c>
+      <c r="AN23" s="37" t="s">
+        <v>117</v>
+      </c>
+      <c r="AO23" s="30"/>
       <c r="AP23" s="3"/>
       <c r="AQ23" s="3"/>
       <c r="AR23" s="24">
@@ -3406,8 +3615,12 @@
       <c r="T24" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U24" s="3"/>
-      <c r="V24" s="3"/>
+      <c r="U24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
@@ -3423,12 +3636,14 @@
       <c r="AI24" s="3">
         <v>2</v>
       </c>
-      <c r="AJ24" s="3"/>
+      <c r="AJ24" s="30"/>
       <c r="AK24" s="37"/>
-      <c r="AL24" s="3"/>
+      <c r="AL24" s="3">
+        <v>2</v>
+      </c>
       <c r="AM24" s="37"/>
       <c r="AN24" s="37"/>
-      <c r="AO24" s="3"/>
+      <c r="AO24" s="30"/>
       <c r="AP24" s="3"/>
       <c r="AQ24" s="3"/>
       <c r="AR24" s="3"/>
@@ -3501,8 +3716,12 @@
       <c r="T25" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="U25" s="3"/>
-      <c r="V25" s="3"/>
+      <c r="U25" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V25" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
       <c r="Y25" s="3"/>
@@ -3526,12 +3745,12 @@
       <c r="AI25" s="3">
         <v>5</v>
       </c>
-      <c r="AJ25" s="3"/>
+      <c r="AJ25" s="30"/>
       <c r="AK25" s="37"/>
       <c r="AL25" s="3"/>
       <c r="AM25" s="37"/>
       <c r="AN25" s="37"/>
-      <c r="AO25" s="3"/>
+      <c r="AO25" s="30"/>
       <c r="AP25" s="3"/>
       <c r="AQ25" s="3"/>
       <c r="AR25" s="24">
@@ -3606,8 +3825,12 @@
       <c r="T26" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="U26" s="3"/>
-      <c r="V26" s="3"/>
+      <c r="U26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="V26" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
       <c r="Y26" s="3"/>
@@ -3623,12 +3846,12 @@
       <c r="AI26" s="3">
         <v>0</v>
       </c>
-      <c r="AJ26" s="3"/>
+      <c r="AJ26" s="30"/>
       <c r="AK26" s="37"/>
       <c r="AL26" s="3"/>
       <c r="AM26" s="37"/>
       <c r="AN26" s="37"/>
-      <c r="AO26" s="3"/>
+      <c r="AO26" s="30"/>
       <c r="AP26" s="3"/>
       <c r="AQ26" s="3"/>
       <c r="AR26" s="3"/>
@@ -3703,8 +3926,12 @@
       <c r="T27" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="U27" s="3"/>
-      <c r="V27" s="3"/>
+      <c r="U27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V27" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
       <c r="Y27" s="3"/>
@@ -3728,12 +3955,12 @@
       <c r="AI27" s="3">
         <v>5</v>
       </c>
-      <c r="AJ27" s="3"/>
+      <c r="AJ27" s="30"/>
       <c r="AK27" s="37"/>
       <c r="AL27" s="3"/>
       <c r="AM27" s="37"/>
       <c r="AN27" s="37"/>
-      <c r="AO27" s="3"/>
+      <c r="AO27" s="30"/>
       <c r="AP27" s="3"/>
       <c r="AQ27" s="3"/>
       <c r="AR27" s="24">
@@ -3810,8 +4037,12 @@
       <c r="T28" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U28" s="3"/>
-      <c r="V28" s="3"/>
+      <c r="U28" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V28" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
@@ -3821,20 +4052,26 @@
         <v>46086</v>
       </c>
       <c r="AC28" s="3"/>
-      <c r="AD28" s="3"/>
+      <c r="AD28" s="24">
+        <v>46149</v>
+      </c>
       <c r="AE28" s="3"/>
-      <c r="AF28" s="3"/>
+      <c r="AF28" s="24">
+        <v>46149</v>
+      </c>
       <c r="AG28" s="3"/>
-      <c r="AH28" s="3"/>
+      <c r="AH28" s="24">
+        <v>46149</v>
+      </c>
       <c r="AI28" s="3">
         <v>3</v>
       </c>
-      <c r="AJ28" s="3"/>
+      <c r="AJ28" s="30"/>
       <c r="AK28" s="37"/>
       <c r="AL28" s="3"/>
       <c r="AM28" s="37"/>
       <c r="AN28" s="37"/>
-      <c r="AO28" s="3"/>
+      <c r="AO28" s="30"/>
       <c r="AP28" s="3"/>
       <c r="AQ28" s="3"/>
       <c r="AR28" s="3"/>
@@ -3907,8 +4144,12 @@
       <c r="T29" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U29" s="3"/>
-      <c r="V29" s="3"/>
+      <c r="U29" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V29" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
       <c r="Y29" s="3"/>
@@ -3932,7 +4173,7 @@
       <c r="AI29" s="3">
         <v>5</v>
       </c>
-      <c r="AJ29" s="3"/>
+      <c r="AJ29" s="30"/>
       <c r="AK29" s="37"/>
       <c r="AL29" s="3"/>
       <c r="AM29" s="24">
@@ -3941,7 +4182,7 @@
       <c r="AN29" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="AO29" s="3"/>
+      <c r="AO29" s="30"/>
       <c r="AP29" s="3"/>
       <c r="AQ29" s="3"/>
       <c r="AR29" s="24">
@@ -4018,8 +4259,12 @@
       <c r="T30" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U30" s="3"/>
-      <c r="V30" s="3"/>
+      <c r="U30" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V30" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
@@ -4043,7 +4288,7 @@
       <c r="AI30" s="3">
         <v>5</v>
       </c>
-      <c r="AJ30" s="40">
+      <c r="AJ30" s="46">
         <v>46135</v>
       </c>
       <c r="AK30" s="37">
@@ -4052,9 +4297,9 @@
       <c r="AL30" s="38"/>
       <c r="AM30" s="37"/>
       <c r="AN30" s="37" t="s">
-        <v>107</v>
-      </c>
-      <c r="AO30" s="3"/>
+        <v>106</v>
+      </c>
+      <c r="AO30" s="30"/>
       <c r="AP30" s="3"/>
       <c r="AQ30" s="3"/>
       <c r="AR30" s="24">
@@ -4072,7 +4317,7 @@
       <c r="AZ30" s="3"/>
       <c r="BA30" s="1"/>
     </row>
-    <row r="31" spans="1:53">
+    <row r="31" spans="1:53" ht="75">
       <c r="A31" s="2">
         <v>28</v>
       </c>
@@ -4133,8 +4378,12 @@
       <c r="T31" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U31" s="3"/>
-      <c r="V31" s="3"/>
+      <c r="U31" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V31" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
       <c r="Y31" s="3"/>
@@ -4158,12 +4407,18 @@
       <c r="AI31" s="3">
         <v>3</v>
       </c>
-      <c r="AJ31" s="3"/>
+      <c r="AJ31" s="30"/>
       <c r="AK31" s="37"/>
-      <c r="AL31" s="3"/>
-      <c r="AM31" s="37"/>
-      <c r="AN31" s="37"/>
-      <c r="AO31" s="3"/>
+      <c r="AL31" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="AM31" s="24">
+        <v>46149</v>
+      </c>
+      <c r="AN31" s="40" t="s">
+        <v>115</v>
+      </c>
+      <c r="AO31" s="30"/>
       <c r="AP31" s="3"/>
       <c r="AQ31" s="3"/>
       <c r="AR31" s="3"/>
@@ -4236,8 +4491,12 @@
       <c r="T32" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U32" s="3"/>
-      <c r="V32" s="3"/>
+      <c r="U32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V32" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="W32" s="3"/>
       <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
@@ -4253,12 +4512,12 @@
       <c r="AI32" s="3">
         <v>2</v>
       </c>
-      <c r="AJ32" s="3"/>
+      <c r="AJ32" s="30"/>
       <c r="AK32" s="37"/>
       <c r="AL32" s="3"/>
       <c r="AM32" s="37"/>
       <c r="AN32" s="37"/>
-      <c r="AO32" s="3"/>
+      <c r="AO32" s="30"/>
       <c r="AP32" s="3"/>
       <c r="AQ32" s="3"/>
       <c r="AR32" s="3"/>
@@ -4331,8 +4590,12 @@
       <c r="T33" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U33" s="3"/>
-      <c r="V33" s="3"/>
+      <c r="U33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V33" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="W33" s="3"/>
       <c r="X33" s="3"/>
       <c r="Y33" s="3"/>
@@ -4356,12 +4619,12 @@
       <c r="AI33" s="3">
         <v>4</v>
       </c>
-      <c r="AJ33" s="3"/>
+      <c r="AJ33" s="30"/>
       <c r="AK33" s="37"/>
       <c r="AL33" s="3"/>
       <c r="AM33" s="37"/>
       <c r="AN33" s="37"/>
-      <c r="AO33" s="3"/>
+      <c r="AO33" s="30"/>
       <c r="AP33" s="3"/>
       <c r="AQ33" s="3"/>
       <c r="AR33" s="3"/>
@@ -4435,7 +4698,9 @@
         <v>17</v>
       </c>
       <c r="U34" s="3"/>
-      <c r="V34" s="3"/>
+      <c r="V34" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
@@ -4459,7 +4724,7 @@
       <c r="AI34" s="5">
         <v>5</v>
       </c>
-      <c r="AJ34" s="40">
+      <c r="AJ34" s="46">
         <v>46135</v>
       </c>
       <c r="AK34" s="34">
@@ -4472,7 +4737,7 @@
       <c r="AN34" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="AO34" s="3"/>
+      <c r="AO34" s="30"/>
       <c r="AP34" s="3"/>
       <c r="AQ34" s="3"/>
       <c r="AR34" s="24">
@@ -4548,7 +4813,9 @@
         <v>17</v>
       </c>
       <c r="U35" s="3"/>
-      <c r="V35" s="3"/>
+      <c r="V35" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="W35" s="3"/>
       <c r="X35" s="3"/>
       <c r="Y35" s="3"/>
@@ -4564,12 +4831,12 @@
       <c r="AI35" s="3">
         <v>2</v>
       </c>
-      <c r="AJ35" s="3"/>
+      <c r="AJ35" s="30"/>
       <c r="AK35" s="37"/>
       <c r="AL35" s="3"/>
       <c r="AM35" s="37"/>
       <c r="AN35" s="37"/>
-      <c r="AO35" s="3"/>
+      <c r="AO35" s="30"/>
       <c r="AP35" s="3"/>
       <c r="AQ35" s="3"/>
       <c r="AR35" s="3"/>
@@ -4642,8 +4909,12 @@
       <c r="T36" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="U36" s="3"/>
-      <c r="V36" s="3"/>
+      <c r="U36" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="V36" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="W36" s="3"/>
       <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
@@ -4657,12 +4928,12 @@
       <c r="AG36" s="3"/>
       <c r="AH36" s="3"/>
       <c r="AI36" s="3"/>
-      <c r="AJ36" s="3"/>
+      <c r="AJ36" s="30"/>
       <c r="AK36" s="37"/>
       <c r="AL36" s="3"/>
       <c r="AM36" s="37"/>
       <c r="AN36" s="37"/>
-      <c r="AO36" s="3"/>
+      <c r="AO36" s="30"/>
       <c r="AP36" s="3"/>
       <c r="AQ36" s="3"/>
       <c r="AR36" s="3"/>
@@ -4757,12 +5028,14 @@
       <c r="AG37" s="3"/>
       <c r="AH37" s="3"/>
       <c r="AI37" s="3"/>
-      <c r="AJ37" s="3"/>
+      <c r="AJ37" s="30"/>
       <c r="AK37" s="37"/>
-      <c r="AL37" s="3"/>
+      <c r="AL37" s="3">
+        <v>8</v>
+      </c>
       <c r="AM37" s="37"/>
       <c r="AN37" s="37"/>
-      <c r="AO37" s="3"/>
+      <c r="AO37" s="30"/>
       <c r="AP37" s="3"/>
       <c r="AQ37" s="3"/>
       <c r="AR37" s="3"/>
@@ -6788,33 +7061,6 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="AO11:AO13"/>
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="AN11:AN13"/>
-    <mergeCell ref="AE11:AE13"/>
-    <mergeCell ref="AF11:AF13"/>
-    <mergeCell ref="AG11:AG13"/>
-    <mergeCell ref="AH11:AH13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="Z11:Z13"/>
-    <mergeCell ref="AA11:AA13"/>
-    <mergeCell ref="AB11:AB13"/>
-    <mergeCell ref="AC11:AC13"/>
-    <mergeCell ref="AD11:AD13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="V11:V13"/>
-    <mergeCell ref="W11:W13"/>
-    <mergeCell ref="X11:X13"/>
-    <mergeCell ref="Y11:Y13"/>
-    <mergeCell ref="P11:P13"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="T11:T13"/>
     <mergeCell ref="A1:AP1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A11:A13"/>
@@ -6831,6 +7077,33 @@
     <mergeCell ref="M11:M13"/>
     <mergeCell ref="N11:N13"/>
     <mergeCell ref="O11:O13"/>
+    <mergeCell ref="P11:P13"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="T11:T13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="V11:V13"/>
+    <mergeCell ref="W11:W13"/>
+    <mergeCell ref="X11:X13"/>
+    <mergeCell ref="Y11:Y13"/>
+    <mergeCell ref="Z11:Z13"/>
+    <mergeCell ref="AA11:AA13"/>
+    <mergeCell ref="AB11:AB13"/>
+    <mergeCell ref="AC11:AC13"/>
+    <mergeCell ref="AD11:AD13"/>
+    <mergeCell ref="AE11:AE13"/>
+    <mergeCell ref="AF11:AF13"/>
+    <mergeCell ref="AG11:AG13"/>
+    <mergeCell ref="AH11:AH13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="AO11:AO13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
+    <mergeCell ref="AN11:AN13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ТКИ-341_Реверс_Инжиниринг.xlsx
+++ b/ТКИ-341_Реверс_Инжиниринг.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\Reverse_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09247BD0-6704-459F-998B-80211BAE764F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1060464-91D8-4791-BD5A-01C187804540}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="122">
   <si>
     <t>ВЕДОМОСТЬ ПОСЕЩАЕМОСТИ ЗАНЯТИЙ СТУДЕНТАМИ ГРУППЫ ТКИ "Компьютерная безопасность" ИТТСУ РУТ (МИИТ)</t>
   </si>
@@ -344,9 +344,6 @@
     <t>Разобраться с графовой БД</t>
   </si>
   <si>
-    <t>KodusAI</t>
-  </si>
-  <si>
     <t>Joern/CPG</t>
   </si>
   <si>
@@ -359,9 +356,6 @@
     <t>Новый инструментарий</t>
   </si>
   <si>
-    <t>VPN</t>
-  </si>
-  <si>
     <t>Боди Иштан</t>
   </si>
   <si>
@@ -423,6 +417,18 @@
   </si>
   <si>
     <t>9-Хоптий, Бойков</t>
+  </si>
+  <si>
+    <t>Gitinspector. SQL запросы от Макшакова</t>
+  </si>
+  <si>
+    <t>Kody-AI через VPN</t>
+  </si>
+  <si>
+    <t>Нахождение пути минимальной стоимости</t>
+  </si>
+  <si>
+    <t>Анализаторы CWE, включая Костенко</t>
   </si>
 </sst>
 </file>
@@ -532,7 +538,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -639,6 +645,16 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -649,13 +665,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -961,71 +970,72 @@
     <col min="41" max="41" width="9" style="32"/>
     <col min="44" max="44" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="9" style="32"/>
-    <col min="47" max="47" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:53" ht="14.45" customHeight="1">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="41"/>
-      <c r="U1" s="41"/>
-      <c r="V1" s="41"/>
-      <c r="W1" s="41"/>
-      <c r="X1" s="41"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="41"/>
-      <c r="AA1" s="41"/>
-      <c r="AB1" s="41"/>
-      <c r="AC1" s="41"/>
-      <c r="AD1" s="41"/>
-      <c r="AE1" s="41"/>
-      <c r="AF1" s="41"/>
-      <c r="AG1" s="41"/>
-      <c r="AH1" s="41"/>
-      <c r="AI1" s="41"/>
-      <c r="AJ1" s="41"/>
-      <c r="AK1" s="41"/>
-      <c r="AL1" s="41"/>
-      <c r="AM1" s="41"/>
-      <c r="AN1" s="41"/>
-      <c r="AO1" s="41"/>
-      <c r="AP1" s="41"/>
-      <c r="AQ1" s="41"/>
-      <c r="AR1" s="41"/>
-      <c r="AS1" s="41"/>
-      <c r="AT1" s="41"/>
-      <c r="AU1" s="41"/>
-      <c r="AV1" s="41"/>
-      <c r="AW1" s="41"/>
-      <c r="AX1" s="41"/>
-      <c r="AY1" s="41"/>
-      <c r="AZ1" s="41"/>
-      <c r="BA1" s="41"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="45"/>
+      <c r="Q1" s="45"/>
+      <c r="R1" s="45"/>
+      <c r="S1" s="45"/>
+      <c r="T1" s="45"/>
+      <c r="U1" s="45"/>
+      <c r="V1" s="45"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
+      <c r="AB1" s="45"/>
+      <c r="AC1" s="45"/>
+      <c r="AD1" s="45"/>
+      <c r="AE1" s="45"/>
+      <c r="AF1" s="45"/>
+      <c r="AG1" s="45"/>
+      <c r="AH1" s="45"/>
+      <c r="AI1" s="45"/>
+      <c r="AJ1" s="45"/>
+      <c r="AK1" s="45"/>
+      <c r="AL1" s="45"/>
+      <c r="AM1" s="45"/>
+      <c r="AN1" s="45"/>
+      <c r="AO1" s="45"/>
+      <c r="AP1" s="45"/>
+      <c r="AQ1" s="45"/>
+      <c r="AR1" s="45"/>
+      <c r="AS1" s="45"/>
+      <c r="AT1" s="45"/>
+      <c r="AU1" s="45"/>
+      <c r="AV1" s="45"/>
+      <c r="AW1" s="45"/>
+      <c r="AX1" s="45"/>
+      <c r="AY1" s="45"/>
+      <c r="AZ1" s="45"/>
+      <c r="BA1" s="45"/>
     </row>
     <row r="2" spans="1:53" ht="27.6" customHeight="1">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="43"/>
+      <c r="B2" s="47"/>
       <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1119,10 +1129,10 @@
         <v>8</v>
       </c>
       <c r="AK2" s="37" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AL2" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AM2" s="37"/>
       <c r="AN2" s="37"/>
@@ -1138,7 +1148,7 @@
       <c r="AU2" s="3"/>
       <c r="AV2" s="3"/>
       <c r="AW2" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AX2" s="3"/>
       <c r="AY2" s="3"/>
@@ -1303,7 +1313,7 @@
       </c>
       <c r="AM4" s="37"/>
       <c r="AN4" s="37"/>
-      <c r="AO4" s="45" t="s">
+      <c r="AO4" s="42" t="s">
         <v>72</v>
       </c>
       <c r="AP4" s="29" t="s">
@@ -1420,7 +1430,7 @@
       </c>
       <c r="AM5" s="37"/>
       <c r="AN5" s="37"/>
-      <c r="AO5" s="45" t="s">
+      <c r="AO5" s="42" t="s">
         <v>75</v>
       </c>
       <c r="AP5" s="28" t="s">
@@ -1533,15 +1543,15 @@
       <c r="AJ6" s="30"/>
       <c r="AK6" s="37"/>
       <c r="AL6" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AM6" s="24">
         <v>46149</v>
       </c>
       <c r="AN6" s="37" t="s">
-        <v>115</v>
-      </c>
-      <c r="AO6" s="45" t="s">
+        <v>113</v>
+      </c>
+      <c r="AO6" s="42" t="s">
         <v>72</v>
       </c>
       <c r="AP6" s="29" t="s">
@@ -1651,22 +1661,22 @@
       <c r="AI7" s="3">
         <v>5</v>
       </c>
-      <c r="AJ7" s="46">
+      <c r="AJ7" s="43">
         <v>46135</v>
       </c>
       <c r="AK7" s="34">
         <v>12</v>
       </c>
       <c r="AL7" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AM7" s="24">
         <v>46135</v>
       </c>
       <c r="AN7" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="AO7" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="AO7" s="42" t="s">
         <v>75</v>
       </c>
       <c r="AP7" s="29" t="s">
@@ -1680,13 +1690,15 @@
         <v>92</v>
       </c>
       <c r="AT7" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AU7" s="24">
         <v>46149</v>
       </c>
       <c r="AV7" s="3"/>
-      <c r="AW7" s="3"/>
+      <c r="AW7" s="24">
+        <v>46149</v>
+      </c>
       <c r="AX7" s="3"/>
       <c r="AY7" s="3"/>
       <c r="AZ7" s="3"/>
@@ -1778,7 +1790,7 @@
       </c>
       <c r="AJ8" s="30"/>
       <c r="AK8" s="37" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AL8" s="3">
         <v>17</v>
@@ -1786,7 +1798,7 @@
       <c r="AM8" s="24">
         <v>46135</v>
       </c>
-      <c r="AO8" s="45" t="s">
+      <c r="AO8" s="42" t="s">
         <v>72</v>
       </c>
       <c r="AP8" s="29" t="s">
@@ -1901,9 +1913,9 @@
         <v>46149</v>
       </c>
       <c r="AN9" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="AO9" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="AO9" s="42" t="s">
         <v>75</v>
       </c>
       <c r="AP9" s="29" t="s">
@@ -2014,13 +2026,15 @@
       <c r="AJ10" s="30"/>
       <c r="AK10" s="37"/>
       <c r="AL10" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AM10" s="24">
         <v>46149</v>
       </c>
-      <c r="AN10" s="37"/>
-      <c r="AO10" s="45" t="s">
+      <c r="AN10" s="37" t="s">
+        <v>120</v>
+      </c>
+      <c r="AO10" s="42" t="s">
         <v>72</v>
       </c>
       <c r="AP10" s="29" t="s">
@@ -2130,10 +2144,10 @@
       </c>
       <c r="AJ11" s="31"/>
       <c r="AK11" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AL11" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM11" s="24">
         <v>46149</v>
@@ -2141,7 +2155,7 @@
       <c r="AN11" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="AO11" s="45" t="s">
+      <c r="AO11" s="42" t="s">
         <v>72</v>
       </c>
       <c r="AP11" s="29" t="s">
@@ -2153,11 +2167,15 @@
       </c>
       <c r="AS11" s="31"/>
       <c r="AT11" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="AU11" s="34"/>
+        <v>94</v>
+      </c>
+      <c r="AU11" s="24">
+        <v>46149</v>
+      </c>
       <c r="AV11" s="5"/>
-      <c r="AW11" s="5"/>
+      <c r="AW11" s="24">
+        <v>46149</v>
+      </c>
       <c r="AX11" s="5"/>
       <c r="AY11" s="5"/>
       <c r="AZ11" s="5"/>
@@ -2260,7 +2278,7 @@
       </c>
       <c r="AM12" s="5"/>
       <c r="AN12" s="5"/>
-      <c r="AO12" s="45" t="s">
+      <c r="AO12" s="42" t="s">
         <v>72</v>
       </c>
       <c r="AP12" s="29" t="s">
@@ -2372,7 +2390,7 @@
       <c r="AI13" s="5">
         <v>5</v>
       </c>
-      <c r="AJ13" s="46">
+      <c r="AJ13" s="43">
         <v>46135</v>
       </c>
       <c r="AK13" s="34">
@@ -2380,9 +2398,9 @@
       </c>
       <c r="AM13" s="5"/>
       <c r="AN13" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="AO13" s="45" t="s">
+        <v>102</v>
+      </c>
+      <c r="AO13" s="42" t="s">
         <v>72</v>
       </c>
       <c r="AP13" s="29" t="s">
@@ -2489,7 +2507,7 @@
       </c>
       <c r="AM14" s="37"/>
       <c r="AN14" s="37"/>
-      <c r="AO14" s="45" t="s">
+      <c r="AO14" s="42" t="s">
         <v>72</v>
       </c>
       <c r="AP14" s="29" t="s">
@@ -2509,7 +2527,7 @@
       <c r="AZ14" s="3"/>
       <c r="BA14" s="1"/>
     </row>
-    <row r="15" spans="1:53" ht="75">
+    <row r="15" spans="1:53" ht="90">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -2602,7 +2620,7 @@
       <c r="AJ15" s="30"/>
       <c r="AK15" s="37"/>
       <c r="AL15" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM15" s="24">
         <v>46149</v>
@@ -2617,8 +2635,12 @@
         <v>46128</v>
       </c>
       <c r="AS15" s="30"/>
-      <c r="AT15" s="3"/>
-      <c r="AU15" s="3"/>
+      <c r="AT15" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AU15" s="24">
+        <v>46149</v>
+      </c>
       <c r="AV15" s="3"/>
       <c r="AW15" s="3"/>
       <c r="AX15" s="3"/>
@@ -2714,18 +2736,18 @@
       <c r="AI16" s="3">
         <v>5</v>
       </c>
-      <c r="AJ16" s="46">
-        <v>46135</v>
-      </c>
+      <c r="AJ16" s="43"/>
       <c r="AK16" s="37"/>
       <c r="AL16" s="38">
         <v>7</v>
       </c>
-      <c r="AM16" s="37"/>
+      <c r="AM16" s="24">
+        <v>46135</v>
+      </c>
       <c r="AN16" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="AO16" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="AO16" s="42" t="s">
         <v>72</v>
       </c>
       <c r="AP16" s="29" t="s">
@@ -2738,12 +2760,16 @@
       <c r="AS16" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="AT16" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="AU16" s="33"/>
-      <c r="AV16" s="3"/>
-      <c r="AW16" s="3"/>
+      <c r="AT16" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="AU16" s="24">
+        <v>46149</v>
+      </c>
+      <c r="AV16" s="41"/>
+      <c r="AW16" s="24">
+        <v>46149</v>
+      </c>
       <c r="AX16" s="3"/>
       <c r="AY16" s="3"/>
       <c r="AZ16" s="3"/>
@@ -2843,16 +2869,16 @@
       <c r="AK17" s="37">
         <v>13</v>
       </c>
-      <c r="AL17" s="47">
+      <c r="AL17" s="44">
         <v>1</v>
       </c>
       <c r="AM17" s="24">
         <v>46135</v>
       </c>
       <c r="AN17" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="AO17" s="45" t="s">
+        <v>102</v>
+      </c>
+      <c r="AO17" s="42" t="s">
         <v>72</v>
       </c>
       <c r="AP17" s="29" t="s">
@@ -2964,7 +2990,7 @@
       <c r="AI18" s="3">
         <v>5</v>
       </c>
-      <c r="AJ18" s="46"/>
+      <c r="AJ18" s="43"/>
       <c r="AK18" s="34">
         <v>12</v>
       </c>
@@ -2973,7 +2999,7 @@
         <v>46135</v>
       </c>
       <c r="AN18" s="40" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="AO18" s="30"/>
       <c r="AP18" s="3"/>
@@ -2987,7 +3013,9 @@
         <v>46149</v>
       </c>
       <c r="AV18" s="3"/>
-      <c r="AW18" s="3"/>
+      <c r="AW18" s="24">
+        <v>46149</v>
+      </c>
       <c r="AX18" s="3"/>
       <c r="AY18" s="3"/>
       <c r="AZ18" s="3"/>
@@ -3086,7 +3114,7 @@
         <v>46149</v>
       </c>
       <c r="AN19" s="40" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AO19" s="30"/>
       <c r="AP19" s="3"/>
@@ -3188,7 +3216,7 @@
       </c>
       <c r="AJ20" s="30"/>
       <c r="AK20" s="37" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AL20" s="3">
         <v>6</v>
@@ -3302,7 +3330,7 @@
         <v>46135</v>
       </c>
       <c r="AN21" s="37" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="AO21" s="30"/>
       <c r="AP21" s="3"/>
@@ -3318,7 +3346,7 @@
       <c r="AZ21" s="3"/>
       <c r="BA21" s="1"/>
     </row>
-    <row r="22" spans="1:53" ht="60">
+    <row r="22" spans="1:53" ht="90">
       <c r="A22" s="2">
         <v>19</v>
       </c>
@@ -3409,15 +3437,15 @@
       <c r="AJ22" s="30"/>
       <c r="AK22" s="37"/>
       <c r="AL22" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="AM22" s="24">
         <v>46135</v>
       </c>
       <c r="AN22" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="AO22" s="45" t="s">
+        <v>115</v>
+      </c>
+      <c r="AO22" s="42" t="s">
         <v>75</v>
       </c>
       <c r="AP22" s="29" t="s">
@@ -3428,8 +3456,12 @@
         <v>46128</v>
       </c>
       <c r="AS22" s="30"/>
-      <c r="AT22" s="3"/>
-      <c r="AU22" s="3"/>
+      <c r="AT22" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="AU22" s="24">
+        <v>46149</v>
+      </c>
       <c r="AV22" s="3"/>
       <c r="AW22" s="3"/>
       <c r="AX22" s="3"/>
@@ -3437,7 +3469,7 @@
       <c r="AZ22" s="3"/>
       <c r="BA22" s="1"/>
     </row>
-    <row r="23" spans="1:53" ht="60">
+    <row r="23" spans="1:53" ht="90">
       <c r="A23" s="2">
         <v>20</v>
       </c>
@@ -3530,13 +3562,13 @@
       <c r="AJ23" s="30"/>
       <c r="AK23" s="37"/>
       <c r="AL23" s="40" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="AM23" s="24">
         <v>46135</v>
       </c>
       <c r="AN23" s="37" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AO23" s="30"/>
       <c r="AP23" s="3"/>
@@ -3545,8 +3577,12 @@
         <v>46128</v>
       </c>
       <c r="AS23" s="30"/>
-      <c r="AT23" s="3"/>
-      <c r="AU23" s="3"/>
+      <c r="AT23" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="AU23" s="24">
+        <v>46149</v>
+      </c>
       <c r="AV23" s="3"/>
       <c r="AW23" s="3"/>
       <c r="AX23" s="3"/>
@@ -4180,7 +4216,7 @@
         <v>46135</v>
       </c>
       <c r="AN29" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AO29" s="30"/>
       <c r="AP29" s="3"/>
@@ -4288,16 +4324,16 @@
       <c r="AI30" s="3">
         <v>5</v>
       </c>
-      <c r="AJ30" s="46">
-        <v>46135</v>
-      </c>
+      <c r="AJ30" s="43"/>
       <c r="AK30" s="37">
         <v>7</v>
       </c>
       <c r="AL30" s="38"/>
-      <c r="AM30" s="37"/>
+      <c r="AM30" s="24">
+        <v>46135</v>
+      </c>
       <c r="AN30" s="37" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AO30" s="30"/>
       <c r="AP30" s="3"/>
@@ -4306,12 +4342,16 @@
         <v>46135</v>
       </c>
       <c r="AS30" s="30"/>
-      <c r="AT30" s="3"/>
-      <c r="AU30" s="33" t="s">
-        <v>98</v>
+      <c r="AT30" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="AU30" s="24">
+        <v>46149</v>
       </c>
       <c r="AV30" s="3"/>
-      <c r="AW30" s="3"/>
+      <c r="AW30" s="24">
+        <v>46149</v>
+      </c>
       <c r="AX30" s="3"/>
       <c r="AY30" s="3"/>
       <c r="AZ30" s="3"/>
@@ -4410,13 +4450,13 @@
       <c r="AJ31" s="30"/>
       <c r="AK31" s="37"/>
       <c r="AL31" s="40" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AM31" s="24">
         <v>46149</v>
       </c>
       <c r="AN31" s="40" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AO31" s="30"/>
       <c r="AP31" s="3"/>
@@ -4531,7 +4571,7 @@
       <c r="AZ32" s="3"/>
       <c r="BA32" s="1"/>
     </row>
-    <row r="33" spans="1:53">
+    <row r="33" spans="1:53" ht="105">
       <c r="A33" s="2">
         <v>30</v>
       </c>
@@ -4621,9 +4661,15 @@
       </c>
       <c r="AJ33" s="30"/>
       <c r="AK33" s="37"/>
-      <c r="AL33" s="3"/>
-      <c r="AM33" s="37"/>
-      <c r="AN33" s="37"/>
+      <c r="AL33" s="41" t="s">
+        <v>110</v>
+      </c>
+      <c r="AM33" s="24">
+        <v>46149</v>
+      </c>
+      <c r="AN33" s="41" t="s">
+        <v>120</v>
+      </c>
       <c r="AO33" s="30"/>
       <c r="AP33" s="3"/>
       <c r="AQ33" s="3"/>
@@ -4724,18 +4770,18 @@
       <c r="AI34" s="5">
         <v>5</v>
       </c>
-      <c r="AJ34" s="46">
+      <c r="AJ34" s="43">
         <v>46135</v>
       </c>
       <c r="AK34" s="34">
         <v>11</v>
       </c>
       <c r="AL34" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AM34" s="5"/>
       <c r="AN34" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AO34" s="30"/>
       <c r="AP34" s="3"/>
@@ -4855,7 +4901,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C36" s="9">
         <v>17</v>
@@ -5192,24 +5238,24 @@
     </row>
     <row r="41" spans="1:53">
       <c r="W41" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="X41" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="X41" s="35" t="s">
-        <v>97</v>
-      </c>
       <c r="Y41" s="38" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Z41" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="42" spans="1:53" ht="9.75" customHeight="1">
       <c r="W42" s="38" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="Z42" s="38" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57" spans="31:33">
@@ -5292,56 +5338,56 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="41"/>
-      <c r="U1" s="41"/>
-      <c r="V1" s="41"/>
-      <c r="W1" s="41"/>
-      <c r="X1" s="41"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="41"/>
-      <c r="AA1" s="41"/>
-      <c r="AB1" s="41"/>
-      <c r="AC1" s="41"/>
-      <c r="AD1" s="41"/>
-      <c r="AE1" s="41"/>
-      <c r="AF1" s="41"/>
-      <c r="AG1" s="41"/>
-      <c r="AH1" s="41"/>
-      <c r="AI1" s="41"/>
-      <c r="AJ1" s="41"/>
-      <c r="AK1" s="41"/>
-      <c r="AL1" s="41"/>
-      <c r="AM1" s="41"/>
-      <c r="AN1" s="41"/>
-      <c r="AO1" s="41"/>
-      <c r="AP1" s="41"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="45"/>
+      <c r="Q1" s="45"/>
+      <c r="R1" s="45"/>
+      <c r="S1" s="45"/>
+      <c r="T1" s="45"/>
+      <c r="U1" s="45"/>
+      <c r="V1" s="45"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
+      <c r="AB1" s="45"/>
+      <c r="AC1" s="45"/>
+      <c r="AD1" s="45"/>
+      <c r="AE1" s="45"/>
+      <c r="AF1" s="45"/>
+      <c r="AG1" s="45"/>
+      <c r="AH1" s="45"/>
+      <c r="AI1" s="45"/>
+      <c r="AJ1" s="45"/>
+      <c r="AK1" s="45"/>
+      <c r="AL1" s="45"/>
+      <c r="AM1" s="45"/>
+      <c r="AN1" s="45"/>
+      <c r="AO1" s="45"/>
+      <c r="AP1" s="45"/>
     </row>
     <row r="2" spans="1:42" ht="30">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="43"/>
+      <c r="B2" s="47"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -5770,142 +5816,142 @@
       <c r="AP10" s="1"/>
     </row>
     <row r="11" spans="1:42">
-      <c r="A11" s="43">
+      <c r="A11" s="47">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="43"/>
-      <c r="I11" s="43"/>
-      <c r="J11" s="43"/>
-      <c r="K11" s="43"/>
-      <c r="L11" s="44"/>
-      <c r="M11" s="44"/>
-      <c r="N11" s="44"/>
-      <c r="O11" s="44"/>
-      <c r="P11" s="44"/>
-      <c r="Q11" s="44"/>
-      <c r="R11" s="44"/>
-      <c r="S11" s="44"/>
-      <c r="T11" s="44"/>
-      <c r="U11" s="44"/>
-      <c r="V11" s="44"/>
-      <c r="W11" s="44"/>
-      <c r="X11" s="44"/>
-      <c r="Y11" s="44"/>
-      <c r="Z11" s="44"/>
-      <c r="AA11" s="44"/>
-      <c r="AB11" s="44"/>
-      <c r="AC11" s="44"/>
-      <c r="AD11" s="44"/>
-      <c r="AE11" s="44"/>
-      <c r="AF11" s="44"/>
-      <c r="AG11" s="44"/>
-      <c r="AH11" s="44"/>
-      <c r="AI11" s="44"/>
-      <c r="AJ11" s="44"/>
-      <c r="AK11" s="44"/>
-      <c r="AL11" s="44"/>
-      <c r="AM11" s="44"/>
-      <c r="AN11" s="44"/>
-      <c r="AO11" s="44"/>
-      <c r="AP11" s="41"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="47"/>
+      <c r="I11" s="47"/>
+      <c r="J11" s="47"/>
+      <c r="K11" s="47"/>
+      <c r="L11" s="48"/>
+      <c r="M11" s="48"/>
+      <c r="N11" s="48"/>
+      <c r="O11" s="48"/>
+      <c r="P11" s="48"/>
+      <c r="Q11" s="48"/>
+      <c r="R11" s="48"/>
+      <c r="S11" s="48"/>
+      <c r="T11" s="48"/>
+      <c r="U11" s="48"/>
+      <c r="V11" s="48"/>
+      <c r="W11" s="48"/>
+      <c r="X11" s="48"/>
+      <c r="Y11" s="48"/>
+      <c r="Z11" s="48"/>
+      <c r="AA11" s="48"/>
+      <c r="AB11" s="48"/>
+      <c r="AC11" s="48"/>
+      <c r="AD11" s="48"/>
+      <c r="AE11" s="48"/>
+      <c r="AF11" s="48"/>
+      <c r="AG11" s="48"/>
+      <c r="AH11" s="48"/>
+      <c r="AI11" s="48"/>
+      <c r="AJ11" s="48"/>
+      <c r="AK11" s="48"/>
+      <c r="AL11" s="48"/>
+      <c r="AM11" s="48"/>
+      <c r="AN11" s="48"/>
+      <c r="AO11" s="48"/>
+      <c r="AP11" s="45"/>
     </row>
     <row r="12" spans="1:42">
-      <c r="A12" s="43"/>
+      <c r="A12" s="47"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="43"/>
-      <c r="K12" s="43"/>
-      <c r="L12" s="44"/>
-      <c r="M12" s="44"/>
-      <c r="N12" s="44"/>
-      <c r="O12" s="44"/>
-      <c r="P12" s="44"/>
-      <c r="Q12" s="44"/>
-      <c r="R12" s="44"/>
-      <c r="S12" s="44"/>
-      <c r="T12" s="44"/>
-      <c r="U12" s="44"/>
-      <c r="V12" s="44"/>
-      <c r="W12" s="44"/>
-      <c r="X12" s="44"/>
-      <c r="Y12" s="44"/>
-      <c r="Z12" s="44"/>
-      <c r="AA12" s="44"/>
-      <c r="AB12" s="44"/>
-      <c r="AC12" s="44"/>
-      <c r="AD12" s="44"/>
-      <c r="AE12" s="44"/>
-      <c r="AF12" s="44"/>
-      <c r="AG12" s="44"/>
-      <c r="AH12" s="44"/>
-      <c r="AI12" s="44"/>
-      <c r="AJ12" s="44"/>
-      <c r="AK12" s="44"/>
-      <c r="AL12" s="44"/>
-      <c r="AM12" s="44"/>
-      <c r="AN12" s="44"/>
-      <c r="AO12" s="44"/>
-      <c r="AP12" s="41"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="47"/>
+      <c r="J12" s="47"/>
+      <c r="K12" s="47"/>
+      <c r="L12" s="48"/>
+      <c r="M12" s="48"/>
+      <c r="N12" s="48"/>
+      <c r="O12" s="48"/>
+      <c r="P12" s="48"/>
+      <c r="Q12" s="48"/>
+      <c r="R12" s="48"/>
+      <c r="S12" s="48"/>
+      <c r="T12" s="48"/>
+      <c r="U12" s="48"/>
+      <c r="V12" s="48"/>
+      <c r="W12" s="48"/>
+      <c r="X12" s="48"/>
+      <c r="Y12" s="48"/>
+      <c r="Z12" s="48"/>
+      <c r="AA12" s="48"/>
+      <c r="AB12" s="48"/>
+      <c r="AC12" s="48"/>
+      <c r="AD12" s="48"/>
+      <c r="AE12" s="48"/>
+      <c r="AF12" s="48"/>
+      <c r="AG12" s="48"/>
+      <c r="AH12" s="48"/>
+      <c r="AI12" s="48"/>
+      <c r="AJ12" s="48"/>
+      <c r="AK12" s="48"/>
+      <c r="AL12" s="48"/>
+      <c r="AM12" s="48"/>
+      <c r="AN12" s="48"/>
+      <c r="AO12" s="48"/>
+      <c r="AP12" s="45"/>
     </row>
     <row r="13" spans="1:42">
-      <c r="A13" s="43"/>
+      <c r="A13" s="47"/>
       <c r="B13" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="43"/>
-      <c r="K13" s="43"/>
-      <c r="L13" s="44"/>
-      <c r="M13" s="44"/>
-      <c r="N13" s="44"/>
-      <c r="O13" s="44"/>
-      <c r="P13" s="44"/>
-      <c r="Q13" s="44"/>
-      <c r="R13" s="44"/>
-      <c r="S13" s="44"/>
-      <c r="T13" s="44"/>
-      <c r="U13" s="44"/>
-      <c r="V13" s="44"/>
-      <c r="W13" s="44"/>
-      <c r="X13" s="44"/>
-      <c r="Y13" s="44"/>
-      <c r="Z13" s="44"/>
-      <c r="AA13" s="44"/>
-      <c r="AB13" s="44"/>
-      <c r="AC13" s="44"/>
-      <c r="AD13" s="44"/>
-      <c r="AE13" s="44"/>
-      <c r="AF13" s="44"/>
-      <c r="AG13" s="44"/>
-      <c r="AH13" s="44"/>
-      <c r="AI13" s="44"/>
-      <c r="AJ13" s="44"/>
-      <c r="AK13" s="44"/>
-      <c r="AL13" s="44"/>
-      <c r="AM13" s="44"/>
-      <c r="AN13" s="44"/>
-      <c r="AO13" s="44"/>
-      <c r="AP13" s="41"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="47"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="47"/>
+      <c r="K13" s="47"/>
+      <c r="L13" s="48"/>
+      <c r="M13" s="48"/>
+      <c r="N13" s="48"/>
+      <c r="O13" s="48"/>
+      <c r="P13" s="48"/>
+      <c r="Q13" s="48"/>
+      <c r="R13" s="48"/>
+      <c r="S13" s="48"/>
+      <c r="T13" s="48"/>
+      <c r="U13" s="48"/>
+      <c r="V13" s="48"/>
+      <c r="W13" s="48"/>
+      <c r="X13" s="48"/>
+      <c r="Y13" s="48"/>
+      <c r="Z13" s="48"/>
+      <c r="AA13" s="48"/>
+      <c r="AB13" s="48"/>
+      <c r="AC13" s="48"/>
+      <c r="AD13" s="48"/>
+      <c r="AE13" s="48"/>
+      <c r="AF13" s="48"/>
+      <c r="AG13" s="48"/>
+      <c r="AH13" s="48"/>
+      <c r="AI13" s="48"/>
+      <c r="AJ13" s="48"/>
+      <c r="AK13" s="48"/>
+      <c r="AL13" s="48"/>
+      <c r="AM13" s="48"/>
+      <c r="AN13" s="48"/>
+      <c r="AO13" s="48"/>
+      <c r="AP13" s="45"/>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" s="2">
@@ -7061,6 +7107,33 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="AO11:AO13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
+    <mergeCell ref="AN11:AN13"/>
+    <mergeCell ref="AE11:AE13"/>
+    <mergeCell ref="AF11:AF13"/>
+    <mergeCell ref="AG11:AG13"/>
+    <mergeCell ref="AH11:AH13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="Z11:Z13"/>
+    <mergeCell ref="AA11:AA13"/>
+    <mergeCell ref="AB11:AB13"/>
+    <mergeCell ref="AC11:AC13"/>
+    <mergeCell ref="AD11:AD13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="V11:V13"/>
+    <mergeCell ref="W11:W13"/>
+    <mergeCell ref="X11:X13"/>
+    <mergeCell ref="Y11:Y13"/>
+    <mergeCell ref="P11:P13"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="T11:T13"/>
     <mergeCell ref="A1:AP1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A11:A13"/>
@@ -7077,33 +7150,6 @@
     <mergeCell ref="M11:M13"/>
     <mergeCell ref="N11:N13"/>
     <mergeCell ref="O11:O13"/>
-    <mergeCell ref="P11:P13"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="T11:T13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="V11:V13"/>
-    <mergeCell ref="W11:W13"/>
-    <mergeCell ref="X11:X13"/>
-    <mergeCell ref="Y11:Y13"/>
-    <mergeCell ref="Z11:Z13"/>
-    <mergeCell ref="AA11:AA13"/>
-    <mergeCell ref="AB11:AB13"/>
-    <mergeCell ref="AC11:AC13"/>
-    <mergeCell ref="AD11:AD13"/>
-    <mergeCell ref="AE11:AE13"/>
-    <mergeCell ref="AF11:AF13"/>
-    <mergeCell ref="AG11:AG13"/>
-    <mergeCell ref="AH11:AH13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="AO11:AO13"/>
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="AN11:AN13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ТКИ-341_Реверс_Инжиниринг.xlsx
+++ b/ТКИ-341_Реверс_Инжиниринг.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\Reverse_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1060464-91D8-4791-BD5A-01C187804540}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8E77AF-25C5-41A5-9E6E-B549EDB0E728}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="127">
   <si>
     <t>ВЕДОМОСТЬ ПОСЕЩАЕМОСТИ ЗАНЯТИЙ СТУДЕНТАМИ ГРУППЫ ТКИ "Компьютерная безопасность" ИТТСУ РУТ (МИИТ)</t>
   </si>
@@ -430,6 +430,21 @@
   <si>
     <t>Анализаторы CWE, включая Костенко</t>
   </si>
+  <si>
+    <t>угадай число, генератор случайных чисел</t>
+  </si>
+  <si>
+    <t>_1_2</t>
+  </si>
+  <si>
+    <t>Githru</t>
+  </si>
+  <si>
+    <t>ast</t>
+  </si>
+  <si>
+    <t>13 сумма элементов массива с нечетными значениями, Винтфельд Рина Дмитриевна, Черемных</t>
+  </si>
 </sst>
 </file>
 
@@ -439,12 +454,20 @@
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -459,6 +482,21 @@
       <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="9">
@@ -538,134 +576,146 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -975,67 +1025,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:53" ht="14.45" customHeight="1">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
-      <c r="T1" s="45"/>
-      <c r="U1" s="45"/>
-      <c r="V1" s="45"/>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="45"/>
-      <c r="AB1" s="45"/>
-      <c r="AC1" s="45"/>
-      <c r="AD1" s="45"/>
-      <c r="AE1" s="45"/>
-      <c r="AF1" s="45"/>
-      <c r="AG1" s="45"/>
-      <c r="AH1" s="45"/>
-      <c r="AI1" s="45"/>
-      <c r="AJ1" s="45"/>
-      <c r="AK1" s="45"/>
-      <c r="AL1" s="45"/>
-      <c r="AM1" s="45"/>
-      <c r="AN1" s="45"/>
-      <c r="AO1" s="45"/>
-      <c r="AP1" s="45"/>
-      <c r="AQ1" s="45"/>
-      <c r="AR1" s="45"/>
-      <c r="AS1" s="45"/>
-      <c r="AT1" s="45"/>
-      <c r="AU1" s="45"/>
-      <c r="AV1" s="45"/>
-      <c r="AW1" s="45"/>
-      <c r="AX1" s="45"/>
-      <c r="AY1" s="45"/>
-      <c r="AZ1" s="45"/>
-      <c r="BA1" s="45"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
+      <c r="S1" s="46"/>
+      <c r="T1" s="46"/>
+      <c r="U1" s="46"/>
+      <c r="V1" s="46"/>
+      <c r="W1" s="46"/>
+      <c r="X1" s="46"/>
+      <c r="Y1" s="46"/>
+      <c r="Z1" s="46"/>
+      <c r="AA1" s="46"/>
+      <c r="AB1" s="46"/>
+      <c r="AC1" s="46"/>
+      <c r="AD1" s="46"/>
+      <c r="AE1" s="46"/>
+      <c r="AF1" s="46"/>
+      <c r="AG1" s="46"/>
+      <c r="AH1" s="46"/>
+      <c r="AI1" s="46"/>
+      <c r="AJ1" s="46"/>
+      <c r="AK1" s="46"/>
+      <c r="AL1" s="46"/>
+      <c r="AM1" s="46"/>
+      <c r="AN1" s="46"/>
+      <c r="AO1" s="46"/>
+      <c r="AP1" s="46"/>
+      <c r="AQ1" s="46"/>
+      <c r="AR1" s="46"/>
+      <c r="AS1" s="46"/>
+      <c r="AT1" s="46"/>
+      <c r="AU1" s="46"/>
+      <c r="AV1" s="46"/>
+      <c r="AW1" s="46"/>
+      <c r="AX1" s="46"/>
+      <c r="AY1" s="46"/>
+      <c r="AZ1" s="46"/>
+      <c r="BA1" s="46"/>
     </row>
     <row r="2" spans="1:53" ht="27.6" customHeight="1">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="47"/>
+      <c r="B2" s="48"/>
       <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1283,7 +1333,9 @@
       <c r="V4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W4" s="3"/>
+      <c r="W4" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
@@ -1400,7 +1452,9 @@
       <c r="V5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="W5" s="3"/>
+      <c r="W5" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
@@ -1517,7 +1571,9 @@
       <c r="V6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W6" s="3"/>
+      <c r="W6" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
@@ -1549,7 +1605,7 @@
         <v>46149</v>
       </c>
       <c r="AN6" s="37" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="AO6" s="42" t="s">
         <v>72</v>
@@ -1638,7 +1694,9 @@
       <c r="V7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W7" s="3"/>
+      <c r="W7" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
@@ -1769,7 +1827,9 @@
       <c r="V8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="W8" s="3"/>
+      <c r="W8" s="3" t="s">
+        <v>123</v>
+      </c>
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
@@ -1885,7 +1945,9 @@
       <c r="V9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W9" s="3"/>
+      <c r="W9" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
@@ -2000,7 +2062,9 @@
       <c r="V10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W10" s="3"/>
+      <c r="W10" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
@@ -2119,7 +2183,9 @@
       <c r="V11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="W11" s="5"/>
+      <c r="W11" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="X11" s="5"/>
       <c r="Y11" s="5"/>
       <c r="Z11" s="5"/>
@@ -2248,7 +2314,9 @@
       <c r="V12" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="W12" s="5"/>
+      <c r="W12" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="X12" s="5"/>
       <c r="Y12" s="5"/>
       <c r="Z12" s="5"/>
@@ -2304,7 +2372,7 @@
       <c r="A13" s="2">
         <v>10</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="54" t="s">
         <v>33</v>
       </c>
       <c r="C13" s="9">
@@ -2367,7 +2435,9 @@
       <c r="V13" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="W13" s="5"/>
+      <c r="W13" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="X13" s="5"/>
       <c r="Y13" s="5"/>
       <c r="Z13" s="5"/>
@@ -2396,8 +2466,13 @@
       <c r="AK13" s="34">
         <v>11</v>
       </c>
-      <c r="AM13" s="5"/>
-      <c r="AN13" s="5" t="s">
+      <c r="AL13" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="AM13" s="24">
+        <v>46149</v>
+      </c>
+      <c r="AN13" s="52" t="s">
         <v>102</v>
       </c>
       <c r="AO13" s="42" t="s">
@@ -2411,10 +2486,16 @@
         <v>46128</v>
       </c>
       <c r="AS13" s="31"/>
-      <c r="AT13" s="5"/>
-      <c r="AU13" s="5"/>
+      <c r="AT13" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="AU13" s="24">
+        <v>46156</v>
+      </c>
       <c r="AV13" s="5"/>
-      <c r="AW13" s="5"/>
+      <c r="AW13" s="24">
+        <v>46156</v>
+      </c>
       <c r="AX13" s="5"/>
       <c r="AY13" s="5"/>
       <c r="AZ13" s="5"/>
@@ -2485,7 +2566,9 @@
       <c r="V14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W14" s="3"/>
+      <c r="W14" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
@@ -2594,7 +2677,9 @@
       <c r="V15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W15" s="3"/>
+      <c r="W15" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
@@ -2713,7 +2798,9 @@
       <c r="V16" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W16" s="3"/>
+      <c r="W16" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
@@ -2775,7 +2862,7 @@
       <c r="AZ16" s="3"/>
       <c r="BA16" s="1"/>
     </row>
-    <row r="17" spans="1:53" ht="135">
+    <row r="17" spans="1:53" ht="240">
       <c r="A17" s="2">
         <v>14</v>
       </c>
@@ -2842,7 +2929,9 @@
       <c r="V17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W17" s="3"/>
+      <c r="W17" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
@@ -2866,8 +2955,8 @@
         <v>5</v>
       </c>
       <c r="AJ17" s="30"/>
-      <c r="AK17" s="37">
-        <v>13</v>
+      <c r="AK17" s="53" t="s">
+        <v>126</v>
       </c>
       <c r="AL17" s="44">
         <v>1</v>
@@ -2875,7 +2964,7 @@
       <c r="AM17" s="24">
         <v>46135</v>
       </c>
-      <c r="AN17" s="5" t="s">
+      <c r="AN17" s="52" t="s">
         <v>102</v>
       </c>
       <c r="AO17" s="42" t="s">
@@ -2891,10 +2980,16 @@
         <v>46135</v>
       </c>
       <c r="AS17" s="30"/>
-      <c r="AT17" s="3"/>
-      <c r="AU17" s="3"/>
+      <c r="AT17" s="51" t="s">
+        <v>125</v>
+      </c>
+      <c r="AU17" s="24">
+        <v>46149</v>
+      </c>
       <c r="AV17" s="3"/>
-      <c r="AW17" s="3"/>
+      <c r="AW17" s="24">
+        <v>46149</v>
+      </c>
       <c r="AX17" s="3"/>
       <c r="AY17" s="3"/>
       <c r="AZ17" s="3"/>
@@ -2967,7 +3062,9 @@
       <c r="V18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W18" s="3"/>
+      <c r="W18" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
@@ -3086,7 +3183,9 @@
       <c r="V19" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W19" s="3"/>
+      <c r="W19" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
@@ -3197,7 +3296,9 @@
       <c r="V20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="W20" s="3"/>
+      <c r="W20" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
@@ -3304,7 +3405,9 @@
       <c r="V21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W21" s="3"/>
+      <c r="W21" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="X21" s="3"/>
       <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
@@ -3411,7 +3514,9 @@
       <c r="V22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W22" s="3"/>
+      <c r="W22" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
@@ -3463,7 +3568,9 @@
         <v>46149</v>
       </c>
       <c r="AV22" s="3"/>
-      <c r="AW22" s="3"/>
+      <c r="AW22" s="24">
+        <v>46156</v>
+      </c>
       <c r="AX22" s="3"/>
       <c r="AY22" s="3"/>
       <c r="AZ22" s="3"/>
@@ -3536,7 +3643,9 @@
       <c r="V23" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W23" s="3"/>
+      <c r="W23" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="X23" s="3"/>
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
@@ -3584,7 +3693,9 @@
         <v>46149</v>
       </c>
       <c r="AV23" s="3"/>
-      <c r="AW23" s="3"/>
+      <c r="AW23" s="24">
+        <v>46156</v>
+      </c>
       <c r="AX23" s="3"/>
       <c r="AY23" s="3"/>
       <c r="AZ23" s="3"/>
@@ -3657,7 +3768,9 @@
       <c r="V24" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="W24" s="3"/>
+      <c r="W24" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
@@ -3758,7 +3871,9 @@
       <c r="V25" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="W25" s="3"/>
+      <c r="W25" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="X25" s="3"/>
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
@@ -3867,7 +3982,9 @@
       <c r="V26" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="W26" s="3"/>
+      <c r="W26" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="X26" s="3"/>
       <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
@@ -3968,7 +4085,9 @@
       <c r="V27" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="W27" s="3"/>
+      <c r="W27" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="X27" s="3"/>
       <c r="Y27" s="3"/>
       <c r="Z27" s="3"/>
@@ -4079,7 +4198,9 @@
       <c r="V28" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W28" s="3"/>
+      <c r="W28" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
@@ -4121,7 +4242,7 @@
       <c r="AZ28" s="3"/>
       <c r="BA28" s="1"/>
     </row>
-    <row r="29" spans="1:53" ht="135">
+    <row r="29" spans="1:53" ht="240">
       <c r="A29" s="2">
         <v>26</v>
       </c>
@@ -4186,7 +4307,9 @@
       <c r="V29" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W29" s="3"/>
+      <c r="W29" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="X29" s="3"/>
       <c r="Y29" s="3"/>
       <c r="Z29" s="3"/>
@@ -4210,25 +4333,41 @@
         <v>5</v>
       </c>
       <c r="AJ29" s="30"/>
-      <c r="AK29" s="37"/>
-      <c r="AL29" s="3"/>
+      <c r="AK29" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL29" s="44">
+        <v>1</v>
+      </c>
       <c r="AM29" s="24">
         <v>46135</v>
       </c>
       <c r="AN29" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="AO29" s="30"/>
-      <c r="AP29" s="3"/>
-      <c r="AQ29" s="3"/>
+      <c r="AO29" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="AP29" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ29" s="28" t="s">
+        <v>87</v>
+      </c>
       <c r="AR29" s="24">
         <v>46135</v>
       </c>
       <c r="AS29" s="30"/>
-      <c r="AT29" s="3"/>
-      <c r="AU29" s="3"/>
-      <c r="AV29" s="3"/>
-      <c r="AW29" s="3"/>
+      <c r="AT29" s="51" t="s">
+        <v>125</v>
+      </c>
+      <c r="AU29" s="24">
+        <v>46149</v>
+      </c>
+      <c r="AV29" s="45"/>
+      <c r="AW29" s="24">
+        <v>46149</v>
+      </c>
       <c r="AX29" s="3"/>
       <c r="AY29" s="3"/>
       <c r="AZ29" s="3"/>
@@ -4301,7 +4440,9 @@
       <c r="V30" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W30" s="3"/>
+      <c r="W30" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
       <c r="Z30" s="3"/>
@@ -4424,7 +4565,9 @@
       <c r="V31" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W31" s="3"/>
+      <c r="W31" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="X31" s="3"/>
       <c r="Y31" s="3"/>
       <c r="Z31" s="3"/>
@@ -4537,7 +4680,9 @@
       <c r="V32" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="W32" s="3"/>
+      <c r="W32" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
       <c r="Z32" s="3"/>
@@ -4636,7 +4781,9 @@
       <c r="V33" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W33" s="3"/>
+      <c r="W33" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="X33" s="3"/>
       <c r="Y33" s="3"/>
       <c r="Z33" s="3"/>
@@ -4747,7 +4894,9 @@
       <c r="V34" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="W34" s="3"/>
+      <c r="W34" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
       <c r="Z34" s="3"/>
@@ -4779,7 +4928,9 @@
       <c r="AL34" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="AM34" s="5"/>
+      <c r="AM34" s="24">
+        <v>46156</v>
+      </c>
       <c r="AN34" s="5" t="s">
         <v>102</v>
       </c>
@@ -4790,10 +4941,16 @@
         <v>46128</v>
       </c>
       <c r="AS34" s="30"/>
-      <c r="AT34" s="3"/>
-      <c r="AU34" s="3"/>
+      <c r="AT34" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="AU34" s="24">
+        <v>46156</v>
+      </c>
       <c r="AV34" s="3"/>
-      <c r="AW34" s="3"/>
+      <c r="AW34" s="24">
+        <v>46156</v>
+      </c>
       <c r="AX34" s="3"/>
       <c r="AY34" s="3"/>
       <c r="AZ34" s="3"/>
@@ -4862,7 +5019,9 @@
       <c r="V35" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="W35" s="3"/>
+      <c r="W35" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="X35" s="3"/>
       <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
@@ -4961,7 +5120,9 @@
       <c r="V36" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="W36" s="3"/>
+      <c r="W36" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
       <c r="Z36" s="3"/>
@@ -5329,6 +5490,7 @@
     <mergeCell ref="A2:B2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5338,56 +5500,56 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
-      <c r="T1" s="45"/>
-      <c r="U1" s="45"/>
-      <c r="V1" s="45"/>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="45"/>
-      <c r="AB1" s="45"/>
-      <c r="AC1" s="45"/>
-      <c r="AD1" s="45"/>
-      <c r="AE1" s="45"/>
-      <c r="AF1" s="45"/>
-      <c r="AG1" s="45"/>
-      <c r="AH1" s="45"/>
-      <c r="AI1" s="45"/>
-      <c r="AJ1" s="45"/>
-      <c r="AK1" s="45"/>
-      <c r="AL1" s="45"/>
-      <c r="AM1" s="45"/>
-      <c r="AN1" s="45"/>
-      <c r="AO1" s="45"/>
-      <c r="AP1" s="45"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
+      <c r="S1" s="46"/>
+      <c r="T1" s="46"/>
+      <c r="U1" s="46"/>
+      <c r="V1" s="46"/>
+      <c r="W1" s="46"/>
+      <c r="X1" s="46"/>
+      <c r="Y1" s="46"/>
+      <c r="Z1" s="46"/>
+      <c r="AA1" s="46"/>
+      <c r="AB1" s="46"/>
+      <c r="AC1" s="46"/>
+      <c r="AD1" s="46"/>
+      <c r="AE1" s="46"/>
+      <c r="AF1" s="46"/>
+      <c r="AG1" s="46"/>
+      <c r="AH1" s="46"/>
+      <c r="AI1" s="46"/>
+      <c r="AJ1" s="46"/>
+      <c r="AK1" s="46"/>
+      <c r="AL1" s="46"/>
+      <c r="AM1" s="46"/>
+      <c r="AN1" s="46"/>
+      <c r="AO1" s="46"/>
+      <c r="AP1" s="46"/>
     </row>
     <row r="2" spans="1:42" ht="30">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="47"/>
+      <c r="B2" s="48"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -5816,142 +5978,142 @@
       <c r="AP10" s="1"/>
     </row>
     <row r="11" spans="1:42">
-      <c r="A11" s="47">
+      <c r="A11" s="48">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C11" s="47"/>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="47"/>
-      <c r="I11" s="47"/>
-      <c r="J11" s="47"/>
-      <c r="K11" s="47"/>
-      <c r="L11" s="48"/>
-      <c r="M11" s="48"/>
-      <c r="N11" s="48"/>
-      <c r="O11" s="48"/>
-      <c r="P11" s="48"/>
-      <c r="Q11" s="48"/>
-      <c r="R11" s="48"/>
-      <c r="S11" s="48"/>
-      <c r="T11" s="48"/>
-      <c r="U11" s="48"/>
-      <c r="V11" s="48"/>
-      <c r="W11" s="48"/>
-      <c r="X11" s="48"/>
-      <c r="Y11" s="48"/>
-      <c r="Z11" s="48"/>
-      <c r="AA11" s="48"/>
-      <c r="AB11" s="48"/>
-      <c r="AC11" s="48"/>
-      <c r="AD11" s="48"/>
-      <c r="AE11" s="48"/>
-      <c r="AF11" s="48"/>
-      <c r="AG11" s="48"/>
-      <c r="AH11" s="48"/>
-      <c r="AI11" s="48"/>
-      <c r="AJ11" s="48"/>
-      <c r="AK11" s="48"/>
-      <c r="AL11" s="48"/>
-      <c r="AM11" s="48"/>
-      <c r="AN11" s="48"/>
-      <c r="AO11" s="48"/>
-      <c r="AP11" s="45"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="48"/>
+      <c r="K11" s="48"/>
+      <c r="L11" s="49"/>
+      <c r="M11" s="49"/>
+      <c r="N11" s="49"/>
+      <c r="O11" s="49"/>
+      <c r="P11" s="49"/>
+      <c r="Q11" s="49"/>
+      <c r="R11" s="49"/>
+      <c r="S11" s="49"/>
+      <c r="T11" s="49"/>
+      <c r="U11" s="49"/>
+      <c r="V11" s="49"/>
+      <c r="W11" s="49"/>
+      <c r="X11" s="49"/>
+      <c r="Y11" s="49"/>
+      <c r="Z11" s="49"/>
+      <c r="AA11" s="49"/>
+      <c r="AB11" s="49"/>
+      <c r="AC11" s="49"/>
+      <c r="AD11" s="49"/>
+      <c r="AE11" s="49"/>
+      <c r="AF11" s="49"/>
+      <c r="AG11" s="49"/>
+      <c r="AH11" s="49"/>
+      <c r="AI11" s="49"/>
+      <c r="AJ11" s="49"/>
+      <c r="AK11" s="49"/>
+      <c r="AL11" s="49"/>
+      <c r="AM11" s="49"/>
+      <c r="AN11" s="49"/>
+      <c r="AO11" s="49"/>
+      <c r="AP11" s="46"/>
     </row>
     <row r="12" spans="1:42">
-      <c r="A12" s="47"/>
+      <c r="A12" s="48"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="47"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="47"/>
-      <c r="I12" s="47"/>
-      <c r="J12" s="47"/>
-      <c r="K12" s="47"/>
-      <c r="L12" s="48"/>
-      <c r="M12" s="48"/>
-      <c r="N12" s="48"/>
-      <c r="O12" s="48"/>
-      <c r="P12" s="48"/>
-      <c r="Q12" s="48"/>
-      <c r="R12" s="48"/>
-      <c r="S12" s="48"/>
-      <c r="T12" s="48"/>
-      <c r="U12" s="48"/>
-      <c r="V12" s="48"/>
-      <c r="W12" s="48"/>
-      <c r="X12" s="48"/>
-      <c r="Y12" s="48"/>
-      <c r="Z12" s="48"/>
-      <c r="AA12" s="48"/>
-      <c r="AB12" s="48"/>
-      <c r="AC12" s="48"/>
-      <c r="AD12" s="48"/>
-      <c r="AE12" s="48"/>
-      <c r="AF12" s="48"/>
-      <c r="AG12" s="48"/>
-      <c r="AH12" s="48"/>
-      <c r="AI12" s="48"/>
-      <c r="AJ12" s="48"/>
-      <c r="AK12" s="48"/>
-      <c r="AL12" s="48"/>
-      <c r="AM12" s="48"/>
-      <c r="AN12" s="48"/>
-      <c r="AO12" s="48"/>
-      <c r="AP12" s="45"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="48"/>
+      <c r="I12" s="48"/>
+      <c r="J12" s="48"/>
+      <c r="K12" s="48"/>
+      <c r="L12" s="49"/>
+      <c r="M12" s="49"/>
+      <c r="N12" s="49"/>
+      <c r="O12" s="49"/>
+      <c r="P12" s="49"/>
+      <c r="Q12" s="49"/>
+      <c r="R12" s="49"/>
+      <c r="S12" s="49"/>
+      <c r="T12" s="49"/>
+      <c r="U12" s="49"/>
+      <c r="V12" s="49"/>
+      <c r="W12" s="49"/>
+      <c r="X12" s="49"/>
+      <c r="Y12" s="49"/>
+      <c r="Z12" s="49"/>
+      <c r="AA12" s="49"/>
+      <c r="AB12" s="49"/>
+      <c r="AC12" s="49"/>
+      <c r="AD12" s="49"/>
+      <c r="AE12" s="49"/>
+      <c r="AF12" s="49"/>
+      <c r="AG12" s="49"/>
+      <c r="AH12" s="49"/>
+      <c r="AI12" s="49"/>
+      <c r="AJ12" s="49"/>
+      <c r="AK12" s="49"/>
+      <c r="AL12" s="49"/>
+      <c r="AM12" s="49"/>
+      <c r="AN12" s="49"/>
+      <c r="AO12" s="49"/>
+      <c r="AP12" s="46"/>
     </row>
     <row r="13" spans="1:42">
-      <c r="A13" s="47"/>
+      <c r="A13" s="48"/>
       <c r="B13" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="47"/>
-      <c r="D13" s="47"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="47"/>
-      <c r="G13" s="47"/>
-      <c r="H13" s="47"/>
-      <c r="I13" s="47"/>
-      <c r="J13" s="47"/>
-      <c r="K13" s="47"/>
-      <c r="L13" s="48"/>
-      <c r="M13" s="48"/>
-      <c r="N13" s="48"/>
-      <c r="O13" s="48"/>
-      <c r="P13" s="48"/>
-      <c r="Q13" s="48"/>
-      <c r="R13" s="48"/>
-      <c r="S13" s="48"/>
-      <c r="T13" s="48"/>
-      <c r="U13" s="48"/>
-      <c r="V13" s="48"/>
-      <c r="W13" s="48"/>
-      <c r="X13" s="48"/>
-      <c r="Y13" s="48"/>
-      <c r="Z13" s="48"/>
-      <c r="AA13" s="48"/>
-      <c r="AB13" s="48"/>
-      <c r="AC13" s="48"/>
-      <c r="AD13" s="48"/>
-      <c r="AE13" s="48"/>
-      <c r="AF13" s="48"/>
-      <c r="AG13" s="48"/>
-      <c r="AH13" s="48"/>
-      <c r="AI13" s="48"/>
-      <c r="AJ13" s="48"/>
-      <c r="AK13" s="48"/>
-      <c r="AL13" s="48"/>
-      <c r="AM13" s="48"/>
-      <c r="AN13" s="48"/>
-      <c r="AO13" s="48"/>
-      <c r="AP13" s="45"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="48"/>
+      <c r="L13" s="49"/>
+      <c r="M13" s="49"/>
+      <c r="N13" s="49"/>
+      <c r="O13" s="49"/>
+      <c r="P13" s="49"/>
+      <c r="Q13" s="49"/>
+      <c r="R13" s="49"/>
+      <c r="S13" s="49"/>
+      <c r="T13" s="49"/>
+      <c r="U13" s="49"/>
+      <c r="V13" s="49"/>
+      <c r="W13" s="49"/>
+      <c r="X13" s="49"/>
+      <c r="Y13" s="49"/>
+      <c r="Z13" s="49"/>
+      <c r="AA13" s="49"/>
+      <c r="AB13" s="49"/>
+      <c r="AC13" s="49"/>
+      <c r="AD13" s="49"/>
+      <c r="AE13" s="49"/>
+      <c r="AF13" s="49"/>
+      <c r="AG13" s="49"/>
+      <c r="AH13" s="49"/>
+      <c r="AI13" s="49"/>
+      <c r="AJ13" s="49"/>
+      <c r="AK13" s="49"/>
+      <c r="AL13" s="49"/>
+      <c r="AM13" s="49"/>
+      <c r="AN13" s="49"/>
+      <c r="AO13" s="49"/>
+      <c r="AP13" s="46"/>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" s="2">
@@ -7107,33 +7269,6 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="AO11:AO13"/>
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="AN11:AN13"/>
-    <mergeCell ref="AE11:AE13"/>
-    <mergeCell ref="AF11:AF13"/>
-    <mergeCell ref="AG11:AG13"/>
-    <mergeCell ref="AH11:AH13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="Z11:Z13"/>
-    <mergeCell ref="AA11:AA13"/>
-    <mergeCell ref="AB11:AB13"/>
-    <mergeCell ref="AC11:AC13"/>
-    <mergeCell ref="AD11:AD13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="V11:V13"/>
-    <mergeCell ref="W11:W13"/>
-    <mergeCell ref="X11:X13"/>
-    <mergeCell ref="Y11:Y13"/>
-    <mergeCell ref="P11:P13"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="T11:T13"/>
     <mergeCell ref="A1:AP1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A11:A13"/>
@@ -7150,6 +7285,33 @@
     <mergeCell ref="M11:M13"/>
     <mergeCell ref="N11:N13"/>
     <mergeCell ref="O11:O13"/>
+    <mergeCell ref="P11:P13"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="T11:T13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="V11:V13"/>
+    <mergeCell ref="W11:W13"/>
+    <mergeCell ref="X11:X13"/>
+    <mergeCell ref="Y11:Y13"/>
+    <mergeCell ref="Z11:Z13"/>
+    <mergeCell ref="AA11:AA13"/>
+    <mergeCell ref="AB11:AB13"/>
+    <mergeCell ref="AC11:AC13"/>
+    <mergeCell ref="AD11:AD13"/>
+    <mergeCell ref="AE11:AE13"/>
+    <mergeCell ref="AF11:AF13"/>
+    <mergeCell ref="AG11:AG13"/>
+    <mergeCell ref="AH11:AH13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="AO11:AO13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
+    <mergeCell ref="AN11:AN13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ТКИ-341_Реверс_Инжиниринг.xlsx
+++ b/ТКИ-341_Реверс_Инжиниринг.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\Reverse_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8E77AF-25C5-41A5-9E6E-B549EDB0E728}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E15C7AF1-AE99-48D4-88A0-0DF631A5C61F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="138">
   <si>
     <t>ВЕДОМОСТЬ ПОСЕЩАЕМОСТИ ЗАНЯТИЙ СТУДЕНТАМИ ГРУППЫ ТКИ "Компьютерная безопасность" ИТТСУ РУТ (МИИТ)</t>
   </si>
@@ -445,6 +445,39 @@
   <si>
     <t>13 сумма элементов массива с нечетными значениями, Винтфельд Рина Дмитриевна, Черемных</t>
   </si>
+  <si>
+    <t>Bevel</t>
+  </si>
+  <si>
+    <t>Не взлетел даже при наличии IDE</t>
+  </si>
+  <si>
+    <t>Левин и ремигайло (15)</t>
+  </si>
+  <si>
+    <t>перевод радиан угла в градусы</t>
+  </si>
+  <si>
+    <t>перевод радиан угла в градусы (Архипов и Микутьев)</t>
+  </si>
+  <si>
+    <t>.biz</t>
+  </si>
+  <si>
+    <t>Town</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Безгодова и Пылаева (10)</t>
+  </si>
+  <si>
+    <t>сумму первых десяти членов арифметической прогрессии</t>
+  </si>
+  <si>
+    <t>GitHub Analyzer</t>
+  </si>
+  <si>
+    <t>сделали инструкцию</t>
+  </si>
 </sst>
 </file>
 
@@ -454,7 +487,7 @@
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -494,6 +527,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="204"/>
@@ -576,7 +616,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -696,6 +736,21 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -707,15 +762,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1025,67 +1078,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:53" ht="14.45" customHeight="1">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
-      <c r="O1" s="46"/>
-      <c r="P1" s="46"/>
-      <c r="Q1" s="46"/>
-      <c r="R1" s="46"/>
-      <c r="S1" s="46"/>
-      <c r="T1" s="46"/>
-      <c r="U1" s="46"/>
-      <c r="V1" s="46"/>
-      <c r="W1" s="46"/>
-      <c r="X1" s="46"/>
-      <c r="Y1" s="46"/>
-      <c r="Z1" s="46"/>
-      <c r="AA1" s="46"/>
-      <c r="AB1" s="46"/>
-      <c r="AC1" s="46"/>
-      <c r="AD1" s="46"/>
-      <c r="AE1" s="46"/>
-      <c r="AF1" s="46"/>
-      <c r="AG1" s="46"/>
-      <c r="AH1" s="46"/>
-      <c r="AI1" s="46"/>
-      <c r="AJ1" s="46"/>
-      <c r="AK1" s="46"/>
-      <c r="AL1" s="46"/>
-      <c r="AM1" s="46"/>
-      <c r="AN1" s="46"/>
-      <c r="AO1" s="46"/>
-      <c r="AP1" s="46"/>
-      <c r="AQ1" s="46"/>
-      <c r="AR1" s="46"/>
-      <c r="AS1" s="46"/>
-      <c r="AT1" s="46"/>
-      <c r="AU1" s="46"/>
-      <c r="AV1" s="46"/>
-      <c r="AW1" s="46"/>
-      <c r="AX1" s="46"/>
-      <c r="AY1" s="46"/>
-      <c r="AZ1" s="46"/>
-      <c r="BA1" s="46"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="53"/>
+      <c r="R1" s="53"/>
+      <c r="S1" s="53"/>
+      <c r="T1" s="53"/>
+      <c r="U1" s="53"/>
+      <c r="V1" s="53"/>
+      <c r="W1" s="53"/>
+      <c r="X1" s="53"/>
+      <c r="Y1" s="53"/>
+      <c r="Z1" s="53"/>
+      <c r="AA1" s="53"/>
+      <c r="AB1" s="53"/>
+      <c r="AC1" s="53"/>
+      <c r="AD1" s="53"/>
+      <c r="AE1" s="53"/>
+      <c r="AF1" s="53"/>
+      <c r="AG1" s="53"/>
+      <c r="AH1" s="53"/>
+      <c r="AI1" s="53"/>
+      <c r="AJ1" s="53"/>
+      <c r="AK1" s="53"/>
+      <c r="AL1" s="53"/>
+      <c r="AM1" s="53"/>
+      <c r="AN1" s="53"/>
+      <c r="AO1" s="53"/>
+      <c r="AP1" s="53"/>
+      <c r="AQ1" s="53"/>
+      <c r="AR1" s="53"/>
+      <c r="AS1" s="53"/>
+      <c r="AT1" s="53"/>
+      <c r="AU1" s="53"/>
+      <c r="AV1" s="53"/>
+      <c r="AW1" s="53"/>
+      <c r="AX1" s="53"/>
+      <c r="AY1" s="53"/>
+      <c r="AZ1" s="53"/>
+      <c r="BA1" s="53"/>
     </row>
     <row r="2" spans="1:53" ht="27.6" customHeight="1">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="48"/>
+      <c r="B2" s="55"/>
       <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1336,9 +1389,13 @@
       <c r="W4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X4" s="3"/>
+      <c r="X4" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="Y4" s="3"/>
-      <c r="Z4" s="3"/>
+      <c r="Z4" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="AA4" s="3"/>
       <c r="AB4" s="17">
         <v>46086</v>
@@ -1360,11 +1417,15 @@
       </c>
       <c r="AJ4" s="30"/>
       <c r="AK4" s="37"/>
-      <c r="AL4" s="3">
-        <v>15</v>
-      </c>
-      <c r="AM4" s="37"/>
-      <c r="AN4" s="37"/>
+      <c r="AL4" s="50" t="s">
+        <v>129</v>
+      </c>
+      <c r="AM4" s="24">
+        <v>46170</v>
+      </c>
+      <c r="AN4" s="50" t="s">
+        <v>130</v>
+      </c>
       <c r="AO4" s="42" t="s">
         <v>72</v>
       </c>
@@ -1374,7 +1435,9 @@
       <c r="AQ4" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="AR4" s="3"/>
+      <c r="AR4" s="24">
+        <v>46170</v>
+      </c>
       <c r="AS4" s="30"/>
       <c r="AT4" s="3"/>
       <c r="AU4" s="3"/>
@@ -1455,9 +1518,13 @@
       <c r="W5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X5" s="3"/>
+      <c r="X5" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="Y5" s="3"/>
-      <c r="Z5" s="3"/>
+      <c r="Z5" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="AA5" s="3"/>
       <c r="AB5" s="11">
         <v>46100</v>
@@ -1574,9 +1641,13 @@
       <c r="W6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X6" s="3"/>
+      <c r="X6" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="Y6" s="3"/>
-      <c r="Z6" s="3"/>
+      <c r="Z6" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="AA6" s="3"/>
       <c r="AB6" s="11">
         <v>46072</v>
@@ -1616,12 +1687,22 @@
       <c r="AQ6" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="AR6" s="3"/>
-      <c r="AS6" s="30"/>
-      <c r="AT6" s="3"/>
-      <c r="AU6" s="3"/>
+      <c r="AR6" s="24">
+        <v>46170</v>
+      </c>
+      <c r="AS6" s="58" t="s">
+        <v>128</v>
+      </c>
+      <c r="AT6" s="57" t="s">
+        <v>127</v>
+      </c>
+      <c r="AU6" s="24">
+        <v>46170</v>
+      </c>
       <c r="AV6" s="3"/>
-      <c r="AW6" s="3"/>
+      <c r="AW6" s="24">
+        <v>46170</v>
+      </c>
       <c r="AX6" s="3"/>
       <c r="AY6" s="3"/>
       <c r="AZ6" s="3"/>
@@ -1697,9 +1778,13 @@
       <c r="W7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="X7" s="3"/>
+      <c r="X7" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="Y7" s="3"/>
-      <c r="Z7" s="3"/>
+      <c r="Z7" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="AA7" s="3"/>
       <c r="AB7" s="22">
         <v>46100</v>
@@ -1830,9 +1915,13 @@
       <c r="W8" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="X8" s="3"/>
+      <c r="X8" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="Y8" s="3"/>
-      <c r="Z8" s="3"/>
+      <c r="Z8" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="AA8" s="3"/>
       <c r="AB8" s="11">
         <v>46100</v>
@@ -1948,9 +2037,13 @@
       <c r="W9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X9" s="3"/>
+      <c r="X9" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="Y9" s="3"/>
-      <c r="Z9" s="3"/>
+      <c r="Z9" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="AA9" s="3"/>
       <c r="AB9" s="11">
         <v>46100</v>
@@ -1960,9 +2053,13 @@
         <v>46135</v>
       </c>
       <c r="AE9" s="3"/>
-      <c r="AF9" s="3"/>
+      <c r="AF9" s="24">
+        <v>46170</v>
+      </c>
       <c r="AG9" s="3"/>
-      <c r="AH9" s="3"/>
+      <c r="AH9" s="24">
+        <v>46170</v>
+      </c>
       <c r="AI9" s="3">
         <v>3</v>
       </c>
@@ -1984,7 +2081,9 @@
         <v>80</v>
       </c>
       <c r="AQ9" s="3"/>
-      <c r="AR9" s="3"/>
+      <c r="AR9" s="24">
+        <v>46170</v>
+      </c>
       <c r="AS9" s="30"/>
       <c r="AT9" s="3"/>
       <c r="AU9" s="3"/>
@@ -2065,9 +2164,13 @@
       <c r="W10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X10" s="3"/>
+      <c r="X10" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="Y10" s="3"/>
-      <c r="Z10" s="3"/>
+      <c r="Z10" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="AA10" s="3"/>
       <c r="AB10" s="11">
         <v>46079</v>
@@ -2107,7 +2210,9 @@
       <c r="AQ10" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="AR10" s="3"/>
+      <c r="AR10" s="24">
+        <v>46170</v>
+      </c>
       <c r="AS10" s="30"/>
       <c r="AT10" s="3"/>
       <c r="AU10" s="3"/>
@@ -2186,9 +2291,13 @@
       <c r="W11" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="X11" s="5"/>
+      <c r="X11" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="Y11" s="5"/>
-      <c r="Z11" s="5"/>
+      <c r="Z11" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="AA11" s="5"/>
       <c r="AB11" s="11">
         <v>46079</v>
@@ -2247,7 +2356,7 @@
       <c r="AZ11" s="5"/>
       <c r="BA11" s="5"/>
     </row>
-    <row r="12" spans="1:53" ht="105">
+    <row r="12" spans="1:53" ht="120">
       <c r="A12" s="2">
         <v>9</v>
       </c>
@@ -2317,9 +2426,13 @@
       <c r="W12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="X12" s="5"/>
+      <c r="X12" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="Y12" s="5"/>
-      <c r="Z12" s="5"/>
+      <c r="Z12" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="AA12" s="5"/>
       <c r="AB12" s="11">
         <v>46072</v>
@@ -2341,11 +2454,15 @@
       </c>
       <c r="AJ12" s="31"/>
       <c r="AK12" s="5"/>
-      <c r="AL12" s="5">
-        <v>10</v>
-      </c>
-      <c r="AM12" s="5"/>
-      <c r="AN12" s="5"/>
+      <c r="AL12" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="AM12" s="24">
+        <v>46170</v>
+      </c>
+      <c r="AN12" s="49" t="s">
+        <v>135</v>
+      </c>
       <c r="AO12" s="42" t="s">
         <v>72</v>
       </c>
@@ -2358,11 +2475,19 @@
       <c r="AR12" s="24">
         <v>46135</v>
       </c>
-      <c r="AS12" s="31"/>
-      <c r="AT12" s="5"/>
-      <c r="AU12" s="34"/>
+      <c r="AS12" s="59" t="s">
+        <v>137</v>
+      </c>
+      <c r="AT12" s="49" t="s">
+        <v>136</v>
+      </c>
+      <c r="AU12" s="24">
+        <v>46170</v>
+      </c>
       <c r="AV12" s="5"/>
-      <c r="AW12" s="5"/>
+      <c r="AW12" s="24">
+        <v>46170</v>
+      </c>
       <c r="AX12" s="5"/>
       <c r="AY12" s="5"/>
       <c r="AZ12" s="5"/>
@@ -2372,7 +2497,7 @@
       <c r="A13" s="2">
         <v>10</v>
       </c>
-      <c r="B13" s="54" t="s">
+      <c r="B13" s="51" t="s">
         <v>33</v>
       </c>
       <c r="C13" s="9">
@@ -2438,9 +2563,15 @@
       <c r="W13" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="X13" s="5"/>
-      <c r="Y13" s="5"/>
-      <c r="Z13" s="5"/>
+      <c r="X13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z13" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="AA13" s="5"/>
       <c r="AB13" s="11">
         <v>46072</v>
@@ -2466,13 +2597,13 @@
       <c r="AK13" s="34">
         <v>11</v>
       </c>
-      <c r="AL13" s="50" t="s">
+      <c r="AL13" s="47" t="s">
         <v>101</v>
       </c>
       <c r="AM13" s="24">
         <v>46149</v>
       </c>
-      <c r="AN13" s="52" t="s">
+      <c r="AN13" s="49" t="s">
         <v>102</v>
       </c>
       <c r="AO13" s="42" t="s">
@@ -2569,9 +2700,13 @@
       <c r="W14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X14" s="3"/>
+      <c r="X14" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="Y14" s="3"/>
-      <c r="Z14" s="3"/>
+      <c r="Z14" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="AA14" s="3"/>
       <c r="AB14" s="3"/>
       <c r="AC14" s="3"/>
@@ -2680,9 +2815,13 @@
       <c r="W15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="X15" s="3"/>
+      <c r="X15" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="Y15" s="3"/>
-      <c r="Z15" s="3"/>
+      <c r="Z15" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="AA15" s="3"/>
       <c r="AB15" s="11">
         <v>46079</v>
@@ -2801,9 +2940,13 @@
       <c r="W16" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X16" s="3"/>
+      <c r="X16" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="Y16" s="3"/>
-      <c r="Z16" s="3"/>
+      <c r="Z16" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="AA16" s="3"/>
       <c r="AB16" s="11">
         <v>46072</v>
@@ -2932,9 +3075,13 @@
       <c r="W17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X17" s="3"/>
+      <c r="X17" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="Y17" s="3"/>
-      <c r="Z17" s="3"/>
+      <c r="Z17" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="AA17" s="3"/>
       <c r="AB17" s="11">
         <v>46072</v>
@@ -2955,7 +3102,7 @@
         <v>5</v>
       </c>
       <c r="AJ17" s="30"/>
-      <c r="AK17" s="53" t="s">
+      <c r="AK17" s="50" t="s">
         <v>126</v>
       </c>
       <c r="AL17" s="44">
@@ -2964,7 +3111,7 @@
       <c r="AM17" s="24">
         <v>46135</v>
       </c>
-      <c r="AN17" s="52" t="s">
+      <c r="AN17" s="49" t="s">
         <v>102</v>
       </c>
       <c r="AO17" s="42" t="s">
@@ -2980,7 +3127,7 @@
         <v>46135</v>
       </c>
       <c r="AS17" s="30"/>
-      <c r="AT17" s="51" t="s">
+      <c r="AT17" s="48" t="s">
         <v>125</v>
       </c>
       <c r="AU17" s="24">
@@ -3065,9 +3212,13 @@
       <c r="W18" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="X18" s="3"/>
+      <c r="X18" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="Y18" s="3"/>
-      <c r="Z18" s="3"/>
+      <c r="Z18" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="AA18" s="3"/>
       <c r="AB18" s="22">
         <v>46100</v>
@@ -3186,9 +3337,13 @@
       <c r="W19" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X19" s="3"/>
+      <c r="X19" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="Y19" s="3"/>
-      <c r="Z19" s="3"/>
+      <c r="Z19" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="AA19" s="3"/>
       <c r="AB19" s="11">
         <v>46100</v>
@@ -3198,9 +3353,13 @@
         <v>46135</v>
       </c>
       <c r="AE19" s="3"/>
-      <c r="AF19" s="3"/>
+      <c r="AF19" s="24">
+        <v>46170</v>
+      </c>
       <c r="AG19" s="3"/>
-      <c r="AH19" s="3"/>
+      <c r="AH19" s="24">
+        <v>46170</v>
+      </c>
       <c r="AI19" s="3">
         <v>3</v>
       </c>
@@ -3215,10 +3374,16 @@
       <c r="AN19" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="AO19" s="30"/>
-      <c r="AP19" s="3"/>
-      <c r="AQ19" s="3"/>
-      <c r="AR19" s="3"/>
+      <c r="AO19" s="42" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP19" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="AQ19" s="46"/>
+      <c r="AR19" s="24">
+        <v>46170</v>
+      </c>
       <c r="AS19" s="30"/>
       <c r="AT19" s="3"/>
       <c r="AU19" s="3"/>
@@ -3299,9 +3464,13 @@
       <c r="W20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="X20" s="3"/>
+      <c r="X20" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="Y20" s="3"/>
-      <c r="Z20" s="3"/>
+      <c r="Z20" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="AA20" s="3"/>
       <c r="AB20" s="24">
         <v>46118</v>
@@ -3324,10 +3493,14 @@
       </c>
       <c r="AM20" s="37"/>
       <c r="AN20" s="37"/>
-      <c r="AO20" s="30"/>
+      <c r="AO20" s="57" t="s">
+        <v>132</v>
+      </c>
       <c r="AP20" s="3"/>
       <c r="AQ20" s="3"/>
-      <c r="AR20" s="3"/>
+      <c r="AR20" s="24">
+        <v>46170</v>
+      </c>
       <c r="AS20" s="30"/>
       <c r="AT20" s="3"/>
       <c r="AU20" s="3"/>
@@ -3408,9 +3581,13 @@
       <c r="W21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X21" s="3"/>
+      <c r="X21" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="Y21" s="3"/>
-      <c r="Z21" s="3"/>
+      <c r="Z21" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="AA21" s="3"/>
       <c r="AB21" s="11">
         <v>46100</v>
@@ -3422,7 +3599,9 @@
         <v>46135</v>
       </c>
       <c r="AG21" s="3"/>
-      <c r="AH21" s="3"/>
+      <c r="AH21" s="24">
+        <v>46170</v>
+      </c>
       <c r="AI21" s="3">
         <v>3</v>
       </c>
@@ -3517,9 +3696,13 @@
       <c r="W22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X22" s="3"/>
+      <c r="X22" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="Y22" s="3"/>
-      <c r="Z22" s="3"/>
+      <c r="Z22" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="AA22" s="3"/>
       <c r="AB22" s="11">
         <v>46072</v>
@@ -3646,9 +3829,13 @@
       <c r="W23" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X23" s="3"/>
+      <c r="X23" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="Y23" s="3"/>
-      <c r="Z23" s="3"/>
+      <c r="Z23" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="AA23" s="3"/>
       <c r="AB23" s="11">
         <v>46072</v>
@@ -3701,7 +3888,7 @@
       <c r="AZ23" s="3"/>
       <c r="BA23" s="1"/>
     </row>
-    <row r="24" spans="1:53">
+    <row r="24" spans="1:53" ht="120">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -3771,13 +3958,21 @@
       <c r="W24" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="X24" s="3"/>
+      <c r="X24" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="Y24" s="3"/>
-      <c r="Z24" s="3"/>
+      <c r="Z24" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="AA24" s="3"/>
-      <c r="AB24" s="3"/>
+      <c r="AB24" s="24">
+        <v>46170</v>
+      </c>
       <c r="AC24" s="3"/>
-      <c r="AD24" s="3"/>
+      <c r="AD24" s="24">
+        <v>46170</v>
+      </c>
       <c r="AE24" s="3"/>
       <c r="AF24" s="3"/>
       <c r="AG24" s="3"/>
@@ -3786,16 +3981,24 @@
         <v>2</v>
       </c>
       <c r="AJ24" s="30"/>
-      <c r="AK24" s="37"/>
+      <c r="AK24" s="50" t="s">
+        <v>131</v>
+      </c>
       <c r="AL24" s="3">
         <v>2</v>
       </c>
       <c r="AM24" s="37"/>
       <c r="AN24" s="37"/>
-      <c r="AO24" s="30"/>
-      <c r="AP24" s="3"/>
+      <c r="AO24" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="AP24" s="50" t="s">
+        <v>133</v>
+      </c>
       <c r="AQ24" s="3"/>
-      <c r="AR24" s="3"/>
+      <c r="AR24" s="24">
+        <v>46170</v>
+      </c>
       <c r="AS24" s="30"/>
       <c r="AT24" s="3"/>
       <c r="AU24" s="3"/>
@@ -3806,7 +4009,7 @@
       <c r="AZ24" s="3"/>
       <c r="BA24" s="1"/>
     </row>
-    <row r="25" spans="1:53">
+    <row r="25" spans="1:53" ht="120">
       <c r="A25" s="2">
         <v>22</v>
       </c>
@@ -3874,9 +4077,13 @@
       <c r="W25" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X25" s="3"/>
+      <c r="X25" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="Y25" s="3"/>
-      <c r="Z25" s="3"/>
+      <c r="Z25" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="AA25" s="3"/>
       <c r="AB25" s="11">
         <v>46072</v>
@@ -3898,20 +4105,34 @@
       </c>
       <c r="AJ25" s="30"/>
       <c r="AK25" s="37"/>
-      <c r="AL25" s="3"/>
-      <c r="AM25" s="37"/>
-      <c r="AN25" s="37"/>
+      <c r="AL25" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="AM25" s="24">
+        <v>46170</v>
+      </c>
+      <c r="AN25" s="49" t="s">
+        <v>135</v>
+      </c>
       <c r="AO25" s="30"/>
       <c r="AP25" s="3"/>
       <c r="AQ25" s="3"/>
       <c r="AR25" s="24">
         <v>46135</v>
       </c>
-      <c r="AS25" s="30"/>
-      <c r="AT25" s="3"/>
-      <c r="AU25" s="3"/>
-      <c r="AV25" s="3"/>
-      <c r="AW25" s="3"/>
+      <c r="AS25" s="59" t="s">
+        <v>137</v>
+      </c>
+      <c r="AT25" s="49" t="s">
+        <v>136</v>
+      </c>
+      <c r="AU25" s="24">
+        <v>46170</v>
+      </c>
+      <c r="AV25" s="5"/>
+      <c r="AW25" s="24">
+        <v>46170</v>
+      </c>
       <c r="AX25" s="3"/>
       <c r="AY25" s="3"/>
       <c r="AZ25" s="3"/>
@@ -3985,9 +4206,13 @@
       <c r="W26" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X26" s="3"/>
+      <c r="X26" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="Y26" s="3"/>
-      <c r="Z26" s="3"/>
+      <c r="Z26" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="AA26" s="3"/>
       <c r="AB26" s="3"/>
       <c r="AC26" s="3"/>
@@ -4088,9 +4313,13 @@
       <c r="W27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X27" s="3"/>
+      <c r="X27" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="Y27" s="3"/>
-      <c r="Z27" s="3"/>
+      <c r="Z27" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="AA27" s="3"/>
       <c r="AB27" s="11">
         <v>46100</v>
@@ -4131,7 +4360,7 @@
       <c r="AZ27" s="3"/>
       <c r="BA27" s="1"/>
     </row>
-    <row r="28" spans="1:53">
+    <row r="28" spans="1:53" ht="105">
       <c r="A28" s="2">
         <v>25</v>
       </c>
@@ -4201,9 +4430,13 @@
       <c r="W28" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X28" s="3"/>
+      <c r="X28" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="Y28" s="3"/>
-      <c r="Z28" s="3"/>
+      <c r="Z28" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="AA28" s="3"/>
       <c r="AB28" s="17">
         <v>46086</v>
@@ -4225,13 +4458,27 @@
       </c>
       <c r="AJ28" s="30"/>
       <c r="AK28" s="37"/>
-      <c r="AL28" s="3"/>
-      <c r="AM28" s="37"/>
-      <c r="AN28" s="37"/>
-      <c r="AO28" s="30"/>
-      <c r="AP28" s="3"/>
-      <c r="AQ28" s="3"/>
-      <c r="AR28" s="3"/>
+      <c r="AL28" s="50" t="s">
+        <v>129</v>
+      </c>
+      <c r="AM28" s="24">
+        <v>46170</v>
+      </c>
+      <c r="AN28" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="AO28" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="AP28" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ28" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR28" s="24">
+        <v>46170</v>
+      </c>
       <c r="AS28" s="30"/>
       <c r="AT28" s="3"/>
       <c r="AU28" s="3"/>
@@ -4310,9 +4557,13 @@
       <c r="W29" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X29" s="3"/>
+      <c r="X29" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="Y29" s="3"/>
-      <c r="Z29" s="3"/>
+      <c r="Z29" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="AA29" s="3"/>
       <c r="AB29" s="11">
         <v>46072</v>
@@ -4333,7 +4584,7 @@
         <v>5</v>
       </c>
       <c r="AJ29" s="30"/>
-      <c r="AK29" s="53" t="s">
+      <c r="AK29" s="50" t="s">
         <v>126</v>
       </c>
       <c r="AL29" s="44">
@@ -4358,7 +4609,7 @@
         <v>46135</v>
       </c>
       <c r="AS29" s="30"/>
-      <c r="AT29" s="51" t="s">
+      <c r="AT29" s="48" t="s">
         <v>125</v>
       </c>
       <c r="AU29" s="24">
@@ -4443,9 +4694,13 @@
       <c r="W30" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="X30" s="3"/>
+      <c r="X30" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="Y30" s="3"/>
-      <c r="Z30" s="3"/>
+      <c r="Z30" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="AA30" s="3"/>
       <c r="AB30" s="11">
         <v>46072</v>
@@ -4498,7 +4753,7 @@
       <c r="AZ30" s="3"/>
       <c r="BA30" s="1"/>
     </row>
-    <row r="31" spans="1:53" ht="75">
+    <row r="31" spans="1:53" ht="105">
       <c r="A31" s="2">
         <v>28</v>
       </c>
@@ -4568,9 +4823,13 @@
       <c r="W31" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X31" s="3"/>
+      <c r="X31" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="Y31" s="3"/>
-      <c r="Z31" s="3"/>
+      <c r="Z31" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="AA31" s="3"/>
       <c r="AB31" s="11">
         <v>46072</v>
@@ -4601,21 +4860,37 @@
       <c r="AN31" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="AO31" s="30"/>
-      <c r="AP31" s="3"/>
-      <c r="AQ31" s="3"/>
-      <c r="AR31" s="3"/>
-      <c r="AS31" s="30"/>
-      <c r="AT31" s="3"/>
-      <c r="AU31" s="3"/>
-      <c r="AV31" s="3"/>
-      <c r="AW31" s="3"/>
+      <c r="AO31" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="AP31" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ31" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="AR31" s="24">
+        <v>46170</v>
+      </c>
+      <c r="AS31" s="58" t="s">
+        <v>128</v>
+      </c>
+      <c r="AT31" s="57" t="s">
+        <v>127</v>
+      </c>
+      <c r="AU31" s="24">
+        <v>46170</v>
+      </c>
+      <c r="AV31" s="52"/>
+      <c r="AW31" s="24">
+        <v>46170</v>
+      </c>
       <c r="AX31" s="3"/>
       <c r="AY31" s="3"/>
       <c r="AZ31" s="3"/>
       <c r="BA31" s="1"/>
     </row>
-    <row r="32" spans="1:53">
+    <row r="32" spans="1:53" ht="120">
       <c r="A32" s="2">
         <v>29</v>
       </c>
@@ -4683,13 +4958,21 @@
       <c r="W32" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="X32" s="3"/>
+      <c r="X32" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="Y32" s="3"/>
-      <c r="Z32" s="3"/>
+      <c r="Z32" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="AA32" s="3"/>
-      <c r="AB32" s="3"/>
+      <c r="AB32" s="24">
+        <v>46170</v>
+      </c>
       <c r="AC32" s="3"/>
-      <c r="AD32" s="3"/>
+      <c r="AD32" s="24">
+        <v>46170</v>
+      </c>
       <c r="AE32" s="3"/>
       <c r="AF32" s="3"/>
       <c r="AG32" s="3"/>
@@ -4698,14 +4981,22 @@
         <v>2</v>
       </c>
       <c r="AJ32" s="30"/>
-      <c r="AK32" s="37"/>
+      <c r="AK32" s="50" t="s">
+        <v>131</v>
+      </c>
       <c r="AL32" s="3"/>
       <c r="AM32" s="37"/>
       <c r="AN32" s="37"/>
-      <c r="AO32" s="30"/>
-      <c r="AP32" s="3"/>
-      <c r="AQ32" s="3"/>
-      <c r="AR32" s="3"/>
+      <c r="AO32" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="AP32" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="AQ32" s="52"/>
+      <c r="AR32" s="24">
+        <v>46170</v>
+      </c>
       <c r="AS32" s="30"/>
       <c r="AT32" s="3"/>
       <c r="AU32" s="3"/>
@@ -4784,9 +5075,13 @@
       <c r="W33" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X33" s="3"/>
+      <c r="X33" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="Y33" s="3"/>
-      <c r="Z33" s="3"/>
+      <c r="Z33" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="AA33" s="3"/>
       <c r="AB33" s="11">
         <v>46079</v>
@@ -4817,10 +5112,18 @@
       <c r="AN33" s="41" t="s">
         <v>120</v>
       </c>
-      <c r="AO33" s="30"/>
-      <c r="AP33" s="3"/>
-      <c r="AQ33" s="3"/>
-      <c r="AR33" s="3"/>
+      <c r="AO33" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="AP33" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ33" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="AR33" s="24">
+        <v>46170</v>
+      </c>
       <c r="AS33" s="30"/>
       <c r="AT33" s="3"/>
       <c r="AU33" s="3"/>
@@ -4897,9 +5200,13 @@
       <c r="W34" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X34" s="3"/>
+      <c r="X34" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="Y34" s="3"/>
-      <c r="Z34" s="3"/>
+      <c r="Z34" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="AA34" s="3"/>
       <c r="AB34" s="11">
         <v>46072</v>
@@ -5022,9 +5329,13 @@
       <c r="W35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X35" s="3"/>
+      <c r="X35" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="Y35" s="3"/>
-      <c r="Z35" s="3"/>
+      <c r="Z35" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="AA35" s="3"/>
       <c r="AB35" s="3"/>
       <c r="AC35" s="3"/>
@@ -5123,9 +5434,13 @@
       <c r="W36" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="X36" s="3"/>
+      <c r="X36" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="Y36" s="3"/>
-      <c r="Z36" s="3"/>
+      <c r="Z36" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="AA36" s="3"/>
       <c r="AB36" s="3"/>
       <c r="AC36" s="3"/>
@@ -5500,56 +5815,56 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
-      <c r="O1" s="46"/>
-      <c r="P1" s="46"/>
-      <c r="Q1" s="46"/>
-      <c r="R1" s="46"/>
-      <c r="S1" s="46"/>
-      <c r="T1" s="46"/>
-      <c r="U1" s="46"/>
-      <c r="V1" s="46"/>
-      <c r="W1" s="46"/>
-      <c r="X1" s="46"/>
-      <c r="Y1" s="46"/>
-      <c r="Z1" s="46"/>
-      <c r="AA1" s="46"/>
-      <c r="AB1" s="46"/>
-      <c r="AC1" s="46"/>
-      <c r="AD1" s="46"/>
-      <c r="AE1" s="46"/>
-      <c r="AF1" s="46"/>
-      <c r="AG1" s="46"/>
-      <c r="AH1" s="46"/>
-      <c r="AI1" s="46"/>
-      <c r="AJ1" s="46"/>
-      <c r="AK1" s="46"/>
-      <c r="AL1" s="46"/>
-      <c r="AM1" s="46"/>
-      <c r="AN1" s="46"/>
-      <c r="AO1" s="46"/>
-      <c r="AP1" s="46"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="53"/>
+      <c r="R1" s="53"/>
+      <c r="S1" s="53"/>
+      <c r="T1" s="53"/>
+      <c r="U1" s="53"/>
+      <c r="V1" s="53"/>
+      <c r="W1" s="53"/>
+      <c r="X1" s="53"/>
+      <c r="Y1" s="53"/>
+      <c r="Z1" s="53"/>
+      <c r="AA1" s="53"/>
+      <c r="AB1" s="53"/>
+      <c r="AC1" s="53"/>
+      <c r="AD1" s="53"/>
+      <c r="AE1" s="53"/>
+      <c r="AF1" s="53"/>
+      <c r="AG1" s="53"/>
+      <c r="AH1" s="53"/>
+      <c r="AI1" s="53"/>
+      <c r="AJ1" s="53"/>
+      <c r="AK1" s="53"/>
+      <c r="AL1" s="53"/>
+      <c r="AM1" s="53"/>
+      <c r="AN1" s="53"/>
+      <c r="AO1" s="53"/>
+      <c r="AP1" s="53"/>
     </row>
     <row r="2" spans="1:42" ht="30">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="48"/>
+      <c r="B2" s="55"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -5978,142 +6293,142 @@
       <c r="AP10" s="1"/>
     </row>
     <row r="11" spans="1:42">
-      <c r="A11" s="48">
+      <c r="A11" s="55">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C11" s="48"/>
-      <c r="D11" s="48"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="48"/>
-      <c r="K11" s="48"/>
-      <c r="L11" s="49"/>
-      <c r="M11" s="49"/>
-      <c r="N11" s="49"/>
-      <c r="O11" s="49"/>
-      <c r="P11" s="49"/>
-      <c r="Q11" s="49"/>
-      <c r="R11" s="49"/>
-      <c r="S11" s="49"/>
-      <c r="T11" s="49"/>
-      <c r="U11" s="49"/>
-      <c r="V11" s="49"/>
-      <c r="W11" s="49"/>
-      <c r="X11" s="49"/>
-      <c r="Y11" s="49"/>
-      <c r="Z11" s="49"/>
-      <c r="AA11" s="49"/>
-      <c r="AB11" s="49"/>
-      <c r="AC11" s="49"/>
-      <c r="AD11" s="49"/>
-      <c r="AE11" s="49"/>
-      <c r="AF11" s="49"/>
-      <c r="AG11" s="49"/>
-      <c r="AH11" s="49"/>
-      <c r="AI11" s="49"/>
-      <c r="AJ11" s="49"/>
-      <c r="AK11" s="49"/>
-      <c r="AL11" s="49"/>
-      <c r="AM11" s="49"/>
-      <c r="AN11" s="49"/>
-      <c r="AO11" s="49"/>
-      <c r="AP11" s="46"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
+      <c r="F11" s="55"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="55"/>
+      <c r="J11" s="55"/>
+      <c r="K11" s="55"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="56"/>
+      <c r="N11" s="56"/>
+      <c r="O11" s="56"/>
+      <c r="P11" s="56"/>
+      <c r="Q11" s="56"/>
+      <c r="R11" s="56"/>
+      <c r="S11" s="56"/>
+      <c r="T11" s="56"/>
+      <c r="U11" s="56"/>
+      <c r="V11" s="56"/>
+      <c r="W11" s="56"/>
+      <c r="X11" s="56"/>
+      <c r="Y11" s="56"/>
+      <c r="Z11" s="56"/>
+      <c r="AA11" s="56"/>
+      <c r="AB11" s="56"/>
+      <c r="AC11" s="56"/>
+      <c r="AD11" s="56"/>
+      <c r="AE11" s="56"/>
+      <c r="AF11" s="56"/>
+      <c r="AG11" s="56"/>
+      <c r="AH11" s="56"/>
+      <c r="AI11" s="56"/>
+      <c r="AJ11" s="56"/>
+      <c r="AK11" s="56"/>
+      <c r="AL11" s="56"/>
+      <c r="AM11" s="56"/>
+      <c r="AN11" s="56"/>
+      <c r="AO11" s="56"/>
+      <c r="AP11" s="53"/>
     </row>
     <row r="12" spans="1:42">
-      <c r="A12" s="48"/>
+      <c r="A12" s="55"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="48"/>
-      <c r="D12" s="48"/>
-      <c r="E12" s="48"/>
-      <c r="F12" s="48"/>
-      <c r="G12" s="48"/>
-      <c r="H12" s="48"/>
-      <c r="I12" s="48"/>
-      <c r="J12" s="48"/>
-      <c r="K12" s="48"/>
-      <c r="L12" s="49"/>
-      <c r="M12" s="49"/>
-      <c r="N12" s="49"/>
-      <c r="O12" s="49"/>
-      <c r="P12" s="49"/>
-      <c r="Q12" s="49"/>
-      <c r="R12" s="49"/>
-      <c r="S12" s="49"/>
-      <c r="T12" s="49"/>
-      <c r="U12" s="49"/>
-      <c r="V12" s="49"/>
-      <c r="W12" s="49"/>
-      <c r="X12" s="49"/>
-      <c r="Y12" s="49"/>
-      <c r="Z12" s="49"/>
-      <c r="AA12" s="49"/>
-      <c r="AB12" s="49"/>
-      <c r="AC12" s="49"/>
-      <c r="AD12" s="49"/>
-      <c r="AE12" s="49"/>
-      <c r="AF12" s="49"/>
-      <c r="AG12" s="49"/>
-      <c r="AH12" s="49"/>
-      <c r="AI12" s="49"/>
-      <c r="AJ12" s="49"/>
-      <c r="AK12" s="49"/>
-      <c r="AL12" s="49"/>
-      <c r="AM12" s="49"/>
-      <c r="AN12" s="49"/>
-      <c r="AO12" s="49"/>
-      <c r="AP12" s="46"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="55"/>
+      <c r="K12" s="55"/>
+      <c r="L12" s="56"/>
+      <c r="M12" s="56"/>
+      <c r="N12" s="56"/>
+      <c r="O12" s="56"/>
+      <c r="P12" s="56"/>
+      <c r="Q12" s="56"/>
+      <c r="R12" s="56"/>
+      <c r="S12" s="56"/>
+      <c r="T12" s="56"/>
+      <c r="U12" s="56"/>
+      <c r="V12" s="56"/>
+      <c r="W12" s="56"/>
+      <c r="X12" s="56"/>
+      <c r="Y12" s="56"/>
+      <c r="Z12" s="56"/>
+      <c r="AA12" s="56"/>
+      <c r="AB12" s="56"/>
+      <c r="AC12" s="56"/>
+      <c r="AD12" s="56"/>
+      <c r="AE12" s="56"/>
+      <c r="AF12" s="56"/>
+      <c r="AG12" s="56"/>
+      <c r="AH12" s="56"/>
+      <c r="AI12" s="56"/>
+      <c r="AJ12" s="56"/>
+      <c r="AK12" s="56"/>
+      <c r="AL12" s="56"/>
+      <c r="AM12" s="56"/>
+      <c r="AN12" s="56"/>
+      <c r="AO12" s="56"/>
+      <c r="AP12" s="53"/>
     </row>
     <row r="13" spans="1:42">
-      <c r="A13" s="48"/>
+      <c r="A13" s="55"/>
       <c r="B13" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="48"/>
-      <c r="D13" s="48"/>
-      <c r="E13" s="48"/>
-      <c r="F13" s="48"/>
-      <c r="G13" s="48"/>
-      <c r="H13" s="48"/>
-      <c r="I13" s="48"/>
-      <c r="J13" s="48"/>
-      <c r="K13" s="48"/>
-      <c r="L13" s="49"/>
-      <c r="M13" s="49"/>
-      <c r="N13" s="49"/>
-      <c r="O13" s="49"/>
-      <c r="P13" s="49"/>
-      <c r="Q13" s="49"/>
-      <c r="R13" s="49"/>
-      <c r="S13" s="49"/>
-      <c r="T13" s="49"/>
-      <c r="U13" s="49"/>
-      <c r="V13" s="49"/>
-      <c r="W13" s="49"/>
-      <c r="X13" s="49"/>
-      <c r="Y13" s="49"/>
-      <c r="Z13" s="49"/>
-      <c r="AA13" s="49"/>
-      <c r="AB13" s="49"/>
-      <c r="AC13" s="49"/>
-      <c r="AD13" s="49"/>
-      <c r="AE13" s="49"/>
-      <c r="AF13" s="49"/>
-      <c r="AG13" s="49"/>
-      <c r="AH13" s="49"/>
-      <c r="AI13" s="49"/>
-      <c r="AJ13" s="49"/>
-      <c r="AK13" s="49"/>
-      <c r="AL13" s="49"/>
-      <c r="AM13" s="49"/>
-      <c r="AN13" s="49"/>
-      <c r="AO13" s="49"/>
-      <c r="AP13" s="46"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="55"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="55"/>
+      <c r="J13" s="55"/>
+      <c r="K13" s="55"/>
+      <c r="L13" s="56"/>
+      <c r="M13" s="56"/>
+      <c r="N13" s="56"/>
+      <c r="O13" s="56"/>
+      <c r="P13" s="56"/>
+      <c r="Q13" s="56"/>
+      <c r="R13" s="56"/>
+      <c r="S13" s="56"/>
+      <c r="T13" s="56"/>
+      <c r="U13" s="56"/>
+      <c r="V13" s="56"/>
+      <c r="W13" s="56"/>
+      <c r="X13" s="56"/>
+      <c r="Y13" s="56"/>
+      <c r="Z13" s="56"/>
+      <c r="AA13" s="56"/>
+      <c r="AB13" s="56"/>
+      <c r="AC13" s="56"/>
+      <c r="AD13" s="56"/>
+      <c r="AE13" s="56"/>
+      <c r="AF13" s="56"/>
+      <c r="AG13" s="56"/>
+      <c r="AH13" s="56"/>
+      <c r="AI13" s="56"/>
+      <c r="AJ13" s="56"/>
+      <c r="AK13" s="56"/>
+      <c r="AL13" s="56"/>
+      <c r="AM13" s="56"/>
+      <c r="AN13" s="56"/>
+      <c r="AO13" s="56"/>
+      <c r="AP13" s="53"/>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" s="2">
@@ -7269,6 +7584,33 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="AO11:AO13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
+    <mergeCell ref="AN11:AN13"/>
+    <mergeCell ref="AE11:AE13"/>
+    <mergeCell ref="AF11:AF13"/>
+    <mergeCell ref="AG11:AG13"/>
+    <mergeCell ref="AH11:AH13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="Z11:Z13"/>
+    <mergeCell ref="AA11:AA13"/>
+    <mergeCell ref="AB11:AB13"/>
+    <mergeCell ref="AC11:AC13"/>
+    <mergeCell ref="AD11:AD13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="V11:V13"/>
+    <mergeCell ref="W11:W13"/>
+    <mergeCell ref="X11:X13"/>
+    <mergeCell ref="Y11:Y13"/>
+    <mergeCell ref="P11:P13"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="T11:T13"/>
     <mergeCell ref="A1:AP1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A11:A13"/>
@@ -7285,33 +7627,6 @@
     <mergeCell ref="M11:M13"/>
     <mergeCell ref="N11:N13"/>
     <mergeCell ref="O11:O13"/>
-    <mergeCell ref="P11:P13"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="T11:T13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="V11:V13"/>
-    <mergeCell ref="W11:W13"/>
-    <mergeCell ref="X11:X13"/>
-    <mergeCell ref="Y11:Y13"/>
-    <mergeCell ref="Z11:Z13"/>
-    <mergeCell ref="AA11:AA13"/>
-    <mergeCell ref="AB11:AB13"/>
-    <mergeCell ref="AC11:AC13"/>
-    <mergeCell ref="AD11:AD13"/>
-    <mergeCell ref="AE11:AE13"/>
-    <mergeCell ref="AF11:AF13"/>
-    <mergeCell ref="AG11:AG13"/>
-    <mergeCell ref="AH11:AH13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="AO11:AO13"/>
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="AN11:AN13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ТКИ-341_Реверс_Инжиниринг.xlsx
+++ b/ТКИ-341_Реверс_Инжиниринг.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\Reverse_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E15C7AF1-AE99-48D4-88A0-0DF631A5C61F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB70B41-6A4C-4453-890A-2239D436BE37}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="145">
   <si>
     <t>ВЕДОМОСТЬ ПОСЕЩАЕМОСТИ ЗАНЯТИЙ СТУДЕНТАМИ ГРУППЫ ТКИ "Компьютерная безопасность" ИТТСУ РУТ (МИИТ)</t>
   </si>
@@ -404,9 +404,6 @@
     <t>Рина (5)</t>
   </si>
   <si>
-    <t>генератор случайных чисел</t>
-  </si>
-  <si>
     <t>Кручинин, Дамир (12)</t>
   </si>
   <si>
@@ -431,9 +428,6 @@
     <t>Анализаторы CWE, включая Костенко</t>
   </si>
   <si>
-    <t>угадай число, генератор случайных чисел</t>
-  </si>
-  <si>
     <t>_1_2</t>
   </si>
   <si>
@@ -467,16 +461,43 @@
     <t>Town</t>
   </si>
   <si>
-    <t xml:space="preserve"> Безгодова и Пылаева (10)</t>
-  </si>
-  <si>
-    <t>сумму первых десяти членов арифметической прогрессии</t>
-  </si>
-  <si>
     <t>GitHub Analyzer</t>
   </si>
   <si>
     <t>сделали инструкцию</t>
+  </si>
+  <si>
+    <t>проверка пароля (ограниченное число попыток)</t>
+  </si>
+  <si>
+    <t>Архипов и Микутьев (5)</t>
+  </si>
+  <si>
+    <t>Tree-sitter</t>
+  </si>
+  <si>
+    <t>Нахождение пути минимальной стоимости (Бойков и Хоптий)</t>
+  </si>
+  <si>
+    <t>13 сумма элементов массива с нечетными значениями Иконников, Наседкин (13)</t>
+  </si>
+  <si>
+    <t>Decrypt, Encrypt Громов и Шабин</t>
+  </si>
+  <si>
+    <t>Вычисление таблицы значений функции (Левин, Ремигайло)</t>
+  </si>
+  <si>
+    <t>Угадай число</t>
+  </si>
+  <si>
+    <t>прогрессия</t>
+  </si>
+  <si>
+    <t>сумму первых десяти членов арифметической прогрессии  Безгодова и Пылаева (10)</t>
+  </si>
+  <si>
+    <t>потенциальная энергия пружины (Зверь)</t>
   </si>
 </sst>
 </file>
@@ -616,7 +637,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -738,7 +759,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -749,6 +769,19 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -762,11 +795,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1044,7 +1080,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BA63"/>
+  <dimension ref="A1:BB63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="37.28515625" customWidth="1"/>
@@ -1064,81 +1100,83 @@
     <col min="22" max="23" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="10.7109375" customWidth="1"/>
     <col min="25" max="26" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="10.5703125" style="32" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="9" style="32"/>
-    <col min="44" max="44" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="9" style="32"/>
-    <col min="47" max="47" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" customWidth="1"/>
+    <col min="29" max="29" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="10.5703125" style="32" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="9" style="32"/>
+    <col min="45" max="45" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="9" style="32"/>
+    <col min="48" max="48" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" ht="14.45" customHeight="1">
-      <c r="A1" s="53" t="s">
+    <row r="1" spans="1:54" ht="14.45" customHeight="1">
+      <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
-      <c r="S1" s="53"/>
-      <c r="T1" s="53"/>
-      <c r="U1" s="53"/>
-      <c r="V1" s="53"/>
-      <c r="W1" s="53"/>
-      <c r="X1" s="53"/>
-      <c r="Y1" s="53"/>
-      <c r="Z1" s="53"/>
-      <c r="AA1" s="53"/>
-      <c r="AB1" s="53"/>
-      <c r="AC1" s="53"/>
-      <c r="AD1" s="53"/>
-      <c r="AE1" s="53"/>
-      <c r="AF1" s="53"/>
-      <c r="AG1" s="53"/>
-      <c r="AH1" s="53"/>
-      <c r="AI1" s="53"/>
-      <c r="AJ1" s="53"/>
-      <c r="AK1" s="53"/>
-      <c r="AL1" s="53"/>
-      <c r="AM1" s="53"/>
-      <c r="AN1" s="53"/>
-      <c r="AO1" s="53"/>
-      <c r="AP1" s="53"/>
-      <c r="AQ1" s="53"/>
-      <c r="AR1" s="53"/>
-      <c r="AS1" s="53"/>
-      <c r="AT1" s="53"/>
-      <c r="AU1" s="53"/>
-      <c r="AV1" s="53"/>
-      <c r="AW1" s="53"/>
-      <c r="AX1" s="53"/>
-      <c r="AY1" s="53"/>
-      <c r="AZ1" s="53"/>
-      <c r="BA1" s="53"/>
-    </row>
-    <row r="2" spans="1:53" ht="27.6" customHeight="1">
-      <c r="A2" s="55" t="s">
+      <c r="B1" s="57"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="57"/>
+      <c r="N1" s="57"/>
+      <c r="O1" s="57"/>
+      <c r="P1" s="57"/>
+      <c r="Q1" s="57"/>
+      <c r="R1" s="57"/>
+      <c r="S1" s="57"/>
+      <c r="T1" s="57"/>
+      <c r="U1" s="57"/>
+      <c r="V1" s="57"/>
+      <c r="W1" s="57"/>
+      <c r="X1" s="57"/>
+      <c r="Y1" s="57"/>
+      <c r="Z1" s="57"/>
+      <c r="AA1" s="57"/>
+      <c r="AB1" s="57"/>
+      <c r="AC1" s="57"/>
+      <c r="AD1" s="57"/>
+      <c r="AE1" s="57"/>
+      <c r="AF1" s="57"/>
+      <c r="AG1" s="57"/>
+      <c r="AH1" s="57"/>
+      <c r="AI1" s="57"/>
+      <c r="AJ1" s="57"/>
+      <c r="AK1" s="57"/>
+      <c r="AL1" s="57"/>
+      <c r="AM1" s="57"/>
+      <c r="AN1" s="57"/>
+      <c r="AO1" s="57"/>
+      <c r="AP1" s="57"/>
+      <c r="AQ1" s="57"/>
+      <c r="AR1" s="57"/>
+      <c r="AS1" s="57"/>
+      <c r="AT1" s="57"/>
+      <c r="AU1" s="57"/>
+      <c r="AV1" s="57"/>
+      <c r="AW1" s="57"/>
+      <c r="AX1" s="57"/>
+      <c r="AY1" s="57"/>
+      <c r="AZ1" s="57"/>
+      <c r="BA1" s="57"/>
+      <c r="BB1" s="57"/>
+    </row>
+    <row r="2" spans="1:54" ht="27.6" customHeight="1">
+      <c r="A2" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="55"/>
+      <c r="B2" s="59"/>
       <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1211,56 +1249,59 @@
       <c r="Z2" s="14">
         <v>46170</v>
       </c>
-      <c r="AA2" s="3"/>
-      <c r="AB2" s="3" t="s">
+      <c r="AA2" s="14">
+        <v>46177</v>
+      </c>
+      <c r="AB2" s="3"/>
+      <c r="AC2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC2" s="3"/>
-      <c r="AD2" s="3" t="s">
+      <c r="AD2" s="3"/>
+      <c r="AE2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE2" s="3"/>
-      <c r="AF2" s="3" t="s">
+      <c r="AF2" s="3"/>
+      <c r="AG2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="AG2" s="3"/>
-      <c r="AH2" s="3" t="s">
+      <c r="AH2" s="3"/>
+      <c r="AI2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="AI2" s="3"/>
-      <c r="AJ2" s="30" t="s">
+      <c r="AJ2" s="3"/>
+      <c r="AK2" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="AK2" s="37" t="s">
+      <c r="AL2" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="AL2" s="3" t="s">
+      <c r="AM2" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="AM2" s="37"/>
       <c r="AN2" s="37"/>
-      <c r="AO2" s="30" t="s">
+      <c r="AO2" s="37"/>
+      <c r="AP2" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="AP2" s="3"/>
-      <c r="AR2" s="3"/>
-      <c r="AS2" s="30" t="s">
+      <c r="AQ2" s="3"/>
+      <c r="AS2" s="3"/>
+      <c r="AT2" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="AT2" s="3"/>
       <c r="AU2" s="3"/>
       <c r="AV2" s="3"/>
-      <c r="AW2" s="3" t="s">
+      <c r="AW2" s="3"/>
+      <c r="AX2" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="AX2" s="3"/>
       <c r="AY2" s="3"/>
       <c r="AZ2" s="3"/>
-      <c r="BA2" s="1" t="s">
+      <c r="BA2" s="3"/>
+      <c r="BB2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:53">
+    <row r="3" spans="1:54">
       <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
@@ -1300,26 +1341,27 @@
       <c r="AG3" s="19"/>
       <c r="AH3" s="19"/>
       <c r="AI3" s="19"/>
-      <c r="AJ3" s="30"/>
-      <c r="AK3" s="19"/>
+      <c r="AJ3" s="19"/>
+      <c r="AK3" s="30"/>
       <c r="AL3" s="19"/>
       <c r="AM3" s="19"/>
       <c r="AN3" s="19"/>
-      <c r="AO3" s="30"/>
-      <c r="AP3" s="19"/>
+      <c r="AO3" s="19"/>
+      <c r="AP3" s="30"/>
       <c r="AQ3" s="19"/>
       <c r="AR3" s="19"/>
-      <c r="AS3" s="30"/>
-      <c r="AT3" s="19"/>
+      <c r="AS3" s="19"/>
+      <c r="AT3" s="30"/>
       <c r="AU3" s="19"/>
       <c r="AV3" s="19"/>
       <c r="AW3" s="19"/>
       <c r="AX3" s="19"/>
       <c r="AY3" s="19"/>
       <c r="AZ3" s="19"/>
-      <c r="BA3" s="21"/>
-    </row>
-    <row r="4" spans="1:53" ht="105">
+      <c r="BA3" s="19"/>
+      <c r="BB3" s="21"/>
+    </row>
+    <row r="4" spans="1:54" ht="105">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -1396,59 +1438,62 @@
       <c r="Z4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA4" s="3"/>
-      <c r="AB4" s="17">
+      <c r="AA4" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="17">
         <v>46086</v>
       </c>
-      <c r="AC4" s="3"/>
-      <c r="AD4" s="24">
+      <c r="AD4" s="3"/>
+      <c r="AE4" s="24">
         <v>46149</v>
       </c>
-      <c r="AE4" s="3"/>
-      <c r="AF4" s="24">
+      <c r="AF4" s="3"/>
+      <c r="AG4" s="24">
         <v>46149</v>
       </c>
-      <c r="AG4" s="3"/>
-      <c r="AH4" s="24">
+      <c r="AH4" s="3"/>
+      <c r="AI4" s="24">
         <v>46149</v>
       </c>
-      <c r="AI4" s="3">
+      <c r="AJ4" s="3">
         <v>3</v>
       </c>
-      <c r="AJ4" s="30"/>
-      <c r="AK4" s="37"/>
-      <c r="AL4" s="50" t="s">
-        <v>129</v>
-      </c>
-      <c r="AM4" s="24">
+      <c r="AK4" s="30"/>
+      <c r="AL4" s="37"/>
+      <c r="AM4" s="49" t="s">
+        <v>127</v>
+      </c>
+      <c r="AN4" s="24">
         <v>46170</v>
       </c>
-      <c r="AN4" s="50" t="s">
-        <v>130</v>
-      </c>
-      <c r="AO4" s="42" t="s">
+      <c r="AO4" s="49" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP4" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="AP4" s="29" t="s">
+      <c r="AQ4" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="AQ4" s="28" t="s">
+      <c r="AR4" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="AR4" s="24">
+      <c r="AS4" s="24">
         <v>46170</v>
       </c>
-      <c r="AS4" s="30"/>
-      <c r="AT4" s="3"/>
+      <c r="AT4" s="30"/>
       <c r="AU4" s="3"/>
       <c r="AV4" s="3"/>
       <c r="AW4" s="3"/>
       <c r="AX4" s="3"/>
       <c r="AY4" s="3"/>
       <c r="AZ4" s="3"/>
-      <c r="BA4" s="1"/>
-    </row>
-    <row r="5" spans="1:53">
+      <c r="BA4" s="3"/>
+      <c r="BB4" s="1"/>
+    </row>
+    <row r="5" spans="1:54" ht="105">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1525,53 +1570,66 @@
       <c r="Z5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AA5" s="3"/>
-      <c r="AB5" s="11">
+      <c r="AA5" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB5" s="3"/>
+      <c r="AC5" s="11">
         <v>46100</v>
       </c>
-      <c r="AC5" s="3"/>
-      <c r="AD5" s="11">
+      <c r="AD5" s="3"/>
+      <c r="AE5" s="11">
         <v>46100</v>
       </c>
-      <c r="AE5" s="3"/>
-      <c r="AF5" s="24">
+      <c r="AF5" s="3"/>
+      <c r="AG5" s="24">
         <v>46114</v>
       </c>
-      <c r="AG5" s="3"/>
-      <c r="AH5" s="24">
+      <c r="AH5" s="3"/>
+      <c r="AI5" s="24">
         <v>46128</v>
       </c>
-      <c r="AI5" s="3">
+      <c r="AJ5" s="3">
         <v>5</v>
       </c>
-      <c r="AJ5" s="30"/>
-      <c r="AK5" s="37"/>
-      <c r="AL5" s="3">
-        <v>13</v>
-      </c>
-      <c r="AM5" s="37"/>
-      <c r="AN5" s="37"/>
-      <c r="AO5" s="42" t="s">
+      <c r="AK5" s="30"/>
+      <c r="AL5" s="37"/>
+      <c r="AM5" s="53" t="s">
+        <v>135</v>
+      </c>
+      <c r="AN5" s="24">
+        <v>46177</v>
+      </c>
+      <c r="AO5" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="AP5" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="AP5" s="28" t="s">
+      <c r="AQ5" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="AQ5" s="3"/>
-      <c r="AR5" s="24">
+      <c r="AR5" s="53"/>
+      <c r="AS5" s="24">
         <v>46135</v>
       </c>
-      <c r="AS5" s="30"/>
-      <c r="AT5" s="3"/>
-      <c r="AU5" s="3"/>
-      <c r="AV5" s="3"/>
-      <c r="AW5" s="3"/>
-      <c r="AX5" s="3"/>
+      <c r="AT5" s="30"/>
+      <c r="AU5" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="AV5" s="24">
+        <v>46177</v>
+      </c>
+      <c r="AW5" s="53"/>
+      <c r="AX5" s="24">
+        <v>46177</v>
+      </c>
       <c r="AY5" s="3"/>
       <c r="AZ5" s="3"/>
-      <c r="BA5" s="1"/>
-    </row>
-    <row r="6" spans="1:53" ht="105">
+      <c r="BA5" s="3"/>
+      <c r="BB5" s="1"/>
+    </row>
+    <row r="6" spans="1:54" ht="105">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1648,67 +1706,72 @@
       <c r="Z6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA6" s="3"/>
-      <c r="AB6" s="11">
+      <c r="AA6" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB6" s="3"/>
+      <c r="AC6" s="11">
         <v>46072</v>
       </c>
-      <c r="AC6" s="3"/>
-      <c r="AD6" s="24">
+      <c r="AD6" s="3"/>
+      <c r="AE6" s="24">
         <v>46121</v>
       </c>
-      <c r="AE6" s="3"/>
-      <c r="AF6" s="24">
+      <c r="AF6" s="3"/>
+      <c r="AG6" s="24">
         <v>46135</v>
       </c>
-      <c r="AG6" s="3"/>
-      <c r="AH6" s="24">
+      <c r="AH6" s="3"/>
+      <c r="AI6" s="24">
         <v>46135</v>
       </c>
-      <c r="AI6" s="3">
+      <c r="AJ6" s="3">
         <v>3</v>
       </c>
-      <c r="AJ6" s="30"/>
-      <c r="AK6" s="37"/>
-      <c r="AL6" s="3" t="s">
+      <c r="AK6" s="30"/>
+      <c r="AL6" s="48" t="s">
+        <v>141</v>
+      </c>
+      <c r="AM6" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="AM6" s="24">
+      <c r="AN6" s="24">
         <v>46149</v>
       </c>
-      <c r="AN6" s="37" t="s">
-        <v>122</v>
-      </c>
-      <c r="AO6" s="42" t="s">
+      <c r="AO6" s="49" t="s">
+        <v>142</v>
+      </c>
+      <c r="AP6" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="AP6" s="29" t="s">
+      <c r="AQ6" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="AQ6" s="28" t="s">
+      <c r="AR6" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="AR6" s="24">
+      <c r="AS6" s="24">
         <v>46170</v>
       </c>
-      <c r="AS6" s="58" t="s">
-        <v>128</v>
-      </c>
-      <c r="AT6" s="57" t="s">
-        <v>127</v>
-      </c>
-      <c r="AU6" s="24">
+      <c r="AT6" s="55" t="s">
+        <v>126</v>
+      </c>
+      <c r="AU6" s="54" t="s">
+        <v>125</v>
+      </c>
+      <c r="AV6" s="24">
         <v>46170</v>
       </c>
-      <c r="AV6" s="3"/>
-      <c r="AW6" s="24">
+      <c r="AW6" s="3"/>
+      <c r="AX6" s="24">
         <v>46170</v>
       </c>
-      <c r="AX6" s="3"/>
-      <c r="AY6" s="3"/>
+      <c r="AY6" s="62"/>
       <c r="AZ6" s="3"/>
-      <c r="BA6" s="1"/>
-    </row>
-    <row r="7" spans="1:53" ht="90">
+      <c r="BA6" s="3"/>
+      <c r="BB6" s="1"/>
+    </row>
+    <row r="7" spans="1:54" ht="90">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -1785,69 +1848,72 @@
       <c r="Z7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AA7" s="3"/>
-      <c r="AB7" s="22">
+      <c r="AA7" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB7" s="3"/>
+      <c r="AC7" s="22">
         <v>46100</v>
       </c>
-      <c r="AC7" s="3"/>
-      <c r="AD7" s="11">
+      <c r="AD7" s="3"/>
+      <c r="AE7" s="11">
         <v>46100</v>
       </c>
-      <c r="AE7" s="3"/>
-      <c r="AF7" s="24">
+      <c r="AF7" s="3"/>
+      <c r="AG7" s="24">
         <v>46100</v>
       </c>
-      <c r="AG7" s="3"/>
-      <c r="AH7" s="24">
+      <c r="AH7" s="3"/>
+      <c r="AI7" s="24">
         <v>46114</v>
       </c>
-      <c r="AI7" s="3">
+      <c r="AJ7" s="3">
         <v>5</v>
       </c>
-      <c r="AJ7" s="43">
+      <c r="AK7" s="43">
         <v>46135</v>
       </c>
-      <c r="AK7" s="34">
-        <v>12</v>
-      </c>
-      <c r="AL7" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="AM7" s="24">
+      <c r="AL7" s="64" t="s">
+        <v>139</v>
+      </c>
+      <c r="AM7" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="AN7" s="24">
         <v>46135</v>
       </c>
-      <c r="AN7" s="37" t="s">
+      <c r="AO7" s="37" t="s">
         <v>103</v>
       </c>
-      <c r="AO7" s="42" t="s">
+      <c r="AP7" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="AP7" s="29" t="s">
+      <c r="AQ7" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="AQ7" s="3"/>
-      <c r="AR7" s="24">
+      <c r="AR7" s="3"/>
+      <c r="AS7" s="24">
         <v>46135</v>
       </c>
-      <c r="AS7" s="30" t="s">
+      <c r="AT7" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="AT7" s="3" t="s">
+      <c r="AU7" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="AU7" s="24">
+      <c r="AV7" s="24">
         <v>46149</v>
       </c>
-      <c r="AV7" s="3"/>
-      <c r="AW7" s="24">
+      <c r="AW7" s="3"/>
+      <c r="AX7" s="24">
         <v>46149</v>
       </c>
-      <c r="AX7" s="3"/>
-      <c r="AY7" s="3"/>
+      <c r="AY7" s="62"/>
       <c r="AZ7" s="3"/>
-      <c r="BA7" s="1"/>
-    </row>
-    <row r="8" spans="1:53" ht="120">
+      <c r="BA7" s="3"/>
+      <c r="BB7" s="1"/>
+    </row>
+    <row r="8" spans="1:54" ht="120">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -1913,7 +1979,7 @@
         <v>17</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="X8" s="3" t="s">
         <v>16</v>
@@ -1922,52 +1988,55 @@
       <c r="Z8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AA8" s="3"/>
-      <c r="AB8" s="11">
+      <c r="AA8" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB8" s="3"/>
+      <c r="AC8" s="11">
         <v>46100</v>
       </c>
-      <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3"/>
-      <c r="AF8" s="24">
+      <c r="AF8" s="3"/>
+      <c r="AG8" s="24">
         <v>46135</v>
       </c>
-      <c r="AG8" s="3"/>
       <c r="AH8" s="3"/>
-      <c r="AI8" s="3">
+      <c r="AI8" s="3"/>
+      <c r="AJ8" s="3">
         <v>3</v>
       </c>
-      <c r="AJ8" s="30"/>
-      <c r="AK8" s="37" t="s">
-        <v>116</v>
-      </c>
-      <c r="AL8" s="3">
-        <v>17</v>
-      </c>
-      <c r="AM8" s="24">
+      <c r="AK8" s="30"/>
+      <c r="AL8" s="37" t="s">
+        <v>115</v>
+      </c>
+      <c r="AM8" s="3">
+        <v>17</v>
+      </c>
+      <c r="AN8" s="24">
         <v>46135</v>
       </c>
-      <c r="AO8" s="42" t="s">
+      <c r="AP8" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="AP8" s="29" t="s">
+      <c r="AQ8" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="AQ8" s="28" t="s">
+      <c r="AR8" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="AR8" s="3"/>
-      <c r="AS8" s="30"/>
-      <c r="AT8" s="3"/>
+      <c r="AS8" s="3"/>
+      <c r="AT8" s="30"/>
       <c r="AU8" s="3"/>
       <c r="AV8" s="3"/>
       <c r="AW8" s="3"/>
       <c r="AX8" s="3"/>
       <c r="AY8" s="3"/>
       <c r="AZ8" s="3"/>
-      <c r="BA8" s="1"/>
-    </row>
-    <row r="9" spans="1:53" ht="75">
+      <c r="BA8" s="3"/>
+      <c r="BB8" s="1"/>
+    </row>
+    <row r="9" spans="1:54" ht="75">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -2044,57 +2113,60 @@
       <c r="Z9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA9" s="3"/>
-      <c r="AB9" s="11">
+      <c r="AA9" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB9" s="3"/>
+      <c r="AC9" s="11">
         <v>46100</v>
       </c>
-      <c r="AC9" s="3"/>
-      <c r="AD9" s="24">
+      <c r="AD9" s="3"/>
+      <c r="AE9" s="24">
         <v>46135</v>
       </c>
-      <c r="AE9" s="3"/>
-      <c r="AF9" s="24">
+      <c r="AF9" s="3"/>
+      <c r="AG9" s="24">
         <v>46170</v>
       </c>
-      <c r="AG9" s="3"/>
-      <c r="AH9" s="24">
+      <c r="AH9" s="3"/>
+      <c r="AI9" s="24">
         <v>46170</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3</v>
       </c>
-      <c r="AJ9" s="30"/>
-      <c r="AK9" s="33"/>
-      <c r="AL9" s="40">
+      <c r="AK9" s="30"/>
+      <c r="AL9" s="33"/>
+      <c r="AM9" s="40">
         <v>14</v>
       </c>
-      <c r="AM9" s="24">
+      <c r="AN9" s="24">
         <v>46149</v>
       </c>
-      <c r="AN9" s="40" t="s">
+      <c r="AO9" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="AO9" s="42" t="s">
+      <c r="AP9" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="AP9" s="29" t="s">
+      <c r="AQ9" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="AQ9" s="3"/>
-      <c r="AR9" s="24">
+      <c r="AR9" s="3"/>
+      <c r="AS9" s="24">
         <v>46170</v>
       </c>
-      <c r="AS9" s="30"/>
-      <c r="AT9" s="3"/>
+      <c r="AT9" s="30"/>
       <c r="AU9" s="3"/>
       <c r="AV9" s="3"/>
       <c r="AW9" s="3"/>
       <c r="AX9" s="3"/>
       <c r="AY9" s="3"/>
       <c r="AZ9" s="3"/>
-      <c r="BA9" s="1"/>
-    </row>
-    <row r="10" spans="1:53" ht="105">
+      <c r="BA9" s="3"/>
+      <c r="BB9" s="1"/>
+    </row>
+    <row r="10" spans="1:54" ht="105">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -2171,59 +2243,62 @@
       <c r="Z10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA10" s="3"/>
-      <c r="AB10" s="11">
+      <c r="AA10" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB10" s="3"/>
+      <c r="AC10" s="11">
         <v>46079</v>
       </c>
-      <c r="AC10" s="3"/>
-      <c r="AD10" s="11">
+      <c r="AD10" s="3"/>
+      <c r="AE10" s="11">
         <v>46118</v>
       </c>
-      <c r="AE10" s="3"/>
-      <c r="AF10" s="24">
+      <c r="AF10" s="3"/>
+      <c r="AG10" s="24">
         <v>46121</v>
       </c>
-      <c r="AG10" s="3"/>
-      <c r="AH10" s="24">
+      <c r="AH10" s="3"/>
+      <c r="AI10" s="24">
         <v>46135</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>4</v>
       </c>
-      <c r="AJ10" s="30"/>
-      <c r="AK10" s="37"/>
-      <c r="AL10" s="3" t="s">
+      <c r="AK10" s="30"/>
+      <c r="AL10" s="37"/>
+      <c r="AM10" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="AM10" s="24">
+      <c r="AN10" s="24">
         <v>46149</v>
       </c>
-      <c r="AN10" s="37" t="s">
-        <v>120</v>
-      </c>
-      <c r="AO10" s="42" t="s">
+      <c r="AO10" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="AP10" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="AP10" s="29" t="s">
+      <c r="AQ10" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="AQ10" s="28" t="s">
+      <c r="AR10" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="AR10" s="24">
+      <c r="AS10" s="24">
         <v>46170</v>
       </c>
-      <c r="AS10" s="30"/>
-      <c r="AT10" s="3"/>
+      <c r="AT10" s="30"/>
       <c r="AU10" s="3"/>
       <c r="AV10" s="3"/>
       <c r="AW10" s="3"/>
       <c r="AX10" s="3"/>
       <c r="AY10" s="3"/>
       <c r="AZ10" s="3"/>
-      <c r="BA10" s="1"/>
-    </row>
-    <row r="11" spans="1:53" ht="89.25" customHeight="1">
+      <c r="BA10" s="3"/>
+      <c r="BB10" s="1"/>
+    </row>
+    <row r="11" spans="1:54" ht="89.25" customHeight="1">
       <c r="A11" s="2">
         <v>8</v>
       </c>
@@ -2298,65 +2373,68 @@
       <c r="Z11" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="AA11" s="5"/>
-      <c r="AB11" s="11">
+      <c r="AA11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB11" s="5"/>
+      <c r="AC11" s="11">
         <v>46079</v>
       </c>
-      <c r="AC11" s="5"/>
-      <c r="AD11" s="25">
+      <c r="AD11" s="5"/>
+      <c r="AE11" s="25">
         <v>46100</v>
       </c>
-      <c r="AE11" s="5"/>
-      <c r="AF11" s="11">
+      <c r="AF11" s="5"/>
+      <c r="AG11" s="11">
         <v>46107</v>
       </c>
-      <c r="AG11" s="5"/>
-      <c r="AH11" s="24">
+      <c r="AH11" s="5"/>
+      <c r="AI11" s="24">
         <v>46114</v>
       </c>
-      <c r="AI11" s="5">
+      <c r="AJ11" s="5">
         <v>5</v>
       </c>
-      <c r="AJ11" s="31"/>
-      <c r="AK11" s="5" t="s">
+      <c r="AK11" s="31"/>
+      <c r="AL11" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="AL11" s="5" t="s">
+      <c r="AM11" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="AM11" s="24">
+      <c r="AN11" s="24">
         <v>46149</v>
       </c>
-      <c r="AN11" s="5" t="s">
+      <c r="AO11" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="AO11" s="42" t="s">
+      <c r="AP11" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="AP11" s="29" t="s">
+      <c r="AQ11" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="AQ11" s="5"/>
-      <c r="AR11" s="24">
+      <c r="AR11" s="5"/>
+      <c r="AS11" s="24">
         <v>46128</v>
       </c>
-      <c r="AS11" s="31"/>
-      <c r="AT11" s="5" t="s">
+      <c r="AT11" s="31"/>
+      <c r="AU11" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="AU11" s="24">
+      <c r="AV11" s="24">
         <v>46149</v>
       </c>
-      <c r="AV11" s="5"/>
-      <c r="AW11" s="24">
+      <c r="AW11" s="5"/>
+      <c r="AX11" s="24">
         <v>46149</v>
       </c>
-      <c r="AX11" s="5"/>
-      <c r="AY11" s="5"/>
+      <c r="AY11" s="61"/>
       <c r="AZ11" s="5"/>
       <c r="BA11" s="5"/>
-    </row>
-    <row r="12" spans="1:53" ht="120">
+      <c r="BB11" s="5"/>
+    </row>
+    <row r="12" spans="1:54" ht="180">
       <c r="A12" s="2">
         <v>9</v>
       </c>
@@ -2433,71 +2511,74 @@
       <c r="Z12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="AA12" s="5"/>
-      <c r="AB12" s="11">
+      <c r="AA12" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB12" s="5"/>
+      <c r="AC12" s="11">
         <v>46072</v>
       </c>
-      <c r="AC12" s="5"/>
-      <c r="AD12" s="25">
+      <c r="AD12" s="5"/>
+      <c r="AE12" s="25">
         <v>46100</v>
       </c>
-      <c r="AE12" s="5"/>
-      <c r="AF12" s="24">
+      <c r="AF12" s="5"/>
+      <c r="AG12" s="24">
         <v>46107</v>
       </c>
-      <c r="AG12" s="5"/>
-      <c r="AH12" s="24">
+      <c r="AH12" s="5"/>
+      <c r="AI12" s="24">
         <v>46114</v>
       </c>
-      <c r="AI12" s="5">
+      <c r="AJ12" s="5">
         <v>5</v>
       </c>
-      <c r="AJ12" s="31"/>
-      <c r="AK12" s="5"/>
-      <c r="AL12" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="AM12" s="24">
+      <c r="AK12" s="31"/>
+      <c r="AL12" s="5"/>
+      <c r="AM12" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="AN12" s="24">
         <v>46170</v>
       </c>
-      <c r="AN12" s="49" t="s">
-        <v>135</v>
-      </c>
-      <c r="AO12" s="42" t="s">
+      <c r="AO12" s="49" t="s">
+        <v>144</v>
+      </c>
+      <c r="AP12" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="AP12" s="29" t="s">
+      <c r="AQ12" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="AQ12" s="28" t="s">
+      <c r="AR12" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="AR12" s="24">
+      <c r="AS12" s="24">
         <v>46135</v>
       </c>
-      <c r="AS12" s="59" t="s">
-        <v>137</v>
-      </c>
-      <c r="AT12" s="49" t="s">
-        <v>136</v>
-      </c>
-      <c r="AU12" s="24">
+      <c r="AT12" s="56" t="s">
+        <v>133</v>
+      </c>
+      <c r="AU12" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="AV12" s="24">
         <v>46170</v>
       </c>
-      <c r="AV12" s="5"/>
-      <c r="AW12" s="24">
+      <c r="AW12" s="5"/>
+      <c r="AX12" s="24">
         <v>46170</v>
       </c>
-      <c r="AX12" s="5"/>
       <c r="AY12" s="5"/>
       <c r="AZ12" s="5"/>
       <c r="BA12" s="5"/>
-    </row>
-    <row r="13" spans="1:53" ht="135">
+      <c r="BB12" s="5"/>
+    </row>
+    <row r="13" spans="1:54" ht="120">
       <c r="A13" s="2">
         <v>10</v>
       </c>
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="50" t="s">
         <v>33</v>
       </c>
       <c r="C13" s="9">
@@ -2572,67 +2653,70 @@
       <c r="Z13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="AA13" s="5"/>
-      <c r="AB13" s="11">
+      <c r="AA13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB13" s="5"/>
+      <c r="AC13" s="11">
         <v>46072</v>
       </c>
-      <c r="AC13" s="5"/>
-      <c r="AD13" s="17">
+      <c r="AD13" s="5"/>
+      <c r="AE13" s="17">
         <v>46093</v>
       </c>
-      <c r="AE13" s="5"/>
-      <c r="AF13" s="24">
+      <c r="AF13" s="5"/>
+      <c r="AG13" s="24">
         <v>46118</v>
       </c>
-      <c r="AG13" s="5"/>
-      <c r="AH13" s="24">
+      <c r="AH13" s="5"/>
+      <c r="AI13" s="24">
         <v>46118</v>
       </c>
-      <c r="AI13" s="5">
+      <c r="AJ13" s="5">
         <v>5</v>
       </c>
-      <c r="AJ13" s="43">
+      <c r="AK13" s="43">
         <v>46135</v>
       </c>
-      <c r="AK13" s="34">
+      <c r="AL13" s="34">
         <v>11</v>
       </c>
-      <c r="AL13" s="47" t="s">
-        <v>101</v>
-      </c>
-      <c r="AM13" s="24">
+      <c r="AM13" s="63" t="s">
+        <v>138</v>
+      </c>
+      <c r="AN13" s="24">
         <v>46149</v>
       </c>
-      <c r="AN13" s="49" t="s">
-        <v>102</v>
-      </c>
-      <c r="AO13" s="42" t="s">
+      <c r="AO13" s="48" t="s">
+        <v>141</v>
+      </c>
+      <c r="AP13" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="AP13" s="29" t="s">
+      <c r="AQ13" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="AQ13" s="28"/>
-      <c r="AR13" s="24">
+      <c r="AR13" s="28"/>
+      <c r="AS13" s="24">
         <v>46128</v>
       </c>
-      <c r="AS13" s="31"/>
-      <c r="AT13" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="AU13" s="24">
+      <c r="AT13" s="31"/>
+      <c r="AU13" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="AV13" s="24">
         <v>46156</v>
       </c>
-      <c r="AV13" s="5"/>
-      <c r="AW13" s="24">
+      <c r="AW13" s="5"/>
+      <c r="AX13" s="24">
         <v>46156</v>
       </c>
-      <c r="AX13" s="5"/>
-      <c r="AY13" s="5"/>
+      <c r="AY13" s="61"/>
       <c r="AZ13" s="5"/>
       <c r="BA13" s="5"/>
-    </row>
-    <row r="14" spans="1:53" ht="105">
+      <c r="BB13" s="5"/>
+    </row>
+    <row r="14" spans="1:54" ht="105">
       <c r="A14" s="2">
         <v>11</v>
       </c>
@@ -2707,45 +2791,48 @@
       <c r="Z14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AA14" s="3"/>
+      <c r="AA14" s="53" t="s">
+        <v>16</v>
+      </c>
       <c r="AB14" s="3"/>
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3"/>
       <c r="AF14" s="3"/>
       <c r="AG14" s="3"/>
-      <c r="AH14" s="39"/>
-      <c r="AI14" s="3">
+      <c r="AH14" s="3"/>
+      <c r="AI14" s="39"/>
+      <c r="AJ14" s="3">
         <v>2</v>
       </c>
-      <c r="AJ14" s="30"/>
-      <c r="AK14" s="37"/>
-      <c r="AL14" s="3">
+      <c r="AK14" s="30"/>
+      <c r="AL14" s="37"/>
+      <c r="AM14" s="3">
         <v>3</v>
       </c>
-      <c r="AM14" s="37"/>
       <c r="AN14" s="37"/>
-      <c r="AO14" s="42" t="s">
+      <c r="AO14" s="37"/>
+      <c r="AP14" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="AP14" s="29" t="s">
+      <c r="AQ14" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="AQ14" s="28" t="s">
+      <c r="AR14" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="AR14" s="3"/>
-      <c r="AS14" s="30"/>
-      <c r="AT14" s="3"/>
+      <c r="AS14" s="3"/>
+      <c r="AT14" s="30"/>
       <c r="AU14" s="3"/>
       <c r="AV14" s="3"/>
       <c r="AW14" s="3"/>
       <c r="AX14" s="3"/>
       <c r="AY14" s="3"/>
       <c r="AZ14" s="3"/>
-      <c r="BA14" s="1"/>
-    </row>
-    <row r="15" spans="1:53" ht="90">
+      <c r="BA14" s="3"/>
+      <c r="BB14" s="1"/>
+    </row>
+    <row r="15" spans="1:54" ht="90">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -2822,57 +2909,62 @@
       <c r="Z15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AA15" s="3"/>
-      <c r="AB15" s="11">
+      <c r="AA15" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB15" s="3"/>
+      <c r="AC15" s="11">
         <v>46079</v>
       </c>
-      <c r="AC15" s="3"/>
-      <c r="AD15" s="24">
+      <c r="AD15" s="3"/>
+      <c r="AE15" s="24">
         <v>46100</v>
       </c>
-      <c r="AE15" s="3"/>
-      <c r="AF15" s="11">
+      <c r="AF15" s="3"/>
+      <c r="AG15" s="11">
         <v>46107</v>
       </c>
-      <c r="AG15" s="3"/>
-      <c r="AH15" s="24">
+      <c r="AH15" s="3"/>
+      <c r="AI15" s="24">
         <v>46114</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>5</v>
       </c>
-      <c r="AJ15" s="30"/>
-      <c r="AK15" s="37"/>
-      <c r="AL15" s="5" t="s">
+      <c r="AK15" s="30"/>
+      <c r="AL15" s="37"/>
+      <c r="AM15" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="AM15" s="24">
+      <c r="AN15" s="24">
         <v>46149</v>
       </c>
-      <c r="AN15" s="5" t="s">
+      <c r="AO15" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="AO15" s="30"/>
-      <c r="AP15" s="3"/>
+      <c r="AP15" s="30"/>
       <c r="AQ15" s="3"/>
-      <c r="AR15" s="24">
+      <c r="AR15" s="3"/>
+      <c r="AS15" s="24">
         <v>46128</v>
       </c>
-      <c r="AS15" s="30"/>
-      <c r="AT15" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AU15" s="24">
+      <c r="AT15" s="30"/>
+      <c r="AU15" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AV15" s="24">
         <v>46149</v>
       </c>
-      <c r="AV15" s="3"/>
       <c r="AW15" s="3"/>
-      <c r="AX15" s="3"/>
-      <c r="AY15" s="3"/>
+      <c r="AX15" s="24">
+        <v>46149</v>
+      </c>
+      <c r="AY15" s="62"/>
       <c r="AZ15" s="3"/>
-      <c r="BA15" s="1"/>
-    </row>
-    <row r="16" spans="1:53" ht="330">
+      <c r="BA15" s="3"/>
+      <c r="BB15" s="1"/>
+    </row>
+    <row r="16" spans="1:54" ht="330">
       <c r="A16" s="2">
         <v>13</v>
       </c>
@@ -2947,65 +3039,70 @@
       <c r="Z16" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AA16" s="3"/>
-      <c r="AB16" s="11">
+      <c r="AA16" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="11">
         <v>46072</v>
       </c>
-      <c r="AC16" s="3"/>
-      <c r="AD16" s="24">
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="24">
         <v>46100</v>
       </c>
-      <c r="AE16" s="3"/>
-      <c r="AF16" s="24">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="24">
         <v>46104</v>
       </c>
-      <c r="AG16" s="3"/>
-      <c r="AH16" s="24">
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="24">
         <v>46107</v>
       </c>
-      <c r="AI16" s="3">
+      <c r="AJ16" s="3">
         <v>5</v>
       </c>
-      <c r="AJ16" s="43"/>
-      <c r="AK16" s="37"/>
-      <c r="AL16" s="38">
+      <c r="AK16" s="43"/>
+      <c r="AL16" s="49" t="s">
+        <v>137</v>
+      </c>
+      <c r="AM16" s="38">
         <v>7</v>
       </c>
-      <c r="AM16" s="24">
+      <c r="AN16" s="24">
         <v>46135</v>
       </c>
-      <c r="AN16" s="3" t="s">
+      <c r="AO16" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="AO16" s="42" t="s">
+      <c r="AP16" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="AP16" s="29" t="s">
+      <c r="AQ16" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="AQ16" s="3"/>
-      <c r="AR16" s="24">
+      <c r="AR16" s="3"/>
+      <c r="AS16" s="24">
         <v>46135</v>
       </c>
-      <c r="AS16" s="30" t="s">
+      <c r="AT16" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="AT16" s="33" t="s">
-        <v>119</v>
-      </c>
-      <c r="AU16" s="24">
+      <c r="AU16" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV16" s="24">
         <v>46149</v>
       </c>
-      <c r="AV16" s="41"/>
-      <c r="AW16" s="24">
+      <c r="AW16" s="41"/>
+      <c r="AX16" s="24">
         <v>46149</v>
       </c>
-      <c r="AX16" s="3"/>
-      <c r="AY16" s="3"/>
+      <c r="AY16" s="62"/>
       <c r="AZ16" s="3"/>
-      <c r="BA16" s="1"/>
-    </row>
-    <row r="17" spans="1:53" ht="240">
+      <c r="BA16" s="3"/>
+      <c r="BB16" s="1"/>
+    </row>
+    <row r="17" spans="1:54" ht="240">
       <c r="A17" s="2">
         <v>14</v>
       </c>
@@ -3082,67 +3179,70 @@
       <c r="Z17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AA17" s="3"/>
-      <c r="AB17" s="11">
+      <c r="AA17" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB17" s="3"/>
+      <c r="AC17" s="11">
         <v>46072</v>
       </c>
-      <c r="AC17" s="3"/>
-      <c r="AD17" s="11">
+      <c r="AD17" s="3"/>
+      <c r="AE17" s="11">
         <v>46100</v>
       </c>
-      <c r="AE17" s="3"/>
-      <c r="AF17" s="24">
+      <c r="AF17" s="3"/>
+      <c r="AG17" s="24">
         <v>46114</v>
       </c>
-      <c r="AG17" s="3"/>
-      <c r="AH17" s="24">
+      <c r="AH17" s="3"/>
+      <c r="AI17" s="24">
         <v>46128</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5</v>
       </c>
-      <c r="AJ17" s="30"/>
-      <c r="AK17" s="50" t="s">
-        <v>126</v>
-      </c>
-      <c r="AL17" s="44">
+      <c r="AK17" s="30"/>
+      <c r="AL17" s="49" t="s">
+        <v>124</v>
+      </c>
+      <c r="AM17" s="44">
         <v>1</v>
       </c>
-      <c r="AM17" s="24">
+      <c r="AN17" s="24">
         <v>46135</v>
       </c>
-      <c r="AN17" s="49" t="s">
+      <c r="AO17" s="48" t="s">
         <v>102</v>
       </c>
-      <c r="AO17" s="42" t="s">
+      <c r="AP17" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="AP17" s="29" t="s">
+      <c r="AQ17" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="AQ17" s="28" t="s">
+      <c r="AR17" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="AR17" s="24">
+      <c r="AS17" s="24">
         <v>46135</v>
       </c>
-      <c r="AS17" s="30"/>
-      <c r="AT17" s="48" t="s">
-        <v>125</v>
-      </c>
-      <c r="AU17" s="24">
+      <c r="AT17" s="30"/>
+      <c r="AU17" s="47" t="s">
+        <v>123</v>
+      </c>
+      <c r="AV17" s="24">
         <v>46149</v>
       </c>
-      <c r="AV17" s="3"/>
-      <c r="AW17" s="24">
+      <c r="AW17" s="3"/>
+      <c r="AX17" s="24">
         <v>46149</v>
       </c>
-      <c r="AX17" s="3"/>
       <c r="AY17" s="3"/>
       <c r="AZ17" s="3"/>
-      <c r="BA17" s="1"/>
-    </row>
-    <row r="18" spans="1:53" ht="90">
+      <c r="BA17" s="3"/>
+      <c r="BB17" s="1"/>
+    </row>
+    <row r="18" spans="1:54" ht="90">
       <c r="A18" s="2">
         <v>15</v>
       </c>
@@ -3219,57 +3319,62 @@
       <c r="Z18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA18" s="3"/>
-      <c r="AB18" s="22">
+      <c r="AA18" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB18" s="3"/>
+      <c r="AC18" s="22">
         <v>46100</v>
       </c>
-      <c r="AC18" s="3"/>
-      <c r="AD18" s="11">
+      <c r="AD18" s="3"/>
+      <c r="AE18" s="11">
         <v>46100</v>
       </c>
-      <c r="AE18" s="3"/>
-      <c r="AF18" s="24">
+      <c r="AF18" s="3"/>
+      <c r="AG18" s="24">
         <v>46100</v>
       </c>
-      <c r="AG18" s="3"/>
-      <c r="AH18" s="24">
+      <c r="AH18" s="3"/>
+      <c r="AI18" s="24">
         <v>46114</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>5</v>
       </c>
-      <c r="AJ18" s="43"/>
-      <c r="AK18" s="34">
+      <c r="AK18" s="43"/>
+      <c r="AL18" s="64" t="s">
+        <v>139</v>
+      </c>
+      <c r="AM18" s="5">
         <v>12</v>
       </c>
-      <c r="AL18" s="5"/>
-      <c r="AM18" s="24">
+      <c r="AN18" s="24">
         <v>46135</v>
       </c>
-      <c r="AN18" s="40" t="s">
+      <c r="AO18" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="AO18" s="30"/>
-      <c r="AP18" s="3"/>
+      <c r="AP18" s="30"/>
       <c r="AQ18" s="3"/>
-      <c r="AR18" s="24">
+      <c r="AR18" s="3"/>
+      <c r="AS18" s="24">
         <v>46135</v>
       </c>
-      <c r="AS18" s="30"/>
-      <c r="AT18" s="3"/>
-      <c r="AU18" s="24">
+      <c r="AT18" s="30"/>
+      <c r="AU18" s="3"/>
+      <c r="AV18" s="24">
         <v>46149</v>
       </c>
-      <c r="AV18" s="3"/>
-      <c r="AW18" s="24">
+      <c r="AW18" s="3"/>
+      <c r="AX18" s="24">
         <v>46149</v>
       </c>
-      <c r="AX18" s="3"/>
-      <c r="AY18" s="3"/>
+      <c r="AY18" s="62"/>
       <c r="AZ18" s="3"/>
-      <c r="BA18" s="1"/>
-    </row>
-    <row r="19" spans="1:53" ht="75">
+      <c r="BA18" s="3"/>
+      <c r="BB18" s="1"/>
+    </row>
+    <row r="19" spans="1:54" ht="75">
       <c r="A19" s="2">
         <v>16</v>
       </c>
@@ -3344,57 +3449,60 @@
       <c r="Z19" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA19" s="3"/>
-      <c r="AB19" s="11">
+      <c r="AA19" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="11">
         <v>46100</v>
       </c>
-      <c r="AC19" s="3"/>
-      <c r="AD19" s="24">
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="24">
         <v>46135</v>
       </c>
-      <c r="AE19" s="3"/>
-      <c r="AF19" s="24">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="24">
         <v>46170</v>
       </c>
-      <c r="AG19" s="3"/>
-      <c r="AH19" s="24">
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="24">
         <v>46170</v>
       </c>
-      <c r="AI19" s="3">
+      <c r="AJ19" s="3">
         <v>3</v>
       </c>
-      <c r="AJ19" s="30"/>
-      <c r="AK19" s="37"/>
-      <c r="AL19" s="40">
+      <c r="AK19" s="30"/>
+      <c r="AL19" s="37"/>
+      <c r="AM19" s="40">
         <v>14</v>
       </c>
-      <c r="AM19" s="24">
+      <c r="AN19" s="24">
         <v>46149</v>
       </c>
-      <c r="AN19" s="40" t="s">
+      <c r="AO19" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="AO19" s="42" t="s">
+      <c r="AP19" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="AP19" s="29" t="s">
+      <c r="AQ19" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="AQ19" s="46"/>
-      <c r="AR19" s="24">
+      <c r="AR19" s="46"/>
+      <c r="AS19" s="24">
         <v>46170</v>
       </c>
-      <c r="AS19" s="30"/>
-      <c r="AT19" s="3"/>
+      <c r="AT19" s="30"/>
       <c r="AU19" s="3"/>
       <c r="AV19" s="3"/>
       <c r="AW19" s="3"/>
       <c r="AX19" s="3"/>
       <c r="AY19" s="3"/>
       <c r="AZ19" s="3"/>
-      <c r="BA19" s="1"/>
-    </row>
-    <row r="20" spans="1:53" ht="135">
+      <c r="BA19" s="3"/>
+      <c r="BB19" s="1"/>
+    </row>
+    <row r="20" spans="1:54" ht="135">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -3471,47 +3579,50 @@
       <c r="Z20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA20" s="3"/>
-      <c r="AB20" s="24">
+      <c r="AA20" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB20" s="3"/>
+      <c r="AC20" s="24">
         <v>46118</v>
       </c>
-      <c r="AC20" s="3"/>
       <c r="AD20" s="3"/>
       <c r="AE20" s="3"/>
       <c r="AF20" s="3"/>
       <c r="AG20" s="3"/>
       <c r="AH20" s="3"/>
-      <c r="AI20" s="3">
+      <c r="AI20" s="3"/>
+      <c r="AJ20" s="3">
         <v>2</v>
       </c>
-      <c r="AJ20" s="30"/>
-      <c r="AK20" s="37" t="s">
+      <c r="AK20" s="30"/>
+      <c r="AL20" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>6</v>
       </c>
-      <c r="AM20" s="37"/>
       <c r="AN20" s="37"/>
-      <c r="AO20" s="57" t="s">
-        <v>132</v>
-      </c>
-      <c r="AP20" s="3"/>
+      <c r="AO20" s="37"/>
+      <c r="AP20" s="54" t="s">
+        <v>130</v>
+      </c>
       <c r="AQ20" s="3"/>
-      <c r="AR20" s="24">
+      <c r="AR20" s="3"/>
+      <c r="AS20" s="24">
         <v>46170</v>
       </c>
-      <c r="AS20" s="30"/>
-      <c r="AT20" s="3"/>
+      <c r="AT20" s="30"/>
       <c r="AU20" s="3"/>
       <c r="AV20" s="3"/>
       <c r="AW20" s="3"/>
       <c r="AX20" s="3"/>
       <c r="AY20" s="3"/>
       <c r="AZ20" s="3"/>
-      <c r="BA20" s="1"/>
-    </row>
-    <row r="21" spans="1:53" ht="90">
+      <c r="BA20" s="3"/>
+      <c r="BB20" s="1"/>
+    </row>
+    <row r="21" spans="1:54" ht="90">
       <c r="A21" s="2">
         <v>18</v>
       </c>
@@ -3588,47 +3699,50 @@
       <c r="Z21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA21" s="3"/>
-      <c r="AB21" s="11">
+      <c r="AA21" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB21" s="3"/>
+      <c r="AC21" s="11">
         <v>46100</v>
       </c>
-      <c r="AC21" s="3"/>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3"/>
-      <c r="AF21" s="24">
+      <c r="AF21" s="3"/>
+      <c r="AG21" s="24">
         <v>46135</v>
       </c>
-      <c r="AG21" s="3"/>
-      <c r="AH21" s="24">
+      <c r="AH21" s="3"/>
+      <c r="AI21" s="24">
         <v>46170</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>3</v>
       </c>
-      <c r="AJ21" s="30"/>
-      <c r="AK21" s="37"/>
-      <c r="AL21" s="3"/>
-      <c r="AM21" s="24">
+      <c r="AK21" s="30"/>
+      <c r="AL21" s="37"/>
+      <c r="AM21" s="3"/>
+      <c r="AN21" s="24">
         <v>46135</v>
       </c>
-      <c r="AN21" s="37" t="s">
+      <c r="AO21" s="37" t="s">
         <v>103</v>
       </c>
-      <c r="AO21" s="30"/>
-      <c r="AP21" s="3"/>
+      <c r="AP21" s="30"/>
       <c r="AQ21" s="3"/>
       <c r="AR21" s="3"/>
-      <c r="AS21" s="30"/>
-      <c r="AT21" s="3"/>
+      <c r="AS21" s="3"/>
+      <c r="AT21" s="30"/>
       <c r="AU21" s="3"/>
       <c r="AV21" s="3"/>
       <c r="AW21" s="3"/>
       <c r="AX21" s="3"/>
       <c r="AY21" s="3"/>
       <c r="AZ21" s="3"/>
-      <c r="BA21" s="1"/>
-    </row>
-    <row r="22" spans="1:53" ht="90">
+      <c r="BA21" s="3"/>
+      <c r="BB21" s="1"/>
+    </row>
+    <row r="22" spans="1:54" ht="120">
       <c r="A22" s="2">
         <v>19</v>
       </c>
@@ -3703,63 +3817,68 @@
       <c r="Z22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AA22" s="3"/>
-      <c r="AB22" s="11">
+      <c r="AA22" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB22" s="3"/>
+      <c r="AC22" s="11">
         <v>46072</v>
       </c>
-      <c r="AC22" s="3"/>
-      <c r="AD22" s="11">
+      <c r="AD22" s="3"/>
+      <c r="AE22" s="11">
         <v>46100</v>
       </c>
-      <c r="AE22" s="3"/>
-      <c r="AF22" s="24">
+      <c r="AF22" s="3"/>
+      <c r="AG22" s="24">
         <v>46107</v>
       </c>
-      <c r="AG22" s="3"/>
-      <c r="AH22" s="24">
+      <c r="AH22" s="3"/>
+      <c r="AI22" s="24">
         <v>46114</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>5</v>
       </c>
-      <c r="AJ22" s="30"/>
-      <c r="AK22" s="37"/>
-      <c r="AL22" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM22" s="24">
+      <c r="AK22" s="30"/>
+      <c r="AL22" s="49" t="s">
+        <v>140</v>
+      </c>
+      <c r="AM22" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="AN22" s="24">
         <v>46135</v>
       </c>
-      <c r="AN22" s="40" t="s">
-        <v>115</v>
-      </c>
-      <c r="AO22" s="42" t="s">
+      <c r="AO22" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="AP22" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="AP22" s="29" t="s">
+      <c r="AQ22" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="AQ22" s="3"/>
-      <c r="AR22" s="24">
+      <c r="AR22" s="3"/>
+      <c r="AS22" s="24">
         <v>46128</v>
       </c>
-      <c r="AS22" s="30"/>
-      <c r="AT22" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="AU22" s="24">
+      <c r="AT22" s="30"/>
+      <c r="AU22" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="AV22" s="24">
         <v>46149</v>
       </c>
-      <c r="AV22" s="3"/>
-      <c r="AW22" s="24">
+      <c r="AW22" s="3"/>
+      <c r="AX22" s="24">
         <v>46156</v>
       </c>
-      <c r="AX22" s="3"/>
-      <c r="AY22" s="3"/>
+      <c r="AY22" s="62"/>
       <c r="AZ22" s="3"/>
-      <c r="BA22" s="1"/>
-    </row>
-    <row r="23" spans="1:53" ht="90">
+      <c r="BA22" s="3"/>
+      <c r="BB22" s="1"/>
+    </row>
+    <row r="23" spans="1:54" ht="120">
       <c r="A23" s="2">
         <v>20</v>
       </c>
@@ -3836,59 +3955,64 @@
       <c r="Z23" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA23" s="3"/>
-      <c r="AB23" s="11">
+      <c r="AA23" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB23" s="3"/>
+      <c r="AC23" s="11">
         <v>46072</v>
       </c>
-      <c r="AC23" s="3"/>
-      <c r="AD23" s="11">
+      <c r="AD23" s="3"/>
+      <c r="AE23" s="11">
         <v>46100</v>
       </c>
-      <c r="AE23" s="3"/>
-      <c r="AF23" s="24">
+      <c r="AF23" s="3"/>
+      <c r="AG23" s="24">
         <v>46107</v>
       </c>
-      <c r="AG23" s="3"/>
-      <c r="AH23" s="24">
+      <c r="AH23" s="3"/>
+      <c r="AI23" s="24">
         <v>46114</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>5</v>
       </c>
-      <c r="AJ23" s="30"/>
-      <c r="AK23" s="37"/>
-      <c r="AL23" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM23" s="24">
+      <c r="AK23" s="30"/>
+      <c r="AL23" s="49" t="s">
+        <v>140</v>
+      </c>
+      <c r="AM23" s="40" t="s">
+        <v>116</v>
+      </c>
+      <c r="AN23" s="24">
         <v>46135</v>
       </c>
-      <c r="AN23" s="37" t="s">
-        <v>115</v>
-      </c>
-      <c r="AO23" s="30"/>
-      <c r="AP23" s="3"/>
+      <c r="AO23" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="AP23" s="30"/>
       <c r="AQ23" s="3"/>
-      <c r="AR23" s="24">
+      <c r="AR23" s="3"/>
+      <c r="AS23" s="24">
         <v>46128</v>
       </c>
-      <c r="AS23" s="30"/>
-      <c r="AT23" s="41" t="s">
-        <v>121</v>
-      </c>
-      <c r="AU23" s="24">
+      <c r="AT23" s="30"/>
+      <c r="AU23" s="41" t="s">
+        <v>120</v>
+      </c>
+      <c r="AV23" s="24">
         <v>46149</v>
       </c>
-      <c r="AV23" s="3"/>
-      <c r="AW23" s="24">
+      <c r="AW23" s="3"/>
+      <c r="AX23" s="24">
         <v>46156</v>
       </c>
-      <c r="AX23" s="3"/>
-      <c r="AY23" s="3"/>
+      <c r="AY23" s="62"/>
       <c r="AZ23" s="3"/>
-      <c r="BA23" s="1"/>
-    </row>
-    <row r="24" spans="1:53" ht="120">
+      <c r="BA23" s="3"/>
+      <c r="BB23" s="1"/>
+    </row>
+    <row r="24" spans="1:54" ht="120">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -3965,51 +4089,54 @@
       <c r="Z24" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA24" s="3"/>
-      <c r="AB24" s="24">
+      <c r="AA24" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB24" s="3"/>
+      <c r="AC24" s="24">
         <v>46170</v>
       </c>
-      <c r="AC24" s="3"/>
-      <c r="AD24" s="24">
+      <c r="AD24" s="3"/>
+      <c r="AE24" s="24">
         <v>46170</v>
       </c>
-      <c r="AE24" s="3"/>
       <c r="AF24" s="3"/>
       <c r="AG24" s="3"/>
       <c r="AH24" s="3"/>
-      <c r="AI24" s="3">
+      <c r="AI24" s="3"/>
+      <c r="AJ24" s="3">
         <v>2</v>
       </c>
-      <c r="AJ24" s="30"/>
-      <c r="AK24" s="50" t="s">
+      <c r="AK24" s="30"/>
+      <c r="AL24" s="49" t="s">
+        <v>129</v>
+      </c>
+      <c r="AM24" s="3">
+        <v>2</v>
+      </c>
+      <c r="AN24" s="37"/>
+      <c r="AO24" s="37"/>
+      <c r="AP24" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="AQ24" s="49" t="s">
         <v>131</v>
       </c>
-      <c r="AL24" s="3">
-        <v>2</v>
-      </c>
-      <c r="AM24" s="37"/>
-      <c r="AN24" s="37"/>
-      <c r="AO24" s="42" t="s">
-        <v>72</v>
-      </c>
-      <c r="AP24" s="50" t="s">
-        <v>133</v>
-      </c>
-      <c r="AQ24" s="3"/>
-      <c r="AR24" s="24">
+      <c r="AR24" s="3"/>
+      <c r="AS24" s="24">
         <v>46170</v>
       </c>
-      <c r="AS24" s="30"/>
-      <c r="AT24" s="3"/>
+      <c r="AT24" s="30"/>
       <c r="AU24" s="3"/>
       <c r="AV24" s="3"/>
       <c r="AW24" s="3"/>
       <c r="AX24" s="3"/>
       <c r="AY24" s="3"/>
       <c r="AZ24" s="3"/>
-      <c r="BA24" s="1"/>
-    </row>
-    <row r="25" spans="1:53" ht="120">
+      <c r="BA24" s="3"/>
+      <c r="BB24" s="1"/>
+    </row>
+    <row r="25" spans="1:54" ht="180">
       <c r="A25" s="2">
         <v>22</v>
       </c>
@@ -4084,61 +4211,64 @@
       <c r="Z25" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AA25" s="3"/>
-      <c r="AB25" s="11">
+      <c r="AA25" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB25" s="3"/>
+      <c r="AC25" s="11">
         <v>46072</v>
       </c>
-      <c r="AC25" s="3"/>
-      <c r="AD25" s="24">
+      <c r="AD25" s="3"/>
+      <c r="AE25" s="24">
         <v>46100</v>
       </c>
-      <c r="AE25" s="3"/>
-      <c r="AF25" s="24">
+      <c r="AF25" s="3"/>
+      <c r="AG25" s="24">
         <v>46107</v>
       </c>
-      <c r="AG25" s="3"/>
-      <c r="AH25" s="24">
+      <c r="AH25" s="3"/>
+      <c r="AI25" s="24">
         <v>46114</v>
       </c>
-      <c r="AI25" s="3">
+      <c r="AJ25" s="3">
         <v>5</v>
       </c>
-      <c r="AJ25" s="30"/>
-      <c r="AK25" s="37"/>
-      <c r="AL25" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="AM25" s="24">
+      <c r="AK25" s="30"/>
+      <c r="AL25" s="37"/>
+      <c r="AM25" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="AN25" s="24">
         <v>46170</v>
       </c>
-      <c r="AN25" s="49" t="s">
-        <v>135</v>
-      </c>
-      <c r="AO25" s="30"/>
-      <c r="AP25" s="3"/>
+      <c r="AO25" s="49" t="s">
+        <v>144</v>
+      </c>
+      <c r="AP25" s="30"/>
       <c r="AQ25" s="3"/>
-      <c r="AR25" s="24">
+      <c r="AR25" s="3"/>
+      <c r="AS25" s="24">
         <v>46135</v>
       </c>
-      <c r="AS25" s="59" t="s">
-        <v>137</v>
-      </c>
-      <c r="AT25" s="49" t="s">
-        <v>136</v>
-      </c>
-      <c r="AU25" s="24">
+      <c r="AT25" s="56" t="s">
+        <v>133</v>
+      </c>
+      <c r="AU25" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="AV25" s="24">
         <v>46170</v>
       </c>
-      <c r="AV25" s="5"/>
-      <c r="AW25" s="24">
+      <c r="AW25" s="5"/>
+      <c r="AX25" s="24">
         <v>46170</v>
       </c>
-      <c r="AX25" s="3"/>
-      <c r="AY25" s="3"/>
+      <c r="AY25" s="62"/>
       <c r="AZ25" s="3"/>
-      <c r="BA25" s="1"/>
-    </row>
-    <row r="26" spans="1:53">
+      <c r="BA25" s="3"/>
+      <c r="BB25" s="1"/>
+    </row>
+    <row r="26" spans="1:54">
       <c r="A26" s="2">
         <v>23</v>
       </c>
@@ -4213,7 +4343,9 @@
       <c r="Z26" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA26" s="3"/>
+      <c r="AA26" s="53" t="s">
+        <v>16</v>
+      </c>
       <c r="AB26" s="3"/>
       <c r="AC26" s="3"/>
       <c r="AD26" s="3"/>
@@ -4221,29 +4353,30 @@
       <c r="AF26" s="3"/>
       <c r="AG26" s="3"/>
       <c r="AH26" s="3"/>
-      <c r="AI26" s="3">
+      <c r="AI26" s="3"/>
+      <c r="AJ26" s="3">
         <v>0</v>
       </c>
-      <c r="AJ26" s="30"/>
-      <c r="AK26" s="37"/>
-      <c r="AL26" s="3"/>
-      <c r="AM26" s="37"/>
+      <c r="AK26" s="30"/>
+      <c r="AL26" s="37"/>
+      <c r="AM26" s="3"/>
       <c r="AN26" s="37"/>
-      <c r="AO26" s="30"/>
-      <c r="AP26" s="3"/>
+      <c r="AO26" s="37"/>
+      <c r="AP26" s="30"/>
       <c r="AQ26" s="3"/>
       <c r="AR26" s="3"/>
-      <c r="AS26" s="30"/>
-      <c r="AT26" s="3"/>
+      <c r="AS26" s="3"/>
+      <c r="AT26" s="30"/>
       <c r="AU26" s="3"/>
       <c r="AV26" s="3"/>
       <c r="AW26" s="3"/>
       <c r="AX26" s="3"/>
       <c r="AY26" s="3"/>
       <c r="AZ26" s="3"/>
-      <c r="BA26" s="1"/>
-    </row>
-    <row r="27" spans="1:53">
+      <c r="BA26" s="3"/>
+      <c r="BB26" s="1"/>
+    </row>
+    <row r="27" spans="1:54" ht="105">
       <c r="A27" s="2">
         <v>24</v>
       </c>
@@ -4320,47 +4453,64 @@
       <c r="Z27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA27" s="3"/>
-      <c r="AB27" s="11">
+      <c r="AA27" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB27" s="3"/>
+      <c r="AC27" s="11">
         <v>46100</v>
       </c>
-      <c r="AC27" s="3"/>
-      <c r="AD27" s="11">
+      <c r="AD27" s="3"/>
+      <c r="AE27" s="11">
         <v>46100</v>
       </c>
-      <c r="AE27" s="3"/>
-      <c r="AF27" s="24">
+      <c r="AF27" s="3"/>
+      <c r="AG27" s="24">
         <v>46114</v>
       </c>
-      <c r="AG27" s="3"/>
-      <c r="AH27" s="24">
+      <c r="AH27" s="3"/>
+      <c r="AI27" s="24">
         <v>46128</v>
       </c>
-      <c r="AI27" s="3">
-        <v>5</v>
-      </c>
-      <c r="AJ27" s="30"/>
-      <c r="AK27" s="37"/>
-      <c r="AL27" s="3"/>
-      <c r="AM27" s="37"/>
-      <c r="AN27" s="37"/>
-      <c r="AO27" s="30"/>
-      <c r="AP27" s="3"/>
-      <c r="AQ27" s="3"/>
-      <c r="AR27" s="24">
+      <c r="AJ27" s="3"/>
+      <c r="AK27" s="30"/>
+      <c r="AL27" s="37"/>
+      <c r="AM27" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="AN27" s="24">
+        <v>46177</v>
+      </c>
+      <c r="AO27" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="AP27" s="42" t="s">
+        <v>75</v>
+      </c>
+      <c r="AQ27" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="AR27" s="53"/>
+      <c r="AS27" s="24">
         <v>46135</v>
       </c>
-      <c r="AS27" s="30"/>
-      <c r="AT27" s="3"/>
-      <c r="AU27" s="3"/>
-      <c r="AV27" s="3"/>
+      <c r="AT27" s="30"/>
+      <c r="AU27" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="AV27" s="24">
+        <v>46177</v>
+      </c>
       <c r="AW27" s="3"/>
-      <c r="AX27" s="3"/>
+      <c r="AX27" s="24">
+        <v>46177</v>
+      </c>
       <c r="AY27" s="3"/>
       <c r="AZ27" s="3"/>
-      <c r="BA27" s="1"/>
-    </row>
-    <row r="28" spans="1:53" ht="105">
+      <c r="BA27" s="3"/>
+      <c r="BB27" s="1"/>
+    </row>
+    <row r="28" spans="1:54" ht="105">
       <c r="A28" s="2">
         <v>25</v>
       </c>
@@ -4437,59 +4587,62 @@
       <c r="Z28" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA28" s="3"/>
-      <c r="AB28" s="17">
+      <c r="AA28" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB28" s="3"/>
+      <c r="AC28" s="17">
         <v>46086</v>
       </c>
-      <c r="AC28" s="3"/>
-      <c r="AD28" s="24">
+      <c r="AD28" s="3"/>
+      <c r="AE28" s="24">
         <v>46149</v>
       </c>
-      <c r="AE28" s="3"/>
-      <c r="AF28" s="24">
+      <c r="AF28" s="3"/>
+      <c r="AG28" s="24">
         <v>46149</v>
       </c>
-      <c r="AG28" s="3"/>
-      <c r="AH28" s="24">
+      <c r="AH28" s="3"/>
+      <c r="AI28" s="24">
         <v>46149</v>
       </c>
-      <c r="AI28" s="3">
+      <c r="AJ28" s="3">
         <v>3</v>
       </c>
-      <c r="AJ28" s="30"/>
-      <c r="AK28" s="37"/>
-      <c r="AL28" s="50" t="s">
-        <v>129</v>
-      </c>
-      <c r="AM28" s="24">
+      <c r="AK28" s="30"/>
+      <c r="AL28" s="37"/>
+      <c r="AM28" s="49" t="s">
+        <v>127</v>
+      </c>
+      <c r="AN28" s="24">
         <v>46170</v>
       </c>
-      <c r="AN28" s="50" t="s">
-        <v>130</v>
-      </c>
-      <c r="AO28" s="42" t="s">
+      <c r="AO28" s="49" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP28" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="AP28" s="29" t="s">
+      <c r="AQ28" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="AQ28" s="28" t="s">
+      <c r="AR28" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="AR28" s="24">
+      <c r="AS28" s="24">
         <v>46170</v>
       </c>
-      <c r="AS28" s="30"/>
-      <c r="AT28" s="3"/>
+      <c r="AT28" s="30"/>
       <c r="AU28" s="3"/>
       <c r="AV28" s="3"/>
       <c r="AW28" s="3"/>
       <c r="AX28" s="3"/>
       <c r="AY28" s="3"/>
       <c r="AZ28" s="3"/>
-      <c r="BA28" s="1"/>
-    </row>
-    <row r="29" spans="1:53" ht="240">
+      <c r="BA28" s="3"/>
+      <c r="BB28" s="1"/>
+    </row>
+    <row r="29" spans="1:54" ht="240">
       <c r="A29" s="2">
         <v>26</v>
       </c>
@@ -4564,67 +4717,70 @@
       <c r="Z29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AA29" s="3"/>
-      <c r="AB29" s="11">
+      <c r="AA29" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB29" s="3"/>
+      <c r="AC29" s="11">
         <v>46072</v>
       </c>
-      <c r="AC29" s="3"/>
-      <c r="AD29" s="11">
+      <c r="AD29" s="3"/>
+      <c r="AE29" s="11">
         <v>46100</v>
       </c>
-      <c r="AE29" s="3"/>
-      <c r="AF29" s="24">
+      <c r="AF29" s="3"/>
+      <c r="AG29" s="24">
         <v>46114</v>
       </c>
-      <c r="AG29" s="3"/>
-      <c r="AH29" s="24">
+      <c r="AH29" s="3"/>
+      <c r="AI29" s="24">
         <v>46128</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>5</v>
       </c>
-      <c r="AJ29" s="30"/>
-      <c r="AK29" s="50" t="s">
-        <v>126</v>
-      </c>
-      <c r="AL29" s="44">
+      <c r="AK29" s="30"/>
+      <c r="AL29" s="49" t="s">
+        <v>124</v>
+      </c>
+      <c r="AM29" s="44">
         <v>1</v>
       </c>
-      <c r="AM29" s="24">
+      <c r="AN29" s="24">
         <v>46135</v>
       </c>
-      <c r="AN29" s="5" t="s">
+      <c r="AO29" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="AO29" s="42" t="s">
+      <c r="AP29" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="AP29" s="29" t="s">
+      <c r="AQ29" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="AQ29" s="28" t="s">
+      <c r="AR29" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="AR29" s="24">
+      <c r="AS29" s="24">
         <v>46135</v>
       </c>
-      <c r="AS29" s="30"/>
-      <c r="AT29" s="48" t="s">
-        <v>125</v>
-      </c>
-      <c r="AU29" s="24">
+      <c r="AT29" s="30"/>
+      <c r="AU29" s="47" t="s">
+        <v>123</v>
+      </c>
+      <c r="AV29" s="24">
         <v>46149</v>
       </c>
-      <c r="AV29" s="45"/>
-      <c r="AW29" s="24">
+      <c r="AW29" s="45"/>
+      <c r="AX29" s="24">
         <v>46149</v>
       </c>
-      <c r="AX29" s="3"/>
       <c r="AY29" s="3"/>
       <c r="AZ29" s="3"/>
-      <c r="BA29" s="1"/>
-    </row>
-    <row r="30" spans="1:53" ht="60">
+      <c r="BA29" s="3"/>
+      <c r="BB29" s="1"/>
+    </row>
+    <row r="30" spans="1:54" ht="150">
       <c r="A30" s="2">
         <v>27</v>
       </c>
@@ -4701,59 +4857,64 @@
       <c r="Z30" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AA30" s="3"/>
-      <c r="AB30" s="11">
+      <c r="AA30" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB30" s="3"/>
+      <c r="AC30" s="11">
         <v>46072</v>
       </c>
-      <c r="AC30" s="3"/>
-      <c r="AD30" s="24">
+      <c r="AD30" s="3"/>
+      <c r="AE30" s="24">
         <v>46100</v>
       </c>
-      <c r="AE30" s="3"/>
-      <c r="AF30" s="24">
+      <c r="AF30" s="3"/>
+      <c r="AG30" s="24">
         <v>46104</v>
       </c>
-      <c r="AG30" s="3"/>
-      <c r="AH30" s="24">
+      <c r="AH30" s="3"/>
+      <c r="AI30" s="24">
         <v>46107</v>
       </c>
-      <c r="AI30" s="3">
+      <c r="AJ30" s="3">
         <v>5</v>
       </c>
-      <c r="AJ30" s="43"/>
-      <c r="AK30" s="37">
+      <c r="AK30" s="43"/>
+      <c r="AL30" s="49" t="s">
+        <v>137</v>
+      </c>
+      <c r="AM30" s="38">
         <v>7</v>
       </c>
-      <c r="AL30" s="38"/>
-      <c r="AM30" s="24">
+      <c r="AN30" s="24">
         <v>46135</v>
       </c>
-      <c r="AN30" s="37" t="s">
+      <c r="AO30" s="37" t="s">
         <v>104</v>
       </c>
-      <c r="AO30" s="30"/>
-      <c r="AP30" s="3"/>
+      <c r="AP30" s="30"/>
       <c r="AQ30" s="3"/>
-      <c r="AR30" s="24">
+      <c r="AR30" s="3"/>
+      <c r="AS30" s="24">
         <v>46135</v>
       </c>
-      <c r="AS30" s="30"/>
-      <c r="AT30" s="33" t="s">
-        <v>119</v>
-      </c>
-      <c r="AU30" s="24">
+      <c r="AT30" s="30"/>
+      <c r="AU30" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV30" s="24">
         <v>46149</v>
       </c>
-      <c r="AV30" s="3"/>
-      <c r="AW30" s="24">
+      <c r="AW30" s="3"/>
+      <c r="AX30" s="24">
         <v>46149</v>
       </c>
-      <c r="AX30" s="3"/>
-      <c r="AY30" s="3"/>
+      <c r="AY30" s="62"/>
       <c r="AZ30" s="3"/>
-      <c r="BA30" s="1"/>
-    </row>
-    <row r="31" spans="1:53" ht="105">
+      <c r="BA30" s="3"/>
+      <c r="BB30" s="1"/>
+    </row>
+    <row r="31" spans="1:54" ht="105">
       <c r="A31" s="2">
         <v>28</v>
       </c>
@@ -4830,67 +4991,72 @@
       <c r="Z31" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA31" s="3"/>
-      <c r="AB31" s="11">
+      <c r="AA31" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB31" s="3"/>
+      <c r="AC31" s="11">
         <v>46072</v>
       </c>
-      <c r="AC31" s="3"/>
-      <c r="AD31" s="24">
+      <c r="AD31" s="3"/>
+      <c r="AE31" s="24">
         <v>46121</v>
       </c>
-      <c r="AE31" s="3"/>
-      <c r="AF31" s="24">
+      <c r="AF31" s="3"/>
+      <c r="AG31" s="24">
         <v>46135</v>
       </c>
-      <c r="AG31" s="3"/>
-      <c r="AH31" s="24">
+      <c r="AH31" s="3"/>
+      <c r="AI31" s="24">
         <v>46135</v>
       </c>
-      <c r="AI31" s="3">
+      <c r="AJ31" s="3">
         <v>3</v>
       </c>
-      <c r="AJ31" s="30"/>
-      <c r="AK31" s="37"/>
-      <c r="AL31" s="40" t="s">
+      <c r="AK31" s="30"/>
+      <c r="AL31" s="48" t="s">
+        <v>141</v>
+      </c>
+      <c r="AM31" s="40" t="s">
         <v>112</v>
       </c>
-      <c r="AM31" s="24">
+      <c r="AN31" s="24">
         <v>46149</v>
       </c>
-      <c r="AN31" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="AO31" s="42" t="s">
+      <c r="AO31" s="49" t="s">
+        <v>142</v>
+      </c>
+      <c r="AP31" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="AP31" s="29" t="s">
+      <c r="AQ31" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="AQ31" s="28" t="s">
+      <c r="AR31" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="AR31" s="24">
+      <c r="AS31" s="24">
         <v>46170</v>
       </c>
-      <c r="AS31" s="58" t="s">
-        <v>128</v>
-      </c>
-      <c r="AT31" s="57" t="s">
-        <v>127</v>
-      </c>
-      <c r="AU31" s="24">
+      <c r="AT31" s="55" t="s">
+        <v>126</v>
+      </c>
+      <c r="AU31" s="54" t="s">
+        <v>125</v>
+      </c>
+      <c r="AV31" s="24">
         <v>46170</v>
       </c>
-      <c r="AV31" s="52"/>
-      <c r="AW31" s="24">
+      <c r="AW31" s="51"/>
+      <c r="AX31" s="24">
         <v>46170</v>
       </c>
-      <c r="AX31" s="3"/>
-      <c r="AY31" s="3"/>
+      <c r="AY31" s="62"/>
       <c r="AZ31" s="3"/>
-      <c r="BA31" s="1"/>
-    </row>
-    <row r="32" spans="1:53" ht="120">
+      <c r="BA31" s="3"/>
+      <c r="BB31" s="1"/>
+    </row>
+    <row r="32" spans="1:54" ht="120">
       <c r="A32" s="2">
         <v>29</v>
       </c>
@@ -4965,49 +5131,52 @@
       <c r="Z32" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AA32" s="3"/>
-      <c r="AB32" s="24">
+      <c r="AA32" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB32" s="3"/>
+      <c r="AC32" s="24">
         <v>46170</v>
       </c>
-      <c r="AC32" s="3"/>
-      <c r="AD32" s="24">
+      <c r="AD32" s="3"/>
+      <c r="AE32" s="24">
         <v>46170</v>
       </c>
-      <c r="AE32" s="3"/>
       <c r="AF32" s="3"/>
       <c r="AG32" s="3"/>
       <c r="AH32" s="3"/>
-      <c r="AI32" s="3">
+      <c r="AI32" s="3"/>
+      <c r="AJ32" s="3">
         <v>2</v>
       </c>
-      <c r="AJ32" s="30"/>
-      <c r="AK32" s="50" t="s">
+      <c r="AK32" s="30"/>
+      <c r="AL32" s="49" t="s">
+        <v>129</v>
+      </c>
+      <c r="AM32" s="3"/>
+      <c r="AN32" s="37"/>
+      <c r="AO32" s="37"/>
+      <c r="AP32" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="AQ32" s="49" t="s">
         <v>131</v>
       </c>
-      <c r="AL32" s="3"/>
-      <c r="AM32" s="37"/>
-      <c r="AN32" s="37"/>
-      <c r="AO32" s="42" t="s">
-        <v>72</v>
-      </c>
-      <c r="AP32" s="50" t="s">
-        <v>133</v>
-      </c>
-      <c r="AQ32" s="52"/>
-      <c r="AR32" s="24">
+      <c r="AR32" s="51"/>
+      <c r="AS32" s="24">
         <v>46170</v>
       </c>
-      <c r="AS32" s="30"/>
-      <c r="AT32" s="3"/>
+      <c r="AT32" s="30"/>
       <c r="AU32" s="3"/>
       <c r="AV32" s="3"/>
       <c r="AW32" s="3"/>
       <c r="AX32" s="3"/>
       <c r="AY32" s="3"/>
       <c r="AZ32" s="3"/>
-      <c r="BA32" s="1"/>
-    </row>
-    <row r="33" spans="1:53" ht="105">
+      <c r="BA32" s="3"/>
+      <c r="BB32" s="1"/>
+    </row>
+    <row r="33" spans="1:54" ht="105">
       <c r="A33" s="2">
         <v>30</v>
       </c>
@@ -5082,59 +5251,62 @@
       <c r="Z33" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AA33" s="3"/>
-      <c r="AB33" s="11">
+      <c r="AA33" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB33" s="3"/>
+      <c r="AC33" s="11">
         <v>46079</v>
       </c>
-      <c r="AC33" s="3"/>
-      <c r="AD33" s="11">
+      <c r="AD33" s="3"/>
+      <c r="AE33" s="11">
         <v>46118</v>
       </c>
-      <c r="AE33" s="3"/>
-      <c r="AF33" s="24">
+      <c r="AF33" s="3"/>
+      <c r="AG33" s="24">
         <v>46121</v>
       </c>
-      <c r="AG33" s="3"/>
-      <c r="AH33" s="24">
+      <c r="AH33" s="3"/>
+      <c r="AI33" s="24">
         <v>46135</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>4</v>
       </c>
-      <c r="AJ33" s="30"/>
-      <c r="AK33" s="37"/>
-      <c r="AL33" s="41" t="s">
+      <c r="AK33" s="30"/>
+      <c r="AL33" s="37"/>
+      <c r="AM33" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="AM33" s="24">
+      <c r="AN33" s="24">
         <v>46149</v>
       </c>
-      <c r="AN33" s="41" t="s">
-        <v>120</v>
-      </c>
-      <c r="AO33" s="42" t="s">
+      <c r="AO33" s="41" t="s">
+        <v>119</v>
+      </c>
+      <c r="AP33" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="AP33" s="29" t="s">
+      <c r="AQ33" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="AQ33" s="28" t="s">
+      <c r="AR33" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="AR33" s="24">
+      <c r="AS33" s="24">
         <v>46170</v>
       </c>
-      <c r="AS33" s="30"/>
-      <c r="AT33" s="3"/>
+      <c r="AT33" s="30"/>
       <c r="AU33" s="3"/>
       <c r="AV33" s="3"/>
       <c r="AW33" s="3"/>
       <c r="AX33" s="3"/>
       <c r="AY33" s="3"/>
       <c r="AZ33" s="3"/>
-      <c r="BA33" s="1"/>
-    </row>
-    <row r="34" spans="1:53" ht="135">
+      <c r="BA33" s="3"/>
+      <c r="BB33" s="1"/>
+    </row>
+    <row r="34" spans="1:54" ht="60">
       <c r="A34" s="2">
         <v>31</v>
       </c>
@@ -5207,63 +5379,66 @@
       <c r="Z34" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AA34" s="3"/>
-      <c r="AB34" s="11">
+      <c r="AA34" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB34" s="3"/>
+      <c r="AC34" s="11">
         <v>46072</v>
       </c>
-      <c r="AC34" s="3"/>
-      <c r="AD34" s="17">
+      <c r="AD34" s="3"/>
+      <c r="AE34" s="17">
         <v>46093</v>
       </c>
-      <c r="AE34" s="3"/>
-      <c r="AF34" s="24">
+      <c r="AF34" s="3"/>
+      <c r="AG34" s="24">
         <v>46118</v>
       </c>
-      <c r="AG34" s="5"/>
-      <c r="AH34" s="24">
+      <c r="AH34" s="5"/>
+      <c r="AI34" s="24">
         <v>46118</v>
       </c>
-      <c r="AI34" s="5">
+      <c r="AJ34" s="5">
         <v>5</v>
       </c>
-      <c r="AJ34" s="43">
+      <c r="AK34" s="43">
         <v>46135</v>
       </c>
-      <c r="AK34" s="34">
-        <v>11</v>
-      </c>
-      <c r="AL34" s="5" t="s">
+      <c r="AL34" s="63" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM34" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="AM34" s="24">
+      <c r="AN34" s="24">
         <v>46156</v>
       </c>
-      <c r="AN34" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="AO34" s="30"/>
-      <c r="AP34" s="3"/>
+      <c r="AO34" s="48" t="s">
+        <v>141</v>
+      </c>
+      <c r="AP34" s="30"/>
       <c r="AQ34" s="3"/>
-      <c r="AR34" s="24">
+      <c r="AR34" s="3"/>
+      <c r="AS34" s="24">
         <v>46128</v>
       </c>
-      <c r="AS34" s="30"/>
-      <c r="AT34" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="AU34" s="24">
+      <c r="AT34" s="30"/>
+      <c r="AU34" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="AV34" s="24">
         <v>46156</v>
       </c>
-      <c r="AV34" s="3"/>
-      <c r="AW34" s="24">
+      <c r="AW34" s="3"/>
+      <c r="AX34" s="24">
         <v>46156</v>
       </c>
-      <c r="AX34" s="3"/>
-      <c r="AY34" s="3"/>
+      <c r="AY34" s="62"/>
       <c r="AZ34" s="3"/>
-      <c r="BA34" s="1"/>
-    </row>
-    <row r="35" spans="1:53">
+      <c r="BA34" s="3"/>
+      <c r="BB34" s="1"/>
+    </row>
+    <row r="35" spans="1:54">
       <c r="A35" s="2">
         <v>32</v>
       </c>
@@ -5336,37 +5511,40 @@
       <c r="Z35" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AA35" s="3"/>
+      <c r="AA35" s="53" t="s">
+        <v>17</v>
+      </c>
       <c r="AB35" s="3"/>
       <c r="AC35" s="3"/>
       <c r="AD35" s="3"/>
       <c r="AE35" s="3"/>
       <c r="AF35" s="3"/>
       <c r="AG35" s="3"/>
-      <c r="AH35" s="39"/>
-      <c r="AI35" s="3">
+      <c r="AH35" s="3"/>
+      <c r="AI35" s="39"/>
+      <c r="AJ35" s="3">
         <v>2</v>
       </c>
-      <c r="AJ35" s="30"/>
-      <c r="AK35" s="37"/>
-      <c r="AL35" s="3"/>
-      <c r="AM35" s="37"/>
+      <c r="AK35" s="30"/>
+      <c r="AL35" s="37"/>
+      <c r="AM35" s="3"/>
       <c r="AN35" s="37"/>
-      <c r="AO35" s="30"/>
-      <c r="AP35" s="3"/>
+      <c r="AO35" s="37"/>
+      <c r="AP35" s="30"/>
       <c r="AQ35" s="3"/>
       <c r="AR35" s="3"/>
-      <c r="AS35" s="30"/>
-      <c r="AT35" s="3"/>
+      <c r="AS35" s="3"/>
+      <c r="AT35" s="30"/>
       <c r="AU35" s="3"/>
       <c r="AV35" s="3"/>
       <c r="AW35" s="3"/>
       <c r="AX35" s="3"/>
       <c r="AY35" s="3"/>
       <c r="AZ35" s="3"/>
-      <c r="BA35" s="1"/>
-    </row>
-    <row r="36" spans="1:53">
+      <c r="BA35" s="3"/>
+      <c r="BB35" s="1"/>
+    </row>
+    <row r="36" spans="1:54">
       <c r="A36" s="36">
         <v>33</v>
       </c>
@@ -5441,7 +5619,9 @@
       <c r="Z36" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AA36" s="3"/>
+      <c r="AA36" s="53" t="s">
+        <v>17</v>
+      </c>
       <c r="AB36" s="3"/>
       <c r="AC36" s="3"/>
       <c r="AD36" s="3"/>
@@ -5450,26 +5630,27 @@
       <c r="AG36" s="3"/>
       <c r="AH36" s="3"/>
       <c r="AI36" s="3"/>
-      <c r="AJ36" s="30"/>
-      <c r="AK36" s="37"/>
-      <c r="AL36" s="3"/>
-      <c r="AM36" s="37"/>
+      <c r="AJ36" s="3"/>
+      <c r="AK36" s="30"/>
+      <c r="AL36" s="37"/>
+      <c r="AM36" s="3"/>
       <c r="AN36" s="37"/>
-      <c r="AO36" s="30"/>
-      <c r="AP36" s="3"/>
+      <c r="AO36" s="37"/>
+      <c r="AP36" s="30"/>
       <c r="AQ36" s="3"/>
       <c r="AR36" s="3"/>
-      <c r="AS36" s="30"/>
-      <c r="AT36" s="3"/>
+      <c r="AS36" s="3"/>
+      <c r="AT36" s="30"/>
       <c r="AU36" s="3"/>
       <c r="AV36" s="3"/>
       <c r="AW36" s="3"/>
       <c r="AX36" s="3"/>
       <c r="AY36" s="3"/>
       <c r="AZ36" s="3"/>
-      <c r="BA36" s="1"/>
-    </row>
-    <row r="37" spans="1:53">
+      <c r="BA36" s="3"/>
+      <c r="BB36" s="1"/>
+    </row>
+    <row r="37" spans="1:54">
       <c r="A37" t="s">
         <v>65</v>
       </c>
@@ -5541,7 +5722,9 @@
       <c r="Z37" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AA37" s="3"/>
+      <c r="AA37" s="52" t="s">
+        <v>67</v>
+      </c>
       <c r="AB37" s="3"/>
       <c r="AC37" s="3"/>
       <c r="AD37" s="3"/>
@@ -5550,28 +5733,29 @@
       <c r="AG37" s="3"/>
       <c r="AH37" s="3"/>
       <c r="AI37" s="3"/>
-      <c r="AJ37" s="30"/>
-      <c r="AK37" s="37"/>
-      <c r="AL37" s="3">
+      <c r="AJ37" s="3"/>
+      <c r="AK37" s="30"/>
+      <c r="AL37" s="37"/>
+      <c r="AM37" s="3">
         <v>8</v>
       </c>
-      <c r="AM37" s="37"/>
       <c r="AN37" s="37"/>
-      <c r="AO37" s="30"/>
-      <c r="AP37" s="3"/>
+      <c r="AO37" s="37"/>
+      <c r="AP37" s="30"/>
       <c r="AQ37" s="3"/>
       <c r="AR37" s="3"/>
-      <c r="AS37" s="30"/>
-      <c r="AT37" s="3"/>
+      <c r="AS37" s="3"/>
+      <c r="AT37" s="30"/>
       <c r="AU37" s="3"/>
       <c r="AV37" s="3"/>
       <c r="AW37" s="3"/>
       <c r="AX37" s="3"/>
       <c r="AY37" s="3"/>
       <c r="AZ37" s="3"/>
-      <c r="BA37" s="1"/>
-    </row>
-    <row r="38" spans="1:53">
+      <c r="BA37" s="3"/>
+      <c r="BB37" s="1"/>
+    </row>
+    <row r="38" spans="1:54">
       <c r="E38">
         <v>1</v>
       </c>
@@ -5630,7 +5814,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:53">
+    <row r="39" spans="1:54">
       <c r="E39" s="13" t="s">
         <v>68</v>
       </c>
@@ -5644,7 +5828,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="40" spans="1:53">
+    <row r="40" spans="1:54">
       <c r="E40">
         <v>1</v>
       </c>
@@ -5712,7 +5896,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="1:53">
+    <row r="41" spans="1:54">
       <c r="W41" s="35" t="s">
         <v>95</v>
       </c>
@@ -5726,82 +5910,83 @@
         <v>99</v>
       </c>
     </row>
-    <row r="42" spans="1:53" ht="9.75" customHeight="1">
+    <row r="42" spans="1:54" ht="9.75" customHeight="1">
       <c r="W42" s="38" t="s">
         <v>100</v>
       </c>
       <c r="Z42" s="38" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="57" spans="31:33">
-      <c r="AE57" s="28"/>
-      <c r="AF57" s="29"/>
-      <c r="AG57" s="28"/>
-    </row>
-    <row r="58" spans="31:33" ht="90">
-      <c r="AE58" s="28" t="s">
+      <c r="AA42" s="38"/>
+    </row>
+    <row r="57" spans="32:34">
+      <c r="AF57" s="28"/>
+      <c r="AG57" s="29"/>
+      <c r="AH57" s="28"/>
+    </row>
+    <row r="58" spans="32:34" ht="90">
+      <c r="AF58" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="AF58" s="29" t="s">
+      <c r="AG58" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="AG58" s="28"/>
-    </row>
-    <row r="59" spans="31:33" ht="90">
-      <c r="AE59" s="28" t="s">
+      <c r="AH58" s="28"/>
+    </row>
+    <row r="59" spans="32:34" ht="90">
+      <c r="AF59" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="AF59" s="29" t="s">
+      <c r="AG59" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="AG59" s="28" t="s">
+      <c r="AH59" s="28" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="60" spans="31:33" ht="90">
-      <c r="AE60" s="28" t="s">
+    <row r="60" spans="32:34" ht="90">
+      <c r="AF60" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="AF60" s="29" t="s">
+      <c r="AG60" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="AG60" s="28" t="s">
+      <c r="AH60" s="28" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="61" spans="31:33" ht="90">
-      <c r="AE61" s="28" t="s">
+    <row r="61" spans="32:34" ht="90">
+      <c r="AF61" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="AF61" s="29" t="s">
+      <c r="AG61" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="AG61" s="28" t="s">
+      <c r="AH61" s="28" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="62" spans="31:33" ht="45">
-      <c r="AE62" s="28" t="s">
+    <row r="62" spans="32:34" ht="45">
+      <c r="AF62" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="AF62" s="29" t="s">
+      <c r="AG62" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="AG62" s="28"/>
-    </row>
-    <row r="63" spans="31:33" ht="90">
-      <c r="AE63" s="28" t="s">
+      <c r="AH62" s="28"/>
+    </row>
+    <row r="63" spans="32:34" ht="90">
+      <c r="AF63" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="AF63" s="29" t="s">
+      <c r="AG63" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="AG63" s="28"/>
+      <c r="AH63" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:BA1"/>
+    <mergeCell ref="A1:BB1"/>
     <mergeCell ref="A2:B2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5815,56 +6000,56 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
-      <c r="S1" s="53"/>
-      <c r="T1" s="53"/>
-      <c r="U1" s="53"/>
-      <c r="V1" s="53"/>
-      <c r="W1" s="53"/>
-      <c r="X1" s="53"/>
-      <c r="Y1" s="53"/>
-      <c r="Z1" s="53"/>
-      <c r="AA1" s="53"/>
-      <c r="AB1" s="53"/>
-      <c r="AC1" s="53"/>
-      <c r="AD1" s="53"/>
-      <c r="AE1" s="53"/>
-      <c r="AF1" s="53"/>
-      <c r="AG1" s="53"/>
-      <c r="AH1" s="53"/>
-      <c r="AI1" s="53"/>
-      <c r="AJ1" s="53"/>
-      <c r="AK1" s="53"/>
-      <c r="AL1" s="53"/>
-      <c r="AM1" s="53"/>
-      <c r="AN1" s="53"/>
-      <c r="AO1" s="53"/>
-      <c r="AP1" s="53"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="57"/>
+      <c r="N1" s="57"/>
+      <c r="O1" s="57"/>
+      <c r="P1" s="57"/>
+      <c r="Q1" s="57"/>
+      <c r="R1" s="57"/>
+      <c r="S1" s="57"/>
+      <c r="T1" s="57"/>
+      <c r="U1" s="57"/>
+      <c r="V1" s="57"/>
+      <c r="W1" s="57"/>
+      <c r="X1" s="57"/>
+      <c r="Y1" s="57"/>
+      <c r="Z1" s="57"/>
+      <c r="AA1" s="57"/>
+      <c r="AB1" s="57"/>
+      <c r="AC1" s="57"/>
+      <c r="AD1" s="57"/>
+      <c r="AE1" s="57"/>
+      <c r="AF1" s="57"/>
+      <c r="AG1" s="57"/>
+      <c r="AH1" s="57"/>
+      <c r="AI1" s="57"/>
+      <c r="AJ1" s="57"/>
+      <c r="AK1" s="57"/>
+      <c r="AL1" s="57"/>
+      <c r="AM1" s="57"/>
+      <c r="AN1" s="57"/>
+      <c r="AO1" s="57"/>
+      <c r="AP1" s="57"/>
     </row>
     <row r="2" spans="1:42" ht="30">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="55"/>
+      <c r="B2" s="59"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -6293,142 +6478,142 @@
       <c r="AP10" s="1"/>
     </row>
     <row r="11" spans="1:42">
-      <c r="A11" s="55">
+      <c r="A11" s="59">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C11" s="55"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="55"/>
-      <c r="F11" s="55"/>
-      <c r="G11" s="55"/>
-      <c r="H11" s="55"/>
-      <c r="I11" s="55"/>
-      <c r="J11" s="55"/>
-      <c r="K11" s="55"/>
-      <c r="L11" s="56"/>
-      <c r="M11" s="56"/>
-      <c r="N11" s="56"/>
-      <c r="O11" s="56"/>
-      <c r="P11" s="56"/>
-      <c r="Q11" s="56"/>
-      <c r="R11" s="56"/>
-      <c r="S11" s="56"/>
-      <c r="T11" s="56"/>
-      <c r="U11" s="56"/>
-      <c r="V11" s="56"/>
-      <c r="W11" s="56"/>
-      <c r="X11" s="56"/>
-      <c r="Y11" s="56"/>
-      <c r="Z11" s="56"/>
-      <c r="AA11" s="56"/>
-      <c r="AB11" s="56"/>
-      <c r="AC11" s="56"/>
-      <c r="AD11" s="56"/>
-      <c r="AE11" s="56"/>
-      <c r="AF11" s="56"/>
-      <c r="AG11" s="56"/>
-      <c r="AH11" s="56"/>
-      <c r="AI11" s="56"/>
-      <c r="AJ11" s="56"/>
-      <c r="AK11" s="56"/>
-      <c r="AL11" s="56"/>
-      <c r="AM11" s="56"/>
-      <c r="AN11" s="56"/>
-      <c r="AO11" s="56"/>
-      <c r="AP11" s="53"/>
+      <c r="C11" s="59"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="59"/>
+      <c r="J11" s="59"/>
+      <c r="K11" s="59"/>
+      <c r="L11" s="60"/>
+      <c r="M11" s="60"/>
+      <c r="N11" s="60"/>
+      <c r="O11" s="60"/>
+      <c r="P11" s="60"/>
+      <c r="Q11" s="60"/>
+      <c r="R11" s="60"/>
+      <c r="S11" s="60"/>
+      <c r="T11" s="60"/>
+      <c r="U11" s="60"/>
+      <c r="V11" s="60"/>
+      <c r="W11" s="60"/>
+      <c r="X11" s="60"/>
+      <c r="Y11" s="60"/>
+      <c r="Z11" s="60"/>
+      <c r="AA11" s="60"/>
+      <c r="AB11" s="60"/>
+      <c r="AC11" s="60"/>
+      <c r="AD11" s="60"/>
+      <c r="AE11" s="60"/>
+      <c r="AF11" s="60"/>
+      <c r="AG11" s="60"/>
+      <c r="AH11" s="60"/>
+      <c r="AI11" s="60"/>
+      <c r="AJ11" s="60"/>
+      <c r="AK11" s="60"/>
+      <c r="AL11" s="60"/>
+      <c r="AM11" s="60"/>
+      <c r="AN11" s="60"/>
+      <c r="AO11" s="60"/>
+      <c r="AP11" s="57"/>
     </row>
     <row r="12" spans="1:42">
-      <c r="A12" s="55"/>
+      <c r="A12" s="59"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="55"/>
-      <c r="J12" s="55"/>
-      <c r="K12" s="55"/>
-      <c r="L12" s="56"/>
-      <c r="M12" s="56"/>
-      <c r="N12" s="56"/>
-      <c r="O12" s="56"/>
-      <c r="P12" s="56"/>
-      <c r="Q12" s="56"/>
-      <c r="R12" s="56"/>
-      <c r="S12" s="56"/>
-      <c r="T12" s="56"/>
-      <c r="U12" s="56"/>
-      <c r="V12" s="56"/>
-      <c r="W12" s="56"/>
-      <c r="X12" s="56"/>
-      <c r="Y12" s="56"/>
-      <c r="Z12" s="56"/>
-      <c r="AA12" s="56"/>
-      <c r="AB12" s="56"/>
-      <c r="AC12" s="56"/>
-      <c r="AD12" s="56"/>
-      <c r="AE12" s="56"/>
-      <c r="AF12" s="56"/>
-      <c r="AG12" s="56"/>
-      <c r="AH12" s="56"/>
-      <c r="AI12" s="56"/>
-      <c r="AJ12" s="56"/>
-      <c r="AK12" s="56"/>
-      <c r="AL12" s="56"/>
-      <c r="AM12" s="56"/>
-      <c r="AN12" s="56"/>
-      <c r="AO12" s="56"/>
-      <c r="AP12" s="53"/>
+      <c r="C12" s="59"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="59"/>
+      <c r="K12" s="59"/>
+      <c r="L12" s="60"/>
+      <c r="M12" s="60"/>
+      <c r="N12" s="60"/>
+      <c r="O12" s="60"/>
+      <c r="P12" s="60"/>
+      <c r="Q12" s="60"/>
+      <c r="R12" s="60"/>
+      <c r="S12" s="60"/>
+      <c r="T12" s="60"/>
+      <c r="U12" s="60"/>
+      <c r="V12" s="60"/>
+      <c r="W12" s="60"/>
+      <c r="X12" s="60"/>
+      <c r="Y12" s="60"/>
+      <c r="Z12" s="60"/>
+      <c r="AA12" s="60"/>
+      <c r="AB12" s="60"/>
+      <c r="AC12" s="60"/>
+      <c r="AD12" s="60"/>
+      <c r="AE12" s="60"/>
+      <c r="AF12" s="60"/>
+      <c r="AG12" s="60"/>
+      <c r="AH12" s="60"/>
+      <c r="AI12" s="60"/>
+      <c r="AJ12" s="60"/>
+      <c r="AK12" s="60"/>
+      <c r="AL12" s="60"/>
+      <c r="AM12" s="60"/>
+      <c r="AN12" s="60"/>
+      <c r="AO12" s="60"/>
+      <c r="AP12" s="57"/>
     </row>
     <row r="13" spans="1:42">
-      <c r="A13" s="55"/>
+      <c r="A13" s="59"/>
       <c r="B13" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="55"/>
-      <c r="D13" s="55"/>
-      <c r="E13" s="55"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="55"/>
-      <c r="I13" s="55"/>
-      <c r="J13" s="55"/>
-      <c r="K13" s="55"/>
-      <c r="L13" s="56"/>
-      <c r="M13" s="56"/>
-      <c r="N13" s="56"/>
-      <c r="O13" s="56"/>
-      <c r="P13" s="56"/>
-      <c r="Q13" s="56"/>
-      <c r="R13" s="56"/>
-      <c r="S13" s="56"/>
-      <c r="T13" s="56"/>
-      <c r="U13" s="56"/>
-      <c r="V13" s="56"/>
-      <c r="W13" s="56"/>
-      <c r="X13" s="56"/>
-      <c r="Y13" s="56"/>
-      <c r="Z13" s="56"/>
-      <c r="AA13" s="56"/>
-      <c r="AB13" s="56"/>
-      <c r="AC13" s="56"/>
-      <c r="AD13" s="56"/>
-      <c r="AE13" s="56"/>
-      <c r="AF13" s="56"/>
-      <c r="AG13" s="56"/>
-      <c r="AH13" s="56"/>
-      <c r="AI13" s="56"/>
-      <c r="AJ13" s="56"/>
-      <c r="AK13" s="56"/>
-      <c r="AL13" s="56"/>
-      <c r="AM13" s="56"/>
-      <c r="AN13" s="56"/>
-      <c r="AO13" s="56"/>
-      <c r="AP13" s="53"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="59"/>
+      <c r="I13" s="59"/>
+      <c r="J13" s="59"/>
+      <c r="K13" s="59"/>
+      <c r="L13" s="60"/>
+      <c r="M13" s="60"/>
+      <c r="N13" s="60"/>
+      <c r="O13" s="60"/>
+      <c r="P13" s="60"/>
+      <c r="Q13" s="60"/>
+      <c r="R13" s="60"/>
+      <c r="S13" s="60"/>
+      <c r="T13" s="60"/>
+      <c r="U13" s="60"/>
+      <c r="V13" s="60"/>
+      <c r="W13" s="60"/>
+      <c r="X13" s="60"/>
+      <c r="Y13" s="60"/>
+      <c r="Z13" s="60"/>
+      <c r="AA13" s="60"/>
+      <c r="AB13" s="60"/>
+      <c r="AC13" s="60"/>
+      <c r="AD13" s="60"/>
+      <c r="AE13" s="60"/>
+      <c r="AF13" s="60"/>
+      <c r="AG13" s="60"/>
+      <c r="AH13" s="60"/>
+      <c r="AI13" s="60"/>
+      <c r="AJ13" s="60"/>
+      <c r="AK13" s="60"/>
+      <c r="AL13" s="60"/>
+      <c r="AM13" s="60"/>
+      <c r="AN13" s="60"/>
+      <c r="AO13" s="60"/>
+      <c r="AP13" s="57"/>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" s="2">
@@ -7584,33 +7769,6 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="AO11:AO13"/>
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="AN11:AN13"/>
-    <mergeCell ref="AE11:AE13"/>
-    <mergeCell ref="AF11:AF13"/>
-    <mergeCell ref="AG11:AG13"/>
-    <mergeCell ref="AH11:AH13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="Z11:Z13"/>
-    <mergeCell ref="AA11:AA13"/>
-    <mergeCell ref="AB11:AB13"/>
-    <mergeCell ref="AC11:AC13"/>
-    <mergeCell ref="AD11:AD13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="V11:V13"/>
-    <mergeCell ref="W11:W13"/>
-    <mergeCell ref="X11:X13"/>
-    <mergeCell ref="Y11:Y13"/>
-    <mergeCell ref="P11:P13"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="T11:T13"/>
     <mergeCell ref="A1:AP1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A11:A13"/>
@@ -7627,6 +7785,33 @@
     <mergeCell ref="M11:M13"/>
     <mergeCell ref="N11:N13"/>
     <mergeCell ref="O11:O13"/>
+    <mergeCell ref="P11:P13"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="T11:T13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="V11:V13"/>
+    <mergeCell ref="W11:W13"/>
+    <mergeCell ref="X11:X13"/>
+    <mergeCell ref="Y11:Y13"/>
+    <mergeCell ref="Z11:Z13"/>
+    <mergeCell ref="AA11:AA13"/>
+    <mergeCell ref="AB11:AB13"/>
+    <mergeCell ref="AC11:AC13"/>
+    <mergeCell ref="AD11:AD13"/>
+    <mergeCell ref="AE11:AE13"/>
+    <mergeCell ref="AF11:AF13"/>
+    <mergeCell ref="AG11:AG13"/>
+    <mergeCell ref="AH11:AH13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="AO11:AO13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
+    <mergeCell ref="AN11:AN13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ТКИ-341_Реверс_Инжиниринг.xlsx
+++ b/ТКИ-341_Реверс_Инжиниринг.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\Reverse_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB70B41-6A4C-4453-890A-2239D436BE37}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F85F0881-B1DD-43FE-BABD-AF65AD0C94AA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="150">
   <si>
     <t>ВЕДОМОСТЬ ПОСЕЩАЕМОСТИ ЗАНЯТИЙ СТУДЕНТАМИ ГРУППЫ ТКИ "Компьютерная безопасность" ИТТСУ РУТ (МИИТ)</t>
   </si>
@@ -395,12 +395,6 @@
     <t>Иконников, Наседкин</t>
   </si>
   <si>
-    <t>Небоваренков Степан (4)</t>
-  </si>
-  <si>
-    <t>площадь и периметрпрямоугольника</t>
-  </si>
-  <si>
     <t>Рина (5)</t>
   </si>
   <si>
@@ -422,9 +416,6 @@
     <t>Kody-AI через VPN</t>
   </si>
   <si>
-    <t>Нахождение пути минимальной стоимости</t>
-  </si>
-  <si>
     <t>Анализаторы CWE, включая Костенко</t>
   </si>
   <si>
@@ -498,6 +489,30 @@
   </si>
   <si>
     <t>потенциальная энергия пружины (Зверь)</t>
+  </si>
+  <si>
+    <t>кодирование base64 (Досталось Круцу)</t>
+  </si>
+  <si>
+    <t>кодирование base64 (от Бахрова и Луканкина)</t>
+  </si>
+  <si>
+    <t>информация о «горячих точках» кода на основе анализа реляционной модели git-репозитория с использование По С.В. Макшакова</t>
+  </si>
+  <si>
+    <t>Нахождение пути минимальной стоимости Небоваренков Степан (4)</t>
+  </si>
+  <si>
+    <t>площадь и периметрпрямоугольника (Громов, Шабин)</t>
+  </si>
+  <si>
+    <t>Sourcegraph</t>
+  </si>
+  <si>
+    <t>анализ двух своих программ</t>
+  </si>
+  <si>
+    <t>GitLab KG не запустился даже после консультаций</t>
   </si>
 </sst>
 </file>
@@ -637,7 +652,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -784,15 +799,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -804,6 +810,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1115,68 +1133,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="14.45" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="57"/>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="57"/>
-      <c r="R1" s="57"/>
-      <c r="S1" s="57"/>
-      <c r="T1" s="57"/>
-      <c r="U1" s="57"/>
-      <c r="V1" s="57"/>
-      <c r="W1" s="57"/>
-      <c r="X1" s="57"/>
-      <c r="Y1" s="57"/>
-      <c r="Z1" s="57"/>
-      <c r="AA1" s="57"/>
-      <c r="AB1" s="57"/>
-      <c r="AC1" s="57"/>
-      <c r="AD1" s="57"/>
-      <c r="AE1" s="57"/>
-      <c r="AF1" s="57"/>
-      <c r="AG1" s="57"/>
-      <c r="AH1" s="57"/>
-      <c r="AI1" s="57"/>
-      <c r="AJ1" s="57"/>
-      <c r="AK1" s="57"/>
-      <c r="AL1" s="57"/>
-      <c r="AM1" s="57"/>
-      <c r="AN1" s="57"/>
-      <c r="AO1" s="57"/>
-      <c r="AP1" s="57"/>
-      <c r="AQ1" s="57"/>
-      <c r="AR1" s="57"/>
-      <c r="AS1" s="57"/>
-      <c r="AT1" s="57"/>
-      <c r="AU1" s="57"/>
-      <c r="AV1" s="57"/>
-      <c r="AW1" s="57"/>
-      <c r="AX1" s="57"/>
-      <c r="AY1" s="57"/>
-      <c r="AZ1" s="57"/>
-      <c r="BA1" s="57"/>
-      <c r="BB1" s="57"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="62"/>
+      <c r="Q1" s="62"/>
+      <c r="R1" s="62"/>
+      <c r="S1" s="62"/>
+      <c r="T1" s="62"/>
+      <c r="U1" s="62"/>
+      <c r="V1" s="62"/>
+      <c r="W1" s="62"/>
+      <c r="X1" s="62"/>
+      <c r="Y1" s="62"/>
+      <c r="Z1" s="62"/>
+      <c r="AA1" s="62"/>
+      <c r="AB1" s="62"/>
+      <c r="AC1" s="62"/>
+      <c r="AD1" s="62"/>
+      <c r="AE1" s="62"/>
+      <c r="AF1" s="62"/>
+      <c r="AG1" s="62"/>
+      <c r="AH1" s="62"/>
+      <c r="AI1" s="62"/>
+      <c r="AJ1" s="62"/>
+      <c r="AK1" s="62"/>
+      <c r="AL1" s="62"/>
+      <c r="AM1" s="62"/>
+      <c r="AN1" s="62"/>
+      <c r="AO1" s="62"/>
+      <c r="AP1" s="62"/>
+      <c r="AQ1" s="62"/>
+      <c r="AR1" s="62"/>
+      <c r="AS1" s="62"/>
+      <c r="AT1" s="62"/>
+      <c r="AU1" s="62"/>
+      <c r="AV1" s="62"/>
+      <c r="AW1" s="62"/>
+      <c r="AX1" s="62"/>
+      <c r="AY1" s="62"/>
+      <c r="AZ1" s="62"/>
+      <c r="BA1" s="62"/>
+      <c r="BB1" s="62"/>
     </row>
     <row r="2" spans="1:54" ht="27.6" customHeight="1">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="59"/>
+      <c r="B2" s="64"/>
       <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1463,13 +1481,13 @@
       <c r="AK4" s="30"/>
       <c r="AL4" s="37"/>
       <c r="AM4" s="49" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AN4" s="24">
         <v>46170</v>
       </c>
       <c r="AO4" s="49" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="AP4" s="42" t="s">
         <v>72</v>
@@ -1484,11 +1502,17 @@
         <v>46170</v>
       </c>
       <c r="AT4" s="30"/>
-      <c r="AU4" s="3"/>
-      <c r="AV4" s="3"/>
+      <c r="AU4" s="49" t="s">
+        <v>149</v>
+      </c>
+      <c r="AV4" s="24">
+        <v>46177</v>
+      </c>
       <c r="AW4" s="3"/>
-      <c r="AX4" s="3"/>
-      <c r="AY4" s="3"/>
+      <c r="AX4" s="24">
+        <v>46177</v>
+      </c>
+      <c r="AY4" s="59"/>
       <c r="AZ4" s="3"/>
       <c r="BA4" s="3"/>
       <c r="BB4" s="1"/>
@@ -1593,15 +1617,17 @@
         <v>5</v>
       </c>
       <c r="AK5" s="30"/>
-      <c r="AL5" s="37"/>
+      <c r="AL5" s="53" t="s">
+        <v>131</v>
+      </c>
       <c r="AM5" s="53" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="AN5" s="24">
         <v>46177</v>
       </c>
-      <c r="AO5" s="53" t="s">
-        <v>134</v>
+      <c r="AO5" s="57" t="s">
+        <v>142</v>
       </c>
       <c r="AP5" s="42" t="s">
         <v>75</v>
@@ -1615,7 +1641,7 @@
       </c>
       <c r="AT5" s="30"/>
       <c r="AU5" s="48" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AV5" s="24">
         <v>46177</v>
@@ -1624,7 +1650,7 @@
       <c r="AX5" s="24">
         <v>46177</v>
       </c>
-      <c r="AY5" s="3"/>
+      <c r="AY5" s="59"/>
       <c r="AZ5" s="3"/>
       <c r="BA5" s="3"/>
       <c r="BB5" s="1"/>
@@ -1730,16 +1756,16 @@
       </c>
       <c r="AK6" s="30"/>
       <c r="AL6" s="48" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AM6" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AN6" s="24">
         <v>46149</v>
       </c>
       <c r="AO6" s="49" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="AP6" s="42" t="s">
         <v>72</v>
@@ -1754,10 +1780,10 @@
         <v>46170</v>
       </c>
       <c r="AT6" s="55" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AU6" s="54" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="AV6" s="24">
         <v>46170</v>
@@ -1766,7 +1792,7 @@
       <c r="AX6" s="24">
         <v>46170</v>
       </c>
-      <c r="AY6" s="62"/>
+      <c r="AY6" s="59"/>
       <c r="AZ6" s="3"/>
       <c r="BA6" s="3"/>
       <c r="BB6" s="1"/>
@@ -1873,11 +1899,11 @@
       <c r="AK7" s="43">
         <v>46135</v>
       </c>
-      <c r="AL7" s="64" t="s">
-        <v>139</v>
+      <c r="AL7" s="61" t="s">
+        <v>136</v>
       </c>
       <c r="AM7" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AN7" s="24">
         <v>46135</v>
@@ -1908,7 +1934,7 @@
       <c r="AX7" s="24">
         <v>46149</v>
       </c>
-      <c r="AY7" s="62"/>
+      <c r="AY7" s="59"/>
       <c r="AZ7" s="3"/>
       <c r="BA7" s="3"/>
       <c r="BB7" s="1"/>
@@ -1979,7 +2005,7 @@
         <v>17</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="X8" s="3" t="s">
         <v>16</v>
@@ -2008,7 +2034,7 @@
       </c>
       <c r="AK8" s="30"/>
       <c r="AL8" s="37" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AM8" s="3">
         <v>17</v>
@@ -2027,7 +2053,6 @@
       </c>
       <c r="AS8" s="3"/>
       <c r="AT8" s="30"/>
-      <c r="AU8" s="3"/>
       <c r="AV8" s="3"/>
       <c r="AW8" s="3"/>
       <c r="AX8" s="3"/>
@@ -2036,7 +2061,7 @@
       <c r="BA8" s="3"/>
       <c r="BB8" s="1"/>
     </row>
-    <row r="9" spans="1:54" ht="75">
+    <row r="9" spans="1:54" ht="105">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -2143,8 +2168,8 @@
       <c r="AN9" s="24">
         <v>46149</v>
       </c>
-      <c r="AO9" s="40" t="s">
-        <v>111</v>
+      <c r="AO9" s="57" t="s">
+        <v>146</v>
       </c>
       <c r="AP9" s="42" t="s">
         <v>75</v>
@@ -2157,16 +2182,22 @@
         <v>46170</v>
       </c>
       <c r="AT9" s="30"/>
-      <c r="AU9" s="3"/>
-      <c r="AV9" s="3"/>
-      <c r="AW9" s="3"/>
-      <c r="AX9" s="3"/>
-      <c r="AY9" s="3"/>
+      <c r="AU9" s="57" t="s">
+        <v>147</v>
+      </c>
+      <c r="AV9" s="24">
+        <v>46177</v>
+      </c>
+      <c r="AW9" s="57"/>
+      <c r="AX9" s="24">
+        <v>46177</v>
+      </c>
+      <c r="AY9" s="59"/>
       <c r="AZ9" s="3"/>
       <c r="BA9" s="3"/>
       <c r="BB9" s="1"/>
     </row>
-    <row r="10" spans="1:54" ht="105">
+    <row r="10" spans="1:54" ht="270">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -2268,13 +2299,13 @@
       <c r="AK10" s="30"/>
       <c r="AL10" s="37"/>
       <c r="AM10" s="3" t="s">
-        <v>110</v>
+        <v>145</v>
       </c>
       <c r="AN10" s="24">
         <v>46149</v>
       </c>
-      <c r="AO10" s="37" t="s">
-        <v>119</v>
+      <c r="AO10" s="57" t="s">
+        <v>112</v>
       </c>
       <c r="AP10" s="42" t="s">
         <v>72</v>
@@ -2289,11 +2320,17 @@
         <v>46170</v>
       </c>
       <c r="AT10" s="30"/>
-      <c r="AU10" s="3"/>
-      <c r="AV10" s="3"/>
+      <c r="AU10" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="AV10" s="24">
+        <v>46177</v>
+      </c>
       <c r="AW10" s="3"/>
-      <c r="AX10" s="3"/>
-      <c r="AY10" s="3"/>
+      <c r="AX10" s="24">
+        <v>46177</v>
+      </c>
+      <c r="AY10" s="59"/>
       <c r="AZ10" s="3"/>
       <c r="BA10" s="3"/>
       <c r="BB10" s="1"/>
@@ -2429,7 +2466,7 @@
       <c r="AX11" s="24">
         <v>46149</v>
       </c>
-      <c r="AY11" s="61"/>
+      <c r="AY11" s="58"/>
       <c r="AZ11" s="5"/>
       <c r="BA11" s="5"/>
       <c r="BB11" s="5"/>
@@ -2536,13 +2573,13 @@
       <c r="AK12" s="31"/>
       <c r="AL12" s="5"/>
       <c r="AM12" s="48" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="AN12" s="24">
         <v>46170</v>
       </c>
       <c r="AO12" s="49" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="AP12" s="42" t="s">
         <v>72</v>
@@ -2557,10 +2594,10 @@
         <v>46135</v>
       </c>
       <c r="AT12" s="56" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="AU12" s="48" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="AV12" s="24">
         <v>46170</v>
@@ -2569,7 +2606,7 @@
       <c r="AX12" s="24">
         <v>46170</v>
       </c>
-      <c r="AY12" s="5"/>
+      <c r="AY12" s="58"/>
       <c r="AZ12" s="5"/>
       <c r="BA12" s="5"/>
       <c r="BB12" s="5"/>
@@ -2681,14 +2718,14 @@
       <c r="AL13" s="34">
         <v>11</v>
       </c>
-      <c r="AM13" s="63" t="s">
-        <v>138</v>
+      <c r="AM13" s="60" t="s">
+        <v>135</v>
       </c>
       <c r="AN13" s="24">
         <v>46149</v>
       </c>
       <c r="AO13" s="48" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AP13" s="42" t="s">
         <v>72</v>
@@ -2702,7 +2739,7 @@
       </c>
       <c r="AT13" s="31"/>
       <c r="AU13" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="AV13" s="24">
         <v>46156</v>
@@ -2711,7 +2748,7 @@
       <c r="AX13" s="24">
         <v>46156</v>
       </c>
-      <c r="AY13" s="61"/>
+      <c r="AY13" s="58"/>
       <c r="AZ13" s="5"/>
       <c r="BA13" s="5"/>
       <c r="BB13" s="5"/>
@@ -2950,7 +2987,7 @@
       </c>
       <c r="AT15" s="30"/>
       <c r="AU15" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AV15" s="24">
         <v>46149</v>
@@ -2959,7 +2996,7 @@
       <c r="AX15" s="24">
         <v>46149</v>
       </c>
-      <c r="AY15" s="62"/>
+      <c r="AY15" s="59"/>
       <c r="AZ15" s="3"/>
       <c r="BA15" s="3"/>
       <c r="BB15" s="1"/>
@@ -3063,7 +3100,7 @@
       </c>
       <c r="AK16" s="43"/>
       <c r="AL16" s="49" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="AM16" s="38">
         <v>7</v>
@@ -3088,7 +3125,7 @@
         <v>91</v>
       </c>
       <c r="AU16" s="33" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AV16" s="24">
         <v>46149</v>
@@ -3097,7 +3134,7 @@
       <c r="AX16" s="24">
         <v>46149</v>
       </c>
-      <c r="AY16" s="62"/>
+      <c r="AY16" s="59"/>
       <c r="AZ16" s="3"/>
       <c r="BA16" s="3"/>
       <c r="BB16" s="1"/>
@@ -3203,7 +3240,7 @@
       </c>
       <c r="AK17" s="30"/>
       <c r="AL17" s="49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AM17" s="44">
         <v>1</v>
@@ -3228,7 +3265,7 @@
       </c>
       <c r="AT17" s="30"/>
       <c r="AU17" s="47" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="AV17" s="24">
         <v>46149</v>
@@ -3342,8 +3379,8 @@
         <v>5</v>
       </c>
       <c r="AK18" s="43"/>
-      <c r="AL18" s="64" t="s">
-        <v>139</v>
+      <c r="AL18" s="61" t="s">
+        <v>136</v>
       </c>
       <c r="AM18" s="5">
         <v>12</v>
@@ -3369,12 +3406,12 @@
       <c r="AX18" s="24">
         <v>46149</v>
       </c>
-      <c r="AY18" s="62"/>
+      <c r="AY18" s="59"/>
       <c r="AZ18" s="3"/>
       <c r="BA18" s="3"/>
       <c r="BB18" s="1"/>
     </row>
-    <row r="19" spans="1:54" ht="75">
+    <row r="19" spans="1:54" ht="105">
       <c r="A19" s="2">
         <v>16</v>
       </c>
@@ -3480,7 +3517,7 @@
         <v>46149</v>
       </c>
       <c r="AO19" s="40" t="s">
-        <v>111</v>
+        <v>146</v>
       </c>
       <c r="AP19" s="42" t="s">
         <v>75</v>
@@ -3493,11 +3530,17 @@
         <v>46170</v>
       </c>
       <c r="AT19" s="30"/>
-      <c r="AU19" s="3"/>
-      <c r="AV19" s="3"/>
-      <c r="AW19" s="3"/>
-      <c r="AX19" s="3"/>
-      <c r="AY19" s="3"/>
+      <c r="AU19" s="57" t="s">
+        <v>147</v>
+      </c>
+      <c r="AV19" s="24">
+        <v>46177</v>
+      </c>
+      <c r="AW19" s="57"/>
+      <c r="AX19" s="24">
+        <v>46177</v>
+      </c>
+      <c r="AY19" s="59"/>
       <c r="AZ19" s="3"/>
       <c r="BA19" s="3"/>
       <c r="BB19" s="1"/>
@@ -3597,15 +3640,17 @@
       </c>
       <c r="AK20" s="30"/>
       <c r="AL20" s="37" t="s">
-        <v>107</v>
+        <v>143</v>
       </c>
       <c r="AM20" s="3">
         <v>6</v>
       </c>
       <c r="AN20" s="37"/>
-      <c r="AO20" s="37"/>
+      <c r="AO20" s="37" t="s">
+        <v>107</v>
+      </c>
       <c r="AP20" s="54" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="AQ20" s="3"/>
       <c r="AR20" s="3"/>
@@ -3720,7 +3765,6 @@
         <v>3</v>
       </c>
       <c r="AK21" s="30"/>
-      <c r="AL21" s="37"/>
       <c r="AM21" s="3"/>
       <c r="AN21" s="24">
         <v>46135</v>
@@ -3841,16 +3885,16 @@
       </c>
       <c r="AK22" s="30"/>
       <c r="AL22" s="49" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AM22" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AN22" s="24">
         <v>46135</v>
       </c>
       <c r="AO22" s="40" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AP22" s="42" t="s">
         <v>75</v>
@@ -3864,7 +3908,7 @@
       </c>
       <c r="AT22" s="30"/>
       <c r="AU22" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="AV22" s="24">
         <v>46149</v>
@@ -3873,7 +3917,7 @@
       <c r="AX22" s="24">
         <v>46156</v>
       </c>
-      <c r="AY22" s="62"/>
+      <c r="AY22" s="59"/>
       <c r="AZ22" s="3"/>
       <c r="BA22" s="3"/>
       <c r="BB22" s="1"/>
@@ -3979,16 +4023,16 @@
       </c>
       <c r="AK23" s="30"/>
       <c r="AL23" s="49" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AM23" s="40" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AN23" s="24">
         <v>46135</v>
       </c>
       <c r="AO23" s="37" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AP23" s="30"/>
       <c r="AQ23" s="3"/>
@@ -3998,7 +4042,7 @@
       </c>
       <c r="AT23" s="30"/>
       <c r="AU23" s="41" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="AV23" s="24">
         <v>46149</v>
@@ -4007,7 +4051,7 @@
       <c r="AX23" s="24">
         <v>46156</v>
       </c>
-      <c r="AY23" s="62"/>
+      <c r="AY23" s="59"/>
       <c r="AZ23" s="3"/>
       <c r="BA23" s="3"/>
       <c r="BB23" s="1"/>
@@ -4101,33 +4145,43 @@
         <v>46170</v>
       </c>
       <c r="AF24" s="3"/>
-      <c r="AG24" s="3"/>
+      <c r="AG24" s="24">
+        <v>46177</v>
+      </c>
       <c r="AH24" s="3"/>
-      <c r="AI24" s="3"/>
+      <c r="AI24" s="24">
+        <v>46177</v>
+      </c>
       <c r="AJ24" s="3">
         <v>2</v>
       </c>
       <c r="AK24" s="30"/>
       <c r="AL24" s="49" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="AM24" s="3">
         <v>2</v>
       </c>
-      <c r="AN24" s="37"/>
-      <c r="AO24" s="37"/>
+      <c r="AN24" s="24">
+        <v>46177</v>
+      </c>
+      <c r="AO24" s="49" t="s">
+        <v>126</v>
+      </c>
       <c r="AP24" s="42" t="s">
         <v>72</v>
       </c>
       <c r="AQ24" s="49" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="AR24" s="3"/>
       <c r="AS24" s="24">
         <v>46170</v>
       </c>
       <c r="AT24" s="30"/>
-      <c r="AU24" s="3"/>
+      <c r="AU24" s="49" t="s">
+        <v>148</v>
+      </c>
       <c r="AV24" s="3"/>
       <c r="AW24" s="3"/>
       <c r="AX24" s="3"/>
@@ -4236,13 +4290,13 @@
       <c r="AK25" s="30"/>
       <c r="AL25" s="37"/>
       <c r="AM25" s="48" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="AN25" s="24">
         <v>46170</v>
       </c>
       <c r="AO25" s="49" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="AP25" s="30"/>
       <c r="AQ25" s="3"/>
@@ -4251,10 +4305,10 @@
         <v>46135</v>
       </c>
       <c r="AT25" s="56" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="AU25" s="48" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="AV25" s="24">
         <v>46170</v>
@@ -4263,7 +4317,7 @@
       <c r="AX25" s="24">
         <v>46170</v>
       </c>
-      <c r="AY25" s="62"/>
+      <c r="AY25" s="59"/>
       <c r="AZ25" s="3"/>
       <c r="BA25" s="3"/>
       <c r="BB25" s="1"/>
@@ -4474,15 +4528,17 @@
       </c>
       <c r="AJ27" s="3"/>
       <c r="AK27" s="30"/>
-      <c r="AL27" s="37"/>
+      <c r="AL27" s="37" t="s">
+        <v>131</v>
+      </c>
       <c r="AM27" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="AN27" s="24">
         <v>46177</v>
       </c>
-      <c r="AO27" s="37" t="s">
-        <v>134</v>
+      <c r="AO27" s="57" t="s">
+        <v>142</v>
       </c>
       <c r="AP27" s="42" t="s">
         <v>75</v>
@@ -4496,7 +4552,7 @@
       </c>
       <c r="AT27" s="30"/>
       <c r="AU27" s="48" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AV27" s="24">
         <v>46177</v>
@@ -4505,7 +4561,7 @@
       <c r="AX27" s="24">
         <v>46177</v>
       </c>
-      <c r="AY27" s="3"/>
+      <c r="AY27" s="59"/>
       <c r="AZ27" s="3"/>
       <c r="BA27" s="3"/>
       <c r="BB27" s="1"/>
@@ -4610,15 +4666,14 @@
         <v>3</v>
       </c>
       <c r="AK28" s="30"/>
-      <c r="AL28" s="37"/>
       <c r="AM28" s="49" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AN28" s="24">
         <v>46170</v>
       </c>
       <c r="AO28" s="49" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="AP28" s="42" t="s">
         <v>72</v>
@@ -4633,11 +4688,17 @@
         <v>46170</v>
       </c>
       <c r="AT28" s="30"/>
-      <c r="AU28" s="3"/>
-      <c r="AV28" s="3"/>
-      <c r="AW28" s="3"/>
-      <c r="AX28" s="3"/>
-      <c r="AY28" s="3"/>
+      <c r="AU28" s="49" t="s">
+        <v>149</v>
+      </c>
+      <c r="AV28" s="24">
+        <v>46177</v>
+      </c>
+      <c r="AW28" s="57"/>
+      <c r="AX28" s="24">
+        <v>46177</v>
+      </c>
+      <c r="AY28" s="59"/>
       <c r="AZ28" s="3"/>
       <c r="BA28" s="3"/>
       <c r="BB28" s="1"/>
@@ -4741,7 +4802,7 @@
       </c>
       <c r="AK29" s="30"/>
       <c r="AL29" s="49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AM29" s="44">
         <v>1</v>
@@ -4766,7 +4827,7 @@
       </c>
       <c r="AT29" s="30"/>
       <c r="AU29" s="47" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="AV29" s="24">
         <v>46149</v>
@@ -4881,7 +4942,7 @@
       </c>
       <c r="AK30" s="43"/>
       <c r="AL30" s="49" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="AM30" s="38">
         <v>7</v>
@@ -4900,7 +4961,7 @@
       </c>
       <c r="AT30" s="30"/>
       <c r="AU30" s="33" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AV30" s="24">
         <v>46149</v>
@@ -4909,7 +4970,7 @@
       <c r="AX30" s="24">
         <v>46149</v>
       </c>
-      <c r="AY30" s="62"/>
+      <c r="AY30" s="59"/>
       <c r="AZ30" s="3"/>
       <c r="BA30" s="3"/>
       <c r="BB30" s="1"/>
@@ -5015,16 +5076,16 @@
       </c>
       <c r="AK31" s="30"/>
       <c r="AL31" s="48" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AM31" s="40" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AN31" s="24">
         <v>46149</v>
       </c>
       <c r="AO31" s="49" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="AP31" s="42" t="s">
         <v>72</v>
@@ -5039,10 +5100,10 @@
         <v>46170</v>
       </c>
       <c r="AT31" s="55" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AU31" s="54" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="AV31" s="24">
         <v>46170</v>
@@ -5051,7 +5112,7 @@
       <c r="AX31" s="24">
         <v>46170</v>
       </c>
-      <c r="AY31" s="62"/>
+      <c r="AY31" s="59"/>
       <c r="AZ31" s="3"/>
       <c r="BA31" s="3"/>
       <c r="BB31" s="1"/>
@@ -5151,7 +5212,7 @@
       </c>
       <c r="AK32" s="30"/>
       <c r="AL32" s="49" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AM32" s="3"/>
       <c r="AN32" s="37"/>
@@ -5160,7 +5221,7 @@
         <v>72</v>
       </c>
       <c r="AQ32" s="49" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="AR32" s="51"/>
       <c r="AS32" s="24">
@@ -5176,7 +5237,7 @@
       <c r="BA32" s="3"/>
       <c r="BB32" s="1"/>
     </row>
-    <row r="33" spans="1:54" ht="105">
+    <row r="33" spans="1:54" ht="270">
       <c r="A33" s="2">
         <v>30</v>
       </c>
@@ -5275,14 +5336,14 @@
       </c>
       <c r="AK33" s="30"/>
       <c r="AL33" s="37"/>
-      <c r="AM33" s="41" t="s">
-        <v>110</v>
+      <c r="AM33" s="57" t="s">
+        <v>145</v>
       </c>
       <c r="AN33" s="24">
         <v>46149</v>
       </c>
-      <c r="AO33" s="41" t="s">
-        <v>119</v>
+      <c r="AO33" s="57" t="s">
+        <v>112</v>
       </c>
       <c r="AP33" s="42" t="s">
         <v>72</v>
@@ -5297,11 +5358,17 @@
         <v>46170</v>
       </c>
       <c r="AT33" s="30"/>
-      <c r="AU33" s="3"/>
-      <c r="AV33" s="3"/>
-      <c r="AW33" s="3"/>
-      <c r="AX33" s="3"/>
-      <c r="AY33" s="3"/>
+      <c r="AU33" s="57" t="s">
+        <v>144</v>
+      </c>
+      <c r="AV33" s="24">
+        <v>46177</v>
+      </c>
+      <c r="AW33" s="57"/>
+      <c r="AX33" s="24">
+        <v>46177</v>
+      </c>
+      <c r="AY33" s="59"/>
       <c r="AZ33" s="3"/>
       <c r="BA33" s="3"/>
       <c r="BB33" s="1"/>
@@ -5404,8 +5471,8 @@
       <c r="AK34" s="43">
         <v>46135</v>
       </c>
-      <c r="AL34" s="63" t="s">
-        <v>138</v>
+      <c r="AL34" s="60" t="s">
+        <v>135</v>
       </c>
       <c r="AM34" s="5" t="s">
         <v>101</v>
@@ -5414,7 +5481,7 @@
         <v>46156</v>
       </c>
       <c r="AO34" s="48" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AP34" s="30"/>
       <c r="AQ34" s="3"/>
@@ -5424,7 +5491,7 @@
       </c>
       <c r="AT34" s="30"/>
       <c r="AU34" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="AV34" s="24">
         <v>46156</v>
@@ -5433,7 +5500,7 @@
       <c r="AX34" s="24">
         <v>46156</v>
       </c>
-      <c r="AY34" s="62"/>
+      <c r="AY34" s="59"/>
       <c r="AZ34" s="3"/>
       <c r="BA34" s="3"/>
       <c r="BB34" s="1"/>
@@ -6000,56 +6067,56 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="57"/>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="57"/>
-      <c r="R1" s="57"/>
-      <c r="S1" s="57"/>
-      <c r="T1" s="57"/>
-      <c r="U1" s="57"/>
-      <c r="V1" s="57"/>
-      <c r="W1" s="57"/>
-      <c r="X1" s="57"/>
-      <c r="Y1" s="57"/>
-      <c r="Z1" s="57"/>
-      <c r="AA1" s="57"/>
-      <c r="AB1" s="57"/>
-      <c r="AC1" s="57"/>
-      <c r="AD1" s="57"/>
-      <c r="AE1" s="57"/>
-      <c r="AF1" s="57"/>
-      <c r="AG1" s="57"/>
-      <c r="AH1" s="57"/>
-      <c r="AI1" s="57"/>
-      <c r="AJ1" s="57"/>
-      <c r="AK1" s="57"/>
-      <c r="AL1" s="57"/>
-      <c r="AM1" s="57"/>
-      <c r="AN1" s="57"/>
-      <c r="AO1" s="57"/>
-      <c r="AP1" s="57"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="62"/>
+      <c r="Q1" s="62"/>
+      <c r="R1" s="62"/>
+      <c r="S1" s="62"/>
+      <c r="T1" s="62"/>
+      <c r="U1" s="62"/>
+      <c r="V1" s="62"/>
+      <c r="W1" s="62"/>
+      <c r="X1" s="62"/>
+      <c r="Y1" s="62"/>
+      <c r="Z1" s="62"/>
+      <c r="AA1" s="62"/>
+      <c r="AB1" s="62"/>
+      <c r="AC1" s="62"/>
+      <c r="AD1" s="62"/>
+      <c r="AE1" s="62"/>
+      <c r="AF1" s="62"/>
+      <c r="AG1" s="62"/>
+      <c r="AH1" s="62"/>
+      <c r="AI1" s="62"/>
+      <c r="AJ1" s="62"/>
+      <c r="AK1" s="62"/>
+      <c r="AL1" s="62"/>
+      <c r="AM1" s="62"/>
+      <c r="AN1" s="62"/>
+      <c r="AO1" s="62"/>
+      <c r="AP1" s="62"/>
     </row>
     <row r="2" spans="1:42" ht="30">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="59"/>
+      <c r="B2" s="64"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -6478,142 +6545,142 @@
       <c r="AP10" s="1"/>
     </row>
     <row r="11" spans="1:42">
-      <c r="A11" s="59">
+      <c r="A11" s="64">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="59"/>
-      <c r="J11" s="59"/>
-      <c r="K11" s="59"/>
-      <c r="L11" s="60"/>
-      <c r="M11" s="60"/>
-      <c r="N11" s="60"/>
-      <c r="O11" s="60"/>
-      <c r="P11" s="60"/>
-      <c r="Q11" s="60"/>
-      <c r="R11" s="60"/>
-      <c r="S11" s="60"/>
-      <c r="T11" s="60"/>
-      <c r="U11" s="60"/>
-      <c r="V11" s="60"/>
-      <c r="W11" s="60"/>
-      <c r="X11" s="60"/>
-      <c r="Y11" s="60"/>
-      <c r="Z11" s="60"/>
-      <c r="AA11" s="60"/>
-      <c r="AB11" s="60"/>
-      <c r="AC11" s="60"/>
-      <c r="AD11" s="60"/>
-      <c r="AE11" s="60"/>
-      <c r="AF11" s="60"/>
-      <c r="AG11" s="60"/>
-      <c r="AH11" s="60"/>
-      <c r="AI11" s="60"/>
-      <c r="AJ11" s="60"/>
-      <c r="AK11" s="60"/>
-      <c r="AL11" s="60"/>
-      <c r="AM11" s="60"/>
-      <c r="AN11" s="60"/>
-      <c r="AO11" s="60"/>
-      <c r="AP11" s="57"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="64"/>
+      <c r="K11" s="64"/>
+      <c r="L11" s="65"/>
+      <c r="M11" s="65"/>
+      <c r="N11" s="65"/>
+      <c r="O11" s="65"/>
+      <c r="P11" s="65"/>
+      <c r="Q11" s="65"/>
+      <c r="R11" s="65"/>
+      <c r="S11" s="65"/>
+      <c r="T11" s="65"/>
+      <c r="U11" s="65"/>
+      <c r="V11" s="65"/>
+      <c r="W11" s="65"/>
+      <c r="X11" s="65"/>
+      <c r="Y11" s="65"/>
+      <c r="Z11" s="65"/>
+      <c r="AA11" s="65"/>
+      <c r="AB11" s="65"/>
+      <c r="AC11" s="65"/>
+      <c r="AD11" s="65"/>
+      <c r="AE11" s="65"/>
+      <c r="AF11" s="65"/>
+      <c r="AG11" s="65"/>
+      <c r="AH11" s="65"/>
+      <c r="AI11" s="65"/>
+      <c r="AJ11" s="65"/>
+      <c r="AK11" s="65"/>
+      <c r="AL11" s="65"/>
+      <c r="AM11" s="65"/>
+      <c r="AN11" s="65"/>
+      <c r="AO11" s="65"/>
+      <c r="AP11" s="62"/>
     </row>
     <row r="12" spans="1:42">
-      <c r="A12" s="59"/>
+      <c r="A12" s="64"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="59"/>
-      <c r="D12" s="59"/>
-      <c r="E12" s="59"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="59"/>
-      <c r="I12" s="59"/>
-      <c r="J12" s="59"/>
-      <c r="K12" s="59"/>
-      <c r="L12" s="60"/>
-      <c r="M12" s="60"/>
-      <c r="N12" s="60"/>
-      <c r="O12" s="60"/>
-      <c r="P12" s="60"/>
-      <c r="Q12" s="60"/>
-      <c r="R12" s="60"/>
-      <c r="S12" s="60"/>
-      <c r="T12" s="60"/>
-      <c r="U12" s="60"/>
-      <c r="V12" s="60"/>
-      <c r="W12" s="60"/>
-      <c r="X12" s="60"/>
-      <c r="Y12" s="60"/>
-      <c r="Z12" s="60"/>
-      <c r="AA12" s="60"/>
-      <c r="AB12" s="60"/>
-      <c r="AC12" s="60"/>
-      <c r="AD12" s="60"/>
-      <c r="AE12" s="60"/>
-      <c r="AF12" s="60"/>
-      <c r="AG12" s="60"/>
-      <c r="AH12" s="60"/>
-      <c r="AI12" s="60"/>
-      <c r="AJ12" s="60"/>
-      <c r="AK12" s="60"/>
-      <c r="AL12" s="60"/>
-      <c r="AM12" s="60"/>
-      <c r="AN12" s="60"/>
-      <c r="AO12" s="60"/>
-      <c r="AP12" s="57"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="64"/>
+      <c r="K12" s="64"/>
+      <c r="L12" s="65"/>
+      <c r="M12" s="65"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="65"/>
+      <c r="P12" s="65"/>
+      <c r="Q12" s="65"/>
+      <c r="R12" s="65"/>
+      <c r="S12" s="65"/>
+      <c r="T12" s="65"/>
+      <c r="U12" s="65"/>
+      <c r="V12" s="65"/>
+      <c r="W12" s="65"/>
+      <c r="X12" s="65"/>
+      <c r="Y12" s="65"/>
+      <c r="Z12" s="65"/>
+      <c r="AA12" s="65"/>
+      <c r="AB12" s="65"/>
+      <c r="AC12" s="65"/>
+      <c r="AD12" s="65"/>
+      <c r="AE12" s="65"/>
+      <c r="AF12" s="65"/>
+      <c r="AG12" s="65"/>
+      <c r="AH12" s="65"/>
+      <c r="AI12" s="65"/>
+      <c r="AJ12" s="65"/>
+      <c r="AK12" s="65"/>
+      <c r="AL12" s="65"/>
+      <c r="AM12" s="65"/>
+      <c r="AN12" s="65"/>
+      <c r="AO12" s="65"/>
+      <c r="AP12" s="62"/>
     </row>
     <row r="13" spans="1:42">
-      <c r="A13" s="59"/>
+      <c r="A13" s="64"/>
       <c r="B13" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="59"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="59"/>
-      <c r="I13" s="59"/>
-      <c r="J13" s="59"/>
-      <c r="K13" s="59"/>
-      <c r="L13" s="60"/>
-      <c r="M13" s="60"/>
-      <c r="N13" s="60"/>
-      <c r="O13" s="60"/>
-      <c r="P13" s="60"/>
-      <c r="Q13" s="60"/>
-      <c r="R13" s="60"/>
-      <c r="S13" s="60"/>
-      <c r="T13" s="60"/>
-      <c r="U13" s="60"/>
-      <c r="V13" s="60"/>
-      <c r="W13" s="60"/>
-      <c r="X13" s="60"/>
-      <c r="Y13" s="60"/>
-      <c r="Z13" s="60"/>
-      <c r="AA13" s="60"/>
-      <c r="AB13" s="60"/>
-      <c r="AC13" s="60"/>
-      <c r="AD13" s="60"/>
-      <c r="AE13" s="60"/>
-      <c r="AF13" s="60"/>
-      <c r="AG13" s="60"/>
-      <c r="AH13" s="60"/>
-      <c r="AI13" s="60"/>
-      <c r="AJ13" s="60"/>
-      <c r="AK13" s="60"/>
-      <c r="AL13" s="60"/>
-      <c r="AM13" s="60"/>
-      <c r="AN13" s="60"/>
-      <c r="AO13" s="60"/>
-      <c r="AP13" s="57"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="64"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="64"/>
+      <c r="J13" s="64"/>
+      <c r="K13" s="64"/>
+      <c r="L13" s="65"/>
+      <c r="M13" s="65"/>
+      <c r="N13" s="65"/>
+      <c r="O13" s="65"/>
+      <c r="P13" s="65"/>
+      <c r="Q13" s="65"/>
+      <c r="R13" s="65"/>
+      <c r="S13" s="65"/>
+      <c r="T13" s="65"/>
+      <c r="U13" s="65"/>
+      <c r="V13" s="65"/>
+      <c r="W13" s="65"/>
+      <c r="X13" s="65"/>
+      <c r="Y13" s="65"/>
+      <c r="Z13" s="65"/>
+      <c r="AA13" s="65"/>
+      <c r="AB13" s="65"/>
+      <c r="AC13" s="65"/>
+      <c r="AD13" s="65"/>
+      <c r="AE13" s="65"/>
+      <c r="AF13" s="65"/>
+      <c r="AG13" s="65"/>
+      <c r="AH13" s="65"/>
+      <c r="AI13" s="65"/>
+      <c r="AJ13" s="65"/>
+      <c r="AK13" s="65"/>
+      <c r="AL13" s="65"/>
+      <c r="AM13" s="65"/>
+      <c r="AN13" s="65"/>
+      <c r="AO13" s="65"/>
+      <c r="AP13" s="62"/>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" s="2">
@@ -7769,6 +7836,33 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="AO11:AO13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
+    <mergeCell ref="AN11:AN13"/>
+    <mergeCell ref="AE11:AE13"/>
+    <mergeCell ref="AF11:AF13"/>
+    <mergeCell ref="AG11:AG13"/>
+    <mergeCell ref="AH11:AH13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="Z11:Z13"/>
+    <mergeCell ref="AA11:AA13"/>
+    <mergeCell ref="AB11:AB13"/>
+    <mergeCell ref="AC11:AC13"/>
+    <mergeCell ref="AD11:AD13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="V11:V13"/>
+    <mergeCell ref="W11:W13"/>
+    <mergeCell ref="X11:X13"/>
+    <mergeCell ref="Y11:Y13"/>
+    <mergeCell ref="P11:P13"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="T11:T13"/>
     <mergeCell ref="A1:AP1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A11:A13"/>
@@ -7785,33 +7879,6 @@
     <mergeCell ref="M11:M13"/>
     <mergeCell ref="N11:N13"/>
     <mergeCell ref="O11:O13"/>
-    <mergeCell ref="P11:P13"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="T11:T13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="V11:V13"/>
-    <mergeCell ref="W11:W13"/>
-    <mergeCell ref="X11:X13"/>
-    <mergeCell ref="Y11:Y13"/>
-    <mergeCell ref="Z11:Z13"/>
-    <mergeCell ref="AA11:AA13"/>
-    <mergeCell ref="AB11:AB13"/>
-    <mergeCell ref="AC11:AC13"/>
-    <mergeCell ref="AD11:AD13"/>
-    <mergeCell ref="AE11:AE13"/>
-    <mergeCell ref="AF11:AF13"/>
-    <mergeCell ref="AG11:AG13"/>
-    <mergeCell ref="AH11:AH13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="AO11:AO13"/>
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="AN11:AN13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ТКИ-341_Реверс_Инжиниринг.xlsx
+++ b/ТКИ-341_Реверс_Инжиниринг.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\Reverse_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F85F0881-B1DD-43FE-BABD-AF65AD0C94AA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB54ECFD-6DAD-49D0-9BA5-18E82B49B4CA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="153">
   <si>
     <t>ВЕДОМОСТЬ ПОСЕЩАЕМОСТИ ЗАНЯТИЙ СТУДЕНТАМИ ГРУППЫ ТКИ "Компьютерная безопасность" ИТТСУ РУТ (МИИТ)</t>
   </si>
@@ -513,6 +513,15 @@
   </si>
   <si>
     <t>GitLab KG не запустился даже после консультаций</t>
+  </si>
+  <si>
+    <t>CodeGraph</t>
+  </si>
+  <si>
+    <t>площадь или периметр треугольника (Беймель)</t>
+  </si>
+  <si>
+    <t>калькулятор</t>
   </si>
 </sst>
 </file>
@@ -652,7 +661,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -812,6 +821,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -822,6 +834,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1133,68 +1148,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="14.45" customHeight="1">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="62"/>
-      <c r="S1" s="62"/>
-      <c r="T1" s="62"/>
-      <c r="U1" s="62"/>
-      <c r="V1" s="62"/>
-      <c r="W1" s="62"/>
-      <c r="X1" s="62"/>
-      <c r="Y1" s="62"/>
-      <c r="Z1" s="62"/>
-      <c r="AA1" s="62"/>
-      <c r="AB1" s="62"/>
-      <c r="AC1" s="62"/>
-      <c r="AD1" s="62"/>
-      <c r="AE1" s="62"/>
-      <c r="AF1" s="62"/>
-      <c r="AG1" s="62"/>
-      <c r="AH1" s="62"/>
-      <c r="AI1" s="62"/>
-      <c r="AJ1" s="62"/>
-      <c r="AK1" s="62"/>
-      <c r="AL1" s="62"/>
-      <c r="AM1" s="62"/>
-      <c r="AN1" s="62"/>
-      <c r="AO1" s="62"/>
-      <c r="AP1" s="62"/>
-      <c r="AQ1" s="62"/>
-      <c r="AR1" s="62"/>
-      <c r="AS1" s="62"/>
-      <c r="AT1" s="62"/>
-      <c r="AU1" s="62"/>
-      <c r="AV1" s="62"/>
-      <c r="AW1" s="62"/>
-      <c r="AX1" s="62"/>
-      <c r="AY1" s="62"/>
-      <c r="AZ1" s="62"/>
-      <c r="BA1" s="62"/>
-      <c r="BB1" s="62"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
+      <c r="R1" s="63"/>
+      <c r="S1" s="63"/>
+      <c r="T1" s="63"/>
+      <c r="U1" s="63"/>
+      <c r="V1" s="63"/>
+      <c r="W1" s="63"/>
+      <c r="X1" s="63"/>
+      <c r="Y1" s="63"/>
+      <c r="Z1" s="63"/>
+      <c r="AA1" s="63"/>
+      <c r="AB1" s="63"/>
+      <c r="AC1" s="63"/>
+      <c r="AD1" s="63"/>
+      <c r="AE1" s="63"/>
+      <c r="AF1" s="63"/>
+      <c r="AG1" s="63"/>
+      <c r="AH1" s="63"/>
+      <c r="AI1" s="63"/>
+      <c r="AJ1" s="63"/>
+      <c r="AK1" s="63"/>
+      <c r="AL1" s="63"/>
+      <c r="AM1" s="63"/>
+      <c r="AN1" s="63"/>
+      <c r="AO1" s="63"/>
+      <c r="AP1" s="63"/>
+      <c r="AQ1" s="63"/>
+      <c r="AR1" s="63"/>
+      <c r="AS1" s="63"/>
+      <c r="AT1" s="63"/>
+      <c r="AU1" s="63"/>
+      <c r="AV1" s="63"/>
+      <c r="AW1" s="63"/>
+      <c r="AX1" s="63"/>
+      <c r="AY1" s="63"/>
+      <c r="AZ1" s="63"/>
+      <c r="BA1" s="63"/>
+      <c r="BB1" s="63"/>
     </row>
     <row r="2" spans="1:54" ht="27.6" customHeight="1">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="64"/>
+      <c r="B2" s="65"/>
       <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
@@ -2022,13 +2037,17 @@
         <v>46100</v>
       </c>
       <c r="AD8" s="3"/>
-      <c r="AE8" s="3"/>
+      <c r="AE8" s="24">
+        <v>46177</v>
+      </c>
       <c r="AF8" s="3"/>
       <c r="AG8" s="24">
         <v>46135</v>
       </c>
       <c r="AH8" s="3"/>
-      <c r="AI8" s="3"/>
+      <c r="AI8" s="24">
+        <v>46177</v>
+      </c>
       <c r="AJ8" s="3">
         <v>3</v>
       </c>
@@ -2039,9 +2058,7 @@
       <c r="AM8" s="3">
         <v>17</v>
       </c>
-      <c r="AN8" s="24">
-        <v>46135</v>
-      </c>
+      <c r="AN8" s="62"/>
       <c r="AP8" s="42" t="s">
         <v>72</v>
       </c>
@@ -2053,7 +2070,12 @@
       </c>
       <c r="AS8" s="3"/>
       <c r="AT8" s="30"/>
-      <c r="AV8" s="3"/>
+      <c r="AU8" s="62" t="s">
+        <v>150</v>
+      </c>
+      <c r="AV8" s="24">
+        <v>46177</v>
+      </c>
       <c r="AW8" s="3"/>
       <c r="AX8" s="3"/>
       <c r="AY8" s="3"/>
@@ -2832,7 +2854,9 @@
         <v>16</v>
       </c>
       <c r="AB14" s="3"/>
-      <c r="AC14" s="3"/>
+      <c r="AC14" s="24">
+        <v>46177</v>
+      </c>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3"/>
       <c r="AF14" s="3"/>
@@ -3274,7 +3298,7 @@
       <c r="AX17" s="24">
         <v>46149</v>
       </c>
-      <c r="AY17" s="3"/>
+      <c r="AY17" s="59"/>
       <c r="AZ17" s="3"/>
       <c r="BA17" s="3"/>
       <c r="BB17" s="1"/>
@@ -3645,7 +3669,9 @@
       <c r="AM20" s="3">
         <v>6</v>
       </c>
-      <c r="AN20" s="37"/>
+      <c r="AN20" s="24">
+        <v>46118</v>
+      </c>
       <c r="AO20" s="37" t="s">
         <v>107</v>
       </c>
@@ -3667,7 +3693,7 @@
       <c r="BA20" s="3"/>
       <c r="BB20" s="1"/>
     </row>
-    <row r="21" spans="1:54" ht="90">
+    <row r="21" spans="1:54" ht="120">
       <c r="A21" s="2">
         <v>18</v>
       </c>
@@ -3752,7 +3778,9 @@
         <v>46100</v>
       </c>
       <c r="AD21" s="3"/>
-      <c r="AE21" s="3"/>
+      <c r="AE21" s="24">
+        <v>46177</v>
+      </c>
       <c r="AF21" s="3"/>
       <c r="AG21" s="24">
         <v>46135</v>
@@ -3766,19 +3794,21 @@
       </c>
       <c r="AK21" s="30"/>
       <c r="AM21" s="3"/>
-      <c r="AN21" s="24">
-        <v>46135</v>
-      </c>
-      <c r="AO21" s="37" t="s">
-        <v>103</v>
+      <c r="AN21" s="62"/>
+      <c r="AO21" s="49" t="s">
+        <v>151</v>
       </c>
       <c r="AP21" s="30"/>
       <c r="AQ21" s="3"/>
       <c r="AR21" s="3"/>
       <c r="AS21" s="3"/>
       <c r="AT21" s="30"/>
-      <c r="AU21" s="3"/>
-      <c r="AV21" s="3"/>
+      <c r="AU21" s="62" t="s">
+        <v>150</v>
+      </c>
+      <c r="AV21" s="24">
+        <v>46177</v>
+      </c>
       <c r="AW21" s="3"/>
       <c r="AX21" s="3"/>
       <c r="AY21" s="3"/>
@@ -4332,7 +4362,9 @@
       <c r="C26" s="9">
         <v>18</v>
       </c>
-      <c r="D26" s="9"/>
+      <c r="D26" s="67" t="s">
+        <v>152</v>
+      </c>
       <c r="E26" s="9" t="s">
         <v>17</v>
       </c>
@@ -4401,13 +4433,13 @@
         <v>16</v>
       </c>
       <c r="AB26" s="3"/>
-      <c r="AC26" s="3"/>
+      <c r="AC26" s="33"/>
       <c r="AD26" s="3"/>
-      <c r="AE26" s="3"/>
+      <c r="AE26" s="33"/>
       <c r="AF26" s="3"/>
-      <c r="AG26" s="3"/>
+      <c r="AG26" s="33"/>
       <c r="AH26" s="3"/>
-      <c r="AI26" s="3"/>
+      <c r="AI26" s="33"/>
       <c r="AJ26" s="3">
         <v>0</v>
       </c>
@@ -5204,31 +5236,43 @@
         <v>46170</v>
       </c>
       <c r="AF32" s="3"/>
-      <c r="AG32" s="3"/>
-      <c r="AH32" s="3"/>
-      <c r="AI32" s="3"/>
-      <c r="AJ32" s="3">
+      <c r="AG32" s="24">
+        <v>46177</v>
+      </c>
+      <c r="AH32" s="62"/>
+      <c r="AI32" s="24">
+        <v>46177</v>
+      </c>
+      <c r="AJ32" s="62">
         <v>2</v>
       </c>
       <c r="AK32" s="30"/>
       <c r="AL32" s="49" t="s">
+        <v>137</v>
+      </c>
+      <c r="AM32" s="62">
+        <v>2</v>
+      </c>
+      <c r="AN32" s="24">
+        <v>46177</v>
+      </c>
+      <c r="AO32" s="49" t="s">
         <v>126</v>
       </c>
-      <c r="AM32" s="3"/>
-      <c r="AN32" s="37"/>
-      <c r="AO32" s="37"/>
       <c r="AP32" s="42" t="s">
         <v>72</v>
       </c>
       <c r="AQ32" s="49" t="s">
         <v>128</v>
       </c>
-      <c r="AR32" s="51"/>
+      <c r="AR32" s="62"/>
       <c r="AS32" s="24">
         <v>46170</v>
       </c>
       <c r="AT32" s="30"/>
-      <c r="AU32" s="3"/>
+      <c r="AU32" s="49" t="s">
+        <v>148</v>
+      </c>
       <c r="AV32" s="3"/>
       <c r="AW32" s="3"/>
       <c r="AX32" s="3"/>
@@ -5582,7 +5626,9 @@
         <v>17</v>
       </c>
       <c r="AB35" s="3"/>
-      <c r="AC35" s="3"/>
+      <c r="AC35" s="24">
+        <v>46177</v>
+      </c>
       <c r="AD35" s="3"/>
       <c r="AE35" s="3"/>
       <c r="AF35" s="3"/>
@@ -6067,56 +6113,56 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="62"/>
-      <c r="S1" s="62"/>
-      <c r="T1" s="62"/>
-      <c r="U1" s="62"/>
-      <c r="V1" s="62"/>
-      <c r="W1" s="62"/>
-      <c r="X1" s="62"/>
-      <c r="Y1" s="62"/>
-      <c r="Z1" s="62"/>
-      <c r="AA1" s="62"/>
-      <c r="AB1" s="62"/>
-      <c r="AC1" s="62"/>
-      <c r="AD1" s="62"/>
-      <c r="AE1" s="62"/>
-      <c r="AF1" s="62"/>
-      <c r="AG1" s="62"/>
-      <c r="AH1" s="62"/>
-      <c r="AI1" s="62"/>
-      <c r="AJ1" s="62"/>
-      <c r="AK1" s="62"/>
-      <c r="AL1" s="62"/>
-      <c r="AM1" s="62"/>
-      <c r="AN1" s="62"/>
-      <c r="AO1" s="62"/>
-      <c r="AP1" s="62"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
+      <c r="R1" s="63"/>
+      <c r="S1" s="63"/>
+      <c r="T1" s="63"/>
+      <c r="U1" s="63"/>
+      <c r="V1" s="63"/>
+      <c r="W1" s="63"/>
+      <c r="X1" s="63"/>
+      <c r="Y1" s="63"/>
+      <c r="Z1" s="63"/>
+      <c r="AA1" s="63"/>
+      <c r="AB1" s="63"/>
+      <c r="AC1" s="63"/>
+      <c r="AD1" s="63"/>
+      <c r="AE1" s="63"/>
+      <c r="AF1" s="63"/>
+      <c r="AG1" s="63"/>
+      <c r="AH1" s="63"/>
+      <c r="AI1" s="63"/>
+      <c r="AJ1" s="63"/>
+      <c r="AK1" s="63"/>
+      <c r="AL1" s="63"/>
+      <c r="AM1" s="63"/>
+      <c r="AN1" s="63"/>
+      <c r="AO1" s="63"/>
+      <c r="AP1" s="63"/>
     </row>
     <row r="2" spans="1:42" ht="30">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="64"/>
+      <c r="B2" s="65"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -6545,142 +6591,142 @@
       <c r="AP10" s="1"/>
     </row>
     <row r="11" spans="1:42">
-      <c r="A11" s="64">
+      <c r="A11" s="65">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C11" s="64"/>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="64"/>
-      <c r="K11" s="64"/>
-      <c r="L11" s="65"/>
-      <c r="M11" s="65"/>
-      <c r="N11" s="65"/>
-      <c r="O11" s="65"/>
-      <c r="P11" s="65"/>
-      <c r="Q11" s="65"/>
-      <c r="R11" s="65"/>
-      <c r="S11" s="65"/>
-      <c r="T11" s="65"/>
-      <c r="U11" s="65"/>
-      <c r="V11" s="65"/>
-      <c r="W11" s="65"/>
-      <c r="X11" s="65"/>
-      <c r="Y11" s="65"/>
-      <c r="Z11" s="65"/>
-      <c r="AA11" s="65"/>
-      <c r="AB11" s="65"/>
-      <c r="AC11" s="65"/>
-      <c r="AD11" s="65"/>
-      <c r="AE11" s="65"/>
-      <c r="AF11" s="65"/>
-      <c r="AG11" s="65"/>
-      <c r="AH11" s="65"/>
-      <c r="AI11" s="65"/>
-      <c r="AJ11" s="65"/>
-      <c r="AK11" s="65"/>
-      <c r="AL11" s="65"/>
-      <c r="AM11" s="65"/>
-      <c r="AN11" s="65"/>
-      <c r="AO11" s="65"/>
-      <c r="AP11" s="62"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="65"/>
+      <c r="J11" s="65"/>
+      <c r="K11" s="65"/>
+      <c r="L11" s="66"/>
+      <c r="M11" s="66"/>
+      <c r="N11" s="66"/>
+      <c r="O11" s="66"/>
+      <c r="P11" s="66"/>
+      <c r="Q11" s="66"/>
+      <c r="R11" s="66"/>
+      <c r="S11" s="66"/>
+      <c r="T11" s="66"/>
+      <c r="U11" s="66"/>
+      <c r="V11" s="66"/>
+      <c r="W11" s="66"/>
+      <c r="X11" s="66"/>
+      <c r="Y11" s="66"/>
+      <c r="Z11" s="66"/>
+      <c r="AA11" s="66"/>
+      <c r="AB11" s="66"/>
+      <c r="AC11" s="66"/>
+      <c r="AD11" s="66"/>
+      <c r="AE11" s="66"/>
+      <c r="AF11" s="66"/>
+      <c r="AG11" s="66"/>
+      <c r="AH11" s="66"/>
+      <c r="AI11" s="66"/>
+      <c r="AJ11" s="66"/>
+      <c r="AK11" s="66"/>
+      <c r="AL11" s="66"/>
+      <c r="AM11" s="66"/>
+      <c r="AN11" s="66"/>
+      <c r="AO11" s="66"/>
+      <c r="AP11" s="63"/>
     </row>
     <row r="12" spans="1:42">
-      <c r="A12" s="64"/>
+      <c r="A12" s="65"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="64"/>
-      <c r="K12" s="64"/>
-      <c r="L12" s="65"/>
-      <c r="M12" s="65"/>
-      <c r="N12" s="65"/>
-      <c r="O12" s="65"/>
-      <c r="P12" s="65"/>
-      <c r="Q12" s="65"/>
-      <c r="R12" s="65"/>
-      <c r="S12" s="65"/>
-      <c r="T12" s="65"/>
-      <c r="U12" s="65"/>
-      <c r="V12" s="65"/>
-      <c r="W12" s="65"/>
-      <c r="X12" s="65"/>
-      <c r="Y12" s="65"/>
-      <c r="Z12" s="65"/>
-      <c r="AA12" s="65"/>
-      <c r="AB12" s="65"/>
-      <c r="AC12" s="65"/>
-      <c r="AD12" s="65"/>
-      <c r="AE12" s="65"/>
-      <c r="AF12" s="65"/>
-      <c r="AG12" s="65"/>
-      <c r="AH12" s="65"/>
-      <c r="AI12" s="65"/>
-      <c r="AJ12" s="65"/>
-      <c r="AK12" s="65"/>
-      <c r="AL12" s="65"/>
-      <c r="AM12" s="65"/>
-      <c r="AN12" s="65"/>
-      <c r="AO12" s="65"/>
-      <c r="AP12" s="62"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="66"/>
+      <c r="M12" s="66"/>
+      <c r="N12" s="66"/>
+      <c r="O12" s="66"/>
+      <c r="P12" s="66"/>
+      <c r="Q12" s="66"/>
+      <c r="R12" s="66"/>
+      <c r="S12" s="66"/>
+      <c r="T12" s="66"/>
+      <c r="U12" s="66"/>
+      <c r="V12" s="66"/>
+      <c r="W12" s="66"/>
+      <c r="X12" s="66"/>
+      <c r="Y12" s="66"/>
+      <c r="Z12" s="66"/>
+      <c r="AA12" s="66"/>
+      <c r="AB12" s="66"/>
+      <c r="AC12" s="66"/>
+      <c r="AD12" s="66"/>
+      <c r="AE12" s="66"/>
+      <c r="AF12" s="66"/>
+      <c r="AG12" s="66"/>
+      <c r="AH12" s="66"/>
+      <c r="AI12" s="66"/>
+      <c r="AJ12" s="66"/>
+      <c r="AK12" s="66"/>
+      <c r="AL12" s="66"/>
+      <c r="AM12" s="66"/>
+      <c r="AN12" s="66"/>
+      <c r="AO12" s="66"/>
+      <c r="AP12" s="63"/>
     </row>
     <row r="13" spans="1:42">
-      <c r="A13" s="64"/>
+      <c r="A13" s="65"/>
       <c r="B13" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="64"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="64"/>
-      <c r="J13" s="64"/>
-      <c r="K13" s="64"/>
-      <c r="L13" s="65"/>
-      <c r="M13" s="65"/>
-      <c r="N13" s="65"/>
-      <c r="O13" s="65"/>
-      <c r="P13" s="65"/>
-      <c r="Q13" s="65"/>
-      <c r="R13" s="65"/>
-      <c r="S13" s="65"/>
-      <c r="T13" s="65"/>
-      <c r="U13" s="65"/>
-      <c r="V13" s="65"/>
-      <c r="W13" s="65"/>
-      <c r="X13" s="65"/>
-      <c r="Y13" s="65"/>
-      <c r="Z13" s="65"/>
-      <c r="AA13" s="65"/>
-      <c r="AB13" s="65"/>
-      <c r="AC13" s="65"/>
-      <c r="AD13" s="65"/>
-      <c r="AE13" s="65"/>
-      <c r="AF13" s="65"/>
-      <c r="AG13" s="65"/>
-      <c r="AH13" s="65"/>
-      <c r="AI13" s="65"/>
-      <c r="AJ13" s="65"/>
-      <c r="AK13" s="65"/>
-      <c r="AL13" s="65"/>
-      <c r="AM13" s="65"/>
-      <c r="AN13" s="65"/>
-      <c r="AO13" s="65"/>
-      <c r="AP13" s="62"/>
+      <c r="C13" s="65"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="65"/>
+      <c r="K13" s="65"/>
+      <c r="L13" s="66"/>
+      <c r="M13" s="66"/>
+      <c r="N13" s="66"/>
+      <c r="O13" s="66"/>
+      <c r="P13" s="66"/>
+      <c r="Q13" s="66"/>
+      <c r="R13" s="66"/>
+      <c r="S13" s="66"/>
+      <c r="T13" s="66"/>
+      <c r="U13" s="66"/>
+      <c r="V13" s="66"/>
+      <c r="W13" s="66"/>
+      <c r="X13" s="66"/>
+      <c r="Y13" s="66"/>
+      <c r="Z13" s="66"/>
+      <c r="AA13" s="66"/>
+      <c r="AB13" s="66"/>
+      <c r="AC13" s="66"/>
+      <c r="AD13" s="66"/>
+      <c r="AE13" s="66"/>
+      <c r="AF13" s="66"/>
+      <c r="AG13" s="66"/>
+      <c r="AH13" s="66"/>
+      <c r="AI13" s="66"/>
+      <c r="AJ13" s="66"/>
+      <c r="AK13" s="66"/>
+      <c r="AL13" s="66"/>
+      <c r="AM13" s="66"/>
+      <c r="AN13" s="66"/>
+      <c r="AO13" s="66"/>
+      <c r="AP13" s="63"/>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" s="2">
@@ -7836,33 +7882,6 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="AO11:AO13"/>
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AL11:AL13"/>
-    <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="AN11:AN13"/>
-    <mergeCell ref="AE11:AE13"/>
-    <mergeCell ref="AF11:AF13"/>
-    <mergeCell ref="AG11:AG13"/>
-    <mergeCell ref="AH11:AH13"/>
-    <mergeCell ref="AI11:AI13"/>
-    <mergeCell ref="Z11:Z13"/>
-    <mergeCell ref="AA11:AA13"/>
-    <mergeCell ref="AB11:AB13"/>
-    <mergeCell ref="AC11:AC13"/>
-    <mergeCell ref="AD11:AD13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="V11:V13"/>
-    <mergeCell ref="W11:W13"/>
-    <mergeCell ref="X11:X13"/>
-    <mergeCell ref="Y11:Y13"/>
-    <mergeCell ref="P11:P13"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="T11:T13"/>
     <mergeCell ref="A1:AP1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A11:A13"/>
@@ -7879,6 +7898,33 @@
     <mergeCell ref="M11:M13"/>
     <mergeCell ref="N11:N13"/>
     <mergeCell ref="O11:O13"/>
+    <mergeCell ref="P11:P13"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="T11:T13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="V11:V13"/>
+    <mergeCell ref="W11:W13"/>
+    <mergeCell ref="X11:X13"/>
+    <mergeCell ref="Y11:Y13"/>
+    <mergeCell ref="Z11:Z13"/>
+    <mergeCell ref="AA11:AA13"/>
+    <mergeCell ref="AB11:AB13"/>
+    <mergeCell ref="AC11:AC13"/>
+    <mergeCell ref="AD11:AD13"/>
+    <mergeCell ref="AE11:AE13"/>
+    <mergeCell ref="AF11:AF13"/>
+    <mergeCell ref="AG11:AG13"/>
+    <mergeCell ref="AH11:AH13"/>
+    <mergeCell ref="AI11:AI13"/>
+    <mergeCell ref="AO11:AO13"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AL11:AL13"/>
+    <mergeCell ref="AM11:AM13"/>
+    <mergeCell ref="AN11:AN13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
